--- a/docs/executive-plan.xlsx
+++ b/docs/executive-plan.xlsx
@@ -11,10 +11,12 @@
     <sheet name="الدليل" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="منافذ البيع" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="المنافسون" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="الخطة التنفيذية" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="المستهدفات الربعية" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="المبادرات" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="المحطات" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="حصص السوق" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="التطبيقات والمنصات" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="الخطة التنفيذية" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="المستهدفات الربعية" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="المبادرات" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="المحطات" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="545">
   <si>
     <t xml:space="preserve">نموذج الخطة التنفيذية — الإدارة التجارية</t>
   </si>
@@ -259,420 +261,816 @@
     <t xml:space="preserve">المنفذ كامل غير مُفعّل</t>
   </si>
   <si>
+    <t xml:space="preserve">التطبيق والولاء — أفراد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">النقد (البديل) · ساسكو وقوستيشن (تطبيقات أفراد)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6% نقداً · ساسكو 653 محطة · قوستيشن 12 محطة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28% حصة التطبيق · 43 محطة بصفر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا نعرف من اشترى</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التسويق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منصات إنفاق الأساطيل — شركات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بترو آب · سيارة آب · Fleet Plus · واعي وكنترول (بطاقات)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بترو آب: 500 ألف مركبة · 10 آلاف منشأة · 5,000 محطة قبول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خارج الشبكة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وسيط يفصلنا عن العميل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المساحات الإعلانية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شركات + وسطاء</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العربية للإعلان الخارجي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62–66% حصة · 4,942 لوحة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صفر إيراد موثّق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355 موقعاً بلا إيراد إعلاني</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الامتياز والتوريد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأسرع في ضمّ المحطات المستقلة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">231 محطة في المنظومة · 31 مكتملة الهوية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200 محطة علامتها غير مُسلَّمة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الشحن الكهربائي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVIQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,000+ شاحن في 1,000 موقع · شراكة PIF والسعودية للكهرباء</t>
+  </si>
+  <si>
+    <t xml:space="preserve">النافذة تُغلق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الديزل بالجملة والتوصيل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الدريس · بترومين</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يملكان أسطول النقل — وهو حاجز الدخول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محطات ديزل عالية بلا توزيع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الخدمات المالية والخزائن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">البنوك (طرف مقابل لا منافس)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بدائل مواقع كثيرة أمامها</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 مواقع من 124 محطة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118 محطة بلا خدمة مالية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المساحات اللوجستية والمواقف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مشغّلو المواقف والمستودعات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سوق مجزّأ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">غير مُستثمر · مواقع تصل 5,420 م²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أرض مملوكة بلا إيراد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الإجمالي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">القراءة الأفقية: عمود «شركات» شبه فارغ — وهذه هي الفجوة كلها. وثلاث خلايا حاسمة في عمود الوسطاء نحن غائبون عنها.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">القاعدة الحاكمة: القناة التي لا نملك فيها العلاقة تُدرّ حجماً اليوم وتُفقدنا التسعير غداً.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أضعف منافذنا هي أقلّها منافسة — التأجير والإعلان والزينة: لا مسيطر فيها، ونحن غائبون.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحليل المنافسين</t>
+  </si>
+  <si>
+    <t xml:space="preserve">من يسيطر على كل منفذ — وبأي مصدر قوة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المنافس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">النوع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحجم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المنافذ التي يسيطر عليها</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مصدر قوته</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نقطة ضعفه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الردّ المقترح</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مشغّل محطات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,300 محطة · 17.11% حصة · ربح صافٍ 421.8 مليون ريال 2025 (+22%) · +69 محطة في الربع الرابع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الوقود · الامتياز والتوريد · الديزل بالجملة · البطاقات (واعي)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحجم والانتشار وسرعة ضمّ المستقلين · واعي يثبّت الأسطول بحاجز تقني</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أدواته محصورة في شبكته — واعي لا يعمل خارج محطات الدريس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا ننافسه على اللتر بل على الربح لكل زيارة — ونستحوذ على المنافذ التي لا يلعب فيها</t>
+  </si>
+  <si>
+    <t xml:space="preserve">argaam.com — نتائج 2025 وحصص الربع الرابع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بترو آب (PetroApp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منصة وساطة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500,000+ مركبة · 10,000 عميل شركة · 5,000 محطة قبول · تمويل 50 مليون دولار بقيادة جدوى</t>
+  </si>
+  <si>
+    <t xml:space="preserve">البطاقات ومنصات الإنفاق · خدمات السيارات (توسّع) · الإكسسوارات (إطارات وبطاريات)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يملك العلاقة مع المنشأة والبيانات وقرار توجيه الحجم — بلا محطة واحدة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا يملك أصلاً مادياً — يعتمد كلياً على شبكة قبول المحطات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المساران معاً: عقود مباشرة لمن نصله بمندوب، والتقاط الباقي عبر المنصة بعمولة — والحساب يُعاد كل ربع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fintechfutures.com · petroapp.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سلسلة خدمة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كثافة الفروع والعلامة في الزيوت والصيانة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا يملك حركة المحطة — يشتريها منّا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نحوّل الـ39 محطة من إيجار إلى نسبة من الخدمة، ونفتح عقود أساطيل دورية في الـ85 الشاغرة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحليل داخلي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وكالة إعلان</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62–66% حصة السوق · 4,942 لوحة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">علاقات المعلنين الوطنيين وحصرية المواقع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يشتري مواقع نحن أصحابها — الأصل بيدنا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تأجير الشبكة للوطني عبر وكالة بحد أدنى مضمون + بيع مباشر للمعلن المحلي والمستأجر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بنية تحتية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,000+ شاحن في 1,000 موقع · شراكة صندوق الاستثمارات العامة والسعودية للكهرباء</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دعم سيادي ورأس مال بنية تحتية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يحتاج مواقع على شرايين الحركة — ونحن نملك 355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استضافة بعقد موقع لا استثمار في الشواحن — المنتج هو زمن الانتظار لا الشحن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pif.gov.sa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ساسكو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">653 محطة · 8.59% حصة · +23 محطة في الربع الرابع · خطة 100 محطة سنوياً · استحوذت على نفط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الوقود · البطاقات (كنترول) · تطبيق الأفراد · الامتياز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الوحيد الذي يجمع تطبيق أفراد ناضجاً + كنترول للشركات · نقاط تُستبدل في مطاعم محطاته</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أصغر شبكة من الدريس · أدواته محصورة في شبكته</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نقلّده في ربط التطبيق بالمستأجرين — وهو ما يجعل النقاط ذات قيمة فعلية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sasco.com.sa · argaam.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سيارة آب (SyarahApp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منصة وساطة + شبكة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,500+ محطة قبول · NFC · استُحوذ عليها يوليو 2026 من مجموعة تشغّل 1,790+ محطة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منصات إنفاق الأساطيل · الوقود</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بعد الصفقة صارت منصة + شبكة معاً — نموذج الدريس بتقنية أحدث وشبكة قبول مفتوحة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الجهة المستحوذة وقيمة الصفقة غير معلنتين · ورقم 1,790 غير موضّح الأساس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">متابعة عاجلة — لو صحّ الرقم فهو أكبر مشغّل في المملكة، وقد يغيّر ترتيب السوق كله</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dealroom.co · entarabi.com — يوليو 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قوستيشن (GoStation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مشغّل صغير + تطبيق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 محطة · المنطقة الشرقية (الخبر) · شركة هلا السعودية للخدمات البترولية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تطبيق الأفراد (محلياً)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منتج رقمي ناضج: محفظة لكل مركبة · ولاء متدرج · توصيل وقود</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 محطة — لا وزن سوقي (0.16%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ليس تهديداً حجمياً بل مرآة: 12 محطة ومنتجه الرقمي أنضج من منتجنا بـ355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gostation.net · Google Play</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fleet Plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,000+ مزوّد خدمة · وقود وإطارات وزيوت وبطاريات وغسيل بفوترة موحدة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">البطاقات ومنصات الإنفاق · خدمات السيارات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حزمة موحّدة ومسارات اعتماد للمنشأة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا يملك أصولاً — نفس ضعف بترو آب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نفس قاعدة بترو آب: عمولة المنصة لكل لتر مقابل تكلفة قوة البيع المباشرة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">النقد ومدى وآبل باي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بديل سلوكي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6% نقد · 26.1% شبكة من مبيعاتنا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التطبيق والولاء</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا احتكاك — الدفع بلمسة بلا تطبيق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا يقدّم للعميل أي ميزة تتجاوز الدفع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التطبيق يجب أن يبيع ما لا يُباع بغيره: سعر عضوية · طابور أسرع · رصيد مُهدى · عرض من المستأجر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بيانات الشركة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حصص سوق محطات الوقود في المملكة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الربع الرابع 2025 · إجمالي السوق 7,600 محطة · المصدر: أرقام</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إجمالي محطات المملكة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نهاية 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الشركة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحصة السوقية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عدد المحطات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المحسوب من الحصة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الفئة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ملاحظة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مشغّل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأكبر · +69 محطة في الربع الرابع · واعي (بطاقة) وبطاقات مسبقة الدفع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+23 محطة في الربع · تطبيق أفراد + كنترول للشركات · خطة 100 محطة سنوياً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جي أويل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مزايا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أرامكو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عبر التسهيلات للتسويق · استحوذت على سهل لخدمات الوقود</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مجموع الشركات الرئيسية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أرقام: 32.3% عبر 2,456 محطة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المستقلون والأفراد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السوق القابل للضمّ عبر الامتياز — وهو ملعب المنفذ رقم ٨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أين نقف نحن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">القياس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحصة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المحسوب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الترتيب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">درب — اسمياً (كل المنظومة)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الثالث</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أعلى من جي أويل ومزايا وأرامكو — لكنه رقم سجل لا رقم تشغيل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">درب — تحت الهوية (126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الخامس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المحطات التي تحمل علامتنا فعلاً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">درب — مشغّلة بالكامل (80)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السادس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49 استثماري مشغّل + 31 امتياز مكتمل الهوية — الرقم الحقيقي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الفارق بين «355» و«80» هو الفارق بين المركز الثالث والمركز السادس. وهو نفس الغموض الذي يكتنف رقم «1,790 محطة» في صفقة سيارة آب — كل رقم شبكة في هذا السوق يجب أن يُسأل عنه: مملوكة أم امتياز أم موردة؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التطبيقات والمنصات والبطاقات — التصنيف الصحيح</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ثلاثة أنواع تُخلط عادةً وهي مختلفة جوهرياً: تطبيق أفراد · منصة شركات · بطاقة/شريحة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الاسم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المالك/المشغّل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التقنية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محطات المالك</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شبكة القبول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% من المملكة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التغطية الجغرافية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحجم المعلن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مصدر القوة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نقطة الضعف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الخطر علينا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ساسكو (مشغّل)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أفراد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QR + محفظة رقمية + نقاط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محطات ساسكو ونخلة ومغاسل أوتوسبا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">غير معلن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شبكة مملوكة + نقاط تُستبدل في مطاعم ومقاهي المحطة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محصور في شبكته — لا يعمل خارجها</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يضع معيار تجربة أعلى من تطبيقنا لعميل الأفراد نفسه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قوستيشن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هلا السعودية (مشغّل)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محفظة + ولاء متدرج (برونزي→بلاتيني) + توصيل وقود</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المنطقة الشرقية — الخبر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منتج رقمي ناضج: محفظة لكل مركبة + توصيل وقود + مستويات عضوية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 محطة فقط — لا وزن سوقي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إشارة تحذير: 12 محطة ومنتجه الرقمي أنضج من منتجنا بـ355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التسهيلات للتسويق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تطبيق محطات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وطني</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العلامة والدعم المؤسسي · استحوذت على سهل لخدمات الوقود</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حديث الدخول في التجزئة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منافس صاعد بعلامة لا تُقاوَم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">درب (نحن)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">درب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تطبيق + تانكي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مكة · جدة · الطائف · جازان · الشرقية · الخرج · القصيم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28% من الإيراد · 43 محطة بصفر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نملك الزيارة: 22.5 مليون زيارة سنوياً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28% — التطبيق ميت عملياً · 62.6% نقد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بترو آب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مستقلة — بقيادة جدوى للاستثمار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NFC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كل مناطق المملكة + مصر وتايلاند ونيجيريا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500,000+ مركبة · 10,000 عميل شركة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يملك العلاقة والبيانات وقرار توجيه الحجم — بلا محطة واحدة · تمويل 50 مليون دولار · طرح مستهدف 2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأخطر: مقبول في نحو ثلثي محطات المملكة ويحوّلنا إلى نقطة تنفيذ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سيارة آب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استُحوذ عليها — مجموعة 1,790+ محطة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صار له أصول بعد الصفقة (يوليو 2026): منصة + شبكة محطات معاً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الجهة المستحوذة غير معلنة وقيمة الصفقة غير معلنة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الخطر الجديد: نموذج المنصة+الشبكة يفوق الدريس عدداً لو صحّ الرقم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مستقلة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فوترة موحدة + مسارات اعتماد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,000+ مزوّد خدمة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حزمة موحّدة: وقود وإطارات وزيوت وبطاريات وغسيل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يقطع محفظتَي الوقود وخدمات السيارات معاً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">واعي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFID داخل فوهة المضخة — ليس تطبيقاً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تعبئة آلية بلا تدخل بشري + تعريف المركبة في الفوهة + منع الغش</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محصور في شبكة الدريس فقط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يثبّت أسطول العميل داخل شبكة الدريس بحاجز تقني</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كنترول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شرائح RFID + بطاقات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ضبط إنفاق ناضج مربوط بشبكة ساسكو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محصور في شبكة ساسكو فقط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يثبّت الأسطول المتوسط داخل شبكة ساسكو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التصنيف الذي يجب ألا يُخلط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«واعي» بطاقة/شريحة لا تطبيق — قارئ RFID داخل فوهة المضخة يعرّف المركبة ويعبّئ آلياً. ومقارنته بتطبيق أفراد خطأ تصنيفي يقود إلى قرار خاطئ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">النمط الحاسم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المشغّلون (الدريس · ساسكو) بنوا أدوات محصورة في شبكاتهم — واعي يعمل في محطات الدريس فقط. أما المنصات المستقلة فبنت شبكات تتجاوز أي مشغّل: بترو آب مقبولة في نحو ثلثي محطات المملكة بلا أن تملك محطة واحدة. الأداة المحصورة تحمي حصة قائمة؛ والمنصة المفتوحة تأخذ حصة الجميع.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ما تغيّر في يوليو 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سيارة آب كانت منصة بلا أصول، وبعد الاستحواذ صارت منصة + شبكة معاً — أي نموذج الدريس لكن بتقنية أحدث وشبكة قبول مفتوحة. هذا يجعل نموذج «منصة تملك محطات» هو المسار الرابح، وهو بالضبط ما نملك مقوّماته ولا نستخدمه.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الخلاصة لنا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لسنا متأخرين في التطبيق فحسب — نحن في السباق الخطأ. منتجنا B2C دفع وولاء (0.28%)، والمعركة الفعلية B2B ضبط إنفاق. ومقارنة 0.28% بـ500 ألف مركبة مقارنة خاطئة من أساسها: السؤال الصحيح هو من يملك عقد الأسطول.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الخطة التنفيذية لمنافذ البيع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الخانات الصفراء تُعبّأ · الفجوة ونسبة النمو تُحسب تلقائياً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خط الأساس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الوحدة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مصدر خط الأساس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المستهدف السنوي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نمو مطلوب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المبادرة الرئيسية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المسؤول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المؤشر الحاسم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحالة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">م</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‹مثال› الخدمات المالية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">البنوك</t>
+  </si>
+  <si>
+    <t xml:space="preserve">موقع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leasing-own.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التعاقد مع بنكين على 14 موقعاً جديداً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‹اسم المسؤول›</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عدد المواقع المُدرّة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لم تبدأ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مليون ريال/سنة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analytics.csv — إسقاط مُطبَّع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الربح لكل زيارة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% إشغال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leasing-franchise.csv — 64 من 256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نسبة الإشغال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محطة بخدمة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الهامش لكل زيارة خدمة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ريال/سنة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا إيراد موثّق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إيراد غير وقودي لكل زيارة</t>
+  </si>
+  <si>
     <t xml:space="preserve">التطبيق والولاء (تانكي)</t>
   </si>
   <si>
     <t xml:space="preserve">النقد ومدى</t>
   </si>
   <si>
-    <t xml:space="preserve">62.6% من مبيعاتنا نقداً</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28% حصة التطبيق · 43 محطة بصفر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لا نعرف من اشترى</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التسويق</t>
+    <t xml:space="preserve">% من الإيراد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analytics.csv — مرجّح بالإيراد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نسبة الزيارات المعرَّفة</t>
   </si>
   <si>
     <t xml:space="preserve">البطاقات ومنصات الإنفاق</t>
   </si>
   <si>
-    <t xml:space="preserve">بترو آب</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500,000+ مركبة · 10,000 عميل شركة · 5,000 محطة قبول</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خارج الشبكة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">وسيط يفصلنا عن العميل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المساحات الإعلانية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">شركات + وسطاء</t>
-  </si>
-  <si>
-    <t xml:space="preserve">العربية للإعلان الخارجي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62–66% حصة · 4,942 لوحة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">صفر إيراد موثّق</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355 موقعاً بلا إيراد إعلاني</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الامتياز والتوريد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الأسرع في ضمّ المحطات المستقلة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">231 محطة في المنظومة · 31 مكتملة الهوية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200 محطة علامتها غير مُسلَّمة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الشحن الكهربائي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EVIQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,000+ شاحن في 1,000 موقع · شراكة PIF والسعودية للكهرباء</t>
-  </si>
-  <si>
-    <t xml:space="preserve">النافذة تُغلق</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الديزل بالجملة والتوصيل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الدريس · بترومين</t>
-  </si>
-  <si>
-    <t xml:space="preserve">يملكان أسطول النقل — وهو حاجز الدخول</t>
-  </si>
-  <si>
-    <t xml:space="preserve">محطات ديزل عالية بلا توزيع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الخدمات المالية والخزائن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">البنوك (طرف مقابل لا منافس)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بدائل مواقع كثيرة أمامها</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 مواقع من 124 محطة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118 محطة بلا خدمة مالية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المساحات اللوجستية والمواقف</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مشغّلو المواقف والمستودعات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سوق مجزّأ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">غير مُستثمر · مواقع تصل 5,420 م²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أرض مملوكة بلا إيراد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الإجمالي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">القراءة الأفقية: عمود «شركات» شبه فارغ — وهذه هي الفجوة كلها. وثلاث خلايا حاسمة في عمود الوسطاء نحن غائبون عنها.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">القاعدة الحاكمة: القناة التي لا نملك فيها العلاقة تُدرّ حجماً اليوم وتُفقدنا التسعير غداً.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أضعف منافذنا هي أقلّها منافسة — التأجير والإعلان والزينة: لا مسيطر فيها، ونحن غائبون.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تحليل المنافسين</t>
-  </si>
-  <si>
-    <t xml:space="preserve">من يسيطر على كل منفذ — وبأي مصدر قوة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المنافس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">النوع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الحجم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المنافذ التي يسيطر عليها</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مصدر قوته</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نقطة ضعفه</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الردّ المقترح</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مشغّل محطات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,300 محطة · 17.11% حصة · ربح صافٍ 421.8 مليون ريال 2025 (+22%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الوقود · الامتياز والتوريد · الديزل بالجملة · البطاقات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الحجم والانتشار وسرعة ضمّ المستقلين</t>
-  </si>
-  <si>
-    <t xml:space="preserve">منافس تقليدي على اللتر — لا يملك ميزة في المنافذ غير الوقودية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لا ننافسه على اللتر بل على الربح لكل زيارة — ونستحوذ على المنافذ التي لا يلعب فيها</t>
-  </si>
-  <si>
-    <t xml:space="preserve">argaam.com — نتائج 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بترو آب (PetroApp)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">منصة وساطة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500,000+ مركبة · 10,000 عميل شركة · 5,000 محطة قبول · تمويل 50 مليون دولار بقيادة جدوى</t>
-  </si>
-  <si>
-    <t xml:space="preserve">البطاقات ومنصات الإنفاق · خدمات السيارات (توسّع) · الإكسسوارات (إطارات وبطاريات)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">يملك العلاقة مع المنشأة والبيانات وقرار توجيه الحجم — بلا محطة واحدة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لا يملك أصلاً مادياً — يعتمد كلياً على شبكة قبول المحطات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المساران معاً: عقود مباشرة لمن نصله بمندوب، والتقاط الباقي عبر المنصة بعمولة — والحساب يُعاد كل ربع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fintechfutures.com · petroapp.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سلسلة خدمة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">كثافة الفروع والعلامة في الزيوت والصيانة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لا يملك حركة المحطة — يشتريها منّا</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نحوّل الـ39 محطة من إيجار إلى نسبة من الخدمة، ونفتح عقود أساطيل دورية في الـ85 الشاغرة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تحليل داخلي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">وكالة إعلان</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62–66% حصة السوق · 4,942 لوحة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">علاقات المعلنين الوطنيين وحصرية المواقع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">يشتري مواقع نحن أصحابها — الأصل بيدنا</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تأجير الشبكة للوطني عبر وكالة بحد أدنى مضمون + بيع مباشر للمعلن المحلي والمستأجر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بنية تحتية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,000+ شاحن في 1,000 موقع · شراكة صندوق الاستثمارات العامة والسعودية للكهرباء</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دعم سيادي ورأس مال بنية تحتية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">يحتاج مواقع على شرايين الحركة — ونحن نملك 355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">استضافة بعقد موقع لا استثمار في الشواحن — المنتج هو زمن الانتظار لا الشحن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pif.gov.sa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ساسكو</t>
-  </si>
-  <si>
-    <t xml:space="preserve">برنامج كنترول (شرائح RFID وبطاقات) · خطة 100 محطة سنوياً</t>
-  </si>
-  <si>
-    <t xml:space="preserve">البطاقات (شركات) · الامتياز</t>
-  </si>
-  <si>
-    <t xml:space="preserve">منتج ضبط إنفاق ناضج وتوسّع مُموّل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أصغر شبكة من الدريس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مراقبة — والتمييز عبر التأجير والإعلان لا عبر البطاقة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sasco.com.sa · argaam.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fleet Plus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,000+ مزوّد خدمة · وقود وإطارات وزيوت وبطاريات وغسيل بفوترة موحدة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">البطاقات ومنصات الإنفاق · خدمات السيارات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حزمة موحّدة ومسارات اعتماد للمنشأة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لا يملك أصولاً — نفس ضعف بترو آب</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نفس قاعدة بترو آب: عمولة المنصة لكل لتر مقابل تكلفة قوة البيع المباشرة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">النقد ومدى وآبل باي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بديل سلوكي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.6% نقد · 26.1% شبكة من مبيعاتنا</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التطبيق والولاء</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لا احتكاك — الدفع بلمسة بلا تطبيق</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لا يقدّم للعميل أي ميزة تتجاوز الدفع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التطبيق يجب أن يبيع ما لا يُباع بغيره: سعر عضوية · طابور أسرع · رصيد مُهدى · عرض من المستأجر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بيانات الشركة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الخطة التنفيذية لمنافذ البيع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الخانات الصفراء تُعبّأ · الفجوة ونسبة النمو تُحسب تلقائياً</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خط الأساس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الوحدة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مصدر خط الأساس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المستهدف السنوي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نمو مطلوب</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المبادرة الرئيسية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المسؤول</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المؤشر الحاسم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الحالة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">م</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‹مثال› الخدمات المالية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">البنوك</t>
-  </si>
-  <si>
-    <t xml:space="preserve">موقع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">leasing-own.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التعاقد مع بنكين على 14 موقعاً جديداً</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‹اسم المسؤول›</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عدد المواقع المُدرّة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لم تبدأ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مليون ريال/سنة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">analytics.csv — إسقاط مُطبَّع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الربح لكل زيارة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% إشغال</t>
-  </si>
-  <si>
-    <t xml:space="preserve">leasing-franchise.csv — 64 من 256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نسبة الإشغال</t>
-  </si>
-  <si>
-    <t xml:space="preserve">محطة بخدمة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الهامش لكل زيارة خدمة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ريال/سنة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لا إيراد موثّق</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إيراد غير وقودي لكل زيارة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% من الإيراد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">analytics.csv — مرجّح بالإيراد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نسبة الزيارات المعرَّفة</t>
-  </si>
-  <si>
     <t xml:space="preserve">لتر متعاقَد</t>
   </si>
   <si>
@@ -1115,9 +1513,6 @@
   </si>
   <si>
     <t xml:space="preserve">جنوب صبيا</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
   </si>
   <si>
     <t xml:space="preserve">MK071</t>
@@ -1274,15 +1669,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="168" formatCode="0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0"/>
+    <numFmt numFmtId="165" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="0.00%"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.00"/>
+    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="170" formatCode="0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1372,6 +1768,14 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF44546A"/>
       <name val="Arial"/>
@@ -1387,7 +1791,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1427,19 +1831,25 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFC6E0B4"/>
+        <bgColor rgb="FFD9E2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE7E6E6"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFD9E2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
         <bgColor rgb="FF333333"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -1492,7 +1902,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="74">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1597,6 +2007,118 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
@@ -1605,19 +2127,15 @@
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1629,55 +2147,43 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1685,11 +2191,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1723,7 +2229,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFE7E6E6"/>
+      <rgbColor rgb="FFD9E2F3"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -1737,7 +2243,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFE7E6E6"/>
       <rgbColor rgb="FFC6E0B4"/>
       <rgbColor rgb="FFFFE699"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -2759,7 +3265,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3002,60 +3508,118 @@
     </row>
     <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>167</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="G11" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>180</v>
+      <c r="B13" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -3074,6 +3638,920 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C3" s="26" t="n">
+        <v>7600</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="28" t="n">
+        <v>0.1711</v>
+      </c>
+      <c r="D5" s="29" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E5" s="29" t="n">
+        <f aca="false">ROUND(C5*$C$3,0)</f>
+        <v>1300</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>0.0859</v>
+      </c>
+      <c r="D6" s="29" t="n">
+        <v>653</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <f aca="false">ROUND(C6*$C$3,0)</f>
+        <v>653</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="C7" s="28" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="D7" s="29" t="n">
+        <v>176</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <f aca="false">ROUND(C7*$C$3,0)</f>
+        <v>176</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="G7" s="16"/>
+    </row>
+    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>173</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <f aca="false">ROUND(C8*$C$3,0)</f>
+        <v>173</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="G8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>0.0203</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>154</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <f aca="false">ROUND(C9*$C$3,0)</f>
+        <v>154</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="30"/>
+      <c r="B10" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="C10" s="32" t="n">
+        <f aca="false">SUM(C5:C9)</f>
+        <v>0.3232</v>
+      </c>
+      <c r="D10" s="33" t="n">
+        <f aca="false">SUM(D5:D9)</f>
+        <v>2456</v>
+      </c>
+      <c r="E10" s="33" t="n">
+        <f aca="false">SUM(E5:E9)</f>
+        <v>2456</v>
+      </c>
+      <c r="F10" s="30"/>
+      <c r="G10" s="34" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="35"/>
+      <c r="B11" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="C11" s="36" t="n">
+        <f aca="false">1-C10</f>
+        <v>0.6768</v>
+      </c>
+      <c r="D11" s="37" t="n">
+        <f aca="false">$C$3-D10</f>
+        <v>5144</v>
+      </c>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="38" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="39" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="C15" s="28" t="n">
+        <f aca="false">D15/$C$3</f>
+        <v>0.0467105263157895</v>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>355</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="C16" s="28" t="n">
+        <f aca="false">D16/$C$3</f>
+        <v>0.0165789473684211</v>
+      </c>
+      <c r="D16" s="29" t="n">
+        <v>126</v>
+      </c>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="40" t="s">
+        <v>229</v>
+      </c>
+      <c r="C17" s="41" t="n">
+        <f aca="false">D17/$C$3</f>
+        <v>0.0105263157894737</v>
+      </c>
+      <c r="D17" s="42" t="n">
+        <v>80</v>
+      </c>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="G17" s="43" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="44" t="s">
+        <v>232</v>
+      </c>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B19:G19"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M18"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="F5" s="29" t="n">
+        <v>653</v>
+      </c>
+      <c r="G5" s="29" t="n">
+        <v>653</v>
+      </c>
+      <c r="H5" s="46" t="n">
+        <f aca="false">IFERROR(G5/'حصص السوق'!$C$3,"")</f>
+        <v>0.085921052631579</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="L5" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="M5" s="16" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" s="46" t="n">
+        <f aca="false">IFERROR(G6/'حصص السوق'!$C$3,"")</f>
+        <v>0.00157894736842105</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>212</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <v>154</v>
+      </c>
+      <c r="G7" s="29" t="n">
+        <v>154</v>
+      </c>
+      <c r="H7" s="46" t="n">
+        <f aca="false">IFERROR(G7/'حصص السوق'!$C$3,"")</f>
+        <v>0.0202631578947368</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="47" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>267</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="E8" s="48" t="s">
+        <v>269</v>
+      </c>
+      <c r="F8" s="49" t="n">
+        <v>355</v>
+      </c>
+      <c r="G8" s="49" t="n">
+        <v>355</v>
+      </c>
+      <c r="H8" s="50" t="n">
+        <f aca="false">IFERROR(G8/'حصص السوق'!$C$3,"")</f>
+        <v>0.0467105263157895</v>
+      </c>
+      <c r="I8" s="48" t="s">
+        <v>270</v>
+      </c>
+      <c r="J8" s="48" t="s">
+        <v>271</v>
+      </c>
+      <c r="K8" s="48" t="s">
+        <v>272</v>
+      </c>
+      <c r="L8" s="48" t="s">
+        <v>273</v>
+      </c>
+      <c r="M8" s="48" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="51" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="29" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H9" s="46" t="n">
+        <f aca="false">IFERROR(G9/'حصص السوق'!$C$3,"")</f>
+        <v>0.657894736842105</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="51" t="s">
+        <v>282</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="F10" s="29" t="n">
+        <v>1790</v>
+      </c>
+      <c r="G10" s="29" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H10" s="46" t="n">
+        <f aca="false">IFERROR(G10/'حصص السوق'!$C$3,"")</f>
+        <v>0.328947368421053</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="29" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H11" s="46" t="n">
+        <f aca="false">IFERROR(G11/'حصص السوق'!$C$3,"")</f>
+        <v>0.657894736842105</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="F12" s="29" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G12" s="29" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H12" s="46" t="n">
+        <f aca="false">IFERROR(G12/'حصص السوق'!$C$3,"")</f>
+        <v>0.171052631578947</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="40" t="s">
+        <v>297</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="F13" s="29" t="n">
+        <v>653</v>
+      </c>
+      <c r="G13" s="29" t="n">
+        <v>653</v>
+      </c>
+      <c r="H13" s="46" t="n">
+        <f aca="false">IFERROR(G13/'حصص السوق'!$C$3,"")</f>
+        <v>0.085921052631579</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="52" t="s">
+        <v>302</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>303</v>
+      </c>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="53"/>
+      <c r="M15" s="53"/>
+    </row>
+    <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="52" t="s">
+        <v>304</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>305</v>
+      </c>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="53"/>
+      <c r="K16" s="53"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="53"/>
+    </row>
+    <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="52" t="s">
+        <v>306</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>307</v>
+      </c>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="53"/>
+      <c r="L17" s="53"/>
+      <c r="M17" s="53"/>
+    </row>
+    <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="52" t="s">
+        <v>308</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>309</v>
+      </c>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="53"/>
+      <c r="L18" s="53"/>
+      <c r="M18" s="53"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="C15:M15"/>
+    <mergeCell ref="C16:M16"/>
+    <mergeCell ref="C17:M17"/>
+    <mergeCell ref="C18:M18"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -3099,7 +4577,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>310</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3118,7 +4596,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>182</v>
+        <v>311</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3149,86 +4627,86 @@
         <v>49</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>183</v>
+        <v>312</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>184</v>
+        <v>313</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>186</v>
+        <v>315</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>52</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>187</v>
+        <v>316</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>188</v>
+        <v>317</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>53</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>189</v>
+        <v>318</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>190</v>
+        <v>319</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>191</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="C4" s="26" t="s">
+      <c r="A4" s="54" t="s">
+        <v>321</v>
+      </c>
+      <c r="B4" s="55" t="s">
+        <v>322</v>
+      </c>
+      <c r="C4" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="E4" s="26" t="n">
+      <c r="D4" s="55" t="s">
+        <v>323</v>
+      </c>
+      <c r="E4" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="G4" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="H4" s="26" t="n">
+      <c r="F4" s="54" t="s">
+        <v>324</v>
+      </c>
+      <c r="G4" s="55" t="s">
+        <v>325</v>
+      </c>
+      <c r="H4" s="54" t="n">
         <v>20</v>
       </c>
-      <c r="I4" s="26" t="n">
+      <c r="I4" s="54" t="n">
         <f aca="false">IF(H4="","",H4-E4)</f>
         <v>14</v>
       </c>
-      <c r="J4" s="28" t="n">
+      <c r="J4" s="56" t="n">
         <f aca="false">IFERROR(IF(H4="","",(H4-E4)/E4),"")</f>
         <v>2.33333333333333</v>
       </c>
-      <c r="K4" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="L4" s="26" t="s">
+      <c r="K4" s="55" t="s">
+        <v>326</v>
+      </c>
+      <c r="L4" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="M4" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="N4" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="O4" s="26" t="s">
-        <v>200</v>
+      <c r="M4" s="55" t="s">
+        <v>327</v>
+      </c>
+      <c r="N4" s="55" t="s">
+        <v>328</v>
+      </c>
+      <c r="O4" s="54" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3244,33 +4722,33 @@
       <c r="D5" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="57" t="n">
         <v>1271</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>201</v>
+        <v>330</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="H5" s="30"/>
-      <c r="I5" s="29" t="str">
+        <v>331</v>
+      </c>
+      <c r="H5" s="58"/>
+      <c r="I5" s="57" t="str">
         <f aca="false">IF(H5="","",H5-E5)</f>
         <v/>
       </c>
-      <c r="J5" s="31" t="str">
+      <c r="J5" s="46" t="str">
         <f aca="false">IFERROR(IF(H5="","",(H5-E5)/E5),"")</f>
         <v/>
       </c>
-      <c r="K5" s="32"/>
+      <c r="K5" s="59"/>
       <c r="L5" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="M5" s="32"/>
+      <c r="M5" s="59"/>
       <c r="N5" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="O5" s="33"/>
+        <v>332</v>
+      </c>
+      <c r="O5" s="60"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="n">
@@ -3285,33 +4763,33 @@
       <c r="D6" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="57" t="n">
         <v>25</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>204</v>
+        <v>333</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="H6" s="30"/>
-      <c r="I6" s="29" t="str">
+        <v>334</v>
+      </c>
+      <c r="H6" s="58"/>
+      <c r="I6" s="57" t="str">
         <f aca="false">IF(H6="","",H6-E6)</f>
         <v/>
       </c>
-      <c r="J6" s="31" t="str">
+      <c r="J6" s="46" t="str">
         <f aca="false">IFERROR(IF(H6="","",(H6-E6)/E6),"")</f>
         <v/>
       </c>
-      <c r="K6" s="32"/>
+      <c r="K6" s="59"/>
       <c r="L6" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M6" s="32"/>
+      <c r="M6" s="59"/>
       <c r="N6" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="O6" s="33"/>
+        <v>335</v>
+      </c>
+      <c r="O6" s="60"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="n">
@@ -3326,33 +4804,33 @@
       <c r="D7" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="57" t="n">
         <v>39</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>207</v>
+        <v>336</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="H7" s="30"/>
-      <c r="I7" s="29" t="str">
+        <v>325</v>
+      </c>
+      <c r="H7" s="58"/>
+      <c r="I7" s="57" t="str">
         <f aca="false">IF(H7="","",H7-E7)</f>
         <v/>
       </c>
-      <c r="J7" s="31" t="str">
+      <c r="J7" s="46" t="str">
         <f aca="false">IFERROR(IF(H7="","",(H7-E7)/E7),"")</f>
         <v/>
       </c>
-      <c r="K7" s="32"/>
+      <c r="K7" s="59"/>
       <c r="L7" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M7" s="32"/>
+      <c r="M7" s="59"/>
       <c r="N7" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="O7" s="33"/>
+        <v>337</v>
+      </c>
+      <c r="O7" s="60"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="n">
@@ -3367,115 +4845,115 @@
       <c r="D8" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="57" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>209</v>
+        <v>338</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="H8" s="30"/>
-      <c r="I8" s="29" t="str">
+        <v>339</v>
+      </c>
+      <c r="H8" s="58"/>
+      <c r="I8" s="57" t="str">
         <f aca="false">IF(H8="","",H8-E8)</f>
         <v/>
       </c>
-      <c r="J8" s="31" t="str">
+      <c r="J8" s="46" t="str">
         <f aca="false">IFERROR(IF(H8="","",(H8-E8)/E8),"")</f>
         <v/>
       </c>
-      <c r="K8" s="32"/>
+      <c r="K8" s="59"/>
       <c r="L8" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M8" s="32"/>
+      <c r="M8" s="59"/>
       <c r="N8" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="O8" s="33"/>
+        <v>340</v>
+      </c>
+      <c r="O8" s="60"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>77</v>
+        <v>341</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="29" t="n">
+        <v>342</v>
+      </c>
+      <c r="E9" s="57" t="n">
         <v>0.28</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>212</v>
+        <v>343</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="H9" s="30"/>
-      <c r="I9" s="29" t="str">
+        <v>344</v>
+      </c>
+      <c r="H9" s="58"/>
+      <c r="I9" s="57" t="str">
         <f aca="false">IF(H9="","",H9-E9)</f>
         <v/>
       </c>
-      <c r="J9" s="31" t="str">
+      <c r="J9" s="46" t="str">
         <f aca="false">IFERROR(IF(H9="","",(H9-E9)/E9),"")</f>
         <v/>
       </c>
-      <c r="K9" s="32"/>
+      <c r="K9" s="59"/>
       <c r="L9" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="M9" s="32"/>
+      <c r="M9" s="59"/>
       <c r="N9" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="O9" s="33"/>
+        <v>345</v>
+      </c>
+      <c r="O9" s="60"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>83</v>
+        <v>346</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" s="29" t="n">
+        <v>275</v>
+      </c>
+      <c r="E10" s="57" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>215</v>
+        <v>347</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="H10" s="30"/>
-      <c r="I10" s="29" t="str">
+        <v>348</v>
+      </c>
+      <c r="H10" s="58"/>
+      <c r="I10" s="57" t="str">
         <f aca="false">IF(H10="","",H10-E10)</f>
         <v/>
       </c>
-      <c r="J10" s="31" t="str">
+      <c r="J10" s="46" t="str">
         <f aca="false">IFERROR(IF(H10="","",(H10-E10)/E10),"")</f>
         <v/>
       </c>
-      <c r="K10" s="32"/>
+      <c r="K10" s="59"/>
       <c r="L10" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M10" s="32"/>
+      <c r="M10" s="59"/>
       <c r="N10" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="O10" s="33"/>
+        <v>349</v>
+      </c>
+      <c r="O10" s="60"/>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="n">
@@ -3488,35 +4966,35 @@
         <v>89</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="E11" s="29" t="n">
+        <v>350</v>
+      </c>
+      <c r="E11" s="57" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>219</v>
+        <v>351</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="H11" s="30"/>
-      <c r="I11" s="29" t="str">
+        <v>352</v>
+      </c>
+      <c r="H11" s="58"/>
+      <c r="I11" s="57" t="str">
         <f aca="false">IF(H11="","",H11-E11)</f>
         <v/>
       </c>
-      <c r="J11" s="31" t="str">
+      <c r="J11" s="46" t="str">
         <f aca="false">IFERROR(IF(H11="","",(H11-E11)/E11),"")</f>
         <v/>
       </c>
-      <c r="K11" s="32"/>
+      <c r="K11" s="59"/>
       <c r="L11" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="M11" s="32"/>
+      <c r="M11" s="59"/>
       <c r="N11" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="O11" s="33"/>
+        <v>353</v>
+      </c>
+      <c r="O11" s="60"/>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="n">
@@ -3531,33 +5009,33 @@
       <c r="D12" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="57" t="n">
         <v>31</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>222</v>
+        <v>354</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="H12" s="30"/>
-      <c r="I12" s="29" t="str">
+        <v>355</v>
+      </c>
+      <c r="H12" s="58"/>
+      <c r="I12" s="57" t="str">
         <f aca="false">IF(H12="","",H12-E12)</f>
         <v/>
       </c>
-      <c r="J12" s="31" t="str">
+      <c r="J12" s="46" t="str">
         <f aca="false">IFERROR(IF(H12="","",(H12-E12)/E12),"")</f>
         <v/>
       </c>
-      <c r="K12" s="32"/>
+      <c r="K12" s="59"/>
       <c r="L12" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M12" s="32"/>
+      <c r="M12" s="59"/>
       <c r="N12" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="O12" s="33"/>
+        <v>356</v>
+      </c>
+      <c r="O12" s="60"/>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="n">
@@ -3572,33 +5050,33 @@
       <c r="D13" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="57" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>225</v>
+        <v>357</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="H13" s="30"/>
-      <c r="I13" s="29" t="str">
+        <v>358</v>
+      </c>
+      <c r="H13" s="58"/>
+      <c r="I13" s="57" t="str">
         <f aca="false">IF(H13="","",H13-E13)</f>
         <v/>
       </c>
-      <c r="J13" s="31" t="str">
+      <c r="J13" s="46" t="str">
         <f aca="false">IFERROR(IF(H13="","",(H13-E13)/E13),"")</f>
         <v/>
       </c>
-      <c r="K13" s="32"/>
+      <c r="K13" s="59"/>
       <c r="L13" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M13" s="32"/>
+      <c r="M13" s="59"/>
       <c r="N13" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="O13" s="33"/>
+        <v>359</v>
+      </c>
+      <c r="O13" s="60"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="n">
@@ -3613,33 +5091,33 @@
       <c r="D14" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="57" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>228</v>
+        <v>360</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="H14" s="30"/>
-      <c r="I14" s="29" t="str">
+        <v>361</v>
+      </c>
+      <c r="H14" s="58"/>
+      <c r="I14" s="57" t="str">
         <f aca="false">IF(H14="","",H14-E14)</f>
         <v/>
       </c>
-      <c r="J14" s="31" t="str">
+      <c r="J14" s="46" t="str">
         <f aca="false">IFERROR(IF(H14="","",(H14-E14)/E14),"")</f>
         <v/>
       </c>
-      <c r="K14" s="32"/>
+      <c r="K14" s="59"/>
       <c r="L14" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="M14" s="32"/>
+      <c r="M14" s="59"/>
       <c r="N14" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="O14" s="33"/>
+        <v>362</v>
+      </c>
+      <c r="O14" s="60"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="n">
@@ -3652,35 +5130,35 @@
         <v>46</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="E15" s="29" t="n">
+        <v>323</v>
+      </c>
+      <c r="E15" s="57" t="n">
         <v>6</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>219</v>
+        <v>351</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="H15" s="30"/>
-      <c r="I15" s="29" t="str">
+        <v>363</v>
+      </c>
+      <c r="H15" s="58"/>
+      <c r="I15" s="57" t="str">
         <f aca="false">IF(H15="","",H15-E15)</f>
         <v/>
       </c>
-      <c r="J15" s="31" t="str">
+      <c r="J15" s="46" t="str">
         <f aca="false">IFERROR(IF(H15="","",(H15-E15)/E15),"")</f>
         <v/>
       </c>
-      <c r="K15" s="32"/>
+      <c r="K15" s="59"/>
       <c r="L15" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M15" s="32"/>
+      <c r="M15" s="59"/>
       <c r="N15" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="O15" s="33"/>
+        <v>364</v>
+      </c>
+      <c r="O15" s="60"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="n">
@@ -3693,51 +5171,51 @@
         <v>46</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="E16" s="29" t="n">
+        <v>365</v>
+      </c>
+      <c r="E16" s="57" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>234</v>
+        <v>366</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="H16" s="30"/>
-      <c r="I16" s="29" t="str">
+        <v>367</v>
+      </c>
+      <c r="H16" s="58"/>
+      <c r="I16" s="57" t="str">
         <f aca="false">IF(H16="","",H16-E16)</f>
         <v/>
       </c>
-      <c r="J16" s="31" t="str">
+      <c r="J16" s="46" t="str">
         <f aca="false">IFERROR(IF(H16="","",(H16-E16)/E16),"")</f>
         <v/>
       </c>
-      <c r="K16" s="32"/>
+      <c r="K16" s="59"/>
       <c r="L16" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M16" s="32"/>
+      <c r="M16" s="59"/>
       <c r="N16" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="O16" s="33"/>
+        <v>368</v>
+      </c>
+      <c r="O16" s="60"/>
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="C18" s="34" t="s">
-        <v>238</v>
-      </c>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="34"/>
+        <v>369</v>
+      </c>
+      <c r="C18" s="61" t="s">
+        <v>370</v>
+      </c>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
+      <c r="K18" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3755,7 +5233,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -3789,7 +5267,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>239</v>
+        <v>371</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3810,31 +5288,31 @@
         <v>44</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>190</v>
+        <v>319</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>183</v>
+        <v>312</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>240</v>
+        <v>372</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>241</v>
+        <v>373</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>242</v>
+        <v>374</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>243</v>
+        <v>375</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>186</v>
+        <v>315</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>244</v>
+        <v>376</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>245</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3844,18 +5322,18 @@
       <c r="B4" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="36" t="s">
-        <v>203</v>
-      </c>
-      <c r="D4" s="37" t="n">
+      <c r="C4" s="38" t="s">
+        <v>332</v>
+      </c>
+      <c r="D4" s="62" t="n">
         <f aca="false">'الخطة التنفيذية'!E5</f>
         <v>1271</v>
       </c>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="37" t="str">
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="62" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H5="","",'الخطة التنفيذية'!H5)</f>
         <v/>
       </c>
@@ -3863,7 +5341,7 @@
         <f aca="false">IF(H4="","",IF(H4=I4,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K4" s="31" t="str">
+      <c r="K4" s="46" t="str">
         <f aca="false">IFERROR(IF(H4="","",(H4-D4)/D4),"")</f>
         <v/>
       </c>
@@ -3875,18 +5353,18 @@
       <c r="B5" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="36" t="s">
-        <v>206</v>
-      </c>
-      <c r="D5" s="37" t="n">
+      <c r="C5" s="38" t="s">
+        <v>335</v>
+      </c>
+      <c r="D5" s="62" t="n">
         <f aca="false">'الخطة التنفيذية'!E6</f>
         <v>25</v>
       </c>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="37" t="str">
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="62" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H6="","",'الخطة التنفيذية'!H6)</f>
         <v/>
       </c>
@@ -3894,7 +5372,7 @@
         <f aca="false">IF(H5="","",IF(H5=I5,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K5" s="31" t="str">
+      <c r="K5" s="46" t="str">
         <f aca="false">IFERROR(IF(H5="","",(H5-D5)/D5),"")</f>
         <v/>
       </c>
@@ -3906,18 +5384,18 @@
       <c r="B6" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="36" t="s">
-        <v>208</v>
-      </c>
-      <c r="D6" s="37" t="n">
+      <c r="C6" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="D6" s="62" t="n">
         <f aca="false">'الخطة التنفيذية'!E7</f>
         <v>39</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="37" t="str">
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="62" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H7="","",'الخطة التنفيذية'!H7)</f>
         <v/>
       </c>
@@ -3925,7 +5403,7 @@
         <f aca="false">IF(H6="","",IF(H6=I6,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K6" s="31" t="str">
+      <c r="K6" s="46" t="str">
         <f aca="false">IFERROR(IF(H6="","",(H6-D6)/D6),"")</f>
         <v/>
       </c>
@@ -3937,18 +5415,18 @@
       <c r="B7" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="36" t="s">
-        <v>211</v>
-      </c>
-      <c r="D7" s="37" t="n">
+      <c r="C7" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="D7" s="62" t="n">
         <f aca="false">'الخطة التنفيذية'!E8</f>
         <v>0</v>
       </c>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="37" t="str">
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="62" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H8="","",'الخطة التنفيذية'!H8)</f>
         <v/>
       </c>
@@ -3956,7 +5434,7 @@
         <f aca="false">IF(H7="","",IF(H7=I7,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K7" s="31" t="str">
+      <c r="K7" s="46" t="str">
         <f aca="false">IFERROR(IF(H7="","",(H7-D7)/D7),"")</f>
         <v/>
       </c>
@@ -3966,20 +5444,20 @@
         <v>5</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>214</v>
-      </c>
-      <c r="D8" s="37" t="n">
+        <v>341</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>345</v>
+      </c>
+      <c r="D8" s="62" t="n">
         <f aca="false">'الخطة التنفيذية'!E9</f>
         <v>0.28</v>
       </c>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="37" t="str">
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="62" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H9="","",'الخطة التنفيذية'!H9)</f>
         <v/>
       </c>
@@ -3987,7 +5465,7 @@
         <f aca="false">IF(H8="","",IF(H8=I8,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K8" s="31" t="str">
+      <c r="K8" s="46" t="str">
         <f aca="false">IFERROR(IF(H8="","",(H8-D8)/D8),"")</f>
         <v/>
       </c>
@@ -3997,20 +5475,20 @@
         <v>6</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>217</v>
-      </c>
-      <c r="D9" s="37" t="n">
+        <v>346</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="D9" s="62" t="n">
         <f aca="false">'الخطة التنفيذية'!E10</f>
         <v>0</v>
       </c>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="37" t="str">
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="62" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H10="","",'الخطة التنفيذية'!H10)</f>
         <v/>
       </c>
@@ -4018,7 +5496,7 @@
         <f aca="false">IF(H9="","",IF(H9=I9,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K9" s="31" t="str">
+      <c r="K9" s="46" t="str">
         <f aca="false">IFERROR(IF(H9="","",(H9-D9)/D9),"")</f>
         <v/>
       </c>
@@ -4030,18 +5508,18 @@
       <c r="B10" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="36" t="s">
-        <v>221</v>
-      </c>
-      <c r="D10" s="37" t="n">
+      <c r="C10" s="38" t="s">
+        <v>353</v>
+      </c>
+      <c r="D10" s="62" t="n">
         <f aca="false">'الخطة التنفيذية'!E11</f>
         <v>0</v>
       </c>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="37" t="str">
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="62" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H11="","",'الخطة التنفيذية'!H11)</f>
         <v/>
       </c>
@@ -4049,7 +5527,7 @@
         <f aca="false">IF(H10="","",IF(H10=I10,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K10" s="31" t="str">
+      <c r="K10" s="46" t="str">
         <f aca="false">IFERROR(IF(H10="","",(H10-D10)/D10),"")</f>
         <v/>
       </c>
@@ -4061,18 +5539,18 @@
       <c r="B11" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="36" t="s">
-        <v>224</v>
-      </c>
-      <c r="D11" s="37" t="n">
+      <c r="C11" s="38" t="s">
+        <v>356</v>
+      </c>
+      <c r="D11" s="62" t="n">
         <f aca="false">'الخطة التنفيذية'!E12</f>
         <v>31</v>
       </c>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="37" t="str">
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="62" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H12="","",'الخطة التنفيذية'!H12)</f>
         <v/>
       </c>
@@ -4080,7 +5558,7 @@
         <f aca="false">IF(H11="","",IF(H11=I11,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K11" s="31" t="str">
+      <c r="K11" s="46" t="str">
         <f aca="false">IFERROR(IF(H11="","",(H11-D11)/D11),"")</f>
         <v/>
       </c>
@@ -4092,18 +5570,18 @@
       <c r="B12" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="D12" s="37" t="n">
+      <c r="C12" s="38" t="s">
+        <v>359</v>
+      </c>
+      <c r="D12" s="62" t="n">
         <f aca="false">'الخطة التنفيذية'!E13</f>
         <v>0</v>
       </c>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="37" t="str">
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="62" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H13="","",'الخطة التنفيذية'!H13)</f>
         <v/>
       </c>
@@ -4111,7 +5589,7 @@
         <f aca="false">IF(H12="","",IF(H12=I12,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K12" s="31" t="str">
+      <c r="K12" s="46" t="str">
         <f aca="false">IFERROR(IF(H12="","",(H12-D12)/D12),"")</f>
         <v/>
       </c>
@@ -4123,18 +5601,18 @@
       <c r="B13" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="36" t="s">
-        <v>230</v>
-      </c>
-      <c r="D13" s="37" t="n">
+      <c r="C13" s="38" t="s">
+        <v>362</v>
+      </c>
+      <c r="D13" s="62" t="n">
         <f aca="false">'الخطة التنفيذية'!E14</f>
         <v>0</v>
       </c>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="37" t="str">
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="62" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H14="","",'الخطة التنفيذية'!H14)</f>
         <v/>
       </c>
@@ -4142,7 +5620,7 @@
         <f aca="false">IF(H13="","",IF(H13=I13,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K13" s="31" t="str">
+      <c r="K13" s="46" t="str">
         <f aca="false">IFERROR(IF(H13="","",(H13-D13)/D13),"")</f>
         <v/>
       </c>
@@ -4154,18 +5632,18 @@
       <c r="B14" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="36" t="s">
-        <v>232</v>
-      </c>
-      <c r="D14" s="37" t="n">
+      <c r="C14" s="38" t="s">
+        <v>364</v>
+      </c>
+      <c r="D14" s="62" t="n">
         <f aca="false">'الخطة التنفيذية'!E15</f>
         <v>6</v>
       </c>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="37" t="str">
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="62" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H15="","",'الخطة التنفيذية'!H15)</f>
         <v/>
       </c>
@@ -4173,7 +5651,7 @@
         <f aca="false">IF(H14="","",IF(H14=I14,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K14" s="31" t="str">
+      <c r="K14" s="46" t="str">
         <f aca="false">IFERROR(IF(H14="","",(H14-D14)/D14),"")</f>
         <v/>
       </c>
@@ -4185,18 +5663,18 @@
       <c r="B15" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="C15" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="D15" s="37" t="n">
+      <c r="C15" s="38" t="s">
+        <v>368</v>
+      </c>
+      <c r="D15" s="62" t="n">
         <f aca="false">'الخطة التنفيذية'!E16</f>
         <v>0</v>
       </c>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="37" t="str">
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="62" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H16="","",'الخطة التنفيذية'!H16)</f>
         <v/>
       </c>
@@ -4204,7 +5682,7 @@
         <f aca="false">IF(H15="","",IF(H15=I15,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K15" s="31" t="str">
+      <c r="K15" s="46" t="str">
         <f aca="false">IFERROR(IF(H15="","",(H15-D15)/D15),"")</f>
         <v/>
       </c>
@@ -4224,7 +5702,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4248,7 +5726,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>246</v>
+        <v>378</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4266,7 +5744,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>247</v>
+        <v>379</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4287,87 +5765,87 @@
         <v>43</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>248</v>
+        <v>380</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>249</v>
+        <v>381</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>53</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>189</v>
+        <v>318</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>250</v>
+        <v>382</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>251</v>
+        <v>383</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>252</v>
+        <v>384</v>
       </c>
       <c r="J3" s="15" t="s">
         <v>54</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>253</v>
+        <v>385</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>254</v>
+        <v>386</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>191</v>
+        <v>320</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>255</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>256</v>
-      </c>
-      <c r="C4" s="26" t="s">
+      <c r="A4" s="54" t="s">
+        <v>321</v>
+      </c>
+      <c r="B4" s="55" t="s">
+        <v>388</v>
+      </c>
+      <c r="C4" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="G4" s="38" t="n">
+      <c r="F4" s="54" t="s">
+        <v>327</v>
+      </c>
+      <c r="G4" s="63" t="n">
         <v>46235</v>
       </c>
-      <c r="H4" s="38" t="n">
+      <c r="H4" s="63" t="n">
         <v>46326</v>
       </c>
-      <c r="I4" s="26" t="n">
+      <c r="I4" s="54" t="n">
         <f aca="false">IF(OR(G4="",H4=""),"",H4-G4)</f>
         <v>91</v>
       </c>
-      <c r="J4" s="26" t="n">
+      <c r="J4" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="L4" s="27" t="s">
-        <v>258</v>
-      </c>
-      <c r="M4" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="N4" s="39" t="n">
+      <c r="K4" s="54" t="s">
+        <v>389</v>
+      </c>
+      <c r="L4" s="55" t="s">
+        <v>390</v>
+      </c>
+      <c r="M4" s="54" t="s">
+        <v>329</v>
+      </c>
+      <c r="N4" s="64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4375,515 +5853,515 @@
       <c r="A5" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="32"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
       <c r="I5" s="21" t="str">
         <f aca="false">IF(OR(G5="",H5=""),"",H5-G5)</f>
         <v/>
       </c>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="41"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="60"/>
+      <c r="L5" s="59"/>
+      <c r="M5" s="60"/>
+      <c r="N5" s="66"/>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
       <c r="I6" s="21" t="str">
         <f aca="false">IF(OR(G6="",H6=""),"",H6-G6)</f>
         <v/>
       </c>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="41"/>
+      <c r="J6" s="60"/>
+      <c r="K6" s="60"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="60"/>
+      <c r="N6" s="66"/>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="32"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
       <c r="I7" s="21" t="str">
         <f aca="false">IF(OR(G7="",H7=""),"",H7-G7)</f>
         <v/>
       </c>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="32"/>
-      <c r="M7" s="33"/>
-      <c r="N7" s="41"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="60"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="60"/>
+      <c r="N7" s="66"/>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="65"/>
       <c r="I8" s="21" t="str">
         <f aca="false">IF(OR(G8="",H8=""),"",H8-G8)</f>
         <v/>
       </c>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="32"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="41"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="60"/>
+      <c r="L8" s="59"/>
+      <c r="M8" s="60"/>
+      <c r="N8" s="66"/>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
       <c r="I9" s="21" t="str">
         <f aca="false">IF(OR(G9="",H9=""),"",H9-G9)</f>
         <v/>
       </c>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="32"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="41"/>
+      <c r="J9" s="60"/>
+      <c r="K9" s="60"/>
+      <c r="L9" s="59"/>
+      <c r="M9" s="60"/>
+      <c r="N9" s="66"/>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
+      <c r="B10" s="59"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="65"/>
       <c r="I10" s="21" t="str">
         <f aca="false">IF(OR(G10="",H10=""),"",H10-G10)</f>
         <v/>
       </c>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="41"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="60"/>
+      <c r="L10" s="59"/>
+      <c r="M10" s="60"/>
+      <c r="N10" s="66"/>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="32"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
       <c r="I11" s="21" t="str">
         <f aca="false">IF(OR(G11="",H11=""),"",H11-G11)</f>
         <v/>
       </c>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="32"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="41"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="60"/>
+      <c r="L11" s="59"/>
+      <c r="M11" s="60"/>
+      <c r="N11" s="66"/>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
       <c r="I12" s="21" t="str">
         <f aca="false">IF(OR(G12="",H12=""),"",H12-G12)</f>
         <v/>
       </c>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="41"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="60"/>
+      <c r="L12" s="59"/>
+      <c r="M12" s="60"/>
+      <c r="N12" s="66"/>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="32"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
       <c r="I13" s="21" t="str">
         <f aca="false">IF(OR(G13="",H13=""),"",H13-G13)</f>
         <v/>
       </c>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="41"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="60"/>
+      <c r="L13" s="59"/>
+      <c r="M13" s="60"/>
+      <c r="N13" s="66"/>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="35" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="32"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
+      <c r="B14" s="59"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
       <c r="I14" s="21" t="str">
         <f aca="false">IF(OR(G14="",H14=""),"",H14-G14)</f>
         <v/>
       </c>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="41"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="60"/>
+      <c r="L14" s="59"/>
+      <c r="M14" s="60"/>
+      <c r="N14" s="66"/>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="35" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="21" t="str">
         <f aca="false">IF(OR(G15="",H15=""),"",H15-G15)</f>
         <v/>
       </c>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="41"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="60"/>
+      <c r="L15" s="59"/>
+      <c r="M15" s="60"/>
+      <c r="N15" s="66"/>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="35" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="32"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="65"/>
+      <c r="H16" s="65"/>
       <c r="I16" s="21" t="str">
         <f aca="false">IF(OR(G16="",H16=""),"",H16-G16)</f>
         <v/>
       </c>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="41"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="60"/>
+      <c r="L16" s="59"/>
+      <c r="M16" s="60"/>
+      <c r="N16" s="66"/>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="35" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="32"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="65"/>
+      <c r="H17" s="65"/>
       <c r="I17" s="21" t="str">
         <f aca="false">IF(OR(G17="",H17=""),"",H17-G17)</f>
         <v/>
       </c>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="41"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="60"/>
+      <c r="L17" s="59"/>
+      <c r="M17" s="60"/>
+      <c r="N17" s="66"/>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="35" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="32"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="65"/>
       <c r="I18" s="21" t="str">
         <f aca="false">IF(OR(G18="",H18=""),"",H18-G18)</f>
         <v/>
       </c>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="41"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="59"/>
+      <c r="M18" s="60"/>
+      <c r="N18" s="66"/>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="35" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="32"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
       <c r="I19" s="21" t="str">
         <f aca="false">IF(OR(G19="",H19=""),"",H19-G19)</f>
         <v/>
       </c>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="41"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="60"/>
+      <c r="L19" s="59"/>
+      <c r="M19" s="60"/>
+      <c r="N19" s="66"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="35" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="32"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="65"/>
+      <c r="H20" s="65"/>
       <c r="I20" s="21" t="str">
         <f aca="false">IF(OR(G20="",H20=""),"",H20-G20)</f>
         <v/>
       </c>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="32"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="41"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="60"/>
+      <c r="L20" s="59"/>
+      <c r="M20" s="60"/>
+      <c r="N20" s="66"/>
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="35" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="65"/>
       <c r="I21" s="21" t="str">
         <f aca="false">IF(OR(G21="",H21=""),"",H21-G21)</f>
         <v/>
       </c>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="33"/>
-      <c r="N21" s="41"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="60"/>
+      <c r="L21" s="59"/>
+      <c r="M21" s="60"/>
+      <c r="N21" s="66"/>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="35" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="32"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="65"/>
       <c r="I22" s="21" t="str">
         <f aca="false">IF(OR(G22="",H22=""),"",H22-G22)</f>
         <v/>
       </c>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="41"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="60"/>
+      <c r="L22" s="59"/>
+      <c r="M22" s="60"/>
+      <c r="N22" s="66"/>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="35" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="32"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
       <c r="I23" s="21" t="str">
         <f aca="false">IF(OR(G23="",H23=""),"",H23-G23)</f>
         <v/>
       </c>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="33"/>
-      <c r="N23" s="41"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="59"/>
+      <c r="M23" s="60"/>
+      <c r="N23" s="66"/>
     </row>
     <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="35" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="32"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="60"/>
+      <c r="D24" s="60"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="60"/>
+      <c r="G24" s="65"/>
+      <c r="H24" s="65"/>
       <c r="I24" s="21" t="str">
         <f aca="false">IF(OR(G24="",H24=""),"",H24-G24)</f>
         <v/>
       </c>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="32"/>
-      <c r="M24" s="33"/>
-      <c r="N24" s="41"/>
+      <c r="J24" s="60"/>
+      <c r="K24" s="60"/>
+      <c r="L24" s="59"/>
+      <c r="M24" s="60"/>
+      <c r="N24" s="66"/>
     </row>
     <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="35" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="40"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="60"/>
+      <c r="D25" s="60"/>
+      <c r="E25" s="60"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
       <c r="I25" s="21" t="str">
         <f aca="false">IF(OR(G25="",H25=""),"",H25-G25)</f>
         <v/>
       </c>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="33"/>
-      <c r="N25" s="41"/>
+      <c r="J25" s="60"/>
+      <c r="K25" s="60"/>
+      <c r="L25" s="59"/>
+      <c r="M25" s="60"/>
+      <c r="N25" s="66"/>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="35" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="32"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
       <c r="I26" s="21" t="str">
         <f aca="false">IF(OR(G26="",H26=""),"",H26-G26)</f>
         <v/>
       </c>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="32"/>
-      <c r="M26" s="33"/>
-      <c r="N26" s="41"/>
+      <c r="J26" s="60"/>
+      <c r="K26" s="60"/>
+      <c r="L26" s="59"/>
+      <c r="M26" s="60"/>
+      <c r="N26" s="66"/>
     </row>
     <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="35" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="65"/>
+      <c r="H27" s="65"/>
       <c r="I27" s="21" t="str">
         <f aca="false">IF(OR(G27="",H27=""),"",H27-G27)</f>
         <v/>
       </c>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="32"/>
-      <c r="M27" s="33"/>
-      <c r="N27" s="41"/>
+      <c r="J27" s="60"/>
+      <c r="K27" s="60"/>
+      <c r="L27" s="59"/>
+      <c r="M27" s="60"/>
+      <c r="N27" s="66"/>
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="35" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="32"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="60"/>
+      <c r="D28" s="60"/>
+      <c r="E28" s="60"/>
+      <c r="F28" s="60"/>
+      <c r="G28" s="65"/>
+      <c r="H28" s="65"/>
       <c r="I28" s="21" t="str">
         <f aca="false">IF(OR(G28="",H28=""),"",H28-G28)</f>
         <v/>
       </c>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="33"/>
-      <c r="N28" s="41"/>
+      <c r="J28" s="60"/>
+      <c r="K28" s="60"/>
+      <c r="L28" s="59"/>
+      <c r="M28" s="60"/>
+      <c r="N28" s="66"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="24" t="s">
-        <v>259</v>
+        <v>391</v>
       </c>
       <c r="M30" s="21" t="str">
         <f aca="false">COUNTA(B5:B28)&amp;" مبادرة"</f>
         <v>0 مبادرة</v>
       </c>
-      <c r="N30" s="42" t="str">
+      <c r="N30" s="67" t="str">
         <f aca="false">IFERROR(AVERAGE(N5:N28),"")</f>
         <v/>
       </c>
@@ -4903,7 +6381,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4929,7 +6407,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>260</v>
+        <v>392</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4948,7 +6426,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>261</v>
+        <v>393</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4967,2733 +6445,2733 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>262</v>
+        <v>394</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>263</v>
+        <v>395</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>264</v>
+        <v>396</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>265</v>
+        <v>397</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>266</v>
+        <v>398</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>267</v>
+        <v>399</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>268</v>
+        <v>400</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>269</v>
+        <v>401</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>270</v>
+        <v>402</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>271</v>
+        <v>403</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>272</v>
+        <v>404</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>273</v>
+        <v>405</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>274</v>
+        <v>406</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>275</v>
+        <v>407</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>276</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>277</v>
+        <v>409</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>278</v>
+        <v>410</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E4" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F4" s="43" t="n">
+      <c r="F4" s="29" t="n">
         <v>49590690</v>
       </c>
-      <c r="G4" s="43" t="n">
+      <c r="G4" s="29" t="n">
         <f aca="false">F4*365/E4</f>
         <v>100003325.138122</v>
       </c>
-      <c r="H4" s="43" t="n">
+      <c r="H4" s="29" t="n">
         <v>766648</v>
       </c>
-      <c r="I4" s="43" t="n">
+      <c r="I4" s="29" t="n">
         <v>23493282</v>
       </c>
-      <c r="J4" s="29" t="n">
+      <c r="J4" s="57" t="n">
         <v>64.69</v>
       </c>
-      <c r="K4" s="44" t="n">
+      <c r="K4" s="68" t="n">
         <v>-0.223</v>
       </c>
-      <c r="L4" s="31" t="n">
+      <c r="L4" s="46" t="n">
         <v>0.006</v>
       </c>
-      <c r="M4" s="31" t="n">
+      <c r="M4" s="46" t="n">
         <v>0.53</v>
       </c>
-      <c r="N4" s="31" t="n">
+      <c r="N4" s="46" t="n">
         <v>0.281</v>
       </c>
       <c r="O4" s="21" t="s">
-        <v>281</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>282</v>
+        <v>414</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>283</v>
+        <v>415</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>284</v>
+        <v>416</v>
       </c>
       <c r="E5" s="21" t="n">
         <v>91</v>
       </c>
-      <c r="F5" s="43" t="n">
+      <c r="F5" s="29" t="n">
         <v>20001382</v>
       </c>
-      <c r="G5" s="43" t="n">
+      <c r="G5" s="29" t="n">
         <f aca="false">F5*365/E5</f>
         <v>80225323.4065934</v>
       </c>
-      <c r="H5" s="43" t="n">
+      <c r="H5" s="29" t="n">
         <v>324068</v>
       </c>
-      <c r="I5" s="43" t="n">
+      <c r="I5" s="29" t="n">
         <v>8841940</v>
       </c>
-      <c r="J5" s="29" t="n">
+      <c r="J5" s="57" t="n">
         <v>61.72</v>
       </c>
-      <c r="K5" s="45" t="n">
+      <c r="K5" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="31" t="n">
+      <c r="L5" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="31" t="n">
+      <c r="M5" s="46" t="n">
         <v>0.364</v>
       </c>
-      <c r="N5" s="31" t="n">
+      <c r="N5" s="46" t="n">
         <v>0</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>285</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>286</v>
+        <v>418</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>287</v>
+        <v>419</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>288</v>
+        <v>420</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E6" s="21" t="n">
         <v>91</v>
       </c>
-      <c r="F6" s="43" t="n">
+      <c r="F6" s="29" t="n">
         <v>15598002</v>
       </c>
-      <c r="G6" s="43" t="n">
+      <c r="G6" s="29" t="n">
         <f aca="false">F6*365/E6</f>
         <v>62563414.6153846</v>
       </c>
-      <c r="H6" s="43" t="n">
+      <c r="H6" s="29" t="n">
         <v>194466</v>
       </c>
-      <c r="I6" s="43" t="n">
+      <c r="I6" s="29" t="n">
         <v>7467484</v>
       </c>
-      <c r="J6" s="29" t="n">
+      <c r="J6" s="57" t="n">
         <v>80.21</v>
       </c>
-      <c r="K6" s="45" t="n">
+      <c r="K6" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="31" t="n">
+      <c r="L6" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="31" t="n">
+      <c r="M6" s="46" t="n">
         <v>0.441</v>
       </c>
-      <c r="N6" s="31" t="n">
+      <c r="N6" s="46" t="n">
         <v>0.344</v>
       </c>
       <c r="O6" s="21" t="s">
-        <v>289</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>290</v>
+        <v>422</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>291</v>
+        <v>423</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>292</v>
+        <v>424</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>284</v>
+        <v>416</v>
       </c>
       <c r="E7" s="21" t="n">
         <v>176</v>
       </c>
-      <c r="F7" s="43" t="n">
+      <c r="F7" s="29" t="n">
         <v>28047704</v>
       </c>
-      <c r="G7" s="43" t="n">
+      <c r="G7" s="29" t="n">
         <f aca="false">F7*365/E7</f>
         <v>58167113.4090909</v>
       </c>
-      <c r="H7" s="43" t="n">
+      <c r="H7" s="29" t="n">
         <v>333050</v>
       </c>
-      <c r="I7" s="43" t="n">
+      <c r="I7" s="29" t="n">
         <v>14552120</v>
       </c>
-      <c r="J7" s="29" t="n">
+      <c r="J7" s="57" t="n">
         <v>84.21</v>
       </c>
-      <c r="K7" s="46" t="n">
+      <c r="K7" s="70" t="n">
         <v>0.273</v>
       </c>
-      <c r="L7" s="31" t="n">
+      <c r="L7" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="31" t="n">
+      <c r="M7" s="46" t="n">
         <v>0.204</v>
       </c>
-      <c r="N7" s="31" t="n">
+      <c r="N7" s="46" t="n">
         <v>0.641</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>293</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>294</v>
+        <v>426</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>295</v>
+        <v>427</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E8" s="21" t="n">
         <v>180</v>
       </c>
-      <c r="F8" s="43" t="n">
+      <c r="F8" s="29" t="n">
         <v>20528975</v>
       </c>
-      <c r="G8" s="43" t="n">
+      <c r="G8" s="29" t="n">
         <f aca="false">F8*365/E8</f>
         <v>41628199.3055556</v>
       </c>
-      <c r="H8" s="43" t="n">
+      <c r="H8" s="29" t="n">
         <v>424628</v>
       </c>
-      <c r="I8" s="43" t="n">
+      <c r="I8" s="29" t="n">
         <v>2916708</v>
       </c>
-      <c r="J8" s="29" t="n">
+      <c r="J8" s="57" t="n">
         <v>48.35</v>
       </c>
-      <c r="K8" s="44" t="n">
+      <c r="K8" s="68" t="n">
         <v>-0.211</v>
       </c>
-      <c r="L8" s="31" t="n">
+      <c r="L8" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="31" t="n">
+      <c r="M8" s="46" t="n">
         <v>0.922</v>
       </c>
-      <c r="N8" s="31" t="n">
+      <c r="N8" s="46" t="n">
         <v>0.134</v>
       </c>
       <c r="O8" s="21" t="s">
-        <v>296</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>297</v>
+        <v>429</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>298</v>
+        <v>430</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>288</v>
+        <v>420</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>299</v>
+        <v>431</v>
       </c>
       <c r="E9" s="21" t="n">
         <v>55</v>
       </c>
-      <c r="F9" s="43" t="n">
+      <c r="F9" s="29" t="n">
         <v>6133992</v>
       </c>
-      <c r="G9" s="43" t="n">
+      <c r="G9" s="29" t="n">
         <f aca="false">F9*365/E9</f>
         <v>40707401.4545455</v>
       </c>
-      <c r="H9" s="43" t="n">
+      <c r="H9" s="29" t="n">
         <v>93189</v>
       </c>
-      <c r="I9" s="43" t="n">
+      <c r="I9" s="29" t="n">
         <v>2916316</v>
       </c>
-      <c r="J9" s="29" t="n">
+      <c r="J9" s="57" t="n">
         <v>65.82</v>
       </c>
-      <c r="K9" s="45" t="n">
+      <c r="K9" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="31" t="n">
+      <c r="L9" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M9" s="31" t="n">
+      <c r="M9" s="46" t="n">
         <v>0.501</v>
       </c>
-      <c r="N9" s="31" t="n">
+      <c r="N9" s="46" t="n">
         <v>0.309</v>
       </c>
       <c r="O9" s="21" t="s">
-        <v>281</v>
+        <v>413</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>300</v>
+        <v>432</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>301</v>
+        <v>433</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>288</v>
+        <v>420</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E10" s="21" t="n">
         <v>63</v>
       </c>
-      <c r="F10" s="43" t="n">
+      <c r="F10" s="29" t="n">
         <v>6430228</v>
       </c>
-      <c r="G10" s="43" t="n">
+      <c r="G10" s="29" t="n">
         <f aca="false">F10*365/E10</f>
         <v>37254495.5555556</v>
       </c>
-      <c r="H10" s="43" t="n">
+      <c r="H10" s="29" t="n">
         <v>108731</v>
       </c>
-      <c r="I10" s="43" t="n">
+      <c r="I10" s="29" t="n">
         <v>2831981</v>
       </c>
-      <c r="J10" s="29" t="n">
+      <c r="J10" s="57" t="n">
         <v>59.14</v>
       </c>
-      <c r="K10" s="45" t="n">
+      <c r="K10" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="31" t="n">
+      <c r="L10" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="31" t="n">
+      <c r="M10" s="46" t="n">
         <v>0.318</v>
       </c>
-      <c r="N10" s="31" t="n">
+      <c r="N10" s="46" t="n">
         <v>0.006</v>
       </c>
       <c r="O10" s="21" t="s">
-        <v>289</v>
+        <v>421</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>302</v>
+        <v>434</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>303</v>
+        <v>435</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>292</v>
+        <v>424</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E11" s="21" t="n">
         <v>65</v>
       </c>
-      <c r="F11" s="43" t="n">
+      <c r="F11" s="29" t="n">
         <v>6610805</v>
       </c>
-      <c r="G11" s="43" t="n">
+      <c r="G11" s="29" t="n">
         <f aca="false">F11*365/E11</f>
         <v>37122212.6923077</v>
       </c>
-      <c r="H11" s="43" t="n">
+      <c r="H11" s="29" t="n">
         <v>132653</v>
       </c>
-      <c r="I11" s="43" t="n">
+      <c r="I11" s="29" t="n">
         <v>2931550</v>
       </c>
-      <c r="J11" s="29" t="n">
+      <c r="J11" s="57" t="n">
         <v>49.84</v>
       </c>
-      <c r="K11" s="45" t="n">
+      <c r="K11" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="31" t="n">
+      <c r="L11" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="31" t="n">
+      <c r="M11" s="46" t="n">
         <v>0.436</v>
       </c>
-      <c r="N11" s="31" t="n">
+      <c r="N11" s="46" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="21" t="s">
-        <v>289</v>
+        <v>421</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>304</v>
+        <v>436</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>305</v>
+        <v>437</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E12" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F12" s="43" t="n">
+      <c r="F12" s="29" t="n">
         <v>18281399</v>
       </c>
-      <c r="G12" s="43" t="n">
+      <c r="G12" s="29" t="n">
         <f aca="false">F12*365/E12</f>
         <v>36865804.6132597</v>
       </c>
-      <c r="H12" s="43" t="n">
+      <c r="H12" s="29" t="n">
         <v>308074</v>
       </c>
-      <c r="I12" s="43" t="n">
+      <c r="I12" s="29" t="n">
         <v>8679738</v>
       </c>
-      <c r="J12" s="29" t="n">
+      <c r="J12" s="57" t="n">
         <v>59.34</v>
       </c>
-      <c r="K12" s="44" t="n">
+      <c r="K12" s="68" t="n">
         <v>-0.09</v>
       </c>
-      <c r="L12" s="31" t="n">
+      <c r="L12" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="31" t="n">
+      <c r="M12" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="N12" s="31" t="n">
+      <c r="N12" s="46" t="n">
         <v>0.277</v>
       </c>
       <c r="O12" s="21" t="s">
-        <v>289</v>
+        <v>421</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>306</v>
+        <v>438</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>307</v>
+        <v>439</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>288</v>
+        <v>420</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>299</v>
+        <v>431</v>
       </c>
       <c r="E13" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F13" s="43" t="n">
+      <c r="F13" s="29" t="n">
         <v>17320811</v>
       </c>
-      <c r="G13" s="43" t="n">
+      <c r="G13" s="29" t="n">
         <f aca="false">F13*365/E13</f>
         <v>34928707.2651934</v>
       </c>
-      <c r="H13" s="43" t="n">
+      <c r="H13" s="29" t="n">
         <v>256011</v>
       </c>
-      <c r="I13" s="43" t="n">
+      <c r="I13" s="29" t="n">
         <v>7729931</v>
       </c>
-      <c r="J13" s="29" t="n">
+      <c r="J13" s="57" t="n">
         <v>67.66</v>
       </c>
-      <c r="K13" s="44" t="n">
+      <c r="K13" s="68" t="n">
         <v>-0.119</v>
       </c>
-      <c r="L13" s="31" t="n">
+      <c r="L13" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="31" t="n">
+      <c r="M13" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="N13" s="31" t="n">
+      <c r="N13" s="46" t="n">
         <v>0.082</v>
       </c>
       <c r="O13" s="21" t="s">
-        <v>289</v>
+        <v>421</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>308</v>
+        <v>440</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>309</v>
+        <v>441</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E14" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F14" s="43" t="n">
+      <c r="F14" s="29" t="n">
         <v>16855372</v>
       </c>
-      <c r="G14" s="43" t="n">
+      <c r="G14" s="29" t="n">
         <f aca="false">F14*365/E14</f>
         <v>33990114.8066298</v>
       </c>
-      <c r="H14" s="43" t="n">
+      <c r="H14" s="29" t="n">
         <v>283446</v>
       </c>
-      <c r="I14" s="43" t="n">
+      <c r="I14" s="29" t="n">
         <v>2676944</v>
       </c>
-      <c r="J14" s="29" t="n">
+      <c r="J14" s="57" t="n">
         <v>59.47</v>
       </c>
-      <c r="K14" s="31" t="n">
+      <c r="K14" s="46" t="n">
         <v>-0.034</v>
       </c>
-      <c r="L14" s="31" t="n">
+      <c r="L14" s="46" t="n">
         <v>0.038</v>
       </c>
-      <c r="M14" s="31" t="n">
+      <c r="M14" s="46" t="n">
         <v>0.488</v>
       </c>
-      <c r="N14" s="31" t="n">
+      <c r="N14" s="46" t="n">
         <v>0.231</v>
       </c>
       <c r="O14" s="21" t="s">
-        <v>289</v>
+        <v>421</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>310</v>
+        <v>442</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>311</v>
+        <v>443</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>284</v>
+        <v>416</v>
       </c>
       <c r="E15" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F15" s="43" t="n">
+      <c r="F15" s="29" t="n">
         <v>15775248</v>
       </c>
-      <c r="G15" s="43" t="n">
+      <c r="G15" s="29" t="n">
         <f aca="false">F15*365/E15</f>
         <v>31811964.198895</v>
       </c>
-      <c r="H15" s="43" t="n">
+      <c r="H15" s="29" t="n">
         <v>249705</v>
       </c>
-      <c r="I15" s="43" t="n">
+      <c r="I15" s="29" t="n">
         <v>7806709</v>
       </c>
-      <c r="J15" s="29" t="n">
+      <c r="J15" s="57" t="n">
         <v>63.18</v>
       </c>
-      <c r="K15" s="44" t="n">
+      <c r="K15" s="68" t="n">
         <v>-0.217</v>
       </c>
-      <c r="L15" s="31" t="n">
+      <c r="L15" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="31" t="n">
+      <c r="M15" s="46" t="n">
         <v>0.894</v>
       </c>
-      <c r="N15" s="31" t="n">
+      <c r="N15" s="46" t="n">
         <v>0.458</v>
       </c>
       <c r="O15" s="21" t="s">
-        <v>296</v>
+        <v>428</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>312</v>
+        <v>444</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>313</v>
+        <v>445</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>314</v>
+        <v>446</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E16" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F16" s="43" t="n">
+      <c r="F16" s="29" t="n">
         <v>15719285</v>
       </c>
-      <c r="G16" s="43" t="n">
+      <c r="G16" s="29" t="n">
         <f aca="false">F16*365/E16</f>
         <v>31699110.6353591</v>
       </c>
-      <c r="H16" s="43" t="n">
+      <c r="H16" s="29" t="n">
         <v>211558</v>
       </c>
-      <c r="I16" s="43" t="n">
+      <c r="I16" s="29" t="n">
         <v>4791911</v>
       </c>
-      <c r="J16" s="29" t="n">
+      <c r="J16" s="57" t="n">
         <v>74.3</v>
       </c>
-      <c r="K16" s="46" t="n">
+      <c r="K16" s="70" t="n">
         <v>0.151</v>
       </c>
-      <c r="L16" s="31" t="n">
+      <c r="L16" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="31" t="n">
+      <c r="M16" s="46" t="n">
         <v>0.247</v>
       </c>
-      <c r="N16" s="31" t="n">
+      <c r="N16" s="46" t="n">
         <v>0.076</v>
       </c>
       <c r="O16" s="21" t="s">
-        <v>289</v>
+        <v>421</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>315</v>
+        <v>447</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>316</v>
+        <v>448</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>288</v>
+        <v>420</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E17" s="21" t="n">
         <v>57</v>
       </c>
-      <c r="F17" s="43" t="n">
+      <c r="F17" s="29" t="n">
         <v>4714627</v>
       </c>
-      <c r="G17" s="43" t="n">
+      <c r="G17" s="29" t="n">
         <f aca="false">F17*365/E17</f>
         <v>30190155.3508772</v>
       </c>
-      <c r="H17" s="43" t="n">
+      <c r="H17" s="29" t="n">
         <v>84547</v>
       </c>
-      <c r="I17" s="43" t="n">
+      <c r="I17" s="29" t="n">
         <v>2078856</v>
       </c>
-      <c r="J17" s="29" t="n">
+      <c r="J17" s="57" t="n">
         <v>55.76</v>
       </c>
-      <c r="K17" s="45" t="n">
+      <c r="K17" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="31" t="n">
+      <c r="L17" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="31" t="n">
+      <c r="M17" s="46" t="n">
         <v>0.432</v>
       </c>
-      <c r="N17" s="31" t="n">
+      <c r="N17" s="46" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="21" t="s">
-        <v>281</v>
+        <v>413</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>317</v>
+        <v>449</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>318</v>
+        <v>450</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E18" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F18" s="43" t="n">
+      <c r="F18" s="29" t="n">
         <v>14811456</v>
       </c>
-      <c r="G18" s="43" t="n">
+      <c r="G18" s="29" t="n">
         <f aca="false">F18*365/E18</f>
         <v>29868405.7458564</v>
       </c>
-      <c r="H18" s="43" t="n">
+      <c r="H18" s="29" t="n">
         <v>338888</v>
       </c>
-      <c r="I18" s="43" t="n">
+      <c r="I18" s="29" t="n">
         <v>6570004</v>
       </c>
-      <c r="J18" s="29" t="n">
+      <c r="J18" s="57" t="n">
         <v>43.71</v>
       </c>
-      <c r="K18" s="31" t="n">
+      <c r="K18" s="46" t="n">
         <v>-0.03</v>
       </c>
-      <c r="L18" s="31" t="n">
+      <c r="L18" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="31" t="n">
+      <c r="M18" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="N18" s="31" t="n">
+      <c r="N18" s="46" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="21" t="s">
-        <v>281</v>
+        <v>413</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>319</v>
+        <v>451</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>320</v>
+        <v>452</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>321</v>
+        <v>453</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>322</v>
+        <v>454</v>
       </c>
       <c r="E19" s="21" t="n">
         <v>130</v>
       </c>
-      <c r="F19" s="43" t="n">
+      <c r="F19" s="29" t="n">
         <v>9901510</v>
       </c>
-      <c r="G19" s="43" t="n">
+      <c r="G19" s="29" t="n">
         <f aca="false">F19*365/E19</f>
         <v>27800393.4615385</v>
       </c>
-      <c r="H19" s="43" t="n">
+      <c r="H19" s="29" t="n">
         <v>234974</v>
       </c>
-      <c r="I19" s="43" t="n">
+      <c r="I19" s="29" t="n">
         <v>4445436</v>
       </c>
-      <c r="J19" s="29" t="n">
+      <c r="J19" s="57" t="n">
         <v>42.14</v>
       </c>
-      <c r="K19" s="46" t="n">
+      <c r="K19" s="70" t="n">
         <v>0.275</v>
       </c>
-      <c r="L19" s="31" t="n">
+      <c r="L19" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="31" t="n">
+      <c r="M19" s="46" t="n">
         <v>0.478</v>
       </c>
-      <c r="N19" s="31" t="n">
+      <c r="N19" s="46" t="n">
         <v>0.048</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>293</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>323</v>
+        <v>455</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>324</v>
+        <v>456</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>325</v>
+        <v>457</v>
       </c>
       <c r="E20" s="21" t="n">
         <v>70</v>
       </c>
-      <c r="F20" s="43" t="n">
+      <c r="F20" s="29" t="n">
         <v>5015246</v>
       </c>
-      <c r="G20" s="43" t="n">
+      <c r="G20" s="29" t="n">
         <f aca="false">F20*365/E20</f>
         <v>26150925.5714286</v>
       </c>
-      <c r="H20" s="43" t="n">
+      <c r="H20" s="29" t="n">
         <v>115020</v>
       </c>
-      <c r="I20" s="43" t="n">
+      <c r="I20" s="29" t="n">
         <v>2229579</v>
       </c>
-      <c r="J20" s="29" t="n">
+      <c r="J20" s="57" t="n">
         <v>43.6</v>
       </c>
-      <c r="K20" s="45" t="n">
+      <c r="K20" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="31" t="n">
+      <c r="L20" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="31" t="n">
+      <c r="M20" s="46" t="n">
         <v>0.678</v>
       </c>
-      <c r="N20" s="31" t="n">
+      <c r="N20" s="46" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="21" t="s">
-        <v>285</v>
+        <v>417</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>326</v>
+        <v>458</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>327</v>
+        <v>459</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E21" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F21" s="43" t="n">
+      <c r="F21" s="29" t="n">
         <v>12392502</v>
       </c>
-      <c r="G21" s="43" t="n">
+      <c r="G21" s="29" t="n">
         <f aca="false">F21*365/E21</f>
         <v>24990404.5856354</v>
       </c>
-      <c r="H21" s="43" t="n">
+      <c r="H21" s="29" t="n">
         <v>284756</v>
       </c>
-      <c r="I21" s="43" t="n">
+      <c r="I21" s="29" t="n">
         <v>5504980</v>
       </c>
-      <c r="J21" s="29" t="n">
+      <c r="J21" s="57" t="n">
         <v>43.52</v>
       </c>
-      <c r="K21" s="44" t="n">
+      <c r="K21" s="68" t="n">
         <v>-0.112</v>
       </c>
-      <c r="L21" s="31" t="n">
+      <c r="L21" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M21" s="31" t="n">
+      <c r="M21" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="N21" s="31" t="n">
+      <c r="N21" s="46" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="21" t="s">
-        <v>289</v>
+        <v>421</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>328</v>
+        <v>460</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>329</v>
+        <v>461</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>292</v>
+        <v>424</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E22" s="21" t="n">
         <v>147</v>
       </c>
-      <c r="F22" s="43" t="n">
+      <c r="F22" s="29" t="n">
         <v>9737128</v>
       </c>
-      <c r="G22" s="43" t="n">
+      <c r="G22" s="29" t="n">
         <f aca="false">F22*365/E22</f>
         <v>24177222.585034</v>
       </c>
-      <c r="H22" s="43" t="n">
+      <c r="H22" s="29" t="n">
         <v>195205</v>
       </c>
-      <c r="I22" s="43" t="n">
+      <c r="I22" s="29" t="n">
         <v>4722403</v>
       </c>
-      <c r="J22" s="29" t="n">
+      <c r="J22" s="57" t="n">
         <v>49.88</v>
       </c>
-      <c r="K22" s="46" t="n">
+      <c r="K22" s="70" t="n">
         <v>0.068</v>
       </c>
-      <c r="L22" s="31" t="n">
+      <c r="L22" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="31" t="n">
+      <c r="M22" s="46" t="n">
         <v>0.673</v>
       </c>
-      <c r="N22" s="31" t="n">
+      <c r="N22" s="46" t="n">
         <v>0.329</v>
       </c>
       <c r="O22" s="21" t="s">
-        <v>296</v>
+        <v>428</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>331</v>
+        <v>463</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E23" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F23" s="43" t="n">
+      <c r="F23" s="29" t="n">
         <v>11129389</v>
       </c>
-      <c r="G23" s="43" t="n">
+      <c r="G23" s="29" t="n">
         <f aca="false">F23*365/E23</f>
         <v>22443243.0110497</v>
       </c>
-      <c r="H23" s="43" t="n">
+      <c r="H23" s="29" t="n">
         <v>233425</v>
       </c>
-      <c r="I23" s="43" t="n">
+      <c r="I23" s="29" t="n">
         <v>4924931</v>
       </c>
-      <c r="J23" s="29" t="n">
+      <c r="J23" s="57" t="n">
         <v>47.68</v>
       </c>
-      <c r="K23" s="46" t="n">
+      <c r="K23" s="70" t="n">
         <v>0.069</v>
       </c>
-      <c r="L23" s="31" t="n">
+      <c r="L23" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="31" t="n">
+      <c r="M23" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="N23" s="31" t="n">
+      <c r="N23" s="46" t="n">
         <v>0</v>
       </c>
       <c r="O23" s="21" t="s">
-        <v>289</v>
+        <v>421</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>332</v>
+        <v>464</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>333</v>
+        <v>465</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E24" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F24" s="43" t="n">
+      <c r="F24" s="29" t="n">
         <v>10708429</v>
       </c>
-      <c r="G24" s="43" t="n">
+      <c r="G24" s="29" t="n">
         <f aca="false">F24*365/E24</f>
         <v>21594345.7734807</v>
       </c>
-      <c r="H24" s="43" t="n">
+      <c r="H24" s="29" t="n">
         <v>246641</v>
       </c>
-      <c r="I24" s="43" t="n">
+      <c r="I24" s="29" t="n">
         <v>4740020</v>
       </c>
-      <c r="J24" s="29" t="n">
+      <c r="J24" s="57" t="n">
         <v>43.42</v>
       </c>
-      <c r="K24" s="31" t="n">
+      <c r="K24" s="46" t="n">
         <v>0.042</v>
       </c>
-      <c r="L24" s="31" t="n">
+      <c r="L24" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="31" t="n">
+      <c r="M24" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="N24" s="31" t="n">
+      <c r="N24" s="46" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="21" t="s">
-        <v>289</v>
+        <v>421</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>334</v>
+        <v>466</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>335</v>
+        <v>467</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>288</v>
+        <v>420</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>299</v>
+        <v>431</v>
       </c>
       <c r="E25" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F25" s="43" t="n">
+      <c r="F25" s="29" t="n">
         <v>10700092</v>
       </c>
-      <c r="G25" s="43" t="n">
+      <c r="G25" s="29" t="n">
         <f aca="false">F25*365/E25</f>
         <v>21577533.5911602</v>
       </c>
-      <c r="H25" s="43" t="n">
+      <c r="H25" s="29" t="n">
         <v>207031</v>
       </c>
-      <c r="I25" s="43" t="n">
+      <c r="I25" s="29" t="n">
         <v>4771577</v>
       </c>
-      <c r="J25" s="29" t="n">
+      <c r="J25" s="57" t="n">
         <v>51.68</v>
       </c>
-      <c r="K25" s="46" t="n">
+      <c r="K25" s="70" t="n">
         <v>0.177</v>
       </c>
-      <c r="L25" s="31" t="n">
+      <c r="L25" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M25" s="31" t="n">
+      <c r="M25" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="N25" s="31" t="n">
+      <c r="N25" s="46" t="n">
         <v>0.058</v>
       </c>
       <c r="O25" s="21" t="s">
-        <v>281</v>
+        <v>413</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>336</v>
+        <v>468</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>337</v>
+        <v>469</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>325</v>
+        <v>457</v>
       </c>
       <c r="E26" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F26" s="43" t="n">
+      <c r="F26" s="29" t="n">
         <v>10414834</v>
       </c>
-      <c r="G26" s="43" t="n">
+      <c r="G26" s="29" t="n">
         <f aca="false">F26*365/E26</f>
         <v>21002289.5580111</v>
       </c>
-      <c r="H26" s="43" t="n">
+      <c r="H26" s="29" t="n">
         <v>201217</v>
       </c>
-      <c r="I26" s="43" t="n">
+      <c r="I26" s="29" t="n">
         <v>4933540</v>
       </c>
-      <c r="J26" s="29" t="n">
+      <c r="J26" s="57" t="n">
         <v>51.76</v>
       </c>
-      <c r="K26" s="31" t="n">
+      <c r="K26" s="46" t="n">
         <v>-0.033</v>
       </c>
-      <c r="L26" s="31" t="n">
+      <c r="L26" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="31" t="n">
+      <c r="M26" s="46" t="n">
         <v>0.634</v>
       </c>
-      <c r="N26" s="31" t="n">
+      <c r="N26" s="46" t="n">
         <v>0.276</v>
       </c>
       <c r="O26" s="21" t="s">
-        <v>281</v>
+        <v>413</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>338</v>
+        <v>470</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>339</v>
+        <v>471</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>288</v>
+        <v>420</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>299</v>
+        <v>431</v>
       </c>
       <c r="E27" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F27" s="43" t="n">
+      <c r="F27" s="29" t="n">
         <v>9869940</v>
       </c>
-      <c r="G27" s="43" t="n">
+      <c r="G27" s="29" t="n">
         <f aca="false">F27*365/E27</f>
         <v>19903470.1657459</v>
       </c>
-      <c r="H27" s="43" t="n">
+      <c r="H27" s="29" t="n">
         <v>148911</v>
       </c>
-      <c r="I27" s="43" t="n">
+      <c r="I27" s="29" t="n">
         <v>4643058</v>
       </c>
-      <c r="J27" s="29" t="n">
+      <c r="J27" s="57" t="n">
         <v>66.28</v>
       </c>
-      <c r="K27" s="46" t="n">
+      <c r="K27" s="70" t="n">
         <v>0.083</v>
       </c>
-      <c r="L27" s="31" t="n">
+      <c r="L27" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="31" t="n">
+      <c r="M27" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="31" t="n">
+      <c r="N27" s="46" t="n">
         <v>0.27</v>
       </c>
       <c r="O27" s="21" t="s">
-        <v>340</v>
+        <v>472</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>341</v>
+        <v>473</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>342</v>
+        <v>474</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>284</v>
+        <v>416</v>
       </c>
       <c r="E28" s="21" t="n">
         <v>111</v>
       </c>
-      <c r="F28" s="43" t="n">
+      <c r="F28" s="29" t="n">
         <v>5875411</v>
       </c>
-      <c r="G28" s="43" t="n">
+      <c r="G28" s="29" t="n">
         <f aca="false">F28*365/E28</f>
         <v>19320045.1801802</v>
       </c>
-      <c r="H28" s="43" t="n">
+      <c r="H28" s="29" t="n">
         <v>75507</v>
       </c>
-      <c r="I28" s="43" t="n">
+      <c r="I28" s="29" t="n">
         <v>2834084</v>
       </c>
-      <c r="J28" s="29" t="n">
+      <c r="J28" s="57" t="n">
         <v>77.81</v>
       </c>
-      <c r="K28" s="45" t="n">
+      <c r="K28" s="69" t="n">
         <v>-0.033</v>
       </c>
-      <c r="L28" s="31" t="n">
+      <c r="L28" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M28" s="31" t="n">
+      <c r="M28" s="46" t="n">
         <v>0.493</v>
       </c>
-      <c r="N28" s="31" t="n">
+      <c r="N28" s="46" t="n">
         <v>0.349</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>293</v>
+        <v>425</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>343</v>
+        <v>475</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>344</v>
+        <v>476</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>325</v>
+        <v>457</v>
       </c>
       <c r="E29" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F29" s="43" t="n">
+      <c r="F29" s="29" t="n">
         <v>9512678</v>
       </c>
-      <c r="G29" s="43" t="n">
+      <c r="G29" s="29" t="n">
         <f aca="false">F29*365/E29</f>
         <v>19183024.6961326</v>
       </c>
-      <c r="H29" s="43" t="n">
+      <c r="H29" s="29" t="n">
         <v>147623</v>
       </c>
-      <c r="I29" s="43" t="n">
+      <c r="I29" s="29" t="n">
         <v>4558563</v>
       </c>
-      <c r="J29" s="29" t="n">
+      <c r="J29" s="57" t="n">
         <v>64.44</v>
       </c>
-      <c r="K29" s="31" t="n">
+      <c r="K29" s="46" t="n">
         <v>-0.045</v>
       </c>
-      <c r="L29" s="31" t="n">
+      <c r="L29" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M29" s="31" t="n">
+      <c r="M29" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="N29" s="31" t="n">
+      <c r="N29" s="46" t="n">
         <v>0.321</v>
       </c>
       <c r="O29" s="21" t="s">
-        <v>281</v>
+        <v>413</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>345</v>
+        <v>477</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>346</v>
+        <v>478</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E30" s="21" t="n">
         <v>92</v>
       </c>
-      <c r="F30" s="43" t="n">
+      <c r="F30" s="29" t="n">
         <v>4575739</v>
       </c>
-      <c r="G30" s="43" t="n">
+      <c r="G30" s="29" t="n">
         <f aca="false">F30*365/E30</f>
         <v>18153747.1195652</v>
       </c>
-      <c r="H30" s="43" t="n">
+      <c r="H30" s="29" t="n">
         <v>94310</v>
       </c>
-      <c r="I30" s="43" t="n">
+      <c r="I30" s="29" t="n">
         <v>2127665</v>
       </c>
-      <c r="J30" s="29" t="n">
+      <c r="J30" s="57" t="n">
         <v>48.52</v>
       </c>
-      <c r="K30" s="45" t="n">
+      <c r="K30" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="L30" s="31" t="n">
+      <c r="L30" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="31" t="n">
+      <c r="M30" s="46" t="n">
         <v>0.685</v>
       </c>
-      <c r="N30" s="31" t="n">
+      <c r="N30" s="46" t="n">
         <v>0.176</v>
       </c>
       <c r="O30" s="21" t="s">
-        <v>281</v>
+        <v>413</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>347</v>
+        <v>479</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>348</v>
+        <v>480</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>349</v>
+        <v>481</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>322</v>
+        <v>454</v>
       </c>
       <c r="E31" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F31" s="43" t="n">
+      <c r="F31" s="29" t="n">
         <v>8563678</v>
       </c>
-      <c r="G31" s="43" t="n">
+      <c r="G31" s="29" t="n">
         <f aca="false">F31*365/E31</f>
         <v>17269295.4143646</v>
       </c>
-      <c r="H31" s="43" t="n">
+      <c r="H31" s="29" t="n">
         <v>156380</v>
       </c>
-      <c r="I31" s="43" t="n">
+      <c r="I31" s="29" t="n">
         <v>3884721</v>
       </c>
-      <c r="J31" s="29" t="n">
+      <c r="J31" s="57" t="n">
         <v>54.76</v>
       </c>
-      <c r="K31" s="46" t="n">
+      <c r="K31" s="70" t="n">
         <v>0.186</v>
       </c>
-      <c r="L31" s="31" t="n">
+      <c r="L31" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M31" s="31" t="n">
+      <c r="M31" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="N31" s="31" t="n">
+      <c r="N31" s="46" t="n">
         <v>0.082</v>
       </c>
       <c r="O31" s="21" t="s">
-        <v>289</v>
+        <v>421</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>350</v>
+        <v>482</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>351</v>
+        <v>483</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>352</v>
+        <v>484</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>322</v>
+        <v>454</v>
       </c>
       <c r="E32" s="21" t="n">
         <v>69</v>
       </c>
-      <c r="F32" s="43" t="n">
+      <c r="F32" s="29" t="n">
         <v>3263896</v>
       </c>
-      <c r="G32" s="43" t="n">
+      <c r="G32" s="29" t="n">
         <f aca="false">F32*365/E32</f>
         <v>17265536.8115942</v>
       </c>
-      <c r="H32" s="43" t="n">
+      <c r="H32" s="29" t="n">
         <v>65707</v>
       </c>
-      <c r="I32" s="43" t="n">
+      <c r="I32" s="29" t="n">
         <v>1471112</v>
       </c>
-      <c r="J32" s="29" t="n">
+      <c r="J32" s="57" t="n">
         <v>49.67</v>
       </c>
-      <c r="K32" s="45" t="n">
+      <c r="K32" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="31" t="n">
+      <c r="L32" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M32" s="31" t="n">
+      <c r="M32" s="46" t="n">
         <v>0.597</v>
       </c>
-      <c r="N32" s="31" t="n">
+      <c r="N32" s="46" t="n">
         <v>0.103</v>
       </c>
       <c r="O32" s="20" t="s">
-        <v>293</v>
+        <v>425</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>353</v>
+        <v>485</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>354</v>
+        <v>486</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>321</v>
+        <v>453</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E33" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F33" s="43" t="n">
+      <c r="F33" s="29" t="n">
         <v>8483209</v>
       </c>
-      <c r="G33" s="43" t="n">
+      <c r="G33" s="29" t="n">
         <f aca="false">F33*365/E33</f>
         <v>17107023.6740332</v>
       </c>
-      <c r="H33" s="43" t="n">
+      <c r="H33" s="29" t="n">
         <v>166967</v>
       </c>
-      <c r="I33" s="43" t="n">
+      <c r="I33" s="29" t="n">
         <v>3774634</v>
       </c>
-      <c r="J33" s="29" t="n">
+      <c r="J33" s="57" t="n">
         <v>50.81</v>
       </c>
-      <c r="K33" s="46" t="n">
+      <c r="K33" s="70" t="n">
         <v>0.18</v>
       </c>
-      <c r="L33" s="31" t="n">
+      <c r="L33" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M33" s="31" t="n">
+      <c r="M33" s="46" t="n">
         <v>0.253</v>
       </c>
-      <c r="N33" s="31" t="n">
+      <c r="N33" s="46" t="n">
         <v>0.023</v>
       </c>
       <c r="O33" s="21" t="s">
-        <v>281</v>
+        <v>413</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>355</v>
+        <v>487</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>356</v>
+        <v>488</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>284</v>
+        <v>416</v>
       </c>
       <c r="E34" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F34" s="43" t="n">
+      <c r="F34" s="29" t="n">
         <v>8421901</v>
       </c>
-      <c r="G34" s="43" t="n">
+      <c r="G34" s="29" t="n">
         <f aca="false">F34*365/E34</f>
         <v>16983391.519337</v>
       </c>
-      <c r="H34" s="43" t="n">
+      <c r="H34" s="29" t="n">
         <v>76519</v>
       </c>
-      <c r="I34" s="43" t="n">
+      <c r="I34" s="29" t="n">
         <v>4263083</v>
       </c>
-      <c r="J34" s="29" t="n">
+      <c r="J34" s="57" t="n">
         <v>110.06</v>
       </c>
-      <c r="K34" s="44" t="n">
+      <c r="K34" s="68" t="n">
         <v>-0.084</v>
       </c>
-      <c r="L34" s="31" t="n">
+      <c r="L34" s="46" t="n">
         <v>0.015</v>
       </c>
-      <c r="M34" s="31" t="n">
+      <c r="M34" s="46" t="n">
         <v>0.357</v>
       </c>
-      <c r="N34" s="31" t="n">
+      <c r="N34" s="46" t="n">
         <v>0.559</v>
       </c>
       <c r="O34" s="21" t="s">
-        <v>340</v>
+        <v>472</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>357</v>
+        <v>489</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>358</v>
+        <v>490</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E35" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F35" s="43" t="n">
+      <c r="F35" s="29" t="n">
         <v>7821875</v>
       </c>
-      <c r="G35" s="43" t="n">
+      <c r="G35" s="29" t="n">
         <f aca="false">F35*365/E35</f>
         <v>15773394.3370166</v>
       </c>
-      <c r="H35" s="43" t="n">
+      <c r="H35" s="29" t="n">
         <v>165177</v>
       </c>
-      <c r="I35" s="43" t="n">
+      <c r="I35" s="29" t="n">
         <v>3471225</v>
       </c>
-      <c r="J35" s="29" t="n">
+      <c r="J35" s="57" t="n">
         <v>47.35</v>
       </c>
-      <c r="K35" s="44" t="n">
+      <c r="K35" s="68" t="n">
         <v>-0.533</v>
       </c>
-      <c r="L35" s="31" t="n">
+      <c r="L35" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M35" s="31" t="n">
+      <c r="M35" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="N35" s="31" t="n">
+      <c r="N35" s="46" t="n">
         <v>0</v>
       </c>
       <c r="O35" s="21" t="s">
-        <v>289</v>
+        <v>421</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>359</v>
+        <v>491</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>360</v>
+        <v>492</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>299</v>
+        <v>431</v>
       </c>
       <c r="E36" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F36" s="43" t="n">
+      <c r="F36" s="29" t="n">
         <v>7731204</v>
       </c>
-      <c r="G36" s="43" t="n">
+      <c r="G36" s="29" t="n">
         <f aca="false">F36*365/E36</f>
         <v>15590549.5027624</v>
       </c>
-      <c r="H36" s="43" t="n">
+      <c r="H36" s="29" t="n">
         <v>168510</v>
       </c>
-      <c r="I36" s="43" t="n">
+      <c r="I36" s="29" t="n">
         <v>3512113</v>
       </c>
-      <c r="J36" s="29" t="n">
+      <c r="J36" s="57" t="n">
         <v>45.88</v>
       </c>
-      <c r="K36" s="44" t="n">
+      <c r="K36" s="68" t="n">
         <v>-0.068</v>
       </c>
-      <c r="L36" s="31" t="n">
+      <c r="L36" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M36" s="31" t="n">
+      <c r="M36" s="46" t="n">
         <v>0.509</v>
       </c>
-      <c r="N36" s="31" t="n">
+      <c r="N36" s="46" t="n">
         <v>0.115</v>
       </c>
       <c r="O36" s="21" t="s">
-        <v>296</v>
+        <v>428</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>361</v>
+        <v>493</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>362</v>
+        <v>494</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>321</v>
+        <v>453</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>322</v>
+        <v>454</v>
       </c>
       <c r="E37" s="21" t="n">
         <v>26</v>
       </c>
-      <c r="F37" s="43" t="n">
+      <c r="F37" s="29" t="n">
         <v>1063910</v>
       </c>
-      <c r="G37" s="43" t="n">
+      <c r="G37" s="29" t="n">
         <f aca="false">F37*365/E37</f>
         <v>14935659.6153846</v>
       </c>
-      <c r="H37" s="43" t="n">
+      <c r="H37" s="29" t="n">
         <v>31905</v>
       </c>
-      <c r="I37" s="43" t="n">
+      <c r="I37" s="29" t="n">
         <v>486162</v>
       </c>
-      <c r="J37" s="29" t="n">
+      <c r="J37" s="57" t="n">
         <v>33.35</v>
       </c>
-      <c r="K37" s="45" t="n">
+      <c r="K37" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="L37" s="31" t="n">
+      <c r="L37" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M37" s="31" t="n">
+      <c r="M37" s="46" t="n">
         <v>0.601</v>
       </c>
-      <c r="N37" s="31" t="n">
+      <c r="N37" s="46" t="n">
         <v>0.114</v>
       </c>
       <c r="O37" s="21" t="s">
-        <v>363</v>
+        <v>274</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
-        <v>364</v>
+        <v>495</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>365</v>
+        <v>496</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>292</v>
+        <v>424</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E38" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F38" s="43" t="n">
+      <c r="F38" s="29" t="n">
         <v>7305589</v>
       </c>
-      <c r="G38" s="43" t="n">
+      <c r="G38" s="29" t="n">
         <f aca="false">F38*365/E38</f>
         <v>14732265.1104972</v>
       </c>
-      <c r="H38" s="43" t="n">
+      <c r="H38" s="29" t="n">
         <v>169734</v>
       </c>
-      <c r="I38" s="43" t="n">
+      <c r="I38" s="29" t="n">
         <v>3406904</v>
       </c>
-      <c r="J38" s="29" t="n">
+      <c r="J38" s="57" t="n">
         <v>43.04</v>
       </c>
-      <c r="K38" s="46" t="n">
+      <c r="K38" s="70" t="n">
         <v>0.083</v>
       </c>
-      <c r="L38" s="31" t="n">
+      <c r="L38" s="46" t="n">
         <v>0.015</v>
       </c>
-      <c r="M38" s="31" t="n">
+      <c r="M38" s="46" t="n">
         <v>0.459</v>
       </c>
-      <c r="N38" s="31" t="n">
+      <c r="N38" s="46" t="n">
         <v>0.167</v>
       </c>
       <c r="O38" s="21" t="s">
-        <v>281</v>
+        <v>413</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="21" t="s">
-        <v>366</v>
+        <v>497</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>367</v>
+        <v>498</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>284</v>
+        <v>416</v>
       </c>
       <c r="E39" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F39" s="43" t="n">
+      <c r="F39" s="29" t="n">
         <v>6769350</v>
       </c>
-      <c r="G39" s="43" t="n">
+      <c r="G39" s="29" t="n">
         <f aca="false">F39*365/E39</f>
         <v>13650899.1712707</v>
       </c>
-      <c r="H39" s="43" t="n">
+      <c r="H39" s="29" t="n">
         <v>97200</v>
       </c>
-      <c r="I39" s="43" t="n">
+      <c r="I39" s="29" t="n">
         <v>3076219</v>
       </c>
-      <c r="J39" s="29" t="n">
+      <c r="J39" s="57" t="n">
         <v>69.64</v>
       </c>
-      <c r="K39" s="44" t="n">
+      <c r="K39" s="68" t="n">
         <v>-0.126</v>
       </c>
-      <c r="L39" s="31" t="n">
+      <c r="L39" s="46" t="n">
         <v>0.002</v>
       </c>
-      <c r="M39" s="31" t="n">
+      <c r="M39" s="46" t="n">
         <v>0.497</v>
       </c>
-      <c r="N39" s="31" t="n">
+      <c r="N39" s="46" t="n">
         <v>0.106</v>
       </c>
       <c r="O39" s="21" t="s">
-        <v>281</v>
+        <v>413</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="21" t="s">
-        <v>368</v>
+        <v>499</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>369</v>
+        <v>500</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>321</v>
+        <v>453</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E40" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F40" s="43" t="n">
+      <c r="F40" s="29" t="n">
         <v>6763759</v>
       </c>
-      <c r="G40" s="43" t="n">
+      <c r="G40" s="29" t="n">
         <f aca="false">F40*365/E40</f>
         <v>13639624.5027624</v>
       </c>
-      <c r="H40" s="43" t="n">
+      <c r="H40" s="29" t="n">
         <v>97406</v>
       </c>
-      <c r="I40" s="43" t="n">
+      <c r="I40" s="29" t="n">
         <v>3314721</v>
       </c>
-      <c r="J40" s="29" t="n">
+      <c r="J40" s="57" t="n">
         <v>69.44</v>
       </c>
-      <c r="K40" s="31" t="n">
+      <c r="K40" s="46" t="n">
         <v>-0.044</v>
       </c>
-      <c r="L40" s="31" t="n">
+      <c r="L40" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M40" s="31" t="n">
+      <c r="M40" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="31" t="n">
+      <c r="N40" s="46" t="n">
         <v>0.373</v>
       </c>
       <c r="O40" s="21" t="s">
-        <v>281</v>
+        <v>413</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="21" t="s">
-        <v>370</v>
+        <v>501</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>371</v>
+        <v>502</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E41" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F41" s="43" t="n">
+      <c r="F41" s="29" t="n">
         <v>6600956</v>
       </c>
-      <c r="G41" s="43" t="n">
+      <c r="G41" s="29" t="n">
         <f aca="false">F41*365/E41</f>
         <v>13311320.1104972</v>
       </c>
-      <c r="H41" s="43" t="n">
+      <c r="H41" s="29" t="n">
         <v>146007</v>
       </c>
-      <c r="I41" s="43" t="n">
+      <c r="I41" s="29" t="n">
         <v>2925368</v>
       </c>
-      <c r="J41" s="29" t="n">
+      <c r="J41" s="57" t="n">
         <v>45.21</v>
       </c>
-      <c r="K41" s="44" t="n">
+      <c r="K41" s="68" t="n">
         <v>-0.121</v>
       </c>
-      <c r="L41" s="31" t="n">
+      <c r="L41" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M41" s="31" t="n">
+      <c r="M41" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="N41" s="31" t="n">
+      <c r="N41" s="46" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="21" t="s">
-        <v>281</v>
+        <v>413</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="21" t="s">
-        <v>372</v>
+        <v>503</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>373</v>
+        <v>504</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>321</v>
+        <v>453</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>322</v>
+        <v>454</v>
       </c>
       <c r="E42" s="21" t="n">
         <v>68</v>
       </c>
-      <c r="F42" s="43" t="n">
+      <c r="F42" s="29" t="n">
         <v>2479043</v>
       </c>
-      <c r="G42" s="43" t="n">
+      <c r="G42" s="29" t="n">
         <f aca="false">F42*365/E42</f>
         <v>13306627.8676471</v>
       </c>
-      <c r="H42" s="43" t="n">
+      <c r="H42" s="29" t="n">
         <v>54370</v>
       </c>
-      <c r="I42" s="43" t="n">
+      <c r="I42" s="29" t="n">
         <v>1114635</v>
       </c>
-      <c r="J42" s="29" t="n">
+      <c r="J42" s="57" t="n">
         <v>45.6</v>
       </c>
-      <c r="K42" s="45" t="n">
+      <c r="K42" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="31" t="n">
+      <c r="L42" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M42" s="31" t="n">
+      <c r="M42" s="46" t="n">
         <v>0.475</v>
       </c>
-      <c r="N42" s="31" t="n">
+      <c r="N42" s="46" t="n">
         <v>0.056</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>293</v>
+        <v>425</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
-        <v>374</v>
+        <v>505</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>375</v>
+        <v>506</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>288</v>
+        <v>420</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>325</v>
+        <v>457</v>
       </c>
       <c r="E43" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F43" s="43" t="n">
+      <c r="F43" s="29" t="n">
         <v>6302158</v>
       </c>
-      <c r="G43" s="43" t="n">
+      <c r="G43" s="29" t="n">
         <f aca="false">F43*365/E43</f>
         <v>12708771.6574586</v>
       </c>
-      <c r="H43" s="43" t="n">
+      <c r="H43" s="29" t="n">
         <v>123912</v>
       </c>
-      <c r="I43" s="43" t="n">
+      <c r="I43" s="29" t="n">
         <v>2839338</v>
       </c>
-      <c r="J43" s="29" t="n">
+      <c r="J43" s="57" t="n">
         <v>50.86</v>
       </c>
-      <c r="K43" s="46" t="n">
+      <c r="K43" s="70" t="n">
         <v>0.082</v>
       </c>
-      <c r="L43" s="31" t="n">
+      <c r="L43" s="46" t="n">
         <v>0.007</v>
       </c>
-      <c r="M43" s="31" t="n">
+      <c r="M43" s="46" t="n">
         <v>0.307</v>
       </c>
-      <c r="N43" s="31" t="n">
+      <c r="N43" s="46" t="n">
         <v>0.077</v>
       </c>
       <c r="O43" s="21" t="s">
-        <v>340</v>
+        <v>472</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
-        <v>376</v>
+        <v>507</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>377</v>
+        <v>508</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>378</v>
+        <v>509</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E44" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F44" s="43" t="n">
+      <c r="F44" s="29" t="n">
         <v>6083371</v>
       </c>
-      <c r="G44" s="43" t="n">
+      <c r="G44" s="29" t="n">
         <f aca="false">F44*365/E44</f>
         <v>12267571.3535912</v>
       </c>
-      <c r="H44" s="43" t="n">
+      <c r="H44" s="29" t="n">
         <v>107035</v>
       </c>
-      <c r="I44" s="43" t="n">
+      <c r="I44" s="29" t="n">
         <v>2759664</v>
       </c>
-      <c r="J44" s="29" t="n">
+      <c r="J44" s="57" t="n">
         <v>56.84</v>
       </c>
-      <c r="K44" s="46" t="n">
+      <c r="K44" s="70" t="n">
         <v>0.327</v>
       </c>
-      <c r="L44" s="31" t="n">
+      <c r="L44" s="46" t="n">
         <v>0.003</v>
       </c>
-      <c r="M44" s="31" t="n">
+      <c r="M44" s="46" t="n">
         <v>0.284</v>
       </c>
-      <c r="N44" s="31" t="n">
+      <c r="N44" s="46" t="n">
         <v>0.066</v>
       </c>
       <c r="O44" s="20" t="s">
-        <v>293</v>
+        <v>425</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="21" t="s">
-        <v>379</v>
+        <v>510</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>380</v>
+        <v>511</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>381</v>
+        <v>512</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>322</v>
+        <v>454</v>
       </c>
       <c r="E45" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F45" s="43" t="n">
+      <c r="F45" s="29" t="n">
         <v>5976488</v>
       </c>
-      <c r="G45" s="43" t="n">
+      <c r="G45" s="29" t="n">
         <f aca="false">F45*365/E45</f>
         <v>12052033.8121547</v>
       </c>
-      <c r="H45" s="43" t="n">
+      <c r="H45" s="29" t="n">
         <v>79761</v>
       </c>
-      <c r="I45" s="43" t="n">
+      <c r="I45" s="29" t="n">
         <v>2940822</v>
       </c>
-      <c r="J45" s="29" t="n">
+      <c r="J45" s="57" t="n">
         <v>74.93</v>
       </c>
-      <c r="K45" s="31" t="n">
+      <c r="K45" s="46" t="n">
         <v>-0.029</v>
       </c>
-      <c r="L45" s="31" t="n">
+      <c r="L45" s="46" t="n">
         <v>0.002</v>
       </c>
-      <c r="M45" s="31" t="n">
+      <c r="M45" s="46" t="n">
         <v>0.336</v>
       </c>
-      <c r="N45" s="31" t="n">
+      <c r="N45" s="46" t="n">
         <v>0.392</v>
       </c>
       <c r="O45" s="20" t="s">
-        <v>293</v>
+        <v>425</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="21" t="s">
-        <v>382</v>
+        <v>513</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>383</v>
+        <v>514</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E46" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F46" s="43" t="n">
+      <c r="F46" s="29" t="n">
         <v>5721087</v>
       </c>
-      <c r="G46" s="43" t="n">
+      <c r="G46" s="29" t="n">
         <f aca="false">F46*365/E46</f>
         <v>11536998.6464088</v>
       </c>
-      <c r="H46" s="43" t="n">
+      <c r="H46" s="29" t="n">
         <v>106073</v>
       </c>
-      <c r="I46" s="43" t="n">
+      <c r="I46" s="29" t="n">
         <v>2694118</v>
       </c>
-      <c r="J46" s="29" t="n">
+      <c r="J46" s="57" t="n">
         <v>53.94</v>
       </c>
-      <c r="K46" s="44" t="n">
+      <c r="K46" s="68" t="n">
         <v>-0.123</v>
       </c>
-      <c r="L46" s="31" t="n">
+      <c r="L46" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M46" s="31" t="n">
+      <c r="M46" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="N46" s="31" t="n">
+      <c r="N46" s="46" t="n">
         <v>0.236</v>
       </c>
       <c r="O46" s="21" t="s">
-        <v>289</v>
+        <v>421</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="21" t="s">
-        <v>384</v>
+        <v>515</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>385</v>
+        <v>516</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>321</v>
+        <v>453</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>386</v>
+        <v>517</v>
       </c>
       <c r="E47" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F47" s="43" t="n">
+      <c r="F47" s="29" t="n">
         <v>5714308</v>
       </c>
-      <c r="G47" s="43" t="n">
+      <c r="G47" s="29" t="n">
         <f aca="false">F47*365/E47</f>
         <v>11523328.2872928</v>
       </c>
-      <c r="H47" s="43" t="n">
+      <c r="H47" s="29" t="n">
         <v>117578</v>
       </c>
-      <c r="I47" s="43" t="n">
+      <c r="I47" s="29" t="n">
         <v>2650896</v>
       </c>
-      <c r="J47" s="29" t="n">
+      <c r="J47" s="57" t="n">
         <v>48.6</v>
       </c>
-      <c r="K47" s="31" t="n">
+      <c r="K47" s="46" t="n">
         <v>-0.009</v>
       </c>
-      <c r="L47" s="31" t="n">
+      <c r="L47" s="46" t="n">
         <v>0.007</v>
       </c>
-      <c r="M47" s="31" t="n">
+      <c r="M47" s="46" t="n">
         <v>0.531</v>
       </c>
-      <c r="N47" s="31" t="n">
+      <c r="N47" s="46" t="n">
         <v>0.184</v>
       </c>
       <c r="O47" s="21" t="s">
-        <v>340</v>
+        <v>472</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="21" t="s">
-        <v>387</v>
+        <v>518</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>388</v>
+        <v>519</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>349</v>
+        <v>481</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>322</v>
+        <v>454</v>
       </c>
       <c r="E48" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F48" s="43" t="n">
+      <c r="F48" s="29" t="n">
         <v>4846644</v>
       </c>
-      <c r="G48" s="43" t="n">
+      <c r="G48" s="29" t="n">
         <f aca="false">F48*365/E48</f>
         <v>9773619.1160221</v>
       </c>
-      <c r="H48" s="43" t="n">
+      <c r="H48" s="29" t="n">
         <v>84802</v>
       </c>
-      <c r="I48" s="43" t="n">
+      <c r="I48" s="29" t="n">
         <v>2153145</v>
       </c>
-      <c r="J48" s="29" t="n">
+      <c r="J48" s="57" t="n">
         <v>57.15</v>
       </c>
-      <c r="K48" s="46" t="n">
+      <c r="K48" s="70" t="n">
         <v>0.064</v>
       </c>
-      <c r="L48" s="31" t="n">
+      <c r="L48" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M48" s="31" t="n">
+      <c r="M48" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="N48" s="31" t="n">
+      <c r="N48" s="46" t="n">
         <v>0</v>
       </c>
       <c r="O48" s="21" t="s">
-        <v>281</v>
+        <v>413</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="21" t="s">
-        <v>389</v>
+        <v>520</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>390</v>
+        <v>521</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>349</v>
+        <v>481</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>325</v>
+        <v>457</v>
       </c>
       <c r="E49" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F49" s="43" t="n">
+      <c r="F49" s="29" t="n">
         <v>4569369</v>
       </c>
-      <c r="G49" s="43" t="n">
+      <c r="G49" s="29" t="n">
         <f aca="false">F49*365/E49</f>
         <v>9214473.39779006</v>
       </c>
-      <c r="H49" s="43" t="n">
+      <c r="H49" s="29" t="n">
         <v>72735</v>
       </c>
-      <c r="I49" s="43" t="n">
+      <c r="I49" s="29" t="n">
         <v>2133587</v>
       </c>
-      <c r="J49" s="29" t="n">
+      <c r="J49" s="57" t="n">
         <v>62.82</v>
       </c>
-      <c r="K49" s="46" t="n">
+      <c r="K49" s="70" t="n">
         <v>0.256</v>
       </c>
-      <c r="L49" s="31" t="n">
+      <c r="L49" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M49" s="31" t="n">
+      <c r="M49" s="46" t="n">
         <v>0.355</v>
       </c>
-      <c r="N49" s="31" t="n">
+      <c r="N49" s="46" t="n">
         <v>0.201</v>
       </c>
       <c r="O49" s="21" t="s">
-        <v>281</v>
+        <v>413</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="21" t="s">
-        <v>391</v>
+        <v>522</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>392</v>
+        <v>523</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E50" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F50" s="43" t="n">
+      <c r="F50" s="29" t="n">
         <v>4331347</v>
       </c>
-      <c r="G50" s="43" t="n">
+      <c r="G50" s="29" t="n">
         <f aca="false">F50*365/E50</f>
         <v>8734484.28176796</v>
       </c>
-      <c r="H50" s="43" t="n">
+      <c r="H50" s="29" t="n">
         <v>82571</v>
       </c>
-      <c r="I50" s="43" t="n">
+      <c r="I50" s="29" t="n">
         <v>1912969</v>
       </c>
-      <c r="J50" s="29" t="n">
+      <c r="J50" s="57" t="n">
         <v>52.46</v>
       </c>
-      <c r="K50" s="44" t="n">
+      <c r="K50" s="68" t="n">
         <v>-0.249</v>
       </c>
-      <c r="L50" s="31" t="n">
+      <c r="L50" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M50" s="31" t="n">
+      <c r="M50" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="N50" s="31" t="n">
+      <c r="N50" s="46" t="n">
         <v>0</v>
       </c>
       <c r="O50" s="21" t="s">
-        <v>289</v>
+        <v>421</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="21" t="s">
-        <v>393</v>
+        <v>524</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>394</v>
+        <v>525</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E51" s="21" t="n">
         <v>56</v>
       </c>
-      <c r="F51" s="43" t="n">
+      <c r="F51" s="29" t="n">
         <v>1285957</v>
       </c>
-      <c r="G51" s="43" t="n">
+      <c r="G51" s="29" t="n">
         <f aca="false">F51*365/E51</f>
         <v>8381684.01785714</v>
       </c>
-      <c r="H51" s="43" t="n">
+      <c r="H51" s="29" t="n">
         <v>25265</v>
       </c>
-      <c r="I51" s="43" t="n">
+      <c r="I51" s="29" t="n">
         <v>568922</v>
       </c>
-      <c r="J51" s="29" t="n">
+      <c r="J51" s="57" t="n">
         <v>50.9</v>
       </c>
-      <c r="K51" s="45" t="n">
+      <c r="K51" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="L51" s="31" t="n">
+      <c r="L51" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M51" s="31" t="n">
+      <c r="M51" s="46" t="n">
         <v>0.372</v>
       </c>
-      <c r="N51" s="31" t="n">
+      <c r="N51" s="46" t="n">
         <v>0</v>
       </c>
       <c r="O51" s="21" t="s">
-        <v>363</v>
+        <v>274</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="21" t="s">
-        <v>395</v>
+        <v>526</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>396</v>
+        <v>527</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>288</v>
+        <v>420</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>325</v>
+        <v>457</v>
       </c>
       <c r="E52" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F52" s="43" t="n">
+      <c r="F52" s="29" t="n">
         <v>3783052</v>
       </c>
-      <c r="G52" s="43" t="n">
+      <c r="G52" s="29" t="n">
         <f aca="false">F52*365/E52</f>
         <v>7628806.51933702</v>
       </c>
-      <c r="H52" s="43" t="n">
+      <c r="H52" s="29" t="n">
         <v>82333</v>
       </c>
-      <c r="I52" s="43" t="n">
+      <c r="I52" s="29" t="n">
         <v>1672588</v>
       </c>
-      <c r="J52" s="29" t="n">
+      <c r="J52" s="57" t="n">
         <v>45.95</v>
       </c>
-      <c r="K52" s="46" t="n">
+      <c r="K52" s="70" t="n">
         <v>0.137</v>
       </c>
-      <c r="L52" s="31" t="n">
+      <c r="L52" s="46" t="n">
         <v>0.008</v>
       </c>
-      <c r="M52" s="31" t="n">
+      <c r="M52" s="46" t="n">
         <v>0.335</v>
       </c>
-      <c r="N52" s="31" t="n">
+      <c r="N52" s="46" t="n">
         <v>0.017</v>
       </c>
       <c r="O52" s="21" t="s">
-        <v>296</v>
+        <v>428</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="21" t="s">
-        <v>397</v>
+        <v>528</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>398</v>
+        <v>529</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>292</v>
+        <v>424</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E53" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F53" s="43" t="n">
+      <c r="F53" s="29" t="n">
         <v>3334226</v>
       </c>
-      <c r="G53" s="43" t="n">
+      <c r="G53" s="29" t="n">
         <f aca="false">F53*365/E53</f>
         <v>6723715.41436464</v>
       </c>
-      <c r="H53" s="43" t="n">
+      <c r="H53" s="29" t="n">
         <v>60202</v>
       </c>
-      <c r="I53" s="43" t="n">
+      <c r="I53" s="29" t="n">
         <v>1601535</v>
       </c>
-      <c r="J53" s="29" t="n">
+      <c r="J53" s="57" t="n">
         <v>55.38</v>
       </c>
-      <c r="K53" s="31" t="n">
+      <c r="K53" s="46" t="n">
         <v>0.045</v>
       </c>
-      <c r="L53" s="31" t="n">
+      <c r="L53" s="46" t="n">
         <v>0.015</v>
       </c>
-      <c r="M53" s="31" t="n">
+      <c r="M53" s="46" t="n">
         <v>0.375</v>
       </c>
-      <c r="N53" s="31" t="n">
+      <c r="N53" s="46" t="n">
         <v>0.292</v>
       </c>
       <c r="O53" s="21" t="s">
-        <v>296</v>
+        <v>428</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="21" t="s">
-        <v>399</v>
+        <v>530</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>400</v>
+        <v>531</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>401</v>
+        <v>532</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>322</v>
+        <v>454</v>
       </c>
       <c r="E54" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F54" s="43" t="n">
+      <c r="F54" s="29" t="n">
         <v>3179944</v>
       </c>
-      <c r="G54" s="43" t="n">
+      <c r="G54" s="29" t="n">
         <f aca="false">F54*365/E54</f>
         <v>6412594.25414365</v>
       </c>
-      <c r="H54" s="43" t="n">
+      <c r="H54" s="29" t="n">
         <v>59244</v>
       </c>
-      <c r="I54" s="43" t="n">
+      <c r="I54" s="29" t="n">
         <v>1431054</v>
       </c>
-      <c r="J54" s="29" t="n">
+      <c r="J54" s="57" t="n">
         <v>53.68</v>
       </c>
-      <c r="K54" s="31" t="n">
+      <c r="K54" s="46" t="n">
         <v>-0.028</v>
       </c>
-      <c r="L54" s="31" t="n">
+      <c r="L54" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M54" s="31" t="n">
+      <c r="M54" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="N54" s="31" t="n">
+      <c r="N54" s="46" t="n">
         <v>0.077</v>
       </c>
       <c r="O54" s="21" t="s">
-        <v>281</v>
+        <v>413</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="21" t="s">
-        <v>402</v>
+        <v>533</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>403</v>
+        <v>534</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>321</v>
+        <v>453</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>325</v>
+        <v>457</v>
       </c>
       <c r="E55" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F55" s="43" t="n">
+      <c r="F55" s="29" t="n">
         <v>2708911</v>
       </c>
-      <c r="G55" s="43" t="n">
+      <c r="G55" s="29" t="n">
         <f aca="false">F55*365/E55</f>
         <v>5462721.07734807</v>
       </c>
-      <c r="H55" s="43" t="n">
+      <c r="H55" s="29" t="n">
         <v>50827</v>
       </c>
-      <c r="I55" s="43" t="n">
+      <c r="I55" s="29" t="n">
         <v>1262094</v>
       </c>
-      <c r="J55" s="29" t="n">
+      <c r="J55" s="57" t="n">
         <v>53.3</v>
       </c>
-      <c r="K55" s="46" t="n">
+      <c r="K55" s="70" t="n">
         <v>0.188</v>
       </c>
-      <c r="L55" s="31" t="n">
+      <c r="L55" s="46" t="n">
         <v>0.005</v>
       </c>
-      <c r="M55" s="31" t="n">
+      <c r="M55" s="46" t="n">
         <v>0.408</v>
       </c>
-      <c r="N55" s="31" t="n">
+      <c r="N55" s="46" t="n">
         <v>0.18</v>
       </c>
       <c r="O55" s="20" t="s">
-        <v>293</v>
+        <v>425</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="21" t="s">
-        <v>404</v>
+        <v>535</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>405</v>
+        <v>536</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>321</v>
+        <v>453</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="E56" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F56" s="43" t="n">
+      <c r="F56" s="29" t="n">
         <v>2574779</v>
       </c>
-      <c r="G56" s="43" t="n">
+      <c r="G56" s="29" t="n">
         <f aca="false">F56*365/E56</f>
         <v>5192233.89502762</v>
       </c>
-      <c r="H56" s="43" t="n">
+      <c r="H56" s="29" t="n">
         <v>73820</v>
       </c>
-      <c r="I56" s="43" t="n">
+      <c r="I56" s="29" t="n">
         <v>1204453</v>
       </c>
-      <c r="J56" s="29" t="n">
+      <c r="J56" s="57" t="n">
         <v>34.88</v>
       </c>
-      <c r="K56" s="46" t="n">
+      <c r="K56" s="70" t="n">
         <v>0.06</v>
       </c>
-      <c r="L56" s="31" t="n">
+      <c r="L56" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M56" s="31" t="n">
+      <c r="M56" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="N56" s="31" t="n">
+      <c r="N56" s="46" t="n">
         <v>0.194</v>
       </c>
       <c r="O56" s="21" t="s">
-        <v>296</v>
+        <v>428</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="21" t="s">
-        <v>406</v>
+        <v>537</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>407</v>
+        <v>538</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>408</v>
+        <v>539</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>322</v>
+        <v>454</v>
       </c>
       <c r="E57" s="21" t="n">
         <v>39</v>
       </c>
-      <c r="F57" s="43" t="n">
+      <c r="F57" s="29" t="n">
         <v>436617</v>
       </c>
-      <c r="G57" s="43" t="n">
+      <c r="G57" s="29" t="n">
         <f aca="false">F57*365/E57</f>
         <v>4086287.30769231</v>
       </c>
-      <c r="H57" s="43" t="n">
+      <c r="H57" s="29" t="n">
         <v>7649</v>
       </c>
-      <c r="I57" s="43" t="n">
+      <c r="I57" s="29" t="n">
         <v>206212</v>
       </c>
-      <c r="J57" s="29" t="n">
+      <c r="J57" s="57" t="n">
         <v>57.08</v>
       </c>
-      <c r="K57" s="45" t="n">
+      <c r="K57" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="L57" s="31" t="n">
+      <c r="L57" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M57" s="31" t="n">
+      <c r="M57" s="46" t="n">
         <v>0.4</v>
       </c>
-      <c r="N57" s="31" t="n">
+      <c r="N57" s="46" t="n">
         <v>0.249</v>
       </c>
       <c r="O57" s="20" t="s">
-        <v>293</v>
+        <v>425</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="21" t="s">
-        <v>409</v>
+        <v>540</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>410</v>
+        <v>541</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>411</v>
+        <v>542</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>322</v>
+        <v>454</v>
       </c>
       <c r="E58" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="F58" s="43" t="n">
+      <c r="F58" s="29" t="n">
         <v>46160</v>
       </c>
-      <c r="G58" s="43" t="n">
+      <c r="G58" s="29" t="n">
         <f aca="false">F58*365/E58</f>
         <v>2808066.66666667</v>
       </c>
-      <c r="H58" s="43" t="n">
+      <c r="H58" s="29" t="n">
         <v>924</v>
       </c>
-      <c r="I58" s="43" t="n">
+      <c r="I58" s="29" t="n">
         <v>21693</v>
       </c>
-      <c r="J58" s="29" t="n">
+      <c r="J58" s="57" t="n">
         <v>49.96</v>
       </c>
-      <c r="K58" s="45" t="n">
+      <c r="K58" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="L58" s="31" t="n">
+      <c r="L58" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M58" s="31" t="n">
+      <c r="M58" s="46" t="n">
         <v>0.505</v>
       </c>
-      <c r="N58" s="31" t="n">
+      <c r="N58" s="46" t="n">
         <v>0.167</v>
       </c>
       <c r="O58" s="20" t="s">
-        <v>293</v>
+        <v>425</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="47" t="s">
-        <v>412</v>
+      <c r="A59" s="71" t="s">
+        <v>543</v>
       </c>
       <c r="B59" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="F59" s="48" t="n">
+      <c r="F59" s="72" t="n">
         <f aca="false">SUM(F4:F58)</f>
         <v>502415662</v>
       </c>
-      <c r="G59" s="48" t="n">
+      <c r="G59" s="72" t="n">
         <f aca="false">SUM(G4:G58)</f>
         <v>1271395370.83428</v>
       </c>
-      <c r="H59" s="48" t="n">
+      <c r="H59" s="72" t="n">
         <f aca="false">SUM(H4:H58)</f>
         <v>8824895</v>
       </c>
-      <c r="I59" s="48" t="n">
+      <c r="I59" s="72" t="n">
         <f aca="false">SUM(I4:I58)</f>
         <v>219475297</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="49" t="s">
-        <v>413</v>
-      </c>
-      <c r="B61" s="49"/>
-      <c r="C61" s="49"/>
-      <c r="D61" s="49"/>
-      <c r="E61" s="49"/>
-      <c r="F61" s="49"/>
-      <c r="G61" s="49"/>
-      <c r="H61" s="49"/>
-      <c r="I61" s="49"/>
-      <c r="J61" s="49"/>
-      <c r="K61" s="49"/>
-      <c r="L61" s="49"/>
-      <c r="M61" s="49"/>
-      <c r="N61" s="49"/>
-      <c r="O61" s="49"/>
+      <c r="A61" s="73" t="s">
+        <v>544</v>
+      </c>
+      <c r="B61" s="73"/>
+      <c r="C61" s="73"/>
+      <c r="D61" s="73"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="73"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="73"/>
+      <c r="I61" s="73"/>
+      <c r="J61" s="73"/>
+      <c r="K61" s="73"/>
+      <c r="L61" s="73"/>
+      <c r="M61" s="73"/>
+      <c r="N61" s="73"/>
+      <c r="O61" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/docs/executive-plan.xlsx
+++ b/docs/executive-plan.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="554">
   <si>
     <t xml:space="preserve">نموذج الخطة التنفيذية — الإدارة التجارية</t>
   </si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">الدريس</t>
   </si>
   <si>
-    <t xml:space="preserve">1,300 محطة · 17.11% حصة سوقية</t>
+    <t xml:space="preserve">1,383 محطة · 18.95% حصة (الربع الثاني 2026)</t>
   </si>
   <si>
     <t xml:space="preserve">~126 محطة تحت الهوية · فاتورة 56.9 ر</t>
@@ -267,7 +267,7 @@
     <t xml:space="preserve">النقد (البديل) · ساسكو وقوستيشن (تطبيقات أفراد)</t>
   </si>
   <si>
-    <t xml:space="preserve">62.6% نقداً · ساسكو 653 محطة · قوستيشن 12 محطة</t>
+    <t xml:space="preserve">62.6% نقداً · ساسكو ~683 محطة · قوستيشن 12 محطة</t>
   </si>
   <si>
     <t xml:space="preserve">0.28% حصة التطبيق · 43 محطة بصفر</t>
@@ -420,7 +420,7 @@
     <t xml:space="preserve">مشغّل محطات</t>
   </si>
   <si>
-    <t xml:space="preserve">1,300 محطة · 17.11% حصة · ربح صافٍ 421.8 مليون ريال 2025 (+22%) · +69 محطة في الربع الرابع</t>
+    <t xml:space="preserve">1,383 محطة · 18.95% حصة (Q2 2026) · +83 محطة في النصف الأول 2026 · ربح صافٍ 421.8 مليون ريال 2025 (+22%)</t>
   </si>
   <si>
     <t xml:space="preserve">الوقود · الامتياز والتوريد · الديزل بالجملة · البطاقات (واعي)</t>
@@ -513,7 +513,7 @@
     <t xml:space="preserve">ساسكو</t>
   </si>
   <si>
-    <t xml:space="preserve">653 محطة · 8.59% حصة · +23 محطة في الربع الرابع · خطة 100 محطة سنوياً · استحوذت على نفط</t>
+    <t xml:space="preserve">~683 محطة (مُقدَّر Q1 2026) · 653 معلن Q4 2025 · +72 محطة 2024 · +81 محطة 2025 · +30 في Q1 2026 · هدف +100 سنوياً</t>
   </si>
   <si>
     <t xml:space="preserve">الوقود · البطاقات (كنترول) · تطبيق الأفراد · الامتياز</t>
@@ -624,123 +624,156 @@
     <t xml:space="preserve">حصص سوق محطات الوقود في المملكة</t>
   </si>
   <si>
-    <t xml:space="preserve">الربع الرابع 2025 · إجمالي السوق 7,600 محطة · المصدر: أرقام</t>
+    <t xml:space="preserve">الربع الثاني 2026 — نفس فترة بياناتنا · إجمالي السوق 7,300 محطة · المصدر: أرقام</t>
   </si>
   <si>
     <t xml:space="preserve">إجمالي محطات المملكة</t>
   </si>
   <si>
-    <t xml:space="preserve">نهاية 2025</t>
+    <t xml:space="preserve">الربع الثاني 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الربع الرابع 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السوق انكمش 300 محطة — تركّز لا نمو</t>
   </si>
   <si>
     <t xml:space="preserve">الشركة</t>
   </si>
   <si>
-    <t xml:space="preserve">الحصة السوقية</t>
+    <t xml:space="preserve">محطات Q4 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حصة Q4 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محطات Q2 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حصة Q2 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التغيّر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حالة الرقم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ملاحظة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">معلن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,300 (Q4 2025) ← 1,383 (Q2 2026) = +83 محطة في النصف الأول. تنبيه: مصدر صحفي ذكر +183 محطة في 6 أشهر ولا يتصالح مع سلسلة الأرباع — المعتمد هنا هو المحسوب من الحصص المعلنة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مُقدَّر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+30 محطة في الربع الأول 2026 · الرئيس التنفيذي (مايو 2026) يقول الشبكة ≈10% · هدف +100 سنوياً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جي أويل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">غير معلن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">آخر رقم منشور: الربع الرابع 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مزايا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أرامكو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عبر التسهيلات للتسويق · استحوذت على سهل لخدمات الوقود</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مجموع الشركات الرئيسية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أرقام: 32.3% عبر 2,456 محطة في الربع الرابع 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المستقلون والأفراد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السوق القابل للضمّ عبر الامتياز — ملعب المنفذ رقم ٨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أين نقف نحن — الربع الثاني 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">القياس</t>
   </si>
   <si>
     <t xml:space="preserve">عدد المحطات</t>
   </si>
   <si>
-    <t xml:space="preserve">المحسوب من الحصة</t>
+    <t xml:space="preserve">الحصة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الترتيب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">درب — اسمياً (كل المنظومة)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الثالث</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أعلى من جي أويل ومزايا وأرامكو — لكنه رقم سجل لا رقم تشغيل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">درب — تحت الهوية (126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الخامس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المحطات التي تحمل علامتنا فعلاً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">درب — مشغّلة بالكامل (80)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السادس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49 استثماري مشغّل + 31 امتياز مكتمل الهوية — الرقم الحقيقي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">في النصف الأول 2026 — نفس فترة بياناتنا بالضبط — أضافت الدريس 83 محطة ورفعت حصتها من 17.11% إلى 18.95%. ونحن في الفترة نفسها: ميزان صافٍ −43.8 مليون ريال.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السوق انكمش من 7,600 إلى 7,300 محطة بينما كبر الكبار — أي أن المستقلين يخرجون ويُضَمّون. هذا يفتح نافذة المنفذ رقم ٨ (الامتياز) ويغلقها في آن.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الفارق بين «355» و«80» هو الفارق بين المركز الثالث والسادس — وهو نفس الغموض في رقم «1,790 محطة» بصفقة سيارة آب. كل رقم شبكة هنا يجب أن يُسأل: مملوكة أم امتياز أم موردة؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التطبيقات والمنصات والبطاقات — التصنيف الصحيح</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ثلاثة أنواع تُخلط عادةً وهي مختلفة جوهرياً: تطبيق أفراد · منصة شركات · بطاقة/شريحة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الاسم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المالك/المشغّل</t>
   </si>
   <si>
     <t xml:space="preserve">الفئة</t>
   </si>
   <si>
-    <t xml:space="preserve">ملاحظة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مشغّل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الأكبر · +69 محطة في الربع الرابع · واعي (بطاقة) وبطاقات مسبقة الدفع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+23 محطة في الربع · تطبيق أفراد + كنترول للشركات · خطة 100 محطة سنوياً</t>
-  </si>
-  <si>
-    <t xml:space="preserve">جي أويل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مزايا</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أرامكو</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عبر التسهيلات للتسويق · استحوذت على سهل لخدمات الوقود</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مجموع الشركات الرئيسية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أرقام: 32.3% عبر 2,456 محطة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المستقلون والأفراد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السوق القابل للضمّ عبر الامتياز — وهو ملعب المنفذ رقم ٨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أين نقف نحن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">القياس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الحصة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المحسوب</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الترتيب</t>
-  </si>
-  <si>
-    <t xml:space="preserve">درب — اسمياً (كل المنظومة)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الثالث</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أعلى من جي أويل ومزايا وأرامكو — لكنه رقم سجل لا رقم تشغيل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">درب — تحت الهوية (126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الخامس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المحطات التي تحمل علامتنا فعلاً</t>
-  </si>
-  <si>
-    <t xml:space="preserve">درب — مشغّلة بالكامل (80)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السادس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49 استثماري مشغّل + 31 امتياز مكتمل الهوية — الرقم الحقيقي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الفارق بين «355» و«80» هو الفارق بين المركز الثالث والمركز السادس. وهو نفس الغموض الذي يكتنف رقم «1,790 محطة» في صفقة سيارة آب — كل رقم شبكة في هذا السوق يجب أن يُسأل عنه: مملوكة أم امتياز أم موردة؟</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التطبيقات والمنصات والبطاقات — التصنيف الصحيح</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ثلاثة أنواع تُخلط عادةً وهي مختلفة جوهرياً: تطبيق أفراد · منصة شركات · بطاقة/شريحة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الاسم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المالك/المشغّل</t>
-  </si>
-  <si>
     <t xml:space="preserve">التقنية</t>
   </si>
   <si>
@@ -777,10 +810,7 @@
     <t xml:space="preserve">QR + محفظة رقمية + نقاط</t>
   </si>
   <si>
-    <t xml:space="preserve">محطات ساسكو ونخلة ومغاسل أوتوسبا</t>
-  </si>
-  <si>
-    <t xml:space="preserve">غير معلن</t>
+    <t xml:space="preserve">محطات ساسكو ونخلة ومغاسل أوتوسبا — وطني</t>
   </si>
   <si>
     <t xml:space="preserve">شبكة مملوكة + نقاط تُستبدل في مطاعم ومقاهي المحطة</t>
@@ -850,9 +880,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.28% — التطبيق ميت عملياً · 62.6% نقد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
   </si>
   <si>
     <t xml:space="preserve">بترو آب</t>
@@ -1669,16 +1696,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="#,##0.00"/>
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="170" formatCode="0%"/>
+    <numFmt numFmtId="167" formatCode="\+#,##0;\-#,##0;\-"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00"/>
+    <numFmt numFmtId="170" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="171" formatCode="0%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1768,9 +1796,24 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="12"/>
       <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1902,7 +1945,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="76">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2015,11 +2058,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2031,11 +2082,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2043,39 +2094,27 @@
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2087,7 +2126,7 @@
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2103,11 +2142,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2127,15 +2170,15 @@
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2147,15 +2190,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2163,7 +2210,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2171,19 +2218,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2195,7 +2246,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3642,15 +3693,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3663,6 +3714,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -3674,16 +3727,27 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
         <v>199</v>
       </c>
       <c r="C3" s="26" t="n">
-        <v>7600</v>
+        <v>7300</v>
       </c>
       <c r="D3" s="27" t="s">
         <v>200</v>
+      </c>
+      <c r="E3" s="28" t="n">
+        <v>7600</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3691,184 +3755,229 @@
         <v>43</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>208</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="24" t="s">
         <v>56</v>
       </c>
       <c r="C5" s="28" t="n">
-        <v>0.1711</v>
-      </c>
-      <c r="D5" s="29" t="n">
         <v>1300</v>
       </c>
-      <c r="E5" s="29" t="n">
-        <f aca="false">ROUND(C5*$C$3,0)</f>
-        <v>1300</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D5" s="30" t="n">
+        <f aca="false">IFERROR(C5/$E$3,"")</f>
+        <v>0.171052631578947</v>
+      </c>
+      <c r="E5" s="28" t="n">
+        <v>1383</v>
+      </c>
+      <c r="F5" s="30" t="n">
+        <f aca="false">IFERROR(E5/$C$3,"")</f>
+        <v>0.189452054794521</v>
+      </c>
+      <c r="G5" s="31" t="n">
+        <f aca="false">IF(E5="","",E5-C5)</f>
+        <v>83</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="24" t="s">
         <v>160</v>
       </c>
       <c r="C6" s="28" t="n">
-        <v>0.0859</v>
-      </c>
-      <c r="D6" s="29" t="n">
         <v>653</v>
       </c>
-      <c r="E6" s="29" t="n">
-        <f aca="false">ROUND(C6*$C$3,0)</f>
-        <v>653</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D6" s="30" t="n">
+        <f aca="false">IFERROR(C6/$E$3,"")</f>
+        <v>0.085921052631579</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>683</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <f aca="false">IFERROR(E6/$C$3,"")</f>
+        <v>0.0935616438356164</v>
+      </c>
+      <c r="G6" s="31" t="n">
+        <f aca="false">IF(E6="","",E6-C6)</f>
+        <v>30</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>210</v>
+      <c r="B7" s="24" t="s">
+        <v>215</v>
       </c>
       <c r="C7" s="28" t="n">
-        <v>0.0232</v>
-      </c>
-      <c r="D7" s="29" t="n">
         <v>176</v>
       </c>
-      <c r="E7" s="29" t="n">
-        <f aca="false">ROUND(C7*$C$3,0)</f>
-        <v>176</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="G7" s="16"/>
-    </row>
-    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D7" s="30" t="n">
+        <f aca="false">IFERROR(C7/$E$3,"")</f>
+        <v>0.0231578947368421</v>
+      </c>
+      <c r="E7" s="21"/>
+      <c r="F7" s="30" t="n">
+        <f aca="false">IFERROR(E7/$C$3,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="31" t="str">
+        <f aca="false">IF(E7="","",E7-C7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>211</v>
+      <c r="B8" s="24" t="s">
+        <v>218</v>
       </c>
       <c r="C8" s="28" t="n">
-        <v>0.0227</v>
-      </c>
-      <c r="D8" s="29" t="n">
         <v>173</v>
       </c>
-      <c r="E8" s="29" t="n">
-        <f aca="false">ROUND(C8*$C$3,0)</f>
-        <v>173</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="G8" s="16"/>
-    </row>
-    <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D8" s="30" t="n">
+        <f aca="false">IFERROR(C8/$E$3,"")</f>
+        <v>0.0227631578947368</v>
+      </c>
+      <c r="E8" s="21"/>
+      <c r="F8" s="30" t="n">
+        <f aca="false">IFERROR(E8/$C$3,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="31" t="str">
+        <f aca="false">IF(E8="","",E8-C8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="17" t="s">
-        <v>212</v>
+      <c r="B9" s="24" t="s">
+        <v>219</v>
       </c>
       <c r="C9" s="28" t="n">
-        <v>0.0203</v>
-      </c>
-      <c r="D9" s="29" t="n">
         <v>154</v>
       </c>
-      <c r="E9" s="29" t="n">
-        <f aca="false">ROUND(C9*$C$3,0)</f>
-        <v>154</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>213</v>
+      <c r="D9" s="30" t="n">
+        <f aca="false">IFERROR(C9/$E$3,"")</f>
+        <v>0.0202631578947368</v>
+      </c>
+      <c r="E9" s="21"/>
+      <c r="F9" s="30" t="n">
+        <f aca="false">IFERROR(E9/$C$3,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="31" t="str">
+        <f aca="false">IF(E9="","",E9-C9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="30"/>
-      <c r="B10" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="C10" s="32" t="n">
+      <c r="A10" s="32"/>
+      <c r="B10" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="C10" s="34" t="n">
         <f aca="false">SUM(C5:C9)</f>
-        <v>0.3232</v>
-      </c>
-      <c r="D10" s="33" t="n">
-        <f aca="false">SUM(D5:D9)</f>
         <v>2456</v>
       </c>
-      <c r="E10" s="33" t="n">
-        <f aca="false">SUM(E5:E9)</f>
-        <v>2456</v>
-      </c>
-      <c r="F10" s="30"/>
-      <c r="G10" s="34" t="s">
-        <v>215</v>
+      <c r="D10" s="35" t="n">
+        <f aca="false">IFERROR(C10/$E$3,"")</f>
+        <v>0.323157894736842</v>
+      </c>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="36" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="35"/>
+      <c r="A11" s="21"/>
       <c r="B11" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="C11" s="36" t="n">
-        <f aca="false">1-C10</f>
-        <v>0.6768</v>
-      </c>
-      <c r="D11" s="37" t="n">
-        <f aca="false">$C$3-D10</f>
+        <v>223</v>
+      </c>
+      <c r="C11" s="28" t="n">
+        <f aca="false">$E$3-C10</f>
         <v>5144</v>
       </c>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="38" t="s">
-        <v>217</v>
+      <c r="D11" s="30" t="n">
+        <f aca="false">IFERROR(C11/$E$3,"")</f>
+        <v>0.676842105263158</v>
+      </c>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="16" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="39" t="s">
-        <v>218</v>
+      <c r="B13" s="37" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3876,105 +3985,145 @@
         <v>43</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>206</v>
+        <v>229</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="17" t="s">
-        <v>223</v>
+      <c r="B15" s="24" t="s">
+        <v>231</v>
       </c>
       <c r="C15" s="28" t="n">
-        <f aca="false">D15/$C$3</f>
-        <v>0.0467105263157895</v>
-      </c>
-      <c r="D15" s="29" t="n">
         <v>355</v>
       </c>
+      <c r="D15" s="30" t="n">
+        <f aca="false">C15/$C$3</f>
+        <v>0.0486301369863014</v>
+      </c>
       <c r="E15" s="21"/>
-      <c r="F15" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>225</v>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="17" t="s">
-        <v>226</v>
+      <c r="B16" s="24" t="s">
+        <v>234</v>
       </c>
       <c r="C16" s="28" t="n">
-        <f aca="false">D16/$C$3</f>
-        <v>0.0165789473684211</v>
-      </c>
-      <c r="D16" s="29" t="n">
         <v>126</v>
       </c>
+      <c r="D16" s="30" t="n">
+        <f aca="false">C16/$C$3</f>
+        <v>0.0172602739726027</v>
+      </c>
       <c r="E16" s="21"/>
-      <c r="F16" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>228</v>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="40" t="s">
-        <v>229</v>
-      </c>
-      <c r="C17" s="41" t="n">
-        <f aca="false">D17/$C$3</f>
-        <v>0.0105263157894737</v>
-      </c>
-      <c r="D17" s="42" t="n">
+      <c r="B17" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="C17" s="39" t="n">
         <v>80</v>
       </c>
+      <c r="D17" s="40" t="n">
+        <f aca="false">C17/$C$3</f>
+        <v>0.010958904109589</v>
+      </c>
       <c r="E17" s="19"/>
-      <c r="F17" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="G17" s="43" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="44" t="s">
-        <v>232</v>
-      </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="I17" s="41" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+    </row>
+    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="43" t="s">
+        <v>241</v>
+      </c>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+    </row>
+    <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="43" t="s">
+        <v>242</v>
+      </c>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="B19:G19"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B21:I21"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4009,7 +4158,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4026,7 +4175,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4046,342 +4195,342 @@
         <v>43</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>205</v>
+        <v>247</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="44" t="s">
         <v>160</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="F5" s="29" t="n">
-        <v>653</v>
-      </c>
-      <c r="G5" s="29" t="n">
-        <v>653</v>
-      </c>
-      <c r="H5" s="46" t="n">
+        <v>259</v>
+      </c>
+      <c r="F5" s="28" t="n">
+        <v>683</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>683</v>
+      </c>
+      <c r="H5" s="45" t="n">
         <f aca="false">IFERROR(G5/'حصص السوق'!$C$3,"")</f>
-        <v>0.085921052631579</v>
+        <v>0.0935616438356164</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="K5" s="16" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="L5" s="16" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="45" t="s">
-        <v>254</v>
+      <c r="B6" s="44" t="s">
+        <v>264</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="F6" s="29" t="n">
+        <v>266</v>
+      </c>
+      <c r="F6" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="G6" s="29" t="n">
+      <c r="G6" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="H6" s="46" t="n">
+      <c r="H6" s="45" t="n">
         <f aca="false">IFERROR(G6/'حصص السوق'!$C$3,"")</f>
-        <v>0.00157894736842105</v>
+        <v>0.00164383561643836</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="L6" s="16" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="M6" s="16" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="45" t="s">
-        <v>212</v>
+      <c r="B7" s="44" t="s">
+        <v>219</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="F7" s="29" t="n">
+        <v>272</v>
+      </c>
+      <c r="F7" s="28" t="n">
         <v>154</v>
       </c>
-      <c r="G7" s="29" t="n">
+      <c r="G7" s="28" t="n">
         <v>154</v>
       </c>
-      <c r="H7" s="46" t="n">
+      <c r="H7" s="45" t="n">
         <f aca="false">IFERROR(G7/'حصص السوق'!$C$3,"")</f>
-        <v>0.0202631578947368</v>
+        <v>0.0210958904109589</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J7" s="16" t="s">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="47" t="n">
+      <c r="A8" s="46" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="34" t="s">
-        <v>267</v>
-      </c>
-      <c r="C8" s="48" t="s">
-        <v>268</v>
-      </c>
-      <c r="D8" s="47" t="s">
-        <v>247</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>269</v>
-      </c>
-      <c r="F8" s="49" t="n">
+      <c r="B8" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>258</v>
+      </c>
+      <c r="E8" s="47" t="s">
+        <v>279</v>
+      </c>
+      <c r="F8" s="48" t="n">
         <v>355</v>
       </c>
-      <c r="G8" s="49" t="n">
+      <c r="G8" s="48" t="n">
         <v>355</v>
       </c>
-      <c r="H8" s="50" t="n">
+      <c r="H8" s="49" t="n">
         <f aca="false">IFERROR(G8/'حصص السوق'!$C$3,"")</f>
-        <v>0.0467105263157895</v>
-      </c>
-      <c r="I8" s="48" t="s">
-        <v>270</v>
-      </c>
-      <c r="J8" s="48" t="s">
-        <v>271</v>
-      </c>
-      <c r="K8" s="48" t="s">
-        <v>272</v>
-      </c>
-      <c r="L8" s="48" t="s">
-        <v>273</v>
-      </c>
-      <c r="M8" s="48" t="s">
-        <v>274</v>
+        <v>0.0486301369863014</v>
+      </c>
+      <c r="I8" s="47" t="s">
+        <v>280</v>
+      </c>
+      <c r="J8" s="47" t="s">
+        <v>281</v>
+      </c>
+      <c r="K8" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="L8" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="M8" s="47" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="51" t="s">
-        <v>275</v>
+      <c r="B9" s="50" t="s">
+        <v>284</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>46</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="F9" s="29" t="n">
+        <v>286</v>
+      </c>
+      <c r="F9" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="29" t="n">
+      <c r="G9" s="28" t="n">
         <v>5000</v>
       </c>
-      <c r="H9" s="46" t="n">
+      <c r="H9" s="45" t="n">
         <f aca="false">IFERROR(G9/'حصص السوق'!$C$3,"")</f>
-        <v>0.657894736842105</v>
+        <v>0.684931506849315</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="L9" s="16" t="s">
         <v>141</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="51" t="s">
-        <v>282</v>
+      <c r="B10" s="50" t="s">
+        <v>291</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>46</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="F10" s="29" t="n">
+        <v>286</v>
+      </c>
+      <c r="F10" s="28" t="n">
         <v>1790</v>
       </c>
-      <c r="G10" s="29" t="n">
+      <c r="G10" s="28" t="n">
         <v>2500</v>
       </c>
-      <c r="H10" s="46" t="n">
+      <c r="H10" s="45" t="n">
         <f aca="false">IFERROR(G10/'حصص السوق'!$C$3,"")</f>
-        <v>0.328947368421053</v>
+        <v>0.342465753424658</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J10" s="16" t="s">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="50" t="s">
         <v>183</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>46</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="F11" s="29" t="n">
+        <v>297</v>
+      </c>
+      <c r="F11" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="29" t="n">
+      <c r="G11" s="28" t="n">
         <v>5000</v>
       </c>
-      <c r="H11" s="46" t="n">
+      <c r="H11" s="45" t="n">
         <f aca="false">IFERROR(G11/'حصص السوق'!$C$3,"")</f>
-        <v>0.657894736842105</v>
+        <v>0.684931506849315</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J11" s="16" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="L11" s="16" t="s">
         <v>187</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="40" t="s">
-        <v>292</v>
+      <c r="B12" s="51" t="s">
+        <v>301</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>56</v>
@@ -4390,40 +4539,40 @@
         <v>46</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>293</v>
-      </c>
-      <c r="F12" s="29" t="n">
-        <v>1300</v>
-      </c>
-      <c r="G12" s="29" t="n">
-        <v>1300</v>
-      </c>
-      <c r="H12" s="46" t="n">
+        <v>302</v>
+      </c>
+      <c r="F12" s="28" t="n">
+        <v>1383</v>
+      </c>
+      <c r="G12" s="28" t="n">
+        <v>1383</v>
+      </c>
+      <c r="H12" s="45" t="n">
         <f aca="false">IFERROR(G12/'حصص السوق'!$C$3,"")</f>
-        <v>0.171052631578947</v>
+        <v>0.189452054794521</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J12" s="16" t="s">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="40" t="s">
-        <v>297</v>
+      <c r="B13" s="51" t="s">
+        <v>306</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>160</v>
@@ -4432,40 +4581,40 @@
         <v>46</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="F13" s="29" t="n">
-        <v>653</v>
-      </c>
-      <c r="G13" s="29" t="n">
-        <v>653</v>
-      </c>
-      <c r="H13" s="46" t="n">
+        <v>307</v>
+      </c>
+      <c r="F13" s="28" t="n">
+        <v>683</v>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>683</v>
+      </c>
+      <c r="H13" s="45" t="n">
         <f aca="false">IFERROR(G13/'حصص السوق'!$C$3,"")</f>
-        <v>0.085921052631579</v>
+        <v>0.0935616438356164</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J13" s="16" t="s">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="52" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="C15" s="53" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="D15" s="53"/>
       <c r="E15" s="53"/>
@@ -4480,10 +4629,10 @@
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="52" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="C16" s="53" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="D16" s="53"/>
       <c r="E16" s="53"/>
@@ -4498,10 +4647,10 @@
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="52" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="D17" s="53"/>
       <c r="E17" s="53"/>
@@ -4516,10 +4665,10 @@
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="52" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C18" s="53" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D18" s="53"/>
       <c r="E18" s="53"/>
@@ -4577,7 +4726,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4596,7 +4745,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4627,60 +4776,60 @@
         <v>49</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>52</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>53</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="54" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="C4" s="54" t="s">
         <v>46</v>
       </c>
       <c r="D4" s="55" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="E4" s="54" t="n">
         <v>6</v>
       </c>
       <c r="F4" s="54" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="G4" s="55" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="H4" s="54" t="n">
         <v>20</v>
@@ -4694,19 +4843,19 @@
         <v>2.33333333333333</v>
       </c>
       <c r="K4" s="55" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="L4" s="54" t="s">
         <v>72</v>
       </c>
       <c r="M4" s="55" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="N4" s="55" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="O4" s="54" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4726,17 +4875,17 @@
         <v>1271</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="H5" s="58"/>
       <c r="I5" s="57" t="str">
         <f aca="false">IF(H5="","",H5-E5)</f>
         <v/>
       </c>
-      <c r="J5" s="46" t="str">
+      <c r="J5" s="45" t="str">
         <f aca="false">IFERROR(IF(H5="","",(H5-E5)/E5),"")</f>
         <v/>
       </c>
@@ -4746,7 +4895,7 @@
       </c>
       <c r="M5" s="59"/>
       <c r="N5" s="16" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="O5" s="60"/>
     </row>
@@ -4767,17 +4916,17 @@
         <v>25</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="H6" s="58"/>
       <c r="I6" s="57" t="str">
         <f aca="false">IF(H6="","",H6-E6)</f>
         <v/>
       </c>
-      <c r="J6" s="46" t="str">
+      <c r="J6" s="45" t="str">
         <f aca="false">IFERROR(IF(H6="","",(H6-E6)/E6),"")</f>
         <v/>
       </c>
@@ -4787,7 +4936,7 @@
       </c>
       <c r="M6" s="59"/>
       <c r="N6" s="16" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="O6" s="60"/>
     </row>
@@ -4808,17 +4957,17 @@
         <v>39</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="H7" s="58"/>
       <c r="I7" s="57" t="str">
         <f aca="false">IF(H7="","",H7-E7)</f>
         <v/>
       </c>
-      <c r="J7" s="46" t="str">
+      <c r="J7" s="45" t="str">
         <f aca="false">IFERROR(IF(H7="","",(H7-E7)/E7),"")</f>
         <v/>
       </c>
@@ -4828,7 +4977,7 @@
       </c>
       <c r="M7" s="59"/>
       <c r="N7" s="16" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="O7" s="60"/>
     </row>
@@ -4849,17 +4998,17 @@
         <v>0</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="H8" s="58"/>
       <c r="I8" s="57" t="str">
         <f aca="false">IF(H8="","",H8-E8)</f>
         <v/>
       </c>
-      <c r="J8" s="46" t="str">
+      <c r="J8" s="45" t="str">
         <f aca="false">IFERROR(IF(H8="","",(H8-E8)/E8),"")</f>
         <v/>
       </c>
@@ -4869,7 +5018,7 @@
       </c>
       <c r="M8" s="59"/>
       <c r="N8" s="16" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="O8" s="60"/>
     </row>
@@ -4878,29 +5027,29 @@
         <v>5</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="E9" s="57" t="n">
         <v>0.28</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="H9" s="58"/>
       <c r="I9" s="57" t="str">
         <f aca="false">IF(H9="","",H9-E9)</f>
         <v/>
       </c>
-      <c r="J9" s="46" t="str">
+      <c r="J9" s="45" t="str">
         <f aca="false">IFERROR(IF(H9="","",(H9-E9)/E9),"")</f>
         <v/>
       </c>
@@ -4910,7 +5059,7 @@
       </c>
       <c r="M9" s="59"/>
       <c r="N9" s="16" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="O9" s="60"/>
     </row>
@@ -4919,29 +5068,29 @@
         <v>6</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E10" s="57" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="H10" s="58"/>
       <c r="I10" s="57" t="str">
         <f aca="false">IF(H10="","",H10-E10)</f>
         <v/>
       </c>
-      <c r="J10" s="46" t="str">
+      <c r="J10" s="45" t="str">
         <f aca="false">IFERROR(IF(H10="","",(H10-E10)/E10),"")</f>
         <v/>
       </c>
@@ -4951,7 +5100,7 @@
       </c>
       <c r="M10" s="59"/>
       <c r="N10" s="16" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="O10" s="60"/>
     </row>
@@ -4966,23 +5115,23 @@
         <v>89</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="E11" s="57" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="H11" s="58"/>
       <c r="I11" s="57" t="str">
         <f aca="false">IF(H11="","",H11-E11)</f>
         <v/>
       </c>
-      <c r="J11" s="46" t="str">
+      <c r="J11" s="45" t="str">
         <f aca="false">IFERROR(IF(H11="","",(H11-E11)/E11),"")</f>
         <v/>
       </c>
@@ -4992,7 +5141,7 @@
       </c>
       <c r="M11" s="59"/>
       <c r="N11" s="16" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="O11" s="60"/>
     </row>
@@ -5013,17 +5162,17 @@
         <v>31</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="H12" s="58"/>
       <c r="I12" s="57" t="str">
         <f aca="false">IF(H12="","",H12-E12)</f>
         <v/>
       </c>
-      <c r="J12" s="46" t="str">
+      <c r="J12" s="45" t="str">
         <f aca="false">IFERROR(IF(H12="","",(H12-E12)/E12),"")</f>
         <v/>
       </c>
@@ -5033,7 +5182,7 @@
       </c>
       <c r="M12" s="59"/>
       <c r="N12" s="16" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="O12" s="60"/>
     </row>
@@ -5054,17 +5203,17 @@
         <v>0</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="H13" s="58"/>
       <c r="I13" s="57" t="str">
         <f aca="false">IF(H13="","",H13-E13)</f>
         <v/>
       </c>
-      <c r="J13" s="46" t="str">
+      <c r="J13" s="45" t="str">
         <f aca="false">IFERROR(IF(H13="","",(H13-E13)/E13),"")</f>
         <v/>
       </c>
@@ -5074,7 +5223,7 @@
       </c>
       <c r="M13" s="59"/>
       <c r="N13" s="16" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="O13" s="60"/>
     </row>
@@ -5095,17 +5244,17 @@
         <v>0</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="H14" s="58"/>
       <c r="I14" s="57" t="str">
         <f aca="false">IF(H14="","",H14-E14)</f>
         <v/>
       </c>
-      <c r="J14" s="46" t="str">
+      <c r="J14" s="45" t="str">
         <f aca="false">IFERROR(IF(H14="","",(H14-E14)/E14),"")</f>
         <v/>
       </c>
@@ -5115,7 +5264,7 @@
       </c>
       <c r="M14" s="59"/>
       <c r="N14" s="16" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="O14" s="60"/>
     </row>
@@ -5130,23 +5279,23 @@
         <v>46</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="E15" s="57" t="n">
         <v>6</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="H15" s="58"/>
       <c r="I15" s="57" t="str">
         <f aca="false">IF(H15="","",H15-E15)</f>
         <v/>
       </c>
-      <c r="J15" s="46" t="str">
+      <c r="J15" s="45" t="str">
         <f aca="false">IFERROR(IF(H15="","",(H15-E15)/E15),"")</f>
         <v/>
       </c>
@@ -5156,7 +5305,7 @@
       </c>
       <c r="M15" s="59"/>
       <c r="N15" s="16" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="O15" s="60"/>
     </row>
@@ -5171,23 +5320,23 @@
         <v>46</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="E16" s="57" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="H16" s="58"/>
       <c r="I16" s="57" t="str">
         <f aca="false">IF(H16="","",H16-E16)</f>
         <v/>
       </c>
-      <c r="J16" s="46" t="str">
+      <c r="J16" s="45" t="str">
         <f aca="false">IFERROR(IF(H16="","",(H16-E16)/E16),"")</f>
         <v/>
       </c>
@@ -5197,16 +5346,16 @@
       </c>
       <c r="M16" s="59"/>
       <c r="N16" s="16" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="O16" s="60"/>
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="C18" s="61" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="D18" s="61"/>
       <c r="E18" s="61"/>
@@ -5267,7 +5416,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5288,44 +5437,44 @@
         <v>44</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="35" t="n">
+      <c r="A4" s="62" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="38" t="s">
-        <v>332</v>
-      </c>
-      <c r="D4" s="62" t="n">
+      <c r="C4" s="63" t="s">
+        <v>341</v>
+      </c>
+      <c r="D4" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E5</f>
         <v>1271</v>
       </c>
@@ -5333,7 +5482,7 @@
       <c r="F4" s="58"/>
       <c r="G4" s="58"/>
       <c r="H4" s="58"/>
-      <c r="I4" s="62" t="str">
+      <c r="I4" s="64" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H5="","",'الخطة التنفيذية'!H5)</f>
         <v/>
       </c>
@@ -5341,22 +5490,22 @@
         <f aca="false">IF(H4="","",IF(H4=I4,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K4" s="46" t="str">
+      <c r="K4" s="45" t="str">
         <f aca="false">IFERROR(IF(H4="","",(H4-D4)/D4),"")</f>
         <v/>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="35" t="n">
+      <c r="A5" s="62" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="38" t="s">
-        <v>335</v>
-      </c>
-      <c r="D5" s="62" t="n">
+      <c r="C5" s="63" t="s">
+        <v>344</v>
+      </c>
+      <c r="D5" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E6</f>
         <v>25</v>
       </c>
@@ -5364,7 +5513,7 @@
       <c r="F5" s="58"/>
       <c r="G5" s="58"/>
       <c r="H5" s="58"/>
-      <c r="I5" s="62" t="str">
+      <c r="I5" s="64" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H6="","",'الخطة التنفيذية'!H6)</f>
         <v/>
       </c>
@@ -5372,22 +5521,22 @@
         <f aca="false">IF(H5="","",IF(H5=I5,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K5" s="46" t="str">
+      <c r="K5" s="45" t="str">
         <f aca="false">IFERROR(IF(H5="","",(H5-D5)/D5),"")</f>
         <v/>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="35" t="n">
+      <c r="A6" s="62" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="38" t="s">
-        <v>337</v>
-      </c>
-      <c r="D6" s="62" t="n">
+      <c r="C6" s="63" t="s">
+        <v>346</v>
+      </c>
+      <c r="D6" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E7</f>
         <v>39</v>
       </c>
@@ -5395,7 +5544,7 @@
       <c r="F6" s="58"/>
       <c r="G6" s="58"/>
       <c r="H6" s="58"/>
-      <c r="I6" s="62" t="str">
+      <c r="I6" s="64" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H7="","",'الخطة التنفيذية'!H7)</f>
         <v/>
       </c>
@@ -5403,22 +5552,22 @@
         <f aca="false">IF(H6="","",IF(H6=I6,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K6" s="46" t="str">
+      <c r="K6" s="45" t="str">
         <f aca="false">IFERROR(IF(H6="","",(H6-D6)/D6),"")</f>
         <v/>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="35" t="n">
+      <c r="A7" s="62" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="38" t="s">
-        <v>340</v>
-      </c>
-      <c r="D7" s="62" t="n">
+      <c r="C7" s="63" t="s">
+        <v>349</v>
+      </c>
+      <c r="D7" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E8</f>
         <v>0</v>
       </c>
@@ -5426,7 +5575,7 @@
       <c r="F7" s="58"/>
       <c r="G7" s="58"/>
       <c r="H7" s="58"/>
-      <c r="I7" s="62" t="str">
+      <c r="I7" s="64" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H8="","",'الخطة التنفيذية'!H8)</f>
         <v/>
       </c>
@@ -5434,22 +5583,22 @@
         <f aca="false">IF(H7="","",IF(H7=I7,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K7" s="46" t="str">
+      <c r="K7" s="45" t="str">
         <f aca="false">IFERROR(IF(H7="","",(H7-D7)/D7),"")</f>
         <v/>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="35" t="n">
+      <c r="A8" s="62" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>341</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>345</v>
-      </c>
-      <c r="D8" s="62" t="n">
+        <v>350</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>354</v>
+      </c>
+      <c r="D8" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E9</f>
         <v>0.28</v>
       </c>
@@ -5457,7 +5606,7 @@
       <c r="F8" s="58"/>
       <c r="G8" s="58"/>
       <c r="H8" s="58"/>
-      <c r="I8" s="62" t="str">
+      <c r="I8" s="64" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H9="","",'الخطة التنفيذية'!H9)</f>
         <v/>
       </c>
@@ -5465,22 +5614,22 @@
         <f aca="false">IF(H8="","",IF(H8=I8,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K8" s="46" t="str">
+      <c r="K8" s="45" t="str">
         <f aca="false">IFERROR(IF(H8="","",(H8-D8)/D8),"")</f>
         <v/>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="35" t="n">
+      <c r="A9" s="62" t="n">
         <v>6</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>346</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>349</v>
-      </c>
-      <c r="D9" s="62" t="n">
+        <v>355</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>358</v>
+      </c>
+      <c r="D9" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E10</f>
         <v>0</v>
       </c>
@@ -5488,7 +5637,7 @@
       <c r="F9" s="58"/>
       <c r="G9" s="58"/>
       <c r="H9" s="58"/>
-      <c r="I9" s="62" t="str">
+      <c r="I9" s="64" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H10="","",'الخطة التنفيذية'!H10)</f>
         <v/>
       </c>
@@ -5496,22 +5645,22 @@
         <f aca="false">IF(H9="","",IF(H9=I9,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K9" s="46" t="str">
+      <c r="K9" s="45" t="str">
         <f aca="false">IFERROR(IF(H9="","",(H9-D9)/D9),"")</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="35" t="n">
+      <c r="A10" s="62" t="n">
         <v>7</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="38" t="s">
-        <v>353</v>
-      </c>
-      <c r="D10" s="62" t="n">
+      <c r="C10" s="63" t="s">
+        <v>362</v>
+      </c>
+      <c r="D10" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E11</f>
         <v>0</v>
       </c>
@@ -5519,7 +5668,7 @@
       <c r="F10" s="58"/>
       <c r="G10" s="58"/>
       <c r="H10" s="58"/>
-      <c r="I10" s="62" t="str">
+      <c r="I10" s="64" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H11="","",'الخطة التنفيذية'!H11)</f>
         <v/>
       </c>
@@ -5527,22 +5676,22 @@
         <f aca="false">IF(H10="","",IF(H10=I10,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K10" s="46" t="str">
+      <c r="K10" s="45" t="str">
         <f aca="false">IFERROR(IF(H10="","",(H10-D10)/D10),"")</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="35" t="n">
+      <c r="A11" s="62" t="n">
         <v>8</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="38" t="s">
-        <v>356</v>
-      </c>
-      <c r="D11" s="62" t="n">
+      <c r="C11" s="63" t="s">
+        <v>365</v>
+      </c>
+      <c r="D11" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E12</f>
         <v>31</v>
       </c>
@@ -5550,7 +5699,7 @@
       <c r="F11" s="58"/>
       <c r="G11" s="58"/>
       <c r="H11" s="58"/>
-      <c r="I11" s="62" t="str">
+      <c r="I11" s="64" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H12="","",'الخطة التنفيذية'!H12)</f>
         <v/>
       </c>
@@ -5558,22 +5707,22 @@
         <f aca="false">IF(H11="","",IF(H11=I11,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K11" s="46" t="str">
+      <c r="K11" s="45" t="str">
         <f aca="false">IFERROR(IF(H11="","",(H11-D11)/D11),"")</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="35" t="n">
+      <c r="A12" s="62" t="n">
         <v>9</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="38" t="s">
-        <v>359</v>
-      </c>
-      <c r="D12" s="62" t="n">
+      <c r="C12" s="63" t="s">
+        <v>368</v>
+      </c>
+      <c r="D12" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E13</f>
         <v>0</v>
       </c>
@@ -5581,7 +5730,7 @@
       <c r="F12" s="58"/>
       <c r="G12" s="58"/>
       <c r="H12" s="58"/>
-      <c r="I12" s="62" t="str">
+      <c r="I12" s="64" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H13="","",'الخطة التنفيذية'!H13)</f>
         <v/>
       </c>
@@ -5589,22 +5738,22 @@
         <f aca="false">IF(H12="","",IF(H12=I12,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K12" s="46" t="str">
+      <c r="K12" s="45" t="str">
         <f aca="false">IFERROR(IF(H12="","",(H12-D12)/D12),"")</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="35" t="n">
+      <c r="A13" s="62" t="n">
         <v>10</v>
       </c>
       <c r="B13" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="38" t="s">
-        <v>362</v>
-      </c>
-      <c r="D13" s="62" t="n">
+      <c r="C13" s="63" t="s">
+        <v>371</v>
+      </c>
+      <c r="D13" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E14</f>
         <v>0</v>
       </c>
@@ -5612,7 +5761,7 @@
       <c r="F13" s="58"/>
       <c r="G13" s="58"/>
       <c r="H13" s="58"/>
-      <c r="I13" s="62" t="str">
+      <c r="I13" s="64" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H14="","",'الخطة التنفيذية'!H14)</f>
         <v/>
       </c>
@@ -5620,22 +5769,22 @@
         <f aca="false">IF(H13="","",IF(H13=I13,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K13" s="46" t="str">
+      <c r="K13" s="45" t="str">
         <f aca="false">IFERROR(IF(H13="","",(H13-D13)/D13),"")</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="35" t="n">
+      <c r="A14" s="62" t="n">
         <v>11</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="38" t="s">
-        <v>364</v>
-      </c>
-      <c r="D14" s="62" t="n">
+      <c r="C14" s="63" t="s">
+        <v>373</v>
+      </c>
+      <c r="D14" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E15</f>
         <v>6</v>
       </c>
@@ -5643,7 +5792,7 @@
       <c r="F14" s="58"/>
       <c r="G14" s="58"/>
       <c r="H14" s="58"/>
-      <c r="I14" s="62" t="str">
+      <c r="I14" s="64" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H15="","",'الخطة التنفيذية'!H15)</f>
         <v/>
       </c>
@@ -5651,22 +5800,22 @@
         <f aca="false">IF(H14="","",IF(H14=I14,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K14" s="46" t="str">
+      <c r="K14" s="45" t="str">
         <f aca="false">IFERROR(IF(H14="","",(H14-D14)/D14),"")</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="35" t="n">
+      <c r="A15" s="62" t="n">
         <v>12</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="C15" s="38" t="s">
-        <v>368</v>
-      </c>
-      <c r="D15" s="62" t="n">
+      <c r="C15" s="63" t="s">
+        <v>377</v>
+      </c>
+      <c r="D15" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E16</f>
         <v>0</v>
       </c>
@@ -5674,7 +5823,7 @@
       <c r="F15" s="58"/>
       <c r="G15" s="58"/>
       <c r="H15" s="58"/>
-      <c r="I15" s="62" t="str">
+      <c r="I15" s="64" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H16="","",'الخطة التنفيذية'!H16)</f>
         <v/>
       </c>
@@ -5682,7 +5831,7 @@
         <f aca="false">IF(H15="","",IF(H15=I15,"مطابق","مختلف"))</f>
         <v/>
       </c>
-      <c r="K15" s="46" t="str">
+      <c r="K15" s="45" t="str">
         <f aca="false">IFERROR(IF(H15="","",(H15-D15)/D15),"")</f>
         <v/>
       </c>
@@ -5726,7 +5875,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5744,7 +5893,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5765,51 +5914,51 @@
         <v>43</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>53</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="J3" s="15" t="s">
         <v>54</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="54" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="C4" s="54" t="s">
         <v>61</v>
@@ -5821,12 +5970,12 @@
         <v>66</v>
       </c>
       <c r="F4" s="54" t="s">
-        <v>327</v>
-      </c>
-      <c r="G4" s="63" t="n">
+        <v>336</v>
+      </c>
+      <c r="G4" s="65" t="n">
         <v>46235</v>
       </c>
-      <c r="H4" s="63" t="n">
+      <c r="H4" s="65" t="n">
         <v>46326</v>
       </c>
       <c r="I4" s="54" t="n">
@@ -5837,20 +5986,20 @@
         <v>1</v>
       </c>
       <c r="K4" s="54" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="L4" s="55" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="M4" s="54" t="s">
-        <v>329</v>
-      </c>
-      <c r="N4" s="64" t="n">
+        <v>338</v>
+      </c>
+      <c r="N4" s="66" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="35" t="n">
+      <c r="A5" s="62" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="59"/>
@@ -5858,8 +6007,8 @@
       <c r="D5" s="60"/>
       <c r="E5" s="60"/>
       <c r="F5" s="60"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
       <c r="I5" s="21" t="str">
         <f aca="false">IF(OR(G5="",H5=""),"",H5-G5)</f>
         <v/>
@@ -5868,10 +6017,10 @@
       <c r="K5" s="60"/>
       <c r="L5" s="59"/>
       <c r="M5" s="60"/>
-      <c r="N5" s="66"/>
+      <c r="N5" s="68"/>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="35" t="n">
+      <c r="A6" s="62" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="59"/>
@@ -5879,8 +6028,8 @@
       <c r="D6" s="60"/>
       <c r="E6" s="60"/>
       <c r="F6" s="60"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
       <c r="I6" s="21" t="str">
         <f aca="false">IF(OR(G6="",H6=""),"",H6-G6)</f>
         <v/>
@@ -5889,10 +6038,10 @@
       <c r="K6" s="60"/>
       <c r="L6" s="59"/>
       <c r="M6" s="60"/>
-      <c r="N6" s="66"/>
+      <c r="N6" s="68"/>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="35" t="n">
+      <c r="A7" s="62" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="59"/>
@@ -5900,8 +6049,8 @@
       <c r="D7" s="60"/>
       <c r="E7" s="60"/>
       <c r="F7" s="60"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
       <c r="I7" s="21" t="str">
         <f aca="false">IF(OR(G7="",H7=""),"",H7-G7)</f>
         <v/>
@@ -5910,10 +6059,10 @@
       <c r="K7" s="60"/>
       <c r="L7" s="59"/>
       <c r="M7" s="60"/>
-      <c r="N7" s="66"/>
+      <c r="N7" s="68"/>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="35" t="n">
+      <c r="A8" s="62" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="59"/>
@@ -5921,8 +6070,8 @@
       <c r="D8" s="60"/>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
-      <c r="G8" s="65"/>
-      <c r="H8" s="65"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
       <c r="I8" s="21" t="str">
         <f aca="false">IF(OR(G8="",H8=""),"",H8-G8)</f>
         <v/>
@@ -5931,10 +6080,10 @@
       <c r="K8" s="60"/>
       <c r="L8" s="59"/>
       <c r="M8" s="60"/>
-      <c r="N8" s="66"/>
+      <c r="N8" s="68"/>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="35" t="n">
+      <c r="A9" s="62" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="59"/>
@@ -5942,8 +6091,8 @@
       <c r="D9" s="60"/>
       <c r="E9" s="60"/>
       <c r="F9" s="60"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
       <c r="I9" s="21" t="str">
         <f aca="false">IF(OR(G9="",H9=""),"",H9-G9)</f>
         <v/>
@@ -5952,10 +6101,10 @@
       <c r="K9" s="60"/>
       <c r="L9" s="59"/>
       <c r="M9" s="60"/>
-      <c r="N9" s="66"/>
+      <c r="N9" s="68"/>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="35" t="n">
+      <c r="A10" s="62" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="59"/>
@@ -5963,8 +6112,8 @@
       <c r="D10" s="60"/>
       <c r="E10" s="60"/>
       <c r="F10" s="60"/>
-      <c r="G10" s="65"/>
-      <c r="H10" s="65"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
       <c r="I10" s="21" t="str">
         <f aca="false">IF(OR(G10="",H10=""),"",H10-G10)</f>
         <v/>
@@ -5973,10 +6122,10 @@
       <c r="K10" s="60"/>
       <c r="L10" s="59"/>
       <c r="M10" s="60"/>
-      <c r="N10" s="66"/>
+      <c r="N10" s="68"/>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="35" t="n">
+      <c r="A11" s="62" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="59"/>
@@ -5984,8 +6133,8 @@
       <c r="D11" s="60"/>
       <c r="E11" s="60"/>
       <c r="F11" s="60"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
       <c r="I11" s="21" t="str">
         <f aca="false">IF(OR(G11="",H11=""),"",H11-G11)</f>
         <v/>
@@ -5994,10 +6143,10 @@
       <c r="K11" s="60"/>
       <c r="L11" s="59"/>
       <c r="M11" s="60"/>
-      <c r="N11" s="66"/>
+      <c r="N11" s="68"/>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="35" t="n">
+      <c r="A12" s="62" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="59"/>
@@ -6005,8 +6154,8 @@
       <c r="D12" s="60"/>
       <c r="E12" s="60"/>
       <c r="F12" s="60"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
       <c r="I12" s="21" t="str">
         <f aca="false">IF(OR(G12="",H12=""),"",H12-G12)</f>
         <v/>
@@ -6015,10 +6164,10 @@
       <c r="K12" s="60"/>
       <c r="L12" s="59"/>
       <c r="M12" s="60"/>
-      <c r="N12" s="66"/>
+      <c r="N12" s="68"/>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="35" t="n">
+      <c r="A13" s="62" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="59"/>
@@ -6026,8 +6175,8 @@
       <c r="D13" s="60"/>
       <c r="E13" s="60"/>
       <c r="F13" s="60"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="65"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
       <c r="I13" s="21" t="str">
         <f aca="false">IF(OR(G13="",H13=""),"",H13-G13)</f>
         <v/>
@@ -6036,10 +6185,10 @@
       <c r="K13" s="60"/>
       <c r="L13" s="59"/>
       <c r="M13" s="60"/>
-      <c r="N13" s="66"/>
+      <c r="N13" s="68"/>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="35" t="n">
+      <c r="A14" s="62" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="59"/>
@@ -6047,8 +6196,8 @@
       <c r="D14" s="60"/>
       <c r="E14" s="60"/>
       <c r="F14" s="60"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="67"/>
       <c r="I14" s="21" t="str">
         <f aca="false">IF(OR(G14="",H14=""),"",H14-G14)</f>
         <v/>
@@ -6057,10 +6206,10 @@
       <c r="K14" s="60"/>
       <c r="L14" s="59"/>
       <c r="M14" s="60"/>
-      <c r="N14" s="66"/>
+      <c r="N14" s="68"/>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="35" t="n">
+      <c r="A15" s="62" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="59"/>
@@ -6068,8 +6217,8 @@
       <c r="D15" s="60"/>
       <c r="E15" s="60"/>
       <c r="F15" s="60"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="65"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
       <c r="I15" s="21" t="str">
         <f aca="false">IF(OR(G15="",H15=""),"",H15-G15)</f>
         <v/>
@@ -6078,10 +6227,10 @@
       <c r="K15" s="60"/>
       <c r="L15" s="59"/>
       <c r="M15" s="60"/>
-      <c r="N15" s="66"/>
+      <c r="N15" s="68"/>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="35" t="n">
+      <c r="A16" s="62" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="59"/>
@@ -6089,8 +6238,8 @@
       <c r="D16" s="60"/>
       <c r="E16" s="60"/>
       <c r="F16" s="60"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="65"/>
+      <c r="G16" s="67"/>
+      <c r="H16" s="67"/>
       <c r="I16" s="21" t="str">
         <f aca="false">IF(OR(G16="",H16=""),"",H16-G16)</f>
         <v/>
@@ -6099,10 +6248,10 @@
       <c r="K16" s="60"/>
       <c r="L16" s="59"/>
       <c r="M16" s="60"/>
-      <c r="N16" s="66"/>
+      <c r="N16" s="68"/>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="35" t="n">
+      <c r="A17" s="62" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="59"/>
@@ -6110,8 +6259,8 @@
       <c r="D17" s="60"/>
       <c r="E17" s="60"/>
       <c r="F17" s="60"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="65"/>
+      <c r="G17" s="67"/>
+      <c r="H17" s="67"/>
       <c r="I17" s="21" t="str">
         <f aca="false">IF(OR(G17="",H17=""),"",H17-G17)</f>
         <v/>
@@ -6120,10 +6269,10 @@
       <c r="K17" s="60"/>
       <c r="L17" s="59"/>
       <c r="M17" s="60"/>
-      <c r="N17" s="66"/>
+      <c r="N17" s="68"/>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="35" t="n">
+      <c r="A18" s="62" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="59"/>
@@ -6131,8 +6280,8 @@
       <c r="D18" s="60"/>
       <c r="E18" s="60"/>
       <c r="F18" s="60"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="65"/>
+      <c r="G18" s="67"/>
+      <c r="H18" s="67"/>
       <c r="I18" s="21" t="str">
         <f aca="false">IF(OR(G18="",H18=""),"",H18-G18)</f>
         <v/>
@@ -6141,10 +6290,10 @@
       <c r="K18" s="60"/>
       <c r="L18" s="59"/>
       <c r="M18" s="60"/>
-      <c r="N18" s="66"/>
+      <c r="N18" s="68"/>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="35" t="n">
+      <c r="A19" s="62" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="59"/>
@@ -6152,8 +6301,8 @@
       <c r="D19" s="60"/>
       <c r="E19" s="60"/>
       <c r="F19" s="60"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="65"/>
+      <c r="G19" s="67"/>
+      <c r="H19" s="67"/>
       <c r="I19" s="21" t="str">
         <f aca="false">IF(OR(G19="",H19=""),"",H19-G19)</f>
         <v/>
@@ -6162,10 +6311,10 @@
       <c r="K19" s="60"/>
       <c r="L19" s="59"/>
       <c r="M19" s="60"/>
-      <c r="N19" s="66"/>
+      <c r="N19" s="68"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="35" t="n">
+      <c r="A20" s="62" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="59"/>
@@ -6173,8 +6322,8 @@
       <c r="D20" s="60"/>
       <c r="E20" s="60"/>
       <c r="F20" s="60"/>
-      <c r="G20" s="65"/>
-      <c r="H20" s="65"/>
+      <c r="G20" s="67"/>
+      <c r="H20" s="67"/>
       <c r="I20" s="21" t="str">
         <f aca="false">IF(OR(G20="",H20=""),"",H20-G20)</f>
         <v/>
@@ -6183,10 +6332,10 @@
       <c r="K20" s="60"/>
       <c r="L20" s="59"/>
       <c r="M20" s="60"/>
-      <c r="N20" s="66"/>
+      <c r="N20" s="68"/>
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="35" t="n">
+      <c r="A21" s="62" t="n">
         <v>17</v>
       </c>
       <c r="B21" s="59"/>
@@ -6194,8 +6343,8 @@
       <c r="D21" s="60"/>
       <c r="E21" s="60"/>
       <c r="F21" s="60"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="65"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="67"/>
       <c r="I21" s="21" t="str">
         <f aca="false">IF(OR(G21="",H21=""),"",H21-G21)</f>
         <v/>
@@ -6204,10 +6353,10 @@
       <c r="K21" s="60"/>
       <c r="L21" s="59"/>
       <c r="M21" s="60"/>
-      <c r="N21" s="66"/>
+      <c r="N21" s="68"/>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="35" t="n">
+      <c r="A22" s="62" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="59"/>
@@ -6215,8 +6364,8 @@
       <c r="D22" s="60"/>
       <c r="E22" s="60"/>
       <c r="F22" s="60"/>
-      <c r="G22" s="65"/>
-      <c r="H22" s="65"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
       <c r="I22" s="21" t="str">
         <f aca="false">IF(OR(G22="",H22=""),"",H22-G22)</f>
         <v/>
@@ -6225,10 +6374,10 @@
       <c r="K22" s="60"/>
       <c r="L22" s="59"/>
       <c r="M22" s="60"/>
-      <c r="N22" s="66"/>
+      <c r="N22" s="68"/>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="35" t="n">
+      <c r="A23" s="62" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="59"/>
@@ -6236,8 +6385,8 @@
       <c r="D23" s="60"/>
       <c r="E23" s="60"/>
       <c r="F23" s="60"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
       <c r="I23" s="21" t="str">
         <f aca="false">IF(OR(G23="",H23=""),"",H23-G23)</f>
         <v/>
@@ -6246,10 +6395,10 @@
       <c r="K23" s="60"/>
       <c r="L23" s="59"/>
       <c r="M23" s="60"/>
-      <c r="N23" s="66"/>
+      <c r="N23" s="68"/>
     </row>
     <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="35" t="n">
+      <c r="A24" s="62" t="n">
         <v>20</v>
       </c>
       <c r="B24" s="59"/>
@@ -6257,8 +6406,8 @@
       <c r="D24" s="60"/>
       <c r="E24" s="60"/>
       <c r="F24" s="60"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="65"/>
+      <c r="G24" s="67"/>
+      <c r="H24" s="67"/>
       <c r="I24" s="21" t="str">
         <f aca="false">IF(OR(G24="",H24=""),"",H24-G24)</f>
         <v/>
@@ -6267,10 +6416,10 @@
       <c r="K24" s="60"/>
       <c r="L24" s="59"/>
       <c r="M24" s="60"/>
-      <c r="N24" s="66"/>
+      <c r="N24" s="68"/>
     </row>
     <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="35" t="n">
+      <c r="A25" s="62" t="n">
         <v>21</v>
       </c>
       <c r="B25" s="59"/>
@@ -6278,8 +6427,8 @@
       <c r="D25" s="60"/>
       <c r="E25" s="60"/>
       <c r="F25" s="60"/>
-      <c r="G25" s="65"/>
-      <c r="H25" s="65"/>
+      <c r="G25" s="67"/>
+      <c r="H25" s="67"/>
       <c r="I25" s="21" t="str">
         <f aca="false">IF(OR(G25="",H25=""),"",H25-G25)</f>
         <v/>
@@ -6288,10 +6437,10 @@
       <c r="K25" s="60"/>
       <c r="L25" s="59"/>
       <c r="M25" s="60"/>
-      <c r="N25" s="66"/>
+      <c r="N25" s="68"/>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="35" t="n">
+      <c r="A26" s="62" t="n">
         <v>22</v>
       </c>
       <c r="B26" s="59"/>
@@ -6299,8 +6448,8 @@
       <c r="D26" s="60"/>
       <c r="E26" s="60"/>
       <c r="F26" s="60"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
+      <c r="G26" s="67"/>
+      <c r="H26" s="67"/>
       <c r="I26" s="21" t="str">
         <f aca="false">IF(OR(G26="",H26=""),"",H26-G26)</f>
         <v/>
@@ -6309,10 +6458,10 @@
       <c r="K26" s="60"/>
       <c r="L26" s="59"/>
       <c r="M26" s="60"/>
-      <c r="N26" s="66"/>
+      <c r="N26" s="68"/>
     </row>
     <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="35" t="n">
+      <c r="A27" s="62" t="n">
         <v>23</v>
       </c>
       <c r="B27" s="59"/>
@@ -6320,8 +6469,8 @@
       <c r="D27" s="60"/>
       <c r="E27" s="60"/>
       <c r="F27" s="60"/>
-      <c r="G27" s="65"/>
-      <c r="H27" s="65"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="67"/>
       <c r="I27" s="21" t="str">
         <f aca="false">IF(OR(G27="",H27=""),"",H27-G27)</f>
         <v/>
@@ -6330,10 +6479,10 @@
       <c r="K27" s="60"/>
       <c r="L27" s="59"/>
       <c r="M27" s="60"/>
-      <c r="N27" s="66"/>
+      <c r="N27" s="68"/>
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="35" t="n">
+      <c r="A28" s="62" t="n">
         <v>24</v>
       </c>
       <c r="B28" s="59"/>
@@ -6341,8 +6490,8 @@
       <c r="D28" s="60"/>
       <c r="E28" s="60"/>
       <c r="F28" s="60"/>
-      <c r="G28" s="65"/>
-      <c r="H28" s="65"/>
+      <c r="G28" s="67"/>
+      <c r="H28" s="67"/>
       <c r="I28" s="21" t="str">
         <f aca="false">IF(OR(G28="",H28=""),"",H28-G28)</f>
         <v/>
@@ -6351,17 +6500,17 @@
       <c r="K28" s="60"/>
       <c r="L28" s="59"/>
       <c r="M28" s="60"/>
-      <c r="N28" s="66"/>
+      <c r="N28" s="68"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="24" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="M30" s="21" t="str">
         <f aca="false">COUNTA(B5:B28)&amp;" مبادرة"</f>
         <v>0 مبادرة</v>
       </c>
-      <c r="N30" s="67" t="str">
+      <c r="N30" s="69" t="str">
         <f aca="false">IFERROR(AVERAGE(N5:N28),"")</f>
         <v/>
       </c>
@@ -6407,7 +6556,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6426,7 +6575,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6445,2733 +6594,2733 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E4" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F4" s="29" t="n">
+      <c r="F4" s="28" t="n">
         <v>49590690</v>
       </c>
-      <c r="G4" s="29" t="n">
+      <c r="G4" s="28" t="n">
         <f aca="false">F4*365/E4</f>
         <v>100003325.138122</v>
       </c>
-      <c r="H4" s="29" t="n">
+      <c r="H4" s="28" t="n">
         <v>766648</v>
       </c>
-      <c r="I4" s="29" t="n">
+      <c r="I4" s="28" t="n">
         <v>23493282</v>
       </c>
       <c r="J4" s="57" t="n">
         <v>64.69</v>
       </c>
-      <c r="K4" s="68" t="n">
+      <c r="K4" s="70" t="n">
         <v>-0.223</v>
       </c>
-      <c r="L4" s="46" t="n">
+      <c r="L4" s="45" t="n">
         <v>0.006</v>
       </c>
-      <c r="M4" s="46" t="n">
+      <c r="M4" s="45" t="n">
         <v>0.53</v>
       </c>
-      <c r="N4" s="46" t="n">
+      <c r="N4" s="45" t="n">
         <v>0.281</v>
       </c>
       <c r="O4" s="21" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="E5" s="21" t="n">
         <v>91</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="28" t="n">
         <v>20001382</v>
       </c>
-      <c r="G5" s="29" t="n">
+      <c r="G5" s="28" t="n">
         <f aca="false">F5*365/E5</f>
         <v>80225323.4065934</v>
       </c>
-      <c r="H5" s="29" t="n">
+      <c r="H5" s="28" t="n">
         <v>324068</v>
       </c>
-      <c r="I5" s="29" t="n">
+      <c r="I5" s="28" t="n">
         <v>8841940</v>
       </c>
       <c r="J5" s="57" t="n">
         <v>61.72</v>
       </c>
-      <c r="K5" s="69" t="n">
+      <c r="K5" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="46" t="n">
+      <c r="L5" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="46" t="n">
+      <c r="M5" s="45" t="n">
         <v>0.364</v>
       </c>
-      <c r="N5" s="46" t="n">
+      <c r="N5" s="45" t="n">
         <v>0</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E6" s="21" t="n">
         <v>91</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="28" t="n">
         <v>15598002</v>
       </c>
-      <c r="G6" s="29" t="n">
+      <c r="G6" s="28" t="n">
         <f aca="false">F6*365/E6</f>
         <v>62563414.6153846</v>
       </c>
-      <c r="H6" s="29" t="n">
+      <c r="H6" s="28" t="n">
         <v>194466</v>
       </c>
-      <c r="I6" s="29" t="n">
+      <c r="I6" s="28" t="n">
         <v>7467484</v>
       </c>
       <c r="J6" s="57" t="n">
         <v>80.21</v>
       </c>
-      <c r="K6" s="69" t="n">
+      <c r="K6" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="46" t="n">
+      <c r="L6" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="46" t="n">
+      <c r="M6" s="45" t="n">
         <v>0.441</v>
       </c>
-      <c r="N6" s="46" t="n">
+      <c r="N6" s="45" t="n">
         <v>0.344</v>
       </c>
       <c r="O6" s="21" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="E7" s="21" t="n">
         <v>176</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="28" t="n">
         <v>28047704</v>
       </c>
-      <c r="G7" s="29" t="n">
+      <c r="G7" s="28" t="n">
         <f aca="false">F7*365/E7</f>
         <v>58167113.4090909</v>
       </c>
-      <c r="H7" s="29" t="n">
+      <c r="H7" s="28" t="n">
         <v>333050</v>
       </c>
-      <c r="I7" s="29" t="n">
+      <c r="I7" s="28" t="n">
         <v>14552120</v>
       </c>
       <c r="J7" s="57" t="n">
         <v>84.21</v>
       </c>
-      <c r="K7" s="70" t="n">
+      <c r="K7" s="72" t="n">
         <v>0.273</v>
       </c>
-      <c r="L7" s="46" t="n">
+      <c r="L7" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="46" t="n">
+      <c r="M7" s="45" t="n">
         <v>0.204</v>
       </c>
-      <c r="N7" s="46" t="n">
+      <c r="N7" s="45" t="n">
         <v>0.641</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E8" s="21" t="n">
         <v>180</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="28" t="n">
         <v>20528975</v>
       </c>
-      <c r="G8" s="29" t="n">
+      <c r="G8" s="28" t="n">
         <f aca="false">F8*365/E8</f>
         <v>41628199.3055556</v>
       </c>
-      <c r="H8" s="29" t="n">
+      <c r="H8" s="28" t="n">
         <v>424628</v>
       </c>
-      <c r="I8" s="29" t="n">
+      <c r="I8" s="28" t="n">
         <v>2916708</v>
       </c>
       <c r="J8" s="57" t="n">
         <v>48.35</v>
       </c>
-      <c r="K8" s="68" t="n">
+      <c r="K8" s="70" t="n">
         <v>-0.211</v>
       </c>
-      <c r="L8" s="46" t="n">
+      <c r="L8" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="46" t="n">
+      <c r="M8" s="45" t="n">
         <v>0.922</v>
       </c>
-      <c r="N8" s="46" t="n">
+      <c r="N8" s="45" t="n">
         <v>0.134</v>
       </c>
       <c r="O8" s="21" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
+        <v>438</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>429</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>430</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>420</v>
-      </c>
       <c r="D9" s="21" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="E9" s="21" t="n">
         <v>55</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="28" t="n">
         <v>6133992</v>
       </c>
-      <c r="G9" s="29" t="n">
+      <c r="G9" s="28" t="n">
         <f aca="false">F9*365/E9</f>
         <v>40707401.4545455</v>
       </c>
-      <c r="H9" s="29" t="n">
+      <c r="H9" s="28" t="n">
         <v>93189</v>
       </c>
-      <c r="I9" s="29" t="n">
+      <c r="I9" s="28" t="n">
         <v>2916316</v>
       </c>
       <c r="J9" s="57" t="n">
         <v>65.82</v>
       </c>
-      <c r="K9" s="69" t="n">
+      <c r="K9" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="46" t="n">
+      <c r="L9" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M9" s="46" t="n">
+      <c r="M9" s="45" t="n">
         <v>0.501</v>
       </c>
-      <c r="N9" s="46" t="n">
+      <c r="N9" s="45" t="n">
         <v>0.309</v>
       </c>
       <c r="O9" s="21" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E10" s="21" t="n">
         <v>63</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="28" t="n">
         <v>6430228</v>
       </c>
-      <c r="G10" s="29" t="n">
+      <c r="G10" s="28" t="n">
         <f aca="false">F10*365/E10</f>
         <v>37254495.5555556</v>
       </c>
-      <c r="H10" s="29" t="n">
+      <c r="H10" s="28" t="n">
         <v>108731</v>
       </c>
-      <c r="I10" s="29" t="n">
+      <c r="I10" s="28" t="n">
         <v>2831981</v>
       </c>
       <c r="J10" s="57" t="n">
         <v>59.14</v>
       </c>
-      <c r="K10" s="69" t="n">
+      <c r="K10" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="46" t="n">
+      <c r="L10" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="46" t="n">
+      <c r="M10" s="45" t="n">
         <v>0.318</v>
       </c>
-      <c r="N10" s="46" t="n">
+      <c r="N10" s="45" t="n">
         <v>0.006</v>
       </c>
       <c r="O10" s="21" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E11" s="21" t="n">
         <v>65</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="28" t="n">
         <v>6610805</v>
       </c>
-      <c r="G11" s="29" t="n">
+      <c r="G11" s="28" t="n">
         <f aca="false">F11*365/E11</f>
         <v>37122212.6923077</v>
       </c>
-      <c r="H11" s="29" t="n">
+      <c r="H11" s="28" t="n">
         <v>132653</v>
       </c>
-      <c r="I11" s="29" t="n">
+      <c r="I11" s="28" t="n">
         <v>2931550</v>
       </c>
       <c r="J11" s="57" t="n">
         <v>49.84</v>
       </c>
-      <c r="K11" s="69" t="n">
+      <c r="K11" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="46" t="n">
+      <c r="L11" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="46" t="n">
+      <c r="M11" s="45" t="n">
         <v>0.436</v>
       </c>
-      <c r="N11" s="46" t="n">
+      <c r="N11" s="45" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="21" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E12" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="28" t="n">
         <v>18281399</v>
       </c>
-      <c r="G12" s="29" t="n">
+      <c r="G12" s="28" t="n">
         <f aca="false">F12*365/E12</f>
         <v>36865804.6132597</v>
       </c>
-      <c r="H12" s="29" t="n">
+      <c r="H12" s="28" t="n">
         <v>308074</v>
       </c>
-      <c r="I12" s="29" t="n">
+      <c r="I12" s="28" t="n">
         <v>8679738</v>
       </c>
       <c r="J12" s="57" t="n">
         <v>59.34</v>
       </c>
-      <c r="K12" s="68" t="n">
+      <c r="K12" s="70" t="n">
         <v>-0.09</v>
       </c>
-      <c r="L12" s="46" t="n">
+      <c r="L12" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="46" t="n">
+      <c r="M12" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="N12" s="46" t="n">
+      <c r="N12" s="45" t="n">
         <v>0.277</v>
       </c>
       <c r="O12" s="21" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="E13" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="28" t="n">
         <v>17320811</v>
       </c>
-      <c r="G13" s="29" t="n">
+      <c r="G13" s="28" t="n">
         <f aca="false">F13*365/E13</f>
         <v>34928707.2651934</v>
       </c>
-      <c r="H13" s="29" t="n">
+      <c r="H13" s="28" t="n">
         <v>256011</v>
       </c>
-      <c r="I13" s="29" t="n">
+      <c r="I13" s="28" t="n">
         <v>7729931</v>
       </c>
       <c r="J13" s="57" t="n">
         <v>67.66</v>
       </c>
-      <c r="K13" s="68" t="n">
+      <c r="K13" s="70" t="n">
         <v>-0.119</v>
       </c>
-      <c r="L13" s="46" t="n">
+      <c r="L13" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="46" t="n">
+      <c r="M13" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="N13" s="46" t="n">
+      <c r="N13" s="45" t="n">
         <v>0.082</v>
       </c>
       <c r="O13" s="21" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E14" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="28" t="n">
         <v>16855372</v>
       </c>
-      <c r="G14" s="29" t="n">
+      <c r="G14" s="28" t="n">
         <f aca="false">F14*365/E14</f>
         <v>33990114.8066298</v>
       </c>
-      <c r="H14" s="29" t="n">
+      <c r="H14" s="28" t="n">
         <v>283446</v>
       </c>
-      <c r="I14" s="29" t="n">
+      <c r="I14" s="28" t="n">
         <v>2676944</v>
       </c>
       <c r="J14" s="57" t="n">
         <v>59.47</v>
       </c>
-      <c r="K14" s="46" t="n">
+      <c r="K14" s="45" t="n">
         <v>-0.034</v>
       </c>
-      <c r="L14" s="46" t="n">
+      <c r="L14" s="45" t="n">
         <v>0.038</v>
       </c>
-      <c r="M14" s="46" t="n">
+      <c r="M14" s="45" t="n">
         <v>0.488</v>
       </c>
-      <c r="N14" s="46" t="n">
+      <c r="N14" s="45" t="n">
         <v>0.231</v>
       </c>
       <c r="O14" s="21" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="E15" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="28" t="n">
         <v>15775248</v>
       </c>
-      <c r="G15" s="29" t="n">
+      <c r="G15" s="28" t="n">
         <f aca="false">F15*365/E15</f>
         <v>31811964.198895</v>
       </c>
-      <c r="H15" s="29" t="n">
+      <c r="H15" s="28" t="n">
         <v>249705</v>
       </c>
-      <c r="I15" s="29" t="n">
+      <c r="I15" s="28" t="n">
         <v>7806709</v>
       </c>
       <c r="J15" s="57" t="n">
         <v>63.18</v>
       </c>
-      <c r="K15" s="68" t="n">
+      <c r="K15" s="70" t="n">
         <v>-0.217</v>
       </c>
-      <c r="L15" s="46" t="n">
+      <c r="L15" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="46" t="n">
+      <c r="M15" s="45" t="n">
         <v>0.894</v>
       </c>
-      <c r="N15" s="46" t="n">
+      <c r="N15" s="45" t="n">
         <v>0.458</v>
       </c>
       <c r="O15" s="21" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E16" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="28" t="n">
         <v>15719285</v>
       </c>
-      <c r="G16" s="29" t="n">
+      <c r="G16" s="28" t="n">
         <f aca="false">F16*365/E16</f>
         <v>31699110.6353591</v>
       </c>
-      <c r="H16" s="29" t="n">
+      <c r="H16" s="28" t="n">
         <v>211558</v>
       </c>
-      <c r="I16" s="29" t="n">
+      <c r="I16" s="28" t="n">
         <v>4791911</v>
       </c>
       <c r="J16" s="57" t="n">
         <v>74.3</v>
       </c>
-      <c r="K16" s="70" t="n">
+      <c r="K16" s="72" t="n">
         <v>0.151</v>
       </c>
-      <c r="L16" s="46" t="n">
+      <c r="L16" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="46" t="n">
+      <c r="M16" s="45" t="n">
         <v>0.247</v>
       </c>
-      <c r="N16" s="46" t="n">
+      <c r="N16" s="45" t="n">
         <v>0.076</v>
       </c>
       <c r="O16" s="21" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E17" s="21" t="n">
         <v>57</v>
       </c>
-      <c r="F17" s="29" t="n">
+      <c r="F17" s="28" t="n">
         <v>4714627</v>
       </c>
-      <c r="G17" s="29" t="n">
+      <c r="G17" s="28" t="n">
         <f aca="false">F17*365/E17</f>
         <v>30190155.3508772</v>
       </c>
-      <c r="H17" s="29" t="n">
+      <c r="H17" s="28" t="n">
         <v>84547</v>
       </c>
-      <c r="I17" s="29" t="n">
+      <c r="I17" s="28" t="n">
         <v>2078856</v>
       </c>
       <c r="J17" s="57" t="n">
         <v>55.76</v>
       </c>
-      <c r="K17" s="69" t="n">
+      <c r="K17" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="46" t="n">
+      <c r="L17" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="46" t="n">
+      <c r="M17" s="45" t="n">
         <v>0.432</v>
       </c>
-      <c r="N17" s="46" t="n">
+      <c r="N17" s="45" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="21" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E18" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="28" t="n">
         <v>14811456</v>
       </c>
-      <c r="G18" s="29" t="n">
+      <c r="G18" s="28" t="n">
         <f aca="false">F18*365/E18</f>
         <v>29868405.7458564</v>
       </c>
-      <c r="H18" s="29" t="n">
+      <c r="H18" s="28" t="n">
         <v>338888</v>
       </c>
-      <c r="I18" s="29" t="n">
+      <c r="I18" s="28" t="n">
         <v>6570004</v>
       </c>
       <c r="J18" s="57" t="n">
         <v>43.71</v>
       </c>
-      <c r="K18" s="46" t="n">
+      <c r="K18" s="45" t="n">
         <v>-0.03</v>
       </c>
-      <c r="L18" s="46" t="n">
+      <c r="L18" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="46" t="n">
+      <c r="M18" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="N18" s="46" t="n">
+      <c r="N18" s="45" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="21" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="E19" s="21" t="n">
         <v>130</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="28" t="n">
         <v>9901510</v>
       </c>
-      <c r="G19" s="29" t="n">
+      <c r="G19" s="28" t="n">
         <f aca="false">F19*365/E19</f>
         <v>27800393.4615385</v>
       </c>
-      <c r="H19" s="29" t="n">
+      <c r="H19" s="28" t="n">
         <v>234974</v>
       </c>
-      <c r="I19" s="29" t="n">
+      <c r="I19" s="28" t="n">
         <v>4445436</v>
       </c>
       <c r="J19" s="57" t="n">
         <v>42.14</v>
       </c>
-      <c r="K19" s="70" t="n">
+      <c r="K19" s="72" t="n">
         <v>0.275</v>
       </c>
-      <c r="L19" s="46" t="n">
+      <c r="L19" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="46" t="n">
+      <c r="M19" s="45" t="n">
         <v>0.478</v>
       </c>
-      <c r="N19" s="46" t="n">
+      <c r="N19" s="45" t="n">
         <v>0.048</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="E20" s="21" t="n">
         <v>70</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="28" t="n">
         <v>5015246</v>
       </c>
-      <c r="G20" s="29" t="n">
+      <c r="G20" s="28" t="n">
         <f aca="false">F20*365/E20</f>
         <v>26150925.5714286</v>
       </c>
-      <c r="H20" s="29" t="n">
+      <c r="H20" s="28" t="n">
         <v>115020</v>
       </c>
-      <c r="I20" s="29" t="n">
+      <c r="I20" s="28" t="n">
         <v>2229579</v>
       </c>
       <c r="J20" s="57" t="n">
         <v>43.6</v>
       </c>
-      <c r="K20" s="69" t="n">
+      <c r="K20" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="46" t="n">
+      <c r="L20" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="46" t="n">
+      <c r="M20" s="45" t="n">
         <v>0.678</v>
       </c>
-      <c r="N20" s="46" t="n">
+      <c r="N20" s="45" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="21" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E21" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="28" t="n">
         <v>12392502</v>
       </c>
-      <c r="G21" s="29" t="n">
+      <c r="G21" s="28" t="n">
         <f aca="false">F21*365/E21</f>
         <v>24990404.5856354</v>
       </c>
-      <c r="H21" s="29" t="n">
+      <c r="H21" s="28" t="n">
         <v>284756</v>
       </c>
-      <c r="I21" s="29" t="n">
+      <c r="I21" s="28" t="n">
         <v>5504980</v>
       </c>
       <c r="J21" s="57" t="n">
         <v>43.52</v>
       </c>
-      <c r="K21" s="68" t="n">
+      <c r="K21" s="70" t="n">
         <v>-0.112</v>
       </c>
-      <c r="L21" s="46" t="n">
+      <c r="L21" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M21" s="46" t="n">
+      <c r="M21" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="N21" s="46" t="n">
+      <c r="N21" s="45" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="21" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E22" s="21" t="n">
         <v>147</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="28" t="n">
         <v>9737128</v>
       </c>
-      <c r="G22" s="29" t="n">
+      <c r="G22" s="28" t="n">
         <f aca="false">F22*365/E22</f>
         <v>24177222.585034</v>
       </c>
-      <c r="H22" s="29" t="n">
+      <c r="H22" s="28" t="n">
         <v>195205</v>
       </c>
-      <c r="I22" s="29" t="n">
+      <c r="I22" s="28" t="n">
         <v>4722403</v>
       </c>
       <c r="J22" s="57" t="n">
         <v>49.88</v>
       </c>
-      <c r="K22" s="70" t="n">
+      <c r="K22" s="72" t="n">
         <v>0.068</v>
       </c>
-      <c r="L22" s="46" t="n">
+      <c r="L22" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="46" t="n">
+      <c r="M22" s="45" t="n">
         <v>0.673</v>
       </c>
-      <c r="N22" s="46" t="n">
+      <c r="N22" s="45" t="n">
         <v>0.329</v>
       </c>
       <c r="O22" s="21" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E23" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="28" t="n">
         <v>11129389</v>
       </c>
-      <c r="G23" s="29" t="n">
+      <c r="G23" s="28" t="n">
         <f aca="false">F23*365/E23</f>
         <v>22443243.0110497</v>
       </c>
-      <c r="H23" s="29" t="n">
+      <c r="H23" s="28" t="n">
         <v>233425</v>
       </c>
-      <c r="I23" s="29" t="n">
+      <c r="I23" s="28" t="n">
         <v>4924931</v>
       </c>
       <c r="J23" s="57" t="n">
         <v>47.68</v>
       </c>
-      <c r="K23" s="70" t="n">
+      <c r="K23" s="72" t="n">
         <v>0.069</v>
       </c>
-      <c r="L23" s="46" t="n">
+      <c r="L23" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="46" t="n">
+      <c r="M23" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="N23" s="46" t="n">
+      <c r="N23" s="45" t="n">
         <v>0</v>
       </c>
       <c r="O23" s="21" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E24" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F24" s="29" t="n">
+      <c r="F24" s="28" t="n">
         <v>10708429</v>
       </c>
-      <c r="G24" s="29" t="n">
+      <c r="G24" s="28" t="n">
         <f aca="false">F24*365/E24</f>
         <v>21594345.7734807</v>
       </c>
-      <c r="H24" s="29" t="n">
+      <c r="H24" s="28" t="n">
         <v>246641</v>
       </c>
-      <c r="I24" s="29" t="n">
+      <c r="I24" s="28" t="n">
         <v>4740020</v>
       </c>
       <c r="J24" s="57" t="n">
         <v>43.42</v>
       </c>
-      <c r="K24" s="46" t="n">
+      <c r="K24" s="45" t="n">
         <v>0.042</v>
       </c>
-      <c r="L24" s="46" t="n">
+      <c r="L24" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="46" t="n">
+      <c r="M24" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="N24" s="46" t="n">
+      <c r="N24" s="45" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="21" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="E25" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="28" t="n">
         <v>10700092</v>
       </c>
-      <c r="G25" s="29" t="n">
+      <c r="G25" s="28" t="n">
         <f aca="false">F25*365/E25</f>
         <v>21577533.5911602</v>
       </c>
-      <c r="H25" s="29" t="n">
+      <c r="H25" s="28" t="n">
         <v>207031</v>
       </c>
-      <c r="I25" s="29" t="n">
+      <c r="I25" s="28" t="n">
         <v>4771577</v>
       </c>
       <c r="J25" s="57" t="n">
         <v>51.68</v>
       </c>
-      <c r="K25" s="70" t="n">
+      <c r="K25" s="72" t="n">
         <v>0.177</v>
       </c>
-      <c r="L25" s="46" t="n">
+      <c r="L25" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M25" s="46" t="n">
+      <c r="M25" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="N25" s="46" t="n">
+      <c r="N25" s="45" t="n">
         <v>0.058</v>
       </c>
       <c r="O25" s="21" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="E26" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="28" t="n">
         <v>10414834</v>
       </c>
-      <c r="G26" s="29" t="n">
+      <c r="G26" s="28" t="n">
         <f aca="false">F26*365/E26</f>
         <v>21002289.5580111</v>
       </c>
-      <c r="H26" s="29" t="n">
+      <c r="H26" s="28" t="n">
         <v>201217</v>
       </c>
-      <c r="I26" s="29" t="n">
+      <c r="I26" s="28" t="n">
         <v>4933540</v>
       </c>
       <c r="J26" s="57" t="n">
         <v>51.76</v>
       </c>
-      <c r="K26" s="46" t="n">
+      <c r="K26" s="45" t="n">
         <v>-0.033</v>
       </c>
-      <c r="L26" s="46" t="n">
+      <c r="L26" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="46" t="n">
+      <c r="M26" s="45" t="n">
         <v>0.634</v>
       </c>
-      <c r="N26" s="46" t="n">
+      <c r="N26" s="45" t="n">
         <v>0.276</v>
       </c>
       <c r="O26" s="21" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="E27" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F27" s="29" t="n">
+      <c r="F27" s="28" t="n">
         <v>9869940</v>
       </c>
-      <c r="G27" s="29" t="n">
+      <c r="G27" s="28" t="n">
         <f aca="false">F27*365/E27</f>
         <v>19903470.1657459</v>
       </c>
-      <c r="H27" s="29" t="n">
+      <c r="H27" s="28" t="n">
         <v>148911</v>
       </c>
-      <c r="I27" s="29" t="n">
+      <c r="I27" s="28" t="n">
         <v>4643058</v>
       </c>
       <c r="J27" s="57" t="n">
         <v>66.28</v>
       </c>
-      <c r="K27" s="70" t="n">
+      <c r="K27" s="72" t="n">
         <v>0.083</v>
       </c>
-      <c r="L27" s="46" t="n">
+      <c r="L27" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="46" t="n">
+      <c r="M27" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="46" t="n">
+      <c r="N27" s="45" t="n">
         <v>0.27</v>
       </c>
       <c r="O27" s="21" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="E28" s="21" t="n">
         <v>111</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="28" t="n">
         <v>5875411</v>
       </c>
-      <c r="G28" s="29" t="n">
+      <c r="G28" s="28" t="n">
         <f aca="false">F28*365/E28</f>
         <v>19320045.1801802</v>
       </c>
-      <c r="H28" s="29" t="n">
+      <c r="H28" s="28" t="n">
         <v>75507</v>
       </c>
-      <c r="I28" s="29" t="n">
+      <c r="I28" s="28" t="n">
         <v>2834084</v>
       </c>
       <c r="J28" s="57" t="n">
         <v>77.81</v>
       </c>
-      <c r="K28" s="69" t="n">
+      <c r="K28" s="71" t="n">
         <v>-0.033</v>
       </c>
-      <c r="L28" s="46" t="n">
+      <c r="L28" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M28" s="46" t="n">
+      <c r="M28" s="45" t="n">
         <v>0.493</v>
       </c>
-      <c r="N28" s="46" t="n">
+      <c r="N28" s="45" t="n">
         <v>0.349</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="E29" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="28" t="n">
         <v>9512678</v>
       </c>
-      <c r="G29" s="29" t="n">
+      <c r="G29" s="28" t="n">
         <f aca="false">F29*365/E29</f>
         <v>19183024.6961326</v>
       </c>
-      <c r="H29" s="29" t="n">
+      <c r="H29" s="28" t="n">
         <v>147623</v>
       </c>
-      <c r="I29" s="29" t="n">
+      <c r="I29" s="28" t="n">
         <v>4558563</v>
       </c>
       <c r="J29" s="57" t="n">
         <v>64.44</v>
       </c>
-      <c r="K29" s="46" t="n">
+      <c r="K29" s="45" t="n">
         <v>-0.045</v>
       </c>
-      <c r="L29" s="46" t="n">
+      <c r="L29" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M29" s="46" t="n">
+      <c r="M29" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="N29" s="46" t="n">
+      <c r="N29" s="45" t="n">
         <v>0.321</v>
       </c>
       <c r="O29" s="21" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E30" s="21" t="n">
         <v>92</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="28" t="n">
         <v>4575739</v>
       </c>
-      <c r="G30" s="29" t="n">
+      <c r="G30" s="28" t="n">
         <f aca="false">F30*365/E30</f>
         <v>18153747.1195652</v>
       </c>
-      <c r="H30" s="29" t="n">
+      <c r="H30" s="28" t="n">
         <v>94310</v>
       </c>
-      <c r="I30" s="29" t="n">
+      <c r="I30" s="28" t="n">
         <v>2127665</v>
       </c>
       <c r="J30" s="57" t="n">
         <v>48.52</v>
       </c>
-      <c r="K30" s="69" t="n">
+      <c r="K30" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="L30" s="46" t="n">
+      <c r="L30" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="46" t="n">
+      <c r="M30" s="45" t="n">
         <v>0.685</v>
       </c>
-      <c r="N30" s="46" t="n">
+      <c r="N30" s="45" t="n">
         <v>0.176</v>
       </c>
       <c r="O30" s="21" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="E31" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="28" t="n">
         <v>8563678</v>
       </c>
-      <c r="G31" s="29" t="n">
+      <c r="G31" s="28" t="n">
         <f aca="false">F31*365/E31</f>
         <v>17269295.4143646</v>
       </c>
-      <c r="H31" s="29" t="n">
+      <c r="H31" s="28" t="n">
         <v>156380</v>
       </c>
-      <c r="I31" s="29" t="n">
+      <c r="I31" s="28" t="n">
         <v>3884721</v>
       </c>
       <c r="J31" s="57" t="n">
         <v>54.76</v>
       </c>
-      <c r="K31" s="70" t="n">
+      <c r="K31" s="72" t="n">
         <v>0.186</v>
       </c>
-      <c r="L31" s="46" t="n">
+      <c r="L31" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M31" s="46" t="n">
+      <c r="M31" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="N31" s="46" t="n">
+      <c r="N31" s="45" t="n">
         <v>0.082</v>
       </c>
       <c r="O31" s="21" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="E32" s="21" t="n">
         <v>69</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="28" t="n">
         <v>3263896</v>
       </c>
-      <c r="G32" s="29" t="n">
+      <c r="G32" s="28" t="n">
         <f aca="false">F32*365/E32</f>
         <v>17265536.8115942</v>
       </c>
-      <c r="H32" s="29" t="n">
+      <c r="H32" s="28" t="n">
         <v>65707</v>
       </c>
-      <c r="I32" s="29" t="n">
+      <c r="I32" s="28" t="n">
         <v>1471112</v>
       </c>
       <c r="J32" s="57" t="n">
         <v>49.67</v>
       </c>
-      <c r="K32" s="69" t="n">
+      <c r="K32" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="46" t="n">
+      <c r="L32" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M32" s="46" t="n">
+      <c r="M32" s="45" t="n">
         <v>0.597</v>
       </c>
-      <c r="N32" s="46" t="n">
+      <c r="N32" s="45" t="n">
         <v>0.103</v>
       </c>
       <c r="O32" s="20" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E33" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="28" t="n">
         <v>8483209</v>
       </c>
-      <c r="G33" s="29" t="n">
+      <c r="G33" s="28" t="n">
         <f aca="false">F33*365/E33</f>
         <v>17107023.6740332</v>
       </c>
-      <c r="H33" s="29" t="n">
+      <c r="H33" s="28" t="n">
         <v>166967</v>
       </c>
-      <c r="I33" s="29" t="n">
+      <c r="I33" s="28" t="n">
         <v>3774634</v>
       </c>
       <c r="J33" s="57" t="n">
         <v>50.81</v>
       </c>
-      <c r="K33" s="70" t="n">
+      <c r="K33" s="72" t="n">
         <v>0.18</v>
       </c>
-      <c r="L33" s="46" t="n">
+      <c r="L33" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M33" s="46" t="n">
+      <c r="M33" s="45" t="n">
         <v>0.253</v>
       </c>
-      <c r="N33" s="46" t="n">
+      <c r="N33" s="45" t="n">
         <v>0.023</v>
       </c>
       <c r="O33" s="21" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="E34" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F34" s="28" t="n">
         <v>8421901</v>
       </c>
-      <c r="G34" s="29" t="n">
+      <c r="G34" s="28" t="n">
         <f aca="false">F34*365/E34</f>
         <v>16983391.519337</v>
       </c>
-      <c r="H34" s="29" t="n">
+      <c r="H34" s="28" t="n">
         <v>76519</v>
       </c>
-      <c r="I34" s="29" t="n">
+      <c r="I34" s="28" t="n">
         <v>4263083</v>
       </c>
       <c r="J34" s="57" t="n">
         <v>110.06</v>
       </c>
-      <c r="K34" s="68" t="n">
+      <c r="K34" s="70" t="n">
         <v>-0.084</v>
       </c>
-      <c r="L34" s="46" t="n">
+      <c r="L34" s="45" t="n">
         <v>0.015</v>
       </c>
-      <c r="M34" s="46" t="n">
+      <c r="M34" s="45" t="n">
         <v>0.357</v>
       </c>
-      <c r="N34" s="46" t="n">
+      <c r="N34" s="45" t="n">
         <v>0.559</v>
       </c>
       <c r="O34" s="21" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E35" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F35" s="29" t="n">
+      <c r="F35" s="28" t="n">
         <v>7821875</v>
       </c>
-      <c r="G35" s="29" t="n">
+      <c r="G35" s="28" t="n">
         <f aca="false">F35*365/E35</f>
         <v>15773394.3370166</v>
       </c>
-      <c r="H35" s="29" t="n">
+      <c r="H35" s="28" t="n">
         <v>165177</v>
       </c>
-      <c r="I35" s="29" t="n">
+      <c r="I35" s="28" t="n">
         <v>3471225</v>
       </c>
       <c r="J35" s="57" t="n">
         <v>47.35</v>
       </c>
-      <c r="K35" s="68" t="n">
+      <c r="K35" s="70" t="n">
         <v>-0.533</v>
       </c>
-      <c r="L35" s="46" t="n">
+      <c r="L35" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M35" s="46" t="n">
+      <c r="M35" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="N35" s="46" t="n">
+      <c r="N35" s="45" t="n">
         <v>0</v>
       </c>
       <c r="O35" s="21" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="E36" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F36" s="29" t="n">
+      <c r="F36" s="28" t="n">
         <v>7731204</v>
       </c>
-      <c r="G36" s="29" t="n">
+      <c r="G36" s="28" t="n">
         <f aca="false">F36*365/E36</f>
         <v>15590549.5027624</v>
       </c>
-      <c r="H36" s="29" t="n">
+      <c r="H36" s="28" t="n">
         <v>168510</v>
       </c>
-      <c r="I36" s="29" t="n">
+      <c r="I36" s="28" t="n">
         <v>3512113</v>
       </c>
       <c r="J36" s="57" t="n">
         <v>45.88</v>
       </c>
-      <c r="K36" s="68" t="n">
+      <c r="K36" s="70" t="n">
         <v>-0.068</v>
       </c>
-      <c r="L36" s="46" t="n">
+      <c r="L36" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M36" s="46" t="n">
+      <c r="M36" s="45" t="n">
         <v>0.509</v>
       </c>
-      <c r="N36" s="46" t="n">
+      <c r="N36" s="45" t="n">
         <v>0.115</v>
       </c>
       <c r="O36" s="21" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="E37" s="21" t="n">
         <v>26</v>
       </c>
-      <c r="F37" s="29" t="n">
+      <c r="F37" s="28" t="n">
         <v>1063910</v>
       </c>
-      <c r="G37" s="29" t="n">
+      <c r="G37" s="28" t="n">
         <f aca="false">F37*365/E37</f>
         <v>14935659.6153846</v>
       </c>
-      <c r="H37" s="29" t="n">
+      <c r="H37" s="28" t="n">
         <v>31905</v>
       </c>
-      <c r="I37" s="29" t="n">
+      <c r="I37" s="28" t="n">
         <v>486162</v>
       </c>
       <c r="J37" s="57" t="n">
         <v>33.35</v>
       </c>
-      <c r="K37" s="69" t="n">
+      <c r="K37" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="L37" s="46" t="n">
+      <c r="L37" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M37" s="46" t="n">
+      <c r="M37" s="45" t="n">
         <v>0.601</v>
       </c>
-      <c r="N37" s="46" t="n">
+      <c r="N37" s="45" t="n">
         <v>0.114</v>
       </c>
       <c r="O37" s="21" t="s">
-        <v>274</v>
+        <v>229</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E38" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F38" s="29" t="n">
+      <c r="F38" s="28" t="n">
         <v>7305589</v>
       </c>
-      <c r="G38" s="29" t="n">
+      <c r="G38" s="28" t="n">
         <f aca="false">F38*365/E38</f>
         <v>14732265.1104972</v>
       </c>
-      <c r="H38" s="29" t="n">
+      <c r="H38" s="28" t="n">
         <v>169734</v>
       </c>
-      <c r="I38" s="29" t="n">
+      <c r="I38" s="28" t="n">
         <v>3406904</v>
       </c>
       <c r="J38" s="57" t="n">
         <v>43.04</v>
       </c>
-      <c r="K38" s="70" t="n">
+      <c r="K38" s="72" t="n">
         <v>0.083</v>
       </c>
-      <c r="L38" s="46" t="n">
+      <c r="L38" s="45" t="n">
         <v>0.015</v>
       </c>
-      <c r="M38" s="46" t="n">
+      <c r="M38" s="45" t="n">
         <v>0.459</v>
       </c>
-      <c r="N38" s="46" t="n">
+      <c r="N38" s="45" t="n">
         <v>0.167</v>
       </c>
       <c r="O38" s="21" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="21" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="E39" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F39" s="29" t="n">
+      <c r="F39" s="28" t="n">
         <v>6769350</v>
       </c>
-      <c r="G39" s="29" t="n">
+      <c r="G39" s="28" t="n">
         <f aca="false">F39*365/E39</f>
         <v>13650899.1712707</v>
       </c>
-      <c r="H39" s="29" t="n">
+      <c r="H39" s="28" t="n">
         <v>97200</v>
       </c>
-      <c r="I39" s="29" t="n">
+      <c r="I39" s="28" t="n">
         <v>3076219</v>
       </c>
       <c r="J39" s="57" t="n">
         <v>69.64</v>
       </c>
-      <c r="K39" s="68" t="n">
+      <c r="K39" s="70" t="n">
         <v>-0.126</v>
       </c>
-      <c r="L39" s="46" t="n">
+      <c r="L39" s="45" t="n">
         <v>0.002</v>
       </c>
-      <c r="M39" s="46" t="n">
+      <c r="M39" s="45" t="n">
         <v>0.497</v>
       </c>
-      <c r="N39" s="46" t="n">
+      <c r="N39" s="45" t="n">
         <v>0.106</v>
       </c>
       <c r="O39" s="21" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="21" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E40" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F40" s="29" t="n">
+      <c r="F40" s="28" t="n">
         <v>6763759</v>
       </c>
-      <c r="G40" s="29" t="n">
+      <c r="G40" s="28" t="n">
         <f aca="false">F40*365/E40</f>
         <v>13639624.5027624</v>
       </c>
-      <c r="H40" s="29" t="n">
+      <c r="H40" s="28" t="n">
         <v>97406</v>
       </c>
-      <c r="I40" s="29" t="n">
+      <c r="I40" s="28" t="n">
         <v>3314721</v>
       </c>
       <c r="J40" s="57" t="n">
         <v>69.44</v>
       </c>
-      <c r="K40" s="46" t="n">
+      <c r="K40" s="45" t="n">
         <v>-0.044</v>
       </c>
-      <c r="L40" s="46" t="n">
+      <c r="L40" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M40" s="46" t="n">
+      <c r="M40" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="46" t="n">
+      <c r="N40" s="45" t="n">
         <v>0.373</v>
       </c>
       <c r="O40" s="21" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="21" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E41" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F41" s="29" t="n">
+      <c r="F41" s="28" t="n">
         <v>6600956</v>
       </c>
-      <c r="G41" s="29" t="n">
+      <c r="G41" s="28" t="n">
         <f aca="false">F41*365/E41</f>
         <v>13311320.1104972</v>
       </c>
-      <c r="H41" s="29" t="n">
+      <c r="H41" s="28" t="n">
         <v>146007</v>
       </c>
-      <c r="I41" s="29" t="n">
+      <c r="I41" s="28" t="n">
         <v>2925368</v>
       </c>
       <c r="J41" s="57" t="n">
         <v>45.21</v>
       </c>
-      <c r="K41" s="68" t="n">
+      <c r="K41" s="70" t="n">
         <v>-0.121</v>
       </c>
-      <c r="L41" s="46" t="n">
+      <c r="L41" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M41" s="46" t="n">
+      <c r="M41" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="N41" s="46" t="n">
+      <c r="N41" s="45" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="21" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="21" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="E42" s="21" t="n">
         <v>68</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F42" s="28" t="n">
         <v>2479043</v>
       </c>
-      <c r="G42" s="29" t="n">
+      <c r="G42" s="28" t="n">
         <f aca="false">F42*365/E42</f>
         <v>13306627.8676471</v>
       </c>
-      <c r="H42" s="29" t="n">
+      <c r="H42" s="28" t="n">
         <v>54370</v>
       </c>
-      <c r="I42" s="29" t="n">
+      <c r="I42" s="28" t="n">
         <v>1114635</v>
       </c>
       <c r="J42" s="57" t="n">
         <v>45.6</v>
       </c>
-      <c r="K42" s="69" t="n">
+      <c r="K42" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="46" t="n">
+      <c r="L42" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M42" s="46" t="n">
+      <c r="M42" s="45" t="n">
         <v>0.475</v>
       </c>
-      <c r="N42" s="46" t="n">
+      <c r="N42" s="45" t="n">
         <v>0.056</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="E43" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F43" s="29" t="n">
+      <c r="F43" s="28" t="n">
         <v>6302158</v>
       </c>
-      <c r="G43" s="29" t="n">
+      <c r="G43" s="28" t="n">
         <f aca="false">F43*365/E43</f>
         <v>12708771.6574586</v>
       </c>
-      <c r="H43" s="29" t="n">
+      <c r="H43" s="28" t="n">
         <v>123912</v>
       </c>
-      <c r="I43" s="29" t="n">
+      <c r="I43" s="28" t="n">
         <v>2839338</v>
       </c>
       <c r="J43" s="57" t="n">
         <v>50.86</v>
       </c>
-      <c r="K43" s="70" t="n">
+      <c r="K43" s="72" t="n">
         <v>0.082</v>
       </c>
-      <c r="L43" s="46" t="n">
+      <c r="L43" s="45" t="n">
         <v>0.007</v>
       </c>
-      <c r="M43" s="46" t="n">
+      <c r="M43" s="45" t="n">
         <v>0.307</v>
       </c>
-      <c r="N43" s="46" t="n">
+      <c r="N43" s="45" t="n">
         <v>0.077</v>
       </c>
       <c r="O43" s="21" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E44" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F44" s="28" t="n">
         <v>6083371</v>
       </c>
-      <c r="G44" s="29" t="n">
+      <c r="G44" s="28" t="n">
         <f aca="false">F44*365/E44</f>
         <v>12267571.3535912</v>
       </c>
-      <c r="H44" s="29" t="n">
+      <c r="H44" s="28" t="n">
         <v>107035</v>
       </c>
-      <c r="I44" s="29" t="n">
+      <c r="I44" s="28" t="n">
         <v>2759664</v>
       </c>
       <c r="J44" s="57" t="n">
         <v>56.84</v>
       </c>
-      <c r="K44" s="70" t="n">
+      <c r="K44" s="72" t="n">
         <v>0.327</v>
       </c>
-      <c r="L44" s="46" t="n">
+      <c r="L44" s="45" t="n">
         <v>0.003</v>
       </c>
-      <c r="M44" s="46" t="n">
+      <c r="M44" s="45" t="n">
         <v>0.284</v>
       </c>
-      <c r="N44" s="46" t="n">
+      <c r="N44" s="45" t="n">
         <v>0.066</v>
       </c>
       <c r="O44" s="20" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="21" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="E45" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F45" s="28" t="n">
         <v>5976488</v>
       </c>
-      <c r="G45" s="29" t="n">
+      <c r="G45" s="28" t="n">
         <f aca="false">F45*365/E45</f>
         <v>12052033.8121547</v>
       </c>
-      <c r="H45" s="29" t="n">
+      <c r="H45" s="28" t="n">
         <v>79761</v>
       </c>
-      <c r="I45" s="29" t="n">
+      <c r="I45" s="28" t="n">
         <v>2940822</v>
       </c>
       <c r="J45" s="57" t="n">
         <v>74.93</v>
       </c>
-      <c r="K45" s="46" t="n">
+      <c r="K45" s="45" t="n">
         <v>-0.029</v>
       </c>
-      <c r="L45" s="46" t="n">
+      <c r="L45" s="45" t="n">
         <v>0.002</v>
       </c>
-      <c r="M45" s="46" t="n">
+      <c r="M45" s="45" t="n">
         <v>0.336</v>
       </c>
-      <c r="N45" s="46" t="n">
+      <c r="N45" s="45" t="n">
         <v>0.392</v>
       </c>
       <c r="O45" s="20" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="21" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E46" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F46" s="29" t="n">
+      <c r="F46" s="28" t="n">
         <v>5721087</v>
       </c>
-      <c r="G46" s="29" t="n">
+      <c r="G46" s="28" t="n">
         <f aca="false">F46*365/E46</f>
         <v>11536998.6464088</v>
       </c>
-      <c r="H46" s="29" t="n">
+      <c r="H46" s="28" t="n">
         <v>106073</v>
       </c>
-      <c r="I46" s="29" t="n">
+      <c r="I46" s="28" t="n">
         <v>2694118</v>
       </c>
       <c r="J46" s="57" t="n">
         <v>53.94</v>
       </c>
-      <c r="K46" s="68" t="n">
+      <c r="K46" s="70" t="n">
         <v>-0.123</v>
       </c>
-      <c r="L46" s="46" t="n">
+      <c r="L46" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M46" s="46" t="n">
+      <c r="M46" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="N46" s="46" t="n">
+      <c r="N46" s="45" t="n">
         <v>0.236</v>
       </c>
       <c r="O46" s="21" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="21" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="E47" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F47" s="29" t="n">
+      <c r="F47" s="28" t="n">
         <v>5714308</v>
       </c>
-      <c r="G47" s="29" t="n">
+      <c r="G47" s="28" t="n">
         <f aca="false">F47*365/E47</f>
         <v>11523328.2872928</v>
       </c>
-      <c r="H47" s="29" t="n">
+      <c r="H47" s="28" t="n">
         <v>117578</v>
       </c>
-      <c r="I47" s="29" t="n">
+      <c r="I47" s="28" t="n">
         <v>2650896</v>
       </c>
       <c r="J47" s="57" t="n">
         <v>48.6</v>
       </c>
-      <c r="K47" s="46" t="n">
+      <c r="K47" s="45" t="n">
         <v>-0.009</v>
       </c>
-      <c r="L47" s="46" t="n">
+      <c r="L47" s="45" t="n">
         <v>0.007</v>
       </c>
-      <c r="M47" s="46" t="n">
+      <c r="M47" s="45" t="n">
         <v>0.531</v>
       </c>
-      <c r="N47" s="46" t="n">
+      <c r="N47" s="45" t="n">
         <v>0.184</v>
       </c>
       <c r="O47" s="21" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="21" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="E48" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F48" s="29" t="n">
+      <c r="F48" s="28" t="n">
         <v>4846644</v>
       </c>
-      <c r="G48" s="29" t="n">
+      <c r="G48" s="28" t="n">
         <f aca="false">F48*365/E48</f>
         <v>9773619.1160221</v>
       </c>
-      <c r="H48" s="29" t="n">
+      <c r="H48" s="28" t="n">
         <v>84802</v>
       </c>
-      <c r="I48" s="29" t="n">
+      <c r="I48" s="28" t="n">
         <v>2153145</v>
       </c>
       <c r="J48" s="57" t="n">
         <v>57.15</v>
       </c>
-      <c r="K48" s="70" t="n">
+      <c r="K48" s="72" t="n">
         <v>0.064</v>
       </c>
-      <c r="L48" s="46" t="n">
+      <c r="L48" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M48" s="46" t="n">
+      <c r="M48" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="N48" s="46" t="n">
+      <c r="N48" s="45" t="n">
         <v>0</v>
       </c>
       <c r="O48" s="21" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="21" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="E49" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F49" s="29" t="n">
+      <c r="F49" s="28" t="n">
         <v>4569369</v>
       </c>
-      <c r="G49" s="29" t="n">
+      <c r="G49" s="28" t="n">
         <f aca="false">F49*365/E49</f>
         <v>9214473.39779006</v>
       </c>
-      <c r="H49" s="29" t="n">
+      <c r="H49" s="28" t="n">
         <v>72735</v>
       </c>
-      <c r="I49" s="29" t="n">
+      <c r="I49" s="28" t="n">
         <v>2133587</v>
       </c>
       <c r="J49" s="57" t="n">
         <v>62.82</v>
       </c>
-      <c r="K49" s="70" t="n">
+      <c r="K49" s="72" t="n">
         <v>0.256</v>
       </c>
-      <c r="L49" s="46" t="n">
+      <c r="L49" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M49" s="46" t="n">
+      <c r="M49" s="45" t="n">
         <v>0.355</v>
       </c>
-      <c r="N49" s="46" t="n">
+      <c r="N49" s="45" t="n">
         <v>0.201</v>
       </c>
       <c r="O49" s="21" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="21" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E50" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F50" s="29" t="n">
+      <c r="F50" s="28" t="n">
         <v>4331347</v>
       </c>
-      <c r="G50" s="29" t="n">
+      <c r="G50" s="28" t="n">
         <f aca="false">F50*365/E50</f>
         <v>8734484.28176796</v>
       </c>
-      <c r="H50" s="29" t="n">
+      <c r="H50" s="28" t="n">
         <v>82571</v>
       </c>
-      <c r="I50" s="29" t="n">
+      <c r="I50" s="28" t="n">
         <v>1912969</v>
       </c>
       <c r="J50" s="57" t="n">
         <v>52.46</v>
       </c>
-      <c r="K50" s="68" t="n">
+      <c r="K50" s="70" t="n">
         <v>-0.249</v>
       </c>
-      <c r="L50" s="46" t="n">
+      <c r="L50" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M50" s="46" t="n">
+      <c r="M50" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="N50" s="46" t="n">
+      <c r="N50" s="45" t="n">
         <v>0</v>
       </c>
       <c r="O50" s="21" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="21" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E51" s="21" t="n">
         <v>56</v>
       </c>
-      <c r="F51" s="29" t="n">
+      <c r="F51" s="28" t="n">
         <v>1285957</v>
       </c>
-      <c r="G51" s="29" t="n">
+      <c r="G51" s="28" t="n">
         <f aca="false">F51*365/E51</f>
         <v>8381684.01785714</v>
       </c>
-      <c r="H51" s="29" t="n">
+      <c r="H51" s="28" t="n">
         <v>25265</v>
       </c>
-      <c r="I51" s="29" t="n">
+      <c r="I51" s="28" t="n">
         <v>568922</v>
       </c>
       <c r="J51" s="57" t="n">
         <v>50.9</v>
       </c>
-      <c r="K51" s="69" t="n">
+      <c r="K51" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="L51" s="46" t="n">
+      <c r="L51" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M51" s="46" t="n">
+      <c r="M51" s="45" t="n">
         <v>0.372</v>
       </c>
-      <c r="N51" s="46" t="n">
+      <c r="N51" s="45" t="n">
         <v>0</v>
       </c>
       <c r="O51" s="21" t="s">
-        <v>274</v>
+        <v>229</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="21" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="E52" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F52" s="29" t="n">
+      <c r="F52" s="28" t="n">
         <v>3783052</v>
       </c>
-      <c r="G52" s="29" t="n">
+      <c r="G52" s="28" t="n">
         <f aca="false">F52*365/E52</f>
         <v>7628806.51933702</v>
       </c>
-      <c r="H52" s="29" t="n">
+      <c r="H52" s="28" t="n">
         <v>82333</v>
       </c>
-      <c r="I52" s="29" t="n">
+      <c r="I52" s="28" t="n">
         <v>1672588</v>
       </c>
       <c r="J52" s="57" t="n">
         <v>45.95</v>
       </c>
-      <c r="K52" s="70" t="n">
+      <c r="K52" s="72" t="n">
         <v>0.137</v>
       </c>
-      <c r="L52" s="46" t="n">
+      <c r="L52" s="45" t="n">
         <v>0.008</v>
       </c>
-      <c r="M52" s="46" t="n">
+      <c r="M52" s="45" t="n">
         <v>0.335</v>
       </c>
-      <c r="N52" s="46" t="n">
+      <c r="N52" s="45" t="n">
         <v>0.017</v>
       </c>
       <c r="O52" s="21" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="21" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E53" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F53" s="29" t="n">
+      <c r="F53" s="28" t="n">
         <v>3334226</v>
       </c>
-      <c r="G53" s="29" t="n">
+      <c r="G53" s="28" t="n">
         <f aca="false">F53*365/E53</f>
         <v>6723715.41436464</v>
       </c>
-      <c r="H53" s="29" t="n">
+      <c r="H53" s="28" t="n">
         <v>60202</v>
       </c>
-      <c r="I53" s="29" t="n">
+      <c r="I53" s="28" t="n">
         <v>1601535</v>
       </c>
       <c r="J53" s="57" t="n">
         <v>55.38</v>
       </c>
-      <c r="K53" s="46" t="n">
+      <c r="K53" s="45" t="n">
         <v>0.045</v>
       </c>
-      <c r="L53" s="46" t="n">
+      <c r="L53" s="45" t="n">
         <v>0.015</v>
       </c>
-      <c r="M53" s="46" t="n">
+      <c r="M53" s="45" t="n">
         <v>0.375</v>
       </c>
-      <c r="N53" s="46" t="n">
+      <c r="N53" s="45" t="n">
         <v>0.292</v>
       </c>
       <c r="O53" s="21" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="21" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="E54" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F54" s="29" t="n">
+      <c r="F54" s="28" t="n">
         <v>3179944</v>
       </c>
-      <c r="G54" s="29" t="n">
+      <c r="G54" s="28" t="n">
         <f aca="false">F54*365/E54</f>
         <v>6412594.25414365</v>
       </c>
-      <c r="H54" s="29" t="n">
+      <c r="H54" s="28" t="n">
         <v>59244</v>
       </c>
-      <c r="I54" s="29" t="n">
+      <c r="I54" s="28" t="n">
         <v>1431054</v>
       </c>
       <c r="J54" s="57" t="n">
         <v>53.68</v>
       </c>
-      <c r="K54" s="46" t="n">
+      <c r="K54" s="45" t="n">
         <v>-0.028</v>
       </c>
-      <c r="L54" s="46" t="n">
+      <c r="L54" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M54" s="46" t="n">
+      <c r="M54" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="N54" s="46" t="n">
+      <c r="N54" s="45" t="n">
         <v>0.077</v>
       </c>
       <c r="O54" s="21" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="21" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="E55" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F55" s="29" t="n">
+      <c r="F55" s="28" t="n">
         <v>2708911</v>
       </c>
-      <c r="G55" s="29" t="n">
+      <c r="G55" s="28" t="n">
         <f aca="false">F55*365/E55</f>
         <v>5462721.07734807</v>
       </c>
-      <c r="H55" s="29" t="n">
+      <c r="H55" s="28" t="n">
         <v>50827</v>
       </c>
-      <c r="I55" s="29" t="n">
+      <c r="I55" s="28" t="n">
         <v>1262094</v>
       </c>
       <c r="J55" s="57" t="n">
         <v>53.3</v>
       </c>
-      <c r="K55" s="70" t="n">
+      <c r="K55" s="72" t="n">
         <v>0.188</v>
       </c>
-      <c r="L55" s="46" t="n">
+      <c r="L55" s="45" t="n">
         <v>0.005</v>
       </c>
-      <c r="M55" s="46" t="n">
+      <c r="M55" s="45" t="n">
         <v>0.408</v>
       </c>
-      <c r="N55" s="46" t="n">
+      <c r="N55" s="45" t="n">
         <v>0.18</v>
       </c>
       <c r="O55" s="20" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="21" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E56" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="F56" s="29" t="n">
+      <c r="F56" s="28" t="n">
         <v>2574779</v>
       </c>
-      <c r="G56" s="29" t="n">
+      <c r="G56" s="28" t="n">
         <f aca="false">F56*365/E56</f>
         <v>5192233.89502762</v>
       </c>
-      <c r="H56" s="29" t="n">
+      <c r="H56" s="28" t="n">
         <v>73820</v>
       </c>
-      <c r="I56" s="29" t="n">
+      <c r="I56" s="28" t="n">
         <v>1204453</v>
       </c>
       <c r="J56" s="57" t="n">
         <v>34.88</v>
       </c>
-      <c r="K56" s="70" t="n">
+      <c r="K56" s="72" t="n">
         <v>0.06</v>
       </c>
-      <c r="L56" s="46" t="n">
+      <c r="L56" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M56" s="46" t="n">
+      <c r="M56" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="N56" s="46" t="n">
+      <c r="N56" s="45" t="n">
         <v>0.194</v>
       </c>
       <c r="O56" s="21" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="21" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="E57" s="21" t="n">
         <v>39</v>
       </c>
-      <c r="F57" s="29" t="n">
+      <c r="F57" s="28" t="n">
         <v>436617</v>
       </c>
-      <c r="G57" s="29" t="n">
+      <c r="G57" s="28" t="n">
         <f aca="false">F57*365/E57</f>
         <v>4086287.30769231</v>
       </c>
-      <c r="H57" s="29" t="n">
+      <c r="H57" s="28" t="n">
         <v>7649</v>
       </c>
-      <c r="I57" s="29" t="n">
+      <c r="I57" s="28" t="n">
         <v>206212</v>
       </c>
       <c r="J57" s="57" t="n">
         <v>57.08</v>
       </c>
-      <c r="K57" s="69" t="n">
+      <c r="K57" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="L57" s="46" t="n">
+      <c r="L57" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M57" s="46" t="n">
+      <c r="M57" s="45" t="n">
         <v>0.4</v>
       </c>
-      <c r="N57" s="46" t="n">
+      <c r="N57" s="45" t="n">
         <v>0.249</v>
       </c>
       <c r="O57" s="20" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="21" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="E58" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="F58" s="29" t="n">
+      <c r="F58" s="28" t="n">
         <v>46160</v>
       </c>
-      <c r="G58" s="29" t="n">
+      <c r="G58" s="28" t="n">
         <f aca="false">F58*365/E58</f>
         <v>2808066.66666667</v>
       </c>
-      <c r="H58" s="29" t="n">
+      <c r="H58" s="28" t="n">
         <v>924</v>
       </c>
-      <c r="I58" s="29" t="n">
+      <c r="I58" s="28" t="n">
         <v>21693</v>
       </c>
       <c r="J58" s="57" t="n">
         <v>49.96</v>
       </c>
-      <c r="K58" s="69" t="n">
+      <c r="K58" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="L58" s="46" t="n">
+      <c r="L58" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="M58" s="46" t="n">
+      <c r="M58" s="45" t="n">
         <v>0.505</v>
       </c>
-      <c r="N58" s="46" t="n">
+      <c r="N58" s="45" t="n">
         <v>0.167</v>
       </c>
       <c r="O58" s="20" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="71" t="s">
-        <v>543</v>
+      <c r="A59" s="73" t="s">
+        <v>552</v>
       </c>
       <c r="B59" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="F59" s="72" t="n">
+      <c r="F59" s="74" t="n">
         <f aca="false">SUM(F4:F58)</f>
         <v>502415662</v>
       </c>
-      <c r="G59" s="72" t="n">
+      <c r="G59" s="74" t="n">
         <f aca="false">SUM(G4:G58)</f>
         <v>1271395370.83428</v>
       </c>
-      <c r="H59" s="72" t="n">
+      <c r="H59" s="74" t="n">
         <f aca="false">SUM(H4:H58)</f>
         <v>8824895</v>
       </c>
-      <c r="I59" s="72" t="n">
+      <c r="I59" s="74" t="n">
         <f aca="false">SUM(I4:I58)</f>
         <v>219475297</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="73" t="s">
-        <v>544</v>
-      </c>
-      <c r="B61" s="73"/>
-      <c r="C61" s="73"/>
-      <c r="D61" s="73"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="73"/>
-      <c r="J61" s="73"/>
-      <c r="K61" s="73"/>
-      <c r="L61" s="73"/>
-      <c r="M61" s="73"/>
-      <c r="N61" s="73"/>
-      <c r="O61" s="73"/>
+      <c r="A61" s="75" t="s">
+        <v>553</v>
+      </c>
+      <c r="B61" s="75"/>
+      <c r="C61" s="75"/>
+      <c r="D61" s="75"/>
+      <c r="E61" s="75"/>
+      <c r="F61" s="75"/>
+      <c r="G61" s="75"/>
+      <c r="H61" s="75"/>
+      <c r="I61" s="75"/>
+      <c r="J61" s="75"/>
+      <c r="K61" s="75"/>
+      <c r="L61" s="75"/>
+      <c r="M61" s="75"/>
+      <c r="N61" s="75"/>
+      <c r="O61" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/docs/executive-plan.xlsx
+++ b/docs/executive-plan.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="555">
   <si>
     <t xml:space="preserve">نموذج الخطة التنفيذية — الإدارة التجارية</t>
   </si>
@@ -513,19 +513,19 @@
     <t xml:space="preserve">ساسكو</t>
   </si>
   <si>
-    <t xml:space="preserve">~683 محطة (مُقدَّر Q1 2026) · 653 معلن Q4 2025 · +72 محطة 2024 · +81 محطة 2025 · +30 في Q1 2026 · هدف +100 سنوياً</t>
+    <t xml:space="preserve">~683 محطة (مُقدَّر Q1 2026) · 653 معلن Q4 2025 · الشبكة = ساسكو + نفط منذ 2022 (80% من خدمات النفط بـ1.1 مليار ريال · 233 موقعاً) · +72 (2024) +81 (2025) +30 (Q1 2026) · هدف +100 سنوياً</t>
   </si>
   <si>
     <t xml:space="preserve">الوقود · البطاقات (كنترول) · تطبيق الأفراد · الامتياز</t>
   </si>
   <si>
-    <t xml:space="preserve">الوحيد الذي يجمع تطبيق أفراد ناضجاً + كنترول للشركات · نقاط تُستبدل في مطاعم محطاته</t>
+    <t xml:space="preserve">ينمو بالاستحواذ على شبكات قائمة لا بالبناء وحده · الوحيد الذي يجمع تطبيق أفراد ناضجاً + كنترول للشركات · نقاط تُستبدل في مطاعم محطاته</t>
   </si>
   <si>
     <t xml:space="preserve">أصغر شبكة من الدريس · أدواته محصورة في شبكته</t>
   </si>
   <si>
-    <t xml:space="preserve">نقلّده في ربط التطبيق بالمستأجرين — وهو ما يجعل النقاط ذات قيمة فعلية</t>
+    <t xml:space="preserve">نقلّده في ربط التطبيق بالمستأجرين · وصفقة نفط تسعّر ضمّ الشبكات بنحو 4.7 مليون ريال للموقع — وهو مرجع لتقييم أصولنا غير المفعّلة</t>
   </si>
   <si>
     <t xml:space="preserve">sasco.com.sa · argaam.com</t>
@@ -672,7 +672,7 @@
     <t xml:space="preserve">مُقدَّر</t>
   </si>
   <si>
-    <t xml:space="preserve">+30 محطة في الربع الأول 2026 · الرئيس التنفيذي (مايو 2026) يقول الشبكة ≈10% · هدف +100 سنوياً</t>
+    <t xml:space="preserve">الشبكة مركّبة: ساسكو + نفط (استحوذت على 80% من خدمات النفط بـ1.1 مليار ريال في يناير 2022 — 233 موقعاً). +30 محطة في Q1 2026 · الرئيس التنفيذي (مايو 2026): الشبكة ≈10% · هدف +100 سنوياً تطويراً أو استحواذاً</t>
   </si>
   <si>
     <t xml:space="preserve">جي أويل</t>
@@ -757,6 +757,9 @@
   </si>
   <si>
     <t xml:space="preserve">الفارق بين «355» و«80» هو الفارق بين المركز الثالث والسادس — وهو نفس الغموض في رقم «1,790 محطة» بصفقة سيارة آب. كل رقم شبكة هنا يجب أن يُسأل: مملوكة أم امتياز أم موردة؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مرجع تسعير: ساسكو دفعت 1.1 مليار ريال مقابل 80% من نفط (233 موقعاً) — أي نحو 4.7 مليون ريال للموقع. فما قيمة الـ200 محطة امتياز في منظومتنا التي لم تكتمل هويتها؟ أصول بأيدينا لم تُفعَّل.</t>
   </si>
   <si>
     <t xml:space="preserve">التطبيقات والمنصات والبطاقات — التصنيف الصحيح</t>
@@ -3693,7 +3696,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -4117,13 +4120,26 @@
       <c r="H21" s="43"/>
       <c r="I21" s="43"/>
     </row>
+    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="42" t="s">
+        <v>243</v>
+      </c>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="B19:I19"/>
     <mergeCell ref="B20:I20"/>
     <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B22:I22"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4158,7 +4174,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4175,7 +4191,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4195,40 +4211,40 @@
         <v>43</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4239,13 +4255,13 @@
         <v>160</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F5" s="28" t="n">
         <v>683</v>
@@ -4258,19 +4274,19 @@
         <v>0.0935616438356164</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J5" s="16" t="s">
         <v>216</v>
       </c>
       <c r="K5" s="16" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L5" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4278,16 +4294,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F6" s="28" t="n">
         <v>12</v>
@@ -4300,19 +4316,19 @@
         <v>0.00164383561643836</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J6" s="16" t="s">
         <v>216</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L6" s="16" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M6" s="16" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4323,13 +4339,13 @@
         <v>219</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F7" s="28" t="n">
         <v>154</v>
@@ -4342,19 +4358,19 @@
         <v>0.0210958904109589</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J7" s="16" t="s">
         <v>216</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4362,16 +4378,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E8" s="47" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F8" s="48" t="n">
         <v>355</v>
@@ -4384,16 +4400,16 @@
         <v>0.0486301369863014</v>
       </c>
       <c r="I8" s="47" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J8" s="47" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K8" s="47" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L8" s="47" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M8" s="47" t="s">
         <v>229</v>
@@ -4404,16 +4420,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>46</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F9" s="28" t="n">
         <v>0</v>
@@ -4426,19 +4442,19 @@
         <v>0.684931506849315</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L9" s="16" t="s">
         <v>141</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4446,16 +4462,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="50" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>46</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F10" s="28" t="n">
         <v>1790</v>
@@ -4468,19 +4484,19 @@
         <v>0.342465753424658</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J10" s="16" t="s">
         <v>216</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4491,13 +4507,13 @@
         <v>183</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>46</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F11" s="28" t="n">
         <v>0</v>
@@ -4510,19 +4526,19 @@
         <v>0.684931506849315</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J11" s="16" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L11" s="16" t="s">
         <v>187</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4530,7 +4546,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>56</v>
@@ -4539,7 +4555,7 @@
         <v>46</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F12" s="28" t="n">
         <v>1383</v>
@@ -4552,19 +4568,19 @@
         <v>0.189452054794521</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J12" s="16" t="s">
         <v>216</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4572,7 +4588,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>160</v>
@@ -4581,7 +4597,7 @@
         <v>46</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F13" s="28" t="n">
         <v>683</v>
@@ -4594,27 +4610,27 @@
         <v>0.0935616438356164</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J13" s="16" t="s">
         <v>216</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="52" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C15" s="53" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D15" s="53"/>
       <c r="E15" s="53"/>
@@ -4629,10 +4645,10 @@
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="52" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C16" s="53" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D16" s="53"/>
       <c r="E16" s="53"/>
@@ -4647,10 +4663,10 @@
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="52" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D17" s="53"/>
       <c r="E17" s="53"/>
@@ -4665,10 +4681,10 @@
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="52" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C18" s="53" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D18" s="53"/>
       <c r="E18" s="53"/>
@@ -4726,7 +4742,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4745,7 +4761,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4776,60 +4792,60 @@
         <v>49</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>52</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>53</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="54" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C4" s="54" t="s">
         <v>46</v>
       </c>
       <c r="D4" s="55" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E4" s="54" t="n">
         <v>6</v>
       </c>
       <c r="F4" s="54" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G4" s="55" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H4" s="54" t="n">
         <v>20</v>
@@ -4843,19 +4859,19 @@
         <v>2.33333333333333</v>
       </c>
       <c r="K4" s="55" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L4" s="54" t="s">
         <v>72</v>
       </c>
       <c r="M4" s="55" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N4" s="55" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O4" s="54" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4875,10 +4891,10 @@
         <v>1271</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H5" s="58"/>
       <c r="I5" s="57" t="str">
@@ -4895,7 +4911,7 @@
       </c>
       <c r="M5" s="59"/>
       <c r="N5" s="16" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O5" s="60"/>
     </row>
@@ -4916,10 +4932,10 @@
         <v>25</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H6" s="58"/>
       <c r="I6" s="57" t="str">
@@ -4936,7 +4952,7 @@
       </c>
       <c r="M6" s="59"/>
       <c r="N6" s="16" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O6" s="60"/>
     </row>
@@ -4957,10 +4973,10 @@
         <v>39</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H7" s="58"/>
       <c r="I7" s="57" t="str">
@@ -4977,7 +4993,7 @@
       </c>
       <c r="M7" s="59"/>
       <c r="N7" s="16" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O7" s="60"/>
     </row>
@@ -4998,10 +5014,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H8" s="58"/>
       <c r="I8" s="57" t="str">
@@ -5018,7 +5034,7 @@
       </c>
       <c r="M8" s="59"/>
       <c r="N8" s="16" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O8" s="60"/>
     </row>
@@ -5027,22 +5043,22 @@
         <v>5</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E9" s="57" t="n">
         <v>0.28</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H9" s="58"/>
       <c r="I9" s="57" t="str">
@@ -5059,7 +5075,7 @@
       </c>
       <c r="M9" s="59"/>
       <c r="N9" s="16" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O9" s="60"/>
     </row>
@@ -5068,22 +5084,22 @@
         <v>6</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E10" s="57" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H10" s="58"/>
       <c r="I10" s="57" t="str">
@@ -5100,7 +5116,7 @@
       </c>
       <c r="M10" s="59"/>
       <c r="N10" s="16" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O10" s="60"/>
     </row>
@@ -5115,16 +5131,16 @@
         <v>89</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E11" s="57" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H11" s="58"/>
       <c r="I11" s="57" t="str">
@@ -5141,7 +5157,7 @@
       </c>
       <c r="M11" s="59"/>
       <c r="N11" s="16" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O11" s="60"/>
     </row>
@@ -5162,10 +5178,10 @@
         <v>31</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H12" s="58"/>
       <c r="I12" s="57" t="str">
@@ -5182,7 +5198,7 @@
       </c>
       <c r="M12" s="59"/>
       <c r="N12" s="16" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O12" s="60"/>
     </row>
@@ -5203,10 +5219,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H13" s="58"/>
       <c r="I13" s="57" t="str">
@@ -5223,7 +5239,7 @@
       </c>
       <c r="M13" s="59"/>
       <c r="N13" s="16" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O13" s="60"/>
     </row>
@@ -5244,10 +5260,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H14" s="58"/>
       <c r="I14" s="57" t="str">
@@ -5264,7 +5280,7 @@
       </c>
       <c r="M14" s="59"/>
       <c r="N14" s="16" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O14" s="60"/>
     </row>
@@ -5279,16 +5295,16 @@
         <v>46</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E15" s="57" t="n">
         <v>6</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H15" s="58"/>
       <c r="I15" s="57" t="str">
@@ -5305,7 +5321,7 @@
       </c>
       <c r="M15" s="59"/>
       <c r="N15" s="16" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O15" s="60"/>
     </row>
@@ -5320,16 +5336,16 @@
         <v>46</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E16" s="57" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H16" s="58"/>
       <c r="I16" s="57" t="str">
@@ -5346,16 +5362,16 @@
       </c>
       <c r="M16" s="59"/>
       <c r="N16" s="16" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O16" s="60"/>
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C18" s="61" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D18" s="61"/>
       <c r="E18" s="61"/>
@@ -5416,7 +5432,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5437,31 +5453,31 @@
         <v>44</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5472,7 +5488,7 @@
         <v>55</v>
       </c>
       <c r="C4" s="63" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D4" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E5</f>
@@ -5503,7 +5519,7 @@
         <v>61</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D5" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E6</f>
@@ -5534,7 +5550,7 @@
         <v>67</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D6" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E7</f>
@@ -5565,7 +5581,7 @@
         <v>73</v>
       </c>
       <c r="C7" s="63" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D7" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E8</f>
@@ -5593,10 +5609,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D8" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E9</f>
@@ -5624,10 +5640,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C9" s="63" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D9" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E10</f>
@@ -5658,7 +5674,7 @@
         <v>88</v>
       </c>
       <c r="C10" s="63" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D10" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E11</f>
@@ -5689,7 +5705,7 @@
         <v>94</v>
       </c>
       <c r="C11" s="63" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D11" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E12</f>
@@ -5720,7 +5736,7 @@
         <v>98</v>
       </c>
       <c r="C12" s="63" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D12" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E13</f>
@@ -5751,7 +5767,7 @@
         <v>102</v>
       </c>
       <c r="C13" s="63" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D13" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E14</f>
@@ -5782,7 +5798,7 @@
         <v>106</v>
       </c>
       <c r="C14" s="63" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D14" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E15</f>
@@ -5813,7 +5829,7 @@
         <v>111</v>
       </c>
       <c r="C15" s="63" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D15" s="64" t="n">
         <f aca="false">'الخطة التنفيذية'!E16</f>
@@ -5875,7 +5891,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5893,7 +5909,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5914,51 +5930,51 @@
         <v>43</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>53</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J3" s="15" t="s">
         <v>54</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="54" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C4" s="54" t="s">
         <v>61</v>
@@ -5970,7 +5986,7 @@
         <v>66</v>
       </c>
       <c r="F4" s="54" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G4" s="65" t="n">
         <v>46235</v>
@@ -5986,13 +6002,13 @@
         <v>1</v>
       </c>
       <c r="K4" s="54" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L4" s="55" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M4" s="54" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N4" s="66" t="n">
         <v>0</v>
@@ -6504,7 +6520,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="24" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M30" s="21" t="str">
         <f aca="false">COUNTA(B5:B28)&amp;" مبادرة"</f>
@@ -6556,7 +6572,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6575,7 +6591,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6594,63 +6610,63 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E4" s="21" t="n">
         <v>181</v>
@@ -6684,21 +6700,21 @@
         <v>0.281</v>
       </c>
       <c r="O4" s="21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E5" s="21" t="n">
         <v>91</v>
@@ -6732,21 +6748,21 @@
         <v>0</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E6" s="21" t="n">
         <v>91</v>
@@ -6780,21 +6796,21 @@
         <v>0.344</v>
       </c>
       <c r="O6" s="21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E7" s="21" t="n">
         <v>176</v>
@@ -6828,21 +6844,21 @@
         <v>0.641</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E8" s="21" t="n">
         <v>180</v>
@@ -6876,21 +6892,21 @@
         <v>0.134</v>
       </c>
       <c r="O8" s="21" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E9" s="21" t="n">
         <v>55</v>
@@ -6924,21 +6940,21 @@
         <v>0.309</v>
       </c>
       <c r="O9" s="21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E10" s="21" t="n">
         <v>63</v>
@@ -6972,21 +6988,21 @@
         <v>0.006</v>
       </c>
       <c r="O10" s="21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E11" s="21" t="n">
         <v>65</v>
@@ -7020,21 +7036,21 @@
         <v>0</v>
       </c>
       <c r="O11" s="21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E12" s="21" t="n">
         <v>181</v>
@@ -7068,21 +7084,21 @@
         <v>0.277</v>
       </c>
       <c r="O12" s="21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E13" s="21" t="n">
         <v>181</v>
@@ -7116,21 +7132,21 @@
         <v>0.082</v>
       </c>
       <c r="O13" s="21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E14" s="21" t="n">
         <v>181</v>
@@ -7164,21 +7180,21 @@
         <v>0.231</v>
       </c>
       <c r="O14" s="21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E15" s="21" t="n">
         <v>181</v>
@@ -7212,21 +7228,21 @@
         <v>0.458</v>
       </c>
       <c r="O15" s="21" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E16" s="21" t="n">
         <v>181</v>
@@ -7260,21 +7276,21 @@
         <v>0.076</v>
       </c>
       <c r="O16" s="21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E17" s="21" t="n">
         <v>57</v>
@@ -7308,21 +7324,21 @@
         <v>0</v>
       </c>
       <c r="O17" s="21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E18" s="21" t="n">
         <v>181</v>
@@ -7356,21 +7372,21 @@
         <v>0</v>
       </c>
       <c r="O18" s="21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E19" s="21" t="n">
         <v>130</v>
@@ -7404,21 +7420,21 @@
         <v>0.048</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E20" s="21" t="n">
         <v>70</v>
@@ -7452,21 +7468,21 @@
         <v>0</v>
       </c>
       <c r="O20" s="21" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E21" s="21" t="n">
         <v>181</v>
@@ -7500,21 +7516,21 @@
         <v>0</v>
       </c>
       <c r="O21" s="21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E22" s="21" t="n">
         <v>147</v>
@@ -7548,21 +7564,21 @@
         <v>0.329</v>
       </c>
       <c r="O22" s="21" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E23" s="21" t="n">
         <v>181</v>
@@ -7596,21 +7612,21 @@
         <v>0</v>
       </c>
       <c r="O23" s="21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E24" s="21" t="n">
         <v>181</v>
@@ -7644,21 +7660,21 @@
         <v>0</v>
       </c>
       <c r="O24" s="21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E25" s="21" t="n">
         <v>181</v>
@@ -7692,21 +7708,21 @@
         <v>0.058</v>
       </c>
       <c r="O25" s="21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E26" s="21" t="n">
         <v>181</v>
@@ -7740,21 +7756,21 @@
         <v>0.276</v>
       </c>
       <c r="O26" s="21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E27" s="21" t="n">
         <v>181</v>
@@ -7788,21 +7804,21 @@
         <v>0.27</v>
       </c>
       <c r="O27" s="21" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E28" s="21" t="n">
         <v>111</v>
@@ -7836,21 +7852,21 @@
         <v>0.349</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E29" s="21" t="n">
         <v>181</v>
@@ -7884,21 +7900,21 @@
         <v>0.321</v>
       </c>
       <c r="O29" s="21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E30" s="21" t="n">
         <v>92</v>
@@ -7932,21 +7948,21 @@
         <v>0.176</v>
       </c>
       <c r="O30" s="21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E31" s="21" t="n">
         <v>181</v>
@@ -7980,21 +7996,21 @@
         <v>0.082</v>
       </c>
       <c r="O31" s="21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E32" s="21" t="n">
         <v>69</v>
@@ -8028,21 +8044,21 @@
         <v>0.103</v>
       </c>
       <c r="O32" s="20" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E33" s="21" t="n">
         <v>181</v>
@@ -8076,21 +8092,21 @@
         <v>0.023</v>
       </c>
       <c r="O33" s="21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E34" s="21" t="n">
         <v>181</v>
@@ -8124,21 +8140,21 @@
         <v>0.559</v>
       </c>
       <c r="O34" s="21" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E35" s="21" t="n">
         <v>181</v>
@@ -8172,21 +8188,21 @@
         <v>0</v>
       </c>
       <c r="O35" s="21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E36" s="21" t="n">
         <v>181</v>
@@ -8220,21 +8236,21 @@
         <v>0.115</v>
       </c>
       <c r="O36" s="21" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E37" s="21" t="n">
         <v>26</v>
@@ -8273,16 +8289,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E38" s="21" t="n">
         <v>181</v>
@@ -8316,21 +8332,21 @@
         <v>0.167</v>
       </c>
       <c r="O38" s="21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="21" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E39" s="21" t="n">
         <v>181</v>
@@ -8364,21 +8380,21 @@
         <v>0.106</v>
       </c>
       <c r="O39" s="21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="21" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E40" s="21" t="n">
         <v>181</v>
@@ -8412,21 +8428,21 @@
         <v>0.373</v>
       </c>
       <c r="O40" s="21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="21" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E41" s="21" t="n">
         <v>181</v>
@@ -8460,21 +8476,21 @@
         <v>0</v>
       </c>
       <c r="O41" s="21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="21" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E42" s="21" t="n">
         <v>68</v>
@@ -8508,21 +8524,21 @@
         <v>0.056</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E43" s="21" t="n">
         <v>181</v>
@@ -8556,21 +8572,21 @@
         <v>0.077</v>
       </c>
       <c r="O43" s="21" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E44" s="21" t="n">
         <v>181</v>
@@ -8604,21 +8620,21 @@
         <v>0.066</v>
       </c>
       <c r="O44" s="20" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="21" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E45" s="21" t="n">
         <v>181</v>
@@ -8652,21 +8668,21 @@
         <v>0.392</v>
       </c>
       <c r="O45" s="20" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="21" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E46" s="21" t="n">
         <v>181</v>
@@ -8700,21 +8716,21 @@
         <v>0.236</v>
       </c>
       <c r="O46" s="21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="21" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E47" s="21" t="n">
         <v>181</v>
@@ -8748,21 +8764,21 @@
         <v>0.184</v>
       </c>
       <c r="O47" s="21" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="21" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E48" s="21" t="n">
         <v>181</v>
@@ -8796,21 +8812,21 @@
         <v>0</v>
       </c>
       <c r="O48" s="21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="21" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E49" s="21" t="n">
         <v>181</v>
@@ -8844,21 +8860,21 @@
         <v>0.201</v>
       </c>
       <c r="O49" s="21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="21" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E50" s="21" t="n">
         <v>181</v>
@@ -8892,21 +8908,21 @@
         <v>0</v>
       </c>
       <c r="O50" s="21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="21" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E51" s="21" t="n">
         <v>56</v>
@@ -8945,16 +8961,16 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="21" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E52" s="21" t="n">
         <v>181</v>
@@ -8988,21 +9004,21 @@
         <v>0.017</v>
       </c>
       <c r="O52" s="21" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="21" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E53" s="21" t="n">
         <v>181</v>
@@ -9036,21 +9052,21 @@
         <v>0.292</v>
       </c>
       <c r="O53" s="21" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="21" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E54" s="21" t="n">
         <v>181</v>
@@ -9084,21 +9100,21 @@
         <v>0.077</v>
       </c>
       <c r="O54" s="21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="21" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E55" s="21" t="n">
         <v>181</v>
@@ -9132,21 +9148,21 @@
         <v>0.18</v>
       </c>
       <c r="O55" s="20" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="21" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E56" s="21" t="n">
         <v>181</v>
@@ -9180,21 +9196,21 @@
         <v>0.194</v>
       </c>
       <c r="O56" s="21" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="21" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E57" s="21" t="n">
         <v>39</v>
@@ -9228,21 +9244,21 @@
         <v>0.249</v>
       </c>
       <c r="O57" s="20" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="21" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E58" s="21" t="n">
         <v>6</v>
@@ -9276,12 +9292,12 @@
         <v>0.167</v>
       </c>
       <c r="O58" s="20" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="73" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B59" s="24" t="s">
         <v>116</v>
@@ -9305,7 +9321,7 @@
     </row>
     <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="75" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B61" s="75"/>
       <c r="C61" s="75"/>

--- a/docs/executive-plan.xlsx
+++ b/docs/executive-plan.xlsx
@@ -15,10 +15,11 @@
     <sheet name="التطبيقات والمنصات" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="منفذ ٢ — العقار والتأجير" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="منفذ ٤ — الإكسسوارات" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="الخطة التنفيذية" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="المستهدفات الربعية" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="المبادرات" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="المحطات" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="تحليل موقفي — المنتجات" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="الخطة التنفيذية" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="المستهدفات الربعية" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="المبادرات" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="المحطات" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="891">
   <si>
     <t xml:space="preserve">نموذج الخطة التنفيذية — الإدارة التجارية</t>
   </si>
@@ -77,24 +78,24 @@
     <t xml:space="preserve">خارطة التنفيذ — مبادرة · مسؤول · تاريخ · حالة.</t>
   </si>
   <si>
+    <t xml:space="preserve">تحليل موقفي — المنتجات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كل منتج داخل رحلة العميل: موقعه ومكوثه ومالكه وفجوته.</t>
+  </si>
+  <si>
     <t xml:space="preserve">منفذ ٢ — العقار</t>
   </si>
   <si>
     <t xml:space="preserve">تفصيل الشواغر والعلامات — الأولوية الأولى.</t>
   </si>
   <si>
-    <t xml:space="preserve">منفذ ٤ — الإكسسوارات</t>
+    <t xml:space="preserve">دليل الألوان</t>
   </si>
   <si>
     <t xml:space="preserve">السوق واللاعبون وقرار التأجير مقابل التشغيل.</t>
   </si>
   <si>
-    <t xml:space="preserve">دليل الألوان</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حصص محطات المملكة وأين نقف.</t>
-  </si>
-  <si>
     <t xml:space="preserve">أصفر + خط أزرق</t>
   </si>
   <si>
@@ -1539,6 +1540,489 @@
   </si>
   <si>
     <t xml:space="preserve">بترو آب و Fleet Plus تبيعان الإطارات والبطاريات والزيوت للأسطول داخل محطاتنا دون عقد معنا. أي أن المنفذ يُستنزف قبل أن نفتحه.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التحليل الموقفي — كل منتج داخل المحطة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أين يقع في رحلة العميل · متى يُقرَّر · كم يحتاج مكوثاً · من يملكه · وأين الفجوة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المبدأ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زمن المكوث هو ما يحدد ما يمكن بيعه. تعبئة الوقود 4 دقائق لا تسمح إلا بقرار يُتخذ في ثوانٍ. والغسيل يفتح نافذة 20 دقيقة، وتغيير الزيت 45، والشحن الكهربائي 30، ومبيت الشاحنة ليلة كاملة. لذلك المنتجات التي تُطيل المكوث تُموّل المنتجات التي تحتاج مكوثاً — ونحن لا نبيع اللتر بل نبيع الزمن الذي يقضيه العميل عندنا.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المنتج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">موقعه في المحطة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لحظة القرار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المكوث</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وجهة/سلة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">من يملك العلاقة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نموذج إيرادنا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحضور</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأساس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الفجوة من 71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">القرار الموقفي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أ · عند المضخة — 3 إلى 5 دقائق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بنزين 91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المضخة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قبل الوصول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 د</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وجهة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نحن — بلا هوية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هامش اللتر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6% من الإيراد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المنتج الأساس — لكن 62.6% نقداً يعني أننا نبيعه لمجهول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بنزين 95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1% من الإيراد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شريحة أعلى قيمة — ولا نعرف من يشتريها لنبني عليها</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ديزل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 د</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأسطول — غالباً بلا عقد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3% من الإيراد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بصمة الأسطول: MK289 ديزلها 64.1% وتنمو 27.3% — حجم قائم بلا عقد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ب · عند الكاشير — ثوانٍ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إكسسوارات سريعة الدوران</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رفّ الكاشير</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اندفاعي بعد الدفع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ثوانٍ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سلة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا أحد — غير مُفعّل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بيع مباشر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أرخص منتج يمكن إطلاقه: رفّ واحد بلا مساحة ولا عقد — يرفع سلة الزيارة فوراً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ماركت / بقالة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وحدة تجارية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بعد الدفع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 د</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مستأجر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إيجار ثابت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أعلى اختراق لدينا · فريش واي في 17 محطة — النموذج الوحيد القابل للتكرار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حلويات وآيسكريم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كشك</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اندفاعي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 د</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مكمّل للقهوة — يرفع السلة في نفس نافذة المكوث</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ج · مكوث قصير — 5 إلى 15 دقيقة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قهوة / كافيه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بعد الدفع أو قصداً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 د</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سلة ← وجهة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مستأجر — 67 علامة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بعلامة قوية يتحوّل من سلة إلى وجهة · لكن 67 علامة تعني صفر قوة تفاوضية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مسار مستقل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مستأجر — علامة قوية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إيجار + نسبة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 وحدات شاغرة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الوحيد الذي يجلب زيارة لا تحتاج وقوداً — أعلى قيمة استراتيجية بين الشواغر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">د · مكوث متوسط — 15 إلى 45 دقيقة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مطعم / وجبات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قصداً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 د</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مستأجر — 48 علامة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يجلب الزيارة ويُطيل المكوث — ماكدونالدز في 7 وكنتاكي في 6 فقط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">غسيل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الساحة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أثناء التعبئة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 د</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مستأجر أو شريك</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إيجار أو نسبة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يفتح نافذة القهوة والوجبة — قيمته في المكوث الذي يصنعه لا في رسمه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زيوت وصيانة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ورشة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قصداً أو مؤجَّل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 د</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بترومين وشركاء — 11 محطة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إيجار — لا هامش خدمة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نأخذ إيجاراً ونترك هامش الخدمة للشريك · وأطول نافذة مكوث في المحطة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بنشر وإطارات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">طارئ أو سنوي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40 د</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أعلى سلة في القطاع وأدنى اختراق عندنا — 61 محطة مفتوحة بلا خدمة إطارات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زينة وتجهيز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مخطَّط ومقارَن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 د</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تأجير + نسبة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مخزون بطيء ومرتجعات — لا تشغيل ذاتي · تُؤجَّر لمتخصص بنسبة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هـ · الساحة والمرافق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صراف آلي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الواجهة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عابر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وجهة صغيرة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بنك</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إيجار موقع ثابت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بيع موقع لا بيع منتج · ميزتنا الوصول 24 ساعة والأمان — و66 محطة بلا صراف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خزائن ذكية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عابر مجدول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 د</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مشغّل الخزائن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redbox في محطة واحدة · نمو التجارة الإلكترونية يجعلها إيراداً ثابتاً بلا تشغيل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شحن كهربائي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 د</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVIQ — لم يبدأ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عقد استضافة موقع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الشاحن ليس المنتج — المنتج نافذة الـ30 دقيقة التي يفتحها للتأجير</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مواقف شاحنات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أرض غير مبنية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ليلة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">غير مُستثمر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رسم موقف + ديزل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صفر · 5,420 م² متاحة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أطول مكوث ممكن · يغذّي الديزل والأسطول مباشرة — سائق يبيت يعبّئ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لوحات إعلانية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الواجهة والسور</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا يشتريه العميل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا أحد — الأصل معطّل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إيجار مساحة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صفر من 355 موقعاً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">◄ مقام مختلف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المسيطر (العربية للإعلان) يشتري مواقع نملكها · إيراد بلا تشغيل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">و · طبقة تعبر كل المنتجات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التطبيق وتانكي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قبل وأثناء وبعد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">طبقة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نحن — نظرياً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بيانات + حملات مموّلة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28% · 43 محطة بصفر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ليس منتجاً بموقع بل الطبقة التي تربط كل المنتجات أعلاه بعميل معروف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بطاقة/عقد الأسطول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قرار المنشأة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بترو آب — لا نحن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عقد شبكة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صفر عقود موثّقة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحجم يمرّ في محطاتنا اليوم — والعقد عند غيرنا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ما يكشفه الترتيب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منتجاتنا القوية كلها «سلة» تركب على زيارة الوقود (ماركت 51% · قهوة 49%). ومنتجات «الوجهة» التي تجلب زيارة مستقلة هي الأضعف: بنشر 14% · درايف ثرو صفر · شحن صفر · مواقف صفر. أي أننا نعيش على حركة الوقود ولا نصنع حركة.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أطول مكوث هو أضعف موقفنا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الزيت والصيانة أطول نافذة في المحطة (45 دقيقة) ونأخذ عنها إيجاراً فقط — الهامش للشريك. والشحن الكهربائي يفتح 30 دقيقة ولم يبدأ. والمواقف تفتح ليلة كاملة وغير مُستثمرة. نملك الزمن ولا نبيعه.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أرخص مبادرة في الملف كله</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رفّ الإكسسوارات سريعة الدوران عند الكاشير: بلا مساحة ولا عقد ولا مستأجر — ويُختبر في محطة واحدة خلال أسابيع. صفر اليوم في 71 محطة مفتوحة.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الفجوات المرقّمة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61 محطة بلا إطارات · 66 بلا صراف · 70 بلا خزائن · 71 بلا إكسسوارات · 71 بلا شحن · 71 بلا مواقف · 355 موقعاً بلا إيراد إعلاني. وكل رقم منها وحدة تجارية شاغرة محتملة.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الطبقة التي تجعل كل ما سبق قابلاً للقياس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التطبيق ليس منتجاً بموقع — هو الطبقة التي تحوّل 22.5 مليون زيارة مجهولة إلى عميل معروف. وبدونه كل منتج أعلاه يُباع مرة واحدة لمجهول، ولا يمكن قياس أثر أي مبادرة.</t>
   </si>
   <si>
     <t xml:space="preserve">الخطة التنفيذية لمنافذ البيع</t>
@@ -2236,7 +2720,7 @@
     <numFmt numFmtId="170" formatCode="#,##0.00"/>
     <numFmt numFmtId="171" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2349,6 +2833,14 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF44546A"/>
       <name val="Arial"/>
@@ -2364,7 +2856,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2410,7 +2902,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE7E6E6"/>
-        <bgColor rgb="FFD9E2F3"/>
+        <bgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -2422,11 +2914,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E2F3"/>
-        <bgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFD9E2F3"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -2441,6 +2939,19 @@
       <right style="thin">
         <color rgb="FFBFBFBF"/>
       </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
@@ -2475,7 +2986,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="83">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2508,11 +3019,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2720,6 +3231,14 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
@@ -2748,7 +3267,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2796,7 +3315,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2830,7 +3349,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFD9E2F3"/>
+      <rgbColor rgb="FFDDEBF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -2844,10 +3363,10 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFE7E6E6"/>
+      <rgbColor rgb="FFD9E2F3"/>
       <rgbColor rgb="FFC6E0B4"/>
       <rgbColor rgb="FFFFE699"/>
-      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFE7E6E6"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFF8CBAD"/>
@@ -3174,15 +3693,15 @@
       <c r="B17" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3195,7 +3714,7 @@
       <c r="B21" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="9" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3203,7 +3722,7 @@
       <c r="B22" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="9" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3211,7 +3730,7 @@
       <c r="B23" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="9" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3219,7 +3738,7 @@
       <c r="B24" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="9" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3227,7 +3746,7 @@
       <c r="B25" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="9" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3263,6 +3782,475 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>673</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>666</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>725</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>726</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>727</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>728</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>729</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="72" t="s">
+        <v>685</v>
+      </c>
+      <c r="D4" s="73" t="n">
+        <f aca="false">'الخطة التنفيذية'!E5</f>
+        <v>1271</v>
+      </c>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="73" t="str">
+        <f aca="false">IF('الخطة التنفيذية'!H5="","",'الخطة التنفيذية'!H5)</f>
+        <v/>
+      </c>
+      <c r="J4" s="21" t="str">
+        <f aca="false">IF(H4="","",IF(H4=I4,"مطابق","مختلف"))</f>
+        <v/>
+      </c>
+      <c r="K4" s="45" t="str">
+        <f aca="false">IFERROR(IF(H4="","",(H4-D4)/D4),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="72" t="s">
+        <v>688</v>
+      </c>
+      <c r="D5" s="73" t="n">
+        <f aca="false">'الخطة التنفيذية'!E6</f>
+        <v>25</v>
+      </c>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="73" t="str">
+        <f aca="false">IF('الخطة التنفيذية'!H6="","",'الخطة التنفيذية'!H6)</f>
+        <v/>
+      </c>
+      <c r="J5" s="21" t="str">
+        <f aca="false">IF(H5="","",IF(H5=I5,"مطابق","مختلف"))</f>
+        <v/>
+      </c>
+      <c r="K5" s="45" t="str">
+        <f aca="false">IFERROR(IF(H5="","",(H5-D5)/D5),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="71" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="72" t="s">
+        <v>690</v>
+      </c>
+      <c r="D6" s="73" t="n">
+        <f aca="false">'الخطة التنفيذية'!E7</f>
+        <v>39</v>
+      </c>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="73" t="str">
+        <f aca="false">IF('الخطة التنفيذية'!H7="","",'الخطة التنفيذية'!H7)</f>
+        <v/>
+      </c>
+      <c r="J6" s="21" t="str">
+        <f aca="false">IF(H6="","",IF(H6=I6,"مطابق","مختلف"))</f>
+        <v/>
+      </c>
+      <c r="K6" s="45" t="str">
+        <f aca="false">IFERROR(IF(H6="","",(H6-D6)/D6),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="71" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="72" t="s">
+        <v>693</v>
+      </c>
+      <c r="D7" s="73" t="n">
+        <f aca="false">'الخطة التنفيذية'!E8</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="73" t="str">
+        <f aca="false">IF('الخطة التنفيذية'!H8="","",'الخطة التنفيذية'!H8)</f>
+        <v/>
+      </c>
+      <c r="J7" s="21" t="str">
+        <f aca="false">IF(H7="","",IF(H7=I7,"مطابق","مختلف"))</f>
+        <v/>
+      </c>
+      <c r="K7" s="45" t="str">
+        <f aca="false">IFERROR(IF(H7="","",(H7-D7)/D7),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="71" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>694</v>
+      </c>
+      <c r="C8" s="72" t="s">
+        <v>698</v>
+      </c>
+      <c r="D8" s="73" t="n">
+        <f aca="false">'الخطة التنفيذية'!E9</f>
+        <v>0.28</v>
+      </c>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="73" t="str">
+        <f aca="false">IF('الخطة التنفيذية'!H9="","",'الخطة التنفيذية'!H9)</f>
+        <v/>
+      </c>
+      <c r="J8" s="21" t="str">
+        <f aca="false">IF(H8="","",IF(H8=I8,"مطابق","مختلف"))</f>
+        <v/>
+      </c>
+      <c r="K8" s="45" t="str">
+        <f aca="false">IFERROR(IF(H8="","",(H8-D8)/D8),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="71" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>699</v>
+      </c>
+      <c r="C9" s="72" t="s">
+        <v>702</v>
+      </c>
+      <c r="D9" s="73" t="n">
+        <f aca="false">'الخطة التنفيذية'!E10</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="73" t="str">
+        <f aca="false">IF('الخطة التنفيذية'!H10="","",'الخطة التنفيذية'!H10)</f>
+        <v/>
+      </c>
+      <c r="J9" s="21" t="str">
+        <f aca="false">IF(H9="","",IF(H9=I9,"مطابق","مختلف"))</f>
+        <v/>
+      </c>
+      <c r="K9" s="45" t="str">
+        <f aca="false">IFERROR(IF(H9="","",(H9-D9)/D9),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="71" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="72" t="s">
+        <v>706</v>
+      </c>
+      <c r="D10" s="73" t="n">
+        <f aca="false">'الخطة التنفيذية'!E11</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="73" t="str">
+        <f aca="false">IF('الخطة التنفيذية'!H11="","",'الخطة التنفيذية'!H11)</f>
+        <v/>
+      </c>
+      <c r="J10" s="21" t="str">
+        <f aca="false">IF(H10="","",IF(H10=I10,"مطابق","مختلف"))</f>
+        <v/>
+      </c>
+      <c r="K10" s="45" t="str">
+        <f aca="false">IFERROR(IF(H10="","",(H10-D10)/D10),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="71" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="72" t="s">
+        <v>709</v>
+      </c>
+      <c r="D11" s="73" t="n">
+        <f aca="false">'الخطة التنفيذية'!E12</f>
+        <v>31</v>
+      </c>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="73" t="str">
+        <f aca="false">IF('الخطة التنفيذية'!H12="","",'الخطة التنفيذية'!H12)</f>
+        <v/>
+      </c>
+      <c r="J11" s="21" t="str">
+        <f aca="false">IF(H11="","",IF(H11=I11,"مطابق","مختلف"))</f>
+        <v/>
+      </c>
+      <c r="K11" s="45" t="str">
+        <f aca="false">IFERROR(IF(H11="","",(H11-D11)/D11),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="71" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="72" t="s">
+        <v>712</v>
+      </c>
+      <c r="D12" s="73" t="n">
+        <f aca="false">'الخطة التنفيذية'!E13</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="73" t="str">
+        <f aca="false">IF('الخطة التنفيذية'!H13="","",'الخطة التنفيذية'!H13)</f>
+        <v/>
+      </c>
+      <c r="J12" s="21" t="str">
+        <f aca="false">IF(H12="","",IF(H12=I12,"مطابق","مختلف"))</f>
+        <v/>
+      </c>
+      <c r="K12" s="45" t="str">
+        <f aca="false">IFERROR(IF(H12="","",(H12-D12)/D12),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="71" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="72" t="s">
+        <v>715</v>
+      </c>
+      <c r="D13" s="73" t="n">
+        <f aca="false">'الخطة التنفيذية'!E14</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="73" t="str">
+        <f aca="false">IF('الخطة التنفيذية'!H14="","",'الخطة التنفيذية'!H14)</f>
+        <v/>
+      </c>
+      <c r="J13" s="21" t="str">
+        <f aca="false">IF(H13="","",IF(H13=I13,"مطابق","مختلف"))</f>
+        <v/>
+      </c>
+      <c r="K13" s="45" t="str">
+        <f aca="false">IFERROR(IF(H13="","",(H13-D13)/D13),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="71" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="72" t="s">
+        <v>717</v>
+      </c>
+      <c r="D14" s="73" t="n">
+        <f aca="false">'الخطة التنفيذية'!E15</f>
+        <v>6</v>
+      </c>
+      <c r="E14" s="67"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="73" t="str">
+        <f aca="false">IF('الخطة التنفيذية'!H15="","",'الخطة التنفيذية'!H15)</f>
+        <v/>
+      </c>
+      <c r="J14" s="21" t="str">
+        <f aca="false">IF(H14="","",IF(H14=I14,"مطابق","مختلف"))</f>
+        <v/>
+      </c>
+      <c r="K14" s="45" t="str">
+        <f aca="false">IFERROR(IF(H14="","",(H14-D14)/D14),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="71" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="72" t="s">
+        <v>721</v>
+      </c>
+      <c r="D15" s="73" t="n">
+        <f aca="false">'الخطة التنفيذية'!E16</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="67"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="73" t="str">
+        <f aca="false">IF('الخطة التنفيذية'!H16="","",'الخطة التنفيذية'!H16)</f>
+        <v/>
+      </c>
+      <c r="J15" s="21" t="str">
+        <f aca="false">IF(H15="","",IF(H15=I15,"مطابق","مختلف"))</f>
+        <v/>
+      </c>
+      <c r="K15" s="45" t="str">
+        <f aca="false">IFERROR(IF(H15="","",(H15-D15)/D15),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -3286,7 +4274,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>570</v>
+        <v>731</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3304,7 +4292,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>571</v>
+        <v>732</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3325,597 +4313,597 @@
         <v>46</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>572</v>
+        <v>733</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>47</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>573</v>
+        <v>734</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>56</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>511</v>
+        <v>672</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>574</v>
+        <v>735</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>575</v>
+        <v>736</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>576</v>
+        <v>737</v>
       </c>
       <c r="J3" s="15" t="s">
         <v>57</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>577</v>
+        <v>738</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>578</v>
+        <v>739</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>378</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>579</v>
+        <v>740</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="61" t="s">
-        <v>513</v>
-      </c>
-      <c r="B4" s="62" t="s">
-        <v>580</v>
-      </c>
-      <c r="C4" s="61" t="s">
+      <c r="A4" s="63" t="s">
+        <v>674</v>
+      </c>
+      <c r="B4" s="64" t="s">
+        <v>741</v>
+      </c>
+      <c r="C4" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="61" t="s">
+      <c r="D4" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="61" t="s">
+      <c r="E4" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="61" t="s">
-        <v>519</v>
-      </c>
-      <c r="G4" s="72" t="n">
+      <c r="F4" s="63" t="s">
+        <v>680</v>
+      </c>
+      <c r="G4" s="74" t="n">
         <v>46235</v>
       </c>
-      <c r="H4" s="72" t="n">
+      <c r="H4" s="74" t="n">
         <v>46326</v>
       </c>
-      <c r="I4" s="61" t="n">
+      <c r="I4" s="63" t="n">
         <f aca="false">IF(OR(G4="",H4=""),"",H4-G4)</f>
         <v>91</v>
       </c>
-      <c r="J4" s="61" t="n">
+      <c r="J4" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="61" t="s">
-        <v>581</v>
-      </c>
-      <c r="L4" s="62" t="s">
-        <v>582</v>
-      </c>
-      <c r="M4" s="61" t="s">
-        <v>521</v>
-      </c>
-      <c r="N4" s="73" t="n">
+      <c r="K4" s="63" t="s">
+        <v>742</v>
+      </c>
+      <c r="L4" s="64" t="s">
+        <v>743</v>
+      </c>
+      <c r="M4" s="63" t="s">
+        <v>682</v>
+      </c>
+      <c r="N4" s="75" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="69" t="n">
+      <c r="A5" s="71" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
       <c r="I5" s="21" t="str">
         <f aca="false">IF(OR(G5="",H5=""),"",H5-G5)</f>
         <v/>
       </c>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="66"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="75"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="77"/>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="69" t="n">
+      <c r="A6" s="71" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
       <c r="I6" s="21" t="str">
         <f aca="false">IF(OR(G6="",H6=""),"",H6-G6)</f>
         <v/>
       </c>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="66"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="75"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="77"/>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="69" t="n">
+      <c r="A7" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="66"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="74"/>
-      <c r="H7" s="74"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="76"/>
       <c r="I7" s="21" t="str">
         <f aca="false">IF(OR(G7="",H7=""),"",H7-G7)</f>
         <v/>
       </c>
-      <c r="J7" s="67"/>
-      <c r="K7" s="67"/>
-      <c r="L7" s="66"/>
-      <c r="M7" s="67"/>
-      <c r="N7" s="75"/>
+      <c r="J7" s="69"/>
+      <c r="K7" s="69"/>
+      <c r="L7" s="68"/>
+      <c r="M7" s="69"/>
+      <c r="N7" s="77"/>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="69" t="n">
+      <c r="A8" s="71" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="66"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="74"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
       <c r="I8" s="21" t="str">
         <f aca="false">IF(OR(G8="",H8=""),"",H8-G8)</f>
         <v/>
       </c>
-      <c r="J8" s="67"/>
-      <c r="K8" s="67"/>
-      <c r="L8" s="66"/>
-      <c r="M8" s="67"/>
-      <c r="N8" s="75"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="69"/>
+      <c r="N8" s="77"/>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="69" t="n">
+      <c r="A9" s="71" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="66"/>
-      <c r="C9" s="67"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
       <c r="I9" s="21" t="str">
         <f aca="false">IF(OR(G9="",H9=""),"",H9-G9)</f>
         <v/>
       </c>
-      <c r="J9" s="67"/>
-      <c r="K9" s="67"/>
-      <c r="L9" s="66"/>
-      <c r="M9" s="67"/>
-      <c r="N9" s="75"/>
+      <c r="J9" s="69"/>
+      <c r="K9" s="69"/>
+      <c r="L9" s="68"/>
+      <c r="M9" s="69"/>
+      <c r="N9" s="77"/>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="69" t="n">
+      <c r="A10" s="71" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="66"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
       <c r="I10" s="21" t="str">
         <f aca="false">IF(OR(G10="",H10=""),"",H10-G10)</f>
         <v/>
       </c>
-      <c r="J10" s="67"/>
-      <c r="K10" s="67"/>
-      <c r="L10" s="66"/>
-      <c r="M10" s="67"/>
-      <c r="N10" s="75"/>
+      <c r="J10" s="69"/>
+      <c r="K10" s="69"/>
+      <c r="L10" s="68"/>
+      <c r="M10" s="69"/>
+      <c r="N10" s="77"/>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="69" t="n">
+      <c r="A11" s="71" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="66"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
       <c r="I11" s="21" t="str">
         <f aca="false">IF(OR(G11="",H11=""),"",H11-G11)</f>
         <v/>
       </c>
-      <c r="J11" s="67"/>
-      <c r="K11" s="67"/>
-      <c r="L11" s="66"/>
-      <c r="M11" s="67"/>
-      <c r="N11" s="75"/>
+      <c r="J11" s="69"/>
+      <c r="K11" s="69"/>
+      <c r="L11" s="68"/>
+      <c r="M11" s="69"/>
+      <c r="N11" s="77"/>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="69" t="n">
+      <c r="A12" s="71" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
       <c r="I12" s="21" t="str">
         <f aca="false">IF(OR(G12="",H12=""),"",H12-G12)</f>
         <v/>
       </c>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="66"/>
-      <c r="M12" s="67"/>
-      <c r="N12" s="75"/>
+      <c r="J12" s="69"/>
+      <c r="K12" s="69"/>
+      <c r="L12" s="68"/>
+      <c r="M12" s="69"/>
+      <c r="N12" s="77"/>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="69" t="n">
+      <c r="A13" s="71" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
       <c r="I13" s="21" t="str">
         <f aca="false">IF(OR(G13="",H13=""),"",H13-G13)</f>
         <v/>
       </c>
-      <c r="J13" s="67"/>
-      <c r="K13" s="67"/>
-      <c r="L13" s="66"/>
-      <c r="M13" s="67"/>
-      <c r="N13" s="75"/>
+      <c r="J13" s="69"/>
+      <c r="K13" s="69"/>
+      <c r="L13" s="68"/>
+      <c r="M13" s="69"/>
+      <c r="N13" s="77"/>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="69" t="n">
+      <c r="A14" s="71" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="66"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="74"/>
+      <c r="B14" s="68"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="76"/>
       <c r="I14" s="21" t="str">
         <f aca="false">IF(OR(G14="",H14=""),"",H14-G14)</f>
         <v/>
       </c>
-      <c r="J14" s="67"/>
-      <c r="K14" s="67"/>
-      <c r="L14" s="66"/>
-      <c r="M14" s="67"/>
-      <c r="N14" s="75"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="69"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="69"/>
+      <c r="N14" s="77"/>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="69" t="n">
+      <c r="A15" s="71" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="67"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="74"/>
-      <c r="H15" s="74"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="76"/>
       <c r="I15" s="21" t="str">
         <f aca="false">IF(OR(G15="",H15=""),"",H15-G15)</f>
         <v/>
       </c>
-      <c r="J15" s="67"/>
-      <c r="K15" s="67"/>
-      <c r="L15" s="66"/>
-      <c r="M15" s="67"/>
-      <c r="N15" s="75"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="69"/>
+      <c r="L15" s="68"/>
+      <c r="M15" s="69"/>
+      <c r="N15" s="77"/>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="69" t="n">
+      <c r="A16" s="71" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="67"/>
-      <c r="D16" s="67"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="67"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="74"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="76"/>
       <c r="I16" s="21" t="str">
         <f aca="false">IF(OR(G16="",H16=""),"",H16-G16)</f>
         <v/>
       </c>
-      <c r="J16" s="67"/>
-      <c r="K16" s="67"/>
-      <c r="L16" s="66"/>
-      <c r="M16" s="67"/>
-      <c r="N16" s="75"/>
+      <c r="J16" s="69"/>
+      <c r="K16" s="69"/>
+      <c r="L16" s="68"/>
+      <c r="M16" s="69"/>
+      <c r="N16" s="77"/>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="69" t="n">
+      <c r="A17" s="71" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="66"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="67"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="74"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="76"/>
       <c r="I17" s="21" t="str">
         <f aca="false">IF(OR(G17="",H17=""),"",H17-G17)</f>
         <v/>
       </c>
-      <c r="J17" s="67"/>
-      <c r="K17" s="67"/>
-      <c r="L17" s="66"/>
-      <c r="M17" s="67"/>
-      <c r="N17" s="75"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="69"/>
+      <c r="L17" s="68"/>
+      <c r="M17" s="69"/>
+      <c r="N17" s="77"/>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="69" t="n">
+      <c r="A18" s="71" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="66"/>
-      <c r="C18" s="67"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="67"/>
-      <c r="G18" s="74"/>
-      <c r="H18" s="74"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="76"/>
       <c r="I18" s="21" t="str">
         <f aca="false">IF(OR(G18="",H18=""),"",H18-G18)</f>
         <v/>
       </c>
-      <c r="J18" s="67"/>
-      <c r="K18" s="67"/>
-      <c r="L18" s="66"/>
-      <c r="M18" s="67"/>
-      <c r="N18" s="75"/>
+      <c r="J18" s="69"/>
+      <c r="K18" s="69"/>
+      <c r="L18" s="68"/>
+      <c r="M18" s="69"/>
+      <c r="N18" s="77"/>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="69" t="n">
+      <c r="A19" s="71" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="66"/>
-      <c r="C19" s="67"/>
-      <c r="D19" s="67"/>
-      <c r="E19" s="67"/>
-      <c r="F19" s="67"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="74"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="76"/>
       <c r="I19" s="21" t="str">
         <f aca="false">IF(OR(G19="",H19=""),"",H19-G19)</f>
         <v/>
       </c>
-      <c r="J19" s="67"/>
-      <c r="K19" s="67"/>
-      <c r="L19" s="66"/>
-      <c r="M19" s="67"/>
-      <c r="N19" s="75"/>
+      <c r="J19" s="69"/>
+      <c r="K19" s="69"/>
+      <c r="L19" s="68"/>
+      <c r="M19" s="69"/>
+      <c r="N19" s="77"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="69" t="n">
+      <c r="A20" s="71" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="66"/>
-      <c r="C20" s="67"/>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="74"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="76"/>
       <c r="I20" s="21" t="str">
         <f aca="false">IF(OR(G20="",H20=""),"",H20-G20)</f>
         <v/>
       </c>
-      <c r="J20" s="67"/>
-      <c r="K20" s="67"/>
-      <c r="L20" s="66"/>
-      <c r="M20" s="67"/>
-      <c r="N20" s="75"/>
+      <c r="J20" s="69"/>
+      <c r="K20" s="69"/>
+      <c r="L20" s="68"/>
+      <c r="M20" s="69"/>
+      <c r="N20" s="77"/>
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="69" t="n">
+      <c r="A21" s="71" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="66"/>
-      <c r="C21" s="67"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="74"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="76"/>
       <c r="I21" s="21" t="str">
         <f aca="false">IF(OR(G21="",H21=""),"",H21-G21)</f>
         <v/>
       </c>
-      <c r="J21" s="67"/>
-      <c r="K21" s="67"/>
-      <c r="L21" s="66"/>
-      <c r="M21" s="67"/>
-      <c r="N21" s="75"/>
+      <c r="J21" s="69"/>
+      <c r="K21" s="69"/>
+      <c r="L21" s="68"/>
+      <c r="M21" s="69"/>
+      <c r="N21" s="77"/>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="69" t="n">
+      <c r="A22" s="71" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="66"/>
-      <c r="C22" s="67"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="74"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="76"/>
       <c r="I22" s="21" t="str">
         <f aca="false">IF(OR(G22="",H22=""),"",H22-G22)</f>
         <v/>
       </c>
-      <c r="J22" s="67"/>
-      <c r="K22" s="67"/>
-      <c r="L22" s="66"/>
-      <c r="M22" s="67"/>
-      <c r="N22" s="75"/>
+      <c r="J22" s="69"/>
+      <c r="K22" s="69"/>
+      <c r="L22" s="68"/>
+      <c r="M22" s="69"/>
+      <c r="N22" s="77"/>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="69" t="n">
+      <c r="A23" s="71" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="66"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="74"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="69"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="76"/>
       <c r="I23" s="21" t="str">
         <f aca="false">IF(OR(G23="",H23=""),"",H23-G23)</f>
         <v/>
       </c>
-      <c r="J23" s="67"/>
-      <c r="K23" s="67"/>
-      <c r="L23" s="66"/>
-      <c r="M23" s="67"/>
-      <c r="N23" s="75"/>
+      <c r="J23" s="69"/>
+      <c r="K23" s="69"/>
+      <c r="L23" s="68"/>
+      <c r="M23" s="69"/>
+      <c r="N23" s="77"/>
     </row>
     <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="69" t="n">
+      <c r="A24" s="71" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="66"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="67"/>
-      <c r="E24" s="67"/>
-      <c r="F24" s="67"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="74"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="69"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="76"/>
       <c r="I24" s="21" t="str">
         <f aca="false">IF(OR(G24="",H24=""),"",H24-G24)</f>
         <v/>
       </c>
-      <c r="J24" s="67"/>
-      <c r="K24" s="67"/>
-      <c r="L24" s="66"/>
-      <c r="M24" s="67"/>
-      <c r="N24" s="75"/>
+      <c r="J24" s="69"/>
+      <c r="K24" s="69"/>
+      <c r="L24" s="68"/>
+      <c r="M24" s="69"/>
+      <c r="N24" s="77"/>
     </row>
     <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="69" t="n">
+      <c r="A25" s="71" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="66"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="74"/>
-      <c r="H25" s="74"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="69"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="76"/>
       <c r="I25" s="21" t="str">
         <f aca="false">IF(OR(G25="",H25=""),"",H25-G25)</f>
         <v/>
       </c>
-      <c r="J25" s="67"/>
-      <c r="K25" s="67"/>
-      <c r="L25" s="66"/>
-      <c r="M25" s="67"/>
-      <c r="N25" s="75"/>
+      <c r="J25" s="69"/>
+      <c r="K25" s="69"/>
+      <c r="L25" s="68"/>
+      <c r="M25" s="69"/>
+      <c r="N25" s="77"/>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="69" t="n">
+      <c r="A26" s="71" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="66"/>
-      <c r="C26" s="67"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="67"/>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="76"/>
       <c r="I26" s="21" t="str">
         <f aca="false">IF(OR(G26="",H26=""),"",H26-G26)</f>
         <v/>
       </c>
-      <c r="J26" s="67"/>
-      <c r="K26" s="67"/>
-      <c r="L26" s="66"/>
-      <c r="M26" s="67"/>
-      <c r="N26" s="75"/>
+      <c r="J26" s="69"/>
+      <c r="K26" s="69"/>
+      <c r="L26" s="68"/>
+      <c r="M26" s="69"/>
+      <c r="N26" s="77"/>
     </row>
     <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="69" t="n">
+      <c r="A27" s="71" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="66"/>
-      <c r="C27" s="67"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="67"/>
-      <c r="F27" s="67"/>
-      <c r="G27" s="74"/>
-      <c r="H27" s="74"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="69"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="76"/>
       <c r="I27" s="21" t="str">
         <f aca="false">IF(OR(G27="",H27=""),"",H27-G27)</f>
         <v/>
       </c>
-      <c r="J27" s="67"/>
-      <c r="K27" s="67"/>
-      <c r="L27" s="66"/>
-      <c r="M27" s="67"/>
-      <c r="N27" s="75"/>
+      <c r="J27" s="69"/>
+      <c r="K27" s="69"/>
+      <c r="L27" s="68"/>
+      <c r="M27" s="69"/>
+      <c r="N27" s="77"/>
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="69" t="n">
+      <c r="A28" s="71" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="66"/>
-      <c r="C28" s="67"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="67"/>
-      <c r="F28" s="67"/>
-      <c r="G28" s="74"/>
-      <c r="H28" s="74"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="69"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="76"/>
       <c r="I28" s="21" t="str">
         <f aca="false">IF(OR(G28="",H28=""),"",H28-G28)</f>
         <v/>
       </c>
-      <c r="J28" s="67"/>
-      <c r="K28" s="67"/>
-      <c r="L28" s="66"/>
-      <c r="M28" s="67"/>
-      <c r="N28" s="75"/>
+      <c r="J28" s="69"/>
+      <c r="K28" s="69"/>
+      <c r="L28" s="68"/>
+      <c r="M28" s="69"/>
+      <c r="N28" s="77"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="24" t="s">
-        <v>583</v>
+        <v>744</v>
       </c>
       <c r="M30" s="21" t="str">
         <f aca="false">COUNTA(B5:B28)&amp;" مبادرة"</f>
@@ -3941,7 +4929,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -3967,7 +4955,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>584</v>
+        <v>745</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3986,7 +4974,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>585</v>
+        <v>746</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4005,63 +4993,63 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>586</v>
+        <v>747</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>587</v>
+        <v>748</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>588</v>
+        <v>749</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>589</v>
+        <v>750</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>590</v>
+        <v>751</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>591</v>
+        <v>752</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>592</v>
+        <v>753</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>593</v>
+        <v>754</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>594</v>
+        <v>755</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>595</v>
+        <v>756</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>596</v>
+        <v>757</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>597</v>
+        <v>758</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>598</v>
+        <v>759</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>599</v>
+        <v>760</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>600</v>
+        <v>761</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>601</v>
+        <v>762</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>602</v>
+        <v>763</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E4" s="21" t="n">
         <v>181</v>
@@ -4079,7 +5067,7 @@
       <c r="I4" s="28" t="n">
         <v>23493282</v>
       </c>
-      <c r="J4" s="64" t="n">
+      <c r="J4" s="66" t="n">
         <v>64.69</v>
       </c>
       <c r="K4" s="57" t="n">
@@ -4095,21 +5083,21 @@
         <v>0.281</v>
       </c>
       <c r="O4" s="21" t="s">
-        <v>605</v>
+        <v>766</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>606</v>
+        <v>767</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>607</v>
+        <v>768</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>608</v>
+        <v>769</v>
       </c>
       <c r="E5" s="21" t="n">
         <v>91</v>
@@ -4127,10 +5115,10 @@
       <c r="I5" s="28" t="n">
         <v>8841940</v>
       </c>
-      <c r="J5" s="64" t="n">
+      <c r="J5" s="66" t="n">
         <v>61.72</v>
       </c>
-      <c r="K5" s="76" t="n">
+      <c r="K5" s="78" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="45" t="n">
@@ -4143,21 +5131,21 @@
         <v>0</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>609</v>
+        <v>770</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>610</v>
+        <v>771</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>611</v>
+        <v>772</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>612</v>
+        <v>773</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E6" s="21" t="n">
         <v>91</v>
@@ -4175,10 +5163,10 @@
       <c r="I6" s="28" t="n">
         <v>7467484</v>
       </c>
-      <c r="J6" s="64" t="n">
+      <c r="J6" s="66" t="n">
         <v>80.21</v>
       </c>
-      <c r="K6" s="76" t="n">
+      <c r="K6" s="78" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="45" t="n">
@@ -4191,21 +5179,21 @@
         <v>0.344</v>
       </c>
       <c r="O6" s="21" t="s">
-        <v>613</v>
+        <v>774</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>614</v>
+        <v>775</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>615</v>
+        <v>776</v>
       </c>
       <c r="C7" s="21" t="s">
         <v>345</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>608</v>
+        <v>769</v>
       </c>
       <c r="E7" s="21" t="n">
         <v>176</v>
@@ -4223,10 +5211,10 @@
       <c r="I7" s="28" t="n">
         <v>14552120</v>
       </c>
-      <c r="J7" s="64" t="n">
+      <c r="J7" s="66" t="n">
         <v>84.21</v>
       </c>
-      <c r="K7" s="77" t="n">
+      <c r="K7" s="79" t="n">
         <v>0.273</v>
       </c>
       <c r="L7" s="45" t="n">
@@ -4239,21 +5227,21 @@
         <v>0.641</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>616</v>
+        <v>777</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>617</v>
+        <v>778</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>618</v>
+        <v>779</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E8" s="21" t="n">
         <v>180</v>
@@ -4271,7 +5259,7 @@
       <c r="I8" s="28" t="n">
         <v>2916708</v>
       </c>
-      <c r="J8" s="64" t="n">
+      <c r="J8" s="66" t="n">
         <v>48.35</v>
       </c>
       <c r="K8" s="57" t="n">
@@ -4287,21 +5275,21 @@
         <v>0.134</v>
       </c>
       <c r="O8" s="21" t="s">
-        <v>619</v>
+        <v>780</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>620</v>
+        <v>781</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>621</v>
+        <v>782</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>612</v>
+        <v>773</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>622</v>
+        <v>783</v>
       </c>
       <c r="E9" s="21" t="n">
         <v>55</v>
@@ -4319,10 +5307,10 @@
       <c r="I9" s="28" t="n">
         <v>2916316</v>
       </c>
-      <c r="J9" s="64" t="n">
+      <c r="J9" s="66" t="n">
         <v>65.82</v>
       </c>
-      <c r="K9" s="76" t="n">
+      <c r="K9" s="78" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="45" t="n">
@@ -4335,21 +5323,21 @@
         <v>0.309</v>
       </c>
       <c r="O9" s="21" t="s">
-        <v>605</v>
+        <v>766</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>623</v>
+        <v>784</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>624</v>
+        <v>785</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>612</v>
+        <v>773</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E10" s="21" t="n">
         <v>63</v>
@@ -4367,10 +5355,10 @@
       <c r="I10" s="28" t="n">
         <v>2831981</v>
       </c>
-      <c r="J10" s="64" t="n">
+      <c r="J10" s="66" t="n">
         <v>59.14</v>
       </c>
-      <c r="K10" s="76" t="n">
+      <c r="K10" s="78" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="45" t="n">
@@ -4383,21 +5371,21 @@
         <v>0.006</v>
       </c>
       <c r="O10" s="21" t="s">
-        <v>613</v>
+        <v>774</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>625</v>
+        <v>786</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>626</v>
+        <v>787</v>
       </c>
       <c r="C11" s="21" t="s">
         <v>345</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E11" s="21" t="n">
         <v>65</v>
@@ -4415,10 +5403,10 @@
       <c r="I11" s="28" t="n">
         <v>2931550</v>
       </c>
-      <c r="J11" s="64" t="n">
+      <c r="J11" s="66" t="n">
         <v>49.84</v>
       </c>
-      <c r="K11" s="76" t="n">
+      <c r="K11" s="78" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="45" t="n">
@@ -4431,21 +5419,21 @@
         <v>0</v>
       </c>
       <c r="O11" s="21" t="s">
-        <v>613</v>
+        <v>774</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>627</v>
+        <v>788</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>628</v>
+        <v>789</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E12" s="21" t="n">
         <v>181</v>
@@ -4463,7 +5451,7 @@
       <c r="I12" s="28" t="n">
         <v>8679738</v>
       </c>
-      <c r="J12" s="64" t="n">
+      <c r="J12" s="66" t="n">
         <v>59.34</v>
       </c>
       <c r="K12" s="57" t="n">
@@ -4479,21 +5467,21 @@
         <v>0.277</v>
       </c>
       <c r="O12" s="21" t="s">
-        <v>613</v>
+        <v>774</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>629</v>
+        <v>790</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>630</v>
+        <v>791</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>612</v>
+        <v>773</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>622</v>
+        <v>783</v>
       </c>
       <c r="E13" s="21" t="n">
         <v>181</v>
@@ -4511,7 +5499,7 @@
       <c r="I13" s="28" t="n">
         <v>7729931</v>
       </c>
-      <c r="J13" s="64" t="n">
+      <c r="J13" s="66" t="n">
         <v>67.66</v>
       </c>
       <c r="K13" s="57" t="n">
@@ -4527,21 +5515,21 @@
         <v>0.082</v>
       </c>
       <c r="O13" s="21" t="s">
-        <v>613</v>
+        <v>774</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>631</v>
+        <v>792</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>632</v>
+        <v>793</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E14" s="21" t="n">
         <v>181</v>
@@ -4559,7 +5547,7 @@
       <c r="I14" s="28" t="n">
         <v>2676944</v>
       </c>
-      <c r="J14" s="64" t="n">
+      <c r="J14" s="66" t="n">
         <v>59.47</v>
       </c>
       <c r="K14" s="45" t="n">
@@ -4575,21 +5563,21 @@
         <v>0.231</v>
       </c>
       <c r="O14" s="21" t="s">
-        <v>613</v>
+        <v>774</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>633</v>
+        <v>794</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>634</v>
+        <v>795</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>608</v>
+        <v>769</v>
       </c>
       <c r="E15" s="21" t="n">
         <v>181</v>
@@ -4607,7 +5595,7 @@
       <c r="I15" s="28" t="n">
         <v>7806709</v>
       </c>
-      <c r="J15" s="64" t="n">
+      <c r="J15" s="66" t="n">
         <v>63.18</v>
       </c>
       <c r="K15" s="57" t="n">
@@ -4623,21 +5611,21 @@
         <v>0.458</v>
       </c>
       <c r="O15" s="21" t="s">
-        <v>619</v>
+        <v>780</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>635</v>
+        <v>796</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>636</v>
+        <v>797</v>
       </c>
       <c r="C16" s="21" t="s">
         <v>350</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E16" s="21" t="n">
         <v>181</v>
@@ -4655,10 +5643,10 @@
       <c r="I16" s="28" t="n">
         <v>4791911</v>
       </c>
-      <c r="J16" s="64" t="n">
+      <c r="J16" s="66" t="n">
         <v>74.3</v>
       </c>
-      <c r="K16" s="77" t="n">
+      <c r="K16" s="79" t="n">
         <v>0.151</v>
       </c>
       <c r="L16" s="45" t="n">
@@ -4671,21 +5659,21 @@
         <v>0.076</v>
       </c>
       <c r="O16" s="21" t="s">
-        <v>613</v>
+        <v>774</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>637</v>
+        <v>798</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>638</v>
+        <v>799</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>612</v>
+        <v>773</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E17" s="21" t="n">
         <v>57</v>
@@ -4703,10 +5691,10 @@
       <c r="I17" s="28" t="n">
         <v>2078856</v>
       </c>
-      <c r="J17" s="64" t="n">
+      <c r="J17" s="66" t="n">
         <v>55.76</v>
       </c>
-      <c r="K17" s="76" t="n">
+      <c r="K17" s="78" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="45" t="n">
@@ -4719,21 +5707,21 @@
         <v>0</v>
       </c>
       <c r="O17" s="21" t="s">
-        <v>605</v>
+        <v>766</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>639</v>
+        <v>800</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>640</v>
+        <v>801</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E18" s="21" t="n">
         <v>181</v>
@@ -4751,7 +5739,7 @@
       <c r="I18" s="28" t="n">
         <v>6570004</v>
       </c>
-      <c r="J18" s="64" t="n">
+      <c r="J18" s="66" t="n">
         <v>43.71</v>
       </c>
       <c r="K18" s="45" t="n">
@@ -4767,21 +5755,21 @@
         <v>0</v>
       </c>
       <c r="O18" s="21" t="s">
-        <v>605</v>
+        <v>766</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>641</v>
+        <v>802</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>642</v>
+        <v>803</v>
       </c>
       <c r="C19" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>643</v>
+        <v>804</v>
       </c>
       <c r="E19" s="21" t="n">
         <v>130</v>
@@ -4799,10 +5787,10 @@
       <c r="I19" s="28" t="n">
         <v>4445436</v>
       </c>
-      <c r="J19" s="64" t="n">
+      <c r="J19" s="66" t="n">
         <v>42.14</v>
       </c>
-      <c r="K19" s="77" t="n">
+      <c r="K19" s="79" t="n">
         <v>0.275</v>
       </c>
       <c r="L19" s="45" t="n">
@@ -4815,21 +5803,21 @@
         <v>0.048</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>616</v>
+        <v>777</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>644</v>
+        <v>805</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>645</v>
+        <v>806</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>646</v>
+        <v>807</v>
       </c>
       <c r="E20" s="21" t="n">
         <v>70</v>
@@ -4847,10 +5835,10 @@
       <c r="I20" s="28" t="n">
         <v>2229579</v>
       </c>
-      <c r="J20" s="64" t="n">
+      <c r="J20" s="66" t="n">
         <v>43.6</v>
       </c>
-      <c r="K20" s="76" t="n">
+      <c r="K20" s="78" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="45" t="n">
@@ -4863,21 +5851,21 @@
         <v>0</v>
       </c>
       <c r="O20" s="21" t="s">
-        <v>609</v>
+        <v>770</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>647</v>
+        <v>808</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>648</v>
+        <v>809</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E21" s="21" t="n">
         <v>181</v>
@@ -4895,7 +5883,7 @@
       <c r="I21" s="28" t="n">
         <v>5504980</v>
       </c>
-      <c r="J21" s="64" t="n">
+      <c r="J21" s="66" t="n">
         <v>43.52</v>
       </c>
       <c r="K21" s="57" t="n">
@@ -4911,21 +5899,21 @@
         <v>0</v>
       </c>
       <c r="O21" s="21" t="s">
-        <v>613</v>
+        <v>774</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>649</v>
+        <v>810</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>650</v>
+        <v>811</v>
       </c>
       <c r="C22" s="21" t="s">
         <v>345</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E22" s="21" t="n">
         <v>147</v>
@@ -4943,10 +5931,10 @@
       <c r="I22" s="28" t="n">
         <v>4722403</v>
       </c>
-      <c r="J22" s="64" t="n">
+      <c r="J22" s="66" t="n">
         <v>49.88</v>
       </c>
-      <c r="K22" s="77" t="n">
+      <c r="K22" s="79" t="n">
         <v>0.068</v>
       </c>
       <c r="L22" s="45" t="n">
@@ -4959,21 +5947,21 @@
         <v>0.329</v>
       </c>
       <c r="O22" s="21" t="s">
-        <v>619</v>
+        <v>780</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>651</v>
+        <v>812</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>652</v>
+        <v>813</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E23" s="21" t="n">
         <v>181</v>
@@ -4991,10 +5979,10 @@
       <c r="I23" s="28" t="n">
         <v>4924931</v>
       </c>
-      <c r="J23" s="64" t="n">
+      <c r="J23" s="66" t="n">
         <v>47.68</v>
       </c>
-      <c r="K23" s="77" t="n">
+      <c r="K23" s="79" t="n">
         <v>0.069</v>
       </c>
       <c r="L23" s="45" t="n">
@@ -5007,21 +5995,21 @@
         <v>0</v>
       </c>
       <c r="O23" s="21" t="s">
-        <v>613</v>
+        <v>774</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>653</v>
+        <v>814</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>654</v>
+        <v>815</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E24" s="21" t="n">
         <v>181</v>
@@ -5039,7 +6027,7 @@
       <c r="I24" s="28" t="n">
         <v>4740020</v>
       </c>
-      <c r="J24" s="64" t="n">
+      <c r="J24" s="66" t="n">
         <v>43.42</v>
       </c>
       <c r="K24" s="45" t="n">
@@ -5055,21 +6043,21 @@
         <v>0</v>
       </c>
       <c r="O24" s="21" t="s">
-        <v>613</v>
+        <v>774</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>655</v>
+        <v>816</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>656</v>
+        <v>817</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>612</v>
+        <v>773</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>622</v>
+        <v>783</v>
       </c>
       <c r="E25" s="21" t="n">
         <v>181</v>
@@ -5087,10 +6075,10 @@
       <c r="I25" s="28" t="n">
         <v>4771577</v>
       </c>
-      <c r="J25" s="64" t="n">
+      <c r="J25" s="66" t="n">
         <v>51.68</v>
       </c>
-      <c r="K25" s="77" t="n">
+      <c r="K25" s="79" t="n">
         <v>0.177</v>
       </c>
       <c r="L25" s="45" t="n">
@@ -5103,21 +6091,21 @@
         <v>0.058</v>
       </c>
       <c r="O25" s="21" t="s">
-        <v>605</v>
+        <v>766</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>657</v>
+        <v>818</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>658</v>
+        <v>819</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>646</v>
+        <v>807</v>
       </c>
       <c r="E26" s="21" t="n">
         <v>181</v>
@@ -5135,7 +6123,7 @@
       <c r="I26" s="28" t="n">
         <v>4933540</v>
       </c>
-      <c r="J26" s="64" t="n">
+      <c r="J26" s="66" t="n">
         <v>51.76</v>
       </c>
       <c r="K26" s="45" t="n">
@@ -5151,21 +6139,21 @@
         <v>0.276</v>
       </c>
       <c r="O26" s="21" t="s">
-        <v>605</v>
+        <v>766</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>659</v>
+        <v>820</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>660</v>
+        <v>821</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>612</v>
+        <v>773</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>622</v>
+        <v>783</v>
       </c>
       <c r="E27" s="21" t="n">
         <v>181</v>
@@ -5183,10 +6171,10 @@
       <c r="I27" s="28" t="n">
         <v>4643058</v>
       </c>
-      <c r="J27" s="64" t="n">
+      <c r="J27" s="66" t="n">
         <v>66.28</v>
       </c>
-      <c r="K27" s="77" t="n">
+      <c r="K27" s="79" t="n">
         <v>0.083</v>
       </c>
       <c r="L27" s="45" t="n">
@@ -5199,21 +6187,21 @@
         <v>0.27</v>
       </c>
       <c r="O27" s="21" t="s">
-        <v>661</v>
+        <v>822</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>662</v>
+        <v>823</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>663</v>
+        <v>824</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>608</v>
+        <v>769</v>
       </c>
       <c r="E28" s="21" t="n">
         <v>111</v>
@@ -5231,10 +6219,10 @@
       <c r="I28" s="28" t="n">
         <v>2834084</v>
       </c>
-      <c r="J28" s="64" t="n">
+      <c r="J28" s="66" t="n">
         <v>77.81</v>
       </c>
-      <c r="K28" s="76" t="n">
+      <c r="K28" s="78" t="n">
         <v>-0.033</v>
       </c>
       <c r="L28" s="45" t="n">
@@ -5247,21 +6235,21 @@
         <v>0.349</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>616</v>
+        <v>777</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>664</v>
+        <v>825</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>665</v>
+        <v>826</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>646</v>
+        <v>807</v>
       </c>
       <c r="E29" s="21" t="n">
         <v>181</v>
@@ -5279,7 +6267,7 @@
       <c r="I29" s="28" t="n">
         <v>4558563</v>
       </c>
-      <c r="J29" s="64" t="n">
+      <c r="J29" s="66" t="n">
         <v>64.44</v>
       </c>
       <c r="K29" s="45" t="n">
@@ -5295,21 +6283,21 @@
         <v>0.321</v>
       </c>
       <c r="O29" s="21" t="s">
-        <v>605</v>
+        <v>766</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>666</v>
+        <v>827</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>667</v>
+        <v>828</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E30" s="21" t="n">
         <v>92</v>
@@ -5327,10 +6315,10 @@
       <c r="I30" s="28" t="n">
         <v>2127665</v>
       </c>
-      <c r="J30" s="64" t="n">
+      <c r="J30" s="66" t="n">
         <v>48.52</v>
       </c>
-      <c r="K30" s="76" t="n">
+      <c r="K30" s="78" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="45" t="n">
@@ -5343,21 +6331,21 @@
         <v>0.176</v>
       </c>
       <c r="O30" s="21" t="s">
-        <v>605</v>
+        <v>766</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>668</v>
+        <v>829</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>669</v>
+        <v>830</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>356</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>643</v>
+        <v>804</v>
       </c>
       <c r="E31" s="21" t="n">
         <v>181</v>
@@ -5375,10 +6363,10 @@
       <c r="I31" s="28" t="n">
         <v>3884721</v>
       </c>
-      <c r="J31" s="64" t="n">
+      <c r="J31" s="66" t="n">
         <v>54.76</v>
       </c>
-      <c r="K31" s="77" t="n">
+      <c r="K31" s="79" t="n">
         <v>0.186</v>
       </c>
       <c r="L31" s="45" t="n">
@@ -5391,21 +6379,21 @@
         <v>0.082</v>
       </c>
       <c r="O31" s="21" t="s">
-        <v>613</v>
+        <v>774</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>670</v>
+        <v>831</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>671</v>
+        <v>832</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>672</v>
+        <v>833</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>643</v>
+        <v>804</v>
       </c>
       <c r="E32" s="21" t="n">
         <v>69</v>
@@ -5423,10 +6411,10 @@
       <c r="I32" s="28" t="n">
         <v>1471112</v>
       </c>
-      <c r="J32" s="64" t="n">
+      <c r="J32" s="66" t="n">
         <v>49.67</v>
       </c>
-      <c r="K32" s="76" t="n">
+      <c r="K32" s="78" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="45" t="n">
@@ -5439,21 +6427,21 @@
         <v>0.103</v>
       </c>
       <c r="O32" s="20" t="s">
-        <v>616</v>
+        <v>777</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>673</v>
+        <v>834</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>674</v>
+        <v>835</v>
       </c>
       <c r="C33" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E33" s="21" t="n">
         <v>181</v>
@@ -5471,10 +6459,10 @@
       <c r="I33" s="28" t="n">
         <v>3774634</v>
       </c>
-      <c r="J33" s="64" t="n">
+      <c r="J33" s="66" t="n">
         <v>50.81</v>
       </c>
-      <c r="K33" s="77" t="n">
+      <c r="K33" s="79" t="n">
         <v>0.18</v>
       </c>
       <c r="L33" s="45" t="n">
@@ -5487,21 +6475,21 @@
         <v>0.023</v>
       </c>
       <c r="O33" s="21" t="s">
-        <v>605</v>
+        <v>766</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>675</v>
+        <v>836</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>676</v>
+        <v>837</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>608</v>
+        <v>769</v>
       </c>
       <c r="E34" s="21" t="n">
         <v>181</v>
@@ -5519,7 +6507,7 @@
       <c r="I34" s="28" t="n">
         <v>4263083</v>
       </c>
-      <c r="J34" s="64" t="n">
+      <c r="J34" s="66" t="n">
         <v>110.06</v>
       </c>
       <c r="K34" s="57" t="n">
@@ -5535,21 +6523,21 @@
         <v>0.559</v>
       </c>
       <c r="O34" s="21" t="s">
-        <v>661</v>
+        <v>822</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>677</v>
+        <v>838</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>678</v>
+        <v>839</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E35" s="21" t="n">
         <v>181</v>
@@ -5567,7 +6555,7 @@
       <c r="I35" s="28" t="n">
         <v>3471225</v>
       </c>
-      <c r="J35" s="64" t="n">
+      <c r="J35" s="66" t="n">
         <v>47.35</v>
       </c>
       <c r="K35" s="57" t="n">
@@ -5583,21 +6571,21 @@
         <v>0</v>
       </c>
       <c r="O35" s="21" t="s">
-        <v>613</v>
+        <v>774</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>679</v>
+        <v>840</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>680</v>
+        <v>841</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>622</v>
+        <v>783</v>
       </c>
       <c r="E36" s="21" t="n">
         <v>181</v>
@@ -5615,7 +6603,7 @@
       <c r="I36" s="28" t="n">
         <v>3512113</v>
       </c>
-      <c r="J36" s="64" t="n">
+      <c r="J36" s="66" t="n">
         <v>45.88</v>
       </c>
       <c r="K36" s="57" t="n">
@@ -5631,21 +6619,21 @@
         <v>0.115</v>
       </c>
       <c r="O36" s="21" t="s">
-        <v>619</v>
+        <v>780</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>681</v>
+        <v>842</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>682</v>
+        <v>843</v>
       </c>
       <c r="C37" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>643</v>
+        <v>804</v>
       </c>
       <c r="E37" s="21" t="n">
         <v>26</v>
@@ -5663,10 +6651,10 @@
       <c r="I37" s="28" t="n">
         <v>486162</v>
       </c>
-      <c r="J37" s="64" t="n">
+      <c r="J37" s="66" t="n">
         <v>33.35</v>
       </c>
-      <c r="K37" s="76" t="n">
+      <c r="K37" s="78" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="45" t="n">
@@ -5684,16 +6672,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
-        <v>683</v>
+        <v>844</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>684</v>
+        <v>845</v>
       </c>
       <c r="C38" s="21" t="s">
         <v>345</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E38" s="21" t="n">
         <v>181</v>
@@ -5711,10 +6699,10 @@
       <c r="I38" s="28" t="n">
         <v>3406904</v>
       </c>
-      <c r="J38" s="64" t="n">
+      <c r="J38" s="66" t="n">
         <v>43.04</v>
       </c>
-      <c r="K38" s="77" t="n">
+      <c r="K38" s="79" t="n">
         <v>0.083</v>
       </c>
       <c r="L38" s="45" t="n">
@@ -5727,21 +6715,21 @@
         <v>0.167</v>
       </c>
       <c r="O38" s="21" t="s">
-        <v>605</v>
+        <v>766</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="21" t="s">
-        <v>685</v>
+        <v>846</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>686</v>
+        <v>847</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>608</v>
+        <v>769</v>
       </c>
       <c r="E39" s="21" t="n">
         <v>181</v>
@@ -5759,7 +6747,7 @@
       <c r="I39" s="28" t="n">
         <v>3076219</v>
       </c>
-      <c r="J39" s="64" t="n">
+      <c r="J39" s="66" t="n">
         <v>69.64</v>
       </c>
       <c r="K39" s="57" t="n">
@@ -5775,21 +6763,21 @@
         <v>0.106</v>
       </c>
       <c r="O39" s="21" t="s">
-        <v>605</v>
+        <v>766</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="21" t="s">
-        <v>687</v>
+        <v>848</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>688</v>
+        <v>849</v>
       </c>
       <c r="C40" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E40" s="21" t="n">
         <v>181</v>
@@ -5807,7 +6795,7 @@
       <c r="I40" s="28" t="n">
         <v>3314721</v>
       </c>
-      <c r="J40" s="64" t="n">
+      <c r="J40" s="66" t="n">
         <v>69.44</v>
       </c>
       <c r="K40" s="45" t="n">
@@ -5823,21 +6811,21 @@
         <v>0.373</v>
       </c>
       <c r="O40" s="21" t="s">
-        <v>605</v>
+        <v>766</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="21" t="s">
-        <v>689</v>
+        <v>850</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>690</v>
+        <v>851</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E41" s="21" t="n">
         <v>181</v>
@@ -5855,7 +6843,7 @@
       <c r="I41" s="28" t="n">
         <v>2925368</v>
       </c>
-      <c r="J41" s="64" t="n">
+      <c r="J41" s="66" t="n">
         <v>45.21</v>
       </c>
       <c r="K41" s="57" t="n">
@@ -5871,21 +6859,21 @@
         <v>0</v>
       </c>
       <c r="O41" s="21" t="s">
-        <v>605</v>
+        <v>766</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="21" t="s">
-        <v>691</v>
+        <v>852</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>692</v>
+        <v>853</v>
       </c>
       <c r="C42" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>643</v>
+        <v>804</v>
       </c>
       <c r="E42" s="21" t="n">
         <v>68</v>
@@ -5903,10 +6891,10 @@
       <c r="I42" s="28" t="n">
         <v>1114635</v>
       </c>
-      <c r="J42" s="64" t="n">
+      <c r="J42" s="66" t="n">
         <v>45.6</v>
       </c>
-      <c r="K42" s="76" t="n">
+      <c r="K42" s="78" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="45" t="n">
@@ -5919,21 +6907,21 @@
         <v>0.056</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>616</v>
+        <v>777</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
-        <v>693</v>
+        <v>854</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>694</v>
+        <v>855</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>612</v>
+        <v>773</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>646</v>
+        <v>807</v>
       </c>
       <c r="E43" s="21" t="n">
         <v>181</v>
@@ -5951,10 +6939,10 @@
       <c r="I43" s="28" t="n">
         <v>2839338</v>
       </c>
-      <c r="J43" s="64" t="n">
+      <c r="J43" s="66" t="n">
         <v>50.86</v>
       </c>
-      <c r="K43" s="77" t="n">
+      <c r="K43" s="79" t="n">
         <v>0.082</v>
       </c>
       <c r="L43" s="45" t="n">
@@ -5967,21 +6955,21 @@
         <v>0.077</v>
       </c>
       <c r="O43" s="21" t="s">
-        <v>661</v>
+        <v>822</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
-        <v>695</v>
+        <v>856</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>696</v>
+        <v>857</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>697</v>
+        <v>858</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E44" s="21" t="n">
         <v>181</v>
@@ -5999,10 +6987,10 @@
       <c r="I44" s="28" t="n">
         <v>2759664</v>
       </c>
-      <c r="J44" s="64" t="n">
+      <c r="J44" s="66" t="n">
         <v>56.84</v>
       </c>
-      <c r="K44" s="77" t="n">
+      <c r="K44" s="79" t="n">
         <v>0.327</v>
       </c>
       <c r="L44" s="45" t="n">
@@ -6015,21 +7003,21 @@
         <v>0.066</v>
       </c>
       <c r="O44" s="20" t="s">
-        <v>616</v>
+        <v>777</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="21" t="s">
-        <v>698</v>
+        <v>859</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>699</v>
+        <v>860</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>700</v>
+        <v>861</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>643</v>
+        <v>804</v>
       </c>
       <c r="E45" s="21" t="n">
         <v>181</v>
@@ -6047,7 +7035,7 @@
       <c r="I45" s="28" t="n">
         <v>2940822</v>
       </c>
-      <c r="J45" s="64" t="n">
+      <c r="J45" s="66" t="n">
         <v>74.93</v>
       </c>
       <c r="K45" s="45" t="n">
@@ -6063,21 +7051,21 @@
         <v>0.392</v>
       </c>
       <c r="O45" s="20" t="s">
-        <v>616</v>
+        <v>777</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="21" t="s">
-        <v>701</v>
+        <v>862</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>702</v>
+        <v>863</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E46" s="21" t="n">
         <v>181</v>
@@ -6095,7 +7083,7 @@
       <c r="I46" s="28" t="n">
         <v>2694118</v>
       </c>
-      <c r="J46" s="64" t="n">
+      <c r="J46" s="66" t="n">
         <v>53.94</v>
       </c>
       <c r="K46" s="57" t="n">
@@ -6111,21 +7099,21 @@
         <v>0.236</v>
       </c>
       <c r="O46" s="21" t="s">
-        <v>613</v>
+        <v>774</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="21" t="s">
-        <v>703</v>
+        <v>864</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>704</v>
+        <v>865</v>
       </c>
       <c r="C47" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>705</v>
+        <v>866</v>
       </c>
       <c r="E47" s="21" t="n">
         <v>181</v>
@@ -6143,7 +7131,7 @@
       <c r="I47" s="28" t="n">
         <v>2650896</v>
       </c>
-      <c r="J47" s="64" t="n">
+      <c r="J47" s="66" t="n">
         <v>48.6</v>
       </c>
       <c r="K47" s="45" t="n">
@@ -6159,21 +7147,21 @@
         <v>0.184</v>
       </c>
       <c r="O47" s="21" t="s">
-        <v>661</v>
+        <v>822</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="21" t="s">
-        <v>706</v>
+        <v>867</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>707</v>
+        <v>868</v>
       </c>
       <c r="C48" s="21" t="s">
         <v>356</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>643</v>
+        <v>804</v>
       </c>
       <c r="E48" s="21" t="n">
         <v>181</v>
@@ -6191,10 +7179,10 @@
       <c r="I48" s="28" t="n">
         <v>2153145</v>
       </c>
-      <c r="J48" s="64" t="n">
+      <c r="J48" s="66" t="n">
         <v>57.15</v>
       </c>
-      <c r="K48" s="77" t="n">
+      <c r="K48" s="79" t="n">
         <v>0.064</v>
       </c>
       <c r="L48" s="45" t="n">
@@ -6207,21 +7195,21 @@
         <v>0</v>
       </c>
       <c r="O48" s="21" t="s">
-        <v>605</v>
+        <v>766</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="21" t="s">
-        <v>708</v>
+        <v>869</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>709</v>
+        <v>870</v>
       </c>
       <c r="C49" s="21" t="s">
         <v>356</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>646</v>
+        <v>807</v>
       </c>
       <c r="E49" s="21" t="n">
         <v>181</v>
@@ -6239,10 +7227,10 @@
       <c r="I49" s="28" t="n">
         <v>2133587</v>
       </c>
-      <c r="J49" s="64" t="n">
+      <c r="J49" s="66" t="n">
         <v>62.82</v>
       </c>
-      <c r="K49" s="77" t="n">
+      <c r="K49" s="79" t="n">
         <v>0.256</v>
       </c>
       <c r="L49" s="45" t="n">
@@ -6255,21 +7243,21 @@
         <v>0.201</v>
       </c>
       <c r="O49" s="21" t="s">
-        <v>605</v>
+        <v>766</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="21" t="s">
-        <v>710</v>
+        <v>871</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>711</v>
+        <v>872</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E50" s="21" t="n">
         <v>181</v>
@@ -6287,7 +7275,7 @@
       <c r="I50" s="28" t="n">
         <v>1912969</v>
       </c>
-      <c r="J50" s="64" t="n">
+      <c r="J50" s="66" t="n">
         <v>52.46</v>
       </c>
       <c r="K50" s="57" t="n">
@@ -6303,21 +7291,21 @@
         <v>0</v>
       </c>
       <c r="O50" s="21" t="s">
-        <v>613</v>
+        <v>774</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="21" t="s">
-        <v>712</v>
+        <v>873</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>713</v>
+        <v>874</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E51" s="21" t="n">
         <v>56</v>
@@ -6335,10 +7323,10 @@
       <c r="I51" s="28" t="n">
         <v>568922</v>
       </c>
-      <c r="J51" s="64" t="n">
+      <c r="J51" s="66" t="n">
         <v>50.9</v>
       </c>
-      <c r="K51" s="76" t="n">
+      <c r="K51" s="78" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="45" t="n">
@@ -6356,16 +7344,16 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="21" t="s">
-        <v>714</v>
+        <v>875</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>715</v>
+        <v>876</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>612</v>
+        <v>773</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>646</v>
+        <v>807</v>
       </c>
       <c r="E52" s="21" t="n">
         <v>181</v>
@@ -6383,10 +7371,10 @@
       <c r="I52" s="28" t="n">
         <v>1672588</v>
       </c>
-      <c r="J52" s="64" t="n">
+      <c r="J52" s="66" t="n">
         <v>45.95</v>
       </c>
-      <c r="K52" s="77" t="n">
+      <c r="K52" s="79" t="n">
         <v>0.137</v>
       </c>
       <c r="L52" s="45" t="n">
@@ -6399,21 +7387,21 @@
         <v>0.017</v>
       </c>
       <c r="O52" s="21" t="s">
-        <v>619</v>
+        <v>780</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="21" t="s">
-        <v>716</v>
+        <v>877</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>717</v>
+        <v>878</v>
       </c>
       <c r="C53" s="21" t="s">
         <v>345</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E53" s="21" t="n">
         <v>181</v>
@@ -6431,7 +7419,7 @@
       <c r="I53" s="28" t="n">
         <v>1601535</v>
       </c>
-      <c r="J53" s="64" t="n">
+      <c r="J53" s="66" t="n">
         <v>55.38</v>
       </c>
       <c r="K53" s="45" t="n">
@@ -6447,21 +7435,21 @@
         <v>0.292</v>
       </c>
       <c r="O53" s="21" t="s">
-        <v>619</v>
+        <v>780</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="21" t="s">
-        <v>718</v>
+        <v>879</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>719</v>
+        <v>880</v>
       </c>
       <c r="C54" s="21" t="s">
         <v>347</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>643</v>
+        <v>804</v>
       </c>
       <c r="E54" s="21" t="n">
         <v>181</v>
@@ -6479,7 +7467,7 @@
       <c r="I54" s="28" t="n">
         <v>1431054</v>
       </c>
-      <c r="J54" s="64" t="n">
+      <c r="J54" s="66" t="n">
         <v>53.68</v>
       </c>
       <c r="K54" s="45" t="n">
@@ -6495,21 +7483,21 @@
         <v>0.077</v>
       </c>
       <c r="O54" s="21" t="s">
-        <v>605</v>
+        <v>766</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="21" t="s">
-        <v>720</v>
+        <v>881</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>721</v>
+        <v>882</v>
       </c>
       <c r="C55" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>646</v>
+        <v>807</v>
       </c>
       <c r="E55" s="21" t="n">
         <v>181</v>
@@ -6527,10 +7515,10 @@
       <c r="I55" s="28" t="n">
         <v>1262094</v>
       </c>
-      <c r="J55" s="64" t="n">
+      <c r="J55" s="66" t="n">
         <v>53.3</v>
       </c>
-      <c r="K55" s="77" t="n">
+      <c r="K55" s="79" t="n">
         <v>0.188</v>
       </c>
       <c r="L55" s="45" t="n">
@@ -6543,21 +7531,21 @@
         <v>0.18</v>
       </c>
       <c r="O55" s="20" t="s">
-        <v>616</v>
+        <v>777</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="21" t="s">
-        <v>722</v>
+        <v>883</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>723</v>
+        <v>884</v>
       </c>
       <c r="C56" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>604</v>
+        <v>765</v>
       </c>
       <c r="E56" s="21" t="n">
         <v>181</v>
@@ -6575,10 +7563,10 @@
       <c r="I56" s="28" t="n">
         <v>1204453</v>
       </c>
-      <c r="J56" s="64" t="n">
+      <c r="J56" s="66" t="n">
         <v>34.88</v>
       </c>
-      <c r="K56" s="77" t="n">
+      <c r="K56" s="79" t="n">
         <v>0.06</v>
       </c>
       <c r="L56" s="45" t="n">
@@ -6591,12 +7579,12 @@
         <v>0.194</v>
       </c>
       <c r="O56" s="21" t="s">
-        <v>619</v>
+        <v>780</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="21" t="s">
-        <v>724</v>
+        <v>885</v>
       </c>
       <c r="B57" s="16" t="s">
         <v>339</v>
@@ -6605,7 +7593,7 @@
         <v>340</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>643</v>
+        <v>804</v>
       </c>
       <c r="E57" s="21" t="n">
         <v>39</v>
@@ -6623,10 +7611,10 @@
       <c r="I57" s="28" t="n">
         <v>206212</v>
       </c>
-      <c r="J57" s="64" t="n">
+      <c r="J57" s="66" t="n">
         <v>57.08</v>
       </c>
-      <c r="K57" s="76" t="n">
+      <c r="K57" s="78" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="45" t="n">
@@ -6639,21 +7627,21 @@
         <v>0.249</v>
       </c>
       <c r="O57" s="20" t="s">
-        <v>616</v>
+        <v>777</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="21" t="s">
-        <v>725</v>
+        <v>886</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>726</v>
+        <v>887</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>727</v>
+        <v>888</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>643</v>
+        <v>804</v>
       </c>
       <c r="E58" s="21" t="n">
         <v>6</v>
@@ -6671,10 +7659,10 @@
       <c r="I58" s="28" t="n">
         <v>21693</v>
       </c>
-      <c r="J58" s="64" t="n">
+      <c r="J58" s="66" t="n">
         <v>49.96</v>
       </c>
-      <c r="K58" s="76" t="n">
+      <c r="K58" s="78" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="45" t="n">
@@ -6687,51 +7675,51 @@
         <v>0.167</v>
       </c>
       <c r="O58" s="20" t="s">
-        <v>616</v>
+        <v>777</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="78" t="s">
-        <v>728</v>
+      <c r="A59" s="80" t="s">
+        <v>889</v>
       </c>
       <c r="B59" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="F59" s="79" t="n">
+      <c r="F59" s="81" t="n">
         <f aca="false">SUM(F4:F58)</f>
         <v>502415662</v>
       </c>
-      <c r="G59" s="79" t="n">
+      <c r="G59" s="81" t="n">
         <f aca="false">SUM(G4:G58)</f>
         <v>1271395370.83428</v>
       </c>
-      <c r="H59" s="79" t="n">
+      <c r="H59" s="81" t="n">
         <f aca="false">SUM(H4:H58)</f>
         <v>8824895</v>
       </c>
-      <c r="I59" s="79" t="n">
+      <c r="I59" s="81" t="n">
         <f aca="false">SUM(I4:I58)</f>
         <v>219475297</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="80" t="s">
-        <v>729</v>
-      </c>
-      <c r="B61" s="80"/>
-      <c r="C61" s="80"/>
-      <c r="D61" s="80"/>
-      <c r="E61" s="80"/>
-      <c r="F61" s="80"/>
-      <c r="G61" s="80"/>
-      <c r="H61" s="80"/>
-      <c r="I61" s="80"/>
-      <c r="J61" s="80"/>
-      <c r="K61" s="80"/>
-      <c r="L61" s="80"/>
-      <c r="M61" s="80"/>
-      <c r="N61" s="80"/>
-      <c r="O61" s="80"/>
+      <c r="A61" s="82" t="s">
+        <v>890</v>
+      </c>
+      <c r="B61" s="82"/>
+      <c r="C61" s="82"/>
+      <c r="D61" s="82"/>
+      <c r="E61" s="82"/>
+      <c r="F61" s="82"/>
+      <c r="G61" s="82"/>
+      <c r="H61" s="82"/>
+      <c r="I61" s="82"/>
+      <c r="J61" s="82"/>
+      <c r="K61" s="82"/>
+      <c r="L61" s="82"/>
+      <c r="M61" s="82"/>
+      <c r="N61" s="82"/>
+      <c r="O61" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -10158,6 +11146,1100 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:L36"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="36"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="52" t="s">
+        <v>505</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>506</v>
+      </c>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>509</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>511</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>512</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>514</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>515</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>516</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="61" t="s">
+        <v>518</v>
+      </c>
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="61"/>
+    </row>
+    <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>519</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>522</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>523</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>524</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>71</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>526</v>
+      </c>
+      <c r="K6" s="21" t="n">
+        <f aca="false">IF(I6="","",71-I6)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>528</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>522</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>523</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>524</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>71</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>529</v>
+      </c>
+      <c r="K7" s="21" t="n">
+        <f aca="false">IF(I7="","",71-I7)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>531</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>523</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>533</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>71</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>534</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <f aca="false">IF(I8="","",71-I8)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="61" t="s">
+        <v>536</v>
+      </c>
+      <c r="B9" s="61"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="61"/>
+      <c r="L9" s="61"/>
+    </row>
+    <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>537</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>538</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>540</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>541</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>543</v>
+      </c>
+      <c r="I10" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <f aca="false">IF(I10="","",71-I10)</f>
+        <v>71</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>547</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>548</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>541</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>549</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>36</v>
+      </c>
+      <c r="J11" s="21" t="s">
+        <v>551</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <f aca="false">IF(I11="","",71-I11)</f>
+        <v>35</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>553</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>554</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>555</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>556</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>541</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>549</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" s="21" t="s">
+        <v>557</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <f aca="false">IF(I12="","",71-I12)</f>
+        <v>62</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="61" t="s">
+        <v>559</v>
+      </c>
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="61"/>
+      <c r="L13" s="61"/>
+    </row>
+    <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>561</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>562</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>563</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>564</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>35</v>
+      </c>
+      <c r="J14" s="21" t="s">
+        <v>565</v>
+      </c>
+      <c r="K14" s="21" t="n">
+        <f aca="false">IF(I14="","",71-I14)</f>
+        <v>36</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>567</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>548</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>523</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>568</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="I15" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="21" t="s">
+        <v>570</v>
+      </c>
+      <c r="K15" s="21" t="n">
+        <f aca="false">IF(I15="","",71-I15)</f>
+        <v>71</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="61" t="s">
+        <v>572</v>
+      </c>
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
+      <c r="K16" s="61"/>
+      <c r="L16" s="61"/>
+    </row>
+    <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>523</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>576</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="J17" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="K17" s="21" t="n">
+        <f aca="false">IF(I17="","",71-I17)</f>
+        <v>46</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>579</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>580</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>581</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>582</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>541</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>583</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>584</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="J18" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="K18" s="21" t="n">
+        <f aca="false">IF(I18="","",71-I18)</f>
+        <v>50</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>587</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>588</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>589</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>590</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>523</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>591</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>592</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="J19" s="21" t="s">
+        <v>593</v>
+      </c>
+      <c r="K19" s="21" t="n">
+        <f aca="false">IF(I19="","",71-I19)</f>
+        <v>43</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>595</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>588</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>596</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>597</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>523</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>549</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="J20" s="21" t="s">
+        <v>598</v>
+      </c>
+      <c r="K20" s="21" t="n">
+        <f aca="false">IF(I20="","",71-I20)</f>
+        <v>61</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>602</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>523</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>603</v>
+      </c>
+      <c r="I21" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="K21" s="21" t="n">
+        <f aca="false">IF(I21="","",71-I21)</f>
+        <v>71</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="61" t="s">
+        <v>605</v>
+      </c>
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="61"/>
+    </row>
+    <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>606</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>607</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>608</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>556</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>609</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>610</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>611</v>
+      </c>
+      <c r="I23" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" s="21" t="s">
+        <v>612</v>
+      </c>
+      <c r="K23" s="21" t="n">
+        <f aca="false">IF(I23="","",71-I23)</f>
+        <v>66</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>614</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>607</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>615</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>616</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>609</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>617</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="21" t="s">
+        <v>618</v>
+      </c>
+      <c r="K24" s="21" t="n">
+        <f aca="false">IF(I24="","",71-I24)</f>
+        <v>70</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>620</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>580</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>621</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>523</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>622</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>623</v>
+      </c>
+      <c r="I25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="K25" s="21" t="n">
+        <f aca="false">IF(I25="","",71-I25)</f>
+        <v>71</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>625</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>626</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>627</v>
+      </c>
+      <c r="F26" s="23" t="s">
+        <v>523</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>628</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>629</v>
+      </c>
+      <c r="I26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="21" t="s">
+        <v>630</v>
+      </c>
+      <c r="K26" s="21" t="n">
+        <f aca="false">IF(I26="","",71-I26)</f>
+        <v>71</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>632</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>633</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>634</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>635</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>636</v>
+      </c>
+      <c r="I27" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="21" t="s">
+        <v>637</v>
+      </c>
+      <c r="K27" s="62" t="s">
+        <v>638</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="61" t="s">
+        <v>640</v>
+      </c>
+      <c r="B28" s="61"/>
+      <c r="C28" s="61"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="61"/>
+      <c r="F28" s="61"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="61"/>
+      <c r="L28" s="61"/>
+    </row>
+    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>641</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>608</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>642</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>643</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>644</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>645</v>
+      </c>
+      <c r="I29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="21" t="s">
+        <v>646</v>
+      </c>
+      <c r="K29" s="62" t="s">
+        <v>638</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>648</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>608</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>649</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>643</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>650</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>651</v>
+      </c>
+      <c r="I30" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="21" t="s">
+        <v>652</v>
+      </c>
+      <c r="K30" s="62" t="s">
+        <v>638</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="54" t="s">
+        <v>654</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>655</v>
+      </c>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="53"/>
+    </row>
+    <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="52" t="s">
+        <v>656</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>657</v>
+      </c>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="53"/>
+    </row>
+    <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="52" t="s">
+        <v>658</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>659</v>
+      </c>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="53"/>
+    </row>
+    <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="54" t="s">
+        <v>660</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>661</v>
+      </c>
+      <c r="D35" s="53"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="53"/>
+    </row>
+    <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="52" t="s">
+        <v>662</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>663</v>
+      </c>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="53"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="C3:L3"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="A16:L16"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C34:L34"/>
+    <mergeCell ref="C35:L35"/>
+    <mergeCell ref="C36:L36"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:O18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -10179,7 +12261,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>503</v>
+        <v>664</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10198,7 +12280,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>504</v>
+        <v>665</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10229,86 +12311,86 @@
         <v>52</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>505</v>
+        <v>666</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>506</v>
+        <v>667</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>507</v>
+        <v>668</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>508</v>
+        <v>669</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>55</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>509</v>
+        <v>670</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>510</v>
+        <v>671</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>56</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>511</v>
+        <v>672</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>512</v>
+        <v>673</v>
       </c>
       <c r="O3" s="15" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="61" t="s">
-        <v>513</v>
-      </c>
-      <c r="B4" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="C4" s="61" t="s">
+      <c r="A4" s="63" t="s">
+        <v>674</v>
+      </c>
+      <c r="B4" s="64" t="s">
+        <v>675</v>
+      </c>
+      <c r="C4" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="62" t="s">
-        <v>515</v>
-      </c>
-      <c r="E4" s="61" t="n">
+      <c r="D4" s="64" t="s">
+        <v>676</v>
+      </c>
+      <c r="E4" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="61" t="s">
-        <v>516</v>
-      </c>
-      <c r="G4" s="62" t="s">
-        <v>517</v>
-      </c>
-      <c r="H4" s="61" t="n">
+      <c r="F4" s="63" t="s">
+        <v>677</v>
+      </c>
+      <c r="G4" s="64" t="s">
+        <v>678</v>
+      </c>
+      <c r="H4" s="63" t="n">
         <v>20</v>
       </c>
-      <c r="I4" s="61" t="n">
+      <c r="I4" s="63" t="n">
         <f aca="false">IF(H4="","",H4-E4)</f>
         <v>14</v>
       </c>
-      <c r="J4" s="63" t="n">
+      <c r="J4" s="65" t="n">
         <f aca="false">IFERROR(IF(H4="","",(H4-E4)/E4),"")</f>
         <v>2.33333333333333</v>
       </c>
-      <c r="K4" s="62" t="s">
-        <v>518</v>
-      </c>
-      <c r="L4" s="61" t="s">
+      <c r="K4" s="64" t="s">
+        <v>679</v>
+      </c>
+      <c r="L4" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="M4" s="62" t="s">
-        <v>519</v>
-      </c>
-      <c r="N4" s="62" t="s">
-        <v>520</v>
-      </c>
-      <c r="O4" s="61" t="s">
-        <v>521</v>
+      <c r="M4" s="64" t="s">
+        <v>680</v>
+      </c>
+      <c r="N4" s="64" t="s">
+        <v>681</v>
+      </c>
+      <c r="O4" s="63" t="s">
+        <v>682</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10324,17 +12406,17 @@
       <c r="D5" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="64" t="n">
+      <c r="E5" s="66" t="n">
         <v>1271</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>522</v>
+        <v>683</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>523</v>
-      </c>
-      <c r="H5" s="65"/>
-      <c r="I5" s="64" t="str">
+        <v>684</v>
+      </c>
+      <c r="H5" s="67"/>
+      <c r="I5" s="66" t="str">
         <f aca="false">IF(H5="","",H5-E5)</f>
         <v/>
       </c>
@@ -10342,15 +12424,15 @@
         <f aca="false">IFERROR(IF(H5="","",(H5-E5)/E5),"")</f>
         <v/>
       </c>
-      <c r="K5" s="66"/>
+      <c r="K5" s="68"/>
       <c r="L5" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="M5" s="66"/>
+      <c r="M5" s="68"/>
       <c r="N5" s="16" t="s">
-        <v>524</v>
-      </c>
-      <c r="O5" s="67"/>
+        <v>685</v>
+      </c>
+      <c r="O5" s="69"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="n">
@@ -10365,17 +12447,17 @@
       <c r="D6" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="64" t="n">
+      <c r="E6" s="66" t="n">
         <v>25</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>525</v>
+        <v>686</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>526</v>
-      </c>
-      <c r="H6" s="65"/>
-      <c r="I6" s="64" t="str">
+        <v>687</v>
+      </c>
+      <c r="H6" s="67"/>
+      <c r="I6" s="66" t="str">
         <f aca="false">IF(H6="","",H6-E6)</f>
         <v/>
       </c>
@@ -10383,15 +12465,15 @@
         <f aca="false">IFERROR(IF(H6="","",(H6-E6)/E6),"")</f>
         <v/>
       </c>
-      <c r="K6" s="66"/>
+      <c r="K6" s="68"/>
       <c r="L6" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="M6" s="66"/>
+      <c r="M6" s="68"/>
       <c r="N6" s="16" t="s">
-        <v>527</v>
-      </c>
-      <c r="O6" s="67"/>
+        <v>688</v>
+      </c>
+      <c r="O6" s="69"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="n">
@@ -10406,17 +12488,17 @@
       <c r="D7" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="64" t="n">
+      <c r="E7" s="66" t="n">
         <v>39</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>528</v>
+        <v>689</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>517</v>
-      </c>
-      <c r="H7" s="65"/>
-      <c r="I7" s="64" t="str">
+        <v>678</v>
+      </c>
+      <c r="H7" s="67"/>
+      <c r="I7" s="66" t="str">
         <f aca="false">IF(H7="","",H7-E7)</f>
         <v/>
       </c>
@@ -10424,15 +12506,15 @@
         <f aca="false">IFERROR(IF(H7="","",(H7-E7)/E7),"")</f>
         <v/>
       </c>
-      <c r="K7" s="66"/>
+      <c r="K7" s="68"/>
       <c r="L7" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="M7" s="66"/>
+      <c r="M7" s="68"/>
       <c r="N7" s="16" t="s">
-        <v>529</v>
-      </c>
-      <c r="O7" s="67"/>
+        <v>690</v>
+      </c>
+      <c r="O7" s="69"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="n">
@@ -10447,17 +12529,17 @@
       <c r="D8" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="64" t="n">
+      <c r="E8" s="66" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>530</v>
+        <v>691</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>531</v>
-      </c>
-      <c r="H8" s="65"/>
-      <c r="I8" s="64" t="str">
+        <v>692</v>
+      </c>
+      <c r="H8" s="67"/>
+      <c r="I8" s="66" t="str">
         <f aca="false">IF(H8="","",H8-E8)</f>
         <v/>
       </c>
@@ -10465,40 +12547,40 @@
         <f aca="false">IFERROR(IF(H8="","",(H8-E8)/E8),"")</f>
         <v/>
       </c>
-      <c r="K8" s="66"/>
+      <c r="K8" s="68"/>
       <c r="L8" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="M8" s="66"/>
+      <c r="M8" s="68"/>
       <c r="N8" s="16" t="s">
-        <v>532</v>
-      </c>
-      <c r="O8" s="67"/>
+        <v>693</v>
+      </c>
+      <c r="O8" s="69"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>533</v>
+        <v>694</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>50</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>534</v>
-      </c>
-      <c r="E9" s="64" t="n">
+        <v>695</v>
+      </c>
+      <c r="E9" s="66" t="n">
         <v>0.28</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>535</v>
+        <v>696</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>536</v>
-      </c>
-      <c r="H9" s="65"/>
-      <c r="I9" s="64" t="str">
+        <v>697</v>
+      </c>
+      <c r="H9" s="67"/>
+      <c r="I9" s="66" t="str">
         <f aca="false">IF(H9="","",H9-E9)</f>
         <v/>
       </c>
@@ -10506,22 +12588,22 @@
         <f aca="false">IFERROR(IF(H9="","",(H9-E9)/E9),"")</f>
         <v/>
       </c>
-      <c r="K9" s="66"/>
+      <c r="K9" s="68"/>
       <c r="L9" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="M9" s="66"/>
+      <c r="M9" s="68"/>
       <c r="N9" s="16" t="s">
-        <v>537</v>
-      </c>
-      <c r="O9" s="67"/>
+        <v>698</v>
+      </c>
+      <c r="O9" s="69"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>538</v>
+        <v>699</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>50</v>
@@ -10529,17 +12611,17 @@
       <c r="D10" s="16" t="s">
         <v>288</v>
       </c>
-      <c r="E10" s="64" t="n">
+      <c r="E10" s="66" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>539</v>
+        <v>700</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>540</v>
-      </c>
-      <c r="H10" s="65"/>
-      <c r="I10" s="64" t="str">
+        <v>701</v>
+      </c>
+      <c r="H10" s="67"/>
+      <c r="I10" s="66" t="str">
         <f aca="false">IF(H10="","",H10-E10)</f>
         <v/>
       </c>
@@ -10547,15 +12629,15 @@
         <f aca="false">IFERROR(IF(H10="","",(H10-E10)/E10),"")</f>
         <v/>
       </c>
-      <c r="K10" s="66"/>
+      <c r="K10" s="68"/>
       <c r="L10" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="M10" s="66"/>
+      <c r="M10" s="68"/>
       <c r="N10" s="16" t="s">
-        <v>541</v>
-      </c>
-      <c r="O10" s="67"/>
+        <v>702</v>
+      </c>
+      <c r="O10" s="69"/>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="n">
@@ -10568,19 +12650,19 @@
         <v>92</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>542</v>
-      </c>
-      <c r="E11" s="64" t="n">
+        <v>703</v>
+      </c>
+      <c r="E11" s="66" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>543</v>
+        <v>704</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>544</v>
-      </c>
-      <c r="H11" s="65"/>
-      <c r="I11" s="64" t="str">
+        <v>705</v>
+      </c>
+      <c r="H11" s="67"/>
+      <c r="I11" s="66" t="str">
         <f aca="false">IF(H11="","",H11-E11)</f>
         <v/>
       </c>
@@ -10588,15 +12670,15 @@
         <f aca="false">IFERROR(IF(H11="","",(H11-E11)/E11),"")</f>
         <v/>
       </c>
-      <c r="K11" s="66"/>
+      <c r="K11" s="68"/>
       <c r="L11" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="M11" s="66"/>
+      <c r="M11" s="68"/>
       <c r="N11" s="16" t="s">
-        <v>545</v>
-      </c>
-      <c r="O11" s="67"/>
+        <v>706</v>
+      </c>
+      <c r="O11" s="69"/>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="n">
@@ -10611,17 +12693,17 @@
       <c r="D12" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="64" t="n">
+      <c r="E12" s="66" t="n">
         <v>31</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>546</v>
+        <v>707</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>547</v>
-      </c>
-      <c r="H12" s="65"/>
-      <c r="I12" s="64" t="str">
+        <v>708</v>
+      </c>
+      <c r="H12" s="67"/>
+      <c r="I12" s="66" t="str">
         <f aca="false">IF(H12="","",H12-E12)</f>
         <v/>
       </c>
@@ -10629,15 +12711,15 @@
         <f aca="false">IFERROR(IF(H12="","",(H12-E12)/E12),"")</f>
         <v/>
       </c>
-      <c r="K12" s="66"/>
+      <c r="K12" s="68"/>
       <c r="L12" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="M12" s="66"/>
+      <c r="M12" s="68"/>
       <c r="N12" s="16" t="s">
-        <v>548</v>
-      </c>
-      <c r="O12" s="67"/>
+        <v>709</v>
+      </c>
+      <c r="O12" s="69"/>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="n">
@@ -10652,17 +12734,17 @@
       <c r="D13" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="E13" s="64" t="n">
+      <c r="E13" s="66" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>549</v>
+        <v>710</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>550</v>
-      </c>
-      <c r="H13" s="65"/>
-      <c r="I13" s="64" t="str">
+        <v>711</v>
+      </c>
+      <c r="H13" s="67"/>
+      <c r="I13" s="66" t="str">
         <f aca="false">IF(H13="","",H13-E13)</f>
         <v/>
       </c>
@@ -10670,15 +12752,15 @@
         <f aca="false">IFERROR(IF(H13="","",(H13-E13)/E13),"")</f>
         <v/>
       </c>
-      <c r="K13" s="66"/>
+      <c r="K13" s="68"/>
       <c r="L13" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="M13" s="66"/>
+      <c r="M13" s="68"/>
       <c r="N13" s="16" t="s">
-        <v>551</v>
-      </c>
-      <c r="O13" s="67"/>
+        <v>712</v>
+      </c>
+      <c r="O13" s="69"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="n">
@@ -10693,17 +12775,17 @@
       <c r="D14" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="E14" s="64" t="n">
+      <c r="E14" s="66" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>552</v>
+        <v>713</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>553</v>
-      </c>
-      <c r="H14" s="65"/>
-      <c r="I14" s="64" t="str">
+        <v>714</v>
+      </c>
+      <c r="H14" s="67"/>
+      <c r="I14" s="66" t="str">
         <f aca="false">IF(H14="","",H14-E14)</f>
         <v/>
       </c>
@@ -10711,15 +12793,15 @@
         <f aca="false">IFERROR(IF(H14="","",(H14-E14)/E14),"")</f>
         <v/>
       </c>
-      <c r="K14" s="66"/>
+      <c r="K14" s="68"/>
       <c r="L14" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="M14" s="66"/>
+      <c r="M14" s="68"/>
       <c r="N14" s="16" t="s">
-        <v>554</v>
-      </c>
-      <c r="O14" s="67"/>
+        <v>715</v>
+      </c>
+      <c r="O14" s="69"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="n">
@@ -10732,19 +12814,19 @@
         <v>49</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>515</v>
-      </c>
-      <c r="E15" s="64" t="n">
+        <v>676</v>
+      </c>
+      <c r="E15" s="66" t="n">
         <v>6</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>543</v>
+        <v>704</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>555</v>
-      </c>
-      <c r="H15" s="65"/>
-      <c r="I15" s="64" t="str">
+        <v>716</v>
+      </c>
+      <c r="H15" s="67"/>
+      <c r="I15" s="66" t="str">
         <f aca="false">IF(H15="","",H15-E15)</f>
         <v/>
       </c>
@@ -10752,15 +12834,15 @@
         <f aca="false">IFERROR(IF(H15="","",(H15-E15)/E15),"")</f>
         <v/>
       </c>
-      <c r="K15" s="66"/>
+      <c r="K15" s="68"/>
       <c r="L15" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="M15" s="66"/>
+      <c r="M15" s="68"/>
       <c r="N15" s="16" t="s">
-        <v>556</v>
-      </c>
-      <c r="O15" s="67"/>
+        <v>717</v>
+      </c>
+      <c r="O15" s="69"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="n">
@@ -10773,19 +12855,19 @@
         <v>49</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>557</v>
-      </c>
-      <c r="E16" s="64" t="n">
+        <v>718</v>
+      </c>
+      <c r="E16" s="66" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>558</v>
+        <v>719</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>559</v>
-      </c>
-      <c r="H16" s="65"/>
-      <c r="I16" s="64" t="str">
+        <v>720</v>
+      </c>
+      <c r="H16" s="67"/>
+      <c r="I16" s="66" t="str">
         <f aca="false">IF(H16="","",H16-E16)</f>
         <v/>
       </c>
@@ -10793,31 +12875,31 @@
         <f aca="false">IFERROR(IF(H16="","",(H16-E16)/E16),"")</f>
         <v/>
       </c>
-      <c r="K16" s="66"/>
+      <c r="K16" s="68"/>
       <c r="L16" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="M16" s="66"/>
+      <c r="M16" s="68"/>
       <c r="N16" s="16" t="s">
-        <v>560</v>
-      </c>
-      <c r="O16" s="67"/>
+        <v>721</v>
+      </c>
+      <c r="O16" s="69"/>
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="C18" s="68" t="s">
-        <v>562</v>
-      </c>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="68"/>
-      <c r="H18" s="68"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="68"/>
-      <c r="K18" s="68"/>
+        <v>722</v>
+      </c>
+      <c r="C18" s="70" t="s">
+        <v>723</v>
+      </c>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -10833,473 +12915,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>512</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>505</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>564</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>565</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>566</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>567</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>508</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>568</v>
-      </c>
-      <c r="K3" s="15" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="70" t="s">
-        <v>524</v>
-      </c>
-      <c r="D4" s="71" t="n">
-        <f aca="false">'الخطة التنفيذية'!E5</f>
-        <v>1271</v>
-      </c>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="71" t="str">
-        <f aca="false">IF('الخطة التنفيذية'!H5="","",'الخطة التنفيذية'!H5)</f>
-        <v/>
-      </c>
-      <c r="J4" s="21" t="str">
-        <f aca="false">IF(H4="","",IF(H4=I4,"مطابق","مختلف"))</f>
-        <v/>
-      </c>
-      <c r="K4" s="45" t="str">
-        <f aca="false">IFERROR(IF(H4="","",(H4-D4)/D4),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="69" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="70" t="s">
-        <v>527</v>
-      </c>
-      <c r="D5" s="71" t="n">
-        <f aca="false">'الخطة التنفيذية'!E6</f>
-        <v>25</v>
-      </c>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="71" t="str">
-        <f aca="false">IF('الخطة التنفيذية'!H6="","",'الخطة التنفيذية'!H6)</f>
-        <v/>
-      </c>
-      <c r="J5" s="21" t="str">
-        <f aca="false">IF(H5="","",IF(H5=I5,"مطابق","مختلف"))</f>
-        <v/>
-      </c>
-      <c r="K5" s="45" t="str">
-        <f aca="false">IFERROR(IF(H5="","",(H5-D5)/D5),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="69" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="70" t="s">
-        <v>529</v>
-      </c>
-      <c r="D6" s="71" t="n">
-        <f aca="false">'الخطة التنفيذية'!E7</f>
-        <v>39</v>
-      </c>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="71" t="str">
-        <f aca="false">IF('الخطة التنفيذية'!H7="","",'الخطة التنفيذية'!H7)</f>
-        <v/>
-      </c>
-      <c r="J6" s="21" t="str">
-        <f aca="false">IF(H6="","",IF(H6=I6,"مطابق","مختلف"))</f>
-        <v/>
-      </c>
-      <c r="K6" s="45" t="str">
-        <f aca="false">IFERROR(IF(H6="","",(H6-D6)/D6),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="70" t="s">
-        <v>532</v>
-      </c>
-      <c r="D7" s="71" t="n">
-        <f aca="false">'الخطة التنفيذية'!E8</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="65"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="71" t="str">
-        <f aca="false">IF('الخطة التنفيذية'!H8="","",'الخطة التنفيذية'!H8)</f>
-        <v/>
-      </c>
-      <c r="J7" s="21" t="str">
-        <f aca="false">IF(H7="","",IF(H7=I7,"مطابق","مختلف"))</f>
-        <v/>
-      </c>
-      <c r="K7" s="45" t="str">
-        <f aca="false">IFERROR(IF(H7="","",(H7-D7)/D7),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="69" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>533</v>
-      </c>
-      <c r="C8" s="70" t="s">
-        <v>537</v>
-      </c>
-      <c r="D8" s="71" t="n">
-        <f aca="false">'الخطة التنفيذية'!E9</f>
-        <v>0.28</v>
-      </c>
-      <c r="E8" s="65"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="65"/>
-      <c r="H8" s="65"/>
-      <c r="I8" s="71" t="str">
-        <f aca="false">IF('الخطة التنفيذية'!H9="","",'الخطة التنفيذية'!H9)</f>
-        <v/>
-      </c>
-      <c r="J8" s="21" t="str">
-        <f aca="false">IF(H8="","",IF(H8=I8,"مطابق","مختلف"))</f>
-        <v/>
-      </c>
-      <c r="K8" s="45" t="str">
-        <f aca="false">IFERROR(IF(H8="","",(H8-D8)/D8),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="69" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>538</v>
-      </c>
-      <c r="C9" s="70" t="s">
-        <v>541</v>
-      </c>
-      <c r="D9" s="71" t="n">
-        <f aca="false">'الخطة التنفيذية'!E10</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="71" t="str">
-        <f aca="false">IF('الخطة التنفيذية'!H10="","",'الخطة التنفيذية'!H10)</f>
-        <v/>
-      </c>
-      <c r="J9" s="21" t="str">
-        <f aca="false">IF(H9="","",IF(H9=I9,"مطابق","مختلف"))</f>
-        <v/>
-      </c>
-      <c r="K9" s="45" t="str">
-        <f aca="false">IFERROR(IF(H9="","",(H9-D9)/D9),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="69" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="70" t="s">
-        <v>545</v>
-      </c>
-      <c r="D10" s="71" t="n">
-        <f aca="false">'الخطة التنفيذية'!E11</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
-      <c r="G10" s="65"/>
-      <c r="H10" s="65"/>
-      <c r="I10" s="71" t="str">
-        <f aca="false">IF('الخطة التنفيذية'!H11="","",'الخطة التنفيذية'!H11)</f>
-        <v/>
-      </c>
-      <c r="J10" s="21" t="str">
-        <f aca="false">IF(H10="","",IF(H10=I10,"مطابق","مختلف"))</f>
-        <v/>
-      </c>
-      <c r="K10" s="45" t="str">
-        <f aca="false">IFERROR(IF(H10="","",(H10-D10)/D10),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="69" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="C11" s="70" t="s">
-        <v>548</v>
-      </c>
-      <c r="D11" s="71" t="n">
-        <f aca="false">'الخطة التنفيذية'!E12</f>
-        <v>31</v>
-      </c>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
-      <c r="I11" s="71" t="str">
-        <f aca="false">IF('الخطة التنفيذية'!H12="","",'الخطة التنفيذية'!H12)</f>
-        <v/>
-      </c>
-      <c r="J11" s="21" t="str">
-        <f aca="false">IF(H11="","",IF(H11=I11,"مطابق","مختلف"))</f>
-        <v/>
-      </c>
-      <c r="K11" s="45" t="str">
-        <f aca="false">IFERROR(IF(H11="","",(H11-D11)/D11),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="69" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" s="70" t="s">
-        <v>551</v>
-      </c>
-      <c r="D12" s="71" t="n">
-        <f aca="false">'الخطة التنفيذية'!E13</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="65"/>
-      <c r="F12" s="65"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
-      <c r="I12" s="71" t="str">
-        <f aca="false">IF('الخطة التنفيذية'!H13="","",'الخطة التنفيذية'!H13)</f>
-        <v/>
-      </c>
-      <c r="J12" s="21" t="str">
-        <f aca="false">IF(H12="","",IF(H12=I12,"مطابق","مختلف"))</f>
-        <v/>
-      </c>
-      <c r="K12" s="45" t="str">
-        <f aca="false">IFERROR(IF(H12="","",(H12-D12)/D12),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="69" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="70" t="s">
-        <v>554</v>
-      </c>
-      <c r="D13" s="71" t="n">
-        <f aca="false">'الخطة التنفيذية'!E14</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="65"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="65"/>
-      <c r="I13" s="71" t="str">
-        <f aca="false">IF('الخطة التنفيذية'!H14="","",'الخطة التنفيذية'!H14)</f>
-        <v/>
-      </c>
-      <c r="J13" s="21" t="str">
-        <f aca="false">IF(H13="","",IF(H13=I13,"مطابق","مختلف"))</f>
-        <v/>
-      </c>
-      <c r="K13" s="45" t="str">
-        <f aca="false">IFERROR(IF(H13="","",(H13-D13)/D13),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="69" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" s="70" t="s">
-        <v>556</v>
-      </c>
-      <c r="D14" s="71" t="n">
-        <f aca="false">'الخطة التنفيذية'!E15</f>
-        <v>6</v>
-      </c>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="71" t="str">
-        <f aca="false">IF('الخطة التنفيذية'!H15="","",'الخطة التنفيذية'!H15)</f>
-        <v/>
-      </c>
-      <c r="J14" s="21" t="str">
-        <f aca="false">IF(H14="","",IF(H14=I14,"مطابق","مختلف"))</f>
-        <v/>
-      </c>
-      <c r="K14" s="45" t="str">
-        <f aca="false">IFERROR(IF(H14="","",(H14-D14)/D14),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="69" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="70" t="s">
-        <v>560</v>
-      </c>
-      <c r="D15" s="71" t="n">
-        <f aca="false">'الخطة التنفيذية'!E16</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="65"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="71" t="str">
-        <f aca="false">IF('الخطة التنفيذية'!H16="","",'الخطة التنفيذية'!H16)</f>
-        <v/>
-      </c>
-      <c r="J15" s="21" t="str">
-        <f aca="false">IF(H15="","",IF(H15=I15,"مطابق","مختلف"))</f>
-        <v/>
-      </c>
-      <c r="K15" s="45" t="str">
-        <f aca="false">IFERROR(IF(H15="","",(H15-D15)/D15),"")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>
--- a/docs/executive-plan.xlsx
+++ b/docs/executive-plan.xlsx
@@ -16,10 +16,11 @@
     <sheet name="منفذ ٢ — العقار والتأجير" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="منفذ ٤ — الإكسسوارات" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="تحليل موقفي — المنتجات" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="الخطة التنفيذية" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="المستهدفات الربعية" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="المبادرات" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="المحطات" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="جاهزية الإطلاق" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="الخطة التنفيذية" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="المستهدفات الربعية" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="المبادرات" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="المحطات" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="1032">
   <si>
     <t xml:space="preserve">نموذج الخطة التنفيذية — الإدارة التجارية</t>
   </si>
@@ -84,18 +85,18 @@
     <t xml:space="preserve">كل منتج داخل رحلة العميل: موقعه ومكوثه ومالكه وفجوته.</t>
   </si>
   <si>
-    <t xml:space="preserve">منفذ ٢ — العقار</t>
+    <t xml:space="preserve">جاهزية الإطلاق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أربع موجات: ما يبدأ الآن وما يتأخر ولماذا.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دليل الألوان</t>
   </si>
   <si>
     <t xml:space="preserve">تفصيل الشواغر والعلامات — الأولوية الأولى.</t>
   </si>
   <si>
-    <t xml:space="preserve">دليل الألوان</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السوق واللاعبون وقرار التأجير مقابل التشغيل.</t>
-  </si>
-  <si>
     <t xml:space="preserve">أصفر + خط أزرق</t>
   </si>
   <si>
@@ -2025,6 +2026,432 @@
     <t xml:space="preserve">التطبيق ليس منتجاً بموقع — هو الطبقة التي تحوّل 22.5 مليون زيارة مجهولة إلى عميل معروف. وبدونه كل منتج أعلاه يُباع مرة واحدة لمجهول، ولا يمكن قياس أثر أي مبادرة.</t>
   </si>
   <si>
+    <t xml:space="preserve">جاهزية الإطلاق — ما نبدأ به الآن وما يتأخر ولماذا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أربع موجات · المُعطِّل الحقيقي لكل منتج · ومن يملك قرار رفعه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قاعدة الترتيب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ليس حسب حجم الفرصة بل حسب المُعطِّل: ما يحتاج قرارنا وحده يبدأ الآن · وما يحتاج فريقاً أو تعاقداً يليه · وما يحتاج تعديلاً إنشائياً أو طرفاً ثالثاً يتأخر · وما يحتاج بنية تقنية أو إعادة تفاوض عقود يأتي أخيراً. والموجة الأولى تموّل ما بعدها.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المنتج / المبادرة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ما نملكه اليوم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المُعطِّل الحقيقي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">من يملك القرار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رأس المال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زمن الإطلاق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأثر المتوقع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الـ52؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الموجة ١ — تبدأ الآن · قرارنا وحدنا · 0–3 أشهر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حصر وتصنيف الشواغر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96 وحدة شاغرة — 60 منها بلا نوع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا شيء يمنعه — عمل ميداني بحت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نحن وحدنا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا يُذكر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4–6 أسابيع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شرط لكل مبادرة تأجير — ما لم يُحصر لا يُسوَّق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رفّ إكسسوارات الكاشير</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71 محطة مفتوحة بكاشير قائم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اختيار مورّد وتسعير — بلا مساحة ولا عقد إيجار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منخفض جداً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6–8 أسابيع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يرفع سلة الزيارة فوراً · يُختبر في محطة واحدة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نعم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تسعير الوحدات المصنّفة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36 وحدة شاغرة معروفة النوع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">غياب جدول أسعار وفريق تأجير</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منخفض</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8–12 أسبوعاً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أول إيراد إيجاري إضافي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ملف الظبية المستقل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 وحدة — وحدة واحدة مؤجّرة (3.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا أحد يملكها كملف — تُعامل ضمن الشبكة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ربع مشكلة الشغور في ملف واحد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إدخال منتجات الموجات القادمة في تصميم الـ52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52 محطة تحت الإنشاء لم تُسلَّم بعد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نافذة تُغلق مع كل محطة تُسلَّم — القرار الآن أو لا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نحن + المشاريع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا يُذكر الآن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فوري</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يحوّل مبادرات الموجة ٣ إلى جاهزة عند الافتتاح</t>
+  </si>
+  <si>
+    <t xml:space="preserve">★</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الموجة ٢ — تحتاج فريقاً أو تعاقداً · 3–9 أشهر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الصرافات والخزائن الذكية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66 محطة بلا صراف · 70 بلا خزائن · وصول 24 ساعة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا قائمة مواقع مبوّبة ولا مندوب يفاوض البنوك</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نحن + البنك/المشغّل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صفر — الطرف الآخر يركّب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3–5 أشهر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إيراد ثابت بلا تشغيل · بيع موقع لا بيع منتج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عقود الأساطيل المباشرة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ديزل 19.3% · MK289 ديزلها 64% وتنمو 27%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا مندوب B2B ولا آلية ائتمان وفوترة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نحن + المنشأة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منخفض–متوسط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4–6 أشهر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحويل حجم قائم بلا عقد إلى حجم متعاقَد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اللوحات الإعلانية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355 موقعاً على شرايين حركة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تراخيص الإعلان الخارجي + اختيار نموذج (وكالة أم بيع مباشر)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نحن + الوكالة + الجهة البلدية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صفر في نموذج الوكالة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4–8 أشهر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إيراد من أصل مملوك معطّل تماماً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اتفاقية إطارية للماركت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فريش واي في 17 محطة — النموذج المثبت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا اتفاقية شبكية — كل فرع يُتفاوض عليه منفرداً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نحن + السلسلة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحويل 190 علامة مفتّتة إلى محفظة قابلة للإدارة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الانضمام لمنصة إنفاق كنقطة قبول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محطات جاهزة · المنصة تملك 500 ألف مركبة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قرار تجاري: عمولة المنصة مقابل تكلفة البيع المباشر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نحن + المنصة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3–6 أشهر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حجم فوري — مقابل التنازل عن العميل والبيانات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الموجة ٣ — تعديل إنشائي أو طرف ثالث · 9–18 شهراً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61 محطة مفتوحة بلا خدمة إطارات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا ورش مجهزة في أغلبها — تحتاج بناءً ومعدات وفنيين</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نحن + الشريك</t>
+  </si>
+  <si>
+    <t xml:space="preserve">متوسط–مرتفع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9–15 شهراً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أعلى سلة في القطاع · وأدنى اختراق عندنا (14%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">★ نعم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وحدات شاغرة تحتمل النشاط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا مستأجر متخصص ولا مساحة مهيّأة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نحن + المتخصص</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منخفض (تأجير)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9–12 شهراً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منفذ بلا مسيطر — لكن سلة لا وجهة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مواقف الشاحنات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,420 م² أرض غير مبنية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحتاج تجهيزاً: إنارة وأمن ودورات مياه — ورخصة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نحن + الجهة التنظيمية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">متوسط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9–18 شهراً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أطول مكوث ممكن · يغذّي الديزل والأسطول مباشرة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 وحدات شاغرة مصنّفة درايف ثرو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يحتاج مسار سيارات مستقل — تعديل إنشائي · وعلامة قوية تقبل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نحن + وكيل الامتياز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مرتفع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12–18 شهراً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المنتج الوحيد الذي يجلب زيارة لا تحتاج وقوداً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">★★ نعم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">علامات مطاعم قوية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 محطة بمطعم · ماكدونالدز في 7 وكنتاكي في 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">القرار عند وكيل الامتياز لا عندنا ولا عند العلامة نفسها</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وكيل الامتياز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يحوّل المحطة من سلة إلى وجهة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الموجة ٤ — بنية تقنية أو عقود قائمة · 18 شهراً فأكثر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قدرة كهربائية + قرار المشغّل (EVIQ) واختياره للمواقع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVIQ لا نحن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صفر في نموذج الاستضافة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12–24 شهراً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المنتج ليس الشاحن بل نافذة الـ30 دقيقة التي يفتحها</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحويل الزيوت من إيجار إلى نسبة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 محطة بخدمة زيوت وصيانة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عقود قائمة — لا تُعدَّل إلا عند التجديد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نحن + الشريك عند التجديد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أطول نافذة مكوث (45 د) ونأخذ عنها إيجاراً فقط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تطبيق قائم · 22.5 مليون زيارة سنوياً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا يبيع شيئاً لا يُباع بغيره · 62.6% نقد بلا احتكاك</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نحن + التقنية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الطبقة التي تجعل كل ما سبق قابلاً للقياس — وشرط قياس أي مبادرة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منصة إنفاق أساطيل خاصة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شبكة محطات — لا منتج تقني</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منتج B2B كامل: ائتمان وفوترة وصلاحيات وشبكة قبول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مرتفع جداً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18–36 شهراً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استعادة العميل والبيانات والهامش — أمام 10 آلاف عميل قائم لبترو آب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الخلاصة العملية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خمس مبادرات تبدأ خلال ثلاثة أشهر بلا رأس مال يُذكر ولا طرف ثالث: حصر الشواغر · رفّ الكاشير · تسعير الوحدات · ملف الظبية · وإدخال المنتجات القادمة في تصميم الـ52. وأربع أخرى تحتاج فريقاً أو تعاقداً فقط — لا بناءً.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">★ النافذة التي تُغلق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خمسة منتجات مؤجَّلة لأنها تحتاج تعديلاً إنشائياً في محطات قائمة: درايف ثرو (مسار مستقل) · إطارات (ورشة) · مواقف (تجهيز أرض) · شحن (قدرة كهربائية). لكن 52 محطة تحت الإنشاء لم تُسلَّم بعد — ووضع هذه المتطلبات في تصميمها الآن يحوّلها من مبادرات 18 شهراً إلى منتجات جاهزة يوم الافتتاح. هذه أرخص قيمة في الملف كله، وتُفقد نهائياً مع كل محطة تُسلَّم.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ما لا يعتمد علينا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الشحن الكهربائي قراره عند EVIQ لا عندنا · وعلامات المطاعم القوية قرارها عند وكيل الامتياز لا عند العلامة نفسها. هذان لا يُخطَّط لهما بجدول زمني بل بفتح قناة تفاوض مبكرة ومتابعتها.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التسلسل المنطقي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الموجة الأولى تنتج إيراداً وبيانات بلا رأس مال، والموجة الثانية تبني الفريق والعلاقات، والثالثة تصرف رأس المال بعد أن ثبتت الجدوى. أما التطبيق — رغم أنه الأخير زمنياً — فهو شرط قياس كل ما قبله، ولذلك يبدأ العمل عليه بالتوازي لا بالتتابع.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">افتراضات يجب التحقق منها</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أزمنة الإطلاق تقديرية ومبنية على طبيعة كل عائق لا على خطة موارد معتمدة. وثلاثة مجاهيل تغيّر الترتيب: آجال عقود الزيوت القائمة · متطلبات ترخيص الإعلان الخارجي والمواقف · وحجم الفريق المتاح للتأجير والمبيعات B2B.</t>
+  </si>
+  <si>
     <t xml:space="preserve">الخطة التنفيذية لمنافذ البيع</t>
   </si>
   <si>
@@ -2248,9 +2675,6 @@
   </si>
   <si>
     <t xml:space="preserve">التكلفة التقديرية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الأثر المتوقع</t>
   </si>
   <si>
     <t xml:space="preserve">الإنجاز</t>
@@ -2856,7 +3280,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2878,7 +3302,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6E0B4"/>
-        <bgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -2896,7 +3320,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFD9E2F3"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -2920,6 +3344,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
         <bgColor rgb="FFD9E2F3"/>
       </patternFill>
     </fill>
@@ -2986,7 +3416,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="87">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3023,12 +3453,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -3239,6 +3669,22 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
@@ -3366,8 +3812,8 @@
       <rgbColor rgb="FFD9E2F3"/>
       <rgbColor rgb="FFC6E0B4"/>
       <rgbColor rgb="FFFFE699"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FFE7E6E6"/>
-      <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFF8CBAD"/>
       <rgbColor rgb="FF3366FF"/>
@@ -3701,7 +4147,7 @@
       <c r="B18" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="4" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3711,10 +4157,10 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="10" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3722,7 +4168,7 @@
       <c r="B22" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="10" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3730,7 +4176,7 @@
       <c r="B23" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="10" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3738,7 +4184,7 @@
       <c r="B24" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="10" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3746,7 +4192,7 @@
       <c r="B25" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="10" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3786,6 +4232,688 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:O18"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>808</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>809</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>810</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>811</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>812</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>813</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>814</v>
+      </c>
+      <c r="N3" s="15" t="s">
+        <v>815</v>
+      </c>
+      <c r="O3" s="15" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="67" t="s">
+        <v>816</v>
+      </c>
+      <c r="B4" s="68" t="s">
+        <v>817</v>
+      </c>
+      <c r="C4" s="67" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="68" t="s">
+        <v>818</v>
+      </c>
+      <c r="E4" s="67" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="67" t="s">
+        <v>819</v>
+      </c>
+      <c r="G4" s="68" t="s">
+        <v>820</v>
+      </c>
+      <c r="H4" s="67" t="n">
+        <v>20</v>
+      </c>
+      <c r="I4" s="67" t="n">
+        <f aca="false">IF(H4="","",H4-E4)</f>
+        <v>14</v>
+      </c>
+      <c r="J4" s="69" t="n">
+        <f aca="false">IFERROR(IF(H4="","",(H4-E4)/E4),"")</f>
+        <v>2.33333333333333</v>
+      </c>
+      <c r="K4" s="68" t="s">
+        <v>821</v>
+      </c>
+      <c r="L4" s="67" t="s">
+        <v>75</v>
+      </c>
+      <c r="M4" s="68" t="s">
+        <v>822</v>
+      </c>
+      <c r="N4" s="68" t="s">
+        <v>823</v>
+      </c>
+      <c r="O4" s="67" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="70" t="n">
+        <v>1271</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>825</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>826</v>
+      </c>
+      <c r="H5" s="71"/>
+      <c r="I5" s="70" t="str">
+        <f aca="false">IF(H5="","",H5-E5)</f>
+        <v/>
+      </c>
+      <c r="J5" s="45" t="str">
+        <f aca="false">IFERROR(IF(H5="","",(H5-E5)/E5),"")</f>
+        <v/>
+      </c>
+      <c r="K5" s="72"/>
+      <c r="L5" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="M5" s="72"/>
+      <c r="N5" s="16" t="s">
+        <v>827</v>
+      </c>
+      <c r="O5" s="73"/>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="70" t="n">
+        <v>25</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>828</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>829</v>
+      </c>
+      <c r="H6" s="71"/>
+      <c r="I6" s="70" t="str">
+        <f aca="false">IF(H6="","",H6-E6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="45" t="str">
+        <f aca="false">IFERROR(IF(H6="","",(H6-E6)/E6),"")</f>
+        <v/>
+      </c>
+      <c r="K6" s="72"/>
+      <c r="L6" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="M6" s="72"/>
+      <c r="N6" s="16" t="s">
+        <v>830</v>
+      </c>
+      <c r="O6" s="73"/>
+    </row>
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="70" t="n">
+        <v>39</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>831</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>820</v>
+      </c>
+      <c r="H7" s="71"/>
+      <c r="I7" s="70" t="str">
+        <f aca="false">IF(H7="","",H7-E7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="45" t="str">
+        <f aca="false">IFERROR(IF(H7="","",(H7-E7)/E7),"")</f>
+        <v/>
+      </c>
+      <c r="K7" s="72"/>
+      <c r="L7" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="M7" s="72"/>
+      <c r="N7" s="16" t="s">
+        <v>832</v>
+      </c>
+      <c r="O7" s="73"/>
+    </row>
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>833</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>834</v>
+      </c>
+      <c r="H8" s="71"/>
+      <c r="I8" s="70" t="str">
+        <f aca="false">IF(H8="","",H8-E8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="45" t="str">
+        <f aca="false">IFERROR(IF(H8="","",(H8-E8)/E8),"")</f>
+        <v/>
+      </c>
+      <c r="K8" s="72"/>
+      <c r="L8" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="M8" s="72"/>
+      <c r="N8" s="16" t="s">
+        <v>835</v>
+      </c>
+      <c r="O8" s="73"/>
+    </row>
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>836</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>837</v>
+      </c>
+      <c r="E9" s="70" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>838</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>839</v>
+      </c>
+      <c r="H9" s="71"/>
+      <c r="I9" s="70" t="str">
+        <f aca="false">IF(H9="","",H9-E9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="45" t="str">
+        <f aca="false">IFERROR(IF(H9="","",(H9-E9)/E9),"")</f>
+        <v/>
+      </c>
+      <c r="K9" s="72"/>
+      <c r="L9" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="M9" s="72"/>
+      <c r="N9" s="16" t="s">
+        <v>840</v>
+      </c>
+      <c r="O9" s="73"/>
+    </row>
+    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>841</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="E10" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>842</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>843</v>
+      </c>
+      <c r="H10" s="71"/>
+      <c r="I10" s="70" t="str">
+        <f aca="false">IF(H10="","",H10-E10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="45" t="str">
+        <f aca="false">IFERROR(IF(H10="","",(H10-E10)/E10),"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="72"/>
+      <c r="L10" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="M10" s="72"/>
+      <c r="N10" s="16" t="s">
+        <v>844</v>
+      </c>
+      <c r="O10" s="73"/>
+    </row>
+    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>845</v>
+      </c>
+      <c r="E11" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>846</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>847</v>
+      </c>
+      <c r="H11" s="71"/>
+      <c r="I11" s="70" t="str">
+        <f aca="false">IF(H11="","",H11-E11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="45" t="str">
+        <f aca="false">IFERROR(IF(H11="","",(H11-E11)/E11),"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="72"/>
+      <c r="L11" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="M11" s="72"/>
+      <c r="N11" s="16" t="s">
+        <v>848</v>
+      </c>
+      <c r="O11" s="73"/>
+    </row>
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="70" t="n">
+        <v>31</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>849</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>850</v>
+      </c>
+      <c r="H12" s="71"/>
+      <c r="I12" s="70" t="str">
+        <f aca="false">IF(H12="","",H12-E12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="45" t="str">
+        <f aca="false">IFERROR(IF(H12="","",(H12-E12)/E12),"")</f>
+        <v/>
+      </c>
+      <c r="K12" s="72"/>
+      <c r="L12" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="M12" s="72"/>
+      <c r="N12" s="16" t="s">
+        <v>851</v>
+      </c>
+      <c r="O12" s="73"/>
+    </row>
+    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="E13" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>852</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>853</v>
+      </c>
+      <c r="H13" s="71"/>
+      <c r="I13" s="70" t="str">
+        <f aca="false">IF(H13="","",H13-E13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="45" t="str">
+        <f aca="false">IFERROR(IF(H13="","",(H13-E13)/E13),"")</f>
+        <v/>
+      </c>
+      <c r="K13" s="72"/>
+      <c r="L13" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="M13" s="72"/>
+      <c r="N13" s="16" t="s">
+        <v>854</v>
+      </c>
+      <c r="O13" s="73"/>
+    </row>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>855</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>856</v>
+      </c>
+      <c r="H14" s="71"/>
+      <c r="I14" s="70" t="str">
+        <f aca="false">IF(H14="","",H14-E14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="45" t="str">
+        <f aca="false">IFERROR(IF(H14="","",(H14-E14)/E14),"")</f>
+        <v/>
+      </c>
+      <c r="K14" s="72"/>
+      <c r="L14" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="M14" s="72"/>
+      <c r="N14" s="16" t="s">
+        <v>857</v>
+      </c>
+      <c r="O14" s="73"/>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>818</v>
+      </c>
+      <c r="E15" s="70" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>846</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>858</v>
+      </c>
+      <c r="H15" s="71"/>
+      <c r="I15" s="70" t="str">
+        <f aca="false">IF(H15="","",H15-E15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="45" t="str">
+        <f aca="false">IFERROR(IF(H15="","",(H15-E15)/E15),"")</f>
+        <v/>
+      </c>
+      <c r="K15" s="72"/>
+      <c r="L15" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="M15" s="72"/>
+      <c r="N15" s="16" t="s">
+        <v>859</v>
+      </c>
+      <c r="O15" s="73"/>
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>860</v>
+      </c>
+      <c r="E16" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>861</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>862</v>
+      </c>
+      <c r="H16" s="71"/>
+      <c r="I16" s="70" t="str">
+        <f aca="false">IF(H16="","",H16-E16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="45" t="str">
+        <f aca="false">IFERROR(IF(H16="","",(H16-E16)/E16),"")</f>
+        <v/>
+      </c>
+      <c r="K16" s="72"/>
+      <c r="L16" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="M16" s="72"/>
+      <c r="N16" s="16" t="s">
+        <v>863</v>
+      </c>
+      <c r="O16" s="73"/>
+    </row>
+    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="C18" s="74" t="s">
+        <v>865</v>
+      </c>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74"/>
+      <c r="G18" s="74"/>
+      <c r="H18" s="74"/>
+      <c r="I18" s="74"/>
+      <c r="J18" s="74"/>
+      <c r="K18" s="74"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="C18:K18"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:K15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -3815,7 +4943,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>724</v>
+        <v>866</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3836,52 +4964,52 @@
         <v>47</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>673</v>
+        <v>815</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>666</v>
+        <v>808</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>725</v>
+        <v>867</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>726</v>
+        <v>868</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>727</v>
+        <v>869</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>728</v>
+        <v>870</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>669</v>
+        <v>811</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>729</v>
+        <v>871</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>730</v>
+        <v>872</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="71" t="n">
+      <c r="A4" s="75" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="72" t="s">
-        <v>685</v>
-      </c>
-      <c r="D4" s="73" t="n">
+      <c r="C4" s="76" t="s">
+        <v>827</v>
+      </c>
+      <c r="D4" s="77" t="n">
         <f aca="false">'الخطة التنفيذية'!E5</f>
         <v>1271</v>
       </c>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="73" t="str">
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="77" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H5="","",'الخطة التنفيذية'!H5)</f>
         <v/>
       </c>
@@ -3895,24 +5023,24 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="71" t="n">
+      <c r="A5" s="75" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="72" t="s">
-        <v>688</v>
-      </c>
-      <c r="D5" s="73" t="n">
+      <c r="C5" s="76" t="s">
+        <v>830</v>
+      </c>
+      <c r="D5" s="77" t="n">
         <f aca="false">'الخطة التنفيذية'!E6</f>
         <v>25</v>
       </c>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="73" t="str">
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="77" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H6="","",'الخطة التنفيذية'!H6)</f>
         <v/>
       </c>
@@ -3926,24 +5054,24 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="71" t="n">
+      <c r="A6" s="75" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="72" t="s">
-        <v>690</v>
-      </c>
-      <c r="D6" s="73" t="n">
+      <c r="C6" s="76" t="s">
+        <v>832</v>
+      </c>
+      <c r="D6" s="77" t="n">
         <f aca="false">'الخطة التنفيذية'!E7</f>
         <v>39</v>
       </c>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="73" t="str">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="77" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H7="","",'الخطة التنفيذية'!H7)</f>
         <v/>
       </c>
@@ -3957,24 +5085,24 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="71" t="n">
+      <c r="A7" s="75" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="72" t="s">
-        <v>693</v>
-      </c>
-      <c r="D7" s="73" t="n">
+      <c r="C7" s="76" t="s">
+        <v>835</v>
+      </c>
+      <c r="D7" s="77" t="n">
         <f aca="false">'الخطة التنفيذية'!E8</f>
         <v>0</v>
       </c>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="73" t="str">
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="77" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H8="","",'الخطة التنفيذية'!H8)</f>
         <v/>
       </c>
@@ -3988,24 +5116,24 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="71" t="n">
+      <c r="A8" s="75" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>694</v>
-      </c>
-      <c r="C8" s="72" t="s">
-        <v>698</v>
-      </c>
-      <c r="D8" s="73" t="n">
+        <v>836</v>
+      </c>
+      <c r="C8" s="76" t="s">
+        <v>840</v>
+      </c>
+      <c r="D8" s="77" t="n">
         <f aca="false">'الخطة التنفيذية'!E9</f>
         <v>0.28</v>
       </c>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="73" t="str">
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="77" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H9="","",'الخطة التنفيذية'!H9)</f>
         <v/>
       </c>
@@ -4019,24 +5147,24 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="71" t="n">
+      <c r="A9" s="75" t="n">
         <v>6</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>699</v>
-      </c>
-      <c r="C9" s="72" t="s">
-        <v>702</v>
-      </c>
-      <c r="D9" s="73" t="n">
+        <v>841</v>
+      </c>
+      <c r="C9" s="76" t="s">
+        <v>844</v>
+      </c>
+      <c r="D9" s="77" t="n">
         <f aca="false">'الخطة التنفيذية'!E10</f>
         <v>0</v>
       </c>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="73" t="str">
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="77" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H10="","",'الخطة التنفيذية'!H10)</f>
         <v/>
       </c>
@@ -4050,24 +5178,24 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="71" t="n">
+      <c r="A10" s="75" t="n">
         <v>7</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="72" t="s">
-        <v>706</v>
-      </c>
-      <c r="D10" s="73" t="n">
+      <c r="C10" s="76" t="s">
+        <v>848</v>
+      </c>
+      <c r="D10" s="77" t="n">
         <f aca="false">'الخطة التنفيذية'!E11</f>
         <v>0</v>
       </c>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="73" t="str">
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="77" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H11="","",'الخطة التنفيذية'!H11)</f>
         <v/>
       </c>
@@ -4081,24 +5209,24 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="71" t="n">
+      <c r="A11" s="75" t="n">
         <v>8</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C11" s="72" t="s">
-        <v>709</v>
-      </c>
-      <c r="D11" s="73" t="n">
+      <c r="C11" s="76" t="s">
+        <v>851</v>
+      </c>
+      <c r="D11" s="77" t="n">
         <f aca="false">'الخطة التنفيذية'!E12</f>
         <v>31</v>
       </c>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="73" t="str">
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="77" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H12="","",'الخطة التنفيذية'!H12)</f>
         <v/>
       </c>
@@ -4112,24 +5240,24 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="71" t="n">
+      <c r="A12" s="75" t="n">
         <v>9</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="72" t="s">
-        <v>712</v>
-      </c>
-      <c r="D12" s="73" t="n">
+      <c r="C12" s="76" t="s">
+        <v>854</v>
+      </c>
+      <c r="D12" s="77" t="n">
         <f aca="false">'الخطة التنفيذية'!E13</f>
         <v>0</v>
       </c>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="73" t="str">
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="77" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H13="","",'الخطة التنفيذية'!H13)</f>
         <v/>
       </c>
@@ -4143,24 +5271,24 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="71" t="n">
+      <c r="A13" s="75" t="n">
         <v>10</v>
       </c>
       <c r="B13" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="72" t="s">
-        <v>715</v>
-      </c>
-      <c r="D13" s="73" t="n">
+      <c r="C13" s="76" t="s">
+        <v>857</v>
+      </c>
+      <c r="D13" s="77" t="n">
         <f aca="false">'الخطة التنفيذية'!E14</f>
         <v>0</v>
       </c>
-      <c r="E13" s="67"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="73" t="str">
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="77" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H14="","",'الخطة التنفيذية'!H14)</f>
         <v/>
       </c>
@@ -4174,24 +5302,24 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="71" t="n">
+      <c r="A14" s="75" t="n">
         <v>11</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="72" t="s">
-        <v>717</v>
-      </c>
-      <c r="D14" s="73" t="n">
+      <c r="C14" s="76" t="s">
+        <v>859</v>
+      </c>
+      <c r="D14" s="77" t="n">
         <f aca="false">'الخطة التنفيذية'!E15</f>
         <v>6</v>
       </c>
-      <c r="E14" s="67"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="67"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="73" t="str">
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="77" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H15="","",'الخطة التنفيذية'!H15)</f>
         <v/>
       </c>
@@ -4205,24 +5333,24 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="71" t="n">
+      <c r="A15" s="75" t="n">
         <v>12</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="72" t="s">
-        <v>721</v>
-      </c>
-      <c r="D15" s="73" t="n">
+      <c r="C15" s="76" t="s">
+        <v>863</v>
+      </c>
+      <c r="D15" s="77" t="n">
         <f aca="false">'الخطة التنفيذية'!E16</f>
         <v>0</v>
       </c>
-      <c r="E15" s="67"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="73" t="str">
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="77" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H16="","",'الخطة التنفيذية'!H16)</f>
         <v/>
       </c>
@@ -4250,7 +5378,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4274,7 +5402,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>731</v>
+        <v>873</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4292,7 +5420,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>732</v>
+        <v>874</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4313,597 +5441,597 @@
         <v>46</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>733</v>
+        <v>875</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>47</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>734</v>
+        <v>876</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>56</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>672</v>
+        <v>814</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>735</v>
+        <v>877</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>736</v>
+        <v>878</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>737</v>
+        <v>879</v>
       </c>
       <c r="J3" s="15" t="s">
         <v>57</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>738</v>
+        <v>880</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>739</v>
+        <v>674</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>378</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>740</v>
+        <v>881</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="63" t="s">
-        <v>674</v>
-      </c>
-      <c r="B4" s="64" t="s">
-        <v>741</v>
-      </c>
-      <c r="C4" s="63" t="s">
+      <c r="A4" s="67" t="s">
+        <v>816</v>
+      </c>
+      <c r="B4" s="68" t="s">
+        <v>882</v>
+      </c>
+      <c r="C4" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="63" t="s">
+      <c r="D4" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="63" t="s">
+      <c r="E4" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="63" t="s">
-        <v>680</v>
-      </c>
-      <c r="G4" s="74" t="n">
+      <c r="F4" s="67" t="s">
+        <v>822</v>
+      </c>
+      <c r="G4" s="78" t="n">
         <v>46235</v>
       </c>
-      <c r="H4" s="74" t="n">
+      <c r="H4" s="78" t="n">
         <v>46326</v>
       </c>
-      <c r="I4" s="63" t="n">
+      <c r="I4" s="67" t="n">
         <f aca="false">IF(OR(G4="",H4=""),"",H4-G4)</f>
         <v>91</v>
       </c>
-      <c r="J4" s="63" t="n">
+      <c r="J4" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="63" t="s">
-        <v>742</v>
-      </c>
-      <c r="L4" s="64" t="s">
-        <v>743</v>
-      </c>
-      <c r="M4" s="63" t="s">
-        <v>682</v>
-      </c>
-      <c r="N4" s="75" t="n">
+      <c r="K4" s="67" t="s">
+        <v>883</v>
+      </c>
+      <c r="L4" s="68" t="s">
+        <v>884</v>
+      </c>
+      <c r="M4" s="67" t="s">
+        <v>824</v>
+      </c>
+      <c r="N4" s="79" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="71" t="n">
+      <c r="A5" s="75" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
       <c r="I5" s="21" t="str">
         <f aca="false">IF(OR(G5="",H5=""),"",H5-G5)</f>
         <v/>
       </c>
-      <c r="J5" s="69"/>
-      <c r="K5" s="69"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="69"/>
-      <c r="N5" s="77"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="72"/>
+      <c r="M5" s="73"/>
+      <c r="N5" s="81"/>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="71" t="n">
+      <c r="A6" s="75" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="68"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
+      <c r="B6" s="72"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
       <c r="I6" s="21" t="str">
         <f aca="false">IF(OR(G6="",H6=""),"",H6-G6)</f>
         <v/>
       </c>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="77"/>
+      <c r="J6" s="73"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="72"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="81"/>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="71" t="n">
+      <c r="A7" s="75" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="68"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="76"/>
-      <c r="H7" s="76"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="73"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
       <c r="I7" s="21" t="str">
         <f aca="false">IF(OR(G7="",H7=""),"",H7-G7)</f>
         <v/>
       </c>
-      <c r="J7" s="69"/>
-      <c r="K7" s="69"/>
-      <c r="L7" s="68"/>
-      <c r="M7" s="69"/>
-      <c r="N7" s="77"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="73"/>
+      <c r="L7" s="72"/>
+      <c r="M7" s="73"/>
+      <c r="N7" s="81"/>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="71" t="n">
+      <c r="A8" s="75" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="68"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="76"/>
-      <c r="H8" s="76"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
       <c r="I8" s="21" t="str">
         <f aca="false">IF(OR(G8="",H8=""),"",H8-G8)</f>
         <v/>
       </c>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="68"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="77"/>
+      <c r="J8" s="73"/>
+      <c r="K8" s="73"/>
+      <c r="L8" s="72"/>
+      <c r="M8" s="73"/>
+      <c r="N8" s="81"/>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="71" t="n">
+      <c r="A9" s="75" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="68"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="76"/>
-      <c r="H9" s="76"/>
+      <c r="B9" s="72"/>
+      <c r="C9" s="73"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="80"/>
       <c r="I9" s="21" t="str">
         <f aca="false">IF(OR(G9="",H9=""),"",H9-G9)</f>
         <v/>
       </c>
-      <c r="J9" s="69"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="68"/>
-      <c r="M9" s="69"/>
-      <c r="N9" s="77"/>
+      <c r="J9" s="73"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="72"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="81"/>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="71" t="n">
+      <c r="A10" s="75" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="68"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="76"/>
-      <c r="H10" s="76"/>
+      <c r="B10" s="72"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="80"/>
+      <c r="H10" s="80"/>
       <c r="I10" s="21" t="str">
         <f aca="false">IF(OR(G10="",H10=""),"",H10-G10)</f>
         <v/>
       </c>
-      <c r="J10" s="69"/>
-      <c r="K10" s="69"/>
-      <c r="L10" s="68"/>
-      <c r="M10" s="69"/>
-      <c r="N10" s="77"/>
+      <c r="J10" s="73"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="72"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="81"/>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="71" t="n">
+      <c r="A11" s="75" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="68"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="76"/>
-      <c r="H11" s="76"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
       <c r="I11" s="21" t="str">
         <f aca="false">IF(OR(G11="",H11=""),"",H11-G11)</f>
         <v/>
       </c>
-      <c r="J11" s="69"/>
-      <c r="K11" s="69"/>
-      <c r="L11" s="68"/>
-      <c r="M11" s="69"/>
-      <c r="N11" s="77"/>
+      <c r="J11" s="73"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="72"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="81"/>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="71" t="n">
+      <c r="A12" s="75" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="68"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="76"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="80"/>
+      <c r="H12" s="80"/>
       <c r="I12" s="21" t="str">
         <f aca="false">IF(OR(G12="",H12=""),"",H12-G12)</f>
         <v/>
       </c>
-      <c r="J12" s="69"/>
-      <c r="K12" s="69"/>
-      <c r="L12" s="68"/>
-      <c r="M12" s="69"/>
-      <c r="N12" s="77"/>
+      <c r="J12" s="73"/>
+      <c r="K12" s="73"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="81"/>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="71" t="n">
+      <c r="A13" s="75" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="68"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="76"/>
-      <c r="H13" s="76"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="73"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="80"/>
+      <c r="H13" s="80"/>
       <c r="I13" s="21" t="str">
         <f aca="false">IF(OR(G13="",H13=""),"",H13-G13)</f>
         <v/>
       </c>
-      <c r="J13" s="69"/>
-      <c r="K13" s="69"/>
-      <c r="L13" s="68"/>
-      <c r="M13" s="69"/>
-      <c r="N13" s="77"/>
+      <c r="J13" s="73"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="72"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="81"/>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="71" t="n">
+      <c r="A14" s="75" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="68"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="76"/>
-      <c r="H14" s="76"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
       <c r="I14" s="21" t="str">
         <f aca="false">IF(OR(G14="",H14=""),"",H14-G14)</f>
         <v/>
       </c>
-      <c r="J14" s="69"/>
-      <c r="K14" s="69"/>
-      <c r="L14" s="68"/>
-      <c r="M14" s="69"/>
-      <c r="N14" s="77"/>
+      <c r="J14" s="73"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="72"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="81"/>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="71" t="n">
+      <c r="A15" s="75" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="68"/>
-      <c r="C15" s="69"/>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="76"/>
-      <c r="H15" s="76"/>
+      <c r="B15" s="72"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
       <c r="I15" s="21" t="str">
         <f aca="false">IF(OR(G15="",H15=""),"",H15-G15)</f>
         <v/>
       </c>
-      <c r="J15" s="69"/>
-      <c r="K15" s="69"/>
-      <c r="L15" s="68"/>
-      <c r="M15" s="69"/>
-      <c r="N15" s="77"/>
+      <c r="J15" s="73"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="72"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="81"/>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="71" t="n">
+      <c r="A16" s="75" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="68"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="76"/>
-      <c r="H16" s="76"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="73"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="73"/>
+      <c r="G16" s="80"/>
+      <c r="H16" s="80"/>
       <c r="I16" s="21" t="str">
         <f aca="false">IF(OR(G16="",H16=""),"",H16-G16)</f>
         <v/>
       </c>
-      <c r="J16" s="69"/>
-      <c r="K16" s="69"/>
-      <c r="L16" s="68"/>
-      <c r="M16" s="69"/>
-      <c r="N16" s="77"/>
+      <c r="J16" s="73"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="72"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="81"/>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="71" t="n">
+      <c r="A17" s="75" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="68"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="76"/>
-      <c r="H17" s="76"/>
+      <c r="B17" s="72"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="80"/>
+      <c r="H17" s="80"/>
       <c r="I17" s="21" t="str">
         <f aca="false">IF(OR(G17="",H17=""),"",H17-G17)</f>
         <v/>
       </c>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
-      <c r="L17" s="68"/>
-      <c r="M17" s="69"/>
-      <c r="N17" s="77"/>
+      <c r="J17" s="73"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="72"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="81"/>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="71" t="n">
+      <c r="A18" s="75" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="68"/>
-      <c r="C18" s="69"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="76"/>
-      <c r="H18" s="76"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="80"/>
+      <c r="H18" s="80"/>
       <c r="I18" s="21" t="str">
         <f aca="false">IF(OR(G18="",H18=""),"",H18-G18)</f>
         <v/>
       </c>
-      <c r="J18" s="69"/>
-      <c r="K18" s="69"/>
-      <c r="L18" s="68"/>
-      <c r="M18" s="69"/>
-      <c r="N18" s="77"/>
+      <c r="J18" s="73"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="72"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="81"/>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="71" t="n">
+      <c r="A19" s="75" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="68"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="76"/>
-      <c r="H19" s="76"/>
+      <c r="B19" s="72"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="80"/>
+      <c r="H19" s="80"/>
       <c r="I19" s="21" t="str">
         <f aca="false">IF(OR(G19="",H19=""),"",H19-G19)</f>
         <v/>
       </c>
-      <c r="J19" s="69"/>
-      <c r="K19" s="69"/>
-      <c r="L19" s="68"/>
-      <c r="M19" s="69"/>
-      <c r="N19" s="77"/>
+      <c r="J19" s="73"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="72"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="81"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="71" t="n">
+      <c r="A20" s="75" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="68"/>
-      <c r="C20" s="69"/>
-      <c r="D20" s="69"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="76"/>
-      <c r="H20" s="76"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="80"/>
       <c r="I20" s="21" t="str">
         <f aca="false">IF(OR(G20="",H20=""),"",H20-G20)</f>
         <v/>
       </c>
-      <c r="J20" s="69"/>
-      <c r="K20" s="69"/>
-      <c r="L20" s="68"/>
-      <c r="M20" s="69"/>
-      <c r="N20" s="77"/>
+      <c r="J20" s="73"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="72"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="81"/>
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="71" t="n">
+      <c r="A21" s="75" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="68"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="76"/>
-      <c r="H21" s="76"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="80"/>
+      <c r="H21" s="80"/>
       <c r="I21" s="21" t="str">
         <f aca="false">IF(OR(G21="",H21=""),"",H21-G21)</f>
         <v/>
       </c>
-      <c r="J21" s="69"/>
-      <c r="K21" s="69"/>
-      <c r="L21" s="68"/>
-      <c r="M21" s="69"/>
-      <c r="N21" s="77"/>
+      <c r="J21" s="73"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="72"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="81"/>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="71" t="n">
+      <c r="A22" s="75" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="68"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="76"/>
-      <c r="H22" s="76"/>
+      <c r="B22" s="72"/>
+      <c r="C22" s="73"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="80"/>
+      <c r="H22" s="80"/>
       <c r="I22" s="21" t="str">
         <f aca="false">IF(OR(G22="",H22=""),"",H22-G22)</f>
         <v/>
       </c>
-      <c r="J22" s="69"/>
-      <c r="K22" s="69"/>
-      <c r="L22" s="68"/>
-      <c r="M22" s="69"/>
-      <c r="N22" s="77"/>
+      <c r="J22" s="73"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="81"/>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="71" t="n">
+      <c r="A23" s="75" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="68"/>
-      <c r="C23" s="69"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="76"/>
-      <c r="H23" s="76"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="80"/>
+      <c r="H23" s="80"/>
       <c r="I23" s="21" t="str">
         <f aca="false">IF(OR(G23="",H23=""),"",H23-G23)</f>
         <v/>
       </c>
-      <c r="J23" s="69"/>
-      <c r="K23" s="69"/>
-      <c r="L23" s="68"/>
-      <c r="M23" s="69"/>
-      <c r="N23" s="77"/>
+      <c r="J23" s="73"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="72"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="81"/>
     </row>
     <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="71" t="n">
+      <c r="A24" s="75" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="68"/>
-      <c r="C24" s="69"/>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="76"/>
-      <c r="H24" s="76"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="73"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="80"/>
+      <c r="H24" s="80"/>
       <c r="I24" s="21" t="str">
         <f aca="false">IF(OR(G24="",H24=""),"",H24-G24)</f>
         <v/>
       </c>
-      <c r="J24" s="69"/>
-      <c r="K24" s="69"/>
-      <c r="L24" s="68"/>
-      <c r="M24" s="69"/>
-      <c r="N24" s="77"/>
+      <c r="J24" s="73"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="81"/>
     </row>
     <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="71" t="n">
+      <c r="A25" s="75" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="68"/>
-      <c r="C25" s="69"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="76"/>
-      <c r="H25" s="76"/>
+      <c r="B25" s="72"/>
+      <c r="C25" s="73"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="80"/>
+      <c r="H25" s="80"/>
       <c r="I25" s="21" t="str">
         <f aca="false">IF(OR(G25="",H25=""),"",H25-G25)</f>
         <v/>
       </c>
-      <c r="J25" s="69"/>
-      <c r="K25" s="69"/>
-      <c r="L25" s="68"/>
-      <c r="M25" s="69"/>
-      <c r="N25" s="77"/>
+      <c r="J25" s="73"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="72"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="81"/>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="71" t="n">
+      <c r="A26" s="75" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="68"/>
-      <c r="C26" s="69"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="76"/>
-      <c r="H26" s="76"/>
+      <c r="B26" s="72"/>
+      <c r="C26" s="73"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="73"/>
+      <c r="G26" s="80"/>
+      <c r="H26" s="80"/>
       <c r="I26" s="21" t="str">
         <f aca="false">IF(OR(G26="",H26=""),"",H26-G26)</f>
         <v/>
       </c>
-      <c r="J26" s="69"/>
-      <c r="K26" s="69"/>
-      <c r="L26" s="68"/>
-      <c r="M26" s="69"/>
-      <c r="N26" s="77"/>
+      <c r="J26" s="73"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="81"/>
     </row>
     <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="71" t="n">
+      <c r="A27" s="75" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="68"/>
-      <c r="C27" s="69"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="76"/>
-      <c r="H27" s="76"/>
+      <c r="B27" s="72"/>
+      <c r="C27" s="73"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="80"/>
+      <c r="H27" s="80"/>
       <c r="I27" s="21" t="str">
         <f aca="false">IF(OR(G27="",H27=""),"",H27-G27)</f>
         <v/>
       </c>
-      <c r="J27" s="69"/>
-      <c r="K27" s="69"/>
-      <c r="L27" s="68"/>
-      <c r="M27" s="69"/>
-      <c r="N27" s="77"/>
+      <c r="J27" s="73"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="72"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="81"/>
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="71" t="n">
+      <c r="A28" s="75" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="68"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="76"/>
-      <c r="H28" s="76"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="73"/>
+      <c r="D28" s="73"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="73"/>
+      <c r="G28" s="80"/>
+      <c r="H28" s="80"/>
       <c r="I28" s="21" t="str">
         <f aca="false">IF(OR(G28="",H28=""),"",H28-G28)</f>
         <v/>
       </c>
-      <c r="J28" s="69"/>
-      <c r="K28" s="69"/>
-      <c r="L28" s="68"/>
-      <c r="M28" s="69"/>
-      <c r="N28" s="77"/>
+      <c r="J28" s="73"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="72"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="81"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="24" t="s">
-        <v>744</v>
+        <v>885</v>
       </c>
       <c r="M30" s="21" t="str">
         <f aca="false">COUNTA(B5:B28)&amp;" مبادرة"</f>
@@ -4929,7 +6057,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4955,7 +6083,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>745</v>
+        <v>886</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4974,7 +6102,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>746</v>
+        <v>887</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4993,63 +6121,63 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>747</v>
+        <v>888</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>748</v>
+        <v>889</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>749</v>
+        <v>890</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>750</v>
+        <v>891</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>751</v>
+        <v>892</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>752</v>
+        <v>893</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>753</v>
+        <v>894</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>754</v>
+        <v>895</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>755</v>
+        <v>896</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>756</v>
+        <v>897</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>757</v>
+        <v>898</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>758</v>
+        <v>899</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>759</v>
+        <v>900</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>760</v>
+        <v>901</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>761</v>
+        <v>902</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>762</v>
+        <v>903</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>763</v>
+        <v>904</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E4" s="21" t="n">
         <v>181</v>
@@ -5067,7 +6195,7 @@
       <c r="I4" s="28" t="n">
         <v>23493282</v>
       </c>
-      <c r="J4" s="66" t="n">
+      <c r="J4" s="70" t="n">
         <v>64.69</v>
       </c>
       <c r="K4" s="57" t="n">
@@ -5083,21 +6211,21 @@
         <v>0.281</v>
       </c>
       <c r="O4" s="21" t="s">
-        <v>766</v>
+        <v>907</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>767</v>
+        <v>908</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>768</v>
+        <v>909</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>769</v>
+        <v>910</v>
       </c>
       <c r="E5" s="21" t="n">
         <v>91</v>
@@ -5115,10 +6243,10 @@
       <c r="I5" s="28" t="n">
         <v>8841940</v>
       </c>
-      <c r="J5" s="66" t="n">
+      <c r="J5" s="70" t="n">
         <v>61.72</v>
       </c>
-      <c r="K5" s="78" t="n">
+      <c r="K5" s="82" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="45" t="n">
@@ -5131,21 +6259,21 @@
         <v>0</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>770</v>
+        <v>911</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>771</v>
+        <v>912</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>772</v>
+        <v>913</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>773</v>
+        <v>914</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E6" s="21" t="n">
         <v>91</v>
@@ -5163,10 +6291,10 @@
       <c r="I6" s="28" t="n">
         <v>7467484</v>
       </c>
-      <c r="J6" s="66" t="n">
+      <c r="J6" s="70" t="n">
         <v>80.21</v>
       </c>
-      <c r="K6" s="78" t="n">
+      <c r="K6" s="82" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="45" t="n">
@@ -5179,21 +6307,21 @@
         <v>0.344</v>
       </c>
       <c r="O6" s="21" t="s">
-        <v>774</v>
+        <v>915</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>775</v>
+        <v>916</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>776</v>
+        <v>917</v>
       </c>
       <c r="C7" s="21" t="s">
         <v>345</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>769</v>
+        <v>910</v>
       </c>
       <c r="E7" s="21" t="n">
         <v>176</v>
@@ -5211,10 +6339,10 @@
       <c r="I7" s="28" t="n">
         <v>14552120</v>
       </c>
-      <c r="J7" s="66" t="n">
+      <c r="J7" s="70" t="n">
         <v>84.21</v>
       </c>
-      <c r="K7" s="79" t="n">
+      <c r="K7" s="83" t="n">
         <v>0.273</v>
       </c>
       <c r="L7" s="45" t="n">
@@ -5227,21 +6355,21 @@
         <v>0.641</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>777</v>
+        <v>918</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>778</v>
+        <v>919</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>779</v>
+        <v>920</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E8" s="21" t="n">
         <v>180</v>
@@ -5259,7 +6387,7 @@
       <c r="I8" s="28" t="n">
         <v>2916708</v>
       </c>
-      <c r="J8" s="66" t="n">
+      <c r="J8" s="70" t="n">
         <v>48.35</v>
       </c>
       <c r="K8" s="57" t="n">
@@ -5275,21 +6403,21 @@
         <v>0.134</v>
       </c>
       <c r="O8" s="21" t="s">
-        <v>780</v>
+        <v>921</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>781</v>
+        <v>922</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>782</v>
+        <v>923</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>773</v>
+        <v>914</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>783</v>
+        <v>924</v>
       </c>
       <c r="E9" s="21" t="n">
         <v>55</v>
@@ -5307,10 +6435,10 @@
       <c r="I9" s="28" t="n">
         <v>2916316</v>
       </c>
-      <c r="J9" s="66" t="n">
+      <c r="J9" s="70" t="n">
         <v>65.82</v>
       </c>
-      <c r="K9" s="78" t="n">
+      <c r="K9" s="82" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="45" t="n">
@@ -5323,21 +6451,21 @@
         <v>0.309</v>
       </c>
       <c r="O9" s="21" t="s">
-        <v>766</v>
+        <v>907</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>784</v>
+        <v>925</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>785</v>
+        <v>926</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>773</v>
+        <v>914</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E10" s="21" t="n">
         <v>63</v>
@@ -5355,10 +6483,10 @@
       <c r="I10" s="28" t="n">
         <v>2831981</v>
       </c>
-      <c r="J10" s="66" t="n">
+      <c r="J10" s="70" t="n">
         <v>59.14</v>
       </c>
-      <c r="K10" s="78" t="n">
+      <c r="K10" s="82" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="45" t="n">
@@ -5371,21 +6499,21 @@
         <v>0.006</v>
       </c>
       <c r="O10" s="21" t="s">
-        <v>774</v>
+        <v>915</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>786</v>
+        <v>927</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>787</v>
+        <v>928</v>
       </c>
       <c r="C11" s="21" t="s">
         <v>345</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E11" s="21" t="n">
         <v>65</v>
@@ -5403,10 +6531,10 @@
       <c r="I11" s="28" t="n">
         <v>2931550</v>
       </c>
-      <c r="J11" s="66" t="n">
+      <c r="J11" s="70" t="n">
         <v>49.84</v>
       </c>
-      <c r="K11" s="78" t="n">
+      <c r="K11" s="82" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="45" t="n">
@@ -5419,21 +6547,21 @@
         <v>0</v>
       </c>
       <c r="O11" s="21" t="s">
-        <v>774</v>
+        <v>915</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>788</v>
+        <v>929</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>789</v>
+        <v>930</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E12" s="21" t="n">
         <v>181</v>
@@ -5451,7 +6579,7 @@
       <c r="I12" s="28" t="n">
         <v>8679738</v>
       </c>
-      <c r="J12" s="66" t="n">
+      <c r="J12" s="70" t="n">
         <v>59.34</v>
       </c>
       <c r="K12" s="57" t="n">
@@ -5467,21 +6595,21 @@
         <v>0.277</v>
       </c>
       <c r="O12" s="21" t="s">
-        <v>774</v>
+        <v>915</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>790</v>
+        <v>931</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>791</v>
+        <v>932</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>773</v>
+        <v>914</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>783</v>
+        <v>924</v>
       </c>
       <c r="E13" s="21" t="n">
         <v>181</v>
@@ -5499,7 +6627,7 @@
       <c r="I13" s="28" t="n">
         <v>7729931</v>
       </c>
-      <c r="J13" s="66" t="n">
+      <c r="J13" s="70" t="n">
         <v>67.66</v>
       </c>
       <c r="K13" s="57" t="n">
@@ -5515,21 +6643,21 @@
         <v>0.082</v>
       </c>
       <c r="O13" s="21" t="s">
-        <v>774</v>
+        <v>915</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>792</v>
+        <v>933</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>793</v>
+        <v>934</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E14" s="21" t="n">
         <v>181</v>
@@ -5547,7 +6675,7 @@
       <c r="I14" s="28" t="n">
         <v>2676944</v>
       </c>
-      <c r="J14" s="66" t="n">
+      <c r="J14" s="70" t="n">
         <v>59.47</v>
       </c>
       <c r="K14" s="45" t="n">
@@ -5563,21 +6691,21 @@
         <v>0.231</v>
       </c>
       <c r="O14" s="21" t="s">
-        <v>774</v>
+        <v>915</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>794</v>
+        <v>935</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>795</v>
+        <v>936</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>769</v>
+        <v>910</v>
       </c>
       <c r="E15" s="21" t="n">
         <v>181</v>
@@ -5595,7 +6723,7 @@
       <c r="I15" s="28" t="n">
         <v>7806709</v>
       </c>
-      <c r="J15" s="66" t="n">
+      <c r="J15" s="70" t="n">
         <v>63.18</v>
       </c>
       <c r="K15" s="57" t="n">
@@ -5611,21 +6739,21 @@
         <v>0.458</v>
       </c>
       <c r="O15" s="21" t="s">
-        <v>780</v>
+        <v>921</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>796</v>
+        <v>937</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>797</v>
+        <v>938</v>
       </c>
       <c r="C16" s="21" t="s">
         <v>350</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E16" s="21" t="n">
         <v>181</v>
@@ -5643,10 +6771,10 @@
       <c r="I16" s="28" t="n">
         <v>4791911</v>
       </c>
-      <c r="J16" s="66" t="n">
+      <c r="J16" s="70" t="n">
         <v>74.3</v>
       </c>
-      <c r="K16" s="79" t="n">
+      <c r="K16" s="83" t="n">
         <v>0.151</v>
       </c>
       <c r="L16" s="45" t="n">
@@ -5659,21 +6787,21 @@
         <v>0.076</v>
       </c>
       <c r="O16" s="21" t="s">
-        <v>774</v>
+        <v>915</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>798</v>
+        <v>939</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>799</v>
+        <v>940</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>773</v>
+        <v>914</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E17" s="21" t="n">
         <v>57</v>
@@ -5691,10 +6819,10 @@
       <c r="I17" s="28" t="n">
         <v>2078856</v>
       </c>
-      <c r="J17" s="66" t="n">
+      <c r="J17" s="70" t="n">
         <v>55.76</v>
       </c>
-      <c r="K17" s="78" t="n">
+      <c r="K17" s="82" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="45" t="n">
@@ -5707,21 +6835,21 @@
         <v>0</v>
       </c>
       <c r="O17" s="21" t="s">
-        <v>766</v>
+        <v>907</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>800</v>
+        <v>941</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>801</v>
+        <v>942</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E18" s="21" t="n">
         <v>181</v>
@@ -5739,7 +6867,7 @@
       <c r="I18" s="28" t="n">
         <v>6570004</v>
       </c>
-      <c r="J18" s="66" t="n">
+      <c r="J18" s="70" t="n">
         <v>43.71</v>
       </c>
       <c r="K18" s="45" t="n">
@@ -5755,21 +6883,21 @@
         <v>0</v>
       </c>
       <c r="O18" s="21" t="s">
-        <v>766</v>
+        <v>907</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>802</v>
+        <v>943</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>803</v>
+        <v>944</v>
       </c>
       <c r="C19" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>804</v>
+        <v>945</v>
       </c>
       <c r="E19" s="21" t="n">
         <v>130</v>
@@ -5787,10 +6915,10 @@
       <c r="I19" s="28" t="n">
         <v>4445436</v>
       </c>
-      <c r="J19" s="66" t="n">
+      <c r="J19" s="70" t="n">
         <v>42.14</v>
       </c>
-      <c r="K19" s="79" t="n">
+      <c r="K19" s="83" t="n">
         <v>0.275</v>
       </c>
       <c r="L19" s="45" t="n">
@@ -5803,21 +6931,21 @@
         <v>0.048</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>777</v>
+        <v>918</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>805</v>
+        <v>946</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>806</v>
+        <v>947</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>807</v>
+        <v>948</v>
       </c>
       <c r="E20" s="21" t="n">
         <v>70</v>
@@ -5835,10 +6963,10 @@
       <c r="I20" s="28" t="n">
         <v>2229579</v>
       </c>
-      <c r="J20" s="66" t="n">
+      <c r="J20" s="70" t="n">
         <v>43.6</v>
       </c>
-      <c r="K20" s="78" t="n">
+      <c r="K20" s="82" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="45" t="n">
@@ -5851,21 +6979,21 @@
         <v>0</v>
       </c>
       <c r="O20" s="21" t="s">
-        <v>770</v>
+        <v>911</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>808</v>
+        <v>949</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>809</v>
+        <v>950</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E21" s="21" t="n">
         <v>181</v>
@@ -5883,7 +7011,7 @@
       <c r="I21" s="28" t="n">
         <v>5504980</v>
       </c>
-      <c r="J21" s="66" t="n">
+      <c r="J21" s="70" t="n">
         <v>43.52</v>
       </c>
       <c r="K21" s="57" t="n">
@@ -5899,21 +7027,21 @@
         <v>0</v>
       </c>
       <c r="O21" s="21" t="s">
-        <v>774</v>
+        <v>915</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>810</v>
+        <v>951</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>811</v>
+        <v>952</v>
       </c>
       <c r="C22" s="21" t="s">
         <v>345</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E22" s="21" t="n">
         <v>147</v>
@@ -5931,10 +7059,10 @@
       <c r="I22" s="28" t="n">
         <v>4722403</v>
       </c>
-      <c r="J22" s="66" t="n">
+      <c r="J22" s="70" t="n">
         <v>49.88</v>
       </c>
-      <c r="K22" s="79" t="n">
+      <c r="K22" s="83" t="n">
         <v>0.068</v>
       </c>
       <c r="L22" s="45" t="n">
@@ -5947,21 +7075,21 @@
         <v>0.329</v>
       </c>
       <c r="O22" s="21" t="s">
-        <v>780</v>
+        <v>921</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>812</v>
+        <v>953</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>813</v>
+        <v>954</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E23" s="21" t="n">
         <v>181</v>
@@ -5979,10 +7107,10 @@
       <c r="I23" s="28" t="n">
         <v>4924931</v>
       </c>
-      <c r="J23" s="66" t="n">
+      <c r="J23" s="70" t="n">
         <v>47.68</v>
       </c>
-      <c r="K23" s="79" t="n">
+      <c r="K23" s="83" t="n">
         <v>0.069</v>
       </c>
       <c r="L23" s="45" t="n">
@@ -5995,21 +7123,21 @@
         <v>0</v>
       </c>
       <c r="O23" s="21" t="s">
-        <v>774</v>
+        <v>915</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>814</v>
+        <v>955</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>815</v>
+        <v>956</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E24" s="21" t="n">
         <v>181</v>
@@ -6027,7 +7155,7 @@
       <c r="I24" s="28" t="n">
         <v>4740020</v>
       </c>
-      <c r="J24" s="66" t="n">
+      <c r="J24" s="70" t="n">
         <v>43.42</v>
       </c>
       <c r="K24" s="45" t="n">
@@ -6043,21 +7171,21 @@
         <v>0</v>
       </c>
       <c r="O24" s="21" t="s">
-        <v>774</v>
+        <v>915</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>816</v>
+        <v>957</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>817</v>
+        <v>958</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>773</v>
+        <v>914</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>783</v>
+        <v>924</v>
       </c>
       <c r="E25" s="21" t="n">
         <v>181</v>
@@ -6075,10 +7203,10 @@
       <c r="I25" s="28" t="n">
         <v>4771577</v>
       </c>
-      <c r="J25" s="66" t="n">
+      <c r="J25" s="70" t="n">
         <v>51.68</v>
       </c>
-      <c r="K25" s="79" t="n">
+      <c r="K25" s="83" t="n">
         <v>0.177</v>
       </c>
       <c r="L25" s="45" t="n">
@@ -6091,21 +7219,21 @@
         <v>0.058</v>
       </c>
       <c r="O25" s="21" t="s">
-        <v>766</v>
+        <v>907</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>818</v>
+        <v>959</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>819</v>
+        <v>960</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>807</v>
+        <v>948</v>
       </c>
       <c r="E26" s="21" t="n">
         <v>181</v>
@@ -6123,7 +7251,7 @@
       <c r="I26" s="28" t="n">
         <v>4933540</v>
       </c>
-      <c r="J26" s="66" t="n">
+      <c r="J26" s="70" t="n">
         <v>51.76</v>
       </c>
       <c r="K26" s="45" t="n">
@@ -6139,21 +7267,21 @@
         <v>0.276</v>
       </c>
       <c r="O26" s="21" t="s">
-        <v>766</v>
+        <v>907</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>820</v>
+        <v>961</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>821</v>
+        <v>962</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>773</v>
+        <v>914</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>783</v>
+        <v>924</v>
       </c>
       <c r="E27" s="21" t="n">
         <v>181</v>
@@ -6171,10 +7299,10 @@
       <c r="I27" s="28" t="n">
         <v>4643058</v>
       </c>
-      <c r="J27" s="66" t="n">
+      <c r="J27" s="70" t="n">
         <v>66.28</v>
       </c>
-      <c r="K27" s="79" t="n">
+      <c r="K27" s="83" t="n">
         <v>0.083</v>
       </c>
       <c r="L27" s="45" t="n">
@@ -6187,21 +7315,21 @@
         <v>0.27</v>
       </c>
       <c r="O27" s="21" t="s">
-        <v>822</v>
+        <v>963</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>823</v>
+        <v>964</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>824</v>
+        <v>965</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>769</v>
+        <v>910</v>
       </c>
       <c r="E28" s="21" t="n">
         <v>111</v>
@@ -6219,10 +7347,10 @@
       <c r="I28" s="28" t="n">
         <v>2834084</v>
       </c>
-      <c r="J28" s="66" t="n">
+      <c r="J28" s="70" t="n">
         <v>77.81</v>
       </c>
-      <c r="K28" s="78" t="n">
+      <c r="K28" s="82" t="n">
         <v>-0.033</v>
       </c>
       <c r="L28" s="45" t="n">
@@ -6235,21 +7363,21 @@
         <v>0.349</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>777</v>
+        <v>918</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>825</v>
+        <v>966</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>826</v>
+        <v>967</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>807</v>
+        <v>948</v>
       </c>
       <c r="E29" s="21" t="n">
         <v>181</v>
@@ -6267,7 +7395,7 @@
       <c r="I29" s="28" t="n">
         <v>4558563</v>
       </c>
-      <c r="J29" s="66" t="n">
+      <c r="J29" s="70" t="n">
         <v>64.44</v>
       </c>
       <c r="K29" s="45" t="n">
@@ -6283,21 +7411,21 @@
         <v>0.321</v>
       </c>
       <c r="O29" s="21" t="s">
-        <v>766</v>
+        <v>907</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>827</v>
+        <v>968</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>828</v>
+        <v>969</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E30" s="21" t="n">
         <v>92</v>
@@ -6315,10 +7443,10 @@
       <c r="I30" s="28" t="n">
         <v>2127665</v>
       </c>
-      <c r="J30" s="66" t="n">
+      <c r="J30" s="70" t="n">
         <v>48.52</v>
       </c>
-      <c r="K30" s="78" t="n">
+      <c r="K30" s="82" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="45" t="n">
@@ -6331,21 +7459,21 @@
         <v>0.176</v>
       </c>
       <c r="O30" s="21" t="s">
-        <v>766</v>
+        <v>907</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>829</v>
+        <v>970</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>830</v>
+        <v>971</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>356</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>804</v>
+        <v>945</v>
       </c>
       <c r="E31" s="21" t="n">
         <v>181</v>
@@ -6363,10 +7491,10 @@
       <c r="I31" s="28" t="n">
         <v>3884721</v>
       </c>
-      <c r="J31" s="66" t="n">
+      <c r="J31" s="70" t="n">
         <v>54.76</v>
       </c>
-      <c r="K31" s="79" t="n">
+      <c r="K31" s="83" t="n">
         <v>0.186</v>
       </c>
       <c r="L31" s="45" t="n">
@@ -6379,21 +7507,21 @@
         <v>0.082</v>
       </c>
       <c r="O31" s="21" t="s">
-        <v>774</v>
+        <v>915</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>831</v>
+        <v>972</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>832</v>
+        <v>973</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>833</v>
+        <v>974</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>804</v>
+        <v>945</v>
       </c>
       <c r="E32" s="21" t="n">
         <v>69</v>
@@ -6411,10 +7539,10 @@
       <c r="I32" s="28" t="n">
         <v>1471112</v>
       </c>
-      <c r="J32" s="66" t="n">
+      <c r="J32" s="70" t="n">
         <v>49.67</v>
       </c>
-      <c r="K32" s="78" t="n">
+      <c r="K32" s="82" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="45" t="n">
@@ -6427,21 +7555,21 @@
         <v>0.103</v>
       </c>
       <c r="O32" s="20" t="s">
-        <v>777</v>
+        <v>918</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>834</v>
+        <v>975</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>835</v>
+        <v>976</v>
       </c>
       <c r="C33" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E33" s="21" t="n">
         <v>181</v>
@@ -6459,10 +7587,10 @@
       <c r="I33" s="28" t="n">
         <v>3774634</v>
       </c>
-      <c r="J33" s="66" t="n">
+      <c r="J33" s="70" t="n">
         <v>50.81</v>
       </c>
-      <c r="K33" s="79" t="n">
+      <c r="K33" s="83" t="n">
         <v>0.18</v>
       </c>
       <c r="L33" s="45" t="n">
@@ -6475,21 +7603,21 @@
         <v>0.023</v>
       </c>
       <c r="O33" s="21" t="s">
-        <v>766</v>
+        <v>907</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>836</v>
+        <v>977</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>837</v>
+        <v>978</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>769</v>
+        <v>910</v>
       </c>
       <c r="E34" s="21" t="n">
         <v>181</v>
@@ -6507,7 +7635,7 @@
       <c r="I34" s="28" t="n">
         <v>4263083</v>
       </c>
-      <c r="J34" s="66" t="n">
+      <c r="J34" s="70" t="n">
         <v>110.06</v>
       </c>
       <c r="K34" s="57" t="n">
@@ -6523,21 +7651,21 @@
         <v>0.559</v>
       </c>
       <c r="O34" s="21" t="s">
-        <v>822</v>
+        <v>963</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>838</v>
+        <v>979</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>839</v>
+        <v>980</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E35" s="21" t="n">
         <v>181</v>
@@ -6555,7 +7683,7 @@
       <c r="I35" s="28" t="n">
         <v>3471225</v>
       </c>
-      <c r="J35" s="66" t="n">
+      <c r="J35" s="70" t="n">
         <v>47.35</v>
       </c>
       <c r="K35" s="57" t="n">
@@ -6571,21 +7699,21 @@
         <v>0</v>
       </c>
       <c r="O35" s="21" t="s">
-        <v>774</v>
+        <v>915</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>840</v>
+        <v>981</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>841</v>
+        <v>982</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>783</v>
+        <v>924</v>
       </c>
       <c r="E36" s="21" t="n">
         <v>181</v>
@@ -6603,7 +7731,7 @@
       <c r="I36" s="28" t="n">
         <v>3512113</v>
       </c>
-      <c r="J36" s="66" t="n">
+      <c r="J36" s="70" t="n">
         <v>45.88</v>
       </c>
       <c r="K36" s="57" t="n">
@@ -6619,21 +7747,21 @@
         <v>0.115</v>
       </c>
       <c r="O36" s="21" t="s">
-        <v>780</v>
+        <v>921</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>842</v>
+        <v>983</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>843</v>
+        <v>984</v>
       </c>
       <c r="C37" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>804</v>
+        <v>945</v>
       </c>
       <c r="E37" s="21" t="n">
         <v>26</v>
@@ -6651,10 +7779,10 @@
       <c r="I37" s="28" t="n">
         <v>486162</v>
       </c>
-      <c r="J37" s="66" t="n">
+      <c r="J37" s="70" t="n">
         <v>33.35</v>
       </c>
-      <c r="K37" s="78" t="n">
+      <c r="K37" s="82" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="45" t="n">
@@ -6672,16 +7800,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
-        <v>844</v>
+        <v>985</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>845</v>
+        <v>986</v>
       </c>
       <c r="C38" s="21" t="s">
         <v>345</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E38" s="21" t="n">
         <v>181</v>
@@ -6699,10 +7827,10 @@
       <c r="I38" s="28" t="n">
         <v>3406904</v>
       </c>
-      <c r="J38" s="66" t="n">
+      <c r="J38" s="70" t="n">
         <v>43.04</v>
       </c>
-      <c r="K38" s="79" t="n">
+      <c r="K38" s="83" t="n">
         <v>0.083</v>
       </c>
       <c r="L38" s="45" t="n">
@@ -6715,21 +7843,21 @@
         <v>0.167</v>
       </c>
       <c r="O38" s="21" t="s">
-        <v>766</v>
+        <v>907</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="21" t="s">
-        <v>846</v>
+        <v>987</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>847</v>
+        <v>988</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>769</v>
+        <v>910</v>
       </c>
       <c r="E39" s="21" t="n">
         <v>181</v>
@@ -6747,7 +7875,7 @@
       <c r="I39" s="28" t="n">
         <v>3076219</v>
       </c>
-      <c r="J39" s="66" t="n">
+      <c r="J39" s="70" t="n">
         <v>69.64</v>
       </c>
       <c r="K39" s="57" t="n">
@@ -6763,21 +7891,21 @@
         <v>0.106</v>
       </c>
       <c r="O39" s="21" t="s">
-        <v>766</v>
+        <v>907</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="21" t="s">
-        <v>848</v>
+        <v>989</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>849</v>
+        <v>990</v>
       </c>
       <c r="C40" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E40" s="21" t="n">
         <v>181</v>
@@ -6795,7 +7923,7 @@
       <c r="I40" s="28" t="n">
         <v>3314721</v>
       </c>
-      <c r="J40" s="66" t="n">
+      <c r="J40" s="70" t="n">
         <v>69.44</v>
       </c>
       <c r="K40" s="45" t="n">
@@ -6811,21 +7939,21 @@
         <v>0.373</v>
       </c>
       <c r="O40" s="21" t="s">
-        <v>766</v>
+        <v>907</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="21" t="s">
-        <v>850</v>
+        <v>991</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>851</v>
+        <v>992</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E41" s="21" t="n">
         <v>181</v>
@@ -6843,7 +7971,7 @@
       <c r="I41" s="28" t="n">
         <v>2925368</v>
       </c>
-      <c r="J41" s="66" t="n">
+      <c r="J41" s="70" t="n">
         <v>45.21</v>
       </c>
       <c r="K41" s="57" t="n">
@@ -6859,21 +7987,21 @@
         <v>0</v>
       </c>
       <c r="O41" s="21" t="s">
-        <v>766</v>
+        <v>907</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="21" t="s">
-        <v>852</v>
+        <v>993</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>853</v>
+        <v>994</v>
       </c>
       <c r="C42" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>804</v>
+        <v>945</v>
       </c>
       <c r="E42" s="21" t="n">
         <v>68</v>
@@ -6891,10 +8019,10 @@
       <c r="I42" s="28" t="n">
         <v>1114635</v>
       </c>
-      <c r="J42" s="66" t="n">
+      <c r="J42" s="70" t="n">
         <v>45.6</v>
       </c>
-      <c r="K42" s="78" t="n">
+      <c r="K42" s="82" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="45" t="n">
@@ -6907,21 +8035,21 @@
         <v>0.056</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>777</v>
+        <v>918</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
-        <v>854</v>
+        <v>995</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>855</v>
+        <v>996</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>773</v>
+        <v>914</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>807</v>
+        <v>948</v>
       </c>
       <c r="E43" s="21" t="n">
         <v>181</v>
@@ -6939,10 +8067,10 @@
       <c r="I43" s="28" t="n">
         <v>2839338</v>
       </c>
-      <c r="J43" s="66" t="n">
+      <c r="J43" s="70" t="n">
         <v>50.86</v>
       </c>
-      <c r="K43" s="79" t="n">
+      <c r="K43" s="83" t="n">
         <v>0.082</v>
       </c>
       <c r="L43" s="45" t="n">
@@ -6955,21 +8083,21 @@
         <v>0.077</v>
       </c>
       <c r="O43" s="21" t="s">
-        <v>822</v>
+        <v>963</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
-        <v>856</v>
+        <v>997</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>857</v>
+        <v>998</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>858</v>
+        <v>999</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E44" s="21" t="n">
         <v>181</v>
@@ -6987,10 +8115,10 @@
       <c r="I44" s="28" t="n">
         <v>2759664</v>
       </c>
-      <c r="J44" s="66" t="n">
+      <c r="J44" s="70" t="n">
         <v>56.84</v>
       </c>
-      <c r="K44" s="79" t="n">
+      <c r="K44" s="83" t="n">
         <v>0.327</v>
       </c>
       <c r="L44" s="45" t="n">
@@ -7003,21 +8131,21 @@
         <v>0.066</v>
       </c>
       <c r="O44" s="20" t="s">
-        <v>777</v>
+        <v>918</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="21" t="s">
-        <v>859</v>
+        <v>1000</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>860</v>
+        <v>1001</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>861</v>
+        <v>1002</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>804</v>
+        <v>945</v>
       </c>
       <c r="E45" s="21" t="n">
         <v>181</v>
@@ -7035,7 +8163,7 @@
       <c r="I45" s="28" t="n">
         <v>2940822</v>
       </c>
-      <c r="J45" s="66" t="n">
+      <c r="J45" s="70" t="n">
         <v>74.93</v>
       </c>
       <c r="K45" s="45" t="n">
@@ -7051,21 +8179,21 @@
         <v>0.392</v>
       </c>
       <c r="O45" s="20" t="s">
-        <v>777</v>
+        <v>918</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="21" t="s">
-        <v>862</v>
+        <v>1003</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>863</v>
+        <v>1004</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E46" s="21" t="n">
         <v>181</v>
@@ -7083,7 +8211,7 @@
       <c r="I46" s="28" t="n">
         <v>2694118</v>
       </c>
-      <c r="J46" s="66" t="n">
+      <c r="J46" s="70" t="n">
         <v>53.94</v>
       </c>
       <c r="K46" s="57" t="n">
@@ -7099,21 +8227,21 @@
         <v>0.236</v>
       </c>
       <c r="O46" s="21" t="s">
-        <v>774</v>
+        <v>915</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="21" t="s">
-        <v>864</v>
+        <v>1005</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>865</v>
+        <v>1006</v>
       </c>
       <c r="C47" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>866</v>
+        <v>1007</v>
       </c>
       <c r="E47" s="21" t="n">
         <v>181</v>
@@ -7131,7 +8259,7 @@
       <c r="I47" s="28" t="n">
         <v>2650896</v>
       </c>
-      <c r="J47" s="66" t="n">
+      <c r="J47" s="70" t="n">
         <v>48.6</v>
       </c>
       <c r="K47" s="45" t="n">
@@ -7147,21 +8275,21 @@
         <v>0.184</v>
       </c>
       <c r="O47" s="21" t="s">
-        <v>822</v>
+        <v>963</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="21" t="s">
-        <v>867</v>
+        <v>1008</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>868</v>
+        <v>1009</v>
       </c>
       <c r="C48" s="21" t="s">
         <v>356</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>804</v>
+        <v>945</v>
       </c>
       <c r="E48" s="21" t="n">
         <v>181</v>
@@ -7179,10 +8307,10 @@
       <c r="I48" s="28" t="n">
         <v>2153145</v>
       </c>
-      <c r="J48" s="66" t="n">
+      <c r="J48" s="70" t="n">
         <v>57.15</v>
       </c>
-      <c r="K48" s="79" t="n">
+      <c r="K48" s="83" t="n">
         <v>0.064</v>
       </c>
       <c r="L48" s="45" t="n">
@@ -7195,21 +8323,21 @@
         <v>0</v>
       </c>
       <c r="O48" s="21" t="s">
-        <v>766</v>
+        <v>907</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="21" t="s">
-        <v>869</v>
+        <v>1010</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>870</v>
+        <v>1011</v>
       </c>
       <c r="C49" s="21" t="s">
         <v>356</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>807</v>
+        <v>948</v>
       </c>
       <c r="E49" s="21" t="n">
         <v>181</v>
@@ -7227,10 +8355,10 @@
       <c r="I49" s="28" t="n">
         <v>2133587</v>
       </c>
-      <c r="J49" s="66" t="n">
+      <c r="J49" s="70" t="n">
         <v>62.82</v>
       </c>
-      <c r="K49" s="79" t="n">
+      <c r="K49" s="83" t="n">
         <v>0.256</v>
       </c>
       <c r="L49" s="45" t="n">
@@ -7243,21 +8371,21 @@
         <v>0.201</v>
       </c>
       <c r="O49" s="21" t="s">
-        <v>766</v>
+        <v>907</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="21" t="s">
-        <v>871</v>
+        <v>1012</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>872</v>
+        <v>1013</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E50" s="21" t="n">
         <v>181</v>
@@ -7275,7 +8403,7 @@
       <c r="I50" s="28" t="n">
         <v>1912969</v>
       </c>
-      <c r="J50" s="66" t="n">
+      <c r="J50" s="70" t="n">
         <v>52.46</v>
       </c>
       <c r="K50" s="57" t="n">
@@ -7291,21 +8419,21 @@
         <v>0</v>
       </c>
       <c r="O50" s="21" t="s">
-        <v>774</v>
+        <v>915</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="21" t="s">
-        <v>873</v>
+        <v>1014</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>874</v>
+        <v>1015</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>764</v>
+        <v>905</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E51" s="21" t="n">
         <v>56</v>
@@ -7323,10 +8451,10 @@
       <c r="I51" s="28" t="n">
         <v>568922</v>
       </c>
-      <c r="J51" s="66" t="n">
+      <c r="J51" s="70" t="n">
         <v>50.9</v>
       </c>
-      <c r="K51" s="78" t="n">
+      <c r="K51" s="82" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="45" t="n">
@@ -7344,16 +8472,16 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="21" t="s">
-        <v>875</v>
+        <v>1016</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>876</v>
+        <v>1017</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>773</v>
+        <v>914</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>807</v>
+        <v>948</v>
       </c>
       <c r="E52" s="21" t="n">
         <v>181</v>
@@ -7371,10 +8499,10 @@
       <c r="I52" s="28" t="n">
         <v>1672588</v>
       </c>
-      <c r="J52" s="66" t="n">
+      <c r="J52" s="70" t="n">
         <v>45.95</v>
       </c>
-      <c r="K52" s="79" t="n">
+      <c r="K52" s="83" t="n">
         <v>0.137</v>
       </c>
       <c r="L52" s="45" t="n">
@@ -7387,21 +8515,21 @@
         <v>0.017</v>
       </c>
       <c r="O52" s="21" t="s">
-        <v>780</v>
+        <v>921</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="21" t="s">
-        <v>877</v>
+        <v>1018</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>878</v>
+        <v>1019</v>
       </c>
       <c r="C53" s="21" t="s">
         <v>345</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E53" s="21" t="n">
         <v>181</v>
@@ -7419,7 +8547,7 @@
       <c r="I53" s="28" t="n">
         <v>1601535</v>
       </c>
-      <c r="J53" s="66" t="n">
+      <c r="J53" s="70" t="n">
         <v>55.38</v>
       </c>
       <c r="K53" s="45" t="n">
@@ -7435,21 +8563,21 @@
         <v>0.292</v>
       </c>
       <c r="O53" s="21" t="s">
-        <v>780</v>
+        <v>921</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="21" t="s">
-        <v>879</v>
+        <v>1020</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>880</v>
+        <v>1021</v>
       </c>
       <c r="C54" s="21" t="s">
         <v>347</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>804</v>
+        <v>945</v>
       </c>
       <c r="E54" s="21" t="n">
         <v>181</v>
@@ -7467,7 +8595,7 @@
       <c r="I54" s="28" t="n">
         <v>1431054</v>
       </c>
-      <c r="J54" s="66" t="n">
+      <c r="J54" s="70" t="n">
         <v>53.68</v>
       </c>
       <c r="K54" s="45" t="n">
@@ -7483,21 +8611,21 @@
         <v>0.077</v>
       </c>
       <c r="O54" s="21" t="s">
-        <v>766</v>
+        <v>907</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="21" t="s">
-        <v>881</v>
+        <v>1022</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>882</v>
+        <v>1023</v>
       </c>
       <c r="C55" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>807</v>
+        <v>948</v>
       </c>
       <c r="E55" s="21" t="n">
         <v>181</v>
@@ -7515,10 +8643,10 @@
       <c r="I55" s="28" t="n">
         <v>1262094</v>
       </c>
-      <c r="J55" s="66" t="n">
+      <c r="J55" s="70" t="n">
         <v>53.3</v>
       </c>
-      <c r="K55" s="79" t="n">
+      <c r="K55" s="83" t="n">
         <v>0.188</v>
       </c>
       <c r="L55" s="45" t="n">
@@ -7531,21 +8659,21 @@
         <v>0.18</v>
       </c>
       <c r="O55" s="20" t="s">
-        <v>777</v>
+        <v>918</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="21" t="s">
-        <v>883</v>
+        <v>1024</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>884</v>
+        <v>1025</v>
       </c>
       <c r="C56" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>765</v>
+        <v>906</v>
       </c>
       <c r="E56" s="21" t="n">
         <v>181</v>
@@ -7563,10 +8691,10 @@
       <c r="I56" s="28" t="n">
         <v>1204453</v>
       </c>
-      <c r="J56" s="66" t="n">
+      <c r="J56" s="70" t="n">
         <v>34.88</v>
       </c>
-      <c r="K56" s="79" t="n">
+      <c r="K56" s="83" t="n">
         <v>0.06</v>
       </c>
       <c r="L56" s="45" t="n">
@@ -7579,12 +8707,12 @@
         <v>0.194</v>
       </c>
       <c r="O56" s="21" t="s">
-        <v>780</v>
+        <v>921</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="21" t="s">
-        <v>885</v>
+        <v>1026</v>
       </c>
       <c r="B57" s="16" t="s">
         <v>339</v>
@@ -7593,7 +8721,7 @@
         <v>340</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>804</v>
+        <v>945</v>
       </c>
       <c r="E57" s="21" t="n">
         <v>39</v>
@@ -7611,10 +8739,10 @@
       <c r="I57" s="28" t="n">
         <v>206212</v>
       </c>
-      <c r="J57" s="66" t="n">
+      <c r="J57" s="70" t="n">
         <v>57.08</v>
       </c>
-      <c r="K57" s="78" t="n">
+      <c r="K57" s="82" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="45" t="n">
@@ -7627,21 +8755,21 @@
         <v>0.249</v>
       </c>
       <c r="O57" s="20" t="s">
-        <v>777</v>
+        <v>918</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="21" t="s">
-        <v>886</v>
+        <v>1027</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>887</v>
+        <v>1028</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>888</v>
+        <v>1029</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>804</v>
+        <v>945</v>
       </c>
       <c r="E58" s="21" t="n">
         <v>6</v>
@@ -7659,10 +8787,10 @@
       <c r="I58" s="28" t="n">
         <v>21693</v>
       </c>
-      <c r="J58" s="66" t="n">
+      <c r="J58" s="70" t="n">
         <v>49.96</v>
       </c>
-      <c r="K58" s="78" t="n">
+      <c r="K58" s="82" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="45" t="n">
@@ -7675,51 +8803,51 @@
         <v>0.167</v>
       </c>
       <c r="O58" s="20" t="s">
-        <v>777</v>
+        <v>918</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="80" t="s">
-        <v>889</v>
+      <c r="A59" s="84" t="s">
+        <v>1030</v>
       </c>
       <c r="B59" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="F59" s="81" t="n">
+      <c r="F59" s="85" t="n">
         <f aca="false">SUM(F4:F58)</f>
         <v>502415662</v>
       </c>
-      <c r="G59" s="81" t="n">
+      <c r="G59" s="85" t="n">
         <f aca="false">SUM(G4:G58)</f>
         <v>1271395370.83428</v>
       </c>
-      <c r="H59" s="81" t="n">
+      <c r="H59" s="85" t="n">
         <f aca="false">SUM(H4:H58)</f>
         <v>8824895</v>
       </c>
-      <c r="I59" s="81" t="n">
+      <c r="I59" s="85" t="n">
         <f aca="false">SUM(I4:I58)</f>
         <v>219475297</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="82" t="s">
-        <v>890</v>
-      </c>
-      <c r="B61" s="82"/>
-      <c r="C61" s="82"/>
-      <c r="D61" s="82"/>
-      <c r="E61" s="82"/>
-      <c r="F61" s="82"/>
-      <c r="G61" s="82"/>
-      <c r="H61" s="82"/>
-      <c r="I61" s="82"/>
-      <c r="J61" s="82"/>
-      <c r="K61" s="82"/>
-      <c r="L61" s="82"/>
-      <c r="M61" s="82"/>
-      <c r="N61" s="82"/>
-      <c r="O61" s="82"/>
+      <c r="A61" s="86" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B61" s="86"/>
+      <c r="C61" s="86"/>
+      <c r="D61" s="86"/>
+      <c r="E61" s="86"/>
+      <c r="F61" s="86"/>
+      <c r="G61" s="86"/>
+      <c r="H61" s="86"/>
+      <c r="I61" s="86"/>
+      <c r="J61" s="86"/>
+      <c r="K61" s="86"/>
+      <c r="L61" s="86"/>
+      <c r="M61" s="86"/>
+      <c r="N61" s="86"/>
+      <c r="O61" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -12240,23 +13368,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12271,12 +13394,6 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -12290,622 +13407,737 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="15" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="52" t="s">
+        <v>666</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>667</v>
+      </c>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>666</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>667</v>
-      </c>
-      <c r="G3" s="15" t="s">
+      <c r="B4" s="15" t="s">
         <v>668</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="C4" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="I3" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="J3" s="15" t="s">
+      <c r="D4" s="15" t="s">
         <v>670</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="E4" s="15" t="s">
         <v>671</v>
       </c>
-      <c r="L3" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="M3" s="15" t="s">
+      <c r="F4" s="15" t="s">
         <v>672</v>
       </c>
-      <c r="N3" s="15" t="s">
+      <c r="G4" s="15" t="s">
         <v>673</v>
       </c>
-      <c r="O3" s="15" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="63" t="s">
+      <c r="H4" s="15" t="s">
         <v>674</v>
       </c>
-      <c r="B4" s="64" t="s">
+      <c r="I4" s="15" t="s">
         <v>675</v>
       </c>
-      <c r="C4" s="63" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="64" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="63" t="s">
         <v>676</v>
       </c>
-      <c r="E4" s="63" t="n">
+      <c r="B5" s="63"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+    </row>
+    <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>677</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>678</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>679</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>680</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>681</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>682</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>683</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>684</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>685</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>686</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>680</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>687</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>688</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>689</v>
+      </c>
+      <c r="I7" s="21" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>691</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>692</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>693</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>680</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>694</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>695</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>696</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>697</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>698</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>699</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>680</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>694</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>695</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>700</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>701</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>702</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>703</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>704</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>705</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>706</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>707</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="64" t="s">
+        <v>709</v>
+      </c>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+    </row>
+    <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="63" t="s">
-        <v>677</v>
-      </c>
-      <c r="G4" s="64" t="s">
-        <v>678</v>
-      </c>
-      <c r="H4" s="63" t="n">
-        <v>20</v>
-      </c>
-      <c r="I4" s="63" t="n">
-        <f aca="false">IF(H4="","",H4-E4)</f>
+      <c r="B12" s="17" t="s">
+        <v>710</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>711</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>712</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>713</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>714</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>715</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>716</v>
+      </c>
+      <c r="I12" s="21" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>717</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>718</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>719</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>720</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>721</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>722</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>723</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>724</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>725</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>726</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>727</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>728</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>729</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>730</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>731</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>732</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>733</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>734</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>681</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>722</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>735</v>
+      </c>
+      <c r="I15" s="21" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>736</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>737</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>738</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>739</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>694</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>740</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>741</v>
+      </c>
+      <c r="I16" s="21" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="65" t="s">
+        <v>742</v>
+      </c>
+      <c r="B17" s="65"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="65"/>
+      <c r="H17" s="65"/>
+      <c r="I17" s="65"/>
+    </row>
+    <row r="18" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>595</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>743</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>744</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>745</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>746</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>747</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>748</v>
+      </c>
+      <c r="I18" s="23" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>750</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>751</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>752</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>753</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>754</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>755</v>
+      </c>
+      <c r="I19" s="21" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>756</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>757</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>758</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>759</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>760</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>761</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>762</v>
+      </c>
+      <c r="I20" s="23" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="J4" s="65" t="n">
-        <f aca="false">IFERROR(IF(H4="","",(H4-E4)/E4),"")</f>
-        <v>2.33333333333333</v>
-      </c>
-      <c r="K4" s="64" t="s">
-        <v>679</v>
-      </c>
-      <c r="L4" s="63" t="s">
-        <v>75</v>
-      </c>
-      <c r="M4" s="64" t="s">
-        <v>680</v>
-      </c>
-      <c r="N4" s="64" t="s">
+      <c r="B21" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>763</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>764</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>765</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>766</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>767</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>768</v>
+      </c>
+      <c r="I21" s="23" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>770</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>771</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>772</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>773</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>760</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>767</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>774</v>
+      </c>
+      <c r="I22" s="21" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="66" t="s">
+        <v>775</v>
+      </c>
+      <c r="B23" s="66"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="66"/>
+    </row>
+    <row r="24" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>725</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>776</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>777</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>778</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>779</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>780</v>
+      </c>
+      <c r="I24" s="23" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>781</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>782</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>783</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>784</v>
+      </c>
+      <c r="F25" s="21" t="s">
         <v>681</v>
       </c>
-      <c r="O4" s="63" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="66" t="n">
-        <v>1271</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>683</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>684</v>
-      </c>
-      <c r="H5" s="67"/>
-      <c r="I5" s="66" t="str">
-        <f aca="false">IF(H5="","",H5-E5)</f>
-        <v/>
-      </c>
-      <c r="J5" s="45" t="str">
-        <f aca="false">IFERROR(IF(H5="","",(H5-E5)/E5),"")</f>
-        <v/>
-      </c>
-      <c r="K5" s="68"/>
-      <c r="L5" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="M5" s="68"/>
-      <c r="N5" s="16" t="s">
-        <v>685</v>
-      </c>
-      <c r="O5" s="69"/>
-    </row>
-    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="66" t="n">
-        <v>25</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>686</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>687</v>
-      </c>
-      <c r="H6" s="67"/>
-      <c r="I6" s="66" t="str">
-        <f aca="false">IF(H6="","",H6-E6)</f>
-        <v/>
-      </c>
-      <c r="J6" s="45" t="str">
-        <f aca="false">IFERROR(IF(H6="","",(H6-E6)/E6),"")</f>
-        <v/>
-      </c>
-      <c r="K6" s="68"/>
-      <c r="L6" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="M6" s="68"/>
-      <c r="N6" s="16" t="s">
-        <v>688</v>
-      </c>
-      <c r="O6" s="69"/>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" s="66" t="n">
-        <v>39</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>689</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>678</v>
-      </c>
-      <c r="H7" s="67"/>
-      <c r="I7" s="66" t="str">
-        <f aca="false">IF(H7="","",H7-E7)</f>
-        <v/>
-      </c>
-      <c r="J7" s="45" t="str">
-        <f aca="false">IFERROR(IF(H7="","",(H7-E7)/E7),"")</f>
-        <v/>
-      </c>
-      <c r="K7" s="68"/>
-      <c r="L7" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="M7" s="68"/>
-      <c r="N7" s="16" t="s">
+      <c r="G25" s="21" t="s">
+        <v>779</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>785</v>
+      </c>
+      <c r="I25" s="21" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>641</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>786</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>787</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>788</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>766</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>779</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>789</v>
+      </c>
+      <c r="I26" s="21" t="s">
         <v>690</v>
       </c>
-      <c r="O7" s="69"/>
-    </row>
-    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>691</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>692</v>
-      </c>
-      <c r="H8" s="67"/>
-      <c r="I8" s="66" t="str">
-        <f aca="false">IF(H8="","",H8-E8)</f>
-        <v/>
-      </c>
-      <c r="J8" s="45" t="str">
-        <f aca="false">IFERROR(IF(H8="","",(H8-E8)/E8),"")</f>
-        <v/>
-      </c>
-      <c r="K8" s="68"/>
-      <c r="L8" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="M8" s="68"/>
-      <c r="N8" s="16" t="s">
-        <v>693</v>
-      </c>
-      <c r="O8" s="69"/>
-    </row>
-    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>694</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>695</v>
-      </c>
-      <c r="E9" s="66" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>696</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>697</v>
-      </c>
-      <c r="H9" s="67"/>
-      <c r="I9" s="66" t="str">
-        <f aca="false">IF(H9="","",H9-E9)</f>
-        <v/>
-      </c>
-      <c r="J9" s="45" t="str">
-        <f aca="false">IFERROR(IF(H9="","",(H9-E9)/E9),"")</f>
-        <v/>
-      </c>
-      <c r="K9" s="68"/>
-      <c r="L9" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="M9" s="68"/>
-      <c r="N9" s="16" t="s">
-        <v>698</v>
-      </c>
-      <c r="O9" s="69"/>
-    </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>699</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="E10" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>700</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>701</v>
-      </c>
-      <c r="H10" s="67"/>
-      <c r="I10" s="66" t="str">
-        <f aca="false">IF(H10="","",H10-E10)</f>
-        <v/>
-      </c>
-      <c r="J10" s="45" t="str">
-        <f aca="false">IFERROR(IF(H10="","",(H10-E10)/E10),"")</f>
-        <v/>
-      </c>
-      <c r="K10" s="68"/>
-      <c r="L10" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="M10" s="68"/>
-      <c r="N10" s="16" t="s">
-        <v>702</v>
-      </c>
-      <c r="O10" s="69"/>
-    </row>
-    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>703</v>
-      </c>
-      <c r="E11" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>704</v>
-      </c>
-      <c r="G11" s="16" t="s">
-        <v>705</v>
-      </c>
-      <c r="H11" s="67"/>
-      <c r="I11" s="66" t="str">
-        <f aca="false">IF(H11="","",H11-E11)</f>
-        <v/>
-      </c>
-      <c r="J11" s="45" t="str">
-        <f aca="false">IFERROR(IF(H11="","",(H11-E11)/E11),"")</f>
-        <v/>
-      </c>
-      <c r="K11" s="68"/>
-      <c r="L11" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="M11" s="68"/>
-      <c r="N11" s="16" t="s">
-        <v>706</v>
-      </c>
-      <c r="O11" s="69"/>
-    </row>
-    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="66" t="n">
-        <v>31</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>707</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>708</v>
-      </c>
-      <c r="H12" s="67"/>
-      <c r="I12" s="66" t="str">
-        <f aca="false">IF(H12="","",H12-E12)</f>
-        <v/>
-      </c>
-      <c r="J12" s="45" t="str">
-        <f aca="false">IFERROR(IF(H12="","",(H12-E12)/E12),"")</f>
-        <v/>
-      </c>
-      <c r="K12" s="68"/>
-      <c r="L12" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="M12" s="68"/>
-      <c r="N12" s="16" t="s">
-        <v>709</v>
-      </c>
-      <c r="O12" s="69"/>
-    </row>
-    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>710</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>711</v>
-      </c>
-      <c r="H13" s="67"/>
-      <c r="I13" s="66" t="str">
-        <f aca="false">IF(H13="","",H13-E13)</f>
-        <v/>
-      </c>
-      <c r="J13" s="45" t="str">
-        <f aca="false">IFERROR(IF(H13="","",(H13-E13)/E13),"")</f>
-        <v/>
-      </c>
-      <c r="K13" s="68"/>
-      <c r="L13" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="M13" s="68"/>
-      <c r="N13" s="16" t="s">
-        <v>712</v>
-      </c>
-      <c r="O13" s="69"/>
-    </row>
-    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>713</v>
-      </c>
-      <c r="G14" s="16" t="s">
-        <v>714</v>
-      </c>
-      <c r="H14" s="67"/>
-      <c r="I14" s="66" t="str">
-        <f aca="false">IF(H14="","",H14-E14)</f>
-        <v/>
-      </c>
-      <c r="J14" s="45" t="str">
-        <f aca="false">IFERROR(IF(H14="","",(H14-E14)/E14),"")</f>
-        <v/>
-      </c>
-      <c r="K14" s="68"/>
-      <c r="L14" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="M14" s="68"/>
-      <c r="N14" s="16" t="s">
-        <v>715</v>
-      </c>
-      <c r="O14" s="69"/>
-    </row>
-    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>676</v>
-      </c>
-      <c r="E15" s="66" t="n">
-        <v>6</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>704</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>716</v>
-      </c>
-      <c r="H15" s="67"/>
-      <c r="I15" s="66" t="str">
-        <f aca="false">IF(H15="","",H15-E15)</f>
-        <v/>
-      </c>
-      <c r="J15" s="45" t="str">
-        <f aca="false">IFERROR(IF(H15="","",(H15-E15)/E15),"")</f>
-        <v/>
-      </c>
-      <c r="K15" s="68"/>
-      <c r="L15" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="M15" s="68"/>
-      <c r="N15" s="16" t="s">
-        <v>717</v>
-      </c>
-      <c r="O15" s="69"/>
-    </row>
-    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>718</v>
-      </c>
-      <c r="E16" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>719</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>720</v>
-      </c>
-      <c r="H16" s="67"/>
-      <c r="I16" s="66" t="str">
-        <f aca="false">IF(H16="","",H16-E16)</f>
-        <v/>
-      </c>
-      <c r="J16" s="45" t="str">
-        <f aca="false">IFERROR(IF(H16="","",(H16-E16)/E16),"")</f>
-        <v/>
-      </c>
-      <c r="K16" s="68"/>
-      <c r="L16" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="M16" s="68"/>
-      <c r="N16" s="16" t="s">
-        <v>721</v>
-      </c>
-      <c r="O16" s="69"/>
-    </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
-        <v>722</v>
-      </c>
-      <c r="C18" s="70" t="s">
-        <v>723</v>
-      </c>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="70"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="70"/>
-      <c r="J18" s="70"/>
-      <c r="K18" s="70"/>
+    </row>
+    <row r="27" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>791</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>792</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>788</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>793</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>794</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>795</v>
+      </c>
+      <c r="I27" s="21" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="52" t="s">
+        <v>796</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>797</v>
+      </c>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+    </row>
+    <row r="30" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="54" t="s">
+        <v>798</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>799</v>
+      </c>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+    </row>
+    <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="52" t="s">
+        <v>800</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>801</v>
+      </c>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+    </row>
+    <row r="32" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="52" t="s">
+        <v>802</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>803</v>
+      </c>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+    </row>
+    <row r="33" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="54" t="s">
+        <v>804</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>805</v>
+      </c>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="C18:K18"/>
+  <mergeCells count="12">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="C29:I29"/>
+    <mergeCell ref="C30:I30"/>
+    <mergeCell ref="C31:I31"/>
+    <mergeCell ref="C32:I32"/>
+    <mergeCell ref="C33:I33"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/docs/executive-plan.xlsx
+++ b/docs/executive-plan.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="1180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="1196">
   <si>
     <t xml:space="preserve">نموذج الخطة التنفيذية — الإدارة التجارية</t>
   </si>
@@ -2730,12 +2730,21 @@
     <t xml:space="preserve">شمال جيزان</t>
   </si>
   <si>
+    <t xml:space="preserve">التكلفة الشهرية للعامل (ريال)</t>
+  </si>
+  <si>
     <t xml:space="preserve">محطة ابها</t>
   </si>
   <si>
+    <t xml:space="preserve">زيارات يخدمها العامل في اليوم</t>
+  </si>
+  <si>
     <t xml:space="preserve">محطة الجبيل</t>
   </si>
   <si>
+    <t xml:space="preserve">🎯 هدف الربح (ريال/لتر)</t>
+  </si>
+  <si>
     <t xml:space="preserve">محطة القصيم</t>
   </si>
   <si>
@@ -2769,10 +2778,22 @@
     <t xml:space="preserve">نقل/لتر</t>
   </si>
   <si>
-    <t xml:space="preserve">تشغيل شهري</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تشغيل/لتر</t>
+    <t xml:space="preserve">زيارة/يوم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عمال فعلي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عمال مطلوب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عمالة/لتر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تشغيل آخر شهري</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تشغيل آخر/لتر</t>
   </si>
   <si>
     <t xml:space="preserve">رأس مال/لتر</t>
@@ -2781,6 +2802,15 @@
     <t xml:space="preserve">التكلفة/لتر</t>
   </si>
   <si>
+    <t xml:space="preserve">سعر البيع/لتر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الربح/لتر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الفجوة عن الهدف</t>
+  </si>
+  <si>
     <t xml:space="preserve">النورية</t>
   </si>
   <si>
@@ -2956,6 +2986,24 @@
   </si>
   <si>
     <t xml:space="preserve">85.3% من اللترات تأتي من «شمال جدة». هذا يبسّط التفاوض على أجرة النقل — لكنه يعني أيضاً أن أي انقطاع أو تغيّر سعري في هذا المصدر يمسّ أربعة أخماس الشبكة دفعة واحدة.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العمالة — أكبر بند تشغيلي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عمود «عمال فعلي» يُعبّأ من الموارد البشرية، و«عمال مطلوب» يُحسب تلقائياً من الزيارات اليومية مقسومة على إنتاجية العامل. الفارق بينهما هو ما يكشف المحطات الزائدة أو الناقصة عمالةً. وإن تُرك «الفعلي» فارغاً استُخدم «المطلوب» في حساب التكلفة. تنبيه: الشبكة لها ذروتان — الساعة 17 (30 محطة) والساعة 21 (13 محطة) — فجدولة الورديات على ذروة واحدة تترك الثانية مكشوفة.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎯 هدف الربح 15 هللة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الهدف مُدخل في الخانة الصفراء، والنموذج يقارن به ربح كل محطة ويصدر حكماً. الربح = سعر البيع المرجّح (من مزيج المحطة بالأسعار المقننة) ناقص التكلفة الكاملة. وسعر الشراء يُرجّح بمزيج كل محطة أيضاً — فمحطة ديزلها 64% تشتري وتبيع بأسعار مختلفة تماماً عن محطة بنزينها 90%، ومقارنتهما بسعر واحد تعطي نتيجة خاطئة.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الرافعات الخمس لسدّ الفجوة عن الهدف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بترتيب حجمها في نموذجنا: ① النقل ~5.5 هللة (محكوم بالمسافة — قابل للتفاوض لا للإلغاء) ② الفاقد (~2 هللة عند 1.1% — لكن RY024 بـ26.9% وحدها فرصة كاملة) ③ التشغيل غير العمالة ④ العمالة ~1.3 هللة ⑤ رأس المال (ضئيل إلا في محطات المخزون البطيء). والرافعة السادسة الأكبر ليست تكلفة أصلاً: رفع اللترات يوزّع الثابت على قاعدة أكبر.</t>
   </si>
   <si>
     <t xml:space="preserve">تنبيه على النطاق</t>
@@ -3580,7 +3628,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="14">
+  <numFmts count="15">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
@@ -3593,8 +3641,9 @@
     <numFmt numFmtId="173" formatCode="\+0.0%;\-0.0%;&quot;لا بيانات&quot;"/>
     <numFmt numFmtId="174" formatCode="0.000"/>
     <numFmt numFmtId="175" formatCode="0.0000"/>
-    <numFmt numFmtId="176" formatCode="#,##0.00"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="\+0.0000;\-0.0000"/>
+    <numFmt numFmtId="177" formatCode="#,##0.00"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -3882,7 +3931,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="108">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4223,7 +4272,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="175" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4243,11 +4300,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4271,11 +4328,11 @@
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4283,7 +4340,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5428,20 +5485,22 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:W77"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="10" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="13" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="20" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5501,6 +5560,13 @@
       <c r="M3" s="79"/>
       <c r="N3" s="79"/>
       <c r="O3" s="79"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="79"/>
+      <c r="R3" s="79"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="79"/>
+      <c r="U3" s="79"/>
+      <c r="V3" s="79"/>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
@@ -5521,6 +5587,13 @@
       <c r="M4" s="80"/>
       <c r="N4" s="80"/>
       <c r="O4" s="80"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="80"/>
+      <c r="R4" s="80"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="80"/>
+      <c r="U4" s="80"/>
+      <c r="V4" s="80"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="78" t="s">
@@ -5583,26 +5656,38 @@
       <c r="F11" s="26"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="10" t="s">
+        <v>898</v>
+      </c>
+      <c r="C12" s="83"/>
       <c r="E12" s="82" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="F12" s="26"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="10" t="s">
+        <v>900</v>
+      </c>
+      <c r="C13" s="83"/>
       <c r="E13" s="82" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="F13" s="26"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="10" t="s">
+        <v>902</v>
+      </c>
+      <c r="C14" s="83"/>
       <c r="E14" s="82" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="F14" s="26"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E15" s="82" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="F15" s="26"/>
     </row>
@@ -5614,43 +5699,67 @@
         <v>858</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="N17" s="15" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="O17" s="15" t="s">
-        <v>914</v>
+        <v>917</v>
+      </c>
+      <c r="P17" s="15" t="s">
+        <v>918</v>
+      </c>
+      <c r="Q17" s="15" t="s">
+        <v>919</v>
+      </c>
+      <c r="R17" s="15" t="s">
+        <v>920</v>
+      </c>
+      <c r="S17" s="15" t="s">
+        <v>921</v>
+      </c>
+      <c r="T17" s="15" t="s">
+        <v>922</v>
+      </c>
+      <c r="U17" s="15" t="s">
+        <v>923</v>
+      </c>
+      <c r="V17" s="15" t="s">
+        <v>924</v>
+      </c>
+      <c r="W17" s="15" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5658,7 +5767,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>915</v>
+        <v>925</v>
       </c>
       <c r="C18" s="82" t="s">
         <v>895</v>
@@ -5692,18 +5801,45 @@
         <f aca="false">IFERROR(J18/F18,"")</f>
         <v>0</v>
       </c>
-      <c r="L18" s="26"/>
-      <c r="M18" s="84" t="n">
-        <f aca="false">IFERROR(L18*181/30/D18,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N18" s="84" t="n">
-        <f aca="false">IFERROR((G18/2)*$C$7*$C$10/(D18*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O18" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K18+M18+N18,"")</f>
-        <v>0</v>
+      <c r="L18" s="28" t="n">
+        <v>4236</v>
+      </c>
+      <c r="M18" s="26"/>
+      <c r="N18" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L18/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O18" s="84" t="str">
+        <f aca="false">IFERROR(IF(M18="",N18,M18)*$C$12*181/30/D18,"")</f>
+        <v/>
+      </c>
+      <c r="P18" s="26"/>
+      <c r="Q18" s="84" t="n">
+        <f aca="false">IFERROR(P18*181/30/D18,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="84" t="n">
+        <f aca="false">IFERROR((G18/2)*(0.357*$C$7+0.362*$C$8+0.281*$C$9)*$C$10/(D18*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="86" t="str">
+        <f aca="false">IFERROR((0.357*$C$7+0.362*$C$8+0.281*$C$9)/(1-$C$11)+K18+O18+Q18+R18,"")</f>
+        <v/>
+      </c>
+      <c r="T18" s="84" t="n">
+        <v>1.9449</v>
+      </c>
+      <c r="U18" s="86" t="str">
+        <f aca="false">IFERROR(T18-S18,"")</f>
+        <v/>
+      </c>
+      <c r="V18" s="87" t="str">
+        <f aca="false">IFERROR(U18-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W18" s="21" t="str">
+        <f aca="false">IF(U18="","",IF(U18&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5711,7 +5847,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>916</v>
+        <v>926</v>
       </c>
       <c r="C19" s="82" t="s">
         <v>895</v>
@@ -5745,18 +5881,45 @@
         <f aca="false">IFERROR(J19/F19,"")</f>
         <v>0</v>
       </c>
-      <c r="L19" s="26"/>
-      <c r="M19" s="84" t="n">
-        <f aca="false">IFERROR(L19*181/30/D19,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N19" s="84" t="n">
-        <f aca="false">IFERROR((G19/2)*$C$7*$C$10/(D19*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O19" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K19+M19+N19,"")</f>
-        <v>0</v>
+      <c r="L19" s="28" t="n">
+        <v>3561</v>
+      </c>
+      <c r="M19" s="26"/>
+      <c r="N19" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L19/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O19" s="84" t="str">
+        <f aca="false">IFERROR(IF(M19="",N19,M19)*$C$12*181/30/D19,"")</f>
+        <v/>
+      </c>
+      <c r="P19" s="26"/>
+      <c r="Q19" s="84" t="n">
+        <f aca="false">IFERROR(P19*181/30/D19,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R19" s="84" t="n">
+        <f aca="false">IFERROR((G19/2)*(0.502*$C$7+0.498*$C$8+0*$C$9)*$C$10/(D19*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="86" t="str">
+        <f aca="false">IFERROR((0.502*$C$7+0.498*$C$8+0*$C$9)/(1-$C$11)+K19+O19+Q19+R19,"")</f>
+        <v/>
+      </c>
+      <c r="T19" s="84" t="n">
+        <v>2.2547</v>
+      </c>
+      <c r="U19" s="86" t="str">
+        <f aca="false">IFERROR(T19-S19,"")</f>
+        <v/>
+      </c>
+      <c r="V19" s="87" t="str">
+        <f aca="false">IFERROR(U19-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W19" s="21" t="str">
+        <f aca="false">IF(U19="","",IF(U19&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5764,7 +5927,7 @@
         <v>3</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>917</v>
+        <v>927</v>
       </c>
       <c r="C20" s="82" t="s">
         <v>895</v>
@@ -5798,18 +5961,45 @@
         <f aca="false">IFERROR(J20/F20,"")</f>
         <v>0</v>
       </c>
-      <c r="L20" s="26"/>
-      <c r="M20" s="84" t="n">
-        <f aca="false">IFERROR(L20*181/30/D20,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N20" s="84" t="n">
-        <f aca="false">IFERROR((G20/2)*$C$7*$C$10/(D20*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O20" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K20+M20+N20,"")</f>
-        <v>0</v>
+      <c r="L20" s="28" t="n">
+        <v>2137</v>
+      </c>
+      <c r="M20" s="26"/>
+      <c r="N20" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L20/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O20" s="84" t="str">
+        <f aca="false">IFERROR(IF(M20="",N20,M20)*$C$12*181/30/D20,"")</f>
+        <v/>
+      </c>
+      <c r="P20" s="26"/>
+      <c r="Q20" s="84" t="n">
+        <f aca="false">IFERROR(P20*181/30/D20,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R20" s="84" t="n">
+        <f aca="false">IFERROR((G20/2)*(0.344*$C$7+0.312*$C$8+0.344*$C$9)*$C$10/(D20*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S20" s="86" t="str">
+        <f aca="false">IFERROR((0.344*$C$7+0.312*$C$8+0.344*$C$9)/(1-$C$11)+K20+O20+Q20+R20,"")</f>
+        <v/>
+      </c>
+      <c r="T20" s="84" t="n">
+        <v>1.8725</v>
+      </c>
+      <c r="U20" s="86" t="str">
+        <f aca="false">IFERROR(T20-S20,"")</f>
+        <v/>
+      </c>
+      <c r="V20" s="87" t="str">
+        <f aca="false">IFERROR(U20-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W20" s="21" t="str">
+        <f aca="false">IF(U20="","",IF(U20&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5817,7 +6007,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>918</v>
+        <v>928</v>
       </c>
       <c r="C21" s="82" t="s">
         <v>895</v>
@@ -5851,18 +6041,45 @@
         <f aca="false">IFERROR(J21/F21,"")</f>
         <v>0</v>
       </c>
-      <c r="L21" s="26"/>
-      <c r="M21" s="84" t="n">
-        <f aca="false">IFERROR(L21*181/30/D21,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N21" s="84" t="n">
-        <f aca="false">IFERROR((G21/2)*$C$7*$C$10/(D21*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O21" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K21+M21+N21,"")</f>
-        <v>0</v>
+      <c r="L21" s="28" t="n">
+        <v>1643</v>
+      </c>
+      <c r="M21" s="26"/>
+      <c r="N21" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L21/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O21" s="84" t="str">
+        <f aca="false">IFERROR(IF(M21="",N21,M21)*$C$12*181/30/D21,"")</f>
+        <v/>
+      </c>
+      <c r="P21" s="26"/>
+      <c r="Q21" s="84" t="n">
+        <f aca="false">IFERROR(P21*181/30/D21,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R21" s="84" t="n">
+        <f aca="false">IFERROR((G21/2)*(0.587*$C$7+0.413*$C$8+0*$C$9)*$C$10/(D21*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S21" s="86" t="str">
+        <f aca="false">IFERROR((0.587*$C$7+0.413*$C$8+0*$C$9)/(1-$C$11)+K21+O21+Q21+R21,"")</f>
+        <v/>
+      </c>
+      <c r="T21" s="84" t="n">
+        <v>2.242</v>
+      </c>
+      <c r="U21" s="86" t="str">
+        <f aca="false">IFERROR(T21-S21,"")</f>
+        <v/>
+      </c>
+      <c r="V21" s="87" t="str">
+        <f aca="false">IFERROR(U21-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W21" s="21" t="str">
+        <f aca="false">IF(U21="","",IF(U21&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5870,7 +6087,7 @@
         <v>5</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>919</v>
+        <v>929</v>
       </c>
       <c r="C22" s="82" t="s">
         <v>895</v>
@@ -5904,18 +6121,45 @@
         <f aca="false">IFERROR(J22/F22,"")</f>
         <v>0</v>
       </c>
-      <c r="L22" s="26"/>
-      <c r="M22" s="84" t="n">
-        <f aca="false">IFERROR(L22*181/30/D22,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N22" s="84" t="n">
-        <f aca="false">IFERROR((G22/2)*$C$7*$C$10/(D22*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O22" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K22+M22+N22,"")</f>
-        <v>0</v>
+      <c r="L22" s="28" t="n">
+        <v>2359</v>
+      </c>
+      <c r="M22" s="26"/>
+      <c r="N22" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L22/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O22" s="84" t="str">
+        <f aca="false">IFERROR(IF(M22="",N22,M22)*$C$12*181/30/D22,"")</f>
+        <v/>
+      </c>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="84" t="n">
+        <f aca="false">IFERROR(P22*181/30/D22,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R22" s="84" t="n">
+        <f aca="false">IFERROR((G22/2)*(0.635*$C$7+0.231*$C$8+0.134*$C$9)*$C$10/(D22*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S22" s="86" t="str">
+        <f aca="false">IFERROR((0.635*$C$7+0.231*$C$8+0.134*$C$9)/(1-$C$11)+K22+O22+Q22+R22,"")</f>
+        <v/>
+      </c>
+      <c r="T22" s="84" t="n">
+        <v>2.0766</v>
+      </c>
+      <c r="U22" s="86" t="str">
+        <f aca="false">IFERROR(T22-S22,"")</f>
+        <v/>
+      </c>
+      <c r="V22" s="87" t="str">
+        <f aca="false">IFERROR(U22-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W22" s="21" t="str">
+        <f aca="false">IF(U22="","",IF(U22&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5923,7 +6167,7 @@
         <v>6</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>920</v>
+        <v>930</v>
       </c>
       <c r="C23" s="82" t="s">
         <v>895</v>
@@ -5957,18 +6201,45 @@
         <f aca="false">IFERROR(J23/F23,"")</f>
         <v>0</v>
       </c>
-      <c r="L23" s="26"/>
-      <c r="M23" s="84" t="n">
-        <f aca="false">IFERROR(L23*181/30/D23,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N23" s="84" t="n">
-        <f aca="false">IFERROR((G23/2)*$C$7*$C$10/(D23*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O23" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K23+M23+N23,"")</f>
-        <v>0</v>
+      <c r="L23" s="28" t="n">
+        <v>1694</v>
+      </c>
+      <c r="M23" s="26"/>
+      <c r="N23" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L23/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O23" s="84" t="str">
+        <f aca="false">IFERROR(IF(M23="",N23,M23)*$C$12*181/30/D23,"")</f>
+        <v/>
+      </c>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="84" t="n">
+        <f aca="false">IFERROR(P23*181/30/D23,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R23" s="84" t="n">
+        <f aca="false">IFERROR((G23/2)*(0.381*$C$7+0.309*$C$8+0.309*$C$9)*$C$10/(D23*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S23" s="86" t="str">
+        <f aca="false">IFERROR((0.381*$C$7+0.309*$C$8+0.309*$C$9)/(1-$C$11)+K23+O23+Q23+R23,"")</f>
+        <v/>
+      </c>
+      <c r="T23" s="84" t="n">
+        <v>1.9059</v>
+      </c>
+      <c r="U23" s="86" t="str">
+        <f aca="false">IFERROR(T23-S23,"")</f>
+        <v/>
+      </c>
+      <c r="V23" s="87" t="str">
+        <f aca="false">IFERROR(U23-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W23" s="21" t="str">
+        <f aca="false">IF(U23="","",IF(U23&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5976,7 +6247,7 @@
         <v>7</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="C24" s="82" t="s">
         <v>895</v>
@@ -6010,18 +6281,45 @@
         <f aca="false">IFERROR(J24/F24,"")</f>
         <v>0</v>
       </c>
-      <c r="L24" s="26"/>
-      <c r="M24" s="84" t="n">
-        <f aca="false">IFERROR(L24*181/30/D24,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N24" s="84" t="n">
-        <f aca="false">IFERROR((G24/2)*$C$7*$C$10/(D24*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O24" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K24+M24+N24,"")</f>
-        <v>0</v>
+      <c r="L24" s="28" t="n">
+        <v>1702</v>
+      </c>
+      <c r="M24" s="26"/>
+      <c r="N24" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L24/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O24" s="84" t="str">
+        <f aca="false">IFERROR(IF(M24="",N24,M24)*$C$12*181/30/D24,"")</f>
+        <v/>
+      </c>
+      <c r="P24" s="26"/>
+      <c r="Q24" s="84" t="n">
+        <f aca="false">IFERROR(P24*181/30/D24,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R24" s="84" t="n">
+        <f aca="false">IFERROR((G24/2)*(0.354*$C$7+0.369*$C$8+0.277*$C$9)*$C$10/(D24*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S24" s="86" t="str">
+        <f aca="false">IFERROR((0.354*$C$7+0.369*$C$8+0.277*$C$9)/(1-$C$11)+K24+O24+Q24+R24,"")</f>
+        <v/>
+      </c>
+      <c r="T24" s="84" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U24" s="86" t="str">
+        <f aca="false">IFERROR(T24-S24,"")</f>
+        <v/>
+      </c>
+      <c r="V24" s="87" t="str">
+        <f aca="false">IFERROR(U24-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W24" s="21" t="str">
+        <f aca="false">IF(U24="","",IF(U24&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6029,7 +6327,7 @@
         <v>8</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>922</v>
+        <v>932</v>
       </c>
       <c r="C25" s="82" t="s">
         <v>895</v>
@@ -6063,18 +6361,45 @@
         <f aca="false">IFERROR(J25/F25,"")</f>
         <v>0</v>
       </c>
-      <c r="L25" s="26"/>
-      <c r="M25" s="84" t="n">
-        <f aca="false">IFERROR(L25*181/30/D25,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N25" s="84" t="n">
-        <f aca="false">IFERROR((G25/2)*$C$7*$C$10/(D25*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O25" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K25+M25+N25,"")</f>
-        <v>0</v>
+      <c r="L25" s="28" t="n">
+        <v>2041</v>
+      </c>
+      <c r="M25" s="26"/>
+      <c r="N25" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L25/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O25" s="84" t="str">
+        <f aca="false">IFERROR(IF(M25="",N25,M25)*$C$12*181/30/D25,"")</f>
+        <v/>
+      </c>
+      <c r="P25" s="26"/>
+      <c r="Q25" s="84" t="n">
+        <f aca="false">IFERROR(P25*181/30/D25,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R25" s="84" t="n">
+        <f aca="false">IFERROR((G25/2)*(0.56*$C$7+0.429*$C$8+0*$C$9)*$C$10/(D25*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S25" s="86" t="str">
+        <f aca="false">IFERROR((0.56*$C$7+0.429*$C$8+0*$C$9)/(1-$C$11)+K25+O25+Q25+R25,"")</f>
+        <v/>
+      </c>
+      <c r="T25" s="84" t="n">
+        <v>2.2204</v>
+      </c>
+      <c r="U25" s="86" t="str">
+        <f aca="false">IFERROR(T25-S25,"")</f>
+        <v/>
+      </c>
+      <c r="V25" s="87" t="str">
+        <f aca="false">IFERROR(U25-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W25" s="21" t="str">
+        <f aca="false">IF(U25="","",IF(U25&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6082,7 +6407,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="C26" s="82" t="s">
         <v>895</v>
@@ -6116,18 +6441,45 @@
         <f aca="false">IFERROR(J26/F26,"")</f>
         <v>0</v>
       </c>
-      <c r="L26" s="26"/>
-      <c r="M26" s="84" t="n">
-        <f aca="false">IFERROR(L26*181/30/D26,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N26" s="84" t="n">
-        <f aca="false">IFERROR((G26/2)*$C$7*$C$10/(D26*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O26" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K26+M26+N26,"")</f>
-        <v>0</v>
+      <c r="L26" s="28" t="n">
+        <v>1726</v>
+      </c>
+      <c r="M26" s="26"/>
+      <c r="N26" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L26/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O26" s="84" t="str">
+        <f aca="false">IFERROR(IF(M26="",N26,M26)*$C$12*181/30/D26,"")</f>
+        <v/>
+      </c>
+      <c r="P26" s="26"/>
+      <c r="Q26" s="84" t="n">
+        <f aca="false">IFERROR(P26*181/30/D26,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R26" s="84" t="n">
+        <f aca="false">IFERROR((G26/2)*(0.526*$C$7+0.468*$C$8+0.006*$C$9)*$C$10/(D26*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S26" s="86" t="str">
+        <f aca="false">IFERROR((0.526*$C$7+0.468*$C$8+0.006*$C$9)/(1-$C$11)+K26+O26+Q26+R26,"")</f>
+        <v/>
+      </c>
+      <c r="T26" s="84" t="n">
+        <v>2.244</v>
+      </c>
+      <c r="U26" s="86" t="str">
+        <f aca="false">IFERROR(T26-S26,"")</f>
+        <v/>
+      </c>
+      <c r="V26" s="87" t="str">
+        <f aca="false">IFERROR(U26-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W26" s="21" t="str">
+        <f aca="false">IF(U26="","",IF(U26&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6135,7 +6487,7 @@
         <v>10</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>924</v>
+        <v>934</v>
       </c>
       <c r="C27" s="82" t="s">
         <v>895</v>
@@ -6169,18 +6521,45 @@
         <f aca="false">IFERROR(J27/F27,"")</f>
         <v>0</v>
       </c>
-      <c r="L27" s="26"/>
-      <c r="M27" s="84" t="n">
-        <f aca="false">IFERROR(L27*181/30/D27,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N27" s="84" t="n">
-        <f aca="false">IFERROR((G27/2)*$C$7*$C$10/(D27*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O27" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K27+M27+N27,"")</f>
-        <v>0</v>
+      <c r="L27" s="28" t="n">
+        <v>1566</v>
+      </c>
+      <c r="M27" s="26"/>
+      <c r="N27" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L27/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O27" s="84" t="str">
+        <f aca="false">IFERROR(IF(M27="",N27,M27)*$C$12*181/30/D27,"")</f>
+        <v/>
+      </c>
+      <c r="P27" s="26"/>
+      <c r="Q27" s="84" t="n">
+        <f aca="false">IFERROR(P27*181/30/D27,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R27" s="84" t="n">
+        <f aca="false">IFERROR((G27/2)*(0.406*$C$7+0.364*$C$8+0.231*$C$9)*$C$10/(D27*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S27" s="86" t="str">
+        <f aca="false">IFERROR((0.406*$C$7+0.364*$C$8+0.231*$C$9)/(1-$C$11)+K27+O27+Q27+R27,"")</f>
+        <v/>
+      </c>
+      <c r="T27" s="84" t="n">
+        <v>1.9989</v>
+      </c>
+      <c r="U27" s="86" t="str">
+        <f aca="false">IFERROR(T27-S27,"")</f>
+        <v/>
+      </c>
+      <c r="V27" s="87" t="str">
+        <f aca="false">IFERROR(U27-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W27" s="21" t="str">
+        <f aca="false">IF(U27="","",IF(U27&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6188,7 +6567,7 @@
         <v>11</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>925</v>
+        <v>935</v>
       </c>
       <c r="C28" s="82" t="s">
         <v>895</v>
@@ -6222,18 +6601,45 @@
         <f aca="false">IFERROR(J28/F28,"")</f>
         <v>0</v>
       </c>
-      <c r="L28" s="26"/>
-      <c r="M28" s="84" t="n">
-        <f aca="false">IFERROR(L28*181/30/D28,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N28" s="84" t="n">
-        <f aca="false">IFERROR((G28/2)*$C$7*$C$10/(D28*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O28" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K28+M28+N28,"")</f>
-        <v>0</v>
+      <c r="L28" s="28" t="n">
+        <v>1414</v>
+      </c>
+      <c r="M28" s="26"/>
+      <c r="N28" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L28/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O28" s="84" t="str">
+        <f aca="false">IFERROR(IF(M28="",N28,M28)*$C$12*181/30/D28,"")</f>
+        <v/>
+      </c>
+      <c r="P28" s="26"/>
+      <c r="Q28" s="84" t="n">
+        <f aca="false">IFERROR(P28*181/30/D28,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R28" s="84" t="n">
+        <f aca="false">IFERROR((G28/2)*(0.465*$C$7+0.453*$C$8+0.082*$C$9)*$C$10/(D28*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S28" s="86" t="str">
+        <f aca="false">IFERROR((0.465*$C$7+0.453*$C$8+0.082*$C$9)/(1-$C$11)+K28+O28+Q28+R28,"")</f>
+        <v/>
+      </c>
+      <c r="T28" s="84" t="n">
+        <v>2.1635</v>
+      </c>
+      <c r="U28" s="86" t="str">
+        <f aca="false">IFERROR(T28-S28,"")</f>
+        <v/>
+      </c>
+      <c r="V28" s="87" t="str">
+        <f aca="false">IFERROR(U28-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W28" s="21" t="str">
+        <f aca="false">IF(U28="","",IF(U28&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6241,7 +6647,7 @@
         <v>12</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>926</v>
+        <v>936</v>
       </c>
       <c r="C29" s="82" t="s">
         <v>895</v>
@@ -6275,18 +6681,45 @@
         <f aca="false">IFERROR(J29/F29,"")</f>
         <v>0</v>
       </c>
-      <c r="L29" s="26"/>
-      <c r="M29" s="84" t="n">
-        <f aca="false">IFERROR(L29*181/30/D29,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N29" s="84" t="n">
-        <f aca="false">IFERROR((G29/2)*$C$7*$C$10/(D29*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O29" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K29+M29+N29,"")</f>
-        <v>0</v>
+      <c r="L29" s="28" t="n">
+        <v>1380</v>
+      </c>
+      <c r="M29" s="26"/>
+      <c r="N29" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L29/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O29" s="84" t="str">
+        <f aca="false">IFERROR(IF(M29="",N29,M29)*$C$12*181/30/D29,"")</f>
+        <v/>
+      </c>
+      <c r="P29" s="26"/>
+      <c r="Q29" s="84" t="n">
+        <f aca="false">IFERROR(P29*181/30/D29,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R29" s="84" t="n">
+        <f aca="false">IFERROR((G29/2)*(0.337*$C$7+0.206*$C$8+0.458*$C$9)*$C$10/(D29*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S29" s="86" t="str">
+        <f aca="false">IFERROR((0.337*$C$7+0.206*$C$8+0.458*$C$9)/(1-$C$11)+K29+O29+Q29+R29,"")</f>
+        <v/>
+      </c>
+      <c r="T29" s="84" t="n">
+        <v>1.7413</v>
+      </c>
+      <c r="U29" s="86" t="str">
+        <f aca="false">IFERROR(T29-S29,"")</f>
+        <v/>
+      </c>
+      <c r="V29" s="87" t="str">
+        <f aca="false">IFERROR(U29-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W29" s="21" t="str">
+        <f aca="false">IF(U29="","",IF(U29&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6294,7 +6727,7 @@
         <v>13</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>927</v>
+        <v>937</v>
       </c>
       <c r="C30" s="82" t="s">
         <v>893</v>
@@ -6328,18 +6761,45 @@
         <f aca="false">IFERROR(J30/F30,"")</f>
         <v>0</v>
       </c>
-      <c r="L30" s="26"/>
-      <c r="M30" s="84" t="n">
-        <f aca="false">IFERROR(L30*181/30/D30,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N30" s="84" t="n">
-        <f aca="false">IFERROR((G30/2)*$C$7*$C$10/(D30*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O30" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K30+M30+N30,"")</f>
-        <v>0</v>
+      <c r="L30" s="28" t="n">
+        <v>1169</v>
+      </c>
+      <c r="M30" s="26"/>
+      <c r="N30" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L30/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O30" s="84" t="str">
+        <f aca="false">IFERROR(IF(M30="",N30,M30)*$C$12*181/30/D30,"")</f>
+        <v/>
+      </c>
+      <c r="P30" s="26"/>
+      <c r="Q30" s="84" t="n">
+        <f aca="false">IFERROR(P30*181/30/D30,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R30" s="84" t="n">
+        <f aca="false">IFERROR((G30/2)*(0.474*$C$7+0.451*$C$8+0.076*$C$9)*$C$10/(D30*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S30" s="86" t="str">
+        <f aca="false">IFERROR((0.474*$C$7+0.451*$C$8+0.076*$C$9)/(1-$C$11)+K30+O30+Q30+R30,"")</f>
+        <v/>
+      </c>
+      <c r="T30" s="84" t="n">
+        <v>2.1716</v>
+      </c>
+      <c r="U30" s="86" t="str">
+        <f aca="false">IFERROR(T30-S30,"")</f>
+        <v/>
+      </c>
+      <c r="V30" s="87" t="str">
+        <f aca="false">IFERROR(U30-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W30" s="21" t="str">
+        <f aca="false">IF(U30="","",IF(U30&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6347,7 +6807,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>928</v>
+        <v>938</v>
       </c>
       <c r="C31" s="82" t="s">
         <v>895</v>
@@ -6381,18 +6841,45 @@
         <f aca="false">IFERROR(J31/F31,"")</f>
         <v>0</v>
       </c>
-      <c r="L31" s="26"/>
-      <c r="M31" s="84" t="n">
-        <f aca="false">IFERROR(L31*181/30/D31,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N31" s="84" t="n">
-        <f aca="false">IFERROR((G31/2)*$C$7*$C$10/(D31*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O31" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K31+M31+N31,"")</f>
-        <v>0</v>
+      <c r="L31" s="28" t="n">
+        <v>1872</v>
+      </c>
+      <c r="M31" s="26"/>
+      <c r="N31" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L31/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O31" s="84" t="str">
+        <f aca="false">IFERROR(IF(M31="",N31,M31)*$C$12*181/30/D31,"")</f>
+        <v/>
+      </c>
+      <c r="P31" s="26"/>
+      <c r="Q31" s="84" t="n">
+        <f aca="false">IFERROR(P31*181/30/D31,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R31" s="84" t="n">
+        <f aca="false">IFERROR((G31/2)*(0.554*$C$7+0.446*$C$8+0*$C$9)*$C$10/(D31*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S31" s="86" t="str">
+        <f aca="false">IFERROR((0.554*$C$7+0.446*$C$8+0*$C$9)/(1-$C$11)+K31+O31+Q31+R31,"")</f>
+        <v/>
+      </c>
+      <c r="T31" s="84" t="n">
+        <v>2.2469</v>
+      </c>
+      <c r="U31" s="86" t="str">
+        <f aca="false">IFERROR(T31-S31,"")</f>
+        <v/>
+      </c>
+      <c r="V31" s="87" t="str">
+        <f aca="false">IFERROR(U31-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W31" s="21" t="str">
+        <f aca="false">IF(U31="","",IF(U31&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6400,7 +6887,7 @@
         <v>15</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>929</v>
+        <v>939</v>
       </c>
       <c r="C32" s="82" t="s">
         <v>895</v>
@@ -6434,18 +6921,45 @@
         <f aca="false">IFERROR(J32/F32,"")</f>
         <v>0</v>
       </c>
-      <c r="L32" s="26"/>
-      <c r="M32" s="84" t="n">
-        <f aca="false">IFERROR(L32*181/30/D32,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N32" s="84" t="n">
-        <f aca="false">IFERROR((G32/2)*$C$7*$C$10/(D32*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O32" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K32+M32+N32,"")</f>
-        <v>0</v>
+      <c r="L32" s="28" t="n">
+        <v>1483</v>
+      </c>
+      <c r="M32" s="26"/>
+      <c r="N32" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L32/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O32" s="84" t="str">
+        <f aca="false">IFERROR(IF(M32="",N32,M32)*$C$12*181/30/D32,"")</f>
+        <v/>
+      </c>
+      <c r="P32" s="26"/>
+      <c r="Q32" s="84" t="n">
+        <f aca="false">IFERROR(P32*181/30/D32,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R32" s="84" t="n">
+        <f aca="false">IFERROR((G32/2)*(0.544*$C$7+0.456*$C$8+0*$C$9)*$C$10/(D32*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S32" s="86" t="str">
+        <f aca="false">IFERROR((0.544*$C$7+0.456*$C$8+0*$C$9)/(1-$C$11)+K32+O32+Q32+R32,"")</f>
+        <v/>
+      </c>
+      <c r="T32" s="84" t="n">
+        <v>2.2484</v>
+      </c>
+      <c r="U32" s="86" t="str">
+        <f aca="false">IFERROR(T32-S32,"")</f>
+        <v/>
+      </c>
+      <c r="V32" s="87" t="str">
+        <f aca="false">IFERROR(U32-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W32" s="21" t="str">
+        <f aca="false">IF(U32="","",IF(U32&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6453,7 +6967,7 @@
         <v>16</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>930</v>
+        <v>940</v>
       </c>
       <c r="C33" s="82" t="s">
         <v>895</v>
@@ -6487,18 +7001,45 @@
         <f aca="false">IFERROR(J33/F33,"")</f>
         <v>0</v>
       </c>
-      <c r="L33" s="26"/>
-      <c r="M33" s="84" t="n">
-        <f aca="false">IFERROR(L33*181/30/D33,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N33" s="84" t="n">
-        <f aca="false">IFERROR((G33/2)*$C$7*$C$10/(D33*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O33" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K33+M33+N33,"")</f>
-        <v>0</v>
+      <c r="L33" s="28" t="n">
+        <v>1573</v>
+      </c>
+      <c r="M33" s="26"/>
+      <c r="N33" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L33/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O33" s="84" t="str">
+        <f aca="false">IFERROR(IF(M33="",N33,M33)*$C$12*181/30/D33,"")</f>
+        <v/>
+      </c>
+      <c r="P33" s="26"/>
+      <c r="Q33" s="84" t="n">
+        <f aca="false">IFERROR(P33*181/30/D33,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R33" s="84" t="n">
+        <f aca="false">IFERROR((G33/2)*(0.575*$C$7+0.425*$C$8+0*$C$9)*$C$10/(D33*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S33" s="86" t="str">
+        <f aca="false">IFERROR((0.575*$C$7+0.425*$C$8+0*$C$9)/(1-$C$11)+K33+O33+Q33+R33,"")</f>
+        <v/>
+      </c>
+      <c r="T33" s="84" t="n">
+        <v>2.2437</v>
+      </c>
+      <c r="U33" s="86" t="str">
+        <f aca="false">IFERROR(T33-S33,"")</f>
+        <v/>
+      </c>
+      <c r="V33" s="87" t="str">
+        <f aca="false">IFERROR(U33-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W33" s="21" t="str">
+        <f aca="false">IF(U33="","",IF(U33&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6506,7 +7047,7 @@
         <v>17</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>931</v>
+        <v>941</v>
       </c>
       <c r="C34" s="82" t="s">
         <v>895</v>
@@ -6540,18 +7081,45 @@
         <f aca="false">IFERROR(J34/F34,"")</f>
         <v>0</v>
       </c>
-      <c r="L34" s="26"/>
-      <c r="M34" s="84" t="n">
-        <f aca="false">IFERROR(L34*181/30/D34,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N34" s="84" t="n">
-        <f aca="false">IFERROR((G34/2)*$C$7*$C$10/(D34*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O34" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K34+M34+N34,"")</f>
-        <v>0</v>
+      <c r="L34" s="28" t="n">
+        <v>1112</v>
+      </c>
+      <c r="M34" s="26"/>
+      <c r="N34" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L34/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O34" s="84" t="str">
+        <f aca="false">IFERROR(IF(M34="",N34,M34)*$C$12*181/30/D34,"")</f>
+        <v/>
+      </c>
+      <c r="P34" s="26"/>
+      <c r="Q34" s="84" t="n">
+        <f aca="false">IFERROR(P34*181/30/D34,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R34" s="84" t="n">
+        <f aca="false">IFERROR((G34/2)*(0.372*$C$7+0.351*$C$8+0.276*$C$9)*$C$10/(D34*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S34" s="86" t="str">
+        <f aca="false">IFERROR((0.372*$C$7+0.351*$C$8+0.276*$C$9)/(1-$C$11)+K34+O34+Q34+R34,"")</f>
+        <v/>
+      </c>
+      <c r="T34" s="84" t="n">
+        <v>1.9462</v>
+      </c>
+      <c r="U34" s="86" t="str">
+        <f aca="false">IFERROR(T34-S34,"")</f>
+        <v/>
+      </c>
+      <c r="V34" s="87" t="str">
+        <f aca="false">IFERROR(U34-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W34" s="21" t="str">
+        <f aca="false">IF(U34="","",IF(U34&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6559,7 +7127,7 @@
         <v>18</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>932</v>
+        <v>942</v>
       </c>
       <c r="C35" s="82" t="s">
         <v>895</v>
@@ -6593,18 +7161,45 @@
         <f aca="false">IFERROR(J35/F35,"")</f>
         <v>0</v>
       </c>
-      <c r="L35" s="26"/>
-      <c r="M35" s="84" t="n">
-        <f aca="false">IFERROR(L35*181/30/D35,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N35" s="84" t="n">
-        <f aca="false">IFERROR((G35/2)*$C$7*$C$10/(D35*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O35" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K35+M35+N35,"")</f>
-        <v>0</v>
+      <c r="L35" s="28" t="n">
+        <v>1144</v>
+      </c>
+      <c r="M35" s="26"/>
+      <c r="N35" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L35/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O35" s="84" t="str">
+        <f aca="false">IFERROR(IF(M35="",N35,M35)*$C$12*181/30/D35,"")</f>
+        <v/>
+      </c>
+      <c r="P35" s="26"/>
+      <c r="Q35" s="84" t="n">
+        <f aca="false">IFERROR(P35*181/30/D35,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R35" s="84" t="n">
+        <f aca="false">IFERROR((G35/2)*(0.461*$C$7+0.481*$C$8+0.058*$C$9)*$C$10/(D35*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S35" s="86" t="str">
+        <f aca="false">IFERROR((0.461*$C$7+0.481*$C$8+0.058*$C$9)/(1-$C$11)+K35+O35+Q35+R35,"")</f>
+        <v/>
+      </c>
+      <c r="T35" s="84" t="n">
+        <v>2.1924</v>
+      </c>
+      <c r="U35" s="86" t="str">
+        <f aca="false">IFERROR(T35-S35,"")</f>
+        <v/>
+      </c>
+      <c r="V35" s="87" t="str">
+        <f aca="false">IFERROR(U35-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W35" s="21" t="str">
+        <f aca="false">IF(U35="","",IF(U35&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6612,7 +7207,7 @@
         <v>19</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>933</v>
+        <v>943</v>
       </c>
       <c r="C36" s="82" t="s">
         <v>895</v>
@@ -6646,18 +7241,45 @@
         <f aca="false">IFERROR(J36/F36,"")</f>
         <v>0</v>
       </c>
-      <c r="L36" s="26"/>
-      <c r="M36" s="84" t="n">
-        <f aca="false">IFERROR(L36*181/30/D36,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N36" s="84" t="n">
-        <f aca="false">IFERROR((G36/2)*$C$7*$C$10/(D36*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O36" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K36+M36+N36,"")</f>
-        <v>0</v>
+      <c r="L36" s="28" t="n">
+        <v>1363</v>
+      </c>
+      <c r="M36" s="26"/>
+      <c r="N36" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L36/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O36" s="84" t="str">
+        <f aca="false">IFERROR(IF(M36="",N36,M36)*$C$12*181/30/D36,"")</f>
+        <v/>
+      </c>
+      <c r="P36" s="26"/>
+      <c r="Q36" s="84" t="n">
+        <f aca="false">IFERROR(P36*181/30/D36,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R36" s="84" t="n">
+        <f aca="false">IFERROR((G36/2)*(0.522*$C$7+0.478*$C$8+0*$C$9)*$C$10/(D36*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S36" s="86" t="str">
+        <f aca="false">IFERROR((0.522*$C$7+0.478*$C$8+0*$C$9)/(1-$C$11)+K36+O36+Q36+R36,"")</f>
+        <v/>
+      </c>
+      <c r="T36" s="84" t="n">
+        <v>2.2517</v>
+      </c>
+      <c r="U36" s="86" t="str">
+        <f aca="false">IFERROR(T36-S36,"")</f>
+        <v/>
+      </c>
+      <c r="V36" s="87" t="str">
+        <f aca="false">IFERROR(U36-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W36" s="21" t="str">
+        <f aca="false">IF(U36="","",IF(U36&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6665,7 +7287,7 @@
         <v>20</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>934</v>
+        <v>944</v>
       </c>
       <c r="C37" s="82" t="s">
         <v>895</v>
@@ -6699,18 +7321,45 @@
         <f aca="false">IFERROR(J37/F37,"")</f>
         <v>0</v>
       </c>
-      <c r="L37" s="26"/>
-      <c r="M37" s="84" t="n">
-        <f aca="false">IFERROR(L37*181/30/D37,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N37" s="84" t="n">
-        <f aca="false">IFERROR((G37/2)*$C$7*$C$10/(D37*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O37" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K37+M37+N37,"")</f>
-        <v>0</v>
+      <c r="L37" s="28" t="n">
+        <v>1290</v>
+      </c>
+      <c r="M37" s="26"/>
+      <c r="N37" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L37/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O37" s="84" t="str">
+        <f aca="false">IFERROR(IF(M37="",N37,M37)*$C$12*181/30/D37,"")</f>
+        <v/>
+      </c>
+      <c r="P37" s="26"/>
+      <c r="Q37" s="84" t="n">
+        <f aca="false">IFERROR(P37*181/30/D37,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R37" s="84" t="n">
+        <f aca="false">IFERROR((G37/2)*(0.517*$C$7+0.483*$C$8+0*$C$9)*$C$10/(D37*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S37" s="86" t="str">
+        <f aca="false">IFERROR((0.517*$C$7+0.483*$C$8+0*$C$9)/(1-$C$11)+K37+O37+Q37+R37,"")</f>
+        <v/>
+      </c>
+      <c r="T37" s="84" t="n">
+        <v>2.2525</v>
+      </c>
+      <c r="U37" s="86" t="str">
+        <f aca="false">IFERROR(T37-S37,"")</f>
+        <v/>
+      </c>
+      <c r="V37" s="87" t="str">
+        <f aca="false">IFERROR(U37-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W37" s="21" t="str">
+        <f aca="false">IF(U37="","",IF(U37&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6718,7 +7367,7 @@
         <v>21</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>935</v>
+        <v>945</v>
       </c>
       <c r="C38" s="82" t="s">
         <v>895</v>
@@ -6752,18 +7401,45 @@
         <f aca="false">IFERROR(J38/F38,"")</f>
         <v>0</v>
       </c>
-      <c r="L38" s="26"/>
-      <c r="M38" s="84" t="n">
-        <f aca="false">IFERROR(L38*181/30/D38,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N38" s="84" t="n">
-        <f aca="false">IFERROR((G38/2)*$C$7*$C$10/(D38*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O38" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K38+M38+N38,"")</f>
-        <v>0</v>
+      <c r="L38" s="28" t="n">
+        <v>823</v>
+      </c>
+      <c r="M38" s="26"/>
+      <c r="N38" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L38/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O38" s="84" t="str">
+        <f aca="false">IFERROR(IF(M38="",N38,M38)*$C$12*181/30/D38,"")</f>
+        <v/>
+      </c>
+      <c r="P38" s="26"/>
+      <c r="Q38" s="84" t="n">
+        <f aca="false">IFERROR(P38*181/30/D38,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R38" s="84" t="n">
+        <f aca="false">IFERROR((G38/2)*(0.374*$C$7+0.356*$C$8+0.27*$C$9)*$C$10/(D38*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S38" s="86" t="str">
+        <f aca="false">IFERROR((0.374*$C$7+0.356*$C$8+0.27*$C$9)/(1-$C$11)+K38+O38+Q38+R38,"")</f>
+        <v/>
+      </c>
+      <c r="T38" s="84" t="n">
+        <v>1.9553</v>
+      </c>
+      <c r="U38" s="86" t="str">
+        <f aca="false">IFERROR(T38-S38,"")</f>
+        <v/>
+      </c>
+      <c r="V38" s="87" t="str">
+        <f aca="false">IFERROR(U38-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W38" s="21" t="str">
+        <f aca="false">IF(U38="","",IF(U38&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6771,7 +7447,7 @@
         <v>22</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>936</v>
+        <v>946</v>
       </c>
       <c r="C39" s="82" t="s">
         <v>895</v>
@@ -6805,18 +7481,45 @@
         <f aca="false">IFERROR(J39/F39,"")</f>
         <v>0</v>
       </c>
-      <c r="L39" s="26"/>
-      <c r="M39" s="84" t="n">
-        <f aca="false">IFERROR(L39*181/30/D39,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N39" s="84" t="n">
-        <f aca="false">IFERROR((G39/2)*$C$7*$C$10/(D39*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O39" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K39+M39+N39,"")</f>
-        <v>0</v>
+      <c r="L39" s="28" t="n">
+        <v>816</v>
+      </c>
+      <c r="M39" s="26"/>
+      <c r="N39" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L39/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O39" s="84" t="str">
+        <f aca="false">IFERROR(IF(M39="",N39,M39)*$C$12*181/30/D39,"")</f>
+        <v/>
+      </c>
+      <c r="P39" s="26"/>
+      <c r="Q39" s="84" t="n">
+        <f aca="false">IFERROR(P39*181/30/D39,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R39" s="84" t="n">
+        <f aca="false">IFERROR((G39/2)*(0.364*$C$7+0.315*$C$8+0.321*$C$9)*$C$10/(D39*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S39" s="86" t="str">
+        <f aca="false">IFERROR((0.364*$C$7+0.315*$C$8+0.321*$C$9)/(1-$C$11)+K39+O39+Q39+R39,"")</f>
+        <v/>
+      </c>
+      <c r="T39" s="84" t="n">
+        <v>1.8966</v>
+      </c>
+      <c r="U39" s="86" t="str">
+        <f aca="false">IFERROR(T39-S39,"")</f>
+        <v/>
+      </c>
+      <c r="V39" s="87" t="str">
+        <f aca="false">IFERROR(U39-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W39" s="21" t="str">
+        <f aca="false">IF(U39="","",IF(U39&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6824,7 +7527,7 @@
         <v>23</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>937</v>
+        <v>947</v>
       </c>
       <c r="C40" s="82" t="s">
         <v>895</v>
@@ -6858,18 +7561,45 @@
         <f aca="false">IFERROR(J40/F40,"")</f>
         <v>0</v>
       </c>
-      <c r="L40" s="26"/>
-      <c r="M40" s="84" t="n">
-        <f aca="false">IFERROR(L40*181/30/D40,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N40" s="84" t="n">
-        <f aca="false">IFERROR((G40/2)*$C$7*$C$10/(D40*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O40" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K40+M40+N40,"")</f>
-        <v>0</v>
+      <c r="L40" s="28" t="n">
+        <v>1025</v>
+      </c>
+      <c r="M40" s="26"/>
+      <c r="N40" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L40/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O40" s="84" t="str">
+        <f aca="false">IFERROR(IF(M40="",N40,M40)*$C$12*181/30/D40,"")</f>
+        <v/>
+      </c>
+      <c r="P40" s="26"/>
+      <c r="Q40" s="84" t="n">
+        <f aca="false">IFERROR(P40*181/30/D40,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R40" s="84" t="n">
+        <f aca="false">IFERROR((G40/2)*(0.514*$C$7+0.31*$C$8+0.176*$C$9)*$C$10/(D40*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S40" s="86" t="str">
+        <f aca="false">IFERROR((0.514*$C$7+0.31*$C$8+0.176*$C$9)/(1-$C$11)+K40+O40+Q40+R40,"")</f>
+        <v/>
+      </c>
+      <c r="T40" s="84" t="n">
+        <v>2.0452</v>
+      </c>
+      <c r="U40" s="86" t="str">
+        <f aca="false">IFERROR(T40-S40,"")</f>
+        <v/>
+      </c>
+      <c r="V40" s="87" t="str">
+        <f aca="false">IFERROR(U40-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W40" s="21" t="str">
+        <f aca="false">IF(U40="","",IF(U40&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6877,7 +7607,7 @@
         <v>24</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>938</v>
+        <v>948</v>
       </c>
       <c r="C41" s="82" t="s">
         <v>895</v>
@@ -6911,18 +7641,45 @@
         <f aca="false">IFERROR(J41/F41,"")</f>
         <v>0</v>
       </c>
-      <c r="L41" s="26"/>
-      <c r="M41" s="84" t="n">
-        <f aca="false">IFERROR(L41*181/30/D41,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N41" s="84" t="n">
-        <f aca="false">IFERROR((G41/2)*$C$7*$C$10/(D41*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O41" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K41+M41+N41,"")</f>
-        <v>0</v>
+      <c r="L41" s="28" t="n">
+        <v>423</v>
+      </c>
+      <c r="M41" s="26"/>
+      <c r="N41" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L41/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O41" s="84" t="str">
+        <f aca="false">IFERROR(IF(M41="",N41,M41)*$C$12*181/30/D41,"")</f>
+        <v/>
+      </c>
+      <c r="P41" s="26"/>
+      <c r="Q41" s="84" t="n">
+        <f aca="false">IFERROR(P41*181/30/D41,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R41" s="84" t="n">
+        <f aca="false">IFERROR((G41/2)*(0.243*$C$7+0.198*$C$8+0.559*$C$9)*$C$10/(D41*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S41" s="86" t="str">
+        <f aca="false">IFERROR((0.243*$C$7+0.198*$C$8+0.559*$C$9)/(1-$C$11)+K41+O41+Q41+R41,"")</f>
+        <v/>
+      </c>
+      <c r="T41" s="84" t="n">
+        <v>1.6339</v>
+      </c>
+      <c r="U41" s="86" t="str">
+        <f aca="false">IFERROR(T41-S41,"")</f>
+        <v/>
+      </c>
+      <c r="V41" s="87" t="str">
+        <f aca="false">IFERROR(U41-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W41" s="21" t="str">
+        <f aca="false">IF(U41="","",IF(U41&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6930,7 +7687,7 @@
         <v>25</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>939</v>
+        <v>949</v>
       </c>
       <c r="C42" s="82" t="s">
         <v>891</v>
@@ -6964,18 +7721,45 @@
         <f aca="false">IFERROR(J42/F42,"")</f>
         <v>0</v>
       </c>
-      <c r="L42" s="26"/>
-      <c r="M42" s="84" t="n">
-        <f aca="false">IFERROR(L42*181/30/D42,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N42" s="84" t="n">
-        <f aca="false">IFERROR((G42/2)*$C$7*$C$10/(D42*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O42" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K42+M42+N42,"")</f>
-        <v>0</v>
+      <c r="L42" s="28" t="n">
+        <v>864</v>
+      </c>
+      <c r="M42" s="26"/>
+      <c r="N42" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L42/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O42" s="84" t="str">
+        <f aca="false">IFERROR(IF(M42="",N42,M42)*$C$12*181/30/D42,"")</f>
+        <v/>
+      </c>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="84" t="n">
+        <f aca="false">IFERROR(P42*181/30/D42,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R42" s="84" t="n">
+        <f aca="false">IFERROR((G42/2)*(0.468*$C$7+0.45*$C$8+0.082*$C$9)*$C$10/(D42*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S42" s="86" t="str">
+        <f aca="false">IFERROR((0.468*$C$7+0.45*$C$8+0.082*$C$9)/(1-$C$11)+K42+O42+Q42+R42,"")</f>
+        <v/>
+      </c>
+      <c r="T42" s="84" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="U42" s="86" t="str">
+        <f aca="false">IFERROR(T42-S42,"")</f>
+        <v/>
+      </c>
+      <c r="V42" s="87" t="str">
+        <f aca="false">IFERROR(U42-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W42" s="21" t="str">
+        <f aca="false">IF(U42="","",IF(U42&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6983,7 +7767,7 @@
         <v>26</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="C43" s="82" t="s">
         <v>897</v>
@@ -7017,18 +7801,45 @@
         <f aca="false">IFERROR(J43/F43,"")</f>
         <v>0</v>
       </c>
-      <c r="L43" s="26"/>
-      <c r="M43" s="84" t="n">
-        <f aca="false">IFERROR(L43*181/30/D43,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N43" s="84" t="n">
-        <f aca="false">IFERROR((G43/2)*$C$7*$C$10/(D43*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O43" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K43+M43+N43,"")</f>
-        <v>0</v>
+      <c r="L43" s="28" t="n">
+        <v>922</v>
+      </c>
+      <c r="M43" s="26"/>
+      <c r="N43" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L43/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O43" s="84" t="str">
+        <f aca="false">IFERROR(IF(M43="",N43,M43)*$C$12*181/30/D43,"")</f>
+        <v/>
+      </c>
+      <c r="P43" s="26"/>
+      <c r="Q43" s="84" t="n">
+        <f aca="false">IFERROR(P43*181/30/D43,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R43" s="84" t="n">
+        <f aca="false">IFERROR((G43/2)*(0.434*$C$7+0.544*$C$8+0.023*$C$9)*$C$10/(D43*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S43" s="86" t="str">
+        <f aca="false">IFERROR((0.434*$C$7+0.544*$C$8+0.023*$C$9)/(1-$C$11)+K43+O43+Q43+R43,"")</f>
+        <v/>
+      </c>
+      <c r="T43" s="84" t="n">
+        <v>2.2401</v>
+      </c>
+      <c r="U43" s="86" t="str">
+        <f aca="false">IFERROR(T43-S43,"")</f>
+        <v/>
+      </c>
+      <c r="V43" s="87" t="str">
+        <f aca="false">IFERROR(U43-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W43" s="21" t="str">
+        <f aca="false">IF(U43="","",IF(U43&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7036,7 +7847,7 @@
         <v>27</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>941</v>
+        <v>951</v>
       </c>
       <c r="C44" s="82" t="s">
         <v>895</v>
@@ -7070,18 +7881,45 @@
         <f aca="false">IFERROR(J44/F44,"")</f>
         <v>0</v>
       </c>
-      <c r="L44" s="26"/>
-      <c r="M44" s="84" t="n">
-        <f aca="false">IFERROR(L44*181/30/D44,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N44" s="84" t="n">
-        <f aca="false">IFERROR((G44/2)*$C$7*$C$10/(D44*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O44" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K44+M44+N44,"")</f>
-        <v>0</v>
+      <c r="L44" s="28" t="n">
+        <v>931</v>
+      </c>
+      <c r="M44" s="26"/>
+      <c r="N44" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L44/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O44" s="84" t="str">
+        <f aca="false">IFERROR(IF(M44="",N44,M44)*$C$12*181/30/D44,"")</f>
+        <v/>
+      </c>
+      <c r="P44" s="26"/>
+      <c r="Q44" s="84" t="n">
+        <f aca="false">IFERROR(P44*181/30/D44,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R44" s="84" t="n">
+        <f aca="false">IFERROR((G44/2)*(0.416*$C$7+0.469*$C$8+0.115*$C$9)*$C$10/(D44*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S44" s="86" t="str">
+        <f aca="false">IFERROR((0.416*$C$7+0.469*$C$8+0.115*$C$9)/(1-$C$11)+K44+O44+Q44+R44,"")</f>
+        <v/>
+      </c>
+      <c r="T44" s="84" t="n">
+        <v>2.1319</v>
+      </c>
+      <c r="U44" s="86" t="str">
+        <f aca="false">IFERROR(T44-S44,"")</f>
+        <v/>
+      </c>
+      <c r="V44" s="87" t="str">
+        <f aca="false">IFERROR(U44-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W44" s="21" t="str">
+        <f aca="false">IF(U44="","",IF(U44&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7089,7 +7927,7 @@
         <v>28</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>942</v>
+        <v>952</v>
       </c>
       <c r="C45" s="82" t="s">
         <v>895</v>
@@ -7123,18 +7961,45 @@
         <f aca="false">IFERROR(J45/F45,"")</f>
         <v>0</v>
       </c>
-      <c r="L45" s="26"/>
-      <c r="M45" s="84" t="n">
-        <f aca="false">IFERROR(L45*181/30/D45,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N45" s="84" t="n">
-        <f aca="false">IFERROR((G45/2)*$C$7*$C$10/(D45*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O45" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K45+M45+N45,"")</f>
-        <v>0</v>
+      <c r="L45" s="28" t="n">
+        <v>913</v>
+      </c>
+      <c r="M45" s="26"/>
+      <c r="N45" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L45/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O45" s="84" t="str">
+        <f aca="false">IFERROR(IF(M45="",N45,M45)*$C$12*181/30/D45,"")</f>
+        <v/>
+      </c>
+      <c r="P45" s="26"/>
+      <c r="Q45" s="84" t="n">
+        <f aca="false">IFERROR(P45*181/30/D45,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R45" s="84" t="n">
+        <f aca="false">IFERROR((G45/2)*(0.561*$C$7+0.439*$C$8+0*$C$9)*$C$10/(D45*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S45" s="86" t="str">
+        <f aca="false">IFERROR((0.561*$C$7+0.439*$C$8+0*$C$9)/(1-$C$11)+K45+O45+Q45+R45,"")</f>
+        <v/>
+      </c>
+      <c r="T45" s="84" t="n">
+        <v>2.2458</v>
+      </c>
+      <c r="U45" s="86" t="str">
+        <f aca="false">IFERROR(T45-S45,"")</f>
+        <v/>
+      </c>
+      <c r="V45" s="87" t="str">
+        <f aca="false">IFERROR(U45-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W45" s="21" t="str">
+        <f aca="false">IF(U45="","",IF(U45&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7142,7 +8007,7 @@
         <v>29</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>943</v>
+        <v>953</v>
       </c>
       <c r="C46" s="82" t="s">
         <v>895</v>
@@ -7176,18 +8041,45 @@
         <f aca="false">IFERROR(J46/F46,"")</f>
         <v>0</v>
       </c>
-      <c r="L46" s="26"/>
-      <c r="M46" s="84" t="n">
-        <f aca="false">IFERROR(L46*181/30/D46,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N46" s="84" t="n">
-        <f aca="false">IFERROR((G46/2)*$C$7*$C$10/(D46*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O46" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K46+M46+N46,"")</f>
-        <v>0</v>
+      <c r="L46" s="28" t="n">
+        <v>938</v>
+      </c>
+      <c r="M46" s="26"/>
+      <c r="N46" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L46/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O46" s="84" t="str">
+        <f aca="false">IFERROR(IF(M46="",N46,M46)*$C$12*181/30/D46,"")</f>
+        <v/>
+      </c>
+      <c r="P46" s="26"/>
+      <c r="Q46" s="84" t="n">
+        <f aca="false">IFERROR(P46*181/30/D46,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R46" s="84" t="n">
+        <f aca="false">IFERROR((G46/2)*(0.523*$C$7+0.31*$C$8+0.167*$C$9)*$C$10/(D46*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S46" s="86" t="str">
+        <f aca="false">IFERROR((0.523*$C$7+0.31*$C$8+0.167*$C$9)/(1-$C$11)+K46+O46+Q46+R46,"")</f>
+        <v/>
+      </c>
+      <c r="T46" s="84" t="n">
+        <v>2.0545</v>
+      </c>
+      <c r="U46" s="86" t="str">
+        <f aca="false">IFERROR(T46-S46,"")</f>
+        <v/>
+      </c>
+      <c r="V46" s="87" t="str">
+        <f aca="false">IFERROR(U46-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W46" s="21" t="str">
+        <f aca="false">IF(U46="","",IF(U46&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7195,7 +8087,7 @@
         <v>30</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>944</v>
+        <v>954</v>
       </c>
       <c r="C47" s="82" t="s">
         <v>897</v>
@@ -7229,18 +8121,45 @@
         <f aca="false">IFERROR(J47/F47,"")</f>
         <v>0</v>
       </c>
-      <c r="L47" s="26"/>
-      <c r="M47" s="84" t="n">
-        <f aca="false">IFERROR(L47*181/30/D47,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N47" s="84" t="n">
-        <f aca="false">IFERROR((G47/2)*$C$7*$C$10/(D47*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O47" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K47+M47+N47,"")</f>
-        <v>0</v>
+      <c r="L47" s="28" t="n">
+        <v>538</v>
+      </c>
+      <c r="M47" s="26"/>
+      <c r="N47" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L47/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O47" s="84" t="str">
+        <f aca="false">IFERROR(IF(M47="",N47,M47)*$C$12*181/30/D47,"")</f>
+        <v/>
+      </c>
+      <c r="P47" s="26"/>
+      <c r="Q47" s="84" t="n">
+        <f aca="false">IFERROR(P47*181/30/D47,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R47" s="84" t="n">
+        <f aca="false">IFERROR((G47/2)*(0.315*$C$7+0.312*$C$8+0.373*$C$9)*$C$10/(D47*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S47" s="86" t="str">
+        <f aca="false">IFERROR((0.315*$C$7+0.312*$C$8+0.373*$C$9)/(1-$C$11)+K47+O47+Q47+R47,"")</f>
+        <v/>
+      </c>
+      <c r="T47" s="84" t="n">
+        <v>1.8426</v>
+      </c>
+      <c r="U47" s="86" t="str">
+        <f aca="false">IFERROR(T47-S47,"")</f>
+        <v/>
+      </c>
+      <c r="V47" s="87" t="str">
+        <f aca="false">IFERROR(U47-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W47" s="21" t="str">
+        <f aca="false">IF(U47="","",IF(U47&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7248,7 +8167,7 @@
         <v>31</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>945</v>
+        <v>955</v>
       </c>
       <c r="C48" s="82" t="s">
         <v>895</v>
@@ -7282,18 +8201,45 @@
         <f aca="false">IFERROR(J48/F48,"")</f>
         <v>0</v>
       </c>
-      <c r="L48" s="26"/>
-      <c r="M48" s="84" t="n">
-        <f aca="false">IFERROR(L48*181/30/D48,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N48" s="84" t="n">
-        <f aca="false">IFERROR((G48/2)*$C$7*$C$10/(D48*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O48" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K48+M48+N48,"")</f>
-        <v>0</v>
+      <c r="L48" s="28" t="n">
+        <v>537</v>
+      </c>
+      <c r="M48" s="26"/>
+      <c r="N48" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L48/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O48" s="84" t="str">
+        <f aca="false">IFERROR(IF(M48="",N48,M48)*$C$12*181/30/D48,"")</f>
+        <v/>
+      </c>
+      <c r="P48" s="26"/>
+      <c r="Q48" s="84" t="n">
+        <f aca="false">IFERROR(P48*181/30/D48,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R48" s="84" t="n">
+        <f aca="false">IFERROR((G48/2)*(0.462*$C$7+0.432*$C$8+0.106*$C$9)*$C$10/(D48*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S48" s="86" t="str">
+        <f aca="false">IFERROR((0.462*$C$7+0.432*$C$8+0.106*$C$9)/(1-$C$11)+K48+O48+Q48+R48,"")</f>
+        <v/>
+      </c>
+      <c r="T48" s="84" t="n">
+        <v>2.1356</v>
+      </c>
+      <c r="U48" s="86" t="str">
+        <f aca="false">IFERROR(T48-S48,"")</f>
+        <v/>
+      </c>
+      <c r="V48" s="87" t="str">
+        <f aca="false">IFERROR(U48-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W48" s="21" t="str">
+        <f aca="false">IF(U48="","",IF(U48&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7301,7 +8247,7 @@
         <v>32</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>946</v>
+        <v>956</v>
       </c>
       <c r="C49" s="82" t="s">
         <v>895</v>
@@ -7335,18 +8281,45 @@
         <f aca="false">IFERROR(J49/F49,"")</f>
         <v>0</v>
       </c>
-      <c r="L49" s="26"/>
-      <c r="M49" s="84" t="n">
-        <f aca="false">IFERROR(L49*181/30/D49,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N49" s="84" t="n">
-        <f aca="false">IFERROR((G49/2)*$C$7*$C$10/(D49*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O49" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K49+M49+N49,"")</f>
-        <v>0</v>
+      <c r="L49" s="28" t="n">
+        <v>680</v>
+      </c>
+      <c r="M49" s="26"/>
+      <c r="N49" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L49/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O49" s="84" t="str">
+        <f aca="false">IFERROR(IF(M49="",N49,M49)*$C$12*181/30/D49,"")</f>
+        <v/>
+      </c>
+      <c r="P49" s="26"/>
+      <c r="Q49" s="84" t="n">
+        <f aca="false">IFERROR(P49*181/30/D49,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R49" s="84" t="n">
+        <f aca="false">IFERROR((G49/2)*(0.35*$C$7+0.301*$C$8+0.349*$C$9)*$C$10/(D49*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S49" s="86" t="str">
+        <f aca="false">IFERROR((0.35*$C$7+0.301*$C$8+0.349*$C$9)/(1-$C$11)+K49+O49+Q49+R49,"")</f>
+        <v/>
+      </c>
+      <c r="T49" s="84" t="n">
+        <v>1.8657</v>
+      </c>
+      <c r="U49" s="86" t="str">
+        <f aca="false">IFERROR(T49-S49,"")</f>
+        <v/>
+      </c>
+      <c r="V49" s="87" t="str">
+        <f aca="false">IFERROR(U49-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W49" s="21" t="str">
+        <f aca="false">IF(U49="","",IF(U49&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7354,7 +8327,7 @@
         <v>33</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>947</v>
+        <v>957</v>
       </c>
       <c r="C50" s="82" t="s">
         <v>891</v>
@@ -7388,18 +8361,45 @@
         <f aca="false">IFERROR(J50/F50,"")</f>
         <v>0</v>
       </c>
-      <c r="L50" s="26"/>
-      <c r="M50" s="84" t="n">
-        <f aca="false">IFERROR(L50*181/30/D50,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N50" s="84" t="n">
-        <f aca="false">IFERROR((G50/2)*$C$7*$C$10/(D50*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O50" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K50+M50+N50,"")</f>
-        <v>0</v>
+      <c r="L50" s="28" t="n">
+        <v>469</v>
+      </c>
+      <c r="M50" s="26"/>
+      <c r="N50" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L50/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O50" s="84" t="str">
+        <f aca="false">IFERROR(IF(M50="",N50,M50)*$C$12*181/30/D50,"")</f>
+        <v/>
+      </c>
+      <c r="P50" s="26"/>
+      <c r="Q50" s="84" t="n">
+        <f aca="false">IFERROR(P50*181/30/D50,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R50" s="84" t="n">
+        <f aca="false">IFERROR((G50/2)*(0.51*$C$7+0.49*$C$8+0*$C$9)*$C$10/(D50*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S50" s="86" t="str">
+        <f aca="false">IFERROR((0.51*$C$7+0.49*$C$8+0*$C$9)/(1-$C$11)+K50+O50+Q50+R50,"")</f>
+        <v/>
+      </c>
+      <c r="T50" s="84" t="n">
+        <v>2.2535</v>
+      </c>
+      <c r="U50" s="86" t="str">
+        <f aca="false">IFERROR(T50-S50,"")</f>
+        <v/>
+      </c>
+      <c r="V50" s="87" t="str">
+        <f aca="false">IFERROR(U50-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W50" s="21" t="str">
+        <f aca="false">IF(U50="","",IF(U50&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7407,7 +8407,7 @@
         <v>34</v>
       </c>
       <c r="B51" s="24" t="s">
-        <v>948</v>
+        <v>958</v>
       </c>
       <c r="C51" s="82" t="s">
         <v>895</v>
@@ -7441,18 +8441,45 @@
         <f aca="false">IFERROR(J51/F51,"")</f>
         <v>0</v>
       </c>
-      <c r="L51" s="26"/>
-      <c r="M51" s="84" t="n">
-        <f aca="false">IFERROR(L51*181/30/D51,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N51" s="84" t="n">
-        <f aca="false">IFERROR((G51/2)*$C$7*$C$10/(D51*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O51" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K51+M51+N51,"")</f>
-        <v>0</v>
+      <c r="L51" s="28" t="n">
+        <v>807</v>
+      </c>
+      <c r="M51" s="26"/>
+      <c r="N51" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L51/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O51" s="84" t="str">
+        <f aca="false">IFERROR(IF(M51="",N51,M51)*$C$12*181/30/D51,"")</f>
+        <v/>
+      </c>
+      <c r="P51" s="26"/>
+      <c r="Q51" s="84" t="n">
+        <f aca="false">IFERROR(P51*181/30/D51,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R51" s="84" t="n">
+        <f aca="false">IFERROR((G51/2)*(0.54*$C$7+0.46*$C$8+0*$C$9)*$C$10/(D51*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S51" s="86" t="str">
+        <f aca="false">IFERROR((0.54*$C$7+0.46*$C$8+0*$C$9)/(1-$C$11)+K51+O51+Q51+R51,"")</f>
+        <v/>
+      </c>
+      <c r="T51" s="84" t="n">
+        <v>2.249</v>
+      </c>
+      <c r="U51" s="86" t="str">
+        <f aca="false">IFERROR(T51-S51,"")</f>
+        <v/>
+      </c>
+      <c r="V51" s="87" t="str">
+        <f aca="false">IFERROR(U51-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W51" s="21" t="str">
+        <f aca="false">IF(U51="","",IF(U51&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7460,10 +8487,10 @@
         <v>35</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>949</v>
+        <v>959</v>
       </c>
       <c r="C52" s="82" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="D52" s="28" t="n">
         <v>2879227</v>
@@ -7494,18 +8521,45 @@
         <f aca="false">IFERROR(J52/F52,"")</f>
         <v>0</v>
       </c>
-      <c r="L52" s="26"/>
-      <c r="M52" s="84" t="n">
-        <f aca="false">IFERROR(L52*181/30/D52,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N52" s="84" t="n">
-        <f aca="false">IFERROR((G52/2)*$C$7*$C$10/(D52*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O52" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K52+M52+N52,"")</f>
-        <v>0</v>
+      <c r="L52" s="28" t="n">
+        <v>441</v>
+      </c>
+      <c r="M52" s="26"/>
+      <c r="N52" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L52/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O52" s="84" t="str">
+        <f aca="false">IFERROR(IF(M52="",N52,M52)*$C$12*181/30/D52,"")</f>
+        <v/>
+      </c>
+      <c r="P52" s="26"/>
+      <c r="Q52" s="84" t="n">
+        <f aca="false">IFERROR(P52*181/30/D52,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R52" s="84" t="n">
+        <f aca="false">IFERROR((G52/2)*(0.347*$C$7+0.26*$C$8+0.392*$C$9)*$C$10/(D52*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S52" s="86" t="str">
+        <f aca="false">IFERROR((0.347*$C$7+0.26*$C$8+0.392*$C$9)/(1-$C$11)+K52+O52+Q52+R52,"")</f>
+        <v/>
+      </c>
+      <c r="T52" s="84" t="n">
+        <v>1.8131</v>
+      </c>
+      <c r="U52" s="86" t="str">
+        <f aca="false">IFERROR(T52-S52,"")</f>
+        <v/>
+      </c>
+      <c r="V52" s="87" t="str">
+        <f aca="false">IFERROR(U52-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W52" s="21" t="str">
+        <f aca="false">IF(U52="","",IF(U52&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7513,7 +8567,7 @@
         <v>36</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>950</v>
+        <v>960</v>
       </c>
       <c r="C53" s="82" t="s">
         <v>895</v>
@@ -7547,18 +8601,45 @@
         <f aca="false">IFERROR(J53/F53,"")</f>
         <v>0</v>
       </c>
-      <c r="L53" s="26"/>
-      <c r="M53" s="84" t="n">
-        <f aca="false">IFERROR(L53*181/30/D53,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N53" s="84" t="n">
-        <f aca="false">IFERROR((G53/2)*$C$7*$C$10/(D53*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O53" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K53+M53+N53,"")</f>
-        <v>0</v>
+      <c r="L53" s="28" t="n">
+        <v>685</v>
+      </c>
+      <c r="M53" s="26"/>
+      <c r="N53" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L53/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O53" s="84" t="str">
+        <f aca="false">IFERROR(IF(M53="",N53,M53)*$C$12*181/30/D53,"")</f>
+        <v/>
+      </c>
+      <c r="P53" s="26"/>
+      <c r="Q53" s="84" t="n">
+        <f aca="false">IFERROR(P53*181/30/D53,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R53" s="84" t="n">
+        <f aca="false">IFERROR((G53/2)*(0.537*$C$7+0.386*$C$8+0.077*$C$9)*$C$10/(D53*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S53" s="86" t="str">
+        <f aca="false">IFERROR((0.537*$C$7+0.386*$C$8+0.077*$C$9)/(1-$C$11)+K53+O53+Q53+R53,"")</f>
+        <v/>
+      </c>
+      <c r="T53" s="84" t="n">
+        <v>2.1586</v>
+      </c>
+      <c r="U53" s="86" t="str">
+        <f aca="false">IFERROR(T53-S53,"")</f>
+        <v/>
+      </c>
+      <c r="V53" s="87" t="str">
+        <f aca="false">IFERROR(U53-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W53" s="21" t="str">
+        <f aca="false">IF(U53="","",IF(U53&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7566,7 +8647,7 @@
         <v>37</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>951</v>
+        <v>961</v>
       </c>
       <c r="C54" s="82" t="s">
         <v>895</v>
@@ -7600,18 +8681,45 @@
         <f aca="false">IFERROR(J54/F54,"")</f>
         <v>0</v>
       </c>
-      <c r="L54" s="26"/>
-      <c r="M54" s="84" t="n">
-        <f aca="false">IFERROR(L54*181/30/D54,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N54" s="84" t="n">
-        <f aca="false">IFERROR((G54/2)*$C$7*$C$10/(D54*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O54" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K54+M54+N54,"")</f>
-        <v>0</v>
+      <c r="L54" s="28" t="n">
+        <v>586</v>
+      </c>
+      <c r="M54" s="26"/>
+      <c r="N54" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L54/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O54" s="84" t="str">
+        <f aca="false">IFERROR(IF(M54="",N54,M54)*$C$12*181/30/D54,"")</f>
+        <v/>
+      </c>
+      <c r="P54" s="26"/>
+      <c r="Q54" s="84" t="n">
+        <f aca="false">IFERROR(P54*181/30/D54,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R54" s="84" t="n">
+        <f aca="false">IFERROR((G54/2)*(0.455*$C$7+0.31*$C$8+0.236*$C$9)*$C$10/(D54*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S54" s="86" t="str">
+        <f aca="false">IFERROR((0.455*$C$7+0.31*$C$8+0.236*$C$9)/(1-$C$11)+K54+O54+Q54+R54,"")</f>
+        <v/>
+      </c>
+      <c r="T54" s="84" t="n">
+        <v>1.9856</v>
+      </c>
+      <c r="U54" s="86" t="str">
+        <f aca="false">IFERROR(T54-S54,"")</f>
+        <v/>
+      </c>
+      <c r="V54" s="87" t="str">
+        <f aca="false">IFERROR(U54-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W54" s="21" t="str">
+        <f aca="false">IF(U54="","",IF(U54&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7619,10 +8727,10 @@
         <v>38</v>
       </c>
       <c r="B55" s="24" t="s">
-        <v>952</v>
+        <v>962</v>
       </c>
       <c r="C55" s="82" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="D55" s="28" t="n">
         <v>2723713</v>
@@ -7653,18 +8761,45 @@
         <f aca="false">IFERROR(J55/F55,"")</f>
         <v>0</v>
       </c>
-      <c r="L55" s="26"/>
-      <c r="M55" s="84" t="n">
-        <f aca="false">IFERROR(L55*181/30/D55,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N55" s="84" t="n">
-        <f aca="false">IFERROR((G55/2)*$C$7*$C$10/(D55*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O55" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K55+M55+N55,"")</f>
-        <v>0</v>
+      <c r="L55" s="28" t="n">
+        <v>591</v>
+      </c>
+      <c r="M55" s="26"/>
+      <c r="N55" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L55/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O55" s="84" t="str">
+        <f aca="false">IFERROR(IF(M55="",N55,M55)*$C$12*181/30/D55,"")</f>
+        <v/>
+      </c>
+      <c r="P55" s="26"/>
+      <c r="Q55" s="84" t="n">
+        <f aca="false">IFERROR(P55*181/30/D55,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R55" s="84" t="n">
+        <f aca="false">IFERROR((G55/2)*(0.538*$C$7+0.396*$C$8+0.066*$C$9)*$C$10/(D55*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S55" s="86" t="str">
+        <f aca="false">IFERROR((0.538*$C$7+0.396*$C$8+0.066*$C$9)/(1-$C$11)+K55+O55+Q55+R55,"")</f>
+        <v/>
+      </c>
+      <c r="T55" s="84" t="n">
+        <v>2.1714</v>
+      </c>
+      <c r="U55" s="86" t="str">
+        <f aca="false">IFERROR(T55-S55,"")</f>
+        <v/>
+      </c>
+      <c r="V55" s="87" t="str">
+        <f aca="false">IFERROR(U55-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W55" s="21" t="str">
+        <f aca="false">IF(U55="","",IF(U55&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7672,10 +8807,10 @@
         <v>39</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>953</v>
+        <v>963</v>
       </c>
       <c r="C56" s="82" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="D56" s="28" t="n">
         <v>2625098</v>
@@ -7706,18 +8841,45 @@
         <f aca="false">IFERROR(J56/F56,"")</f>
         <v>0</v>
       </c>
-      <c r="L56" s="26"/>
-      <c r="M56" s="84" t="n">
-        <f aca="false">IFERROR(L56*181/30/D56,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N56" s="84" t="n">
-        <f aca="false">IFERROR((G56/2)*$C$7*$C$10/(D56*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O56" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K56+M56+N56,"")</f>
-        <v>0</v>
+      <c r="L56" s="28" t="n">
+        <v>650</v>
+      </c>
+      <c r="M56" s="26"/>
+      <c r="N56" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L56/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O56" s="84" t="str">
+        <f aca="false">IFERROR(IF(M56="",N56,M56)*$C$12*181/30/D56,"")</f>
+        <v/>
+      </c>
+      <c r="P56" s="26"/>
+      <c r="Q56" s="84" t="n">
+        <f aca="false">IFERROR(P56*181/30/D56,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R56" s="84" t="n">
+        <f aca="false">IFERROR((G56/2)*(0.37*$C$7+0.446*$C$8+0.184*$C$9)*$C$10/(D56*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S56" s="86" t="str">
+        <f aca="false">IFERROR((0.37*$C$7+0.446*$C$8+0.184*$C$9)/(1-$C$11)+K56+O56+Q56+R56,"")</f>
+        <v/>
+      </c>
+      <c r="T56" s="84" t="n">
+        <v>2.0574</v>
+      </c>
+      <c r="U56" s="86" t="str">
+        <f aca="false">IFERROR(T56-S56,"")</f>
+        <v/>
+      </c>
+      <c r="V56" s="87" t="str">
+        <f aca="false">IFERROR(U56-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W56" s="21" t="str">
+        <f aca="false">IF(U56="","",IF(U56&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7725,7 +8887,7 @@
         <v>40</v>
       </c>
       <c r="B57" s="24" t="s">
-        <v>954</v>
+        <v>964</v>
       </c>
       <c r="C57" s="82" t="s">
         <v>893</v>
@@ -7759,18 +8921,45 @@
         <f aca="false">IFERROR(J57/F57,"")</f>
         <v>0</v>
       </c>
-      <c r="L57" s="26"/>
-      <c r="M57" s="84" t="n">
-        <f aca="false">IFERROR(L57*181/30/D57,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N57" s="84" t="n">
-        <f aca="false">IFERROR((G57/2)*$C$7*$C$10/(D57*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O57" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K57+M57+N57,"")</f>
-        <v>0</v>
+      <c r="L57" s="28" t="n">
+        <v>402</v>
+      </c>
+      <c r="M57" s="26"/>
+      <c r="N57" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L57/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O57" s="84" t="str">
+        <f aca="false">IFERROR(IF(M57="",N57,M57)*$C$12*181/30/D57,"")</f>
+        <v/>
+      </c>
+      <c r="P57" s="26"/>
+      <c r="Q57" s="84" t="n">
+        <f aca="false">IFERROR(P57*181/30/D57,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R57" s="84" t="n">
+        <f aca="false">IFERROR((G57/2)*(0.394*$C$7+0.404*$C$8+0.201*$C$9)*$C$10/(D57*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S57" s="86" t="str">
+        <f aca="false">IFERROR((0.394*$C$7+0.404*$C$8+0.201*$C$9)/(1-$C$11)+K57+O57+Q57+R57,"")</f>
+        <v/>
+      </c>
+      <c r="T57" s="84" t="n">
+        <v>2.0314</v>
+      </c>
+      <c r="U57" s="86" t="str">
+        <f aca="false">IFERROR(T57-S57,"")</f>
+        <v/>
+      </c>
+      <c r="V57" s="87" t="str">
+        <f aca="false">IFERROR(U57-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W57" s="21" t="str">
+        <f aca="false">IF(U57="","",IF(U57&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7778,7 +8967,7 @@
         <v>41</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>955</v>
+        <v>965</v>
       </c>
       <c r="C58" s="82" t="s">
         <v>895</v>
@@ -7812,18 +9001,45 @@
         <f aca="false">IFERROR(J58/F58,"")</f>
         <v>0</v>
       </c>
-      <c r="L58" s="26"/>
-      <c r="M58" s="84" t="n">
-        <f aca="false">IFERROR(L58*181/30/D58,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N58" s="84" t="n">
-        <f aca="false">IFERROR((G58/2)*$C$7*$C$10/(D58*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O58" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K58+M58+N58,"")</f>
-        <v>0</v>
+      <c r="L58" s="28" t="n">
+        <v>456</v>
+      </c>
+      <c r="M58" s="26"/>
+      <c r="N58" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L58/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O58" s="84" t="str">
+        <f aca="false">IFERROR(IF(M58="",N58,M58)*$C$12*181/30/D58,"")</f>
+        <v/>
+      </c>
+      <c r="P58" s="26"/>
+      <c r="Q58" s="84" t="n">
+        <f aca="false">IFERROR(P58*181/30/D58,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R58" s="84" t="n">
+        <f aca="false">IFERROR((G58/2)*(0.488*$C$7+0.512*$C$8+0*$C$9)*$C$10/(D58*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S58" s="86" t="str">
+        <f aca="false">IFERROR((0.488*$C$7+0.512*$C$8+0*$C$9)/(1-$C$11)+K58+O58+Q58+R58,"")</f>
+        <v/>
+      </c>
+      <c r="T58" s="84" t="n">
+        <v>2.2568</v>
+      </c>
+      <c r="U58" s="86" t="str">
+        <f aca="false">IFERROR(T58-S58,"")</f>
+        <v/>
+      </c>
+      <c r="V58" s="87" t="str">
+        <f aca="false">IFERROR(U58-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W58" s="21" t="str">
+        <f aca="false">IF(U58="","",IF(U58&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7831,7 +9047,7 @@
         <v>42</v>
       </c>
       <c r="B59" s="24" t="s">
-        <v>956</v>
+        <v>966</v>
       </c>
       <c r="C59" s="82" t="s">
         <v>895</v>
@@ -7865,18 +9081,45 @@
         <f aca="false">IFERROR(J59/F59,"")</f>
         <v>0</v>
       </c>
-      <c r="L59" s="26"/>
-      <c r="M59" s="84" t="n">
-        <f aca="false">IFERROR(L59*181/30/D59,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N59" s="84" t="n">
-        <f aca="false">IFERROR((G59/2)*$C$7*$C$10/(D59*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O59" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K59+M59+N59,"")</f>
-        <v>0</v>
+      <c r="L59" s="28" t="n">
+        <v>455</v>
+      </c>
+      <c r="M59" s="26"/>
+      <c r="N59" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L59/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O59" s="84" t="str">
+        <f aca="false">IFERROR(IF(M59="",N59,M59)*$C$12*181/30/D59,"")</f>
+        <v/>
+      </c>
+      <c r="P59" s="26"/>
+      <c r="Q59" s="84" t="n">
+        <f aca="false">IFERROR(P59*181/30/D59,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R59" s="84" t="n">
+        <f aca="false">IFERROR((G59/2)*(0.511*$C$7+0.472*$C$8+0.017*$C$9)*$C$10/(D59*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S59" s="86" t="str">
+        <f aca="false">IFERROR((0.511*$C$7+0.472*$C$8+0.017*$C$9)/(1-$C$11)+K59+O59+Q59+R59,"")</f>
+        <v/>
+      </c>
+      <c r="T59" s="84" t="n">
+        <v>2.2333</v>
+      </c>
+      <c r="U59" s="86" t="str">
+        <f aca="false">IFERROR(T59-S59,"")</f>
+        <v/>
+      </c>
+      <c r="V59" s="87" t="str">
+        <f aca="false">IFERROR(U59-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W59" s="21" t="str">
+        <f aca="false">IF(U59="","",IF(U59&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7884,7 +9127,7 @@
         <v>43</v>
       </c>
       <c r="B60" s="24" t="s">
-        <v>957</v>
+        <v>967</v>
       </c>
       <c r="C60" s="82" t="s">
         <v>895</v>
@@ -7918,18 +9161,45 @@
         <f aca="false">IFERROR(J60/F60,"")</f>
         <v>0</v>
       </c>
-      <c r="L60" s="26"/>
-      <c r="M60" s="84" t="n">
-        <f aca="false">IFERROR(L60*181/30/D60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N60" s="84" t="n">
-        <f aca="false">IFERROR((G60/2)*$C$7*$C$10/(D60*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O60" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K60+M60+N60,"")</f>
-        <v>0</v>
+      <c r="L60" s="28" t="n">
+        <v>333</v>
+      </c>
+      <c r="M60" s="26"/>
+      <c r="N60" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L60/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O60" s="84" t="str">
+        <f aca="false">IFERROR(IF(M60="",N60,M60)*$C$12*181/30/D60,"")</f>
+        <v/>
+      </c>
+      <c r="P60" s="26"/>
+      <c r="Q60" s="84" t="n">
+        <f aca="false">IFERROR(P60*181/30/D60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R60" s="84" t="n">
+        <f aca="false">IFERROR((G60/2)*(0.449*$C$7+0.259*$C$8+0.292*$C$9)*$C$10/(D60*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S60" s="86" t="str">
+        <f aca="false">IFERROR((0.449*$C$7+0.259*$C$8+0.292*$C$9)/(1-$C$11)+K60+O60+Q60+R60,"")</f>
+        <v/>
+      </c>
+      <c r="T60" s="84" t="n">
+        <v>1.9181</v>
+      </c>
+      <c r="U60" s="86" t="str">
+        <f aca="false">IFERROR(T60-S60,"")</f>
+        <v/>
+      </c>
+      <c r="V60" s="87" t="str">
+        <f aca="false">IFERROR(U60-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W60" s="21" t="str">
+        <f aca="false">IF(U60="","",IF(U60&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7937,7 +9207,7 @@
         <v>44</v>
       </c>
       <c r="B61" s="24" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="C61" s="82" t="s">
         <v>897</v>
@@ -7971,18 +9241,45 @@
         <f aca="false">IFERROR(J61/F61,"")</f>
         <v>0</v>
       </c>
-      <c r="L61" s="26"/>
-      <c r="M61" s="84" t="n">
-        <f aca="false">IFERROR(L61*181/30/D61,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N61" s="84" t="n">
-        <f aca="false">IFERROR((G61/2)*$C$7*$C$10/(D61*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O61" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K61+M61+N61,"")</f>
-        <v>0</v>
+      <c r="L61" s="28" t="n">
+        <v>952</v>
+      </c>
+      <c r="M61" s="26"/>
+      <c r="N61" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L61/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O61" s="84" t="str">
+        <f aca="false">IFERROR(IF(M61="",N61,M61)*$C$12*181/30/D61,"")</f>
+        <v/>
+      </c>
+      <c r="P61" s="26"/>
+      <c r="Q61" s="84" t="n">
+        <f aca="false">IFERROR(P61*181/30/D61,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R61" s="84" t="n">
+        <f aca="false">IFERROR((G61/2)*(0.503*$C$7+0.394*$C$8+0.103*$C$9)*$C$10/(D61*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S61" s="86" t="str">
+        <f aca="false">IFERROR((0.503*$C$7+0.394*$C$8+0.103*$C$9)/(1-$C$11)+K61+O61+Q61+R61,"")</f>
+        <v/>
+      </c>
+      <c r="T61" s="84" t="n">
+        <v>2.133</v>
+      </c>
+      <c r="U61" s="86" t="str">
+        <f aca="false">IFERROR(T61-S61,"")</f>
+        <v/>
+      </c>
+      <c r="V61" s="87" t="str">
+        <f aca="false">IFERROR(U61-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W61" s="21" t="str">
+        <f aca="false">IF(U61="","",IF(U61&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7990,10 +9287,10 @@
         <v>45</v>
       </c>
       <c r="B62" s="24" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="C62" s="82" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="D62" s="28" t="n">
         <v>1428185</v>
@@ -8024,18 +9321,45 @@
         <f aca="false">IFERROR(J62/F62,"")</f>
         <v>0</v>
       </c>
-      <c r="L62" s="26"/>
-      <c r="M62" s="84" t="n">
-        <f aca="false">IFERROR(L62*181/30/D62,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N62" s="84" t="n">
-        <f aca="false">IFERROR((G62/2)*$C$7*$C$10/(D62*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O62" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K62+M62+N62,"")</f>
-        <v>0</v>
+      <c r="L62" s="28" t="n">
+        <v>327</v>
+      </c>
+      <c r="M62" s="26"/>
+      <c r="N62" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L62/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O62" s="84" t="str">
+        <f aca="false">IFERROR(IF(M62="",N62,M62)*$C$12*181/30/D62,"")</f>
+        <v/>
+      </c>
+      <c r="P62" s="26"/>
+      <c r="Q62" s="84" t="n">
+        <f aca="false">IFERROR(P62*181/30/D62,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R62" s="84" t="n">
+        <f aca="false">IFERROR((G62/2)*(0.576*$C$7+0.347*$C$8+0.077*$C$9)*$C$10/(D62*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S62" s="86" t="str">
+        <f aca="false">IFERROR((0.576*$C$7+0.347*$C$8+0.077*$C$9)/(1-$C$11)+K62+O62+Q62+R62,"")</f>
+        <v/>
+      </c>
+      <c r="T62" s="84" t="n">
+        <v>2.1527</v>
+      </c>
+      <c r="U62" s="86" t="str">
+        <f aca="false">IFERROR(T62-S62,"")</f>
+        <v/>
+      </c>
+      <c r="V62" s="87" t="str">
+        <f aca="false">IFERROR(U62-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W62" s="21" t="str">
+        <f aca="false">IF(U62="","",IF(U62&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8043,10 +9367,10 @@
         <v>46</v>
       </c>
       <c r="B63" s="24" t="s">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="C63" s="82" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="D63" s="28" t="n">
         <v>1280084</v>
@@ -8077,18 +9401,45 @@
         <f aca="false">IFERROR(J63/F63,"")</f>
         <v>0</v>
       </c>
-      <c r="L63" s="26"/>
-      <c r="M63" s="84" t="n">
-        <f aca="false">IFERROR(L63*181/30/D63,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N63" s="84" t="n">
-        <f aca="false">IFERROR((G63/2)*$C$7*$C$10/(D63*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O63" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K63+M63+N63,"")</f>
-        <v>0</v>
+      <c r="L63" s="28" t="n">
+        <v>281</v>
+      </c>
+      <c r="M63" s="26"/>
+      <c r="N63" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L63/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O63" s="84" t="str">
+        <f aca="false">IFERROR(IF(M63="",N63,M63)*$C$12*181/30/D63,"")</f>
+        <v/>
+      </c>
+      <c r="P63" s="26"/>
+      <c r="Q63" s="84" t="n">
+        <f aca="false">IFERROR(P63*181/30/D63,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R63" s="84" t="n">
+        <f aca="false">IFERROR((G63/2)*(0.427*$C$7+0.393*$C$8+0.18*$C$9)*$C$10/(D63*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S63" s="86" t="str">
+        <f aca="false">IFERROR((0.427*$C$7+0.393*$C$8+0.18*$C$9)/(1-$C$11)+K63+O63+Q63+R63,"")</f>
+        <v/>
+      </c>
+      <c r="T63" s="84" t="n">
+        <v>2.0535</v>
+      </c>
+      <c r="U63" s="86" t="str">
+        <f aca="false">IFERROR(T63-S63,"")</f>
+        <v/>
+      </c>
+      <c r="V63" s="87" t="str">
+        <f aca="false">IFERROR(U63-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W63" s="21" t="str">
+        <f aca="false">IF(U63="","",IF(U63&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8096,7 +9447,7 @@
         <v>47</v>
       </c>
       <c r="B64" s="24" t="s">
-        <v>961</v>
+        <v>971</v>
       </c>
       <c r="C64" s="82" t="s">
         <v>897</v>
@@ -8130,18 +9481,45 @@
         <f aca="false">IFERROR(J64/F64,"")</f>
         <v>0</v>
       </c>
-      <c r="L64" s="26"/>
-      <c r="M64" s="84" t="n">
-        <f aca="false">IFERROR(L64*181/30/D64,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N64" s="84" t="n">
-        <f aca="false">IFERROR((G64/2)*$C$7*$C$10/(D64*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O64" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K64+M64+N64,"")</f>
-        <v>0</v>
+      <c r="L64" s="28" t="n">
+        <v>800</v>
+      </c>
+      <c r="M64" s="26"/>
+      <c r="N64" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L64/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O64" s="84" t="str">
+        <f aca="false">IFERROR(IF(M64="",N64,M64)*$C$12*181/30/D64,"")</f>
+        <v/>
+      </c>
+      <c r="P64" s="26"/>
+      <c r="Q64" s="84" t="n">
+        <f aca="false">IFERROR(P64*181/30/D64,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R64" s="84" t="n">
+        <f aca="false">IFERROR((G64/2)*(0.447*$C$7+0.497*$C$8+0.056*$C$9)*$C$10/(D64*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S64" s="86" t="str">
+        <f aca="false">IFERROR((0.447*$C$7+0.497*$C$8+0.056*$C$9)/(1-$C$11)+K64+O64+Q64+R64,"")</f>
+        <v/>
+      </c>
+      <c r="T64" s="84" t="n">
+        <v>2.1969</v>
+      </c>
+      <c r="U64" s="86" t="str">
+        <f aca="false">IFERROR(T64-S64,"")</f>
+        <v/>
+      </c>
+      <c r="V64" s="87" t="str">
+        <f aca="false">IFERROR(U64-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W64" s="21" t="str">
+        <f aca="false">IF(U64="","",IF(U64&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8149,10 +9527,10 @@
         <v>48</v>
       </c>
       <c r="B65" s="24" t="s">
-        <v>962</v>
+        <v>972</v>
       </c>
       <c r="C65" s="82" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="D65" s="28" t="n">
         <v>1248165</v>
@@ -8183,18 +9561,45 @@
         <f aca="false">IFERROR(J65/F65,"")</f>
         <v>0</v>
       </c>
-      <c r="L65" s="26"/>
-      <c r="M65" s="84" t="n">
-        <f aca="false">IFERROR(L65*181/30/D65,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N65" s="84" t="n">
-        <f aca="false">IFERROR((G65/2)*$C$7*$C$10/(D65*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O65" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K65+M65+N65,"")</f>
-        <v>0</v>
+      <c r="L65" s="28" t="n">
+        <v>408</v>
+      </c>
+      <c r="M65" s="26"/>
+      <c r="N65" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L65/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O65" s="84" t="str">
+        <f aca="false">IFERROR(IF(M65="",N65,M65)*$C$12*181/30/D65,"")</f>
+        <v/>
+      </c>
+      <c r="P65" s="26"/>
+      <c r="Q65" s="84" t="n">
+        <f aca="false">IFERROR(P65*181/30/D65,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R65" s="84" t="n">
+        <f aca="false">IFERROR((G65/2)*(0.459*$C$7+0.348*$C$8+0.194*$C$9)*$C$10/(D65*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S65" s="86" t="str">
+        <f aca="false">IFERROR((0.459*$C$7+0.348*$C$8+0.194*$C$9)/(1-$C$11)+K65+O65+Q65+R65,"")</f>
+        <v/>
+      </c>
+      <c r="T65" s="84" t="n">
+        <v>2.0346</v>
+      </c>
+      <c r="U65" s="86" t="str">
+        <f aca="false">IFERROR(T65-S65,"")</f>
+        <v/>
+      </c>
+      <c r="V65" s="87" t="str">
+        <f aca="false">IFERROR(U65-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W65" s="21" t="str">
+        <f aca="false">IF(U65="","",IF(U65&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8202,7 +9607,7 @@
         <v>49</v>
       </c>
       <c r="B66" s="24" t="s">
-        <v>963</v>
+        <v>973</v>
       </c>
       <c r="C66" s="82" t="s">
         <v>895</v>
@@ -8236,18 +9641,41 @@
         <f aca="false">IFERROR(J66/F66,"")</f>
         <v>0</v>
       </c>
-      <c r="L66" s="26"/>
-      <c r="M66" s="84" t="n">
-        <f aca="false">IFERROR(L66*181/30/D66,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N66" s="84" t="n">
+      <c r="L66" s="21"/>
+      <c r="M66" s="26"/>
+      <c r="N66" s="28" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L66/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O66" s="84" t="str">
+        <f aca="false">IFERROR(IF(M66="",N66,M66)*$C$12*181/30/D66,"")</f>
+        <v/>
+      </c>
+      <c r="P66" s="26"/>
+      <c r="Q66" s="84" t="n">
+        <f aca="false">IFERROR(P66*181/30/D66,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R66" s="84" t="n">
         <f aca="false">IFERROR((G66/2)*$C$7*$C$10/(D66*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="O66" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K66+M66+N66,"")</f>
-        <v>0</v>
+      <c r="S66" s="86" t="str">
+        <f aca="false">IFERROR($C$7/(1-$C$11)+K66+O66+Q66+R66,"")</f>
+        <v/>
+      </c>
+      <c r="T66" s="21"/>
+      <c r="U66" s="86" t="str">
+        <f aca="false">IFERROR(T66-S66,"")</f>
+        <v/>
+      </c>
+      <c r="V66" s="87" t="str">
+        <f aca="false">IFERROR(U66-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W66" s="21" t="str">
+        <f aca="false">IF(U66="","",IF(U66&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8255,10 +9683,10 @@
         <v>50</v>
       </c>
       <c r="B67" s="24" t="s">
-        <v>964</v>
+        <v>974</v>
       </c>
       <c r="C67" s="82" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D67" s="28" t="n">
         <v>96032</v>
@@ -8289,24 +9717,51 @@
         <f aca="false">IFERROR(J67/F67,"")</f>
         <v>0</v>
       </c>
-      <c r="L67" s="26"/>
-      <c r="M67" s="84" t="n">
-        <f aca="false">IFERROR(L67*181/30/D67,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N67" s="84" t="n">
-        <f aca="false">IFERROR((G67/2)*$C$7*$C$10/(D67*365/181),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O67" s="85" t="n">
-        <f aca="false">IFERROR($C$7*(1+$C$11)+K67+M67+N67,"")</f>
-        <v>0</v>
+      <c r="L67" s="28" t="n">
+        <v>154</v>
+      </c>
+      <c r="M67" s="26"/>
+      <c r="N67" s="85" t="str">
+        <f aca="false">IFERROR(ROUNDUP(L67/$C$13,0),"")</f>
+        <v/>
+      </c>
+      <c r="O67" s="84" t="str">
+        <f aca="false">IFERROR(IF(M67="",N67,M67)*$C$12*181/30/D67,"")</f>
+        <v/>
+      </c>
+      <c r="P67" s="26"/>
+      <c r="Q67" s="84" t="n">
+        <f aca="false">IFERROR(P67*181/30/D67,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R67" s="84" t="n">
+        <f aca="false">IFERROR((G67/2)*(0.503*$C$7+0.33*$C$8+0.167*$C$9)*$C$10/(D67*365/181),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S67" s="86" t="str">
+        <f aca="false">IFERROR((0.503*$C$7+0.33*$C$8+0.167*$C$9)/(1-$C$11)+K67+O67+Q67+R67,"")</f>
+        <v/>
+      </c>
+      <c r="T67" s="84" t="n">
+        <v>2.0575</v>
+      </c>
+      <c r="U67" s="86" t="str">
+        <f aca="false">IFERROR(T67-S67,"")</f>
+        <v/>
+      </c>
+      <c r="V67" s="87" t="str">
+        <f aca="false">IFERROR(U67-$C$14,"")</f>
+        <v/>
+      </c>
+      <c r="W67" s="21" t="str">
+        <f aca="false">IF(U67="","",IF(U67&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
+        <v/>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="32"/>
       <c r="B68" s="33" t="s">
-        <v>965</v>
+        <v>975</v>
       </c>
       <c r="C68" s="32"/>
       <c r="D68" s="34" t="n">
@@ -8329,20 +9784,33 @@
       <c r="I68" s="32"/>
       <c r="J68" s="32"/>
       <c r="K68" s="32"/>
-      <c r="L68" s="32"/>
-      <c r="M68" s="32"/>
-      <c r="N68" s="32"/>
-      <c r="O68" s="86" t="n">
-        <f aca="false">IFERROR(SUMPRODUCT(D18:D67,O18:O67)/D68,"")</f>
+      <c r="L68" s="34" t="n">
+        <f aca="false">SUM(L18:L67)</f>
+        <v>54672</v>
+      </c>
+      <c r="M68" s="34" t="n">
+        <f aca="false">SUM(M18:M67)</f>
+        <v>0</v>
+      </c>
+      <c r="N68" s="34" t="n">
+        <f aca="false">SUM(N18:N67)</f>
+        <v>0</v>
+      </c>
+      <c r="O68" s="32"/>
+      <c r="P68" s="32"/>
+      <c r="Q68" s="32"/>
+      <c r="R68" s="32"/>
+      <c r="S68" s="88" t="n">
+        <f aca="false">IFERROR(SUMPRODUCT(D18:D67,S18:S67)/D68,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="52" t="s">
-        <v>966</v>
+        <v>976</v>
       </c>
       <c r="C70" s="53" t="s">
-        <v>967</v>
+        <v>977</v>
       </c>
       <c r="D70" s="53"/>
       <c r="E70" s="53"/>
@@ -8356,13 +9824,20 @@
       <c r="M70" s="53"/>
       <c r="N70" s="53"/>
       <c r="O70" s="53"/>
+      <c r="P70" s="53"/>
+      <c r="Q70" s="53"/>
+      <c r="R70" s="53"/>
+      <c r="S70" s="53"/>
+      <c r="T70" s="53"/>
+      <c r="U70" s="53"/>
+      <c r="V70" s="53"/>
     </row>
     <row r="71" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="52" t="s">
-        <v>968</v>
+        <v>978</v>
       </c>
       <c r="C71" s="53" t="s">
-        <v>969</v>
+        <v>979</v>
       </c>
       <c r="D71" s="53"/>
       <c r="E71" s="53"/>
@@ -8376,13 +9851,20 @@
       <c r="M71" s="53"/>
       <c r="N71" s="53"/>
       <c r="O71" s="53"/>
+      <c r="P71" s="53"/>
+      <c r="Q71" s="53"/>
+      <c r="R71" s="53"/>
+      <c r="S71" s="53"/>
+      <c r="T71" s="53"/>
+      <c r="U71" s="53"/>
+      <c r="V71" s="53"/>
     </row>
     <row r="72" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="54" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="C72" s="53" t="s">
-        <v>971</v>
+        <v>981</v>
       </c>
       <c r="D72" s="53"/>
       <c r="E72" s="53"/>
@@ -8396,13 +9878,20 @@
       <c r="M72" s="53"/>
       <c r="N72" s="53"/>
       <c r="O72" s="53"/>
+      <c r="P72" s="53"/>
+      <c r="Q72" s="53"/>
+      <c r="R72" s="53"/>
+      <c r="S72" s="53"/>
+      <c r="T72" s="53"/>
+      <c r="U72" s="53"/>
+      <c r="V72" s="53"/>
     </row>
     <row r="73" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="52" t="s">
-        <v>972</v>
+        <v>982</v>
       </c>
       <c r="C73" s="53" t="s">
-        <v>973</v>
+        <v>983</v>
       </c>
       <c r="D73" s="53"/>
       <c r="E73" s="53"/>
@@ -8416,13 +9905,20 @@
       <c r="M73" s="53"/>
       <c r="N73" s="53"/>
       <c r="O73" s="53"/>
+      <c r="P73" s="53"/>
+      <c r="Q73" s="53"/>
+      <c r="R73" s="53"/>
+      <c r="S73" s="53"/>
+      <c r="T73" s="53"/>
+      <c r="U73" s="53"/>
+      <c r="V73" s="53"/>
     </row>
     <row r="74" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B74" s="54" t="s">
-        <v>974</v>
+      <c r="B74" s="52" t="s">
+        <v>984</v>
       </c>
       <c r="C74" s="53" t="s">
-        <v>975</v>
+        <v>985</v>
       </c>
       <c r="D74" s="53"/>
       <c r="E74" s="53"/>
@@ -8436,18 +9932,109 @@
       <c r="M74" s="53"/>
       <c r="N74" s="53"/>
       <c r="O74" s="53"/>
+      <c r="P74" s="53"/>
+      <c r="Q74" s="53"/>
+      <c r="R74" s="53"/>
+      <c r="S74" s="53"/>
+      <c r="T74" s="53"/>
+      <c r="U74" s="53"/>
+      <c r="V74" s="53"/>
+    </row>
+    <row r="75" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B75" s="52" t="s">
+        <v>986</v>
+      </c>
+      <c r="C75" s="53" t="s">
+        <v>987</v>
+      </c>
+      <c r="D75" s="53"/>
+      <c r="E75" s="53"/>
+      <c r="F75" s="53"/>
+      <c r="G75" s="53"/>
+      <c r="H75" s="53"/>
+      <c r="I75" s="53"/>
+      <c r="J75" s="53"/>
+      <c r="K75" s="53"/>
+      <c r="L75" s="53"/>
+      <c r="M75" s="53"/>
+      <c r="N75" s="53"/>
+      <c r="O75" s="53"/>
+      <c r="P75" s="53"/>
+      <c r="Q75" s="53"/>
+      <c r="R75" s="53"/>
+      <c r="S75" s="53"/>
+      <c r="T75" s="53"/>
+      <c r="U75" s="53"/>
+      <c r="V75" s="53"/>
+    </row>
+    <row r="76" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B76" s="54" t="s">
+        <v>988</v>
+      </c>
+      <c r="C76" s="53" t="s">
+        <v>989</v>
+      </c>
+      <c r="D76" s="53"/>
+      <c r="E76" s="53"/>
+      <c r="F76" s="53"/>
+      <c r="G76" s="53"/>
+      <c r="H76" s="53"/>
+      <c r="I76" s="53"/>
+      <c r="J76" s="53"/>
+      <c r="K76" s="53"/>
+      <c r="L76" s="53"/>
+      <c r="M76" s="53"/>
+      <c r="N76" s="53"/>
+      <c r="O76" s="53"/>
+      <c r="P76" s="53"/>
+      <c r="Q76" s="53"/>
+      <c r="R76" s="53"/>
+      <c r="S76" s="53"/>
+      <c r="T76" s="53"/>
+      <c r="U76" s="53"/>
+      <c r="V76" s="53"/>
+    </row>
+    <row r="77" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B77" s="54" t="s">
+        <v>990</v>
+      </c>
+      <c r="C77" s="53" t="s">
+        <v>991</v>
+      </c>
+      <c r="D77" s="53"/>
+      <c r="E77" s="53"/>
+      <c r="F77" s="53"/>
+      <c r="G77" s="53"/>
+      <c r="H77" s="53"/>
+      <c r="I77" s="53"/>
+      <c r="J77" s="53"/>
+      <c r="K77" s="53"/>
+      <c r="L77" s="53"/>
+      <c r="M77" s="53"/>
+      <c r="N77" s="53"/>
+      <c r="O77" s="53"/>
+      <c r="P77" s="53"/>
+      <c r="Q77" s="53"/>
+      <c r="R77" s="53"/>
+      <c r="S77" s="53"/>
+      <c r="T77" s="53"/>
+      <c r="U77" s="53"/>
+      <c r="V77" s="53"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="12">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
-    <mergeCell ref="C3:O3"/>
-    <mergeCell ref="C4:O4"/>
-    <mergeCell ref="C70:O70"/>
-    <mergeCell ref="C71:O71"/>
-    <mergeCell ref="C72:O72"/>
-    <mergeCell ref="C73:O73"/>
-    <mergeCell ref="C74:O74"/>
+    <mergeCell ref="C3:V3"/>
+    <mergeCell ref="C4:V4"/>
+    <mergeCell ref="C70:V70"/>
+    <mergeCell ref="C71:V71"/>
+    <mergeCell ref="C72:V72"/>
+    <mergeCell ref="C73:V73"/>
+    <mergeCell ref="C74:V74"/>
+    <mergeCell ref="C75:V75"/>
+    <mergeCell ref="C76:V76"/>
+    <mergeCell ref="C77:V77"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8485,7 +10072,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>976</v>
+        <v>992</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8504,7 +10091,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>977</v>
+        <v>993</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8535,86 +10122,86 @@
         <v>55</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>978</v>
+        <v>994</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>979</v>
+        <v>995</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>980</v>
+        <v>996</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>981</v>
+        <v>997</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>58</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>982</v>
+        <v>998</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>983</v>
+        <v>999</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>59</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>984</v>
+        <v>1000</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>985</v>
+        <v>1001</v>
       </c>
       <c r="O3" s="15" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="87" t="s">
-        <v>986</v>
-      </c>
-      <c r="B4" s="88" t="s">
-        <v>987</v>
-      </c>
-      <c r="C4" s="87" t="s">
+      <c r="A4" s="89" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B4" s="90" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C4" s="89" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="88" t="s">
-        <v>988</v>
-      </c>
-      <c r="E4" s="87" t="n">
+      <c r="D4" s="90" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E4" s="89" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="87" t="s">
-        <v>989</v>
-      </c>
-      <c r="G4" s="88" t="s">
-        <v>990</v>
-      </c>
-      <c r="H4" s="87" t="n">
+      <c r="F4" s="89" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G4" s="90" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H4" s="89" t="n">
         <v>20</v>
       </c>
-      <c r="I4" s="87" t="n">
+      <c r="I4" s="89" t="n">
         <f aca="false">IF(H4="","",H4-E4)</f>
         <v>14</v>
       </c>
-      <c r="J4" s="89" t="n">
+      <c r="J4" s="91" t="n">
         <f aca="false">IFERROR(IF(H4="","",(H4-E4)/E4),"")</f>
         <v>2.33333333333333</v>
       </c>
-      <c r="K4" s="88" t="s">
-        <v>991</v>
-      </c>
-      <c r="L4" s="87" t="s">
+      <c r="K4" s="90" t="s">
+        <v>1007</v>
+      </c>
+      <c r="L4" s="89" t="s">
         <v>78</v>
       </c>
-      <c r="M4" s="88" t="s">
-        <v>992</v>
-      </c>
-      <c r="N4" s="88" t="s">
-        <v>993</v>
-      </c>
-      <c r="O4" s="87" t="s">
-        <v>994</v>
+      <c r="M4" s="90" t="s">
+        <v>1008</v>
+      </c>
+      <c r="N4" s="90" t="s">
+        <v>1009</v>
+      </c>
+      <c r="O4" s="89" t="s">
+        <v>1010</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8630,17 +10217,17 @@
       <c r="D5" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="90" t="n">
+      <c r="E5" s="92" t="n">
         <v>1271</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>995</v>
+        <v>1011</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>996</v>
-      </c>
-      <c r="H5" s="91"/>
-      <c r="I5" s="90" t="str">
+        <v>1012</v>
+      </c>
+      <c r="H5" s="93"/>
+      <c r="I5" s="92" t="str">
         <f aca="false">IF(H5="","",H5-E5)</f>
         <v/>
       </c>
@@ -8648,15 +10235,15 @@
         <f aca="false">IFERROR(IF(H5="","",(H5-E5)/E5),"")</f>
         <v/>
       </c>
-      <c r="K5" s="92"/>
+      <c r="K5" s="94"/>
       <c r="L5" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M5" s="92"/>
+      <c r="M5" s="94"/>
       <c r="N5" s="16" t="s">
-        <v>997</v>
-      </c>
-      <c r="O5" s="93"/>
+        <v>1013</v>
+      </c>
+      <c r="O5" s="95"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="n">
@@ -8671,17 +10258,17 @@
       <c r="D6" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="90" t="n">
+      <c r="E6" s="92" t="n">
         <v>25</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>998</v>
+        <v>1014</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>999</v>
-      </c>
-      <c r="H6" s="91"/>
-      <c r="I6" s="90" t="str">
+        <v>1015</v>
+      </c>
+      <c r="H6" s="93"/>
+      <c r="I6" s="92" t="str">
         <f aca="false">IF(H6="","",H6-E6)</f>
         <v/>
       </c>
@@ -8689,15 +10276,15 @@
         <f aca="false">IFERROR(IF(H6="","",(H6-E6)/E6),"")</f>
         <v/>
       </c>
-      <c r="K6" s="92"/>
+      <c r="K6" s="94"/>
       <c r="L6" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M6" s="92"/>
+      <c r="M6" s="94"/>
       <c r="N6" s="16" t="s">
-        <v>1000</v>
-      </c>
-      <c r="O6" s="93"/>
+        <v>1016</v>
+      </c>
+      <c r="O6" s="95"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="n">
@@ -8712,17 +10299,17 @@
       <c r="D7" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="90" t="n">
+      <c r="E7" s="92" t="n">
         <v>39</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>990</v>
-      </c>
-      <c r="H7" s="91"/>
-      <c r="I7" s="90" t="str">
+        <v>1006</v>
+      </c>
+      <c r="H7" s="93"/>
+      <c r="I7" s="92" t="str">
         <f aca="false">IF(H7="","",H7-E7)</f>
         <v/>
       </c>
@@ -8730,15 +10317,15 @@
         <f aca="false">IFERROR(IF(H7="","",(H7-E7)/E7),"")</f>
         <v/>
       </c>
-      <c r="K7" s="92"/>
+      <c r="K7" s="94"/>
       <c r="L7" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M7" s="92"/>
+      <c r="M7" s="94"/>
       <c r="N7" s="16" t="s">
-        <v>1002</v>
-      </c>
-      <c r="O7" s="93"/>
+        <v>1018</v>
+      </c>
+      <c r="O7" s="95"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="n">
@@ -8753,17 +10340,17 @@
       <c r="D8" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="90" t="n">
+      <c r="E8" s="92" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>1003</v>
+        <v>1019</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>1004</v>
-      </c>
-      <c r="H8" s="91"/>
-      <c r="I8" s="90" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H8" s="93"/>
+      <c r="I8" s="92" t="str">
         <f aca="false">IF(H8="","",H8-E8)</f>
         <v/>
       </c>
@@ -8771,40 +10358,40 @@
         <f aca="false">IFERROR(IF(H8="","",(H8-E8)/E8),"")</f>
         <v/>
       </c>
-      <c r="K8" s="92"/>
+      <c r="K8" s="94"/>
       <c r="L8" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="92"/>
+      <c r="M8" s="94"/>
       <c r="N8" s="16" t="s">
-        <v>1005</v>
-      </c>
-      <c r="O8" s="93"/>
+        <v>1021</v>
+      </c>
+      <c r="O8" s="95"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1006</v>
+        <v>1022</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>53</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>1007</v>
-      </c>
-      <c r="E9" s="90" t="n">
+        <v>1023</v>
+      </c>
+      <c r="E9" s="92" t="n">
         <v>0.28</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>1008</v>
+        <v>1024</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>1009</v>
-      </c>
-      <c r="H9" s="91"/>
-      <c r="I9" s="90" t="str">
+        <v>1025</v>
+      </c>
+      <c r="H9" s="93"/>
+      <c r="I9" s="92" t="str">
         <f aca="false">IF(H9="","",H9-E9)</f>
         <v/>
       </c>
@@ -8812,22 +10399,22 @@
         <f aca="false">IFERROR(IF(H9="","",(H9-E9)/E9),"")</f>
         <v/>
       </c>
-      <c r="K9" s="92"/>
+      <c r="K9" s="94"/>
       <c r="L9" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="M9" s="92"/>
+      <c r="M9" s="94"/>
       <c r="N9" s="16" t="s">
-        <v>1010</v>
-      </c>
-      <c r="O9" s="93"/>
+        <v>1026</v>
+      </c>
+      <c r="O9" s="95"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1011</v>
+        <v>1027</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>53</v>
@@ -8835,17 +10422,17 @@
       <c r="D10" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="E10" s="90" t="n">
+      <c r="E10" s="92" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>1013</v>
-      </c>
-      <c r="H10" s="91"/>
-      <c r="I10" s="90" t="str">
+        <v>1029</v>
+      </c>
+      <c r="H10" s="93"/>
+      <c r="I10" s="92" t="str">
         <f aca="false">IF(H10="","",H10-E10)</f>
         <v/>
       </c>
@@ -8853,15 +10440,15 @@
         <f aca="false">IFERROR(IF(H10="","",(H10-E10)/E10),"")</f>
         <v/>
       </c>
-      <c r="K10" s="92"/>
+      <c r="K10" s="94"/>
       <c r="L10" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M10" s="92"/>
+      <c r="M10" s="94"/>
       <c r="N10" s="16" t="s">
-        <v>1014</v>
-      </c>
-      <c r="O10" s="93"/>
+        <v>1030</v>
+      </c>
+      <c r="O10" s="95"/>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="n">
@@ -8874,19 +10461,19 @@
         <v>95</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E11" s="90" t="n">
+        <v>1031</v>
+      </c>
+      <c r="E11" s="92" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>1016</v>
+        <v>1032</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>1017</v>
-      </c>
-      <c r="H11" s="91"/>
-      <c r="I11" s="90" t="str">
+        <v>1033</v>
+      </c>
+      <c r="H11" s="93"/>
+      <c r="I11" s="92" t="str">
         <f aca="false">IF(H11="","",H11-E11)</f>
         <v/>
       </c>
@@ -8894,15 +10481,15 @@
         <f aca="false">IFERROR(IF(H11="","",(H11-E11)/E11),"")</f>
         <v/>
       </c>
-      <c r="K11" s="92"/>
+      <c r="K11" s="94"/>
       <c r="L11" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="M11" s="92"/>
+      <c r="M11" s="94"/>
       <c r="N11" s="16" t="s">
-        <v>1018</v>
-      </c>
-      <c r="O11" s="93"/>
+        <v>1034</v>
+      </c>
+      <c r="O11" s="95"/>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="n">
@@ -8917,17 +10504,17 @@
       <c r="D12" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="90" t="n">
+      <c r="E12" s="92" t="n">
         <v>31</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>1019</v>
+        <v>1035</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>1020</v>
-      </c>
-      <c r="H12" s="91"/>
-      <c r="I12" s="90" t="str">
+        <v>1036</v>
+      </c>
+      <c r="H12" s="93"/>
+      <c r="I12" s="92" t="str">
         <f aca="false">IF(H12="","",H12-E12)</f>
         <v/>
       </c>
@@ -8935,15 +10522,15 @@
         <f aca="false">IFERROR(IF(H12="","",(H12-E12)/E12),"")</f>
         <v/>
       </c>
-      <c r="K12" s="92"/>
+      <c r="K12" s="94"/>
       <c r="L12" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M12" s="92"/>
+      <c r="M12" s="94"/>
       <c r="N12" s="16" t="s">
-        <v>1021</v>
-      </c>
-      <c r="O12" s="93"/>
+        <v>1037</v>
+      </c>
+      <c r="O12" s="95"/>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="n">
@@ -8958,17 +10545,17 @@
       <c r="D13" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="E13" s="90" t="n">
+      <c r="E13" s="92" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>1022</v>
+        <v>1038</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>1023</v>
-      </c>
-      <c r="H13" s="91"/>
-      <c r="I13" s="90" t="str">
+        <v>1039</v>
+      </c>
+      <c r="H13" s="93"/>
+      <c r="I13" s="92" t="str">
         <f aca="false">IF(H13="","",H13-E13)</f>
         <v/>
       </c>
@@ -8976,15 +10563,15 @@
         <f aca="false">IFERROR(IF(H13="","",(H13-E13)/E13),"")</f>
         <v/>
       </c>
-      <c r="K13" s="92"/>
+      <c r="K13" s="94"/>
       <c r="L13" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M13" s="92"/>
+      <c r="M13" s="94"/>
       <c r="N13" s="16" t="s">
-        <v>1024</v>
-      </c>
-      <c r="O13" s="93"/>
+        <v>1040</v>
+      </c>
+      <c r="O13" s="95"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="n">
@@ -8999,17 +10586,17 @@
       <c r="D14" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="E14" s="90" t="n">
+      <c r="E14" s="92" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>1025</v>
+        <v>1041</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>1026</v>
-      </c>
-      <c r="H14" s="91"/>
-      <c r="I14" s="90" t="str">
+        <v>1042</v>
+      </c>
+      <c r="H14" s="93"/>
+      <c r="I14" s="92" t="str">
         <f aca="false">IF(H14="","",H14-E14)</f>
         <v/>
       </c>
@@ -9017,15 +10604,15 @@
         <f aca="false">IFERROR(IF(H14="","",(H14-E14)/E14),"")</f>
         <v/>
       </c>
-      <c r="K14" s="92"/>
+      <c r="K14" s="94"/>
       <c r="L14" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="92"/>
+      <c r="M14" s="94"/>
       <c r="N14" s="16" t="s">
-        <v>1027</v>
-      </c>
-      <c r="O14" s="93"/>
+        <v>1043</v>
+      </c>
+      <c r="O14" s="95"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="n">
@@ -9038,19 +10625,19 @@
         <v>52</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>988</v>
-      </c>
-      <c r="E15" s="90" t="n">
+        <v>1004</v>
+      </c>
+      <c r="E15" s="92" t="n">
         <v>6</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>1016</v>
+        <v>1032</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>1028</v>
-      </c>
-      <c r="H15" s="91"/>
-      <c r="I15" s="90" t="str">
+        <v>1044</v>
+      </c>
+      <c r="H15" s="93"/>
+      <c r="I15" s="92" t="str">
         <f aca="false">IF(H15="","",H15-E15)</f>
         <v/>
       </c>
@@ -9058,15 +10645,15 @@
         <f aca="false">IFERROR(IF(H15="","",(H15-E15)/E15),"")</f>
         <v/>
       </c>
-      <c r="K15" s="92"/>
+      <c r="K15" s="94"/>
       <c r="L15" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M15" s="92"/>
+      <c r="M15" s="94"/>
       <c r="N15" s="16" t="s">
-        <v>1029</v>
-      </c>
-      <c r="O15" s="93"/>
+        <v>1045</v>
+      </c>
+      <c r="O15" s="95"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="n">
@@ -9079,19 +10666,19 @@
         <v>52</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>1030</v>
-      </c>
-      <c r="E16" s="90" t="n">
+        <v>1046</v>
+      </c>
+      <c r="E16" s="92" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>1031</v>
+        <v>1047</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>1032</v>
-      </c>
-      <c r="H16" s="91"/>
-      <c r="I16" s="90" t="str">
+        <v>1048</v>
+      </c>
+      <c r="H16" s="93"/>
+      <c r="I16" s="92" t="str">
         <f aca="false">IF(H16="","",H16-E16)</f>
         <v/>
       </c>
@@ -9099,31 +10686,31 @@
         <f aca="false">IFERROR(IF(H16="","",(H16-E16)/E16),"")</f>
         <v/>
       </c>
-      <c r="K16" s="92"/>
+      <c r="K16" s="94"/>
       <c r="L16" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M16" s="92"/>
+      <c r="M16" s="94"/>
       <c r="N16" s="16" t="s">
-        <v>1033</v>
-      </c>
-      <c r="O16" s="93"/>
+        <v>1049</v>
+      </c>
+      <c r="O16" s="95"/>
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C18" s="94" t="s">
-        <v>1035</v>
-      </c>
-      <c r="D18" s="94"/>
-      <c r="E18" s="94"/>
-      <c r="F18" s="94"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="94"/>
-      <c r="J18" s="94"/>
-      <c r="K18" s="94"/>
+        <v>1050</v>
+      </c>
+      <c r="C18" s="96" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D18" s="96"/>
+      <c r="E18" s="96"/>
+      <c r="F18" s="96"/>
+      <c r="G18" s="96"/>
+      <c r="H18" s="96"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="96"/>
+      <c r="K18" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -9175,7 +10762,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1036</v>
+        <v>1052</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -9196,52 +10783,52 @@
         <v>50</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>985</v>
+        <v>1001</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>978</v>
+        <v>994</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>1037</v>
+        <v>1053</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1038</v>
+        <v>1054</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1039</v>
+        <v>1055</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1040</v>
+        <v>1056</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>981</v>
+        <v>997</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>1041</v>
+        <v>1057</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>1042</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="95" t="n">
+      <c r="A4" s="97" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="96" t="s">
-        <v>997</v>
-      </c>
-      <c r="D4" s="97" t="n">
+      <c r="C4" s="98" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D4" s="99" t="n">
         <f aca="false">'الخطة التنفيذية'!E5</f>
         <v>1271</v>
       </c>
-      <c r="E4" s="91"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="97" t="str">
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="99" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H5="","",'الخطة التنفيذية'!H5)</f>
         <v/>
       </c>
@@ -9255,24 +10842,24 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="95" t="n">
+      <c r="A5" s="97" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="96" t="s">
-        <v>1000</v>
-      </c>
-      <c r="D5" s="97" t="n">
+      <c r="C5" s="98" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D5" s="99" t="n">
         <f aca="false">'الخطة التنفيذية'!E6</f>
         <v>25</v>
       </c>
-      <c r="E5" s="91"/>
-      <c r="F5" s="91"/>
-      <c r="G5" s="91"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="97" t="str">
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="93"/>
+      <c r="I5" s="99" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H6="","",'الخطة التنفيذية'!H6)</f>
         <v/>
       </c>
@@ -9286,24 +10873,24 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="95" t="n">
+      <c r="A6" s="97" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="96" t="s">
-        <v>1002</v>
-      </c>
-      <c r="D6" s="97" t="n">
+      <c r="C6" s="98" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D6" s="99" t="n">
         <f aca="false">'الخطة التنفيذية'!E7</f>
         <v>39</v>
       </c>
-      <c r="E6" s="91"/>
-      <c r="F6" s="91"/>
-      <c r="G6" s="91"/>
-      <c r="H6" s="91"/>
-      <c r="I6" s="97" t="str">
+      <c r="E6" s="93"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="99" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H7="","",'الخطة التنفيذية'!H7)</f>
         <v/>
       </c>
@@ -9317,24 +10904,24 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="95" t="n">
+      <c r="A7" s="97" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="96" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D7" s="97" t="n">
+      <c r="C7" s="98" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D7" s="99" t="n">
         <f aca="false">'الخطة التنفيذية'!E8</f>
         <v>0</v>
       </c>
-      <c r="E7" s="91"/>
-      <c r="F7" s="91"/>
-      <c r="G7" s="91"/>
-      <c r="H7" s="91"/>
-      <c r="I7" s="97" t="str">
+      <c r="E7" s="93"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="99" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H8="","",'الخطة التنفيذية'!H8)</f>
         <v/>
       </c>
@@ -9348,24 +10935,24 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="95" t="n">
+      <c r="A8" s="97" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C8" s="96" t="s">
-        <v>1010</v>
-      </c>
-      <c r="D8" s="97" t="n">
+        <v>1022</v>
+      </c>
+      <c r="C8" s="98" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D8" s="99" t="n">
         <f aca="false">'الخطة التنفيذية'!E9</f>
         <v>0.28</v>
       </c>
-      <c r="E8" s="91"/>
-      <c r="F8" s="91"/>
-      <c r="G8" s="91"/>
-      <c r="H8" s="91"/>
-      <c r="I8" s="97" t="str">
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="99" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H9="","",'الخطة التنفيذية'!H9)</f>
         <v/>
       </c>
@@ -9379,24 +10966,24 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="95" t="n">
+      <c r="A9" s="97" t="n">
         <v>6</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C9" s="96" t="s">
-        <v>1014</v>
-      </c>
-      <c r="D9" s="97" t="n">
+        <v>1027</v>
+      </c>
+      <c r="C9" s="98" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D9" s="99" t="n">
         <f aca="false">'الخطة التنفيذية'!E10</f>
         <v>0</v>
       </c>
-      <c r="E9" s="91"/>
-      <c r="F9" s="91"/>
-      <c r="G9" s="91"/>
-      <c r="H9" s="91"/>
-      <c r="I9" s="97" t="str">
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="99" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H10="","",'الخطة التنفيذية'!H10)</f>
         <v/>
       </c>
@@ -9410,24 +10997,24 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="95" t="n">
+      <c r="A10" s="97" t="n">
         <v>7</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="96" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D10" s="97" t="n">
+      <c r="C10" s="98" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D10" s="99" t="n">
         <f aca="false">'الخطة التنفيذية'!E11</f>
         <v>0</v>
       </c>
-      <c r="E10" s="91"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="91"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="97" t="str">
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="99" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H11="","",'الخطة التنفيذية'!H11)</f>
         <v/>
       </c>
@@ -9441,24 +11028,24 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="95" t="n">
+      <c r="A11" s="97" t="n">
         <v>8</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="96" t="s">
-        <v>1021</v>
-      </c>
-      <c r="D11" s="97" t="n">
+      <c r="C11" s="98" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D11" s="99" t="n">
         <f aca="false">'الخطة التنفيذية'!E12</f>
         <v>31</v>
       </c>
-      <c r="E11" s="91"/>
-      <c r="F11" s="91"/>
-      <c r="G11" s="91"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="97" t="str">
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="99" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H12="","",'الخطة التنفيذية'!H12)</f>
         <v/>
       </c>
@@ -9472,24 +11059,24 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="95" t="n">
+      <c r="A12" s="97" t="n">
         <v>9</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="C12" s="96" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D12" s="97" t="n">
+      <c r="C12" s="98" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D12" s="99" t="n">
         <f aca="false">'الخطة التنفيذية'!E13</f>
         <v>0</v>
       </c>
-      <c r="E12" s="91"/>
-      <c r="F12" s="91"/>
-      <c r="G12" s="91"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="97" t="str">
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="99" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H13="","",'الخطة التنفيذية'!H13)</f>
         <v/>
       </c>
@@ -9503,24 +11090,24 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="95" t="n">
+      <c r="A13" s="97" t="n">
         <v>10</v>
       </c>
       <c r="B13" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="96" t="s">
-        <v>1027</v>
-      </c>
-      <c r="D13" s="97" t="n">
+      <c r="C13" s="98" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D13" s="99" t="n">
         <f aca="false">'الخطة التنفيذية'!E14</f>
         <v>0</v>
       </c>
-      <c r="E13" s="91"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="97" t="str">
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="99" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H14="","",'الخطة التنفيذية'!H14)</f>
         <v/>
       </c>
@@ -9534,24 +11121,24 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="95" t="n">
+      <c r="A14" s="97" t="n">
         <v>11</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="96" t="s">
-        <v>1029</v>
-      </c>
-      <c r="D14" s="97" t="n">
+      <c r="C14" s="98" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D14" s="99" t="n">
         <f aca="false">'الخطة التنفيذية'!E15</f>
         <v>6</v>
       </c>
-      <c r="E14" s="91"/>
-      <c r="F14" s="91"/>
-      <c r="G14" s="91"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="97" t="str">
+      <c r="E14" s="93"/>
+      <c r="F14" s="93"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="99" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H15="","",'الخطة التنفيذية'!H15)</f>
         <v/>
       </c>
@@ -9565,24 +11152,24 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="95" t="n">
+      <c r="A15" s="97" t="n">
         <v>12</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="96" t="s">
-        <v>1033</v>
-      </c>
-      <c r="D15" s="97" t="n">
+      <c r="C15" s="98" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D15" s="99" t="n">
         <f aca="false">'الخطة التنفيذية'!E16</f>
         <v>0</v>
       </c>
-      <c r="E15" s="91"/>
-      <c r="F15" s="91"/>
-      <c r="G15" s="91"/>
-      <c r="H15" s="91"/>
-      <c r="I15" s="97" t="str">
+      <c r="E15" s="93"/>
+      <c r="F15" s="93"/>
+      <c r="G15" s="93"/>
+      <c r="H15" s="93"/>
+      <c r="I15" s="99" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H16="","",'الخطة التنفيذية'!H16)</f>
         <v/>
       </c>
@@ -9634,7 +11221,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1043</v>
+        <v>1059</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9652,7 +11239,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1044</v>
+        <v>1060</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -9673,34 +11260,34 @@
         <v>49</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>1045</v>
+        <v>1061</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>50</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>1046</v>
+        <v>1062</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>59</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>984</v>
+        <v>1000</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1047</v>
+        <v>1063</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1048</v>
+        <v>1064</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="J3" s="15" t="s">
         <v>60</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>1050</v>
+        <v>1066</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>679</v>
@@ -9709,561 +11296,561 @@
         <v>383</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>1051</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="87" t="s">
-        <v>986</v>
-      </c>
-      <c r="B4" s="88" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C4" s="87" t="s">
+      <c r="A4" s="89" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B4" s="90" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C4" s="89" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="87" t="s">
+      <c r="D4" s="89" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="87" t="s">
+      <c r="E4" s="89" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="87" t="s">
-        <v>992</v>
-      </c>
-      <c r="G4" s="98" t="n">
+      <c r="F4" s="89" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G4" s="100" t="n">
         <v>46235</v>
       </c>
-      <c r="H4" s="98" t="n">
+      <c r="H4" s="100" t="n">
         <v>46326</v>
       </c>
-      <c r="I4" s="87" t="n">
+      <c r="I4" s="89" t="n">
         <f aca="false">IF(OR(G4="",H4=""),"",H4-G4)</f>
         <v>91</v>
       </c>
-      <c r="J4" s="87" t="n">
+      <c r="J4" s="89" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="87" t="s">
-        <v>1053</v>
-      </c>
-      <c r="L4" s="88" t="s">
-        <v>1054</v>
-      </c>
-      <c r="M4" s="87" t="s">
-        <v>994</v>
-      </c>
-      <c r="N4" s="99" t="n">
+      <c r="K4" s="89" t="s">
+        <v>1069</v>
+      </c>
+      <c r="L4" s="90" t="s">
+        <v>1070</v>
+      </c>
+      <c r="M4" s="89" t="s">
+        <v>1010</v>
+      </c>
+      <c r="N4" s="101" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="95" t="n">
+      <c r="A5" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="92"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="100"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="102"/>
+      <c r="H5" s="102"/>
       <c r="I5" s="21" t="str">
         <f aca="false">IF(OR(G5="",H5=""),"",H5-G5)</f>
         <v/>
       </c>
-      <c r="J5" s="93"/>
-      <c r="K5" s="93"/>
-      <c r="L5" s="92"/>
-      <c r="M5" s="93"/>
-      <c r="N5" s="101"/>
+      <c r="J5" s="95"/>
+      <c r="K5" s="95"/>
+      <c r="L5" s="94"/>
+      <c r="M5" s="95"/>
+      <c r="N5" s="103"/>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="95" t="n">
+      <c r="A6" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="92"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="100"/>
-      <c r="H6" s="100"/>
+      <c r="B6" s="94"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="102"/>
       <c r="I6" s="21" t="str">
         <f aca="false">IF(OR(G6="",H6=""),"",H6-G6)</f>
         <v/>
       </c>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="92"/>
-      <c r="M6" s="93"/>
-      <c r="N6" s="101"/>
+      <c r="J6" s="95"/>
+      <c r="K6" s="95"/>
+      <c r="L6" s="94"/>
+      <c r="M6" s="95"/>
+      <c r="N6" s="103"/>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="95" t="n">
+      <c r="A7" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="92"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="93"/>
-      <c r="E7" s="93"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="100"/>
-      <c r="H7" s="100"/>
+      <c r="B7" s="94"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
+      <c r="F7" s="95"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="102"/>
       <c r="I7" s="21" t="str">
         <f aca="false">IF(OR(G7="",H7=""),"",H7-G7)</f>
         <v/>
       </c>
-      <c r="J7" s="93"/>
-      <c r="K7" s="93"/>
-      <c r="L7" s="92"/>
-      <c r="M7" s="93"/>
-      <c r="N7" s="101"/>
+      <c r="J7" s="95"/>
+      <c r="K7" s="95"/>
+      <c r="L7" s="94"/>
+      <c r="M7" s="95"/>
+      <c r="N7" s="103"/>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="95" t="n">
+      <c r="A8" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="92"/>
-      <c r="C8" s="93"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="93"/>
-      <c r="F8" s="93"/>
-      <c r="G8" s="100"/>
-      <c r="H8" s="100"/>
+      <c r="B8" s="94"/>
+      <c r="C8" s="95"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="102"/>
       <c r="I8" s="21" t="str">
         <f aca="false">IF(OR(G8="",H8=""),"",H8-G8)</f>
         <v/>
       </c>
-      <c r="J8" s="93"/>
-      <c r="K8" s="93"/>
-      <c r="L8" s="92"/>
-      <c r="M8" s="93"/>
-      <c r="N8" s="101"/>
+      <c r="J8" s="95"/>
+      <c r="K8" s="95"/>
+      <c r="L8" s="94"/>
+      <c r="M8" s="95"/>
+      <c r="N8" s="103"/>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="95" t="n">
+      <c r="A9" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="92"/>
-      <c r="C9" s="93"/>
-      <c r="D9" s="93"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="100"/>
-      <c r="H9" s="100"/>
+      <c r="B9" s="94"/>
+      <c r="C9" s="95"/>
+      <c r="D9" s="95"/>
+      <c r="E9" s="95"/>
+      <c r="F9" s="95"/>
+      <c r="G9" s="102"/>
+      <c r="H9" s="102"/>
       <c r="I9" s="21" t="str">
         <f aca="false">IF(OR(G9="",H9=""),"",H9-G9)</f>
         <v/>
       </c>
-      <c r="J9" s="93"/>
-      <c r="K9" s="93"/>
-      <c r="L9" s="92"/>
-      <c r="M9" s="93"/>
-      <c r="N9" s="101"/>
+      <c r="J9" s="95"/>
+      <c r="K9" s="95"/>
+      <c r="L9" s="94"/>
+      <c r="M9" s="95"/>
+      <c r="N9" s="103"/>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="95" t="n">
+      <c r="A10" s="97" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="92"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="100"/>
-      <c r="H10" s="100"/>
+      <c r="B10" s="94"/>
+      <c r="C10" s="95"/>
+      <c r="D10" s="95"/>
+      <c r="E10" s="95"/>
+      <c r="F10" s="95"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
       <c r="I10" s="21" t="str">
         <f aca="false">IF(OR(G10="",H10=""),"",H10-G10)</f>
         <v/>
       </c>
-      <c r="J10" s="93"/>
-      <c r="K10" s="93"/>
-      <c r="L10" s="92"/>
-      <c r="M10" s="93"/>
-      <c r="N10" s="101"/>
+      <c r="J10" s="95"/>
+      <c r="K10" s="95"/>
+      <c r="L10" s="94"/>
+      <c r="M10" s="95"/>
+      <c r="N10" s="103"/>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="95" t="n">
+      <c r="A11" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="92"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="100"/>
-      <c r="H11" s="100"/>
+      <c r="B11" s="94"/>
+      <c r="C11" s="95"/>
+      <c r="D11" s="95"/>
+      <c r="E11" s="95"/>
+      <c r="F11" s="95"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="102"/>
       <c r="I11" s="21" t="str">
         <f aca="false">IF(OR(G11="",H11=""),"",H11-G11)</f>
         <v/>
       </c>
-      <c r="J11" s="93"/>
-      <c r="K11" s="93"/>
-      <c r="L11" s="92"/>
-      <c r="M11" s="93"/>
-      <c r="N11" s="101"/>
+      <c r="J11" s="95"/>
+      <c r="K11" s="95"/>
+      <c r="L11" s="94"/>
+      <c r="M11" s="95"/>
+      <c r="N11" s="103"/>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="95" t="n">
+      <c r="A12" s="97" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="92"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="100"/>
-      <c r="H12" s="100"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="102"/>
       <c r="I12" s="21" t="str">
         <f aca="false">IF(OR(G12="",H12=""),"",H12-G12)</f>
         <v/>
       </c>
-      <c r="J12" s="93"/>
-      <c r="K12" s="93"/>
-      <c r="L12" s="92"/>
-      <c r="M12" s="93"/>
-      <c r="N12" s="101"/>
+      <c r="J12" s="95"/>
+      <c r="K12" s="95"/>
+      <c r="L12" s="94"/>
+      <c r="M12" s="95"/>
+      <c r="N12" s="103"/>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="95" t="n">
+      <c r="A13" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="92"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="93"/>
-      <c r="G13" s="100"/>
-      <c r="H13" s="100"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="102"/>
+      <c r="H13" s="102"/>
       <c r="I13" s="21" t="str">
         <f aca="false">IF(OR(G13="",H13=""),"",H13-G13)</f>
         <v/>
       </c>
-      <c r="J13" s="93"/>
-      <c r="K13" s="93"/>
-      <c r="L13" s="92"/>
-      <c r="M13" s="93"/>
-      <c r="N13" s="101"/>
+      <c r="J13" s="95"/>
+      <c r="K13" s="95"/>
+      <c r="L13" s="94"/>
+      <c r="M13" s="95"/>
+      <c r="N13" s="103"/>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="95" t="n">
+      <c r="A14" s="97" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="92"/>
-      <c r="C14" s="93"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="93"/>
-      <c r="F14" s="93"/>
-      <c r="G14" s="100"/>
-      <c r="H14" s="100"/>
+      <c r="B14" s="94"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="102"/>
+      <c r="H14" s="102"/>
       <c r="I14" s="21" t="str">
         <f aca="false">IF(OR(G14="",H14=""),"",H14-G14)</f>
         <v/>
       </c>
-      <c r="J14" s="93"/>
-      <c r="K14" s="93"/>
-      <c r="L14" s="92"/>
-      <c r="M14" s="93"/>
-      <c r="N14" s="101"/>
+      <c r="J14" s="95"/>
+      <c r="K14" s="95"/>
+      <c r="L14" s="94"/>
+      <c r="M14" s="95"/>
+      <c r="N14" s="103"/>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="95" t="n">
+      <c r="A15" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="92"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="93"/>
-      <c r="E15" s="93"/>
-      <c r="F15" s="93"/>
-      <c r="G15" s="100"/>
-      <c r="H15" s="100"/>
+      <c r="B15" s="94"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="102"/>
       <c r="I15" s="21" t="str">
         <f aca="false">IF(OR(G15="",H15=""),"",H15-G15)</f>
         <v/>
       </c>
-      <c r="J15" s="93"/>
-      <c r="K15" s="93"/>
-      <c r="L15" s="92"/>
-      <c r="M15" s="93"/>
-      <c r="N15" s="101"/>
+      <c r="J15" s="95"/>
+      <c r="K15" s="95"/>
+      <c r="L15" s="94"/>
+      <c r="M15" s="95"/>
+      <c r="N15" s="103"/>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="95" t="n">
+      <c r="A16" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="92"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="93"/>
-      <c r="E16" s="93"/>
-      <c r="F16" s="93"/>
-      <c r="G16" s="100"/>
-      <c r="H16" s="100"/>
+      <c r="B16" s="94"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="102"/>
+      <c r="H16" s="102"/>
       <c r="I16" s="21" t="str">
         <f aca="false">IF(OR(G16="",H16=""),"",H16-G16)</f>
         <v/>
       </c>
-      <c r="J16" s="93"/>
-      <c r="K16" s="93"/>
-      <c r="L16" s="92"/>
-      <c r="M16" s="93"/>
-      <c r="N16" s="101"/>
+      <c r="J16" s="95"/>
+      <c r="K16" s="95"/>
+      <c r="L16" s="94"/>
+      <c r="M16" s="95"/>
+      <c r="N16" s="103"/>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="95" t="n">
+      <c r="A17" s="97" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="92"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="93"/>
-      <c r="F17" s="93"/>
-      <c r="G17" s="100"/>
-      <c r="H17" s="100"/>
+      <c r="B17" s="94"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="102"/>
+      <c r="H17" s="102"/>
       <c r="I17" s="21" t="str">
         <f aca="false">IF(OR(G17="",H17=""),"",H17-G17)</f>
         <v/>
       </c>
-      <c r="J17" s="93"/>
-      <c r="K17" s="93"/>
-      <c r="L17" s="92"/>
-      <c r="M17" s="93"/>
-      <c r="N17" s="101"/>
+      <c r="J17" s="95"/>
+      <c r="K17" s="95"/>
+      <c r="L17" s="94"/>
+      <c r="M17" s="95"/>
+      <c r="N17" s="103"/>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="95" t="n">
+      <c r="A18" s="97" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="92"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="93"/>
-      <c r="F18" s="93"/>
-      <c r="G18" s="100"/>
-      <c r="H18" s="100"/>
+      <c r="B18" s="94"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="102"/>
+      <c r="H18" s="102"/>
       <c r="I18" s="21" t="str">
         <f aca="false">IF(OR(G18="",H18=""),"",H18-G18)</f>
         <v/>
       </c>
-      <c r="J18" s="93"/>
-      <c r="K18" s="93"/>
-      <c r="L18" s="92"/>
-      <c r="M18" s="93"/>
-      <c r="N18" s="101"/>
+      <c r="J18" s="95"/>
+      <c r="K18" s="95"/>
+      <c r="L18" s="94"/>
+      <c r="M18" s="95"/>
+      <c r="N18" s="103"/>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="95" t="n">
+      <c r="A19" s="97" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="92"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="93"/>
-      <c r="G19" s="100"/>
-      <c r="H19" s="100"/>
+      <c r="B19" s="94"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="102"/>
       <c r="I19" s="21" t="str">
         <f aca="false">IF(OR(G19="",H19=""),"",H19-G19)</f>
         <v/>
       </c>
-      <c r="J19" s="93"/>
-      <c r="K19" s="93"/>
-      <c r="L19" s="92"/>
-      <c r="M19" s="93"/>
-      <c r="N19" s="101"/>
+      <c r="J19" s="95"/>
+      <c r="K19" s="95"/>
+      <c r="L19" s="94"/>
+      <c r="M19" s="95"/>
+      <c r="N19" s="103"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="95" t="n">
+      <c r="A20" s="97" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="92"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="93"/>
-      <c r="F20" s="93"/>
-      <c r="G20" s="100"/>
-      <c r="H20" s="100"/>
+      <c r="B20" s="94"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="95"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="102"/>
       <c r="I20" s="21" t="str">
         <f aca="false">IF(OR(G20="",H20=""),"",H20-G20)</f>
         <v/>
       </c>
-      <c r="J20" s="93"/>
-      <c r="K20" s="93"/>
-      <c r="L20" s="92"/>
-      <c r="M20" s="93"/>
-      <c r="N20" s="101"/>
+      <c r="J20" s="95"/>
+      <c r="K20" s="95"/>
+      <c r="L20" s="94"/>
+      <c r="M20" s="95"/>
+      <c r="N20" s="103"/>
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="95" t="n">
+      <c r="A21" s="97" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="92"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="93"/>
-      <c r="E21" s="93"/>
-      <c r="F21" s="93"/>
-      <c r="G21" s="100"/>
-      <c r="H21" s="100"/>
+      <c r="B21" s="94"/>
+      <c r="C21" s="95"/>
+      <c r="D21" s="95"/>
+      <c r="E21" s="95"/>
+      <c r="F21" s="95"/>
+      <c r="G21" s="102"/>
+      <c r="H21" s="102"/>
       <c r="I21" s="21" t="str">
         <f aca="false">IF(OR(G21="",H21=""),"",H21-G21)</f>
         <v/>
       </c>
-      <c r="J21" s="93"/>
-      <c r="K21" s="93"/>
-      <c r="L21" s="92"/>
-      <c r="M21" s="93"/>
-      <c r="N21" s="101"/>
+      <c r="J21" s="95"/>
+      <c r="K21" s="95"/>
+      <c r="L21" s="94"/>
+      <c r="M21" s="95"/>
+      <c r="N21" s="103"/>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="95" t="n">
+      <c r="A22" s="97" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="93"/>
-      <c r="E22" s="93"/>
-      <c r="F22" s="93"/>
-      <c r="G22" s="100"/>
-      <c r="H22" s="100"/>
+      <c r="B22" s="94"/>
+      <c r="C22" s="95"/>
+      <c r="D22" s="95"/>
+      <c r="E22" s="95"/>
+      <c r="F22" s="95"/>
+      <c r="G22" s="102"/>
+      <c r="H22" s="102"/>
       <c r="I22" s="21" t="str">
         <f aca="false">IF(OR(G22="",H22=""),"",H22-G22)</f>
         <v/>
       </c>
-      <c r="J22" s="93"/>
-      <c r="K22" s="93"/>
-      <c r="L22" s="92"/>
-      <c r="M22" s="93"/>
-      <c r="N22" s="101"/>
+      <c r="J22" s="95"/>
+      <c r="K22" s="95"/>
+      <c r="L22" s="94"/>
+      <c r="M22" s="95"/>
+      <c r="N22" s="103"/>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="95" t="n">
+      <c r="A23" s="97" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="92"/>
-      <c r="C23" s="93"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="93"/>
-      <c r="F23" s="93"/>
-      <c r="G23" s="100"/>
-      <c r="H23" s="100"/>
+      <c r="B23" s="94"/>
+      <c r="C23" s="95"/>
+      <c r="D23" s="95"/>
+      <c r="E23" s="95"/>
+      <c r="F23" s="95"/>
+      <c r="G23" s="102"/>
+      <c r="H23" s="102"/>
       <c r="I23" s="21" t="str">
         <f aca="false">IF(OR(G23="",H23=""),"",H23-G23)</f>
         <v/>
       </c>
-      <c r="J23" s="93"/>
-      <c r="K23" s="93"/>
-      <c r="L23" s="92"/>
-      <c r="M23" s="93"/>
-      <c r="N23" s="101"/>
+      <c r="J23" s="95"/>
+      <c r="K23" s="95"/>
+      <c r="L23" s="94"/>
+      <c r="M23" s="95"/>
+      <c r="N23" s="103"/>
     </row>
     <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="95" t="n">
+      <c r="A24" s="97" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="92"/>
-      <c r="C24" s="93"/>
-      <c r="D24" s="93"/>
-      <c r="E24" s="93"/>
-      <c r="F24" s="93"/>
-      <c r="G24" s="100"/>
-      <c r="H24" s="100"/>
+      <c r="B24" s="94"/>
+      <c r="C24" s="95"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="95"/>
+      <c r="F24" s="95"/>
+      <c r="G24" s="102"/>
+      <c r="H24" s="102"/>
       <c r="I24" s="21" t="str">
         <f aca="false">IF(OR(G24="",H24=""),"",H24-G24)</f>
         <v/>
       </c>
-      <c r="J24" s="93"/>
-      <c r="K24" s="93"/>
-      <c r="L24" s="92"/>
-      <c r="M24" s="93"/>
-      <c r="N24" s="101"/>
+      <c r="J24" s="95"/>
+      <c r="K24" s="95"/>
+      <c r="L24" s="94"/>
+      <c r="M24" s="95"/>
+      <c r="N24" s="103"/>
     </row>
     <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="95" t="n">
+      <c r="A25" s="97" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="92"/>
-      <c r="C25" s="93"/>
-      <c r="D25" s="93"/>
-      <c r="E25" s="93"/>
-      <c r="F25" s="93"/>
-      <c r="G25" s="100"/>
-      <c r="H25" s="100"/>
+      <c r="B25" s="94"/>
+      <c r="C25" s="95"/>
+      <c r="D25" s="95"/>
+      <c r="E25" s="95"/>
+      <c r="F25" s="95"/>
+      <c r="G25" s="102"/>
+      <c r="H25" s="102"/>
       <c r="I25" s="21" t="str">
         <f aca="false">IF(OR(G25="",H25=""),"",H25-G25)</f>
         <v/>
       </c>
-      <c r="J25" s="93"/>
-      <c r="K25" s="93"/>
-      <c r="L25" s="92"/>
-      <c r="M25" s="93"/>
-      <c r="N25" s="101"/>
+      <c r="J25" s="95"/>
+      <c r="K25" s="95"/>
+      <c r="L25" s="94"/>
+      <c r="M25" s="95"/>
+      <c r="N25" s="103"/>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="95" t="n">
+      <c r="A26" s="97" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="92"/>
-      <c r="C26" s="93"/>
-      <c r="D26" s="93"/>
-      <c r="E26" s="93"/>
-      <c r="F26" s="93"/>
-      <c r="G26" s="100"/>
-      <c r="H26" s="100"/>
+      <c r="B26" s="94"/>
+      <c r="C26" s="95"/>
+      <c r="D26" s="95"/>
+      <c r="E26" s="95"/>
+      <c r="F26" s="95"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="102"/>
       <c r="I26" s="21" t="str">
         <f aca="false">IF(OR(G26="",H26=""),"",H26-G26)</f>
         <v/>
       </c>
-      <c r="J26" s="93"/>
-      <c r="K26" s="93"/>
-      <c r="L26" s="92"/>
-      <c r="M26" s="93"/>
-      <c r="N26" s="101"/>
+      <c r="J26" s="95"/>
+      <c r="K26" s="95"/>
+      <c r="L26" s="94"/>
+      <c r="M26" s="95"/>
+      <c r="N26" s="103"/>
     </row>
     <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="95" t="n">
+      <c r="A27" s="97" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="92"/>
-      <c r="C27" s="93"/>
-      <c r="D27" s="93"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="100"/>
-      <c r="H27" s="100"/>
+      <c r="B27" s="94"/>
+      <c r="C27" s="95"/>
+      <c r="D27" s="95"/>
+      <c r="E27" s="95"/>
+      <c r="F27" s="95"/>
+      <c r="G27" s="102"/>
+      <c r="H27" s="102"/>
       <c r="I27" s="21" t="str">
         <f aca="false">IF(OR(G27="",H27=""),"",H27-G27)</f>
         <v/>
       </c>
-      <c r="J27" s="93"/>
-      <c r="K27" s="93"/>
-      <c r="L27" s="92"/>
-      <c r="M27" s="93"/>
-      <c r="N27" s="101"/>
+      <c r="J27" s="95"/>
+      <c r="K27" s="95"/>
+      <c r="L27" s="94"/>
+      <c r="M27" s="95"/>
+      <c r="N27" s="103"/>
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="95" t="n">
+      <c r="A28" s="97" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="92"/>
-      <c r="C28" s="93"/>
-      <c r="D28" s="93"/>
-      <c r="E28" s="93"/>
-      <c r="F28" s="93"/>
-      <c r="G28" s="100"/>
-      <c r="H28" s="100"/>
+      <c r="B28" s="94"/>
+      <c r="C28" s="95"/>
+      <c r="D28" s="95"/>
+      <c r="E28" s="95"/>
+      <c r="F28" s="95"/>
+      <c r="G28" s="102"/>
+      <c r="H28" s="102"/>
       <c r="I28" s="21" t="str">
         <f aca="false">IF(OR(G28="",H28=""),"",H28-G28)</f>
         <v/>
       </c>
-      <c r="J28" s="93"/>
-      <c r="K28" s="93"/>
-      <c r="L28" s="92"/>
-      <c r="M28" s="93"/>
-      <c r="N28" s="101"/>
+      <c r="J28" s="95"/>
+      <c r="K28" s="95"/>
+      <c r="L28" s="94"/>
+      <c r="M28" s="95"/>
+      <c r="N28" s="103"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="24" t="s">
-        <v>1055</v>
+        <v>1071</v>
       </c>
       <c r="M30" s="21" t="str">
         <f aca="false">COUNTA(B5:B28)&amp;" مبادرة"</f>
@@ -10315,7 +11902,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1056</v>
+        <v>1072</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10334,7 +11921,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1057</v>
+        <v>1073</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10353,60 +11940,60 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>1058</v>
+        <v>1074</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>858</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>1059</v>
+        <v>1075</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>1060</v>
+        <v>1076</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>1061</v>
+        <v>1077</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1062</v>
+        <v>1078</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1063</v>
+        <v>1079</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1064</v>
+        <v>1080</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>1065</v>
+        <v>1081</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>1066</v>
+        <v>1082</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>860</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>1067</v>
+        <v>1083</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>1068</v>
+        <v>1084</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>1069</v>
+        <v>1085</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>1070</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>1071</v>
+        <v>1087</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>1072</v>
+        <v>1088</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>868</v>
@@ -10427,7 +12014,7 @@
       <c r="I4" s="28" t="n">
         <v>23493282</v>
       </c>
-      <c r="J4" s="90" t="n">
+      <c r="J4" s="92" t="n">
         <v>64.69</v>
       </c>
       <c r="K4" s="57" t="n">
@@ -10443,18 +12030,18 @@
         <v>0.281</v>
       </c>
       <c r="O4" s="21" t="s">
-        <v>1074</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>1075</v>
+        <v>1091</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>916</v>
+        <v>926</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>862</v>
@@ -10475,10 +12062,10 @@
       <c r="I5" s="28" t="n">
         <v>8841940</v>
       </c>
-      <c r="J5" s="90" t="n">
+      <c r="J5" s="92" t="n">
         <v>61.72</v>
       </c>
-      <c r="K5" s="102" t="n">
+      <c r="K5" s="104" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="45" t="n">
@@ -10491,18 +12078,18 @@
         <v>0</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>1076</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>1077</v>
+        <v>1093</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>917</v>
+        <v>927</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>1078</v>
+        <v>1094</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>868</v>
@@ -10523,10 +12110,10 @@
       <c r="I6" s="28" t="n">
         <v>7467484</v>
       </c>
-      <c r="J6" s="90" t="n">
+      <c r="J6" s="92" t="n">
         <v>80.21</v>
       </c>
-      <c r="K6" s="102" t="n">
+      <c r="K6" s="104" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="45" t="n">
@@ -10539,15 +12126,15 @@
         <v>0.344</v>
       </c>
       <c r="O6" s="21" t="s">
-        <v>1079</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>1080</v>
+        <v>1096</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>1081</v>
+        <v>1097</v>
       </c>
       <c r="C7" s="21" t="s">
         <v>350</v>
@@ -10571,10 +12158,10 @@
       <c r="I7" s="28" t="n">
         <v>14552120</v>
       </c>
-      <c r="J7" s="90" t="n">
+      <c r="J7" s="92" t="n">
         <v>84.21</v>
       </c>
-      <c r="K7" s="103" t="n">
+      <c r="K7" s="105" t="n">
         <v>0.273</v>
       </c>
       <c r="L7" s="45" t="n">
@@ -10587,18 +12174,18 @@
         <v>0.641</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>1083</v>
+        <v>1099</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>1084</v>
+        <v>1100</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>868</v>
@@ -10619,7 +12206,7 @@
       <c r="I8" s="28" t="n">
         <v>2916708</v>
       </c>
-      <c r="J8" s="90" t="n">
+      <c r="J8" s="92" t="n">
         <v>48.35</v>
       </c>
       <c r="K8" s="57" t="n">
@@ -10635,21 +12222,21 @@
         <v>0.134</v>
       </c>
       <c r="O8" s="21" t="s">
-        <v>1085</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>1086</v>
+        <v>1102</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>1087</v>
+        <v>1103</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>1078</v>
+        <v>1094</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>1088</v>
+        <v>1104</v>
       </c>
       <c r="E9" s="21" t="n">
         <v>55</v>
@@ -10667,10 +12254,10 @@
       <c r="I9" s="28" t="n">
         <v>2916316</v>
       </c>
-      <c r="J9" s="90" t="n">
+      <c r="J9" s="92" t="n">
         <v>65.82</v>
       </c>
-      <c r="K9" s="102" t="n">
+      <c r="K9" s="104" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="45" t="n">
@@ -10683,18 +12270,18 @@
         <v>0.309</v>
       </c>
       <c r="O9" s="21" t="s">
-        <v>1074</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>1089</v>
+        <v>1105</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>1090</v>
+        <v>1106</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>1078</v>
+        <v>1094</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>868</v>
@@ -10715,10 +12302,10 @@
       <c r="I10" s="28" t="n">
         <v>2831981</v>
       </c>
-      <c r="J10" s="90" t="n">
+      <c r="J10" s="92" t="n">
         <v>59.14</v>
       </c>
-      <c r="K10" s="102" t="n">
+      <c r="K10" s="104" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="45" t="n">
@@ -10731,15 +12318,15 @@
         <v>0.006</v>
       </c>
       <c r="O10" s="21" t="s">
-        <v>1079</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>1091</v>
+        <v>1107</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>1092</v>
+        <v>1108</v>
       </c>
       <c r="C11" s="21" t="s">
         <v>350</v>
@@ -10763,10 +12350,10 @@
       <c r="I11" s="28" t="n">
         <v>2931550</v>
       </c>
-      <c r="J11" s="90" t="n">
+      <c r="J11" s="92" t="n">
         <v>49.84</v>
       </c>
-      <c r="K11" s="102" t="n">
+      <c r="K11" s="104" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="45" t="n">
@@ -10779,18 +12366,18 @@
         <v>0</v>
       </c>
       <c r="O11" s="21" t="s">
-        <v>1079</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>1093</v>
+        <v>1109</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>868</v>
@@ -10811,7 +12398,7 @@
       <c r="I12" s="28" t="n">
         <v>8679738</v>
       </c>
-      <c r="J12" s="90" t="n">
+      <c r="J12" s="92" t="n">
         <v>59.34</v>
       </c>
       <c r="K12" s="57" t="n">
@@ -10827,21 +12414,21 @@
         <v>0.277</v>
       </c>
       <c r="O12" s="21" t="s">
-        <v>1079</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C13" s="21" t="s">
         <v>1094</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>1095</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>1078</v>
-      </c>
       <c r="D13" s="21" t="s">
-        <v>1088</v>
+        <v>1104</v>
       </c>
       <c r="E13" s="21" t="n">
         <v>181</v>
@@ -10859,7 +12446,7 @@
       <c r="I13" s="28" t="n">
         <v>7729931</v>
       </c>
-      <c r="J13" s="90" t="n">
+      <c r="J13" s="92" t="n">
         <v>67.66</v>
       </c>
       <c r="K13" s="57" t="n">
@@ -10875,18 +12462,18 @@
         <v>0.082</v>
       </c>
       <c r="O13" s="21" t="s">
-        <v>1079</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>1096</v>
+        <v>1112</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>1097</v>
+        <v>1113</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>868</v>
@@ -10907,7 +12494,7 @@
       <c r="I14" s="28" t="n">
         <v>2676944</v>
       </c>
-      <c r="J14" s="90" t="n">
+      <c r="J14" s="92" t="n">
         <v>59.47</v>
       </c>
       <c r="K14" s="45" t="n">
@@ -10923,18 +12510,18 @@
         <v>0.231</v>
       </c>
       <c r="O14" s="21" t="s">
-        <v>1079</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>1098</v>
+        <v>1114</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>1099</v>
+        <v>1115</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>862</v>
@@ -10955,7 +12542,7 @@
       <c r="I15" s="28" t="n">
         <v>7806709</v>
       </c>
-      <c r="J15" s="90" t="n">
+      <c r="J15" s="92" t="n">
         <v>63.18</v>
       </c>
       <c r="K15" s="57" t="n">
@@ -10971,15 +12558,15 @@
         <v>0.458</v>
       </c>
       <c r="O15" s="21" t="s">
-        <v>1085</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>1100</v>
+        <v>1116</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>1101</v>
+        <v>1117</v>
       </c>
       <c r="C16" s="21" t="s">
         <v>355</v>
@@ -11003,10 +12590,10 @@
       <c r="I16" s="28" t="n">
         <v>4791911</v>
       </c>
-      <c r="J16" s="90" t="n">
+      <c r="J16" s="92" t="n">
         <v>74.3</v>
       </c>
-      <c r="K16" s="103" t="n">
+      <c r="K16" s="105" t="n">
         <v>0.151</v>
       </c>
       <c r="L16" s="45" t="n">
@@ -11019,18 +12606,18 @@
         <v>0.076</v>
       </c>
       <c r="O16" s="21" t="s">
-        <v>1079</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>1102</v>
+        <v>1118</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>1103</v>
+        <v>1119</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>1078</v>
+        <v>1094</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>868</v>
@@ -11051,10 +12638,10 @@
       <c r="I17" s="28" t="n">
         <v>2078856</v>
       </c>
-      <c r="J17" s="90" t="n">
+      <c r="J17" s="92" t="n">
         <v>55.76</v>
       </c>
-      <c r="K17" s="102" t="n">
+      <c r="K17" s="104" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="45" t="n">
@@ -11067,18 +12654,18 @@
         <v>0</v>
       </c>
       <c r="O17" s="21" t="s">
-        <v>1074</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>1104</v>
+        <v>1120</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>928</v>
+        <v>938</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>868</v>
@@ -11099,7 +12686,7 @@
       <c r="I18" s="28" t="n">
         <v>6570004</v>
       </c>
-      <c r="J18" s="90" t="n">
+      <c r="J18" s="92" t="n">
         <v>43.71</v>
       </c>
       <c r="K18" s="45" t="n">
@@ -11115,15 +12702,15 @@
         <v>0</v>
       </c>
       <c r="O18" s="21" t="s">
-        <v>1074</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>1105</v>
+        <v>1121</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>1106</v>
+        <v>1122</v>
       </c>
       <c r="C19" s="21" t="s">
         <v>347</v>
@@ -11147,10 +12734,10 @@
       <c r="I19" s="28" t="n">
         <v>4445436</v>
       </c>
-      <c r="J19" s="90" t="n">
+      <c r="J19" s="92" t="n">
         <v>42.14</v>
       </c>
-      <c r="K19" s="103" t="n">
+      <c r="K19" s="105" t="n">
         <v>0.275</v>
       </c>
       <c r="L19" s="45" t="n">
@@ -11163,21 +12750,21 @@
         <v>0.048</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>1107</v>
+        <v>1123</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>1108</v>
+        <v>1124</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>1109</v>
+        <v>1125</v>
       </c>
       <c r="E20" s="21" t="n">
         <v>70</v>
@@ -11195,10 +12782,10 @@
       <c r="I20" s="28" t="n">
         <v>2229579</v>
       </c>
-      <c r="J20" s="90" t="n">
+      <c r="J20" s="92" t="n">
         <v>43.6</v>
       </c>
-      <c r="K20" s="102" t="n">
+      <c r="K20" s="104" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="45" t="n">
@@ -11211,18 +12798,18 @@
         <v>0</v>
       </c>
       <c r="O20" s="21" t="s">
-        <v>1076</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>1110</v>
+        <v>1126</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>930</v>
+        <v>940</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D21" s="21" t="s">
         <v>868</v>
@@ -11243,7 +12830,7 @@
       <c r="I21" s="28" t="n">
         <v>5504980</v>
       </c>
-      <c r="J21" s="90" t="n">
+      <c r="J21" s="92" t="n">
         <v>43.52</v>
       </c>
       <c r="K21" s="57" t="n">
@@ -11259,15 +12846,15 @@
         <v>0</v>
       </c>
       <c r="O21" s="21" t="s">
-        <v>1079</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>1111</v>
+        <v>1127</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>1112</v>
+        <v>1128</v>
       </c>
       <c r="C22" s="21" t="s">
         <v>350</v>
@@ -11291,10 +12878,10 @@
       <c r="I22" s="28" t="n">
         <v>4722403</v>
       </c>
-      <c r="J22" s="90" t="n">
+      <c r="J22" s="92" t="n">
         <v>49.88</v>
       </c>
-      <c r="K22" s="103" t="n">
+      <c r="K22" s="105" t="n">
         <v>0.068</v>
       </c>
       <c r="L22" s="45" t="n">
@@ -11307,18 +12894,18 @@
         <v>0.329</v>
       </c>
       <c r="O22" s="21" t="s">
-        <v>1085</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>1113</v>
+        <v>1129</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>934</v>
+        <v>944</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D23" s="21" t="s">
         <v>868</v>
@@ -11339,10 +12926,10 @@
       <c r="I23" s="28" t="n">
         <v>4924931</v>
       </c>
-      <c r="J23" s="90" t="n">
+      <c r="J23" s="92" t="n">
         <v>47.68</v>
       </c>
-      <c r="K23" s="103" t="n">
+      <c r="K23" s="105" t="n">
         <v>0.069</v>
       </c>
       <c r="L23" s="45" t="n">
@@ -11355,18 +12942,18 @@
         <v>0</v>
       </c>
       <c r="O23" s="21" t="s">
-        <v>1079</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>1114</v>
+        <v>1130</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>933</v>
+        <v>943</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D24" s="21" t="s">
         <v>868</v>
@@ -11387,7 +12974,7 @@
       <c r="I24" s="28" t="n">
         <v>4740020</v>
       </c>
-      <c r="J24" s="90" t="n">
+      <c r="J24" s="92" t="n">
         <v>43.42</v>
       </c>
       <c r="K24" s="45" t="n">
@@ -11403,21 +12990,21 @@
         <v>0</v>
       </c>
       <c r="O24" s="21" t="s">
-        <v>1079</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>1115</v>
+        <v>1131</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>1116</v>
+        <v>1132</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>1078</v>
+        <v>1094</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>1088</v>
+        <v>1104</v>
       </c>
       <c r="E25" s="21" t="n">
         <v>181</v>
@@ -11435,10 +13022,10 @@
       <c r="I25" s="28" t="n">
         <v>4771577</v>
       </c>
-      <c r="J25" s="90" t="n">
+      <c r="J25" s="92" t="n">
         <v>51.68</v>
       </c>
-      <c r="K25" s="103" t="n">
+      <c r="K25" s="105" t="n">
         <v>0.177</v>
       </c>
       <c r="L25" s="45" t="n">
@@ -11451,21 +13038,21 @@
         <v>0.058</v>
       </c>
       <c r="O25" s="21" t="s">
-        <v>1074</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>1117</v>
+        <v>1133</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>1118</v>
+        <v>1134</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>1109</v>
+        <v>1125</v>
       </c>
       <c r="E26" s="21" t="n">
         <v>181</v>
@@ -11483,7 +13070,7 @@
       <c r="I26" s="28" t="n">
         <v>4933540</v>
       </c>
-      <c r="J26" s="90" t="n">
+      <c r="J26" s="92" t="n">
         <v>51.76</v>
       </c>
       <c r="K26" s="45" t="n">
@@ -11499,21 +13086,21 @@
         <v>0.276</v>
       </c>
       <c r="O26" s="21" t="s">
-        <v>1074</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>1119</v>
+        <v>1135</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>1120</v>
+        <v>1136</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>1078</v>
+        <v>1094</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>1088</v>
+        <v>1104</v>
       </c>
       <c r="E27" s="21" t="n">
         <v>181</v>
@@ -11531,10 +13118,10 @@
       <c r="I27" s="28" t="n">
         <v>4643058</v>
       </c>
-      <c r="J27" s="90" t="n">
+      <c r="J27" s="92" t="n">
         <v>66.28</v>
       </c>
-      <c r="K27" s="103" t="n">
+      <c r="K27" s="105" t="n">
         <v>0.083</v>
       </c>
       <c r="L27" s="45" t="n">
@@ -11547,18 +13134,18 @@
         <v>0.27</v>
       </c>
       <c r="O27" s="21" t="s">
-        <v>1121</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>1122</v>
+        <v>1138</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>1123</v>
+        <v>1139</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D28" s="21" t="s">
         <v>862</v>
@@ -11579,10 +13166,10 @@
       <c r="I28" s="28" t="n">
         <v>2834084</v>
       </c>
-      <c r="J28" s="90" t="n">
+      <c r="J28" s="92" t="n">
         <v>77.81</v>
       </c>
-      <c r="K28" s="102" t="n">
+      <c r="K28" s="104" t="n">
         <v>-0.033</v>
       </c>
       <c r="L28" s="45" t="n">
@@ -11595,21 +13182,21 @@
         <v>0.349</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>1124</v>
+        <v>1140</v>
       </c>
       <c r="B29" s="16" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D29" s="21" t="s">
         <v>1125</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>1109</v>
       </c>
       <c r="E29" s="21" t="n">
         <v>181</v>
@@ -11627,7 +13214,7 @@
       <c r="I29" s="28" t="n">
         <v>4558563</v>
       </c>
-      <c r="J29" s="90" t="n">
+      <c r="J29" s="92" t="n">
         <v>64.44</v>
       </c>
       <c r="K29" s="45" t="n">
@@ -11643,18 +13230,18 @@
         <v>0.321</v>
       </c>
       <c r="O29" s="21" t="s">
-        <v>1074</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>1126</v>
+        <v>1142</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>1127</v>
+        <v>1143</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D30" s="21" t="s">
         <v>868</v>
@@ -11675,10 +13262,10 @@
       <c r="I30" s="28" t="n">
         <v>2127665</v>
       </c>
-      <c r="J30" s="90" t="n">
+      <c r="J30" s="92" t="n">
         <v>48.52</v>
       </c>
-      <c r="K30" s="102" t="n">
+      <c r="K30" s="104" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="45" t="n">
@@ -11691,15 +13278,15 @@
         <v>0.176</v>
       </c>
       <c r="O30" s="21" t="s">
-        <v>1074</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>1128</v>
+        <v>1144</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>1129</v>
+        <v>1145</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>361</v>
@@ -11723,10 +13310,10 @@
       <c r="I31" s="28" t="n">
         <v>3884721</v>
       </c>
-      <c r="J31" s="90" t="n">
+      <c r="J31" s="92" t="n">
         <v>54.76</v>
       </c>
-      <c r="K31" s="103" t="n">
+      <c r="K31" s="105" t="n">
         <v>0.186</v>
       </c>
       <c r="L31" s="45" t="n">
@@ -11739,18 +13326,18 @@
         <v>0.082</v>
       </c>
       <c r="O31" s="21" t="s">
-        <v>1079</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>1130</v>
+        <v>1146</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>1131</v>
+        <v>1147</v>
       </c>
       <c r="D32" s="21" t="s">
         <v>866</v>
@@ -11771,10 +13358,10 @@
       <c r="I32" s="28" t="n">
         <v>1471112</v>
       </c>
-      <c r="J32" s="90" t="n">
+      <c r="J32" s="92" t="n">
         <v>49.67</v>
       </c>
-      <c r="K32" s="102" t="n">
+      <c r="K32" s="104" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="45" t="n">
@@ -11787,15 +13374,15 @@
         <v>0.103</v>
       </c>
       <c r="O32" s="20" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>1132</v>
+        <v>1148</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="C33" s="21" t="s">
         <v>347</v>
@@ -11819,10 +13406,10 @@
       <c r="I33" s="28" t="n">
         <v>3774634</v>
       </c>
-      <c r="J33" s="90" t="n">
+      <c r="J33" s="92" t="n">
         <v>50.81</v>
       </c>
-      <c r="K33" s="103" t="n">
+      <c r="K33" s="105" t="n">
         <v>0.18</v>
       </c>
       <c r="L33" s="45" t="n">
@@ -11835,18 +13422,18 @@
         <v>0.023</v>
       </c>
       <c r="O33" s="21" t="s">
-        <v>1074</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>1133</v>
+        <v>1149</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>938</v>
+        <v>948</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D34" s="21" t="s">
         <v>862</v>
@@ -11867,7 +13454,7 @@
       <c r="I34" s="28" t="n">
         <v>4263083</v>
       </c>
-      <c r="J34" s="90" t="n">
+      <c r="J34" s="92" t="n">
         <v>110.06</v>
       </c>
       <c r="K34" s="57" t="n">
@@ -11883,18 +13470,18 @@
         <v>0.559</v>
       </c>
       <c r="O34" s="21" t="s">
-        <v>1121</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>1134</v>
+        <v>1150</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>942</v>
+        <v>952</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D35" s="21" t="s">
         <v>868</v>
@@ -11915,7 +13502,7 @@
       <c r="I35" s="28" t="n">
         <v>3471225</v>
       </c>
-      <c r="J35" s="90" t="n">
+      <c r="J35" s="92" t="n">
         <v>47.35</v>
       </c>
       <c r="K35" s="57" t="n">
@@ -11931,21 +13518,21 @@
         <v>0</v>
       </c>
       <c r="O35" s="21" t="s">
-        <v>1079</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>1135</v>
+        <v>1151</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>1136</v>
+        <v>1152</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>1088</v>
+        <v>1104</v>
       </c>
       <c r="E36" s="21" t="n">
         <v>181</v>
@@ -11963,7 +13550,7 @@
       <c r="I36" s="28" t="n">
         <v>3512113</v>
       </c>
-      <c r="J36" s="90" t="n">
+      <c r="J36" s="92" t="n">
         <v>45.88</v>
       </c>
       <c r="K36" s="57" t="n">
@@ -11979,15 +13566,15 @@
         <v>0.115</v>
       </c>
       <c r="O36" s="21" t="s">
-        <v>1085</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>1137</v>
+        <v>1153</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>1138</v>
+        <v>1154</v>
       </c>
       <c r="C37" s="21" t="s">
         <v>347</v>
@@ -12011,10 +13598,10 @@
       <c r="I37" s="28" t="n">
         <v>486162</v>
       </c>
-      <c r="J37" s="90" t="n">
+      <c r="J37" s="92" t="n">
         <v>33.35</v>
       </c>
-      <c r="K37" s="102" t="n">
+      <c r="K37" s="104" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="45" t="n">
@@ -12032,10 +13619,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
-        <v>1139</v>
+        <v>1155</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>1140</v>
+        <v>1156</v>
       </c>
       <c r="C38" s="21" t="s">
         <v>350</v>
@@ -12059,10 +13646,10 @@
       <c r="I38" s="28" t="n">
         <v>3406904</v>
       </c>
-      <c r="J38" s="90" t="n">
+      <c r="J38" s="92" t="n">
         <v>43.04</v>
       </c>
-      <c r="K38" s="103" t="n">
+      <c r="K38" s="105" t="n">
         <v>0.083</v>
       </c>
       <c r="L38" s="45" t="n">
@@ -12075,18 +13662,18 @@
         <v>0.167</v>
       </c>
       <c r="O38" s="21" t="s">
-        <v>1074</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="21" t="s">
-        <v>1141</v>
+        <v>1157</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>1142</v>
+        <v>1158</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D39" s="21" t="s">
         <v>862</v>
@@ -12107,7 +13694,7 @@
       <c r="I39" s="28" t="n">
         <v>3076219</v>
       </c>
-      <c r="J39" s="90" t="n">
+      <c r="J39" s="92" t="n">
         <v>69.64</v>
       </c>
       <c r="K39" s="57" t="n">
@@ -12123,15 +13710,15 @@
         <v>0.106</v>
       </c>
       <c r="O39" s="21" t="s">
-        <v>1074</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="21" t="s">
-        <v>1143</v>
+        <v>1159</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>1144</v>
+        <v>1160</v>
       </c>
       <c r="C40" s="21" t="s">
         <v>347</v>
@@ -12155,7 +13742,7 @@
       <c r="I40" s="28" t="n">
         <v>3314721</v>
       </c>
-      <c r="J40" s="90" t="n">
+      <c r="J40" s="92" t="n">
         <v>69.44</v>
       </c>
       <c r="K40" s="45" t="n">
@@ -12171,18 +13758,18 @@
         <v>0.373</v>
       </c>
       <c r="O40" s="21" t="s">
-        <v>1074</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="21" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>1146</v>
+        <v>1162</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D41" s="21" t="s">
         <v>868</v>
@@ -12203,7 +13790,7 @@
       <c r="I41" s="28" t="n">
         <v>2925368</v>
       </c>
-      <c r="J41" s="90" t="n">
+      <c r="J41" s="92" t="n">
         <v>45.21</v>
       </c>
       <c r="K41" s="57" t="n">
@@ -12219,15 +13806,15 @@
         <v>0</v>
       </c>
       <c r="O41" s="21" t="s">
-        <v>1074</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="21" t="s">
-        <v>1147</v>
+        <v>1163</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>1148</v>
+        <v>1164</v>
       </c>
       <c r="C42" s="21" t="s">
         <v>347</v>
@@ -12251,10 +13838,10 @@
       <c r="I42" s="28" t="n">
         <v>1114635</v>
       </c>
-      <c r="J42" s="90" t="n">
+      <c r="J42" s="92" t="n">
         <v>45.6</v>
       </c>
-      <c r="K42" s="102" t="n">
+      <c r="K42" s="104" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="45" t="n">
@@ -12267,21 +13854,21 @@
         <v>0.056</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
-        <v>1149</v>
+        <v>1165</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>1150</v>
+        <v>1166</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>1078</v>
+        <v>1094</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>1109</v>
+        <v>1125</v>
       </c>
       <c r="E43" s="21" t="n">
         <v>181</v>
@@ -12299,10 +13886,10 @@
       <c r="I43" s="28" t="n">
         <v>2839338</v>
       </c>
-      <c r="J43" s="90" t="n">
+      <c r="J43" s="92" t="n">
         <v>50.86</v>
       </c>
-      <c r="K43" s="103" t="n">
+      <c r="K43" s="105" t="n">
         <v>0.082</v>
       </c>
       <c r="L43" s="45" t="n">
@@ -12315,18 +13902,18 @@
         <v>0.077</v>
       </c>
       <c r="O43" s="21" t="s">
-        <v>1121</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
-        <v>1151</v>
+        <v>1167</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>952</v>
+        <v>962</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>1152</v>
+        <v>1168</v>
       </c>
       <c r="D44" s="21" t="s">
         <v>868</v>
@@ -12347,10 +13934,10 @@
       <c r="I44" s="28" t="n">
         <v>2759664</v>
       </c>
-      <c r="J44" s="90" t="n">
+      <c r="J44" s="92" t="n">
         <v>56.84</v>
       </c>
-      <c r="K44" s="103" t="n">
+      <c r="K44" s="105" t="n">
         <v>0.327</v>
       </c>
       <c r="L44" s="45" t="n">
@@ -12363,18 +13950,18 @@
         <v>0.066</v>
       </c>
       <c r="O44" s="20" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="21" t="s">
-        <v>1153</v>
+        <v>1169</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>949</v>
+        <v>959</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>1154</v>
+        <v>1170</v>
       </c>
       <c r="D45" s="21" t="s">
         <v>866</v>
@@ -12395,7 +13982,7 @@
       <c r="I45" s="28" t="n">
         <v>2940822</v>
       </c>
-      <c r="J45" s="90" t="n">
+      <c r="J45" s="92" t="n">
         <v>74.93</v>
       </c>
       <c r="K45" s="45" t="n">
@@ -12411,18 +13998,18 @@
         <v>0.392</v>
       </c>
       <c r="O45" s="20" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="21" t="s">
-        <v>1155</v>
+        <v>1171</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>1156</v>
+        <v>1172</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D46" s="21" t="s">
         <v>868</v>
@@ -12443,7 +14030,7 @@
       <c r="I46" s="28" t="n">
         <v>2694118</v>
       </c>
-      <c r="J46" s="90" t="n">
+      <c r="J46" s="92" t="n">
         <v>53.94</v>
       </c>
       <c r="K46" s="57" t="n">
@@ -12459,21 +14046,21 @@
         <v>0.236</v>
       </c>
       <c r="O46" s="21" t="s">
-        <v>1079</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="21" t="s">
-        <v>1157</v>
+        <v>1173</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>953</v>
+        <v>963</v>
       </c>
       <c r="C47" s="21" t="s">
         <v>347</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>1158</v>
+        <v>1174</v>
       </c>
       <c r="E47" s="21" t="n">
         <v>181</v>
@@ -12491,7 +14078,7 @@
       <c r="I47" s="28" t="n">
         <v>2650896</v>
       </c>
-      <c r="J47" s="90" t="n">
+      <c r="J47" s="92" t="n">
         <v>48.6</v>
       </c>
       <c r="K47" s="45" t="n">
@@ -12507,15 +14094,15 @@
         <v>0.184</v>
       </c>
       <c r="O47" s="21" t="s">
-        <v>1121</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="21" t="s">
-        <v>1159</v>
+        <v>1175</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>1160</v>
+        <v>1176</v>
       </c>
       <c r="C48" s="21" t="s">
         <v>361</v>
@@ -12539,10 +14126,10 @@
       <c r="I48" s="28" t="n">
         <v>2153145</v>
       </c>
-      <c r="J48" s="90" t="n">
+      <c r="J48" s="92" t="n">
         <v>57.15</v>
       </c>
-      <c r="K48" s="103" t="n">
+      <c r="K48" s="105" t="n">
         <v>0.064</v>
       </c>
       <c r="L48" s="45" t="n">
@@ -12555,21 +14142,21 @@
         <v>0</v>
       </c>
       <c r="O48" s="21" t="s">
-        <v>1074</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="21" t="s">
-        <v>1161</v>
+        <v>1177</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>1162</v>
+        <v>1178</v>
       </c>
       <c r="C49" s="21" t="s">
         <v>361</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>1109</v>
+        <v>1125</v>
       </c>
       <c r="E49" s="21" t="n">
         <v>181</v>
@@ -12587,10 +14174,10 @@
       <c r="I49" s="28" t="n">
         <v>2133587</v>
       </c>
-      <c r="J49" s="90" t="n">
+      <c r="J49" s="92" t="n">
         <v>62.82</v>
       </c>
-      <c r="K49" s="103" t="n">
+      <c r="K49" s="105" t="n">
         <v>0.256</v>
       </c>
       <c r="L49" s="45" t="n">
@@ -12603,18 +14190,18 @@
         <v>0.201</v>
       </c>
       <c r="O49" s="21" t="s">
-        <v>1074</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="21" t="s">
-        <v>1163</v>
+        <v>1179</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>1164</v>
+        <v>1180</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D50" s="21" t="s">
         <v>868</v>
@@ -12635,7 +14222,7 @@
       <c r="I50" s="28" t="n">
         <v>1912969</v>
       </c>
-      <c r="J50" s="90" t="n">
+      <c r="J50" s="92" t="n">
         <v>52.46</v>
       </c>
       <c r="K50" s="57" t="n">
@@ -12651,18 +14238,18 @@
         <v>0</v>
       </c>
       <c r="O50" s="21" t="s">
-        <v>1079</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="21" t="s">
-        <v>1165</v>
+        <v>1181</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D51" s="21" t="s">
         <v>868</v>
@@ -12683,10 +14270,10 @@
       <c r="I51" s="28" t="n">
         <v>568922</v>
       </c>
-      <c r="J51" s="90" t="n">
+      <c r="J51" s="92" t="n">
         <v>50.9</v>
       </c>
-      <c r="K51" s="102" t="n">
+      <c r="K51" s="104" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="45" t="n">
@@ -12704,16 +14291,16 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="21" t="s">
-        <v>1167</v>
+        <v>1183</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>1168</v>
+        <v>1184</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>1078</v>
+        <v>1094</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>1109</v>
+        <v>1125</v>
       </c>
       <c r="E52" s="21" t="n">
         <v>181</v>
@@ -12731,10 +14318,10 @@
       <c r="I52" s="28" t="n">
         <v>1672588</v>
       </c>
-      <c r="J52" s="90" t="n">
+      <c r="J52" s="92" t="n">
         <v>45.95</v>
       </c>
-      <c r="K52" s="103" t="n">
+      <c r="K52" s="105" t="n">
         <v>0.137</v>
       </c>
       <c r="L52" s="45" t="n">
@@ -12747,15 +14334,15 @@
         <v>0.017</v>
       </c>
       <c r="O52" s="21" t="s">
-        <v>1085</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="21" t="s">
-        <v>1169</v>
+        <v>1185</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>957</v>
+        <v>967</v>
       </c>
       <c r="C53" s="21" t="s">
         <v>350</v>
@@ -12779,7 +14366,7 @@
       <c r="I53" s="28" t="n">
         <v>1601535</v>
       </c>
-      <c r="J53" s="90" t="n">
+      <c r="J53" s="92" t="n">
         <v>55.38</v>
       </c>
       <c r="K53" s="45" t="n">
@@ -12795,15 +14382,15 @@
         <v>0.292</v>
       </c>
       <c r="O53" s="21" t="s">
-        <v>1085</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="21" t="s">
-        <v>1170</v>
+        <v>1186</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="C54" s="21" t="s">
         <v>352</v>
@@ -12827,7 +14414,7 @@
       <c r="I54" s="28" t="n">
         <v>1431054</v>
       </c>
-      <c r="J54" s="90" t="n">
+      <c r="J54" s="92" t="n">
         <v>53.68</v>
       </c>
       <c r="K54" s="45" t="n">
@@ -12843,21 +14430,21 @@
         <v>0.077</v>
       </c>
       <c r="O54" s="21" t="s">
-        <v>1074</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="21" t="s">
-        <v>1171</v>
+        <v>1187</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>1172</v>
+        <v>1188</v>
       </c>
       <c r="C55" s="21" t="s">
         <v>347</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>1109</v>
+        <v>1125</v>
       </c>
       <c r="E55" s="21" t="n">
         <v>181</v>
@@ -12875,10 +14462,10 @@
       <c r="I55" s="28" t="n">
         <v>1262094</v>
       </c>
-      <c r="J55" s="90" t="n">
+      <c r="J55" s="92" t="n">
         <v>53.3</v>
       </c>
-      <c r="K55" s="103" t="n">
+      <c r="K55" s="105" t="n">
         <v>0.188</v>
       </c>
       <c r="L55" s="45" t="n">
@@ -12891,15 +14478,15 @@
         <v>0.18</v>
       </c>
       <c r="O55" s="20" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="21" t="s">
-        <v>1173</v>
+        <v>1189</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>1174</v>
+        <v>1190</v>
       </c>
       <c r="C56" s="21" t="s">
         <v>347</v>
@@ -12923,10 +14510,10 @@
       <c r="I56" s="28" t="n">
         <v>1204453</v>
       </c>
-      <c r="J56" s="90" t="n">
+      <c r="J56" s="92" t="n">
         <v>34.88</v>
       </c>
-      <c r="K56" s="103" t="n">
+      <c r="K56" s="105" t="n">
         <v>0.06</v>
       </c>
       <c r="L56" s="45" t="n">
@@ -12939,12 +14526,12 @@
         <v>0.194</v>
       </c>
       <c r="O56" s="21" t="s">
-        <v>1085</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="21" t="s">
-        <v>1175</v>
+        <v>1191</v>
       </c>
       <c r="B57" s="16" t="s">
         <v>344</v>
@@ -12971,10 +14558,10 @@
       <c r="I57" s="28" t="n">
         <v>206212</v>
       </c>
-      <c r="J57" s="90" t="n">
+      <c r="J57" s="92" t="n">
         <v>57.08</v>
       </c>
-      <c r="K57" s="102" t="n">
+      <c r="K57" s="104" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="45" t="n">
@@ -12987,18 +14574,18 @@
         <v>0.249</v>
       </c>
       <c r="O57" s="20" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="21" t="s">
-        <v>1176</v>
+        <v>1192</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>964</v>
+        <v>974</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>1177</v>
+        <v>1193</v>
       </c>
       <c r="D58" s="21" t="s">
         <v>866</v>
@@ -13019,10 +14606,10 @@
       <c r="I58" s="28" t="n">
         <v>21693</v>
       </c>
-      <c r="J58" s="90" t="n">
+      <c r="J58" s="92" t="n">
         <v>49.96</v>
       </c>
-      <c r="K58" s="102" t="n">
+      <c r="K58" s="104" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="45" t="n">
@@ -13035,51 +14622,51 @@
         <v>0.167</v>
       </c>
       <c r="O58" s="20" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="67" t="s">
-        <v>1178</v>
+        <v>1194</v>
       </c>
       <c r="B59" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="F59" s="104" t="n">
+      <c r="F59" s="106" t="n">
         <f aca="false">SUM(F4:F58)</f>
         <v>502415662</v>
       </c>
-      <c r="G59" s="104" t="n">
+      <c r="G59" s="106" t="n">
         <f aca="false">SUM(G4:G58)</f>
         <v>1271395370.83428</v>
       </c>
-      <c r="H59" s="104" t="n">
+      <c r="H59" s="106" t="n">
         <f aca="false">SUM(H4:H58)</f>
         <v>8824895</v>
       </c>
-      <c r="I59" s="104" t="n">
+      <c r="I59" s="106" t="n">
         <f aca="false">SUM(I4:I58)</f>
         <v>219475297</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="105" t="s">
-        <v>1179</v>
-      </c>
-      <c r="B61" s="105"/>
-      <c r="C61" s="105"/>
-      <c r="D61" s="105"/>
-      <c r="E61" s="105"/>
-      <c r="F61" s="105"/>
-      <c r="G61" s="105"/>
-      <c r="H61" s="105"/>
-      <c r="I61" s="105"/>
-      <c r="J61" s="105"/>
-      <c r="K61" s="105"/>
-      <c r="L61" s="105"/>
-      <c r="M61" s="105"/>
-      <c r="N61" s="105"/>
-      <c r="O61" s="105"/>
+      <c r="A61" s="107" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B61" s="107"/>
+      <c r="C61" s="107"/>
+      <c r="D61" s="107"/>
+      <c r="E61" s="107"/>
+      <c r="F61" s="107"/>
+      <c r="G61" s="107"/>
+      <c r="H61" s="107"/>
+      <c r="I61" s="107"/>
+      <c r="J61" s="107"/>
+      <c r="K61" s="107"/>
+      <c r="L61" s="107"/>
+      <c r="M61" s="107"/>
+      <c r="N61" s="107"/>
+      <c r="O61" s="107"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/docs/executive-plan.xlsx
+++ b/docs/executive-plan.xlsx
@@ -19,10 +19,11 @@
     <sheet name="جاهزية الإطلاق" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="منفذ ١ — الوقود" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="تكلفة اللتر" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="الخطة التنفيذية" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="المستهدفات الربعية" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="المبادرات" sheetId="14" state="visible" r:id="rId16"/>
-    <sheet name="المحطات" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="مستهدفات البنزين" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="الخطة التنفيذية" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="المستهدفات الربعية" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="المبادرات" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="المحطات" sheetId="16" state="visible" r:id="rId18"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="1196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2116" uniqueCount="1240">
   <si>
     <t xml:space="preserve">نموذج الخطة التنفيذية — الإدارة التجارية</t>
   </si>
@@ -123,18 +124,18 @@
     <t xml:space="preserve">صف مثال توضيحي — يُحذف قبل الاعتماد</t>
   </si>
   <si>
-    <t xml:space="preserve">التطبيقات والمنصات</t>
+    <t xml:space="preserve">حصص السوق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حصص محطات المملكة وأين نقف.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حالة المنفذ</t>
   </si>
   <si>
     <t xml:space="preserve">تصنيف تطبيق أفراد · منصة شركات · بطاقة.</t>
   </si>
   <si>
-    <t xml:space="preserve">حالة المنفذ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بيانات 55 محطة (النصف الأول 2026) لربط المنافذ بالمواقع.</t>
-  </si>
-  <si>
     <t xml:space="preserve">قائم</t>
   </si>
   <si>
@@ -3012,6 +3013,444 @@
     <t xml:space="preserve">بيانات التوريد تغطي 50 محطة فقط، والمبيعات 55، والشبكة 355. فنموذج التكلفة هذا يمثّل الجزء الموثّق لا الشبكة كاملة.</t>
   </si>
   <si>
+    <t xml:space="preserve">مستهدفات البنزين لكل محطة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الهدف مفرّق حسب اتجاه كل محطة لا موحّد · وكل لتر إضافي = ربح مُدخل في الخانة الصفراء</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هدف موحّد على كل المحطات يفشل: طلب نمو 10% من محطة تفقد 22% خيال، ومن محطة تنمو 27% تقصير. لذلك تُصنَّف المحطات بأربع فئات ولكل فئة معدل هدف خاص — والهابطة هدفها الأول تقليل النزيف لا النمو، لأن لتراً محفوظاً يساوي لتراً مكتسباً.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المُدخلات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">معدل الهدف حسب الفئة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الربح لكل لتر (ريال)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">◄ 0.15 = 15 هللة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المعدل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المنطق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سعة الصهريج (لتر)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">◄ من بيانات التوريد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هابطة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عامل يُضرب في نزيف كل محطة — 0.5 يعني تقليله للنصف · لتر محفوظ = لتر مكتسب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">راكدة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نمو معتدل — الطاقة متاحة والاتجاه محايد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صاعدة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حافظ على الزخم مع دفعة إضافية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بلا بيانات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مؤقّت — يُراجع فور اكتمال بيانات النمو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الكود</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المنطقة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">النمط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بنزين سنوي (أساس)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">النمو الحالي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">معدل الهدف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المستهدف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الزيادة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نمو %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رحلات إضافية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أيام مخزون الآن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أثر الربح (ريال)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مكة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العمرة الجديدة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الطائف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العزيزية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الشيباني</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">النسيم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أحلى مساء</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مختلط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحليس - طريق الجنوب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جنوب الطائف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RY075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الدائري الشمالي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الدائري الثالث - الذكرى</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JA092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الصفا - أحد المسارحة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحسينية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">طريق الليث - الفضيلة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السواط - شهار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أبو وافي العمرة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الفلاح - فلسطين</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JA069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الجعرانة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RY025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحمرا - طريق الملك عبدالله</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AS153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عسير</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الرصيفة المسار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الجمعية الوسام</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الجموم - الكنيدري</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بطحاء قريش 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">طريق السيل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JA348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جنوب صبيا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بن درويش</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأجاويد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JA041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">القسوم - أحد المسارحة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الكر النازل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الملك خالد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EP051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الشرقية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JA053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نائية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RY024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">غرناطة - طريق الملك عبدالله</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JA061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">طريق صبيا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بطحاء قريش 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الشرايع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جبل ثور - جوهرة النسيم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QS055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">القصيم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RY042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الناصفة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">البيعة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HA043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JA056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الروابي - المودة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JA060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صناعية صامطة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MD009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NJ219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نجران</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لماذا الفئات وليس معدلاً واحداً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">البنزين 478.9 مليون لتر سنوياً = 81.4% من لتراتنا. لكنه موزّع على أربع حالات مختلفة جوهرياً: 13 محطة هابطة تحمل 28.0% من البنزين · 17 صاعدة تحمل 24.2% · 11 راكدة 14.9% · و14 بلا بيانات نمو تحمل 33.0%. معدل واحد على الأربع يظلم بعضها ويجامل بعضها.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كيف تُقرأ معدلات الفئات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ثلاث فئات معدّلها نسبة نمو مباشرة (راكدة · صاعدة · بلا بيانات). أما الهابطة فمعدّلها عامل يُضرب في نزيف كل محطة على حدة: 0.50 يعني تقليل النزيف للنصف، فمحطة تفقد 22.3% يصبح هدفها −11.2% وأخرى تفقد 53.3% يصبح هدفها −26.7%. معدل مطلق واحد كان سيظلم الأولى ويجامل الثانية.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الهابطة: لتر محفوظ = لتر مكتسب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK007 العمرة الجديدة تفقد 22.3% على 34.1 مليون لتر بنزين. تقليل النزيف إلى النصف يحفظ نحو 3.8 مليون لتر — أي أكثر مما تنتجه أي مبادرة نمو في محطة صغيرة. ولذلك ترتيب الأولوية في الجدول يقيس اللترات لا النسب.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔴 قيد الطاقة الاستيعابية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عمود «أيام مخزون الآن» يكشف من لا يحتمل الزيادة: MK007 و MK072 مخزونهما 2.6 يوم بنزين فقط. زيادة المبيعات فيهما تعني نفاداً أسرع — فالهدف هناك يتطلب رفع تردد التوريد أولاً، وعمود «رحلات إضافية» يحسب كم رحلة يلزم إضافتها. أي هدف بلا هذه الرحلات هدف على الورق.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحلقة مع نموذج التكلفة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كل لتر إضافي يحمل ربح 15 هللة — لكنه يستدعي أيضاً رحلة نقل إضافية كل 32,500 لتر. وبما أن أجرة الرحلة تُقسَّم على حمولة كاملة، فالزيادة تبقى مربحة ما دام هامش التوزيع يغطي النقل. والرابح الأكبر: الزيادة توزّع التكاليف الثابتة (العمالة والإيجار) على قاعدة أكبر، فتنخفض تكلفة اللتر لكل اللترات لا للإضافية فقط.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔴 اختبار السيناريوهات — اقرأه قبل تثبيت أي معدل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خط الأساس 478.9 مليون لتر بنزين. والنزيف الحالي من الـ13 محطة الهابطة وحده −24.4 مليون لتر سنوياً. النتيجة: تقليل النزيف للنصف مع نمو 3–8% على الباقي يعطي الشبكة +0.6% فقط (+440 ألف ريال). أي أن الهدف المعتدل يستهلكه النزيف ولا يبقى منه شيء. أما إيقاف النزيف تماماً مع نمو 5–10% فيعطي +4.6% (+3.3 مليون ريال)، وإيقافه مع دفع قوي 8–12% يعطي +6.6% (+4.7 مليون ريال). والرقم الحاكم: لتعويض نزيف الهابطة وحده يحتاج باقي الشبكة نمواً بـ7.1%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ما يجب حسمه قبل اعتماد المستهدفات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① معدلات الفئات الأربع (الخانات الصفراء) قرار إدارة لا حساب. ② الـ14 محطة «بلا بيانات» تحمل ثلث البنزين — ومستهدفاتها مؤقّتة حتى تكتمل بياناتها. ③ تشخيص تراجع مكة ما زال مفتوحاً: بلا معرفة السبب، هدف «تقليل النزيف» أمنية لا خطة.</t>
+  </si>
+  <si>
     <t xml:space="preserve">الخطة التنفيذية لمنافذ البيع</t>
   </si>
   <si>
@@ -3261,9 +3700,6 @@
     <t xml:space="preserve">الرمز</t>
   </si>
   <si>
-    <t xml:space="preserve">المنطقة</t>
-  </si>
-  <si>
     <t xml:space="preserve">نمط الموقع</t>
   </si>
   <si>
@@ -3297,325 +3733,22 @@
     <t xml:space="preserve">نشاط تجاري</t>
   </si>
   <si>
-    <t xml:space="preserve">MK007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">العمرة الجديدة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مكة</t>
-  </si>
-  <si>
     <t xml:space="preserve">3 نشاط</t>
   </si>
   <si>
-    <t xml:space="preserve">MK003</t>
-  </si>
-  <si>
     <t xml:space="preserve">5 نشاط</t>
   </si>
   <si>
-    <t xml:space="preserve">MK004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الطائف</t>
-  </si>
-  <si>
     <t xml:space="preserve">4 نشاط</t>
   </si>
   <si>
-    <t xml:space="preserve">MK289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">طريق الليث - الفضيلة</t>
-  </si>
-  <si>
     <t xml:space="preserve">لا يوجد</t>
   </si>
   <si>
-    <t xml:space="preserve">MK072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">العزيزية</t>
-  </si>
-  <si>
     <t xml:space="preserve">2 نشاط</t>
   </si>
   <si>
-    <t xml:space="preserve">MK046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الحليس - طريق الجنوب</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مختلط</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الشيباني</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">النسيم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أحلى مساء</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الدائري الثالث - الذكرى</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أبو وافي العمرة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RY075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الدائري الشمالي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">جنوب الطائف</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الصفا - أحد المسارحة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الحسينية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الفلاح - فلسطين</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السواط - شهار</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الجعرانة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الجمعية الوسام</t>
-  </si>
-  <si>
     <t xml:space="preserve">1 نشاط</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">طريق السيل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بطحاء قريش 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الرصيفة المسار</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RY025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الحمرا - طريق الملك عبدالله</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AS153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عسير</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الجموم - الكنيدري</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">جنوب صبيا</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الأجاويد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الكر النازل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">طريق صبيا</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بن درويش</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">القسوم - أحد المسارحة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الملك خالد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EP051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الشرقية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QS055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">القصيم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بطحاء قريش 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نائية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RY024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">غرناطة - طريق الملك عبدالله</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RY042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الناصفة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الشرايع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">جبل ثور - جوهرة النسيم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">البيعة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HA043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الروابي - المودة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">صناعية صامطة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MD009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NJ219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نجران</t>
   </si>
   <si>
     <t xml:space="preserve">55</t>
@@ -3628,7 +3761,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="15">
+  <numFmts count="17">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
@@ -3642,8 +3775,10 @@
     <numFmt numFmtId="174" formatCode="0.000"/>
     <numFmt numFmtId="175" formatCode="0.0000"/>
     <numFmt numFmtId="176" formatCode="\+0.0000;\-0.0000"/>
-    <numFmt numFmtId="177" formatCode="#,##0.00"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="\+0.0%;\-0.0%"/>
+    <numFmt numFmtId="178" formatCode="\+#,##0;\-#,##0"/>
+    <numFmt numFmtId="179" formatCode="#,##0.00"/>
+    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -3931,7 +4066,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="116">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3972,12 +4107,12 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -4288,6 +4423,38 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
@@ -4300,11 +4467,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="179" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4328,11 +4495,11 @@
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="180" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4340,7 +4507,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="180" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4770,15 +4937,15 @@
       <c r="B21" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="11" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4786,7 +4953,7 @@
       <c r="B23" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="11" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4794,7 +4961,7 @@
       <c r="B24" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="11" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4802,7 +4969,7 @@
       <c r="B25" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="11" t="s">
         <v>42</v>
       </c>
     </row>
@@ -4933,7 +5100,7 @@
       <c r="C6" s="21" t="s">
         <v>822</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="10" t="s">
         <v>823</v>
       </c>
       <c r="E6" s="21"/>
@@ -4952,7 +5119,7 @@
       <c r="C7" s="21" t="s">
         <v>826</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="10" t="s">
         <v>827</v>
       </c>
       <c r="E7" s="21"/>
@@ -4971,7 +5138,7 @@
       <c r="C8" s="21" t="s">
         <v>830</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="10" t="s">
         <v>831</v>
       </c>
       <c r="E8" s="21"/>
@@ -5604,7 +5771,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="11" t="s">
         <v>888</v>
       </c>
       <c r="C7" s="81"/>
@@ -5616,7 +5783,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="11" t="s">
         <v>890</v>
       </c>
       <c r="C8" s="81"/>
@@ -5626,7 +5793,7 @@
       <c r="F8" s="26"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="11" t="s">
         <v>892</v>
       </c>
       <c r="C9" s="81"/>
@@ -5636,7 +5803,7 @@
       <c r="F9" s="26"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="11" t="s">
         <v>894</v>
       </c>
       <c r="C10" s="83"/>
@@ -5646,7 +5813,7 @@
       <c r="F10" s="26"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
         <v>896</v>
       </c>
       <c r="C11" s="83"/>
@@ -5656,7 +5823,7 @@
       <c r="F11" s="26"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="11" t="s">
         <v>898</v>
       </c>
       <c r="C12" s="83"/>
@@ -5666,7 +5833,7 @@
       <c r="F12" s="26"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="11" t="s">
         <v>900</v>
       </c>
       <c r="C13" s="83"/>
@@ -5676,7 +5843,7 @@
       <c r="F13" s="26"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="11" t="s">
         <v>902</v>
       </c>
       <c r="C14" s="83"/>
@@ -10051,6 +10218,3545 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:P75"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="52" t="s">
+        <v>510</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>994</v>
+      </c>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="53"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="78" t="s">
+        <v>995</v>
+      </c>
+      <c r="G5" s="78" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="11" t="s">
+        <v>997</v>
+      </c>
+      <c r="D6" s="69"/>
+      <c r="E6" s="70" t="s">
+        <v>998</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>999</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>32500</v>
+      </c>
+      <c r="E7" s="70" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H7" s="69"/>
+      <c r="I7" s="89" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G8" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H8" s="90"/>
+      <c r="I8" s="89" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G9" s="6" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H9" s="90"/>
+      <c r="I9" s="89" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G10" s="6" t="s">
+        <v>1009</v>
+      </c>
+      <c r="H10" s="90"/>
+      <c r="I10" s="89" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>858</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>1016</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>1017</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>1018</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>1019</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>1020</v>
+      </c>
+      <c r="N11" s="15" t="s">
+        <v>1021</v>
+      </c>
+      <c r="O11" s="15" t="s">
+        <v>1022</v>
+      </c>
+      <c r="P11" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>926</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>862</v>
+      </c>
+      <c r="F12" s="28" t="n">
+        <v>35464924</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I12" s="91" t="n">
+        <f aca="false">IFERROR(IF(H12="هابطة",G12*$H$7,INDEX($H$7:$H$10,MATCH(H12,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="28" t="n">
+        <f aca="false">IFERROR(F12*(1+I12),"")</f>
+        <v>35464924</v>
+      </c>
+      <c r="K12" s="92" t="n">
+        <f aca="false">IFERROR(J12-F12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="91" t="n">
+        <f aca="false">IFERROR(K12/F12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K12/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="73" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O12" s="93" t="n">
+        <f aca="false">IFERROR(K12*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K12,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F13" s="28" t="n">
+        <v>34063312</v>
+      </c>
+      <c r="G13" s="91" t="n">
+        <v>-0.223</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I13" s="91" t="n">
+        <f aca="false">IFERROR(IF(H13="هابطة",G13*$H$7,INDEX($H$7:$H$10,MATCH(H13,$G$7:$G$10,0))),"")</f>
+        <v>-0</v>
+      </c>
+      <c r="J13" s="28" t="n">
+        <f aca="false">IFERROR(F13*(1+I13),"")</f>
+        <v>34063312</v>
+      </c>
+      <c r="K13" s="92" t="n">
+        <f aca="false">IFERROR(J13-F13,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="91" t="n">
+        <f aca="false">IFERROR(K13/F13,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K13/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="94" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O13" s="93" t="n">
+        <f aca="false">IFERROR(K13*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K13,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>927</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F14" s="28" t="n">
+        <v>19648510</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I14" s="91" t="n">
+        <f aca="false">IFERROR(IF(H14="هابطة",G14*$H$7,INDEX($H$7:$H$10,MATCH(H14,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="28" t="n">
+        <f aca="false">IFERROR(F14*(1+I14),"")</f>
+        <v>19648510</v>
+      </c>
+      <c r="K14" s="92" t="n">
+        <f aca="false">IFERROR(J14-F14,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="91" t="n">
+        <f aca="false">IFERROR(K14/F14,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K14/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="73" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O14" s="93" t="n">
+        <f aca="false">IFERROR(K14*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K14,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F15" s="28" t="n">
+        <v>16732843</v>
+      </c>
+      <c r="G15" s="91" t="n">
+        <v>-0.211</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I15" s="91" t="n">
+        <f aca="false">IFERROR(IF(H15="هابطة",G15*$H$7,INDEX($H$7:$H$10,MATCH(H15,$G$7:$G$10,0))),"")</f>
+        <v>-0</v>
+      </c>
+      <c r="J15" s="28" t="n">
+        <f aca="false">IFERROR(F15*(1+I15),"")</f>
+        <v>16732843</v>
+      </c>
+      <c r="K15" s="92" t="n">
+        <f aca="false">IFERROR(J15-F15,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="91" t="n">
+        <f aca="false">IFERROR(K15/F15,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K15/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="94" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O15" s="93" t="n">
+        <f aca="false">IFERROR(K15*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K15,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F16" s="28" t="n">
+        <v>16309064</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I16" s="91" t="n">
+        <f aca="false">IFERROR(IF(H16="هابطة",G16*$H$7,INDEX($H$7:$H$10,MATCH(H16,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="28" t="n">
+        <f aca="false">IFERROR(F16*(1+I16),"")</f>
+        <v>16309064</v>
+      </c>
+      <c r="K16" s="92" t="n">
+        <f aca="false">IFERROR(J16-F16,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="91" t="n">
+        <f aca="false">IFERROR(K16/F16,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K16/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="73" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="O16" s="93" t="n">
+        <f aca="false">IFERROR(K16*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K16,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F17" s="28" t="n">
+        <v>16280701</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H17" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I17" s="91" t="n">
+        <f aca="false">IFERROR(IF(H17="هابطة",G17*$H$7,INDEX($H$7:$H$10,MATCH(H17,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="28" t="n">
+        <f aca="false">IFERROR(F17*(1+I17),"")</f>
+        <v>16280701</v>
+      </c>
+      <c r="K17" s="92" t="n">
+        <f aca="false">IFERROR(J17-F17,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="91" t="n">
+        <f aca="false">IFERROR(K17/F17,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K17/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="73" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="O17" s="93" t="n">
+        <f aca="false">IFERROR(K17*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K17,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F18" s="28" t="n">
+        <v>14309768</v>
+      </c>
+      <c r="G18" s="91" t="n">
+        <v>-0.119</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I18" s="91" t="n">
+        <f aca="false">IFERROR(IF(H18="هابطة",G18*$H$7,INDEX($H$7:$H$10,MATCH(H18,$G$7:$G$10,0))),"")</f>
+        <v>-0</v>
+      </c>
+      <c r="J18" s="28" t="n">
+        <f aca="false">IFERROR(F18*(1+I18),"")</f>
+        <v>14309768</v>
+      </c>
+      <c r="K18" s="92" t="n">
+        <f aca="false">IFERROR(J18-F18,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="91" t="n">
+        <f aca="false">IFERROR(K18/F18,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K18/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="73" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O18" s="93" t="n">
+        <f aca="false">IFERROR(K18*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K18,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F19" s="28" t="n">
+        <v>13354076</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H19" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I19" s="91" t="n">
+        <f aca="false">IFERROR(IF(H19="هابطة",G19*$H$7,INDEX($H$7:$H$10,MATCH(H19,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="28" t="n">
+        <f aca="false">IFERROR(F19*(1+I19),"")</f>
+        <v>13354076</v>
+      </c>
+      <c r="K19" s="92" t="n">
+        <f aca="false">IFERROR(J19-F19,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="91" t="n">
+        <f aca="false">IFERROR(K19/F19,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K19/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="73" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O19" s="93" t="n">
+        <f aca="false">IFERROR(K19*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K19,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F20" s="28" t="n">
+        <v>13311973</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H20" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I20" s="91" t="n">
+        <f aca="false">IFERROR(IF(H20="هابطة",G20*$H$7,INDEX($H$7:$H$10,MATCH(H20,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="28" t="n">
+        <f aca="false">IFERROR(F20*(1+I20),"")</f>
+        <v>13311973</v>
+      </c>
+      <c r="K20" s="92" t="n">
+        <f aca="false">IFERROR(J20-F20,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="91" t="n">
+        <f aca="false">IFERROR(K20/F20,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K20/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="73" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O20" s="93" t="n">
+        <f aca="false">IFERROR(K20*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P20" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K20,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>938</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F21" s="28" t="n">
+        <v>13248903</v>
+      </c>
+      <c r="G21" s="91" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I21" s="91" t="n">
+        <f aca="false">IFERROR(IF(H21="هابطة",G21*$H$7,INDEX($H$7:$H$10,MATCH(H21,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="28" t="n">
+        <f aca="false">IFERROR(F21*(1+I21),"")</f>
+        <v>13248903</v>
+      </c>
+      <c r="K21" s="92" t="n">
+        <f aca="false">IFERROR(J21-F21,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="91" t="n">
+        <f aca="false">IFERROR(K21/F21,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K21/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N21" s="73" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O21" s="93" t="n">
+        <f aca="false">IFERROR(K21*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P21" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K21,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F22" s="28" t="n">
+        <v>13247588</v>
+      </c>
+      <c r="G22" s="91" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I22" s="91" t="n">
+        <f aca="false">IFERROR(IF(H22="هابطة",G22*$H$7,INDEX($H$7:$H$10,MATCH(H22,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="28" t="n">
+        <f aca="false">IFERROR(F22*(1+I22),"")</f>
+        <v>13247588</v>
+      </c>
+      <c r="K22" s="92" t="n">
+        <f aca="false">IFERROR(J22-F22,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="91" t="n">
+        <f aca="false">IFERROR(K22/F22,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K22/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="73" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O22" s="93" t="n">
+        <f aca="false">IFERROR(K22*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P22" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K22,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>931</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F23" s="28" t="n">
+        <v>12654914</v>
+      </c>
+      <c r="G23" s="91" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="H23" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I23" s="91" t="n">
+        <f aca="false">IFERROR(IF(H23="هابطة",G23*$H$7,INDEX($H$7:$H$10,MATCH(H23,$G$7:$G$10,0))),"")</f>
+        <v>-0</v>
+      </c>
+      <c r="J23" s="28" t="n">
+        <f aca="false">IFERROR(F23*(1+I23),"")</f>
+        <v>12654914</v>
+      </c>
+      <c r="K23" s="92" t="n">
+        <f aca="false">IFERROR(J23-F23,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="91" t="n">
+        <f aca="false">IFERROR(K23/F23,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K23/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N23" s="73" t="n">
+        <v>4</v>
+      </c>
+      <c r="O23" s="93" t="n">
+        <f aca="false">IFERROR(K23*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P23" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K23,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F24" s="28" t="n">
+        <v>11988986</v>
+      </c>
+      <c r="G24" s="91" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I24" s="91" t="n">
+        <f aca="false">IFERROR(IF(H24="هابطة",G24*$H$7,INDEX($H$7:$H$10,MATCH(H24,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="28" t="n">
+        <f aca="false">IFERROR(F24*(1+I24),"")</f>
+        <v>11988986</v>
+      </c>
+      <c r="K24" s="92" t="n">
+        <f aca="false">IFERROR(J24-F24,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="91" t="n">
+        <f aca="false">IFERROR(K24/F24,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K24/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="73" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O24" s="93" t="n">
+        <f aca="false">IFERROR(K24*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P24" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K24,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>866</v>
+      </c>
+      <c r="F25" s="28" t="n">
+        <v>11882308</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H25" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I25" s="91" t="n">
+        <f aca="false">IFERROR(IF(H25="هابطة",G25*$H$7,INDEX($H$7:$H$10,MATCH(H25,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="28" t="n">
+        <f aca="false">IFERROR(F25*(1+I25),"")</f>
+        <v>11882308</v>
+      </c>
+      <c r="K25" s="92" t="n">
+        <f aca="false">IFERROR(J25-F25,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="91" t="n">
+        <f aca="false">IFERROR(K25/F25,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K25/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N25" s="21"/>
+      <c r="O25" s="93" t="n">
+        <f aca="false">IFERROR(K25*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K25,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F26" s="28" t="n">
+        <v>11625662</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H26" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I26" s="91" t="n">
+        <f aca="false">IFERROR(IF(H26="هابطة",G26*$H$7,INDEX($H$7:$H$10,MATCH(H26,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="28" t="n">
+        <f aca="false">IFERROR(F26*(1+I26),"")</f>
+        <v>11625662</v>
+      </c>
+      <c r="K26" s="92" t="n">
+        <f aca="false">IFERROR(J26-F26,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="91" t="n">
+        <f aca="false">IFERROR(K26/F26,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K26/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N26" s="73" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O26" s="93" t="n">
+        <f aca="false">IFERROR(K26*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P26" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K26,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>940</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F27" s="28" t="n">
+        <v>11101203</v>
+      </c>
+      <c r="G27" s="91" t="n">
+        <v>-0.112</v>
+      </c>
+      <c r="H27" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I27" s="91" t="n">
+        <f aca="false">IFERROR(IF(H27="هابطة",G27*$H$7,INDEX($H$7:$H$10,MATCH(H27,$G$7:$G$10,0))),"")</f>
+        <v>-0</v>
+      </c>
+      <c r="J27" s="28" t="n">
+        <f aca="false">IFERROR(F27*(1+I27),"")</f>
+        <v>11101203</v>
+      </c>
+      <c r="K27" s="92" t="n">
+        <f aca="false">IFERROR(J27-F27,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="91" t="n">
+        <f aca="false">IFERROR(K27/F27,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K27/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N27" s="73" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="O27" s="93" t="n">
+        <f aca="false">IFERROR(K27*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P27" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K27,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>862</v>
+      </c>
+      <c r="F28" s="28" t="n">
+        <v>10864480</v>
+      </c>
+      <c r="G28" s="91" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I28" s="91" t="n">
+        <f aca="false">IFERROR(IF(H28="هابطة",G28*$H$7,INDEX($H$7:$H$10,MATCH(H28,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="28" t="n">
+        <f aca="false">IFERROR(F28*(1+I28),"")</f>
+        <v>10864480</v>
+      </c>
+      <c r="K28" s="92" t="n">
+        <f aca="false">IFERROR(J28-F28,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="91" t="n">
+        <f aca="false">IFERROR(K28/F28,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K28/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N28" s="21"/>
+      <c r="O28" s="93" t="n">
+        <f aca="false">IFERROR(K28*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P28" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K28,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>944</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F29" s="28" t="n">
+        <v>9931491</v>
+      </c>
+      <c r="G29" s="91" t="n">
+        <v>0.069</v>
+      </c>
+      <c r="H29" s="18" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I29" s="91" t="n">
+        <f aca="false">IFERROR(IF(H29="هابطة",G29*$H$7,INDEX($H$7:$H$10,MATCH(H29,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="28" t="n">
+        <f aca="false">IFERROR(F29*(1+I29),"")</f>
+        <v>9931491</v>
+      </c>
+      <c r="K29" s="92" t="n">
+        <f aca="false">IFERROR(J29-F29,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="91" t="n">
+        <f aca="false">IFERROR(K29/F29,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K29/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N29" s="73" t="n">
+        <v>8.8</v>
+      </c>
+      <c r="O29" s="93" t="n">
+        <f aca="false">IFERROR(K29*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P29" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K29,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>943</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F30" s="28" t="n">
+        <v>9558604</v>
+      </c>
+      <c r="G30" s="91" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I30" s="91" t="n">
+        <f aca="false">IFERROR(IF(H30="هابطة",G30*$H$7,INDEX($H$7:$H$10,MATCH(H30,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="28" t="n">
+        <f aca="false">IFERROR(F30*(1+I30),"")</f>
+        <v>9558604</v>
+      </c>
+      <c r="K30" s="92" t="n">
+        <f aca="false">IFERROR(J30-F30,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="91" t="n">
+        <f aca="false">IFERROR(K30/F30,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K30/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N30" s="73" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O30" s="93" t="n">
+        <f aca="false">IFERROR(K30*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P30" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K30,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F31" s="28" t="n">
+        <v>9064151</v>
+      </c>
+      <c r="G31" s="91" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="H31" s="18" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I31" s="91" t="n">
+        <f aca="false">IFERROR(IF(H31="هابطة",G31*$H$7,INDEX($H$7:$H$10,MATCH(H31,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="28" t="n">
+        <f aca="false">IFERROR(F31*(1+I31),"")</f>
+        <v>9064151</v>
+      </c>
+      <c r="K31" s="92" t="n">
+        <f aca="false">IFERROR(J31-F31,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="91" t="n">
+        <f aca="false">IFERROR(K31/F31,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K31/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N31" s="73" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O31" s="93" t="n">
+        <f aca="false">IFERROR(K31*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P31" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K31,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>862</v>
+      </c>
+      <c r="F32" s="28" t="n">
+        <v>8548346</v>
+      </c>
+      <c r="G32" s="91" t="n">
+        <v>-0.217</v>
+      </c>
+      <c r="H32" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I32" s="91" t="n">
+        <f aca="false">IFERROR(IF(H32="هابطة",G32*$H$7,INDEX($H$7:$H$10,MATCH(H32,$G$7:$G$10,0))),"")</f>
+        <v>-0</v>
+      </c>
+      <c r="J32" s="28" t="n">
+        <f aca="false">IFERROR(F32*(1+I32),"")</f>
+        <v>8548346</v>
+      </c>
+      <c r="K32" s="92" t="n">
+        <f aca="false">IFERROR(J32-F32,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="91" t="n">
+        <f aca="false">IFERROR(K32/F32,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K32/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N32" s="73" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O32" s="93" t="n">
+        <f aca="false">IFERROR(K32*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P32" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K32,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F33" s="28" t="n">
+        <v>7867941</v>
+      </c>
+      <c r="G33" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H33" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I33" s="91" t="n">
+        <f aca="false">IFERROR(IF(H33="هابطة",G33*$H$7,INDEX($H$7:$H$10,MATCH(H33,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="28" t="n">
+        <f aca="false">IFERROR(F33*(1+I33),"")</f>
+        <v>7867941</v>
+      </c>
+      <c r="K33" s="92" t="n">
+        <f aca="false">IFERROR(J33-F33,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="91" t="n">
+        <f aca="false">IFERROR(K33/F33,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K33/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N33" s="21"/>
+      <c r="O33" s="93" t="n">
+        <f aca="false">IFERROR(K33*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P33" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K33,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>950</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F34" s="28" t="n">
+        <v>7444371</v>
+      </c>
+      <c r="G34" s="91" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I34" s="91" t="n">
+        <f aca="false">IFERROR(IF(H34="هابطة",G34*$H$7,INDEX($H$7:$H$10,MATCH(H34,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="28" t="n">
+        <f aca="false">IFERROR(F34*(1+I34),"")</f>
+        <v>7444371</v>
+      </c>
+      <c r="K34" s="92" t="n">
+        <f aca="false">IFERROR(J34-F34,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="91" t="n">
+        <f aca="false">IFERROR(K34/F34,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K34/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="73" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O34" s="93" t="n">
+        <f aca="false">IFERROR(K34*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P34" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K34,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F35" s="28" t="n">
+        <v>7193020</v>
+      </c>
+      <c r="G35" s="91" t="n">
+        <v>-0.033</v>
+      </c>
+      <c r="H35" s="19" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I35" s="91" t="n">
+        <f aca="false">IFERROR(IF(H35="هابطة",G35*$H$7,INDEX($H$7:$H$10,MATCH(H35,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="28" t="n">
+        <f aca="false">IFERROR(F35*(1+I35),"")</f>
+        <v>7193020</v>
+      </c>
+      <c r="K35" s="92" t="n">
+        <f aca="false">IFERROR(J35-F35,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L35" s="91" t="n">
+        <f aca="false">IFERROR(K35/F35,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M35" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K35/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N35" s="73" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O35" s="93" t="n">
+        <f aca="false">IFERROR(K35*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P35" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K35,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>866</v>
+      </c>
+      <c r="F36" s="28" t="n">
+        <v>7191456</v>
+      </c>
+      <c r="G36" s="91" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="H36" s="18" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I36" s="91" t="n">
+        <f aca="false">IFERROR(IF(H36="هابطة",G36*$H$7,INDEX($H$7:$H$10,MATCH(H36,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="28" t="n">
+        <f aca="false">IFERROR(F36*(1+I36),"")</f>
+        <v>7191456</v>
+      </c>
+      <c r="K36" s="92" t="n">
+        <f aca="false">IFERROR(J36-F36,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L36" s="91" t="n">
+        <f aca="false">IFERROR(K36/F36,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M36" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K36/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N36" s="73" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O36" s="93" t="n">
+        <f aca="false">IFERROR(K36*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P36" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K36,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>952</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F37" s="28" t="n">
+        <v>6999984</v>
+      </c>
+      <c r="G37" s="91" t="n">
+        <v>-0.533</v>
+      </c>
+      <c r="H37" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I37" s="91" t="n">
+        <f aca="false">IFERROR(IF(H37="هابطة",G37*$H$7,INDEX($H$7:$H$10,MATCH(H37,$G$7:$G$10,0))),"")</f>
+        <v>-0</v>
+      </c>
+      <c r="J37" s="28" t="n">
+        <f aca="false">IFERROR(F37*(1+I37),"")</f>
+        <v>6999984</v>
+      </c>
+      <c r="K37" s="92" t="n">
+        <f aca="false">IFERROR(J37-F37,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L37" s="91" t="n">
+        <f aca="false">IFERROR(K37/F37,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M37" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K37/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N37" s="73" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="O37" s="93" t="n">
+        <f aca="false">IFERROR(K37*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P37" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K37,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>968</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>866</v>
+      </c>
+      <c r="F38" s="28" t="n">
+        <v>6980426</v>
+      </c>
+      <c r="G38" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H38" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I38" s="91" t="n">
+        <f aca="false">IFERROR(IF(H38="هابطة",G38*$H$7,INDEX($H$7:$H$10,MATCH(H38,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="28" t="n">
+        <f aca="false">IFERROR(F38*(1+I38),"")</f>
+        <v>6980426</v>
+      </c>
+      <c r="K38" s="92" t="n">
+        <f aca="false">IFERROR(J38-F38,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L38" s="91" t="n">
+        <f aca="false">IFERROR(K38/F38,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M38" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K38/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N38" s="73" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O38" s="93" t="n">
+        <f aca="false">IFERROR(K38*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P38" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K38,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F39" s="28" t="n">
+        <v>6955614</v>
+      </c>
+      <c r="G39" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H39" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I39" s="91" t="n">
+        <f aca="false">IFERROR(IF(H39="هابطة",G39*$H$7,INDEX($H$7:$H$10,MATCH(H39,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="28" t="n">
+        <f aca="false">IFERROR(F39*(1+I39),"")</f>
+        <v>6955614</v>
+      </c>
+      <c r="K39" s="92" t="n">
+        <f aca="false">IFERROR(J39-F39,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="91" t="n">
+        <f aca="false">IFERROR(K39/F39,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M39" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K39/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N39" s="73" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O39" s="93" t="n">
+        <f aca="false">IFERROR(K39*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P39" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K39,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C40" s="24" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F40" s="28" t="n">
+        <v>6835043</v>
+      </c>
+      <c r="G40" s="91" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="H40" s="18" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I40" s="91" t="n">
+        <f aca="false">IFERROR(IF(H40="هابطة",G40*$H$7,INDEX($H$7:$H$10,MATCH(H40,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="28" t="n">
+        <f aca="false">IFERROR(F40*(1+I40),"")</f>
+        <v>6835043</v>
+      </c>
+      <c r="K40" s="92" t="n">
+        <f aca="false">IFERROR(J40-F40,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L40" s="91" t="n">
+        <f aca="false">IFERROR(K40/F40,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M40" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K40/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N40" s="73" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O40" s="93" t="n">
+        <f aca="false">IFERROR(K40*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P40" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K40,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F41" s="28" t="n">
+        <v>6267957</v>
+      </c>
+      <c r="G41" s="91" t="n">
+        <v>-0.068</v>
+      </c>
+      <c r="H41" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I41" s="91" t="n">
+        <f aca="false">IFERROR(IF(H41="هابطة",G41*$H$7,INDEX($H$7:$H$10,MATCH(H41,$G$7:$G$10,0))),"")</f>
+        <v>-0</v>
+      </c>
+      <c r="J41" s="28" t="n">
+        <f aca="false">IFERROR(F41*(1+I41),"")</f>
+        <v>6267957</v>
+      </c>
+      <c r="K41" s="92" t="n">
+        <f aca="false">IFERROR(J41-F41,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L41" s="91" t="n">
+        <f aca="false">IFERROR(K41/F41,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M41" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K41/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N41" s="73" t="n">
+        <v>7</v>
+      </c>
+      <c r="O41" s="93" t="n">
+        <f aca="false">IFERROR(K41*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P41" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K41,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E42" s="21" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F42" s="28" t="n">
+        <v>6241831</v>
+      </c>
+      <c r="G42" s="91" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I42" s="91" t="n">
+        <f aca="false">IFERROR(IF(H42="هابطة",G42*$H$7,INDEX($H$7:$H$10,MATCH(H42,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="28" t="n">
+        <f aca="false">IFERROR(F42*(1+I42),"")</f>
+        <v>6241831</v>
+      </c>
+      <c r="K42" s="92" t="n">
+        <f aca="false">IFERROR(J42-F42,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="91" t="n">
+        <f aca="false">IFERROR(K42/F42,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M42" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K42/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N42" s="73" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="O42" s="93" t="n">
+        <f aca="false">IFERROR(K42*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P42" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K42,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C43" s="24" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E43" s="21" t="s">
+        <v>862</v>
+      </c>
+      <c r="F43" s="28" t="n">
+        <v>6066855</v>
+      </c>
+      <c r="G43" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H43" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I43" s="91" t="n">
+        <f aca="false">IFERROR(IF(H43="هابطة",G43*$H$7,INDEX($H$7:$H$10,MATCH(H43,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="28" t="n">
+        <f aca="false">IFERROR(F43*(1+I43),"")</f>
+        <v>6066855</v>
+      </c>
+      <c r="K43" s="92" t="n">
+        <f aca="false">IFERROR(J43-F43,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L43" s="91" t="n">
+        <f aca="false">IFERROR(K43/F43,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M43" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K43/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N43" s="73" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="O43" s="93" t="n">
+        <f aca="false">IFERROR(K43*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P43" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K43,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D44" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E44" s="21" t="s">
+        <v>866</v>
+      </c>
+      <c r="F44" s="28" t="n">
+        <v>6046920</v>
+      </c>
+      <c r="G44" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H44" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I44" s="91" t="n">
+        <f aca="false">IFERROR(IF(H44="هابطة",G44*$H$7,INDEX($H$7:$H$10,MATCH(H44,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="28" t="n">
+        <f aca="false">IFERROR(F44*(1+I44),"")</f>
+        <v>6046920</v>
+      </c>
+      <c r="K44" s="92" t="n">
+        <f aca="false">IFERROR(J44-F44,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L44" s="91" t="n">
+        <f aca="false">IFERROR(K44/F44,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M44" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K44/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N44" s="21"/>
+      <c r="O44" s="93" t="n">
+        <f aca="false">IFERROR(K44*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P44" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K44,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C45" s="24" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E45" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F45" s="28" t="n">
+        <v>5899223</v>
+      </c>
+      <c r="G45" s="91" t="n">
+        <v>-0.121</v>
+      </c>
+      <c r="H45" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I45" s="91" t="n">
+        <f aca="false">IFERROR(IF(H45="هابطة",G45*$H$7,INDEX($H$7:$H$10,MATCH(H45,$G$7:$G$10,0))),"")</f>
+        <v>-0</v>
+      </c>
+      <c r="J45" s="28" t="n">
+        <f aca="false">IFERROR(F45*(1+I45),"")</f>
+        <v>5899223</v>
+      </c>
+      <c r="K45" s="92" t="n">
+        <f aca="false">IFERROR(J45-F45,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L45" s="91" t="n">
+        <f aca="false">IFERROR(K45/F45,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M45" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K45/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N45" s="73" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="O45" s="93" t="n">
+        <f aca="false">IFERROR(K45*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P45" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K45,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="B46" s="21" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C46" s="24" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D46" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F46" s="28" t="n">
+        <v>5722940</v>
+      </c>
+      <c r="G46" s="91" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="H46" s="18" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I46" s="91" t="n">
+        <f aca="false">IFERROR(IF(H46="هابطة",G46*$H$7,INDEX($H$7:$H$10,MATCH(H46,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="28" t="n">
+        <f aca="false">IFERROR(F46*(1+I46),"")</f>
+        <v>5722940</v>
+      </c>
+      <c r="K46" s="92" t="n">
+        <f aca="false">IFERROR(J46-F46,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L46" s="91" t="n">
+        <f aca="false">IFERROR(K46/F46,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M46" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K46/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N46" s="73" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="O46" s="93" t="n">
+        <f aca="false">IFERROR(K46*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P46" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K46,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C47" s="24" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E47" s="21" t="s">
+        <v>866</v>
+      </c>
+      <c r="F47" s="28" t="n">
+        <v>5647921</v>
+      </c>
+      <c r="G47" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H47" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I47" s="91" t="n">
+        <f aca="false">IFERROR(IF(H47="هابطة",G47*$H$7,INDEX($H$7:$H$10,MATCH(H47,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="28" t="n">
+        <f aca="false">IFERROR(F47*(1+I47),"")</f>
+        <v>5647921</v>
+      </c>
+      <c r="K47" s="92" t="n">
+        <f aca="false">IFERROR(J47-F47,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L47" s="91" t="n">
+        <f aca="false">IFERROR(K47/F47,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M47" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K47/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N47" s="73" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="O47" s="93" t="n">
+        <f aca="false">IFERROR(K47*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P47" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K47,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C48" s="24" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D48" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>862</v>
+      </c>
+      <c r="F48" s="28" t="n">
+        <v>5545862</v>
+      </c>
+      <c r="G48" s="91" t="n">
+        <v>-0.126</v>
+      </c>
+      <c r="H48" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I48" s="91" t="n">
+        <f aca="false">IFERROR(IF(H48="هابطة",G48*$H$7,INDEX($H$7:$H$10,MATCH(H48,$G$7:$G$10,0))),"")</f>
+        <v>-0</v>
+      </c>
+      <c r="J48" s="28" t="n">
+        <f aca="false">IFERROR(F48*(1+I48),"")</f>
+        <v>5545862</v>
+      </c>
+      <c r="K48" s="92" t="n">
+        <f aca="false">IFERROR(J48-F48,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L48" s="91" t="n">
+        <f aca="false">IFERROR(K48/F48,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M48" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K48/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N48" s="73" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O48" s="93" t="n">
+        <f aca="false">IFERROR(K48*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P48" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K48,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C49" s="24" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E49" s="21" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F49" s="28" t="n">
+        <v>5284855</v>
+      </c>
+      <c r="G49" s="91" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="H49" s="18" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I49" s="91" t="n">
+        <f aca="false">IFERROR(IF(H49="هابطة",G49*$H$7,INDEX($H$7:$H$10,MATCH(H49,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="28" t="n">
+        <f aca="false">IFERROR(F49*(1+I49),"")</f>
+        <v>5284855</v>
+      </c>
+      <c r="K49" s="92" t="n">
+        <f aca="false">IFERROR(J49-F49,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L49" s="91" t="n">
+        <f aca="false">IFERROR(K49/F49,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M49" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K49/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N49" s="73" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="O49" s="93" t="n">
+        <f aca="false">IFERROR(K49*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P49" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K49,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C50" s="24" t="s">
+        <v>962</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E50" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F50" s="28" t="n">
+        <v>5197774</v>
+      </c>
+      <c r="G50" s="91" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="H50" s="18" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I50" s="91" t="n">
+        <f aca="false">IFERROR(IF(H50="هابطة",G50*$H$7,INDEX($H$7:$H$10,MATCH(H50,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="28" t="n">
+        <f aca="false">IFERROR(F50*(1+I50),"")</f>
+        <v>5197774</v>
+      </c>
+      <c r="K50" s="92" t="n">
+        <f aca="false">IFERROR(J50-F50,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L50" s="91" t="n">
+        <f aca="false">IFERROR(K50/F50,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M50" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K50/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N50" s="73" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="O50" s="93" t="n">
+        <f aca="false">IFERROR(K50*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P50" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K50,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>963</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E51" s="21" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F51" s="28" t="n">
+        <v>4362115</v>
+      </c>
+      <c r="G51" s="91" t="n">
+        <v>-0.009</v>
+      </c>
+      <c r="H51" s="19" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I51" s="91" t="n">
+        <f aca="false">IFERROR(IF(H51="هابطة",G51*$H$7,INDEX($H$7:$H$10,MATCH(H51,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="28" t="n">
+        <f aca="false">IFERROR(F51*(1+I51),"")</f>
+        <v>4362115</v>
+      </c>
+      <c r="K51" s="92" t="n">
+        <f aca="false">IFERROR(J51-F51,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L51" s="91" t="n">
+        <f aca="false">IFERROR(K51/F51,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M51" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K51/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N51" s="73" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="O51" s="93" t="n">
+        <f aca="false">IFERROR(K51*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P51" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K51,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D52" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="E52" s="21" t="s">
+        <v>866</v>
+      </c>
+      <c r="F52" s="28" t="n">
+        <v>4341977</v>
+      </c>
+      <c r="G52" s="91" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="H52" s="18" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I52" s="91" t="n">
+        <f aca="false">IFERROR(IF(H52="هابطة",G52*$H$7,INDEX($H$7:$H$10,MATCH(H52,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="28" t="n">
+        <f aca="false">IFERROR(F52*(1+I52),"")</f>
+        <v>4341977</v>
+      </c>
+      <c r="K52" s="92" t="n">
+        <f aca="false">IFERROR(J52-F52,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L52" s="91" t="n">
+        <f aca="false">IFERROR(K52/F52,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M52" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K52/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N52" s="73" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="O52" s="93" t="n">
+        <f aca="false">IFERROR(K52*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P52" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K52,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E53" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F53" s="28" t="n">
+        <v>4191108</v>
+      </c>
+      <c r="G53" s="91" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="H53" s="19" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I53" s="91" t="n">
+        <f aca="false">IFERROR(IF(H53="هابطة",G53*$H$7,INDEX($H$7:$H$10,MATCH(H53,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="28" t="n">
+        <f aca="false">IFERROR(F53*(1+I53),"")</f>
+        <v>4191108</v>
+      </c>
+      <c r="K53" s="92" t="n">
+        <f aca="false">IFERROR(J53-F53,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L53" s="91" t="n">
+        <f aca="false">IFERROR(K53/F53,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M53" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K53/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N53" s="73" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O53" s="93" t="n">
+        <f aca="false">IFERROR(K53*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P53" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K53,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="21" t="n">
+        <v>43</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C54" s="24" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E54" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F54" s="28" t="n">
+        <v>4156161</v>
+      </c>
+      <c r="G54" s="91" t="n">
+        <v>-0.123</v>
+      </c>
+      <c r="H54" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I54" s="91" t="n">
+        <f aca="false">IFERROR(IF(H54="هابطة",G54*$H$7,INDEX($H$7:$H$10,MATCH(H54,$G$7:$G$10,0))),"")</f>
+        <v>-0</v>
+      </c>
+      <c r="J54" s="28" t="n">
+        <f aca="false">IFERROR(F54*(1+I54),"")</f>
+        <v>4156161</v>
+      </c>
+      <c r="K54" s="92" t="n">
+        <f aca="false">IFERROR(J54-F54,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L54" s="91" t="n">
+        <f aca="false">IFERROR(K54/F54,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M54" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K54/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N54" s="73" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="O54" s="93" t="n">
+        <f aca="false">IFERROR(K54*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P54" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K54,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C55" s="24" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D55" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E55" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F55" s="28" t="n">
+        <v>3857645</v>
+      </c>
+      <c r="G55" s="91" t="n">
+        <v>-0.249</v>
+      </c>
+      <c r="H55" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I55" s="91" t="n">
+        <f aca="false">IFERROR(IF(H55="هابطة",G55*$H$7,INDEX($H$7:$H$10,MATCH(H55,$G$7:$G$10,0))),"")</f>
+        <v>-0</v>
+      </c>
+      <c r="J55" s="28" t="n">
+        <f aca="false">IFERROR(F55*(1+I55),"")</f>
+        <v>3857645</v>
+      </c>
+      <c r="K55" s="92" t="n">
+        <f aca="false">IFERROR(J55-F55,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L55" s="91" t="n">
+        <f aca="false">IFERROR(K55/F55,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M55" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K55/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N55" s="73" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="O55" s="93" t="n">
+        <f aca="false">IFERROR(K55*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P55" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K55,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>948</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E56" s="21" t="s">
+        <v>862</v>
+      </c>
+      <c r="F56" s="28" t="n">
+        <v>3791200</v>
+      </c>
+      <c r="G56" s="91" t="n">
+        <v>-0.084</v>
+      </c>
+      <c r="H56" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I56" s="91" t="n">
+        <f aca="false">IFERROR(IF(H56="هابطة",G56*$H$7,INDEX($H$7:$H$10,MATCH(H56,$G$7:$G$10,0))),"")</f>
+        <v>-0</v>
+      </c>
+      <c r="J56" s="28" t="n">
+        <f aca="false">IFERROR(F56*(1+I56),"")</f>
+        <v>3791200</v>
+      </c>
+      <c r="K56" s="92" t="n">
+        <f aca="false">IFERROR(J56-F56,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L56" s="91" t="n">
+        <f aca="false">IFERROR(K56/F56,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M56" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K56/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N56" s="73" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="O56" s="93" t="n">
+        <f aca="false">IFERROR(K56*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P56" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K56,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C57" s="24" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D57" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E57" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F57" s="28" t="n">
+        <v>3708152</v>
+      </c>
+      <c r="G57" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H57" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I57" s="91" t="n">
+        <f aca="false">IFERROR(IF(H57="هابطة",G57*$H$7,INDEX($H$7:$H$10,MATCH(H57,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J57" s="28" t="n">
+        <f aca="false">IFERROR(F57*(1+I57),"")</f>
+        <v>3708152</v>
+      </c>
+      <c r="K57" s="92" t="n">
+        <f aca="false">IFERROR(J57-F57,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L57" s="91" t="n">
+        <f aca="false">IFERROR(K57/F57,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M57" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K57/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N57" s="21"/>
+      <c r="O57" s="93" t="n">
+        <f aca="false">IFERROR(K57*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P57" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K57,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C58" s="24" t="s">
+        <v>959</v>
+      </c>
+      <c r="D58" s="21" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>866</v>
+      </c>
+      <c r="F58" s="28" t="n">
+        <v>3599745</v>
+      </c>
+      <c r="G58" s="91" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="H58" s="19" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I58" s="91" t="n">
+        <f aca="false">IFERROR(IF(H58="هابطة",G58*$H$7,INDEX($H$7:$H$10,MATCH(H58,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J58" s="28" t="n">
+        <f aca="false">IFERROR(F58*(1+I58),"")</f>
+        <v>3599745</v>
+      </c>
+      <c r="K58" s="92" t="n">
+        <f aca="false">IFERROR(J58-F58,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L58" s="91" t="n">
+        <f aca="false">IFERROR(K58/F58,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M58" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K58/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="73" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="O58" s="93" t="n">
+        <f aca="false">IFERROR(K58*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P58" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K58,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C59" s="24" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="E59" s="21" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F59" s="28" t="n">
+        <v>3433425</v>
+      </c>
+      <c r="G59" s="91" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="H59" s="18" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I59" s="91" t="n">
+        <f aca="false">IFERROR(IF(H59="هابطة",G59*$H$7,INDEX($H$7:$H$10,MATCH(H59,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J59" s="28" t="n">
+        <f aca="false">IFERROR(F59*(1+I59),"")</f>
+        <v>3433425</v>
+      </c>
+      <c r="K59" s="92" t="n">
+        <f aca="false">IFERROR(J59-F59,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L59" s="91" t="n">
+        <f aca="false">IFERROR(K59/F59,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M59" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K59/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N59" s="73" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="O59" s="93" t="n">
+        <f aca="false">IFERROR(K59*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P59" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K59,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="21" t="n">
+        <v>49</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C60" s="24" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F60" s="28" t="n">
+        <v>3315559</v>
+      </c>
+      <c r="G60" s="91" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="H60" s="18" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I60" s="91" t="n">
+        <f aca="false">IFERROR(IF(H60="هابطة",G60*$H$7,INDEX($H$7:$H$10,MATCH(H60,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J60" s="28" t="n">
+        <f aca="false">IFERROR(F60*(1+I60),"")</f>
+        <v>3315559</v>
+      </c>
+      <c r="K60" s="92" t="n">
+        <f aca="false">IFERROR(J60-F60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L60" s="91" t="n">
+        <f aca="false">IFERROR(K60/F60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K60/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N60" s="73" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="O60" s="93" t="n">
+        <f aca="false">IFERROR(K60*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P60" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K60,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="B61" s="21" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C61" s="24" t="s">
+        <v>969</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>866</v>
+      </c>
+      <c r="F61" s="28" t="n">
+        <v>2663618</v>
+      </c>
+      <c r="G61" s="91" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="H61" s="19" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I61" s="91" t="n">
+        <f aca="false">IFERROR(IF(H61="هابطة",G61*$H$7,INDEX($H$7:$H$10,MATCH(H61,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J61" s="28" t="n">
+        <f aca="false">IFERROR(F61*(1+I61),"")</f>
+        <v>2663618</v>
+      </c>
+      <c r="K61" s="92" t="n">
+        <f aca="false">IFERROR(J61-F61,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L61" s="91" t="n">
+        <f aca="false">IFERROR(K61/F61,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M61" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K61/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N61" s="73" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="O61" s="93" t="n">
+        <f aca="false">IFERROR(K61*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P61" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K61,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="21" t="n">
+        <v>51</v>
+      </c>
+      <c r="B62" s="21" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C62" s="24" t="s">
+        <v>967</v>
+      </c>
+      <c r="D62" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="E62" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F62" s="28" t="n">
+        <v>2286567</v>
+      </c>
+      <c r="G62" s="91" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="H62" s="19" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I62" s="91" t="n">
+        <f aca="false">IFERROR(IF(H62="هابطة",G62*$H$7,INDEX($H$7:$H$10,MATCH(H62,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J62" s="28" t="n">
+        <f aca="false">IFERROR(F62*(1+I62),"")</f>
+        <v>2286567</v>
+      </c>
+      <c r="K62" s="92" t="n">
+        <f aca="false">IFERROR(J62-F62,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L62" s="91" t="n">
+        <f aca="false">IFERROR(K62/F62,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M62" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K62/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N62" s="73" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="O62" s="93" t="n">
+        <f aca="false">IFERROR(K62*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P62" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K62,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="21" t="n">
+        <v>52</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C63" s="24" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E63" s="21" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F63" s="28" t="n">
+        <v>2086987</v>
+      </c>
+      <c r="G63" s="91" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="H63" s="18" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I63" s="91" t="n">
+        <f aca="false">IFERROR(IF(H63="هابطة",G63*$H$7,INDEX($H$7:$H$10,MATCH(H63,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J63" s="28" t="n">
+        <f aca="false">IFERROR(F63*(1+I63),"")</f>
+        <v>2086987</v>
+      </c>
+      <c r="K63" s="92" t="n">
+        <f aca="false">IFERROR(J63-F63,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L63" s="91" t="n">
+        <f aca="false">IFERROR(K63/F63,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M63" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K63/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N63" s="73" t="n">
+        <v>28</v>
+      </c>
+      <c r="O63" s="93" t="n">
+        <f aca="false">IFERROR(K63*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P63" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K63,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="B64" s="21" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C64" s="24" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D64" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E64" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="F64" s="28" t="n">
+        <v>1960098</v>
+      </c>
+      <c r="G64" s="91" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H64" s="18" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I64" s="91" t="n">
+        <f aca="false">IFERROR(IF(H64="هابطة",G64*$H$7,INDEX($H$7:$H$10,MATCH(H64,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J64" s="28" t="n">
+        <f aca="false">IFERROR(F64*(1+I64),"")</f>
+        <v>1960098</v>
+      </c>
+      <c r="K64" s="92" t="n">
+        <f aca="false">IFERROR(J64-F64,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L64" s="91" t="n">
+        <f aca="false">IFERROR(K64/F64,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M64" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K64/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N64" s="73" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="O64" s="93" t="n">
+        <f aca="false">IFERROR(K64*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P64" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K64,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="B65" s="21" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C65" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="E65" s="21" t="s">
+        <v>866</v>
+      </c>
+      <c r="F65" s="28" t="n">
+        <v>1451309</v>
+      </c>
+      <c r="G65" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H65" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I65" s="91" t="n">
+        <f aca="false">IFERROR(IF(H65="هابطة",G65*$H$7,INDEX($H$7:$H$10,MATCH(H65,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J65" s="28" t="n">
+        <f aca="false">IFERROR(F65*(1+I65),"")</f>
+        <v>1451309</v>
+      </c>
+      <c r="K65" s="92" t="n">
+        <f aca="false">IFERROR(J65-F65,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L65" s="91" t="n">
+        <f aca="false">IFERROR(K65/F65,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M65" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K65/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N65" s="21"/>
+      <c r="O65" s="93" t="n">
+        <f aca="false">IFERROR(K65*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P65" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K65,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="B66" s="21" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C66" s="24" t="s">
+        <v>974</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E66" s="21" t="s">
+        <v>866</v>
+      </c>
+      <c r="F66" s="28" t="n">
+        <v>1099275</v>
+      </c>
+      <c r="G66" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H66" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I66" s="91" t="n">
+        <f aca="false">IFERROR(IF(H66="هابطة",G66*$H$7,INDEX($H$7:$H$10,MATCH(H66,$G$7:$G$10,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J66" s="28" t="n">
+        <f aca="false">IFERROR(F66*(1+I66),"")</f>
+        <v>1099275</v>
+      </c>
+      <c r="K66" s="92" t="n">
+        <f aca="false">IFERROR(J66-F66,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L66" s="91" t="n">
+        <f aca="false">IFERROR(K66/F66,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M66" s="92" t="n">
+        <f aca="false">IFERROR(ROUNDUP(K66/$D$7,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N66" s="73" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="O66" s="93" t="n">
+        <f aca="false">IFERROR(K66*$D$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P66" s="21" t="n">
+        <f aca="false">IFERROR(RANK(K66,$K$12:$K$66),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="32"/>
+      <c r="B67" s="32"/>
+      <c r="C67" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="D67" s="32"/>
+      <c r="E67" s="32"/>
+      <c r="F67" s="34" t="n">
+        <f aca="false">SUM(F12:F66)</f>
+        <v>478886741</v>
+      </c>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="32"/>
+      <c r="J67" s="34" t="n">
+        <f aca="false">SUM(J12:J66)</f>
+        <v>478886741</v>
+      </c>
+      <c r="K67" s="95" t="n">
+        <f aca="false">SUM(K12:K66)</f>
+        <v>0</v>
+      </c>
+      <c r="L67" s="96" t="n">
+        <f aca="false">IFERROR(K67/F67,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M67" s="95" t="n">
+        <f aca="false">SUM(M12:M66)</f>
+        <v>0</v>
+      </c>
+      <c r="N67" s="32"/>
+      <c r="O67" s="95" t="n">
+        <f aca="false">SUM(O12:O66)</f>
+        <v>0</v>
+      </c>
+      <c r="P67" s="32"/>
+    </row>
+    <row r="69" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B69" s="52" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C69" s="53" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D69" s="53"/>
+      <c r="E69" s="53"/>
+      <c r="F69" s="53"/>
+      <c r="G69" s="53"/>
+      <c r="H69" s="53"/>
+      <c r="I69" s="53"/>
+      <c r="J69" s="53"/>
+      <c r="K69" s="53"/>
+      <c r="L69" s="53"/>
+      <c r="M69" s="53"/>
+      <c r="N69" s="53"/>
+      <c r="O69" s="53"/>
+      <c r="P69" s="53"/>
+    </row>
+    <row r="70" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B70" s="52" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C70" s="53" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D70" s="53"/>
+      <c r="E70" s="53"/>
+      <c r="F70" s="53"/>
+      <c r="G70" s="53"/>
+      <c r="H70" s="53"/>
+      <c r="I70" s="53"/>
+      <c r="J70" s="53"/>
+      <c r="K70" s="53"/>
+      <c r="L70" s="53"/>
+      <c r="M70" s="53"/>
+      <c r="N70" s="53"/>
+      <c r="O70" s="53"/>
+      <c r="P70" s="53"/>
+    </row>
+    <row r="71" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B71" s="54" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C71" s="53" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D71" s="53"/>
+      <c r="E71" s="53"/>
+      <c r="F71" s="53"/>
+      <c r="G71" s="53"/>
+      <c r="H71" s="53"/>
+      <c r="I71" s="53"/>
+      <c r="J71" s="53"/>
+      <c r="K71" s="53"/>
+      <c r="L71" s="53"/>
+      <c r="M71" s="53"/>
+      <c r="N71" s="53"/>
+      <c r="O71" s="53"/>
+      <c r="P71" s="53"/>
+    </row>
+    <row r="72" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B72" s="54" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C72" s="53" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D72" s="53"/>
+      <c r="E72" s="53"/>
+      <c r="F72" s="53"/>
+      <c r="G72" s="53"/>
+      <c r="H72" s="53"/>
+      <c r="I72" s="53"/>
+      <c r="J72" s="53"/>
+      <c r="K72" s="53"/>
+      <c r="L72" s="53"/>
+      <c r="M72" s="53"/>
+      <c r="N72" s="53"/>
+      <c r="O72" s="53"/>
+      <c r="P72" s="53"/>
+    </row>
+    <row r="73" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B73" s="52" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C73" s="53" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D73" s="53"/>
+      <c r="E73" s="53"/>
+      <c r="F73" s="53"/>
+      <c r="G73" s="53"/>
+      <c r="H73" s="53"/>
+      <c r="I73" s="53"/>
+      <c r="J73" s="53"/>
+      <c r="K73" s="53"/>
+      <c r="L73" s="53"/>
+      <c r="M73" s="53"/>
+      <c r="N73" s="53"/>
+      <c r="O73" s="53"/>
+      <c r="P73" s="53"/>
+    </row>
+    <row r="74" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B74" s="54" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C74" s="53" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D74" s="53"/>
+      <c r="E74" s="53"/>
+      <c r="F74" s="53"/>
+      <c r="G74" s="53"/>
+      <c r="H74" s="53"/>
+      <c r="I74" s="53"/>
+      <c r="J74" s="53"/>
+      <c r="K74" s="53"/>
+      <c r="L74" s="53"/>
+      <c r="M74" s="53"/>
+      <c r="N74" s="53"/>
+      <c r="O74" s="53"/>
+      <c r="P74" s="53"/>
+    </row>
+    <row r="75" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B75" s="54" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C75" s="53" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D75" s="53"/>
+      <c r="E75" s="53"/>
+      <c r="F75" s="53"/>
+      <c r="G75" s="53"/>
+      <c r="H75" s="53"/>
+      <c r="I75" s="53"/>
+      <c r="J75" s="53"/>
+      <c r="K75" s="53"/>
+      <c r="L75" s="53"/>
+      <c r="M75" s="53"/>
+      <c r="N75" s="53"/>
+      <c r="O75" s="53"/>
+      <c r="P75" s="53"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="C3:P3"/>
+    <mergeCell ref="C69:P69"/>
+    <mergeCell ref="C70:P70"/>
+    <mergeCell ref="C71:P71"/>
+    <mergeCell ref="C72:P72"/>
+    <mergeCell ref="C73:P73"/>
+    <mergeCell ref="C74:P74"/>
+    <mergeCell ref="C75:P75"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:O18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -10072,7 +13778,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>992</v>
+        <v>1138</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10091,7 +13797,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>993</v>
+        <v>1139</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10122,86 +13828,86 @@
         <v>55</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>994</v>
+        <v>1140</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>995</v>
+        <v>1141</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>996</v>
+        <v>1142</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>997</v>
+        <v>1143</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>58</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>998</v>
+        <v>1144</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>999</v>
+        <v>1145</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>59</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>1000</v>
+        <v>1146</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>1001</v>
+        <v>1147</v>
       </c>
       <c r="O3" s="15" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="89" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B4" s="90" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C4" s="89" t="s">
+      <c r="A4" s="97" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B4" s="98" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C4" s="97" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="90" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E4" s="89" t="n">
+      <c r="D4" s="98" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E4" s="97" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="89" t="s">
-        <v>1005</v>
-      </c>
-      <c r="G4" s="90" t="s">
-        <v>1006</v>
-      </c>
-      <c r="H4" s="89" t="n">
+      <c r="F4" s="97" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G4" s="98" t="s">
+        <v>1152</v>
+      </c>
+      <c r="H4" s="97" t="n">
         <v>20</v>
       </c>
-      <c r="I4" s="89" t="n">
+      <c r="I4" s="97" t="n">
         <f aca="false">IF(H4="","",H4-E4)</f>
         <v>14</v>
       </c>
-      <c r="J4" s="91" t="n">
+      <c r="J4" s="99" t="n">
         <f aca="false">IFERROR(IF(H4="","",(H4-E4)/E4),"")</f>
         <v>2.33333333333333</v>
       </c>
-      <c r="K4" s="90" t="s">
-        <v>1007</v>
-      </c>
-      <c r="L4" s="89" t="s">
+      <c r="K4" s="98" t="s">
+        <v>1153</v>
+      </c>
+      <c r="L4" s="97" t="s">
         <v>78</v>
       </c>
-      <c r="M4" s="90" t="s">
-        <v>1008</v>
-      </c>
-      <c r="N4" s="90" t="s">
-        <v>1009</v>
-      </c>
-      <c r="O4" s="89" t="s">
-        <v>1010</v>
+      <c r="M4" s="98" t="s">
+        <v>1154</v>
+      </c>
+      <c r="N4" s="98" t="s">
+        <v>1155</v>
+      </c>
+      <c r="O4" s="97" t="s">
+        <v>1156</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10217,17 +13923,17 @@
       <c r="D5" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="92" t="n">
+      <c r="E5" s="100" t="n">
         <v>1271</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>1011</v>
+        <v>1157</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>1012</v>
-      </c>
-      <c r="H5" s="93"/>
-      <c r="I5" s="92" t="str">
+        <v>1158</v>
+      </c>
+      <c r="H5" s="101"/>
+      <c r="I5" s="100" t="str">
         <f aca="false">IF(H5="","",H5-E5)</f>
         <v/>
       </c>
@@ -10235,15 +13941,15 @@
         <f aca="false">IFERROR(IF(H5="","",(H5-E5)/E5),"")</f>
         <v/>
       </c>
-      <c r="K5" s="94"/>
+      <c r="K5" s="102"/>
       <c r="L5" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M5" s="94"/>
+      <c r="M5" s="102"/>
       <c r="N5" s="16" t="s">
-        <v>1013</v>
-      </c>
-      <c r="O5" s="95"/>
+        <v>1159</v>
+      </c>
+      <c r="O5" s="103"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="n">
@@ -10258,17 +13964,17 @@
       <c r="D6" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="92" t="n">
+      <c r="E6" s="100" t="n">
         <v>25</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>1014</v>
+        <v>1160</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>1015</v>
-      </c>
-      <c r="H6" s="93"/>
-      <c r="I6" s="92" t="str">
+        <v>1161</v>
+      </c>
+      <c r="H6" s="101"/>
+      <c r="I6" s="100" t="str">
         <f aca="false">IF(H6="","",H6-E6)</f>
         <v/>
       </c>
@@ -10276,15 +13982,15 @@
         <f aca="false">IFERROR(IF(H6="","",(H6-E6)/E6),"")</f>
         <v/>
       </c>
-      <c r="K6" s="94"/>
+      <c r="K6" s="102"/>
       <c r="L6" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M6" s="94"/>
+      <c r="M6" s="102"/>
       <c r="N6" s="16" t="s">
-        <v>1016</v>
-      </c>
-      <c r="O6" s="95"/>
+        <v>1162</v>
+      </c>
+      <c r="O6" s="103"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="n">
@@ -10299,17 +14005,17 @@
       <c r="D7" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="92" t="n">
+      <c r="E7" s="100" t="n">
         <v>39</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>1017</v>
+        <v>1163</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>1006</v>
-      </c>
-      <c r="H7" s="93"/>
-      <c r="I7" s="92" t="str">
+        <v>1152</v>
+      </c>
+      <c r="H7" s="101"/>
+      <c r="I7" s="100" t="str">
         <f aca="false">IF(H7="","",H7-E7)</f>
         <v/>
       </c>
@@ -10317,15 +14023,15 @@
         <f aca="false">IFERROR(IF(H7="","",(H7-E7)/E7),"")</f>
         <v/>
       </c>
-      <c r="K7" s="94"/>
+      <c r="K7" s="102"/>
       <c r="L7" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M7" s="94"/>
+      <c r="M7" s="102"/>
       <c r="N7" s="16" t="s">
-        <v>1018</v>
-      </c>
-      <c r="O7" s="95"/>
+        <v>1164</v>
+      </c>
+      <c r="O7" s="103"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="n">
@@ -10340,17 +14046,17 @@
       <c r="D8" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="92" t="n">
+      <c r="E8" s="100" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>1019</v>
+        <v>1165</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>1020</v>
-      </c>
-      <c r="H8" s="93"/>
-      <c r="I8" s="92" t="str">
+        <v>1166</v>
+      </c>
+      <c r="H8" s="101"/>
+      <c r="I8" s="100" t="str">
         <f aca="false">IF(H8="","",H8-E8)</f>
         <v/>
       </c>
@@ -10358,40 +14064,40 @@
         <f aca="false">IFERROR(IF(H8="","",(H8-E8)/E8),"")</f>
         <v/>
       </c>
-      <c r="K8" s="94"/>
+      <c r="K8" s="102"/>
       <c r="L8" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="94"/>
+      <c r="M8" s="102"/>
       <c r="N8" s="16" t="s">
-        <v>1021</v>
-      </c>
-      <c r="O8" s="95"/>
+        <v>1167</v>
+      </c>
+      <c r="O8" s="103"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1022</v>
+        <v>1168</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>53</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>1023</v>
-      </c>
-      <c r="E9" s="92" t="n">
+        <v>1169</v>
+      </c>
+      <c r="E9" s="100" t="n">
         <v>0.28</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>1024</v>
+        <v>1170</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>1025</v>
-      </c>
-      <c r="H9" s="93"/>
-      <c r="I9" s="92" t="str">
+        <v>1171</v>
+      </c>
+      <c r="H9" s="101"/>
+      <c r="I9" s="100" t="str">
         <f aca="false">IF(H9="","",H9-E9)</f>
         <v/>
       </c>
@@ -10399,22 +14105,22 @@
         <f aca="false">IFERROR(IF(H9="","",(H9-E9)/E9),"")</f>
         <v/>
       </c>
-      <c r="K9" s="94"/>
+      <c r="K9" s="102"/>
       <c r="L9" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="M9" s="94"/>
+      <c r="M9" s="102"/>
       <c r="N9" s="16" t="s">
-        <v>1026</v>
-      </c>
-      <c r="O9" s="95"/>
+        <v>1172</v>
+      </c>
+      <c r="O9" s="103"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1027</v>
+        <v>1173</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>53</v>
@@ -10422,17 +14128,17 @@
       <c r="D10" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="E10" s="92" t="n">
+      <c r="E10" s="100" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>1028</v>
+        <v>1174</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>1029</v>
-      </c>
-      <c r="H10" s="93"/>
-      <c r="I10" s="92" t="str">
+        <v>1175</v>
+      </c>
+      <c r="H10" s="101"/>
+      <c r="I10" s="100" t="str">
         <f aca="false">IF(H10="","",H10-E10)</f>
         <v/>
       </c>
@@ -10440,15 +14146,15 @@
         <f aca="false">IFERROR(IF(H10="","",(H10-E10)/E10),"")</f>
         <v/>
       </c>
-      <c r="K10" s="94"/>
+      <c r="K10" s="102"/>
       <c r="L10" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M10" s="94"/>
+      <c r="M10" s="102"/>
       <c r="N10" s="16" t="s">
-        <v>1030</v>
-      </c>
-      <c r="O10" s="95"/>
+        <v>1176</v>
+      </c>
+      <c r="O10" s="103"/>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="n">
@@ -10461,19 +14167,19 @@
         <v>95</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>1031</v>
-      </c>
-      <c r="E11" s="92" t="n">
+        <v>1177</v>
+      </c>
+      <c r="E11" s="100" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>1032</v>
+        <v>1178</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>1033</v>
-      </c>
-      <c r="H11" s="93"/>
-      <c r="I11" s="92" t="str">
+        <v>1179</v>
+      </c>
+      <c r="H11" s="101"/>
+      <c r="I11" s="100" t="str">
         <f aca="false">IF(H11="","",H11-E11)</f>
         <v/>
       </c>
@@ -10481,15 +14187,15 @@
         <f aca="false">IFERROR(IF(H11="","",(H11-E11)/E11),"")</f>
         <v/>
       </c>
-      <c r="K11" s="94"/>
+      <c r="K11" s="102"/>
       <c r="L11" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="M11" s="94"/>
+      <c r="M11" s="102"/>
       <c r="N11" s="16" t="s">
-        <v>1034</v>
-      </c>
-      <c r="O11" s="95"/>
+        <v>1180</v>
+      </c>
+      <c r="O11" s="103"/>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="n">
@@ -10504,17 +14210,17 @@
       <c r="D12" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="92" t="n">
+      <c r="E12" s="100" t="n">
         <v>31</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>1035</v>
+        <v>1181</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>1036</v>
-      </c>
-      <c r="H12" s="93"/>
-      <c r="I12" s="92" t="str">
+        <v>1182</v>
+      </c>
+      <c r="H12" s="101"/>
+      <c r="I12" s="100" t="str">
         <f aca="false">IF(H12="","",H12-E12)</f>
         <v/>
       </c>
@@ -10522,15 +14228,15 @@
         <f aca="false">IFERROR(IF(H12="","",(H12-E12)/E12),"")</f>
         <v/>
       </c>
-      <c r="K12" s="94"/>
+      <c r="K12" s="102"/>
       <c r="L12" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M12" s="94"/>
+      <c r="M12" s="102"/>
       <c r="N12" s="16" t="s">
-        <v>1037</v>
-      </c>
-      <c r="O12" s="95"/>
+        <v>1183</v>
+      </c>
+      <c r="O12" s="103"/>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="n">
@@ -10545,17 +14251,17 @@
       <c r="D13" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="E13" s="92" t="n">
+      <c r="E13" s="100" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>1038</v>
+        <v>1184</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>1039</v>
-      </c>
-      <c r="H13" s="93"/>
-      <c r="I13" s="92" t="str">
+        <v>1185</v>
+      </c>
+      <c r="H13" s="101"/>
+      <c r="I13" s="100" t="str">
         <f aca="false">IF(H13="","",H13-E13)</f>
         <v/>
       </c>
@@ -10563,15 +14269,15 @@
         <f aca="false">IFERROR(IF(H13="","",(H13-E13)/E13),"")</f>
         <v/>
       </c>
-      <c r="K13" s="94"/>
+      <c r="K13" s="102"/>
       <c r="L13" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M13" s="94"/>
+      <c r="M13" s="102"/>
       <c r="N13" s="16" t="s">
-        <v>1040</v>
-      </c>
-      <c r="O13" s="95"/>
+        <v>1186</v>
+      </c>
+      <c r="O13" s="103"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="n">
@@ -10586,17 +14292,17 @@
       <c r="D14" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="E14" s="92" t="n">
+      <c r="E14" s="100" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>1041</v>
+        <v>1187</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>1042</v>
-      </c>
-      <c r="H14" s="93"/>
-      <c r="I14" s="92" t="str">
+        <v>1188</v>
+      </c>
+      <c r="H14" s="101"/>
+      <c r="I14" s="100" t="str">
         <f aca="false">IF(H14="","",H14-E14)</f>
         <v/>
       </c>
@@ -10604,15 +14310,15 @@
         <f aca="false">IFERROR(IF(H14="","",(H14-E14)/E14),"")</f>
         <v/>
       </c>
-      <c r="K14" s="94"/>
+      <c r="K14" s="102"/>
       <c r="L14" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="94"/>
+      <c r="M14" s="102"/>
       <c r="N14" s="16" t="s">
-        <v>1043</v>
-      </c>
-      <c r="O14" s="95"/>
+        <v>1189</v>
+      </c>
+      <c r="O14" s="103"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="n">
@@ -10625,19 +14331,19 @@
         <v>52</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E15" s="92" t="n">
+        <v>1150</v>
+      </c>
+      <c r="E15" s="100" t="n">
         <v>6</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>1032</v>
+        <v>1178</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>1044</v>
-      </c>
-      <c r="H15" s="93"/>
-      <c r="I15" s="92" t="str">
+        <v>1190</v>
+      </c>
+      <c r="H15" s="101"/>
+      <c r="I15" s="100" t="str">
         <f aca="false">IF(H15="","",H15-E15)</f>
         <v/>
       </c>
@@ -10645,15 +14351,15 @@
         <f aca="false">IFERROR(IF(H15="","",(H15-E15)/E15),"")</f>
         <v/>
       </c>
-      <c r="K15" s="94"/>
+      <c r="K15" s="102"/>
       <c r="L15" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M15" s="94"/>
+      <c r="M15" s="102"/>
       <c r="N15" s="16" t="s">
-        <v>1045</v>
-      </c>
-      <c r="O15" s="95"/>
+        <v>1191</v>
+      </c>
+      <c r="O15" s="103"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="n">
@@ -10666,19 +14372,19 @@
         <v>52</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>1046</v>
-      </c>
-      <c r="E16" s="92" t="n">
+        <v>1192</v>
+      </c>
+      <c r="E16" s="100" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>1047</v>
+        <v>1193</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>1048</v>
-      </c>
-      <c r="H16" s="93"/>
-      <c r="I16" s="92" t="str">
+        <v>1194</v>
+      </c>
+      <c r="H16" s="101"/>
+      <c r="I16" s="100" t="str">
         <f aca="false">IF(H16="","",H16-E16)</f>
         <v/>
       </c>
@@ -10686,31 +14392,31 @@
         <f aca="false">IFERROR(IF(H16="","",(H16-E16)/E16),"")</f>
         <v/>
       </c>
-      <c r="K16" s="94"/>
+      <c r="K16" s="102"/>
       <c r="L16" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M16" s="94"/>
+      <c r="M16" s="102"/>
       <c r="N16" s="16" t="s">
-        <v>1049</v>
-      </c>
-      <c r="O16" s="95"/>
+        <v>1195</v>
+      </c>
+      <c r="O16" s="103"/>
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
-        <v>1050</v>
-      </c>
-      <c r="C18" s="96" t="s">
-        <v>1051</v>
-      </c>
-      <c r="D18" s="96"/>
-      <c r="E18" s="96"/>
-      <c r="F18" s="96"/>
-      <c r="G18" s="96"/>
-      <c r="H18" s="96"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="96"/>
-      <c r="K18" s="96"/>
+        <v>1196</v>
+      </c>
+      <c r="C18" s="104" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D18" s="104"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="104"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="104"/>
+      <c r="I18" s="104"/>
+      <c r="J18" s="104"/>
+      <c r="K18" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -10728,7 +14434,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -10762,7 +14468,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1052</v>
+        <v>1198</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10783,52 +14489,52 @@
         <v>50</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>1001</v>
+        <v>1147</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>994</v>
+        <v>1140</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>1053</v>
+        <v>1199</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1054</v>
+        <v>1200</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1055</v>
+        <v>1201</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1056</v>
+        <v>1202</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>997</v>
+        <v>1143</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>1057</v>
+        <v>1203</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>1058</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="97" t="n">
+      <c r="A4" s="105" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="98" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D4" s="99" t="n">
+      <c r="C4" s="106" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D4" s="107" t="n">
         <f aca="false">'الخطة التنفيذية'!E5</f>
         <v>1271</v>
       </c>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="99" t="str">
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="107" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H5="","",'الخطة التنفيذية'!H5)</f>
         <v/>
       </c>
@@ -10842,24 +14548,24 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="97" t="n">
+      <c r="A5" s="105" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="98" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D5" s="99" t="n">
+      <c r="C5" s="106" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D5" s="107" t="n">
         <f aca="false">'الخطة التنفيذية'!E6</f>
         <v>25</v>
       </c>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="99" t="str">
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="101"/>
+      <c r="H5" s="101"/>
+      <c r="I5" s="107" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H6="","",'الخطة التنفيذية'!H6)</f>
         <v/>
       </c>
@@ -10873,24 +14579,24 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="97" t="n">
+      <c r="A6" s="105" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="98" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D6" s="99" t="n">
+      <c r="C6" s="106" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D6" s="107" t="n">
         <f aca="false">'الخطة التنفيذية'!E7</f>
         <v>39</v>
       </c>
-      <c r="E6" s="93"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="99" t="str">
+      <c r="E6" s="101"/>
+      <c r="F6" s="101"/>
+      <c r="G6" s="101"/>
+      <c r="H6" s="101"/>
+      <c r="I6" s="107" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H7="","",'الخطة التنفيذية'!H7)</f>
         <v/>
       </c>
@@ -10904,24 +14610,24 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="97" t="n">
+      <c r="A7" s="105" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="98" t="s">
-        <v>1021</v>
-      </c>
-      <c r="D7" s="99" t="n">
+      <c r="C7" s="106" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D7" s="107" t="n">
         <f aca="false">'الخطة التنفيذية'!E8</f>
         <v>0</v>
       </c>
-      <c r="E7" s="93"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="93"/>
-      <c r="H7" s="93"/>
-      <c r="I7" s="99" t="str">
+      <c r="E7" s="101"/>
+      <c r="F7" s="101"/>
+      <c r="G7" s="101"/>
+      <c r="H7" s="101"/>
+      <c r="I7" s="107" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H8="","",'الخطة التنفيذية'!H8)</f>
         <v/>
       </c>
@@ -10935,24 +14641,24 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="97" t="n">
+      <c r="A8" s="105" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C8" s="98" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D8" s="99" t="n">
+        <v>1168</v>
+      </c>
+      <c r="C8" s="106" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D8" s="107" t="n">
         <f aca="false">'الخطة التنفيذية'!E9</f>
         <v>0.28</v>
       </c>
-      <c r="E8" s="93"/>
-      <c r="F8" s="93"/>
-      <c r="G8" s="93"/>
-      <c r="H8" s="93"/>
-      <c r="I8" s="99" t="str">
+      <c r="E8" s="101"/>
+      <c r="F8" s="101"/>
+      <c r="G8" s="101"/>
+      <c r="H8" s="101"/>
+      <c r="I8" s="107" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H9="","",'الخطة التنفيذية'!H9)</f>
         <v/>
       </c>
@@ -10966,24 +14672,24 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="97" t="n">
+      <c r="A9" s="105" t="n">
         <v>6</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C9" s="98" t="s">
-        <v>1030</v>
-      </c>
-      <c r="D9" s="99" t="n">
+        <v>1173</v>
+      </c>
+      <c r="C9" s="106" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D9" s="107" t="n">
         <f aca="false">'الخطة التنفيذية'!E10</f>
         <v>0</v>
       </c>
-      <c r="E9" s="93"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="99" t="str">
+      <c r="E9" s="101"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="101"/>
+      <c r="H9" s="101"/>
+      <c r="I9" s="107" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H10="","",'الخطة التنفيذية'!H10)</f>
         <v/>
       </c>
@@ -10997,24 +14703,24 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="97" t="n">
+      <c r="A10" s="105" t="n">
         <v>7</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="98" t="s">
-        <v>1034</v>
-      </c>
-      <c r="D10" s="99" t="n">
+      <c r="C10" s="106" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D10" s="107" t="n">
         <f aca="false">'الخطة التنفيذية'!E11</f>
         <v>0</v>
       </c>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="93"/>
-      <c r="H10" s="93"/>
-      <c r="I10" s="99" t="str">
+      <c r="E10" s="101"/>
+      <c r="F10" s="101"/>
+      <c r="G10" s="101"/>
+      <c r="H10" s="101"/>
+      <c r="I10" s="107" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H11="","",'الخطة التنفيذية'!H11)</f>
         <v/>
       </c>
@@ -11028,24 +14734,24 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="97" t="n">
+      <c r="A11" s="105" t="n">
         <v>8</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="98" t="s">
-        <v>1037</v>
-      </c>
-      <c r="D11" s="99" t="n">
+      <c r="C11" s="106" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D11" s="107" t="n">
         <f aca="false">'الخطة التنفيذية'!E12</f>
         <v>31</v>
       </c>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="93"/>
-      <c r="I11" s="99" t="str">
+      <c r="E11" s="101"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="101"/>
+      <c r="I11" s="107" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H12="","",'الخطة التنفيذية'!H12)</f>
         <v/>
       </c>
@@ -11059,24 +14765,24 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="97" t="n">
+      <c r="A12" s="105" t="n">
         <v>9</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="C12" s="98" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D12" s="99" t="n">
+      <c r="C12" s="106" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D12" s="107" t="n">
         <f aca="false">'الخطة التنفيذية'!E13</f>
         <v>0</v>
       </c>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="99" t="str">
+      <c r="E12" s="101"/>
+      <c r="F12" s="101"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="101"/>
+      <c r="I12" s="107" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H13="","",'الخطة التنفيذية'!H13)</f>
         <v/>
       </c>
@@ -11090,24 +14796,24 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="97" t="n">
+      <c r="A13" s="105" t="n">
         <v>10</v>
       </c>
       <c r="B13" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="98" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D13" s="99" t="n">
+      <c r="C13" s="106" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D13" s="107" t="n">
         <f aca="false">'الخطة التنفيذية'!E14</f>
         <v>0</v>
       </c>
-      <c r="E13" s="93"/>
-      <c r="F13" s="93"/>
-      <c r="G13" s="93"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="99" t="str">
+      <c r="E13" s="101"/>
+      <c r="F13" s="101"/>
+      <c r="G13" s="101"/>
+      <c r="H13" s="101"/>
+      <c r="I13" s="107" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H14="","",'الخطة التنفيذية'!H14)</f>
         <v/>
       </c>
@@ -11121,24 +14827,24 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="97" t="n">
+      <c r="A14" s="105" t="n">
         <v>11</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="98" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D14" s="99" t="n">
+      <c r="C14" s="106" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D14" s="107" t="n">
         <f aca="false">'الخطة التنفيذية'!E15</f>
         <v>6</v>
       </c>
-      <c r="E14" s="93"/>
-      <c r="F14" s="93"/>
-      <c r="G14" s="93"/>
-      <c r="H14" s="93"/>
-      <c r="I14" s="99" t="str">
+      <c r="E14" s="101"/>
+      <c r="F14" s="101"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="101"/>
+      <c r="I14" s="107" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H15="","",'الخطة التنفيذية'!H15)</f>
         <v/>
       </c>
@@ -11152,24 +14858,24 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="97" t="n">
+      <c r="A15" s="105" t="n">
         <v>12</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="98" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D15" s="99" t="n">
+      <c r="C15" s="106" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D15" s="107" t="n">
         <f aca="false">'الخطة التنفيذية'!E16</f>
         <v>0</v>
       </c>
-      <c r="E15" s="93"/>
-      <c r="F15" s="93"/>
-      <c r="G15" s="93"/>
-      <c r="H15" s="93"/>
-      <c r="I15" s="99" t="str">
+      <c r="E15" s="101"/>
+      <c r="F15" s="101"/>
+      <c r="G15" s="101"/>
+      <c r="H15" s="101"/>
+      <c r="I15" s="107" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H16="","",'الخطة التنفيذية'!H16)</f>
         <v/>
       </c>
@@ -11197,7 +14903,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -11221,7 +14927,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1059</v>
+        <v>1205</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11239,7 +14945,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1060</v>
+        <v>1206</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11260,34 +14966,34 @@
         <v>49</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>1061</v>
+        <v>1207</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>50</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>1062</v>
+        <v>1208</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>59</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1000</v>
+        <v>1146</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1063</v>
+        <v>1209</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1064</v>
+        <v>1210</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>1065</v>
+        <v>1211</v>
       </c>
       <c r="J3" s="15" t="s">
         <v>60</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>1066</v>
+        <v>1212</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>679</v>
@@ -11296,561 +15002,561 @@
         <v>383</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>1067</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="89" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B4" s="90" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C4" s="89" t="s">
+      <c r="A4" s="97" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B4" s="98" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C4" s="97" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="89" t="s">
+      <c r="D4" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="89" t="s">
+      <c r="E4" s="97" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="89" t="s">
-        <v>1008</v>
-      </c>
-      <c r="G4" s="100" t="n">
+      <c r="F4" s="97" t="s">
+        <v>1154</v>
+      </c>
+      <c r="G4" s="108" t="n">
         <v>46235</v>
       </c>
-      <c r="H4" s="100" t="n">
+      <c r="H4" s="108" t="n">
         <v>46326</v>
       </c>
-      <c r="I4" s="89" t="n">
+      <c r="I4" s="97" t="n">
         <f aca="false">IF(OR(G4="",H4=""),"",H4-G4)</f>
         <v>91</v>
       </c>
-      <c r="J4" s="89" t="n">
+      <c r="J4" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="89" t="s">
-        <v>1069</v>
-      </c>
-      <c r="L4" s="90" t="s">
-        <v>1070</v>
-      </c>
-      <c r="M4" s="89" t="s">
-        <v>1010</v>
-      </c>
-      <c r="N4" s="101" t="n">
+      <c r="K4" s="97" t="s">
+        <v>1215</v>
+      </c>
+      <c r="L4" s="98" t="s">
+        <v>1216</v>
+      </c>
+      <c r="M4" s="97" t="s">
+        <v>1156</v>
+      </c>
+      <c r="N4" s="109" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="97" t="n">
+      <c r="A5" s="105" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="95"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="102"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="110"/>
       <c r="I5" s="21" t="str">
         <f aca="false">IF(OR(G5="",H5=""),"",H5-G5)</f>
         <v/>
       </c>
-      <c r="J5" s="95"/>
-      <c r="K5" s="95"/>
-      <c r="L5" s="94"/>
-      <c r="M5" s="95"/>
-      <c r="N5" s="103"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
+      <c r="L5" s="102"/>
+      <c r="M5" s="103"/>
+      <c r="N5" s="111"/>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="97" t="n">
+      <c r="A6" s="105" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="94"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="102"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="103"/>
+      <c r="G6" s="110"/>
+      <c r="H6" s="110"/>
       <c r="I6" s="21" t="str">
         <f aca="false">IF(OR(G6="",H6=""),"",H6-G6)</f>
         <v/>
       </c>
-      <c r="J6" s="95"/>
-      <c r="K6" s="95"/>
-      <c r="L6" s="94"/>
-      <c r="M6" s="95"/>
-      <c r="N6" s="103"/>
+      <c r="J6" s="103"/>
+      <c r="K6" s="103"/>
+      <c r="L6" s="102"/>
+      <c r="M6" s="103"/>
+      <c r="N6" s="111"/>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="97" t="n">
+      <c r="A7" s="105" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="94"/>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="102"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="110"/>
       <c r="I7" s="21" t="str">
         <f aca="false">IF(OR(G7="",H7=""),"",H7-G7)</f>
         <v/>
       </c>
-      <c r="J7" s="95"/>
-      <c r="K7" s="95"/>
-      <c r="L7" s="94"/>
-      <c r="M7" s="95"/>
-      <c r="N7" s="103"/>
+      <c r="J7" s="103"/>
+      <c r="K7" s="103"/>
+      <c r="L7" s="102"/>
+      <c r="M7" s="103"/>
+      <c r="N7" s="111"/>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="97" t="n">
+      <c r="A8" s="105" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="94"/>
-      <c r="C8" s="95"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="95"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="102"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
+      <c r="G8" s="110"/>
+      <c r="H8" s="110"/>
       <c r="I8" s="21" t="str">
         <f aca="false">IF(OR(G8="",H8=""),"",H8-G8)</f>
         <v/>
       </c>
-      <c r="J8" s="95"/>
-      <c r="K8" s="95"/>
-      <c r="L8" s="94"/>
-      <c r="M8" s="95"/>
-      <c r="N8" s="103"/>
+      <c r="J8" s="103"/>
+      <c r="K8" s="103"/>
+      <c r="L8" s="102"/>
+      <c r="M8" s="103"/>
+      <c r="N8" s="111"/>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="97" t="n">
+      <c r="A9" s="105" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="94"/>
-      <c r="C9" s="95"/>
-      <c r="D9" s="95"/>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="102"/>
-      <c r="H9" s="102"/>
+      <c r="B9" s="102"/>
+      <c r="C9" s="103"/>
+      <c r="D9" s="103"/>
+      <c r="E9" s="103"/>
+      <c r="F9" s="103"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="110"/>
       <c r="I9" s="21" t="str">
         <f aca="false">IF(OR(G9="",H9=""),"",H9-G9)</f>
         <v/>
       </c>
-      <c r="J9" s="95"/>
-      <c r="K9" s="95"/>
-      <c r="L9" s="94"/>
-      <c r="M9" s="95"/>
-      <c r="N9" s="103"/>
+      <c r="J9" s="103"/>
+      <c r="K9" s="103"/>
+      <c r="L9" s="102"/>
+      <c r="M9" s="103"/>
+      <c r="N9" s="111"/>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="97" t="n">
+      <c r="A10" s="105" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="94"/>
-      <c r="C10" s="95"/>
-      <c r="D10" s="95"/>
-      <c r="E10" s="95"/>
-      <c r="F10" s="95"/>
-      <c r="G10" s="102"/>
-      <c r="H10" s="102"/>
+      <c r="B10" s="102"/>
+      <c r="C10" s="103"/>
+      <c r="D10" s="103"/>
+      <c r="E10" s="103"/>
+      <c r="F10" s="103"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="110"/>
       <c r="I10" s="21" t="str">
         <f aca="false">IF(OR(G10="",H10=""),"",H10-G10)</f>
         <v/>
       </c>
-      <c r="J10" s="95"/>
-      <c r="K10" s="95"/>
-      <c r="L10" s="94"/>
-      <c r="M10" s="95"/>
-      <c r="N10" s="103"/>
+      <c r="J10" s="103"/>
+      <c r="K10" s="103"/>
+      <c r="L10" s="102"/>
+      <c r="M10" s="103"/>
+      <c r="N10" s="111"/>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="97" t="n">
+      <c r="A11" s="105" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="94"/>
-      <c r="C11" s="95"/>
-      <c r="D11" s="95"/>
-      <c r="E11" s="95"/>
-      <c r="F11" s="95"/>
-      <c r="G11" s="102"/>
-      <c r="H11" s="102"/>
+      <c r="B11" s="102"/>
+      <c r="C11" s="103"/>
+      <c r="D11" s="103"/>
+      <c r="E11" s="103"/>
+      <c r="F11" s="103"/>
+      <c r="G11" s="110"/>
+      <c r="H11" s="110"/>
       <c r="I11" s="21" t="str">
         <f aca="false">IF(OR(G11="",H11=""),"",H11-G11)</f>
         <v/>
       </c>
-      <c r="J11" s="95"/>
-      <c r="K11" s="95"/>
-      <c r="L11" s="94"/>
-      <c r="M11" s="95"/>
-      <c r="N11" s="103"/>
+      <c r="J11" s="103"/>
+      <c r="K11" s="103"/>
+      <c r="L11" s="102"/>
+      <c r="M11" s="103"/>
+      <c r="N11" s="111"/>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="97" t="n">
+      <c r="A12" s="105" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="94"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="102"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="110"/>
+      <c r="H12" s="110"/>
       <c r="I12" s="21" t="str">
         <f aca="false">IF(OR(G12="",H12=""),"",H12-G12)</f>
         <v/>
       </c>
-      <c r="J12" s="95"/>
-      <c r="K12" s="95"/>
-      <c r="L12" s="94"/>
-      <c r="M12" s="95"/>
-      <c r="N12" s="103"/>
+      <c r="J12" s="103"/>
+      <c r="K12" s="103"/>
+      <c r="L12" s="102"/>
+      <c r="M12" s="103"/>
+      <c r="N12" s="111"/>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="97" t="n">
+      <c r="A13" s="105" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="94"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="102"/>
-      <c r="H13" s="102"/>
+      <c r="B13" s="102"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="103"/>
+      <c r="G13" s="110"/>
+      <c r="H13" s="110"/>
       <c r="I13" s="21" t="str">
         <f aca="false">IF(OR(G13="",H13=""),"",H13-G13)</f>
         <v/>
       </c>
-      <c r="J13" s="95"/>
-      <c r="K13" s="95"/>
-      <c r="L13" s="94"/>
-      <c r="M13" s="95"/>
-      <c r="N13" s="103"/>
+      <c r="J13" s="103"/>
+      <c r="K13" s="103"/>
+      <c r="L13" s="102"/>
+      <c r="M13" s="103"/>
+      <c r="N13" s="111"/>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="97" t="n">
+      <c r="A14" s="105" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="94"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="102"/>
-      <c r="H14" s="102"/>
+      <c r="B14" s="102"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="103"/>
+      <c r="G14" s="110"/>
+      <c r="H14" s="110"/>
       <c r="I14" s="21" t="str">
         <f aca="false">IF(OR(G14="",H14=""),"",H14-G14)</f>
         <v/>
       </c>
-      <c r="J14" s="95"/>
-      <c r="K14" s="95"/>
-      <c r="L14" s="94"/>
-      <c r="M14" s="95"/>
-      <c r="N14" s="103"/>
+      <c r="J14" s="103"/>
+      <c r="K14" s="103"/>
+      <c r="L14" s="102"/>
+      <c r="M14" s="103"/>
+      <c r="N14" s="111"/>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="97" t="n">
+      <c r="A15" s="105" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="94"/>
-      <c r="C15" s="95"/>
-      <c r="D15" s="95"/>
-      <c r="E15" s="95"/>
-      <c r="F15" s="95"/>
-      <c r="G15" s="102"/>
-      <c r="H15" s="102"/>
+      <c r="B15" s="102"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="103"/>
+      <c r="G15" s="110"/>
+      <c r="H15" s="110"/>
       <c r="I15" s="21" t="str">
         <f aca="false">IF(OR(G15="",H15=""),"",H15-G15)</f>
         <v/>
       </c>
-      <c r="J15" s="95"/>
-      <c r="K15" s="95"/>
-      <c r="L15" s="94"/>
-      <c r="M15" s="95"/>
-      <c r="N15" s="103"/>
+      <c r="J15" s="103"/>
+      <c r="K15" s="103"/>
+      <c r="L15" s="102"/>
+      <c r="M15" s="103"/>
+      <c r="N15" s="111"/>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="97" t="n">
+      <c r="A16" s="105" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="94"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="102"/>
-      <c r="H16" s="102"/>
+      <c r="B16" s="102"/>
+      <c r="C16" s="103"/>
+      <c r="D16" s="103"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="103"/>
+      <c r="G16" s="110"/>
+      <c r="H16" s="110"/>
       <c r="I16" s="21" t="str">
         <f aca="false">IF(OR(G16="",H16=""),"",H16-G16)</f>
         <v/>
       </c>
-      <c r="J16" s="95"/>
-      <c r="K16" s="95"/>
-      <c r="L16" s="94"/>
-      <c r="M16" s="95"/>
-      <c r="N16" s="103"/>
+      <c r="J16" s="103"/>
+      <c r="K16" s="103"/>
+      <c r="L16" s="102"/>
+      <c r="M16" s="103"/>
+      <c r="N16" s="111"/>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="97" t="n">
+      <c r="A17" s="105" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="94"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="102"/>
-      <c r="H17" s="102"/>
+      <c r="B17" s="102"/>
+      <c r="C17" s="103"/>
+      <c r="D17" s="103"/>
+      <c r="E17" s="103"/>
+      <c r="F17" s="103"/>
+      <c r="G17" s="110"/>
+      <c r="H17" s="110"/>
       <c r="I17" s="21" t="str">
         <f aca="false">IF(OR(G17="",H17=""),"",H17-G17)</f>
         <v/>
       </c>
-      <c r="J17" s="95"/>
-      <c r="K17" s="95"/>
-      <c r="L17" s="94"/>
-      <c r="M17" s="95"/>
-      <c r="N17" s="103"/>
+      <c r="J17" s="103"/>
+      <c r="K17" s="103"/>
+      <c r="L17" s="102"/>
+      <c r="M17" s="103"/>
+      <c r="N17" s="111"/>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="97" t="n">
+      <c r="A18" s="105" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="94"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="102"/>
-      <c r="H18" s="102"/>
+      <c r="B18" s="102"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="103"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="103"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="110"/>
       <c r="I18" s="21" t="str">
         <f aca="false">IF(OR(G18="",H18=""),"",H18-G18)</f>
         <v/>
       </c>
-      <c r="J18" s="95"/>
-      <c r="K18" s="95"/>
-      <c r="L18" s="94"/>
-      <c r="M18" s="95"/>
-      <c r="N18" s="103"/>
+      <c r="J18" s="103"/>
+      <c r="K18" s="103"/>
+      <c r="L18" s="102"/>
+      <c r="M18" s="103"/>
+      <c r="N18" s="111"/>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="97" t="n">
+      <c r="A19" s="105" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="94"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="102"/>
-      <c r="H19" s="102"/>
+      <c r="B19" s="102"/>
+      <c r="C19" s="103"/>
+      <c r="D19" s="103"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="103"/>
+      <c r="G19" s="110"/>
+      <c r="H19" s="110"/>
       <c r="I19" s="21" t="str">
         <f aca="false">IF(OR(G19="",H19=""),"",H19-G19)</f>
         <v/>
       </c>
-      <c r="J19" s="95"/>
-      <c r="K19" s="95"/>
-      <c r="L19" s="94"/>
-      <c r="M19" s="95"/>
-      <c r="N19" s="103"/>
+      <c r="J19" s="103"/>
+      <c r="K19" s="103"/>
+      <c r="L19" s="102"/>
+      <c r="M19" s="103"/>
+      <c r="N19" s="111"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="97" t="n">
+      <c r="A20" s="105" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="94"/>
-      <c r="C20" s="95"/>
-      <c r="D20" s="95"/>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="102"/>
-      <c r="H20" s="102"/>
+      <c r="B20" s="102"/>
+      <c r="C20" s="103"/>
+      <c r="D20" s="103"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="103"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="110"/>
       <c r="I20" s="21" t="str">
         <f aca="false">IF(OR(G20="",H20=""),"",H20-G20)</f>
         <v/>
       </c>
-      <c r="J20" s="95"/>
-      <c r="K20" s="95"/>
-      <c r="L20" s="94"/>
-      <c r="M20" s="95"/>
-      <c r="N20" s="103"/>
+      <c r="J20" s="103"/>
+      <c r="K20" s="103"/>
+      <c r="L20" s="102"/>
+      <c r="M20" s="103"/>
+      <c r="N20" s="111"/>
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="97" t="n">
+      <c r="A21" s="105" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="94"/>
-      <c r="C21" s="95"/>
-      <c r="D21" s="95"/>
-      <c r="E21" s="95"/>
-      <c r="F21" s="95"/>
-      <c r="G21" s="102"/>
-      <c r="H21" s="102"/>
+      <c r="B21" s="102"/>
+      <c r="C21" s="103"/>
+      <c r="D21" s="103"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="103"/>
+      <c r="G21" s="110"/>
+      <c r="H21" s="110"/>
       <c r="I21" s="21" t="str">
         <f aca="false">IF(OR(G21="",H21=""),"",H21-G21)</f>
         <v/>
       </c>
-      <c r="J21" s="95"/>
-      <c r="K21" s="95"/>
-      <c r="L21" s="94"/>
-      <c r="M21" s="95"/>
-      <c r="N21" s="103"/>
+      <c r="J21" s="103"/>
+      <c r="K21" s="103"/>
+      <c r="L21" s="102"/>
+      <c r="M21" s="103"/>
+      <c r="N21" s="111"/>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="97" t="n">
+      <c r="A22" s="105" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="94"/>
-      <c r="C22" s="95"/>
-      <c r="D22" s="95"/>
-      <c r="E22" s="95"/>
-      <c r="F22" s="95"/>
-      <c r="G22" s="102"/>
-      <c r="H22" s="102"/>
+      <c r="B22" s="102"/>
+      <c r="C22" s="103"/>
+      <c r="D22" s="103"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="103"/>
+      <c r="G22" s="110"/>
+      <c r="H22" s="110"/>
       <c r="I22" s="21" t="str">
         <f aca="false">IF(OR(G22="",H22=""),"",H22-G22)</f>
         <v/>
       </c>
-      <c r="J22" s="95"/>
-      <c r="K22" s="95"/>
-      <c r="L22" s="94"/>
-      <c r="M22" s="95"/>
-      <c r="N22" s="103"/>
+      <c r="J22" s="103"/>
+      <c r="K22" s="103"/>
+      <c r="L22" s="102"/>
+      <c r="M22" s="103"/>
+      <c r="N22" s="111"/>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="97" t="n">
+      <c r="A23" s="105" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="94"/>
-      <c r="C23" s="95"/>
-      <c r="D23" s="95"/>
-      <c r="E23" s="95"/>
-      <c r="F23" s="95"/>
-      <c r="G23" s="102"/>
-      <c r="H23" s="102"/>
+      <c r="B23" s="102"/>
+      <c r="C23" s="103"/>
+      <c r="D23" s="103"/>
+      <c r="E23" s="103"/>
+      <c r="F23" s="103"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="110"/>
       <c r="I23" s="21" t="str">
         <f aca="false">IF(OR(G23="",H23=""),"",H23-G23)</f>
         <v/>
       </c>
-      <c r="J23" s="95"/>
-      <c r="K23" s="95"/>
-      <c r="L23" s="94"/>
-      <c r="M23" s="95"/>
-      <c r="N23" s="103"/>
+      <c r="J23" s="103"/>
+      <c r="K23" s="103"/>
+      <c r="L23" s="102"/>
+      <c r="M23" s="103"/>
+      <c r="N23" s="111"/>
     </row>
     <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="97" t="n">
+      <c r="A24" s="105" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="94"/>
-      <c r="C24" s="95"/>
-      <c r="D24" s="95"/>
-      <c r="E24" s="95"/>
-      <c r="F24" s="95"/>
-      <c r="G24" s="102"/>
-      <c r="H24" s="102"/>
+      <c r="B24" s="102"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="103"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="103"/>
+      <c r="G24" s="110"/>
+      <c r="H24" s="110"/>
       <c r="I24" s="21" t="str">
         <f aca="false">IF(OR(G24="",H24=""),"",H24-G24)</f>
         <v/>
       </c>
-      <c r="J24" s="95"/>
-      <c r="K24" s="95"/>
-      <c r="L24" s="94"/>
-      <c r="M24" s="95"/>
-      <c r="N24" s="103"/>
+      <c r="J24" s="103"/>
+      <c r="K24" s="103"/>
+      <c r="L24" s="102"/>
+      <c r="M24" s="103"/>
+      <c r="N24" s="111"/>
     </row>
     <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="97" t="n">
+      <c r="A25" s="105" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="94"/>
-      <c r="C25" s="95"/>
-      <c r="D25" s="95"/>
-      <c r="E25" s="95"/>
-      <c r="F25" s="95"/>
-      <c r="G25" s="102"/>
-      <c r="H25" s="102"/>
+      <c r="B25" s="102"/>
+      <c r="C25" s="103"/>
+      <c r="D25" s="103"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="110"/>
+      <c r="H25" s="110"/>
       <c r="I25" s="21" t="str">
         <f aca="false">IF(OR(G25="",H25=""),"",H25-G25)</f>
         <v/>
       </c>
-      <c r="J25" s="95"/>
-      <c r="K25" s="95"/>
-      <c r="L25" s="94"/>
-      <c r="M25" s="95"/>
-      <c r="N25" s="103"/>
+      <c r="J25" s="103"/>
+      <c r="K25" s="103"/>
+      <c r="L25" s="102"/>
+      <c r="M25" s="103"/>
+      <c r="N25" s="111"/>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="97" t="n">
+      <c r="A26" s="105" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="94"/>
-      <c r="C26" s="95"/>
-      <c r="D26" s="95"/>
-      <c r="E26" s="95"/>
-      <c r="F26" s="95"/>
-      <c r="G26" s="102"/>
-      <c r="H26" s="102"/>
+      <c r="B26" s="102"/>
+      <c r="C26" s="103"/>
+      <c r="D26" s="103"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="103"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="110"/>
       <c r="I26" s="21" t="str">
         <f aca="false">IF(OR(G26="",H26=""),"",H26-G26)</f>
         <v/>
       </c>
-      <c r="J26" s="95"/>
-      <c r="K26" s="95"/>
-      <c r="L26" s="94"/>
-      <c r="M26" s="95"/>
-      <c r="N26" s="103"/>
+      <c r="J26" s="103"/>
+      <c r="K26" s="103"/>
+      <c r="L26" s="102"/>
+      <c r="M26" s="103"/>
+      <c r="N26" s="111"/>
     </row>
     <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="97" t="n">
+      <c r="A27" s="105" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="94"/>
-      <c r="C27" s="95"/>
-      <c r="D27" s="95"/>
-      <c r="E27" s="95"/>
-      <c r="F27" s="95"/>
-      <c r="G27" s="102"/>
-      <c r="H27" s="102"/>
+      <c r="B27" s="102"/>
+      <c r="C27" s="103"/>
+      <c r="D27" s="103"/>
+      <c r="E27" s="103"/>
+      <c r="F27" s="103"/>
+      <c r="G27" s="110"/>
+      <c r="H27" s="110"/>
       <c r="I27" s="21" t="str">
         <f aca="false">IF(OR(G27="",H27=""),"",H27-G27)</f>
         <v/>
       </c>
-      <c r="J27" s="95"/>
-      <c r="K27" s="95"/>
-      <c r="L27" s="94"/>
-      <c r="M27" s="95"/>
-      <c r="N27" s="103"/>
+      <c r="J27" s="103"/>
+      <c r="K27" s="103"/>
+      <c r="L27" s="102"/>
+      <c r="M27" s="103"/>
+      <c r="N27" s="111"/>
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="97" t="n">
+      <c r="A28" s="105" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="94"/>
-      <c r="C28" s="95"/>
-      <c r="D28" s="95"/>
-      <c r="E28" s="95"/>
-      <c r="F28" s="95"/>
-      <c r="G28" s="102"/>
-      <c r="H28" s="102"/>
+      <c r="B28" s="102"/>
+      <c r="C28" s="103"/>
+      <c r="D28" s="103"/>
+      <c r="E28" s="103"/>
+      <c r="F28" s="103"/>
+      <c r="G28" s="110"/>
+      <c r="H28" s="110"/>
       <c r="I28" s="21" t="str">
         <f aca="false">IF(OR(G28="",H28=""),"",H28-G28)</f>
         <v/>
       </c>
-      <c r="J28" s="95"/>
-      <c r="K28" s="95"/>
-      <c r="L28" s="94"/>
-      <c r="M28" s="95"/>
-      <c r="N28" s="103"/>
+      <c r="J28" s="103"/>
+      <c r="K28" s="103"/>
+      <c r="L28" s="102"/>
+      <c r="M28" s="103"/>
+      <c r="N28" s="111"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="24" t="s">
-        <v>1071</v>
+        <v>1217</v>
       </c>
       <c r="M30" s="21" t="str">
         <f aca="false">COUNTA(B5:B28)&amp;" مبادرة"</f>
@@ -11876,7 +15582,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -11902,7 +15608,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1072</v>
+        <v>1218</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11921,7 +15627,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1073</v>
+        <v>1219</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11940,60 +15646,60 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>1074</v>
+        <v>1220</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>858</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>1075</v>
+        <v>1012</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>1076</v>
+        <v>1221</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>1077</v>
+        <v>1222</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1078</v>
+        <v>1223</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1079</v>
+        <v>1224</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1080</v>
+        <v>1225</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>1081</v>
+        <v>1226</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>1082</v>
+        <v>1227</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>860</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>1083</v>
+        <v>1228</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>1084</v>
+        <v>1229</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>1085</v>
+        <v>1230</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>1086</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>1087</v>
+        <v>1025</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>1088</v>
+        <v>1026</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>868</v>
@@ -12014,7 +15720,7 @@
       <c r="I4" s="28" t="n">
         <v>23493282</v>
       </c>
-      <c r="J4" s="92" t="n">
+      <c r="J4" s="100" t="n">
         <v>64.69</v>
       </c>
       <c r="K4" s="57" t="n">
@@ -12030,18 +15736,18 @@
         <v>0.281</v>
       </c>
       <c r="O4" s="21" t="s">
-        <v>1090</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>1091</v>
+        <v>1023</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>926</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>862</v>
@@ -12062,10 +15768,10 @@
       <c r="I5" s="28" t="n">
         <v>8841940</v>
       </c>
-      <c r="J5" s="92" t="n">
+      <c r="J5" s="100" t="n">
         <v>61.72</v>
       </c>
-      <c r="K5" s="104" t="n">
+      <c r="K5" s="112" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="45" t="n">
@@ -12078,18 +15784,18 @@
         <v>0</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>1092</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>1093</v>
+        <v>1027</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>927</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>1094</v>
+        <v>1028</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>868</v>
@@ -12110,10 +15816,10 @@
       <c r="I6" s="28" t="n">
         <v>7467484</v>
       </c>
-      <c r="J6" s="92" t="n">
+      <c r="J6" s="100" t="n">
         <v>80.21</v>
       </c>
-      <c r="K6" s="104" t="n">
+      <c r="K6" s="112" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="45" t="n">
@@ -12126,15 +15832,15 @@
         <v>0.344</v>
       </c>
       <c r="O6" s="21" t="s">
-        <v>1095</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>1096</v>
+        <v>1054</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>1097</v>
+        <v>1055</v>
       </c>
       <c r="C7" s="21" t="s">
         <v>350</v>
@@ -12158,10 +15864,10 @@
       <c r="I7" s="28" t="n">
         <v>14552120</v>
       </c>
-      <c r="J7" s="92" t="n">
+      <c r="J7" s="100" t="n">
         <v>84.21</v>
       </c>
-      <c r="K7" s="105" t="n">
+      <c r="K7" s="113" t="n">
         <v>0.273</v>
       </c>
       <c r="L7" s="45" t="n">
@@ -12174,18 +15880,18 @@
         <v>0.641</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>1098</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>1099</v>
+        <v>1029</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>1100</v>
+        <v>1030</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>868</v>
@@ -12206,7 +15912,7 @@
       <c r="I8" s="28" t="n">
         <v>2916708</v>
       </c>
-      <c r="J8" s="92" t="n">
+      <c r="J8" s="100" t="n">
         <v>48.35</v>
       </c>
       <c r="K8" s="57" t="n">
@@ -12222,21 +15928,21 @@
         <v>0.134</v>
       </c>
       <c r="O8" s="21" t="s">
-        <v>1101</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>1102</v>
+        <v>1038</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>1103</v>
+        <v>1039</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>1094</v>
+        <v>1028</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>1104</v>
+        <v>1037</v>
       </c>
       <c r="E9" s="21" t="n">
         <v>55</v>
@@ -12254,10 +15960,10 @@
       <c r="I9" s="28" t="n">
         <v>2916316</v>
       </c>
-      <c r="J9" s="92" t="n">
+      <c r="J9" s="100" t="n">
         <v>65.82</v>
       </c>
-      <c r="K9" s="104" t="n">
+      <c r="K9" s="112" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="45" t="n">
@@ -12270,18 +15976,18 @@
         <v>0.309</v>
       </c>
       <c r="O9" s="21" t="s">
-        <v>1090</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>1105</v>
+        <v>1031</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>1106</v>
+        <v>1032</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>1094</v>
+        <v>1028</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>868</v>
@@ -12302,10 +16008,10 @@
       <c r="I10" s="28" t="n">
         <v>2831981</v>
       </c>
-      <c r="J10" s="92" t="n">
+      <c r="J10" s="100" t="n">
         <v>59.14</v>
       </c>
-      <c r="K10" s="104" t="n">
+      <c r="K10" s="112" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="45" t="n">
@@ -12318,15 +16024,15 @@
         <v>0.006</v>
       </c>
       <c r="O10" s="21" t="s">
-        <v>1095</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>1107</v>
+        <v>1033</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>1108</v>
+        <v>1034</v>
       </c>
       <c r="C11" s="21" t="s">
         <v>350</v>
@@ -12350,10 +16056,10 @@
       <c r="I11" s="28" t="n">
         <v>2931550</v>
       </c>
-      <c r="J11" s="92" t="n">
+      <c r="J11" s="100" t="n">
         <v>49.84</v>
       </c>
-      <c r="K11" s="104" t="n">
+      <c r="K11" s="112" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="45" t="n">
@@ -12366,18 +16072,18 @@
         <v>0</v>
       </c>
       <c r="O11" s="21" t="s">
-        <v>1095</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>1109</v>
+        <v>1045</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>931</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>868</v>
@@ -12398,7 +16104,7 @@
       <c r="I12" s="28" t="n">
         <v>8679738</v>
       </c>
-      <c r="J12" s="92" t="n">
+      <c r="J12" s="100" t="n">
         <v>59.34</v>
       </c>
       <c r="K12" s="57" t="n">
@@ -12414,21 +16120,21 @@
         <v>0.277</v>
       </c>
       <c r="O12" s="21" t="s">
-        <v>1095</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>1110</v>
+        <v>1035</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>1111</v>
+        <v>1036</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>1094</v>
+        <v>1028</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>1104</v>
+        <v>1037</v>
       </c>
       <c r="E13" s="21" t="n">
         <v>181</v>
@@ -12446,7 +16152,7 @@
       <c r="I13" s="28" t="n">
         <v>7729931</v>
       </c>
-      <c r="J13" s="92" t="n">
+      <c r="J13" s="100" t="n">
         <v>67.66</v>
       </c>
       <c r="K13" s="57" t="n">
@@ -12462,18 +16168,18 @@
         <v>0.082</v>
       </c>
       <c r="O13" s="21" t="s">
-        <v>1095</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>1112</v>
+        <v>1046</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>1113</v>
+        <v>1047</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>868</v>
@@ -12494,7 +16200,7 @@
       <c r="I14" s="28" t="n">
         <v>2676944</v>
       </c>
-      <c r="J14" s="92" t="n">
+      <c r="J14" s="100" t="n">
         <v>59.47</v>
       </c>
       <c r="K14" s="45" t="n">
@@ -12510,18 +16216,18 @@
         <v>0.231</v>
       </c>
       <c r="O14" s="21" t="s">
-        <v>1095</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>1114</v>
+        <v>1060</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>1115</v>
+        <v>1061</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>862</v>
@@ -12542,7 +16248,7 @@
       <c r="I15" s="28" t="n">
         <v>7806709</v>
       </c>
-      <c r="J15" s="92" t="n">
+      <c r="J15" s="100" t="n">
         <v>63.18</v>
       </c>
       <c r="K15" s="57" t="n">
@@ -12558,15 +16264,15 @@
         <v>0.458</v>
       </c>
       <c r="O15" s="21" t="s">
-        <v>1101</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>1116</v>
+        <v>1043</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>1117</v>
+        <v>1044</v>
       </c>
       <c r="C16" s="21" t="s">
         <v>355</v>
@@ -12590,10 +16296,10 @@
       <c r="I16" s="28" t="n">
         <v>4791911</v>
       </c>
-      <c r="J16" s="92" t="n">
+      <c r="J16" s="100" t="n">
         <v>74.3</v>
       </c>
-      <c r="K16" s="105" t="n">
+      <c r="K16" s="113" t="n">
         <v>0.151</v>
       </c>
       <c r="L16" s="45" t="n">
@@ -12606,18 +16312,18 @@
         <v>0.076</v>
       </c>
       <c r="O16" s="21" t="s">
-        <v>1095</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>1118</v>
+        <v>1040</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>1119</v>
+        <v>1041</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>1094</v>
+        <v>1028</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>868</v>
@@ -12638,10 +16344,10 @@
       <c r="I17" s="28" t="n">
         <v>2078856</v>
       </c>
-      <c r="J17" s="92" t="n">
+      <c r="J17" s="100" t="n">
         <v>55.76</v>
       </c>
-      <c r="K17" s="104" t="n">
+      <c r="K17" s="112" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="45" t="n">
@@ -12654,18 +16360,18 @@
         <v>0</v>
       </c>
       <c r="O17" s="21" t="s">
-        <v>1090</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>1120</v>
+        <v>1042</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>938</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>868</v>
@@ -12686,7 +16392,7 @@
       <c r="I18" s="28" t="n">
         <v>6570004</v>
       </c>
-      <c r="J18" s="92" t="n">
+      <c r="J18" s="100" t="n">
         <v>43.71</v>
       </c>
       <c r="K18" s="45" t="n">
@@ -12702,15 +16408,15 @@
         <v>0</v>
       </c>
       <c r="O18" s="21" t="s">
-        <v>1090</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>1121</v>
+        <v>1048</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>1122</v>
+        <v>1049</v>
       </c>
       <c r="C19" s="21" t="s">
         <v>347</v>
@@ -12734,10 +16440,10 @@
       <c r="I19" s="28" t="n">
         <v>4445436</v>
       </c>
-      <c r="J19" s="92" t="n">
+      <c r="J19" s="100" t="n">
         <v>42.14</v>
       </c>
-      <c r="K19" s="105" t="n">
+      <c r="K19" s="113" t="n">
         <v>0.275</v>
       </c>
       <c r="L19" s="45" t="n">
@@ -12750,21 +16456,21 @@
         <v>0.048</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>1098</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>1123</v>
+        <v>1050</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>1124</v>
+        <v>1051</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>1125</v>
+        <v>1052</v>
       </c>
       <c r="E20" s="21" t="n">
         <v>70</v>
@@ -12782,10 +16488,10 @@
       <c r="I20" s="28" t="n">
         <v>2229579</v>
       </c>
-      <c r="J20" s="92" t="n">
+      <c r="J20" s="100" t="n">
         <v>43.6</v>
       </c>
-      <c r="K20" s="104" t="n">
+      <c r="K20" s="112" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="45" t="n">
@@ -12798,18 +16504,18 @@
         <v>0</v>
       </c>
       <c r="O20" s="21" t="s">
-        <v>1092</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>1126</v>
+        <v>1053</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>940</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D21" s="21" t="s">
         <v>868</v>
@@ -12830,7 +16536,7 @@
       <c r="I21" s="28" t="n">
         <v>5504980</v>
       </c>
-      <c r="J21" s="92" t="n">
+      <c r="J21" s="100" t="n">
         <v>43.52</v>
       </c>
       <c r="K21" s="57" t="n">
@@ -12846,15 +16552,15 @@
         <v>0</v>
       </c>
       <c r="O21" s="21" t="s">
-        <v>1095</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>1127</v>
+        <v>1062</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>1128</v>
+        <v>1063</v>
       </c>
       <c r="C22" s="21" t="s">
         <v>350</v>
@@ -12878,10 +16584,10 @@
       <c r="I22" s="28" t="n">
         <v>4722403</v>
       </c>
-      <c r="J22" s="92" t="n">
+      <c r="J22" s="100" t="n">
         <v>49.88</v>
       </c>
-      <c r="K22" s="105" t="n">
+      <c r="K22" s="113" t="n">
         <v>0.068</v>
       </c>
       <c r="L22" s="45" t="n">
@@ -12894,18 +16600,18 @@
         <v>0.329</v>
       </c>
       <c r="O22" s="21" t="s">
-        <v>1101</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>1129</v>
+        <v>1056</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>944</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D23" s="21" t="s">
         <v>868</v>
@@ -12926,10 +16632,10 @@
       <c r="I23" s="28" t="n">
         <v>4924931</v>
       </c>
-      <c r="J23" s="92" t="n">
+      <c r="J23" s="100" t="n">
         <v>47.68</v>
       </c>
-      <c r="K23" s="105" t="n">
+      <c r="K23" s="113" t="n">
         <v>0.069</v>
       </c>
       <c r="L23" s="45" t="n">
@@ -12942,18 +16648,18 @@
         <v>0</v>
       </c>
       <c r="O23" s="21" t="s">
-        <v>1095</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>1130</v>
+        <v>1057</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>943</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D24" s="21" t="s">
         <v>868</v>
@@ -12974,7 +16680,7 @@
       <c r="I24" s="28" t="n">
         <v>4740020</v>
       </c>
-      <c r="J24" s="92" t="n">
+      <c r="J24" s="100" t="n">
         <v>43.42</v>
       </c>
       <c r="K24" s="45" t="n">
@@ -12990,21 +16696,21 @@
         <v>0</v>
       </c>
       <c r="O24" s="21" t="s">
-        <v>1095</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>1131</v>
+        <v>1058</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>1132</v>
+        <v>1059</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>1094</v>
+        <v>1028</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>1104</v>
+        <v>1037</v>
       </c>
       <c r="E25" s="21" t="n">
         <v>181</v>
@@ -13022,10 +16728,10 @@
       <c r="I25" s="28" t="n">
         <v>4771577</v>
       </c>
-      <c r="J25" s="92" t="n">
+      <c r="J25" s="100" t="n">
         <v>51.68</v>
       </c>
-      <c r="K25" s="105" t="n">
+      <c r="K25" s="113" t="n">
         <v>0.177</v>
       </c>
       <c r="L25" s="45" t="n">
@@ -13038,21 +16744,21 @@
         <v>0.058</v>
       </c>
       <c r="O25" s="21" t="s">
-        <v>1090</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>1133</v>
+        <v>1065</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>1134</v>
+        <v>1066</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>1125</v>
+        <v>1052</v>
       </c>
       <c r="E26" s="21" t="n">
         <v>181</v>
@@ -13070,7 +16776,7 @@
       <c r="I26" s="28" t="n">
         <v>4933540</v>
       </c>
-      <c r="J26" s="92" t="n">
+      <c r="J26" s="100" t="n">
         <v>51.76</v>
       </c>
       <c r="K26" s="45" t="n">
@@ -13086,21 +16792,21 @@
         <v>0.276</v>
       </c>
       <c r="O26" s="21" t="s">
-        <v>1090</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>1135</v>
+        <v>1074</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>1136</v>
+        <v>1075</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>1094</v>
+        <v>1028</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>1104</v>
+        <v>1037</v>
       </c>
       <c r="E27" s="21" t="n">
         <v>181</v>
@@ -13118,10 +16824,10 @@
       <c r="I27" s="28" t="n">
         <v>4643058</v>
       </c>
-      <c r="J27" s="92" t="n">
+      <c r="J27" s="100" t="n">
         <v>66.28</v>
       </c>
-      <c r="K27" s="105" t="n">
+      <c r="K27" s="113" t="n">
         <v>0.083</v>
       </c>
       <c r="L27" s="45" t="n">
@@ -13134,18 +16840,18 @@
         <v>0.27</v>
       </c>
       <c r="O27" s="21" t="s">
-        <v>1137</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>1138</v>
+        <v>1080</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>1139</v>
+        <v>1081</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D28" s="21" t="s">
         <v>862</v>
@@ -13166,10 +16872,10 @@
       <c r="I28" s="28" t="n">
         <v>2834084</v>
       </c>
-      <c r="J28" s="92" t="n">
+      <c r="J28" s="100" t="n">
         <v>77.81</v>
       </c>
-      <c r="K28" s="104" t="n">
+      <c r="K28" s="112" t="n">
         <v>-0.033</v>
       </c>
       <c r="L28" s="45" t="n">
@@ -13182,21 +16888,21 @@
         <v>0.349</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>1098</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>1140</v>
+        <v>1078</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>1141</v>
+        <v>1079</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>1125</v>
+        <v>1052</v>
       </c>
       <c r="E29" s="21" t="n">
         <v>181</v>
@@ -13214,7 +16920,7 @@
       <c r="I29" s="28" t="n">
         <v>4558563</v>
       </c>
-      <c r="J29" s="92" t="n">
+      <c r="J29" s="100" t="n">
         <v>64.44</v>
       </c>
       <c r="K29" s="45" t="n">
@@ -13230,18 +16936,18 @@
         <v>0.321</v>
       </c>
       <c r="O29" s="21" t="s">
-        <v>1090</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>1142</v>
+        <v>1072</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>1143</v>
+        <v>1073</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D30" s="21" t="s">
         <v>868</v>
@@ -13262,10 +16968,10 @@
       <c r="I30" s="28" t="n">
         <v>2127665</v>
       </c>
-      <c r="J30" s="92" t="n">
+      <c r="J30" s="100" t="n">
         <v>48.52</v>
       </c>
-      <c r="K30" s="104" t="n">
+      <c r="K30" s="112" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="45" t="n">
@@ -13278,15 +16984,15 @@
         <v>0.176</v>
       </c>
       <c r="O30" s="21" t="s">
-        <v>1090</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>1144</v>
+        <v>1067</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>1145</v>
+        <v>1068</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>361</v>
@@ -13310,10 +17016,10 @@
       <c r="I31" s="28" t="n">
         <v>3884721</v>
       </c>
-      <c r="J31" s="92" t="n">
+      <c r="J31" s="100" t="n">
         <v>54.76</v>
       </c>
-      <c r="K31" s="105" t="n">
+      <c r="K31" s="113" t="n">
         <v>0.186</v>
       </c>
       <c r="L31" s="45" t="n">
@@ -13326,18 +17032,18 @@
         <v>0.082</v>
       </c>
       <c r="O31" s="21" t="s">
-        <v>1095</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>1146</v>
+        <v>1070</v>
       </c>
       <c r="B32" s="16" t="s">
         <v>968</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>1147</v>
+        <v>1071</v>
       </c>
       <c r="D32" s="21" t="s">
         <v>866</v>
@@ -13358,10 +17064,10 @@
       <c r="I32" s="28" t="n">
         <v>1471112</v>
       </c>
-      <c r="J32" s="92" t="n">
+      <c r="J32" s="100" t="n">
         <v>49.67</v>
       </c>
-      <c r="K32" s="104" t="n">
+      <c r="K32" s="112" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="45" t="n">
@@ -13374,12 +17080,12 @@
         <v>0.103</v>
       </c>
       <c r="O32" s="20" t="s">
-        <v>1098</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>1148</v>
+        <v>1064</v>
       </c>
       <c r="B33" s="16" t="s">
         <v>950</v>
@@ -13406,10 +17112,10 @@
       <c r="I33" s="28" t="n">
         <v>3774634</v>
       </c>
-      <c r="J33" s="92" t="n">
+      <c r="J33" s="100" t="n">
         <v>50.81</v>
       </c>
-      <c r="K33" s="105" t="n">
+      <c r="K33" s="113" t="n">
         <v>0.18</v>
       </c>
       <c r="L33" s="45" t="n">
@@ -13422,18 +17128,18 @@
         <v>0.023</v>
       </c>
       <c r="O33" s="21" t="s">
-        <v>1090</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>1149</v>
+        <v>1106</v>
       </c>
       <c r="B34" s="16" t="s">
         <v>948</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D34" s="21" t="s">
         <v>862</v>
@@ -13454,7 +17160,7 @@
       <c r="I34" s="28" t="n">
         <v>4263083</v>
       </c>
-      <c r="J34" s="92" t="n">
+      <c r="J34" s="100" t="n">
         <v>110.06</v>
       </c>
       <c r="K34" s="57" t="n">
@@ -13470,18 +17176,18 @@
         <v>0.559</v>
       </c>
       <c r="O34" s="21" t="s">
-        <v>1137</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>1150</v>
+        <v>1069</v>
       </c>
       <c r="B35" s="16" t="s">
         <v>952</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D35" s="21" t="s">
         <v>868</v>
@@ -13502,7 +17208,7 @@
       <c r="I35" s="28" t="n">
         <v>3471225</v>
       </c>
-      <c r="J35" s="92" t="n">
+      <c r="J35" s="100" t="n">
         <v>47.35</v>
       </c>
       <c r="K35" s="57" t="n">
@@ -13518,21 +17224,21 @@
         <v>0</v>
       </c>
       <c r="O35" s="21" t="s">
-        <v>1095</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>1151</v>
+        <v>1076</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>1152</v>
+        <v>1077</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>1104</v>
+        <v>1037</v>
       </c>
       <c r="E36" s="21" t="n">
         <v>181</v>
@@ -13550,7 +17256,7 @@
       <c r="I36" s="28" t="n">
         <v>3512113</v>
       </c>
-      <c r="J36" s="92" t="n">
+      <c r="J36" s="100" t="n">
         <v>45.88</v>
       </c>
       <c r="K36" s="57" t="n">
@@ -13566,15 +17272,15 @@
         <v>0.115</v>
       </c>
       <c r="O36" s="21" t="s">
-        <v>1101</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>1153</v>
+        <v>1082</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>1154</v>
+        <v>1083</v>
       </c>
       <c r="C37" s="21" t="s">
         <v>347</v>
@@ -13598,10 +17304,10 @@
       <c r="I37" s="28" t="n">
         <v>486162</v>
       </c>
-      <c r="J37" s="92" t="n">
+      <c r="J37" s="100" t="n">
         <v>33.35</v>
       </c>
-      <c r="K37" s="104" t="n">
+      <c r="K37" s="112" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="45" t="n">
@@ -13619,10 +17325,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
-        <v>1155</v>
+        <v>1086</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>1156</v>
+        <v>1087</v>
       </c>
       <c r="C38" s="21" t="s">
         <v>350</v>
@@ -13646,10 +17352,10 @@
       <c r="I38" s="28" t="n">
         <v>3406904</v>
       </c>
-      <c r="J38" s="92" t="n">
+      <c r="J38" s="100" t="n">
         <v>43.04</v>
       </c>
-      <c r="K38" s="105" t="n">
+      <c r="K38" s="113" t="n">
         <v>0.083</v>
       </c>
       <c r="L38" s="45" t="n">
@@ -13662,18 +17368,18 @@
         <v>0.167</v>
       </c>
       <c r="O38" s="21" t="s">
-        <v>1090</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="21" t="s">
-        <v>1157</v>
+        <v>1090</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>1158</v>
+        <v>1091</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D39" s="21" t="s">
         <v>862</v>
@@ -13694,7 +17400,7 @@
       <c r="I39" s="28" t="n">
         <v>3076219</v>
       </c>
-      <c r="J39" s="92" t="n">
+      <c r="J39" s="100" t="n">
         <v>69.64</v>
       </c>
       <c r="K39" s="57" t="n">
@@ -13710,15 +17416,15 @@
         <v>0.106</v>
       </c>
       <c r="O39" s="21" t="s">
-        <v>1090</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="21" t="s">
-        <v>1159</v>
+        <v>1100</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>1160</v>
+        <v>1101</v>
       </c>
       <c r="C40" s="21" t="s">
         <v>347</v>
@@ -13742,7 +17448,7 @@
       <c r="I40" s="28" t="n">
         <v>3314721</v>
       </c>
-      <c r="J40" s="92" t="n">
+      <c r="J40" s="100" t="n">
         <v>69.44</v>
       </c>
       <c r="K40" s="45" t="n">
@@ -13758,18 +17464,18 @@
         <v>0.373</v>
       </c>
       <c r="O40" s="21" t="s">
-        <v>1090</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="21" t="s">
-        <v>1161</v>
+        <v>1084</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>1162</v>
+        <v>1085</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D41" s="21" t="s">
         <v>868</v>
@@ -13790,7 +17496,7 @@
       <c r="I41" s="28" t="n">
         <v>2925368</v>
       </c>
-      <c r="J41" s="92" t="n">
+      <c r="J41" s="100" t="n">
         <v>45.21</v>
       </c>
       <c r="K41" s="57" t="n">
@@ -13806,15 +17512,15 @@
         <v>0</v>
       </c>
       <c r="O41" s="21" t="s">
-        <v>1090</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="21" t="s">
-        <v>1163</v>
+        <v>1088</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>1164</v>
+        <v>1089</v>
       </c>
       <c r="C42" s="21" t="s">
         <v>347</v>
@@ -13838,10 +17544,10 @@
       <c r="I42" s="28" t="n">
         <v>1114635</v>
       </c>
-      <c r="J42" s="92" t="n">
+      <c r="J42" s="100" t="n">
         <v>45.6</v>
       </c>
-      <c r="K42" s="104" t="n">
+      <c r="K42" s="112" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="45" t="n">
@@ -13854,21 +17560,21 @@
         <v>0.056</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>1098</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
-        <v>1165</v>
+        <v>1092</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>1166</v>
+        <v>1093</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>1094</v>
+        <v>1028</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>1125</v>
+        <v>1052</v>
       </c>
       <c r="E43" s="21" t="n">
         <v>181</v>
@@ -13886,10 +17592,10 @@
       <c r="I43" s="28" t="n">
         <v>2839338</v>
       </c>
-      <c r="J43" s="92" t="n">
+      <c r="J43" s="100" t="n">
         <v>50.86</v>
       </c>
-      <c r="K43" s="105" t="n">
+      <c r="K43" s="113" t="n">
         <v>0.082</v>
       </c>
       <c r="L43" s="45" t="n">
@@ -13902,18 +17608,18 @@
         <v>0.077</v>
       </c>
       <c r="O43" s="21" t="s">
-        <v>1137</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
-        <v>1167</v>
+        <v>1094</v>
       </c>
       <c r="B44" s="16" t="s">
         <v>962</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>1168</v>
+        <v>1095</v>
       </c>
       <c r="D44" s="21" t="s">
         <v>868</v>
@@ -13934,10 +17640,10 @@
       <c r="I44" s="28" t="n">
         <v>2759664</v>
       </c>
-      <c r="J44" s="92" t="n">
+      <c r="J44" s="100" t="n">
         <v>56.84</v>
       </c>
-      <c r="K44" s="105" t="n">
+      <c r="K44" s="113" t="n">
         <v>0.327</v>
       </c>
       <c r="L44" s="45" t="n">
@@ -13950,18 +17656,18 @@
         <v>0.066</v>
       </c>
       <c r="O44" s="20" t="s">
-        <v>1098</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="21" t="s">
-        <v>1169</v>
+        <v>1109</v>
       </c>
       <c r="B45" s="16" t="s">
         <v>959</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>1170</v>
+        <v>1110</v>
       </c>
       <c r="D45" s="21" t="s">
         <v>866</v>
@@ -13982,7 +17688,7 @@
       <c r="I45" s="28" t="n">
         <v>2940822</v>
       </c>
-      <c r="J45" s="92" t="n">
+      <c r="J45" s="100" t="n">
         <v>74.93</v>
       </c>
       <c r="K45" s="45" t="n">
@@ -13998,18 +17704,18 @@
         <v>0.392</v>
       </c>
       <c r="O45" s="20" t="s">
-        <v>1098</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="21" t="s">
-        <v>1171</v>
+        <v>1102</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>1172</v>
+        <v>1103</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D46" s="21" t="s">
         <v>868</v>
@@ -14030,7 +17736,7 @@
       <c r="I46" s="28" t="n">
         <v>2694118</v>
       </c>
-      <c r="J46" s="92" t="n">
+      <c r="J46" s="100" t="n">
         <v>53.94</v>
       </c>
       <c r="K46" s="57" t="n">
@@ -14046,12 +17752,12 @@
         <v>0.236</v>
       </c>
       <c r="O46" s="21" t="s">
-        <v>1095</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="21" t="s">
-        <v>1173</v>
+        <v>1096</v>
       </c>
       <c r="B47" s="16" t="s">
         <v>963</v>
@@ -14060,7 +17766,7 @@
         <v>347</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>1174</v>
+        <v>1097</v>
       </c>
       <c r="E47" s="21" t="n">
         <v>181</v>
@@ -14078,7 +17784,7 @@
       <c r="I47" s="28" t="n">
         <v>2650896</v>
       </c>
-      <c r="J47" s="92" t="n">
+      <c r="J47" s="100" t="n">
         <v>48.6</v>
       </c>
       <c r="K47" s="45" t="n">
@@ -14094,15 +17800,15 @@
         <v>0.184</v>
       </c>
       <c r="O47" s="21" t="s">
-        <v>1137</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="21" t="s">
-        <v>1175</v>
+        <v>1098</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>1176</v>
+        <v>1099</v>
       </c>
       <c r="C48" s="21" t="s">
         <v>361</v>
@@ -14126,10 +17832,10 @@
       <c r="I48" s="28" t="n">
         <v>2153145</v>
       </c>
-      <c r="J48" s="92" t="n">
+      <c r="J48" s="100" t="n">
         <v>57.15</v>
       </c>
-      <c r="K48" s="105" t="n">
+      <c r="K48" s="113" t="n">
         <v>0.064</v>
       </c>
       <c r="L48" s="45" t="n">
@@ -14142,21 +17848,21 @@
         <v>0</v>
       </c>
       <c r="O48" s="21" t="s">
-        <v>1090</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="21" t="s">
-        <v>1177</v>
+        <v>1111</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>1178</v>
+        <v>1112</v>
       </c>
       <c r="C49" s="21" t="s">
         <v>361</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>1125</v>
+        <v>1052</v>
       </c>
       <c r="E49" s="21" t="n">
         <v>181</v>
@@ -14174,10 +17880,10 @@
       <c r="I49" s="28" t="n">
         <v>2133587</v>
       </c>
-      <c r="J49" s="92" t="n">
+      <c r="J49" s="100" t="n">
         <v>62.82</v>
       </c>
-      <c r="K49" s="105" t="n">
+      <c r="K49" s="113" t="n">
         <v>0.256</v>
       </c>
       <c r="L49" s="45" t="n">
@@ -14190,18 +17896,18 @@
         <v>0.201</v>
       </c>
       <c r="O49" s="21" t="s">
-        <v>1090</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="21" t="s">
-        <v>1179</v>
+        <v>1104</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>1180</v>
+        <v>1105</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D50" s="21" t="s">
         <v>868</v>
@@ -14222,7 +17928,7 @@
       <c r="I50" s="28" t="n">
         <v>1912969</v>
       </c>
-      <c r="J50" s="92" t="n">
+      <c r="J50" s="100" t="n">
         <v>52.46</v>
       </c>
       <c r="K50" s="57" t="n">
@@ -14238,18 +17944,18 @@
         <v>0</v>
       </c>
       <c r="O50" s="21" t="s">
-        <v>1095</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="21" t="s">
-        <v>1181</v>
+        <v>1107</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>1182</v>
+        <v>1108</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>1089</v>
+        <v>1024</v>
       </c>
       <c r="D51" s="21" t="s">
         <v>868</v>
@@ -14270,10 +17976,10 @@
       <c r="I51" s="28" t="n">
         <v>568922</v>
       </c>
-      <c r="J51" s="92" t="n">
+      <c r="J51" s="100" t="n">
         <v>50.9</v>
       </c>
-      <c r="K51" s="104" t="n">
+      <c r="K51" s="112" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="45" t="n">
@@ -14291,16 +17997,16 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="21" t="s">
-        <v>1183</v>
+        <v>1113</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>1184</v>
+        <v>1114</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>1094</v>
+        <v>1028</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>1125</v>
+        <v>1052</v>
       </c>
       <c r="E52" s="21" t="n">
         <v>181</v>
@@ -14318,10 +18024,10 @@
       <c r="I52" s="28" t="n">
         <v>1672588</v>
       </c>
-      <c r="J52" s="92" t="n">
+      <c r="J52" s="100" t="n">
         <v>45.95</v>
       </c>
-      <c r="K52" s="105" t="n">
+      <c r="K52" s="113" t="n">
         <v>0.137</v>
       </c>
       <c r="L52" s="45" t="n">
@@ -14334,12 +18040,12 @@
         <v>0.017</v>
       </c>
       <c r="O52" s="21" t="s">
-        <v>1101</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="21" t="s">
-        <v>1185</v>
+        <v>1116</v>
       </c>
       <c r="B53" s="16" t="s">
         <v>967</v>
@@ -14366,7 +18072,7 @@
       <c r="I53" s="28" t="n">
         <v>1601535</v>
       </c>
-      <c r="J53" s="92" t="n">
+      <c r="J53" s="100" t="n">
         <v>55.38</v>
       </c>
       <c r="K53" s="45" t="n">
@@ -14382,12 +18088,12 @@
         <v>0.292</v>
       </c>
       <c r="O53" s="21" t="s">
-        <v>1101</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="21" t="s">
-        <v>1186</v>
+        <v>1115</v>
       </c>
       <c r="B54" s="16" t="s">
         <v>969</v>
@@ -14414,7 +18120,7 @@
       <c r="I54" s="28" t="n">
         <v>1431054</v>
       </c>
-      <c r="J54" s="92" t="n">
+      <c r="J54" s="100" t="n">
         <v>53.68</v>
       </c>
       <c r="K54" s="45" t="n">
@@ -14430,21 +18136,21 @@
         <v>0.077</v>
       </c>
       <c r="O54" s="21" t="s">
-        <v>1090</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="21" t="s">
-        <v>1187</v>
+        <v>1117</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>1188</v>
+        <v>1118</v>
       </c>
       <c r="C55" s="21" t="s">
         <v>347</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>1125</v>
+        <v>1052</v>
       </c>
       <c r="E55" s="21" t="n">
         <v>181</v>
@@ -14462,10 +18168,10 @@
       <c r="I55" s="28" t="n">
         <v>1262094</v>
       </c>
-      <c r="J55" s="92" t="n">
+      <c r="J55" s="100" t="n">
         <v>53.3</v>
       </c>
-      <c r="K55" s="105" t="n">
+      <c r="K55" s="113" t="n">
         <v>0.188</v>
       </c>
       <c r="L55" s="45" t="n">
@@ -14478,15 +18184,15 @@
         <v>0.18</v>
       </c>
       <c r="O55" s="20" t="s">
-        <v>1098</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="21" t="s">
-        <v>1189</v>
+        <v>1119</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>1190</v>
+        <v>1120</v>
       </c>
       <c r="C56" s="21" t="s">
         <v>347</v>
@@ -14510,10 +18216,10 @@
       <c r="I56" s="28" t="n">
         <v>1204453</v>
       </c>
-      <c r="J56" s="92" t="n">
+      <c r="J56" s="100" t="n">
         <v>34.88</v>
       </c>
-      <c r="K56" s="105" t="n">
+      <c r="K56" s="113" t="n">
         <v>0.06</v>
       </c>
       <c r="L56" s="45" t="n">
@@ -14526,12 +18232,12 @@
         <v>0.194</v>
       </c>
       <c r="O56" s="21" t="s">
-        <v>1101</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="21" t="s">
-        <v>1191</v>
+        <v>1121</v>
       </c>
       <c r="B57" s="16" t="s">
         <v>344</v>
@@ -14558,10 +18264,10 @@
       <c r="I57" s="28" t="n">
         <v>206212</v>
       </c>
-      <c r="J57" s="92" t="n">
+      <c r="J57" s="100" t="n">
         <v>57.08</v>
       </c>
-      <c r="K57" s="104" t="n">
+      <c r="K57" s="112" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="45" t="n">
@@ -14574,18 +18280,18 @@
         <v>0.249</v>
       </c>
       <c r="O57" s="20" t="s">
-        <v>1098</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="21" t="s">
-        <v>1192</v>
+        <v>1122</v>
       </c>
       <c r="B58" s="16" t="s">
         <v>974</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>1193</v>
+        <v>1123</v>
       </c>
       <c r="D58" s="21" t="s">
         <v>866</v>
@@ -14606,10 +18312,10 @@
       <c r="I58" s="28" t="n">
         <v>21693</v>
       </c>
-      <c r="J58" s="92" t="n">
+      <c r="J58" s="100" t="n">
         <v>49.96</v>
       </c>
-      <c r="K58" s="104" t="n">
+      <c r="K58" s="112" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="45" t="n">
@@ -14622,51 +18328,51 @@
         <v>0.167</v>
       </c>
       <c r="O58" s="20" t="s">
-        <v>1098</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="67" t="s">
-        <v>1194</v>
+        <v>1238</v>
       </c>
       <c r="B59" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="F59" s="106" t="n">
+      <c r="F59" s="114" t="n">
         <f aca="false">SUM(F4:F58)</f>
         <v>502415662</v>
       </c>
-      <c r="G59" s="106" t="n">
+      <c r="G59" s="114" t="n">
         <f aca="false">SUM(G4:G58)</f>
         <v>1271395370.83428</v>
       </c>
-      <c r="H59" s="106" t="n">
+      <c r="H59" s="114" t="n">
         <f aca="false">SUM(H4:H58)</f>
         <v>8824895</v>
       </c>
-      <c r="I59" s="106" t="n">
+      <c r="I59" s="114" t="n">
         <f aca="false">SUM(I4:I58)</f>
         <v>219475297</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="107" t="s">
-        <v>1195</v>
-      </c>
-      <c r="B61" s="107"/>
-      <c r="C61" s="107"/>
-      <c r="D61" s="107"/>
-      <c r="E61" s="107"/>
-      <c r="F61" s="107"/>
-      <c r="G61" s="107"/>
-      <c r="H61" s="107"/>
-      <c r="I61" s="107"/>
-      <c r="J61" s="107"/>
-      <c r="K61" s="107"/>
-      <c r="L61" s="107"/>
-      <c r="M61" s="107"/>
-      <c r="N61" s="107"/>
-      <c r="O61" s="107"/>
+      <c r="A61" s="115" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B61" s="115"/>
+      <c r="C61" s="115"/>
+      <c r="D61" s="115"/>
+      <c r="E61" s="115"/>
+      <c r="F61" s="115"/>
+      <c r="G61" s="115"/>
+      <c r="H61" s="115"/>
+      <c r="I61" s="115"/>
+      <c r="J61" s="115"/>
+      <c r="K61" s="115"/>
+      <c r="L61" s="115"/>
+      <c r="M61" s="115"/>
+      <c r="N61" s="115"/>
+      <c r="O61" s="115"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/docs/executive-plan.xlsx
+++ b/docs/executive-plan.xlsx
@@ -20,10 +20,11 @@
     <sheet name="منفذ ١ — الوقود" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="تكلفة اللتر" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="مستهدفات البنزين" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="الخطة التنفيذية" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="المستهدفات الربعية" sheetId="14" state="visible" r:id="rId16"/>
-    <sheet name="المبادرات" sheetId="15" state="visible" r:id="rId17"/>
-    <sheet name="المحطات" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="العمالة والمضخات" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="الخطة التنفيذية" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="المستهدفات الربعية" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="المبادرات" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="المحطات" sheetId="17" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2116" uniqueCount="1240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2368" uniqueCount="1294">
   <si>
     <t xml:space="preserve">نموذج الخطة التنفيذية — الإدارة التجارية</t>
   </si>
@@ -124,18 +125,18 @@
     <t xml:space="preserve">صف مثال توضيحي — يُحذف قبل الاعتماد</t>
   </si>
   <si>
-    <t xml:space="preserve">حصص السوق</t>
+    <t xml:space="preserve">منفذ ٤ — الإكسسوارات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السوق واللاعبون وقرار التأجير مقابل التشغيل.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حالة المنفذ</t>
   </si>
   <si>
     <t xml:space="preserve">حصص محطات المملكة وأين نقف.</t>
   </si>
   <si>
-    <t xml:space="preserve">حالة المنفذ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تصنيف تطبيق أفراد · منصة شركات · بطاقة.</t>
-  </si>
-  <si>
     <t xml:space="preserve">قائم</t>
   </si>
   <si>
@@ -3449,6 +3450,168 @@
   </si>
   <si>
     <t xml:space="preserve">① معدلات الفئات الأربع (الخانات الصفراء) قرار إدارة لا حساب. ② الـ14 محطة «بلا بيانات» تحمل ثلث البنزين — ومستهدفاتها مؤقّتة حتى تكتمل بياناتها. ③ تشخيص تراجع مكة ما زال مفتوحاً: بلا معرفة السبب، هدف «تقليل النزيف» أمنية لا خطة.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العمالة والمضخات لكل محطة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52 محطة · بيانات التشغيل 29 يوليو 2026 · الإنتاجية محسوبة بالصيغ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التعاقد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المساحة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مضخات بنزين</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مضخات ديزل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إجمالي المضخات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">متفق عليه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الفارق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زيارة/عامل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زيارة/مضخة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ايجار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تغطية مبيعات ناقصة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العمرة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جدة النسيم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تشغيل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أبو وافي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الذكرى الخالدة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحليس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سلطان المطرفي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الرياض الدائري الشمالي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السواط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جعرانة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بطحاء قريش</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صبيا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الخرج الحمراء</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الاجاويد-جدة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الجموم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محايل عسير</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الرصيفة مسار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الجمعية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الخبر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الربوة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا بيانات مبيعات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الستين</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العرجاني الخرج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الملك خالد طائف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صامطة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الروابي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BH050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الاطاوله الباحه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الباحه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العمالة — مشكلة توزيع لا مشكلة إجمالي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">498 عاملاً فعلياً مقابل 475 متفقاً عليه = +23 فقط (+4.8%). لكن التوزيع هو المشكلة: 13 محطة زائدة و14 ناقصة و22 مطابقة. أكبر فائض في MK015 النسيم (+6)، وأكبر عجز في MK001 جبل النور و MK007 العمرة (−2 لكل منهما). أي أن إعادة التوزيع تسدّ العجز بلا توظيف جديد.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الإنتاجية تتفاوت ستة أضعاف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زيارة لكل عامل يومياً: من 31 (المركب) إلى 187 (جبل النور) — الوسيط 114. وزيارة لكل مضخة: من 26 إلى 468 — الوسيط 128. هذا التفاوت لا يُفسَّر بحجم المحطة وحده، وهو أول ما يجب مراجعته في أي خطة تشغيل.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔴 فرضية الازدحام — اختُبرت ورُفضت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بدا لأول وهلة أن الازدحام يفسّر التراجع: المحطات الهابطة وسيطها 157 زيارة/مضخة مقابل 106 للصاعدة — أي أزحم بـ48%. لكن بضبط الحجم انهار الفرق: بين المحطات الكبيرة، المزدحمة تتراجع 4.8% والمريحة 2.4% (فرق ضئيل)، وبين الصغيرة المزدحمة تنمو 2.8% والمريحة 0.6% — أي عكس الفرضية. والارتباط بين النمو والازدحام −0.185 فقط، بينما ارتباطه بحجم الزيارات −0.340 وهو أقوى. الخلاصة: الفارق الظاهر كان أثر حجم لا أثر ازدحام، و**زيادة المضخات ليست علاج التراجع**.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ما يبقى بعد رفض الفرضية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الإشارة الأقوى — رغم ضعفها — أن المحطات الأكبر هي التي تتراجع أكثر. وهذا يتسق مع فقدان حصة لمنافس يستهدف المواقع الكبيرة، لا مع قيد طاقة داخلي. والعيّنة 37 محطة فقط، فكل هذه الارتباطات إشارات لا براهين.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حدود البيانات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عمود «عدد المحلات التجارية» مملوء في 3 محطات فقط من 52 — غير قابل للاستخدام. وعمود «عمال الصيانة» نصّي لا رقمي («لجميع المحطات»). و«July Sales» مبيعات بالريال لا عدد معاملات رغم وقوعه في مجموعة Transactions. وخمسة أكواد صُحّحت بالمطابقة بالاسم، ومحطتان (MK257 الربوة · MK258 الستين) لا مقابل لهما في بيانات المبيعات — وقد تكونا محطتين جديدتين.</t>
   </si>
   <si>
     <t xml:space="preserve">الخطة التنفيذية لمنافذ البيع</t>
@@ -3761,7 +3924,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
@@ -3777,8 +3940,9 @@
     <numFmt numFmtId="176" formatCode="\+0.0000;\-0.0000"/>
     <numFmt numFmtId="177" formatCode="\+0.0%;\-0.0%"/>
     <numFmt numFmtId="178" formatCode="\+#,##0;\-#,##0"/>
-    <numFmt numFmtId="179" formatCode="#,##0.00"/>
-    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="\+0;\-0;0"/>
+    <numFmt numFmtId="180" formatCode="#,##0.00"/>
+    <numFmt numFmtId="181" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -4066,7 +4230,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="117">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4111,12 +4275,12 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -4455,6 +4619,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
@@ -4467,11 +4635,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="180" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="180" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4495,11 +4663,11 @@
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="180" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="180" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="181" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4507,7 +4675,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="180" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="181" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4945,15 +5113,15 @@
       <c r="B22" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="12" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4961,7 +5129,7 @@
       <c r="B24" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="12" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4969,7 +5137,7 @@
       <c r="B25" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="12" t="s">
         <v>42</v>
       </c>
     </row>
@@ -5771,7 +5939,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="12" t="s">
         <v>888</v>
       </c>
       <c r="C7" s="81"/>
@@ -5783,7 +5951,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>890</v>
       </c>
       <c r="C8" s="81"/>
@@ -5793,7 +5961,7 @@
       <c r="F8" s="26"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="12" t="s">
         <v>892</v>
       </c>
       <c r="C9" s="81"/>
@@ -5803,7 +5971,7 @@
       <c r="F9" s="26"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="12" t="s">
         <v>894</v>
       </c>
       <c r="C10" s="83"/>
@@ -5813,7 +5981,7 @@
       <c r="F10" s="26"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="12" t="s">
         <v>896</v>
       </c>
       <c r="C11" s="83"/>
@@ -5823,7 +5991,7 @@
       <c r="F11" s="26"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="12" t="s">
         <v>898</v>
       </c>
       <c r="C12" s="83"/>
@@ -5833,7 +6001,7 @@
       <c r="F12" s="26"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="12" t="s">
         <v>900</v>
       </c>
       <c r="C13" s="83"/>
@@ -5843,7 +6011,7 @@
       <c r="F13" s="26"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="12" t="s">
         <v>902</v>
       </c>
       <c r="C14" s="83"/>
@@ -5971,14 +6139,16 @@
       <c r="L18" s="28" t="n">
         <v>4236</v>
       </c>
-      <c r="M18" s="26"/>
+      <c r="M18" s="28" t="n">
+        <v>32</v>
+      </c>
       <c r="N18" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L18/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O18" s="84" t="str">
+      <c r="O18" s="84" t="n">
         <f aca="false">IFERROR(IF(M18="",N18,M18)*$C$12*181/30/D18,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P18" s="26"/>
       <c r="Q18" s="84" t="n">
@@ -5989,24 +6159,24 @@
         <f aca="false">IFERROR((G18/2)*(0.357*$C$7+0.362*$C$8+0.281*$C$9)*$C$10/(D18*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S18" s="86" t="str">
+      <c r="S18" s="86" t="n">
         <f aca="false">IFERROR((0.357*$C$7+0.362*$C$8+0.281*$C$9)/(1-$C$11)+K18+O18+Q18+R18,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T18" s="84" t="n">
         <v>1.9449</v>
       </c>
-      <c r="U18" s="86" t="str">
+      <c r="U18" s="86" t="n">
         <f aca="false">IFERROR(T18-S18,"")</f>
-        <v/>
-      </c>
-      <c r="V18" s="87" t="str">
+        <v>1.9449</v>
+      </c>
+      <c r="V18" s="87" t="n">
         <f aca="false">IFERROR(U18-$C$14,"")</f>
-        <v/>
+        <v>1.9449</v>
       </c>
       <c r="W18" s="21" t="str">
         <f aca="false">IF(U18="","",IF(U18&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6051,14 +6221,16 @@
       <c r="L19" s="28" t="n">
         <v>3561</v>
       </c>
-      <c r="M19" s="26"/>
+      <c r="M19" s="28" t="n">
+        <v>42</v>
+      </c>
       <c r="N19" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L19/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O19" s="84" t="str">
+      <c r="O19" s="84" t="n">
         <f aca="false">IFERROR(IF(M19="",N19,M19)*$C$12*181/30/D19,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P19" s="26"/>
       <c r="Q19" s="84" t="n">
@@ -6069,24 +6241,24 @@
         <f aca="false">IFERROR((G19/2)*(0.502*$C$7+0.498*$C$8+0*$C$9)*$C$10/(D19*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S19" s="86" t="str">
+      <c r="S19" s="86" t="n">
         <f aca="false">IFERROR((0.502*$C$7+0.498*$C$8+0*$C$9)/(1-$C$11)+K19+O19+Q19+R19,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T19" s="84" t="n">
         <v>2.2547</v>
       </c>
-      <c r="U19" s="86" t="str">
+      <c r="U19" s="86" t="n">
         <f aca="false">IFERROR(T19-S19,"")</f>
-        <v/>
-      </c>
-      <c r="V19" s="87" t="str">
+        <v>2.2547</v>
+      </c>
+      <c r="V19" s="87" t="n">
         <f aca="false">IFERROR(U19-$C$14,"")</f>
-        <v/>
+        <v>2.2547</v>
       </c>
       <c r="W19" s="21" t="str">
         <f aca="false">IF(U19="","",IF(U19&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6131,14 +6303,16 @@
       <c r="L20" s="28" t="n">
         <v>2137</v>
       </c>
-      <c r="M20" s="26"/>
+      <c r="M20" s="28" t="n">
+        <v>19</v>
+      </c>
       <c r="N20" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L20/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O20" s="84" t="str">
+      <c r="O20" s="84" t="n">
         <f aca="false">IFERROR(IF(M20="",N20,M20)*$C$12*181/30/D20,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P20" s="26"/>
       <c r="Q20" s="84" t="n">
@@ -6149,24 +6323,24 @@
         <f aca="false">IFERROR((G20/2)*(0.344*$C$7+0.312*$C$8+0.344*$C$9)*$C$10/(D20*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S20" s="86" t="str">
+      <c r="S20" s="86" t="n">
         <f aca="false">IFERROR((0.344*$C$7+0.312*$C$8+0.344*$C$9)/(1-$C$11)+K20+O20+Q20+R20,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T20" s="84" t="n">
         <v>1.8725</v>
       </c>
-      <c r="U20" s="86" t="str">
+      <c r="U20" s="86" t="n">
         <f aca="false">IFERROR(T20-S20,"")</f>
-        <v/>
-      </c>
-      <c r="V20" s="87" t="str">
+        <v>1.8725</v>
+      </c>
+      <c r="V20" s="87" t="n">
         <f aca="false">IFERROR(U20-$C$14,"")</f>
-        <v/>
+        <v>1.8725</v>
       </c>
       <c r="W20" s="21" t="str">
         <f aca="false">IF(U20="","",IF(U20&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6211,14 +6385,16 @@
       <c r="L21" s="28" t="n">
         <v>1643</v>
       </c>
-      <c r="M21" s="26"/>
+      <c r="M21" s="28" t="n">
+        <v>9</v>
+      </c>
       <c r="N21" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L21/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O21" s="84" t="str">
+      <c r="O21" s="84" t="n">
         <f aca="false">IFERROR(IF(M21="",N21,M21)*$C$12*181/30/D21,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P21" s="26"/>
       <c r="Q21" s="84" t="n">
@@ -6229,24 +6405,24 @@
         <f aca="false">IFERROR((G21/2)*(0.587*$C$7+0.413*$C$8+0*$C$9)*$C$10/(D21*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S21" s="86" t="str">
+      <c r="S21" s="86" t="n">
         <f aca="false">IFERROR((0.587*$C$7+0.413*$C$8+0*$C$9)/(1-$C$11)+K21+O21+Q21+R21,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T21" s="84" t="n">
         <v>2.242</v>
       </c>
-      <c r="U21" s="86" t="str">
+      <c r="U21" s="86" t="n">
         <f aca="false">IFERROR(T21-S21,"")</f>
-        <v/>
-      </c>
-      <c r="V21" s="87" t="str">
+        <v>2.242</v>
+      </c>
+      <c r="V21" s="87" t="n">
         <f aca="false">IFERROR(U21-$C$14,"")</f>
-        <v/>
+        <v>2.242</v>
       </c>
       <c r="W21" s="21" t="str">
         <f aca="false">IF(U21="","",IF(U21&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6291,14 +6467,16 @@
       <c r="L22" s="28" t="n">
         <v>2359</v>
       </c>
-      <c r="M22" s="26"/>
+      <c r="M22" s="28" t="n">
+        <v>14</v>
+      </c>
       <c r="N22" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L22/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O22" s="84" t="str">
+      <c r="O22" s="84" t="n">
         <f aca="false">IFERROR(IF(M22="",N22,M22)*$C$12*181/30/D22,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P22" s="26"/>
       <c r="Q22" s="84" t="n">
@@ -6309,24 +6487,24 @@
         <f aca="false">IFERROR((G22/2)*(0.635*$C$7+0.231*$C$8+0.134*$C$9)*$C$10/(D22*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S22" s="86" t="str">
+      <c r="S22" s="86" t="n">
         <f aca="false">IFERROR((0.635*$C$7+0.231*$C$8+0.134*$C$9)/(1-$C$11)+K22+O22+Q22+R22,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T22" s="84" t="n">
         <v>2.0766</v>
       </c>
-      <c r="U22" s="86" t="str">
+      <c r="U22" s="86" t="n">
         <f aca="false">IFERROR(T22-S22,"")</f>
-        <v/>
-      </c>
-      <c r="V22" s="87" t="str">
+        <v>2.0766</v>
+      </c>
+      <c r="V22" s="87" t="n">
         <f aca="false">IFERROR(U22-$C$14,"")</f>
-        <v/>
+        <v>2.0766</v>
       </c>
       <c r="W22" s="21" t="str">
         <f aca="false">IF(U22="","",IF(U22&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6371,14 +6549,16 @@
       <c r="L23" s="28" t="n">
         <v>1694</v>
       </c>
-      <c r="M23" s="26"/>
+      <c r="M23" s="28" t="n">
+        <v>12</v>
+      </c>
       <c r="N23" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L23/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O23" s="84" t="str">
+      <c r="O23" s="84" t="n">
         <f aca="false">IFERROR(IF(M23="",N23,M23)*$C$12*181/30/D23,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P23" s="26"/>
       <c r="Q23" s="84" t="n">
@@ -6389,24 +6569,24 @@
         <f aca="false">IFERROR((G23/2)*(0.381*$C$7+0.309*$C$8+0.309*$C$9)*$C$10/(D23*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S23" s="86" t="str">
+      <c r="S23" s="86" t="n">
         <f aca="false">IFERROR((0.381*$C$7+0.309*$C$8+0.309*$C$9)/(1-$C$11)+K23+O23+Q23+R23,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T23" s="84" t="n">
         <v>1.9059</v>
       </c>
-      <c r="U23" s="86" t="str">
+      <c r="U23" s="86" t="n">
         <f aca="false">IFERROR(T23-S23,"")</f>
-        <v/>
-      </c>
-      <c r="V23" s="87" t="str">
+        <v>1.9059</v>
+      </c>
+      <c r="V23" s="87" t="n">
         <f aca="false">IFERROR(U23-$C$14,"")</f>
-        <v/>
+        <v>1.9059</v>
       </c>
       <c r="W23" s="21" t="str">
         <f aca="false">IF(U23="","",IF(U23&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6451,14 +6631,16 @@
       <c r="L24" s="28" t="n">
         <v>1702</v>
       </c>
-      <c r="M24" s="26"/>
+      <c r="M24" s="28" t="n">
+        <v>10</v>
+      </c>
       <c r="N24" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L24/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O24" s="84" t="str">
+      <c r="O24" s="84" t="n">
         <f aca="false">IFERROR(IF(M24="",N24,M24)*$C$12*181/30/D24,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P24" s="26"/>
       <c r="Q24" s="84" t="n">
@@ -6469,24 +6651,24 @@
         <f aca="false">IFERROR((G24/2)*(0.354*$C$7+0.369*$C$8+0.277*$C$9)*$C$10/(D24*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S24" s="86" t="str">
+      <c r="S24" s="86" t="n">
         <f aca="false">IFERROR((0.354*$C$7+0.369*$C$8+0.277*$C$9)/(1-$C$11)+K24+O24+Q24+R24,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T24" s="84" t="n">
         <v>1.95</v>
       </c>
-      <c r="U24" s="86" t="str">
+      <c r="U24" s="86" t="n">
         <f aca="false">IFERROR(T24-S24,"")</f>
-        <v/>
-      </c>
-      <c r="V24" s="87" t="str">
+        <v>1.95</v>
+      </c>
+      <c r="V24" s="87" t="n">
         <f aca="false">IFERROR(U24-$C$14,"")</f>
-        <v/>
+        <v>1.95</v>
       </c>
       <c r="W24" s="21" t="str">
         <f aca="false">IF(U24="","",IF(U24&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6531,14 +6713,16 @@
       <c r="L25" s="28" t="n">
         <v>2041</v>
       </c>
-      <c r="M25" s="26"/>
+      <c r="M25" s="28" t="n">
+        <v>20</v>
+      </c>
       <c r="N25" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L25/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O25" s="84" t="str">
+      <c r="O25" s="84" t="n">
         <f aca="false">IFERROR(IF(M25="",N25,M25)*$C$12*181/30/D25,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P25" s="26"/>
       <c r="Q25" s="84" t="n">
@@ -6549,24 +6733,24 @@
         <f aca="false">IFERROR((G25/2)*(0.56*$C$7+0.429*$C$8+0*$C$9)*$C$10/(D25*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S25" s="86" t="str">
+      <c r="S25" s="86" t="n">
         <f aca="false">IFERROR((0.56*$C$7+0.429*$C$8+0*$C$9)/(1-$C$11)+K25+O25+Q25+R25,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T25" s="84" t="n">
         <v>2.2204</v>
       </c>
-      <c r="U25" s="86" t="str">
+      <c r="U25" s="86" t="n">
         <f aca="false">IFERROR(T25-S25,"")</f>
-        <v/>
-      </c>
-      <c r="V25" s="87" t="str">
+        <v>2.2204</v>
+      </c>
+      <c r="V25" s="87" t="n">
         <f aca="false">IFERROR(U25-$C$14,"")</f>
-        <v/>
+        <v>2.2204</v>
       </c>
       <c r="W25" s="21" t="str">
         <f aca="false">IF(U25="","",IF(U25&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6611,14 +6795,16 @@
       <c r="L26" s="28" t="n">
         <v>1726</v>
       </c>
-      <c r="M26" s="26"/>
+      <c r="M26" s="28" t="n">
+        <v>18</v>
+      </c>
       <c r="N26" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L26/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O26" s="84" t="str">
+      <c r="O26" s="84" t="n">
         <f aca="false">IFERROR(IF(M26="",N26,M26)*$C$12*181/30/D26,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P26" s="26"/>
       <c r="Q26" s="84" t="n">
@@ -6629,24 +6815,24 @@
         <f aca="false">IFERROR((G26/2)*(0.526*$C$7+0.468*$C$8+0.006*$C$9)*$C$10/(D26*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S26" s="86" t="str">
+      <c r="S26" s="86" t="n">
         <f aca="false">IFERROR((0.526*$C$7+0.468*$C$8+0.006*$C$9)/(1-$C$11)+K26+O26+Q26+R26,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T26" s="84" t="n">
         <v>2.244</v>
       </c>
-      <c r="U26" s="86" t="str">
+      <c r="U26" s="86" t="n">
         <f aca="false">IFERROR(T26-S26,"")</f>
-        <v/>
-      </c>
-      <c r="V26" s="87" t="str">
+        <v>2.244</v>
+      </c>
+      <c r="V26" s="87" t="n">
         <f aca="false">IFERROR(U26-$C$14,"")</f>
-        <v/>
+        <v>2.244</v>
       </c>
       <c r="W26" s="21" t="str">
         <f aca="false">IF(U26="","",IF(U26&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6691,14 +6877,16 @@
       <c r="L27" s="28" t="n">
         <v>1566</v>
       </c>
-      <c r="M27" s="26"/>
+      <c r="M27" s="28" t="n">
+        <v>12</v>
+      </c>
       <c r="N27" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L27/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O27" s="84" t="str">
+      <c r="O27" s="84" t="n">
         <f aca="false">IFERROR(IF(M27="",N27,M27)*$C$12*181/30/D27,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P27" s="26"/>
       <c r="Q27" s="84" t="n">
@@ -6709,24 +6897,24 @@
         <f aca="false">IFERROR((G27/2)*(0.406*$C$7+0.364*$C$8+0.231*$C$9)*$C$10/(D27*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S27" s="86" t="str">
+      <c r="S27" s="86" t="n">
         <f aca="false">IFERROR((0.406*$C$7+0.364*$C$8+0.231*$C$9)/(1-$C$11)+K27+O27+Q27+R27,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T27" s="84" t="n">
         <v>1.9989</v>
       </c>
-      <c r="U27" s="86" t="str">
+      <c r="U27" s="86" t="n">
         <f aca="false">IFERROR(T27-S27,"")</f>
-        <v/>
-      </c>
-      <c r="V27" s="87" t="str">
+        <v>1.9989</v>
+      </c>
+      <c r="V27" s="87" t="n">
         <f aca="false">IFERROR(U27-$C$14,"")</f>
-        <v/>
+        <v>1.9989</v>
       </c>
       <c r="W27" s="21" t="str">
         <f aca="false">IF(U27="","",IF(U27&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6771,14 +6959,16 @@
       <c r="L28" s="28" t="n">
         <v>1414</v>
       </c>
-      <c r="M28" s="26"/>
+      <c r="M28" s="28" t="n">
+        <v>13</v>
+      </c>
       <c r="N28" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L28/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O28" s="84" t="str">
+      <c r="O28" s="84" t="n">
         <f aca="false">IFERROR(IF(M28="",N28,M28)*$C$12*181/30/D28,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P28" s="26"/>
       <c r="Q28" s="84" t="n">
@@ -6789,24 +6979,24 @@
         <f aca="false">IFERROR((G28/2)*(0.465*$C$7+0.453*$C$8+0.082*$C$9)*$C$10/(D28*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S28" s="86" t="str">
+      <c r="S28" s="86" t="n">
         <f aca="false">IFERROR((0.465*$C$7+0.453*$C$8+0.082*$C$9)/(1-$C$11)+K28+O28+Q28+R28,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T28" s="84" t="n">
         <v>2.1635</v>
       </c>
-      <c r="U28" s="86" t="str">
+      <c r="U28" s="86" t="n">
         <f aca="false">IFERROR(T28-S28,"")</f>
-        <v/>
-      </c>
-      <c r="V28" s="87" t="str">
+        <v>2.1635</v>
+      </c>
+      <c r="V28" s="87" t="n">
         <f aca="false">IFERROR(U28-$C$14,"")</f>
-        <v/>
+        <v>2.1635</v>
       </c>
       <c r="W28" s="21" t="str">
         <f aca="false">IF(U28="","",IF(U28&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6851,14 +7041,16 @@
       <c r="L29" s="28" t="n">
         <v>1380</v>
       </c>
-      <c r="M29" s="26"/>
+      <c r="M29" s="28" t="n">
+        <v>13</v>
+      </c>
       <c r="N29" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L29/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O29" s="84" t="str">
+      <c r="O29" s="84" t="n">
         <f aca="false">IFERROR(IF(M29="",N29,M29)*$C$12*181/30/D29,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P29" s="26"/>
       <c r="Q29" s="84" t="n">
@@ -6869,24 +7061,24 @@
         <f aca="false">IFERROR((G29/2)*(0.337*$C$7+0.206*$C$8+0.458*$C$9)*$C$10/(D29*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S29" s="86" t="str">
+      <c r="S29" s="86" t="n">
         <f aca="false">IFERROR((0.337*$C$7+0.206*$C$8+0.458*$C$9)/(1-$C$11)+K29+O29+Q29+R29,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T29" s="84" t="n">
         <v>1.7413</v>
       </c>
-      <c r="U29" s="86" t="str">
+      <c r="U29" s="86" t="n">
         <f aca="false">IFERROR(T29-S29,"")</f>
-        <v/>
-      </c>
-      <c r="V29" s="87" t="str">
+        <v>1.7413</v>
+      </c>
+      <c r="V29" s="87" t="n">
         <f aca="false">IFERROR(U29-$C$14,"")</f>
-        <v/>
+        <v>1.7413</v>
       </c>
       <c r="W29" s="21" t="str">
         <f aca="false">IF(U29="","",IF(U29&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6931,14 +7123,16 @@
       <c r="L30" s="28" t="n">
         <v>1169</v>
       </c>
-      <c r="M30" s="26"/>
+      <c r="M30" s="28" t="n">
+        <v>10</v>
+      </c>
       <c r="N30" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L30/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O30" s="84" t="str">
+      <c r="O30" s="84" t="n">
         <f aca="false">IFERROR(IF(M30="",N30,M30)*$C$12*181/30/D30,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P30" s="26"/>
       <c r="Q30" s="84" t="n">
@@ -6949,24 +7143,24 @@
         <f aca="false">IFERROR((G30/2)*(0.474*$C$7+0.451*$C$8+0.076*$C$9)*$C$10/(D30*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S30" s="86" t="str">
+      <c r="S30" s="86" t="n">
         <f aca="false">IFERROR((0.474*$C$7+0.451*$C$8+0.076*$C$9)/(1-$C$11)+K30+O30+Q30+R30,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T30" s="84" t="n">
         <v>2.1716</v>
       </c>
-      <c r="U30" s="86" t="str">
+      <c r="U30" s="86" t="n">
         <f aca="false">IFERROR(T30-S30,"")</f>
-        <v/>
-      </c>
-      <c r="V30" s="87" t="str">
+        <v>2.1716</v>
+      </c>
+      <c r="V30" s="87" t="n">
         <f aca="false">IFERROR(U30-$C$14,"")</f>
-        <v/>
+        <v>2.1716</v>
       </c>
       <c r="W30" s="21" t="str">
         <f aca="false">IF(U30="","",IF(U30&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7011,14 +7205,16 @@
       <c r="L31" s="28" t="n">
         <v>1872</v>
       </c>
-      <c r="M31" s="26"/>
+      <c r="M31" s="28" t="n">
+        <v>10</v>
+      </c>
       <c r="N31" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L31/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O31" s="84" t="str">
+      <c r="O31" s="84" t="n">
         <f aca="false">IFERROR(IF(M31="",N31,M31)*$C$12*181/30/D31,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P31" s="26"/>
       <c r="Q31" s="84" t="n">
@@ -7029,24 +7225,24 @@
         <f aca="false">IFERROR((G31/2)*(0.554*$C$7+0.446*$C$8+0*$C$9)*$C$10/(D31*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S31" s="86" t="str">
+      <c r="S31" s="86" t="n">
         <f aca="false">IFERROR((0.554*$C$7+0.446*$C$8+0*$C$9)/(1-$C$11)+K31+O31+Q31+R31,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T31" s="84" t="n">
         <v>2.2469</v>
       </c>
-      <c r="U31" s="86" t="str">
+      <c r="U31" s="86" t="n">
         <f aca="false">IFERROR(T31-S31,"")</f>
-        <v/>
-      </c>
-      <c r="V31" s="87" t="str">
+        <v>2.2469</v>
+      </c>
+      <c r="V31" s="87" t="n">
         <f aca="false">IFERROR(U31-$C$14,"")</f>
-        <v/>
+        <v>2.2469</v>
       </c>
       <c r="W31" s="21" t="str">
         <f aca="false">IF(U31="","",IF(U31&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7091,14 +7287,16 @@
       <c r="L32" s="28" t="n">
         <v>1483</v>
       </c>
-      <c r="M32" s="26"/>
+      <c r="M32" s="28" t="n">
+        <v>13</v>
+      </c>
       <c r="N32" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L32/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O32" s="84" t="str">
+      <c r="O32" s="84" t="n">
         <f aca="false">IFERROR(IF(M32="",N32,M32)*$C$12*181/30/D32,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P32" s="26"/>
       <c r="Q32" s="84" t="n">
@@ -7109,24 +7307,24 @@
         <f aca="false">IFERROR((G32/2)*(0.544*$C$7+0.456*$C$8+0*$C$9)*$C$10/(D32*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S32" s="86" t="str">
+      <c r="S32" s="86" t="n">
         <f aca="false">IFERROR((0.544*$C$7+0.456*$C$8+0*$C$9)/(1-$C$11)+K32+O32+Q32+R32,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T32" s="84" t="n">
         <v>2.2484</v>
       </c>
-      <c r="U32" s="86" t="str">
+      <c r="U32" s="86" t="n">
         <f aca="false">IFERROR(T32-S32,"")</f>
-        <v/>
-      </c>
-      <c r="V32" s="87" t="str">
+        <v>2.2484</v>
+      </c>
+      <c r="V32" s="87" t="n">
         <f aca="false">IFERROR(U32-$C$14,"")</f>
-        <v/>
+        <v>2.2484</v>
       </c>
       <c r="W32" s="21" t="str">
         <f aca="false">IF(U32="","",IF(U32&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7171,14 +7369,16 @@
       <c r="L33" s="28" t="n">
         <v>1573</v>
       </c>
-      <c r="M33" s="26"/>
+      <c r="M33" s="28" t="n">
+        <v>11</v>
+      </c>
       <c r="N33" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L33/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O33" s="84" t="str">
+      <c r="O33" s="84" t="n">
         <f aca="false">IFERROR(IF(M33="",N33,M33)*$C$12*181/30/D33,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P33" s="26"/>
       <c r="Q33" s="84" t="n">
@@ -7189,24 +7389,24 @@
         <f aca="false">IFERROR((G33/2)*(0.575*$C$7+0.425*$C$8+0*$C$9)*$C$10/(D33*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S33" s="86" t="str">
+      <c r="S33" s="86" t="n">
         <f aca="false">IFERROR((0.575*$C$7+0.425*$C$8+0*$C$9)/(1-$C$11)+K33+O33+Q33+R33,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T33" s="84" t="n">
         <v>2.2437</v>
       </c>
-      <c r="U33" s="86" t="str">
+      <c r="U33" s="86" t="n">
         <f aca="false">IFERROR(T33-S33,"")</f>
-        <v/>
-      </c>
-      <c r="V33" s="87" t="str">
+        <v>2.2437</v>
+      </c>
+      <c r="V33" s="87" t="n">
         <f aca="false">IFERROR(U33-$C$14,"")</f>
-        <v/>
+        <v>2.2437</v>
       </c>
       <c r="W33" s="21" t="str">
         <f aca="false">IF(U33="","",IF(U33&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7251,14 +7451,16 @@
       <c r="L34" s="28" t="n">
         <v>1112</v>
       </c>
-      <c r="M34" s="26"/>
+      <c r="M34" s="28" t="n">
+        <v>9</v>
+      </c>
       <c r="N34" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L34/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O34" s="84" t="str">
+      <c r="O34" s="84" t="n">
         <f aca="false">IFERROR(IF(M34="",N34,M34)*$C$12*181/30/D34,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P34" s="26"/>
       <c r="Q34" s="84" t="n">
@@ -7269,24 +7471,24 @@
         <f aca="false">IFERROR((G34/2)*(0.372*$C$7+0.351*$C$8+0.276*$C$9)*$C$10/(D34*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S34" s="86" t="str">
+      <c r="S34" s="86" t="n">
         <f aca="false">IFERROR((0.372*$C$7+0.351*$C$8+0.276*$C$9)/(1-$C$11)+K34+O34+Q34+R34,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T34" s="84" t="n">
         <v>1.9462</v>
       </c>
-      <c r="U34" s="86" t="str">
+      <c r="U34" s="86" t="n">
         <f aca="false">IFERROR(T34-S34,"")</f>
-        <v/>
-      </c>
-      <c r="V34" s="87" t="str">
+        <v>1.9462</v>
+      </c>
+      <c r="V34" s="87" t="n">
         <f aca="false">IFERROR(U34-$C$14,"")</f>
-        <v/>
+        <v>1.9462</v>
       </c>
       <c r="W34" s="21" t="str">
         <f aca="false">IF(U34="","",IF(U34&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7331,14 +7533,16 @@
       <c r="L35" s="28" t="n">
         <v>1144</v>
       </c>
-      <c r="M35" s="26"/>
+      <c r="M35" s="28" t="n">
+        <v>9</v>
+      </c>
       <c r="N35" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L35/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O35" s="84" t="str">
+      <c r="O35" s="84" t="n">
         <f aca="false">IFERROR(IF(M35="",N35,M35)*$C$12*181/30/D35,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P35" s="26"/>
       <c r="Q35" s="84" t="n">
@@ -7349,24 +7553,24 @@
         <f aca="false">IFERROR((G35/2)*(0.461*$C$7+0.481*$C$8+0.058*$C$9)*$C$10/(D35*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S35" s="86" t="str">
+      <c r="S35" s="86" t="n">
         <f aca="false">IFERROR((0.461*$C$7+0.481*$C$8+0.058*$C$9)/(1-$C$11)+K35+O35+Q35+R35,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T35" s="84" t="n">
         <v>2.1924</v>
       </c>
-      <c r="U35" s="86" t="str">
+      <c r="U35" s="86" t="n">
         <f aca="false">IFERROR(T35-S35,"")</f>
-        <v/>
-      </c>
-      <c r="V35" s="87" t="str">
+        <v>2.1924</v>
+      </c>
+      <c r="V35" s="87" t="n">
         <f aca="false">IFERROR(U35-$C$14,"")</f>
-        <v/>
+        <v>2.1924</v>
       </c>
       <c r="W35" s="21" t="str">
         <f aca="false">IF(U35="","",IF(U35&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7411,14 +7615,16 @@
       <c r="L36" s="28" t="n">
         <v>1363</v>
       </c>
-      <c r="M36" s="26"/>
+      <c r="M36" s="28" t="n">
+        <v>9</v>
+      </c>
       <c r="N36" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L36/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O36" s="84" t="str">
+      <c r="O36" s="84" t="n">
         <f aca="false">IFERROR(IF(M36="",N36,M36)*$C$12*181/30/D36,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P36" s="26"/>
       <c r="Q36" s="84" t="n">
@@ -7429,24 +7635,24 @@
         <f aca="false">IFERROR((G36/2)*(0.522*$C$7+0.478*$C$8+0*$C$9)*$C$10/(D36*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S36" s="86" t="str">
+      <c r="S36" s="86" t="n">
         <f aca="false">IFERROR((0.522*$C$7+0.478*$C$8+0*$C$9)/(1-$C$11)+K36+O36+Q36+R36,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T36" s="84" t="n">
         <v>2.2517</v>
       </c>
-      <c r="U36" s="86" t="str">
+      <c r="U36" s="86" t="n">
         <f aca="false">IFERROR(T36-S36,"")</f>
-        <v/>
-      </c>
-      <c r="V36" s="87" t="str">
+        <v>2.2517</v>
+      </c>
+      <c r="V36" s="87" t="n">
         <f aca="false">IFERROR(U36-$C$14,"")</f>
-        <v/>
+        <v>2.2517</v>
       </c>
       <c r="W36" s="21" t="str">
         <f aca="false">IF(U36="","",IF(U36&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7491,14 +7697,16 @@
       <c r="L37" s="28" t="n">
         <v>1290</v>
       </c>
-      <c r="M37" s="26"/>
+      <c r="M37" s="28" t="n">
+        <v>9</v>
+      </c>
       <c r="N37" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L37/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O37" s="84" t="str">
+      <c r="O37" s="84" t="n">
         <f aca="false">IFERROR(IF(M37="",N37,M37)*$C$12*181/30/D37,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P37" s="26"/>
       <c r="Q37" s="84" t="n">
@@ -7509,24 +7717,24 @@
         <f aca="false">IFERROR((G37/2)*(0.517*$C$7+0.483*$C$8+0*$C$9)*$C$10/(D37*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S37" s="86" t="str">
+      <c r="S37" s="86" t="n">
         <f aca="false">IFERROR((0.517*$C$7+0.483*$C$8+0*$C$9)/(1-$C$11)+K37+O37+Q37+R37,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T37" s="84" t="n">
         <v>2.2525</v>
       </c>
-      <c r="U37" s="86" t="str">
+      <c r="U37" s="86" t="n">
         <f aca="false">IFERROR(T37-S37,"")</f>
-        <v/>
-      </c>
-      <c r="V37" s="87" t="str">
+        <v>2.2525</v>
+      </c>
+      <c r="V37" s="87" t="n">
         <f aca="false">IFERROR(U37-$C$14,"")</f>
-        <v/>
+        <v>2.2525</v>
       </c>
       <c r="W37" s="21" t="str">
         <f aca="false">IF(U37="","",IF(U37&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7571,14 +7779,16 @@
       <c r="L38" s="28" t="n">
         <v>823</v>
       </c>
-      <c r="M38" s="26"/>
+      <c r="M38" s="28" t="n">
+        <v>6</v>
+      </c>
       <c r="N38" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L38/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O38" s="84" t="str">
+      <c r="O38" s="84" t="n">
         <f aca="false">IFERROR(IF(M38="",N38,M38)*$C$12*181/30/D38,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P38" s="26"/>
       <c r="Q38" s="84" t="n">
@@ -7589,24 +7799,24 @@
         <f aca="false">IFERROR((G38/2)*(0.374*$C$7+0.356*$C$8+0.27*$C$9)*$C$10/(D38*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S38" s="86" t="str">
+      <c r="S38" s="86" t="n">
         <f aca="false">IFERROR((0.374*$C$7+0.356*$C$8+0.27*$C$9)/(1-$C$11)+K38+O38+Q38+R38,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T38" s="84" t="n">
         <v>1.9553</v>
       </c>
-      <c r="U38" s="86" t="str">
+      <c r="U38" s="86" t="n">
         <f aca="false">IFERROR(T38-S38,"")</f>
-        <v/>
-      </c>
-      <c r="V38" s="87" t="str">
+        <v>1.9553</v>
+      </c>
+      <c r="V38" s="87" t="n">
         <f aca="false">IFERROR(U38-$C$14,"")</f>
-        <v/>
+        <v>1.9553</v>
       </c>
       <c r="W38" s="21" t="str">
         <f aca="false">IF(U38="","",IF(U38&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7651,14 +7861,16 @@
       <c r="L39" s="28" t="n">
         <v>816</v>
       </c>
-      <c r="M39" s="26"/>
+      <c r="M39" s="28" t="n">
+        <v>8</v>
+      </c>
       <c r="N39" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L39/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O39" s="84" t="str">
+      <c r="O39" s="84" t="n">
         <f aca="false">IFERROR(IF(M39="",N39,M39)*$C$12*181/30/D39,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P39" s="26"/>
       <c r="Q39" s="84" t="n">
@@ -7669,24 +7881,24 @@
         <f aca="false">IFERROR((G39/2)*(0.364*$C$7+0.315*$C$8+0.321*$C$9)*$C$10/(D39*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S39" s="86" t="str">
+      <c r="S39" s="86" t="n">
         <f aca="false">IFERROR((0.364*$C$7+0.315*$C$8+0.321*$C$9)/(1-$C$11)+K39+O39+Q39+R39,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T39" s="84" t="n">
         <v>1.8966</v>
       </c>
-      <c r="U39" s="86" t="str">
+      <c r="U39" s="86" t="n">
         <f aca="false">IFERROR(T39-S39,"")</f>
-        <v/>
-      </c>
-      <c r="V39" s="87" t="str">
+        <v>1.8966</v>
+      </c>
+      <c r="V39" s="87" t="n">
         <f aca="false">IFERROR(U39-$C$14,"")</f>
-        <v/>
+        <v>1.8966</v>
       </c>
       <c r="W39" s="21" t="str">
         <f aca="false">IF(U39="","",IF(U39&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7731,14 +7943,16 @@
       <c r="L40" s="28" t="n">
         <v>1025</v>
       </c>
-      <c r="M40" s="26"/>
+      <c r="M40" s="28" t="n">
+        <v>6</v>
+      </c>
       <c r="N40" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L40/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O40" s="84" t="str">
+      <c r="O40" s="84" t="n">
         <f aca="false">IFERROR(IF(M40="",N40,M40)*$C$12*181/30/D40,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P40" s="26"/>
       <c r="Q40" s="84" t="n">
@@ -7749,24 +7963,24 @@
         <f aca="false">IFERROR((G40/2)*(0.514*$C$7+0.31*$C$8+0.176*$C$9)*$C$10/(D40*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S40" s="86" t="str">
+      <c r="S40" s="86" t="n">
         <f aca="false">IFERROR((0.514*$C$7+0.31*$C$8+0.176*$C$9)/(1-$C$11)+K40+O40+Q40+R40,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T40" s="84" t="n">
         <v>2.0452</v>
       </c>
-      <c r="U40" s="86" t="str">
+      <c r="U40" s="86" t="n">
         <f aca="false">IFERROR(T40-S40,"")</f>
-        <v/>
-      </c>
-      <c r="V40" s="87" t="str">
+        <v>2.0452</v>
+      </c>
+      <c r="V40" s="87" t="n">
         <f aca="false">IFERROR(U40-$C$14,"")</f>
-        <v/>
+        <v>2.0452</v>
       </c>
       <c r="W40" s="21" t="str">
         <f aca="false">IF(U40="","",IF(U40&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7811,14 +8025,16 @@
       <c r="L41" s="28" t="n">
         <v>423</v>
       </c>
-      <c r="M41" s="26"/>
+      <c r="M41" s="28" t="n">
+        <v>9</v>
+      </c>
       <c r="N41" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L41/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O41" s="84" t="str">
+      <c r="O41" s="84" t="n">
         <f aca="false">IFERROR(IF(M41="",N41,M41)*$C$12*181/30/D41,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P41" s="26"/>
       <c r="Q41" s="84" t="n">
@@ -7829,24 +8045,24 @@
         <f aca="false">IFERROR((G41/2)*(0.243*$C$7+0.198*$C$8+0.559*$C$9)*$C$10/(D41*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S41" s="86" t="str">
+      <c r="S41" s="86" t="n">
         <f aca="false">IFERROR((0.243*$C$7+0.198*$C$8+0.559*$C$9)/(1-$C$11)+K41+O41+Q41+R41,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T41" s="84" t="n">
         <v>1.6339</v>
       </c>
-      <c r="U41" s="86" t="str">
+      <c r="U41" s="86" t="n">
         <f aca="false">IFERROR(T41-S41,"")</f>
-        <v/>
-      </c>
-      <c r="V41" s="87" t="str">
+        <v>1.6339</v>
+      </c>
+      <c r="V41" s="87" t="n">
         <f aca="false">IFERROR(U41-$C$14,"")</f>
-        <v/>
+        <v>1.6339</v>
       </c>
       <c r="W41" s="21" t="str">
         <f aca="false">IF(U41="","",IF(U41&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7891,14 +8107,16 @@
       <c r="L42" s="28" t="n">
         <v>864</v>
       </c>
-      <c r="M42" s="26"/>
+      <c r="M42" s="28" t="n">
+        <v>7</v>
+      </c>
       <c r="N42" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L42/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O42" s="84" t="str">
+      <c r="O42" s="84" t="n">
         <f aca="false">IFERROR(IF(M42="",N42,M42)*$C$12*181/30/D42,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P42" s="26"/>
       <c r="Q42" s="84" t="n">
@@ -7909,24 +8127,24 @@
         <f aca="false">IFERROR((G42/2)*(0.468*$C$7+0.45*$C$8+0.082*$C$9)*$C$10/(D42*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S42" s="86" t="str">
+      <c r="S42" s="86" t="n">
         <f aca="false">IFERROR((0.468*$C$7+0.45*$C$8+0.082*$C$9)/(1-$C$11)+K42+O42+Q42+R42,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T42" s="84" t="n">
         <v>2.163</v>
       </c>
-      <c r="U42" s="86" t="str">
+      <c r="U42" s="86" t="n">
         <f aca="false">IFERROR(T42-S42,"")</f>
-        <v/>
-      </c>
-      <c r="V42" s="87" t="str">
+        <v>2.163</v>
+      </c>
+      <c r="V42" s="87" t="n">
         <f aca="false">IFERROR(U42-$C$14,"")</f>
-        <v/>
+        <v>2.163</v>
       </c>
       <c r="W42" s="21" t="str">
         <f aca="false">IF(U42="","",IF(U42&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7971,14 +8189,16 @@
       <c r="L43" s="28" t="n">
         <v>922</v>
       </c>
-      <c r="M43" s="26"/>
+      <c r="M43" s="28" t="n">
+        <v>8</v>
+      </c>
       <c r="N43" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L43/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O43" s="84" t="str">
+      <c r="O43" s="84" t="n">
         <f aca="false">IFERROR(IF(M43="",N43,M43)*$C$12*181/30/D43,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P43" s="26"/>
       <c r="Q43" s="84" t="n">
@@ -7989,24 +8209,24 @@
         <f aca="false">IFERROR((G43/2)*(0.434*$C$7+0.544*$C$8+0.023*$C$9)*$C$10/(D43*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S43" s="86" t="str">
+      <c r="S43" s="86" t="n">
         <f aca="false">IFERROR((0.434*$C$7+0.544*$C$8+0.023*$C$9)/(1-$C$11)+K43+O43+Q43+R43,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T43" s="84" t="n">
         <v>2.2401</v>
       </c>
-      <c r="U43" s="86" t="str">
+      <c r="U43" s="86" t="n">
         <f aca="false">IFERROR(T43-S43,"")</f>
-        <v/>
-      </c>
-      <c r="V43" s="87" t="str">
+        <v>2.2401</v>
+      </c>
+      <c r="V43" s="87" t="n">
         <f aca="false">IFERROR(U43-$C$14,"")</f>
-        <v/>
+        <v>2.2401</v>
       </c>
       <c r="W43" s="21" t="str">
         <f aca="false">IF(U43="","",IF(U43&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8051,14 +8271,16 @@
       <c r="L44" s="28" t="n">
         <v>931</v>
       </c>
-      <c r="M44" s="26"/>
+      <c r="M44" s="28" t="n">
+        <v>7</v>
+      </c>
       <c r="N44" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L44/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O44" s="84" t="str">
+      <c r="O44" s="84" t="n">
         <f aca="false">IFERROR(IF(M44="",N44,M44)*$C$12*181/30/D44,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P44" s="26"/>
       <c r="Q44" s="84" t="n">
@@ -8069,24 +8291,24 @@
         <f aca="false">IFERROR((G44/2)*(0.416*$C$7+0.469*$C$8+0.115*$C$9)*$C$10/(D44*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S44" s="86" t="str">
+      <c r="S44" s="86" t="n">
         <f aca="false">IFERROR((0.416*$C$7+0.469*$C$8+0.115*$C$9)/(1-$C$11)+K44+O44+Q44+R44,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T44" s="84" t="n">
         <v>2.1319</v>
       </c>
-      <c r="U44" s="86" t="str">
+      <c r="U44" s="86" t="n">
         <f aca="false">IFERROR(T44-S44,"")</f>
-        <v/>
-      </c>
-      <c r="V44" s="87" t="str">
+        <v>2.1319</v>
+      </c>
+      <c r="V44" s="87" t="n">
         <f aca="false">IFERROR(U44-$C$14,"")</f>
-        <v/>
+        <v>2.1319</v>
       </c>
       <c r="W44" s="21" t="str">
         <f aca="false">IF(U44="","",IF(U44&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8131,14 +8353,16 @@
       <c r="L45" s="28" t="n">
         <v>913</v>
       </c>
-      <c r="M45" s="26"/>
+      <c r="M45" s="28" t="n">
+        <v>7</v>
+      </c>
       <c r="N45" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L45/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O45" s="84" t="str">
+      <c r="O45" s="84" t="n">
         <f aca="false">IFERROR(IF(M45="",N45,M45)*$C$12*181/30/D45,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P45" s="26"/>
       <c r="Q45" s="84" t="n">
@@ -8149,24 +8373,24 @@
         <f aca="false">IFERROR((G45/2)*(0.561*$C$7+0.439*$C$8+0*$C$9)*$C$10/(D45*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S45" s="86" t="str">
+      <c r="S45" s="86" t="n">
         <f aca="false">IFERROR((0.561*$C$7+0.439*$C$8+0*$C$9)/(1-$C$11)+K45+O45+Q45+R45,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T45" s="84" t="n">
         <v>2.2458</v>
       </c>
-      <c r="U45" s="86" t="str">
+      <c r="U45" s="86" t="n">
         <f aca="false">IFERROR(T45-S45,"")</f>
-        <v/>
-      </c>
-      <c r="V45" s="87" t="str">
+        <v>2.2458</v>
+      </c>
+      <c r="V45" s="87" t="n">
         <f aca="false">IFERROR(U45-$C$14,"")</f>
-        <v/>
+        <v>2.2458</v>
       </c>
       <c r="W45" s="21" t="str">
         <f aca="false">IF(U45="","",IF(U45&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8211,14 +8435,16 @@
       <c r="L46" s="28" t="n">
         <v>938</v>
       </c>
-      <c r="M46" s="26"/>
+      <c r="M46" s="28" t="n">
+        <v>7</v>
+      </c>
       <c r="N46" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L46/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O46" s="84" t="str">
+      <c r="O46" s="84" t="n">
         <f aca="false">IFERROR(IF(M46="",N46,M46)*$C$12*181/30/D46,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P46" s="26"/>
       <c r="Q46" s="84" t="n">
@@ -8229,24 +8455,24 @@
         <f aca="false">IFERROR((G46/2)*(0.523*$C$7+0.31*$C$8+0.167*$C$9)*$C$10/(D46*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S46" s="86" t="str">
+      <c r="S46" s="86" t="n">
         <f aca="false">IFERROR((0.523*$C$7+0.31*$C$8+0.167*$C$9)/(1-$C$11)+K46+O46+Q46+R46,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T46" s="84" t="n">
         <v>2.0545</v>
       </c>
-      <c r="U46" s="86" t="str">
+      <c r="U46" s="86" t="n">
         <f aca="false">IFERROR(T46-S46,"")</f>
-        <v/>
-      </c>
-      <c r="V46" s="87" t="str">
+        <v>2.0545</v>
+      </c>
+      <c r="V46" s="87" t="n">
         <f aca="false">IFERROR(U46-$C$14,"")</f>
-        <v/>
+        <v>2.0545</v>
       </c>
       <c r="W46" s="21" t="str">
         <f aca="false">IF(U46="","",IF(U46&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8291,14 +8517,16 @@
       <c r="L47" s="28" t="n">
         <v>538</v>
       </c>
-      <c r="M47" s="26"/>
+      <c r="M47" s="28" t="n">
+        <v>6</v>
+      </c>
       <c r="N47" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L47/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O47" s="84" t="str">
+      <c r="O47" s="84" t="n">
         <f aca="false">IFERROR(IF(M47="",N47,M47)*$C$12*181/30/D47,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P47" s="26"/>
       <c r="Q47" s="84" t="n">
@@ -8309,24 +8537,24 @@
         <f aca="false">IFERROR((G47/2)*(0.315*$C$7+0.312*$C$8+0.373*$C$9)*$C$10/(D47*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S47" s="86" t="str">
+      <c r="S47" s="86" t="n">
         <f aca="false">IFERROR((0.315*$C$7+0.312*$C$8+0.373*$C$9)/(1-$C$11)+K47+O47+Q47+R47,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T47" s="84" t="n">
         <v>1.8426</v>
       </c>
-      <c r="U47" s="86" t="str">
+      <c r="U47" s="86" t="n">
         <f aca="false">IFERROR(T47-S47,"")</f>
-        <v/>
-      </c>
-      <c r="V47" s="87" t="str">
+        <v>1.8426</v>
+      </c>
+      <c r="V47" s="87" t="n">
         <f aca="false">IFERROR(U47-$C$14,"")</f>
-        <v/>
+        <v>1.8426</v>
       </c>
       <c r="W47" s="21" t="str">
         <f aca="false">IF(U47="","",IF(U47&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8371,14 +8599,16 @@
       <c r="L48" s="28" t="n">
         <v>537</v>
       </c>
-      <c r="M48" s="26"/>
+      <c r="M48" s="28" t="n">
+        <v>8</v>
+      </c>
       <c r="N48" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L48/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O48" s="84" t="str">
+      <c r="O48" s="84" t="n">
         <f aca="false">IFERROR(IF(M48="",N48,M48)*$C$12*181/30/D48,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P48" s="26"/>
       <c r="Q48" s="84" t="n">
@@ -8389,24 +8619,24 @@
         <f aca="false">IFERROR((G48/2)*(0.462*$C$7+0.432*$C$8+0.106*$C$9)*$C$10/(D48*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S48" s="86" t="str">
+      <c r="S48" s="86" t="n">
         <f aca="false">IFERROR((0.462*$C$7+0.432*$C$8+0.106*$C$9)/(1-$C$11)+K48+O48+Q48+R48,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T48" s="84" t="n">
         <v>2.1356</v>
       </c>
-      <c r="U48" s="86" t="str">
+      <c r="U48" s="86" t="n">
         <f aca="false">IFERROR(T48-S48,"")</f>
-        <v/>
-      </c>
-      <c r="V48" s="87" t="str">
+        <v>2.1356</v>
+      </c>
+      <c r="V48" s="87" t="n">
         <f aca="false">IFERROR(U48-$C$14,"")</f>
-        <v/>
+        <v>2.1356</v>
       </c>
       <c r="W48" s="21" t="str">
         <f aca="false">IF(U48="","",IF(U48&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8451,14 +8681,16 @@
       <c r="L49" s="28" t="n">
         <v>680</v>
       </c>
-      <c r="M49" s="26"/>
+      <c r="M49" s="28" t="n">
+        <v>11</v>
+      </c>
       <c r="N49" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L49/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O49" s="84" t="str">
+      <c r="O49" s="84" t="n">
         <f aca="false">IFERROR(IF(M49="",N49,M49)*$C$12*181/30/D49,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P49" s="26"/>
       <c r="Q49" s="84" t="n">
@@ -8469,24 +8701,24 @@
         <f aca="false">IFERROR((G49/2)*(0.35*$C$7+0.301*$C$8+0.349*$C$9)*$C$10/(D49*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S49" s="86" t="str">
+      <c r="S49" s="86" t="n">
         <f aca="false">IFERROR((0.35*$C$7+0.301*$C$8+0.349*$C$9)/(1-$C$11)+K49+O49+Q49+R49,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T49" s="84" t="n">
         <v>1.8657</v>
       </c>
-      <c r="U49" s="86" t="str">
+      <c r="U49" s="86" t="n">
         <f aca="false">IFERROR(T49-S49,"")</f>
-        <v/>
-      </c>
-      <c r="V49" s="87" t="str">
+        <v>1.8657</v>
+      </c>
+      <c r="V49" s="87" t="n">
         <f aca="false">IFERROR(U49-$C$14,"")</f>
-        <v/>
+        <v>1.8657</v>
       </c>
       <c r="W49" s="21" t="str">
         <f aca="false">IF(U49="","",IF(U49&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8531,14 +8763,16 @@
       <c r="L50" s="28" t="n">
         <v>469</v>
       </c>
-      <c r="M50" s="26"/>
+      <c r="M50" s="28" t="n">
+        <v>7</v>
+      </c>
       <c r="N50" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L50/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O50" s="84" t="str">
+      <c r="O50" s="84" t="n">
         <f aca="false">IFERROR(IF(M50="",N50,M50)*$C$12*181/30/D50,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P50" s="26"/>
       <c r="Q50" s="84" t="n">
@@ -8549,24 +8783,24 @@
         <f aca="false">IFERROR((G50/2)*(0.51*$C$7+0.49*$C$8+0*$C$9)*$C$10/(D50*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S50" s="86" t="str">
+      <c r="S50" s="86" t="n">
         <f aca="false">IFERROR((0.51*$C$7+0.49*$C$8+0*$C$9)/(1-$C$11)+K50+O50+Q50+R50,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T50" s="84" t="n">
         <v>2.2535</v>
       </c>
-      <c r="U50" s="86" t="str">
+      <c r="U50" s="86" t="n">
         <f aca="false">IFERROR(T50-S50,"")</f>
-        <v/>
-      </c>
-      <c r="V50" s="87" t="str">
+        <v>2.2535</v>
+      </c>
+      <c r="V50" s="87" t="n">
         <f aca="false">IFERROR(U50-$C$14,"")</f>
-        <v/>
+        <v>2.2535</v>
       </c>
       <c r="W50" s="21" t="str">
         <f aca="false">IF(U50="","",IF(U50&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8611,14 +8845,16 @@
       <c r="L51" s="28" t="n">
         <v>807</v>
       </c>
-      <c r="M51" s="26"/>
+      <c r="M51" s="28" t="n">
+        <v>7</v>
+      </c>
       <c r="N51" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L51/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O51" s="84" t="str">
+      <c r="O51" s="84" t="n">
         <f aca="false">IFERROR(IF(M51="",N51,M51)*$C$12*181/30/D51,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P51" s="26"/>
       <c r="Q51" s="84" t="n">
@@ -8629,24 +8865,24 @@
         <f aca="false">IFERROR((G51/2)*(0.54*$C$7+0.46*$C$8+0*$C$9)*$C$10/(D51*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S51" s="86" t="str">
+      <c r="S51" s="86" t="n">
         <f aca="false">IFERROR((0.54*$C$7+0.46*$C$8+0*$C$9)/(1-$C$11)+K51+O51+Q51+R51,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T51" s="84" t="n">
         <v>2.249</v>
       </c>
-      <c r="U51" s="86" t="str">
+      <c r="U51" s="86" t="n">
         <f aca="false">IFERROR(T51-S51,"")</f>
-        <v/>
-      </c>
-      <c r="V51" s="87" t="str">
+        <v>2.249</v>
+      </c>
+      <c r="V51" s="87" t="n">
         <f aca="false">IFERROR(U51-$C$14,"")</f>
-        <v/>
+        <v>2.249</v>
       </c>
       <c r="W51" s="21" t="str">
         <f aca="false">IF(U51="","",IF(U51&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8691,14 +8927,16 @@
       <c r="L52" s="28" t="n">
         <v>441</v>
       </c>
-      <c r="M52" s="26"/>
+      <c r="M52" s="28" t="n">
+        <v>6</v>
+      </c>
       <c r="N52" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L52/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O52" s="84" t="str">
+      <c r="O52" s="84" t="n">
         <f aca="false">IFERROR(IF(M52="",N52,M52)*$C$12*181/30/D52,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P52" s="26"/>
       <c r="Q52" s="84" t="n">
@@ -8709,24 +8947,24 @@
         <f aca="false">IFERROR((G52/2)*(0.347*$C$7+0.26*$C$8+0.392*$C$9)*$C$10/(D52*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S52" s="86" t="str">
+      <c r="S52" s="86" t="n">
         <f aca="false">IFERROR((0.347*$C$7+0.26*$C$8+0.392*$C$9)/(1-$C$11)+K52+O52+Q52+R52,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T52" s="84" t="n">
         <v>1.8131</v>
       </c>
-      <c r="U52" s="86" t="str">
+      <c r="U52" s="86" t="n">
         <f aca="false">IFERROR(T52-S52,"")</f>
-        <v/>
-      </c>
-      <c r="V52" s="87" t="str">
+        <v>1.8131</v>
+      </c>
+      <c r="V52" s="87" t="n">
         <f aca="false">IFERROR(U52-$C$14,"")</f>
-        <v/>
+        <v>1.8131</v>
       </c>
       <c r="W52" s="21" t="str">
         <f aca="false">IF(U52="","",IF(U52&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8771,14 +9009,16 @@
       <c r="L53" s="28" t="n">
         <v>685</v>
       </c>
-      <c r="M53" s="26"/>
+      <c r="M53" s="28" t="n">
+        <v>5</v>
+      </c>
       <c r="N53" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L53/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O53" s="84" t="str">
+      <c r="O53" s="84" t="n">
         <f aca="false">IFERROR(IF(M53="",N53,M53)*$C$12*181/30/D53,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P53" s="26"/>
       <c r="Q53" s="84" t="n">
@@ -8789,24 +9029,24 @@
         <f aca="false">IFERROR((G53/2)*(0.537*$C$7+0.386*$C$8+0.077*$C$9)*$C$10/(D53*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S53" s="86" t="str">
+      <c r="S53" s="86" t="n">
         <f aca="false">IFERROR((0.537*$C$7+0.386*$C$8+0.077*$C$9)/(1-$C$11)+K53+O53+Q53+R53,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T53" s="84" t="n">
         <v>2.1586</v>
       </c>
-      <c r="U53" s="86" t="str">
+      <c r="U53" s="86" t="n">
         <f aca="false">IFERROR(T53-S53,"")</f>
-        <v/>
-      </c>
-      <c r="V53" s="87" t="str">
+        <v>2.1586</v>
+      </c>
+      <c r="V53" s="87" t="n">
         <f aca="false">IFERROR(U53-$C$14,"")</f>
-        <v/>
+        <v>2.1586</v>
       </c>
       <c r="W53" s="21" t="str">
         <f aca="false">IF(U53="","",IF(U53&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8851,14 +9091,16 @@
       <c r="L54" s="28" t="n">
         <v>586</v>
       </c>
-      <c r="M54" s="26"/>
+      <c r="M54" s="28" t="n">
+        <v>5</v>
+      </c>
       <c r="N54" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L54/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O54" s="84" t="str">
+      <c r="O54" s="84" t="n">
         <f aca="false">IFERROR(IF(M54="",N54,M54)*$C$12*181/30/D54,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P54" s="26"/>
       <c r="Q54" s="84" t="n">
@@ -8869,24 +9111,24 @@
         <f aca="false">IFERROR((G54/2)*(0.455*$C$7+0.31*$C$8+0.236*$C$9)*$C$10/(D54*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S54" s="86" t="str">
+      <c r="S54" s="86" t="n">
         <f aca="false">IFERROR((0.455*$C$7+0.31*$C$8+0.236*$C$9)/(1-$C$11)+K54+O54+Q54+R54,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T54" s="84" t="n">
         <v>1.9856</v>
       </c>
-      <c r="U54" s="86" t="str">
+      <c r="U54" s="86" t="n">
         <f aca="false">IFERROR(T54-S54,"")</f>
-        <v/>
-      </c>
-      <c r="V54" s="87" t="str">
+        <v>1.9856</v>
+      </c>
+      <c r="V54" s="87" t="n">
         <f aca="false">IFERROR(U54-$C$14,"")</f>
-        <v/>
+        <v>1.9856</v>
       </c>
       <c r="W54" s="21" t="str">
         <f aca="false">IF(U54="","",IF(U54&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8931,14 +9173,16 @@
       <c r="L55" s="28" t="n">
         <v>591</v>
       </c>
-      <c r="M55" s="26"/>
+      <c r="M55" s="28" t="n">
+        <v>6</v>
+      </c>
       <c r="N55" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L55/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O55" s="84" t="str">
+      <c r="O55" s="84" t="n">
         <f aca="false">IFERROR(IF(M55="",N55,M55)*$C$12*181/30/D55,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P55" s="26"/>
       <c r="Q55" s="84" t="n">
@@ -8949,24 +9193,24 @@
         <f aca="false">IFERROR((G55/2)*(0.538*$C$7+0.396*$C$8+0.066*$C$9)*$C$10/(D55*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S55" s="86" t="str">
+      <c r="S55" s="86" t="n">
         <f aca="false">IFERROR((0.538*$C$7+0.396*$C$8+0.066*$C$9)/(1-$C$11)+K55+O55+Q55+R55,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T55" s="84" t="n">
         <v>2.1714</v>
       </c>
-      <c r="U55" s="86" t="str">
+      <c r="U55" s="86" t="n">
         <f aca="false">IFERROR(T55-S55,"")</f>
-        <v/>
-      </c>
-      <c r="V55" s="87" t="str">
+        <v>2.1714</v>
+      </c>
+      <c r="V55" s="87" t="n">
         <f aca="false">IFERROR(U55-$C$14,"")</f>
-        <v/>
+        <v>2.1714</v>
       </c>
       <c r="W55" s="21" t="str">
         <f aca="false">IF(U55="","",IF(U55&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9011,14 +9255,16 @@
       <c r="L56" s="28" t="n">
         <v>650</v>
       </c>
-      <c r="M56" s="26"/>
+      <c r="M56" s="28" t="n">
+        <v>8</v>
+      </c>
       <c r="N56" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L56/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O56" s="84" t="str">
+      <c r="O56" s="84" t="n">
         <f aca="false">IFERROR(IF(M56="",N56,M56)*$C$12*181/30/D56,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P56" s="26"/>
       <c r="Q56" s="84" t="n">
@@ -9029,24 +9275,24 @@
         <f aca="false">IFERROR((G56/2)*(0.37*$C$7+0.446*$C$8+0.184*$C$9)*$C$10/(D56*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S56" s="86" t="str">
+      <c r="S56" s="86" t="n">
         <f aca="false">IFERROR((0.37*$C$7+0.446*$C$8+0.184*$C$9)/(1-$C$11)+K56+O56+Q56+R56,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T56" s="84" t="n">
         <v>2.0574</v>
       </c>
-      <c r="U56" s="86" t="str">
+      <c r="U56" s="86" t="n">
         <f aca="false">IFERROR(T56-S56,"")</f>
-        <v/>
-      </c>
-      <c r="V56" s="87" t="str">
+        <v>2.0574</v>
+      </c>
+      <c r="V56" s="87" t="n">
         <f aca="false">IFERROR(U56-$C$14,"")</f>
-        <v/>
+        <v>2.0574</v>
       </c>
       <c r="W56" s="21" t="str">
         <f aca="false">IF(U56="","",IF(U56&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9091,14 +9337,16 @@
       <c r="L57" s="28" t="n">
         <v>402</v>
       </c>
-      <c r="M57" s="26"/>
+      <c r="M57" s="28" t="n">
+        <v>5</v>
+      </c>
       <c r="N57" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L57/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O57" s="84" t="str">
+      <c r="O57" s="84" t="n">
         <f aca="false">IFERROR(IF(M57="",N57,M57)*$C$12*181/30/D57,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P57" s="26"/>
       <c r="Q57" s="84" t="n">
@@ -9109,24 +9357,24 @@
         <f aca="false">IFERROR((G57/2)*(0.394*$C$7+0.404*$C$8+0.201*$C$9)*$C$10/(D57*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S57" s="86" t="str">
+      <c r="S57" s="86" t="n">
         <f aca="false">IFERROR((0.394*$C$7+0.404*$C$8+0.201*$C$9)/(1-$C$11)+K57+O57+Q57+R57,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T57" s="84" t="n">
         <v>2.0314</v>
       </c>
-      <c r="U57" s="86" t="str">
+      <c r="U57" s="86" t="n">
         <f aca="false">IFERROR(T57-S57,"")</f>
-        <v/>
-      </c>
-      <c r="V57" s="87" t="str">
+        <v>2.0314</v>
+      </c>
+      <c r="V57" s="87" t="n">
         <f aca="false">IFERROR(U57-$C$14,"")</f>
-        <v/>
+        <v>2.0314</v>
       </c>
       <c r="W57" s="21" t="str">
         <f aca="false">IF(U57="","",IF(U57&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9171,14 +9419,16 @@
       <c r="L58" s="28" t="n">
         <v>456</v>
       </c>
-      <c r="M58" s="26"/>
+      <c r="M58" s="28" t="n">
+        <v>5</v>
+      </c>
       <c r="N58" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L58/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O58" s="84" t="str">
+      <c r="O58" s="84" t="n">
         <f aca="false">IFERROR(IF(M58="",N58,M58)*$C$12*181/30/D58,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P58" s="26"/>
       <c r="Q58" s="84" t="n">
@@ -9189,24 +9439,24 @@
         <f aca="false">IFERROR((G58/2)*(0.488*$C$7+0.512*$C$8+0*$C$9)*$C$10/(D58*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S58" s="86" t="str">
+      <c r="S58" s="86" t="n">
         <f aca="false">IFERROR((0.488*$C$7+0.512*$C$8+0*$C$9)/(1-$C$11)+K58+O58+Q58+R58,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T58" s="84" t="n">
         <v>2.2568</v>
       </c>
-      <c r="U58" s="86" t="str">
+      <c r="U58" s="86" t="n">
         <f aca="false">IFERROR(T58-S58,"")</f>
-        <v/>
-      </c>
-      <c r="V58" s="87" t="str">
+        <v>2.2568</v>
+      </c>
+      <c r="V58" s="87" t="n">
         <f aca="false">IFERROR(U58-$C$14,"")</f>
-        <v/>
+        <v>2.2568</v>
       </c>
       <c r="W58" s="21" t="str">
         <f aca="false">IF(U58="","",IF(U58&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9251,14 +9501,16 @@
       <c r="L59" s="28" t="n">
         <v>455</v>
       </c>
-      <c r="M59" s="26"/>
+      <c r="M59" s="28" t="n">
+        <v>5</v>
+      </c>
       <c r="N59" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L59/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O59" s="84" t="str">
+      <c r="O59" s="84" t="n">
         <f aca="false">IFERROR(IF(M59="",N59,M59)*$C$12*181/30/D59,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P59" s="26"/>
       <c r="Q59" s="84" t="n">
@@ -9269,24 +9521,24 @@
         <f aca="false">IFERROR((G59/2)*(0.511*$C$7+0.472*$C$8+0.017*$C$9)*$C$10/(D59*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S59" s="86" t="str">
+      <c r="S59" s="86" t="n">
         <f aca="false">IFERROR((0.511*$C$7+0.472*$C$8+0.017*$C$9)/(1-$C$11)+K59+O59+Q59+R59,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T59" s="84" t="n">
         <v>2.2333</v>
       </c>
-      <c r="U59" s="86" t="str">
+      <c r="U59" s="86" t="n">
         <f aca="false">IFERROR(T59-S59,"")</f>
-        <v/>
-      </c>
-      <c r="V59" s="87" t="str">
+        <v>2.2333</v>
+      </c>
+      <c r="V59" s="87" t="n">
         <f aca="false">IFERROR(U59-$C$14,"")</f>
-        <v/>
+        <v>2.2333</v>
       </c>
       <c r="W59" s="21" t="str">
         <f aca="false">IF(U59="","",IF(U59&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9331,14 +9583,16 @@
       <c r="L60" s="28" t="n">
         <v>333</v>
       </c>
-      <c r="M60" s="26"/>
+      <c r="M60" s="28" t="n">
+        <v>6</v>
+      </c>
       <c r="N60" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L60/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O60" s="84" t="str">
+      <c r="O60" s="84" t="n">
         <f aca="false">IFERROR(IF(M60="",N60,M60)*$C$12*181/30/D60,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P60" s="26"/>
       <c r="Q60" s="84" t="n">
@@ -9349,24 +9603,24 @@
         <f aca="false">IFERROR((G60/2)*(0.449*$C$7+0.259*$C$8+0.292*$C$9)*$C$10/(D60*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S60" s="86" t="str">
+      <c r="S60" s="86" t="n">
         <f aca="false">IFERROR((0.449*$C$7+0.259*$C$8+0.292*$C$9)/(1-$C$11)+K60+O60+Q60+R60,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T60" s="84" t="n">
         <v>1.9181</v>
       </c>
-      <c r="U60" s="86" t="str">
+      <c r="U60" s="86" t="n">
         <f aca="false">IFERROR(T60-S60,"")</f>
-        <v/>
-      </c>
-      <c r="V60" s="87" t="str">
+        <v>1.9181</v>
+      </c>
+      <c r="V60" s="87" t="n">
         <f aca="false">IFERROR(U60-$C$14,"")</f>
-        <v/>
+        <v>1.9181</v>
       </c>
       <c r="W60" s="21" t="str">
         <f aca="false">IF(U60="","",IF(U60&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9411,14 +9665,16 @@
       <c r="L61" s="28" t="n">
         <v>952</v>
       </c>
-      <c r="M61" s="26"/>
+      <c r="M61" s="28" t="n">
+        <v>7</v>
+      </c>
       <c r="N61" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L61/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O61" s="84" t="str">
+      <c r="O61" s="84" t="n">
         <f aca="false">IFERROR(IF(M61="",N61,M61)*$C$12*181/30/D61,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P61" s="26"/>
       <c r="Q61" s="84" t="n">
@@ -9429,24 +9685,24 @@
         <f aca="false">IFERROR((G61/2)*(0.503*$C$7+0.394*$C$8+0.103*$C$9)*$C$10/(D61*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S61" s="86" t="str">
+      <c r="S61" s="86" t="n">
         <f aca="false">IFERROR((0.503*$C$7+0.394*$C$8+0.103*$C$9)/(1-$C$11)+K61+O61+Q61+R61,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T61" s="84" t="n">
         <v>2.133</v>
       </c>
-      <c r="U61" s="86" t="str">
+      <c r="U61" s="86" t="n">
         <f aca="false">IFERROR(T61-S61,"")</f>
-        <v/>
-      </c>
-      <c r="V61" s="87" t="str">
+        <v>2.133</v>
+      </c>
+      <c r="V61" s="87" t="n">
         <f aca="false">IFERROR(U61-$C$14,"")</f>
-        <v/>
+        <v>2.133</v>
       </c>
       <c r="W61" s="21" t="str">
         <f aca="false">IF(U61="","",IF(U61&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9491,14 +9747,16 @@
       <c r="L62" s="28" t="n">
         <v>327</v>
       </c>
-      <c r="M62" s="26"/>
+      <c r="M62" s="28" t="n">
+        <v>6</v>
+      </c>
       <c r="N62" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L62/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O62" s="84" t="str">
+      <c r="O62" s="84" t="n">
         <f aca="false">IFERROR(IF(M62="",N62,M62)*$C$12*181/30/D62,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P62" s="26"/>
       <c r="Q62" s="84" t="n">
@@ -9509,24 +9767,24 @@
         <f aca="false">IFERROR((G62/2)*(0.576*$C$7+0.347*$C$8+0.077*$C$9)*$C$10/(D62*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S62" s="86" t="str">
+      <c r="S62" s="86" t="n">
         <f aca="false">IFERROR((0.576*$C$7+0.347*$C$8+0.077*$C$9)/(1-$C$11)+K62+O62+Q62+R62,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T62" s="84" t="n">
         <v>2.1527</v>
       </c>
-      <c r="U62" s="86" t="str">
+      <c r="U62" s="86" t="n">
         <f aca="false">IFERROR(T62-S62,"")</f>
-        <v/>
-      </c>
-      <c r="V62" s="87" t="str">
+        <v>2.1527</v>
+      </c>
+      <c r="V62" s="87" t="n">
         <f aca="false">IFERROR(U62-$C$14,"")</f>
-        <v/>
+        <v>2.1527</v>
       </c>
       <c r="W62" s="21" t="str">
         <f aca="false">IF(U62="","",IF(U62&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9571,14 +9829,16 @@
       <c r="L63" s="28" t="n">
         <v>281</v>
       </c>
-      <c r="M63" s="26"/>
+      <c r="M63" s="28" t="n">
+        <v>4</v>
+      </c>
       <c r="N63" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L63/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O63" s="84" t="str">
+      <c r="O63" s="84" t="n">
         <f aca="false">IFERROR(IF(M63="",N63,M63)*$C$12*181/30/D63,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P63" s="26"/>
       <c r="Q63" s="84" t="n">
@@ -9589,24 +9849,24 @@
         <f aca="false">IFERROR((G63/2)*(0.427*$C$7+0.393*$C$8+0.18*$C$9)*$C$10/(D63*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S63" s="86" t="str">
+      <c r="S63" s="86" t="n">
         <f aca="false">IFERROR((0.427*$C$7+0.393*$C$8+0.18*$C$9)/(1-$C$11)+K63+O63+Q63+R63,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T63" s="84" t="n">
         <v>2.0535</v>
       </c>
-      <c r="U63" s="86" t="str">
+      <c r="U63" s="86" t="n">
         <f aca="false">IFERROR(T63-S63,"")</f>
-        <v/>
-      </c>
-      <c r="V63" s="87" t="str">
+        <v>2.0535</v>
+      </c>
+      <c r="V63" s="87" t="n">
         <f aca="false">IFERROR(U63-$C$14,"")</f>
-        <v/>
+        <v>2.0535</v>
       </c>
       <c r="W63" s="21" t="str">
         <f aca="false">IF(U63="","",IF(U63&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9651,14 +9911,16 @@
       <c r="L64" s="28" t="n">
         <v>800</v>
       </c>
-      <c r="M64" s="26"/>
+      <c r="M64" s="28" t="n">
+        <v>7</v>
+      </c>
       <c r="N64" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L64/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O64" s="84" t="str">
+      <c r="O64" s="84" t="n">
         <f aca="false">IFERROR(IF(M64="",N64,M64)*$C$12*181/30/D64,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P64" s="26"/>
       <c r="Q64" s="84" t="n">
@@ -9669,24 +9931,24 @@
         <f aca="false">IFERROR((G64/2)*(0.447*$C$7+0.497*$C$8+0.056*$C$9)*$C$10/(D64*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S64" s="86" t="str">
+      <c r="S64" s="86" t="n">
         <f aca="false">IFERROR((0.447*$C$7+0.497*$C$8+0.056*$C$9)/(1-$C$11)+K64+O64+Q64+R64,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T64" s="84" t="n">
         <v>2.1969</v>
       </c>
-      <c r="U64" s="86" t="str">
+      <c r="U64" s="86" t="n">
         <f aca="false">IFERROR(T64-S64,"")</f>
-        <v/>
-      </c>
-      <c r="V64" s="87" t="str">
+        <v>2.1969</v>
+      </c>
+      <c r="V64" s="87" t="n">
         <f aca="false">IFERROR(U64-$C$14,"")</f>
-        <v/>
+        <v>2.1969</v>
       </c>
       <c r="W64" s="21" t="str">
         <f aca="false">IF(U64="","",IF(U64&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9731,14 +9993,16 @@
       <c r="L65" s="28" t="n">
         <v>408</v>
       </c>
-      <c r="M65" s="26"/>
+      <c r="M65" s="28" t="n">
+        <v>4</v>
+      </c>
       <c r="N65" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L65/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O65" s="84" t="str">
+      <c r="O65" s="84" t="n">
         <f aca="false">IFERROR(IF(M65="",N65,M65)*$C$12*181/30/D65,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P65" s="26"/>
       <c r="Q65" s="84" t="n">
@@ -9749,24 +10013,24 @@
         <f aca="false">IFERROR((G65/2)*(0.459*$C$7+0.348*$C$8+0.194*$C$9)*$C$10/(D65*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S65" s="86" t="str">
+      <c r="S65" s="86" t="n">
         <f aca="false">IFERROR((0.459*$C$7+0.348*$C$8+0.194*$C$9)/(1-$C$11)+K65+O65+Q65+R65,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T65" s="84" t="n">
         <v>2.0346</v>
       </c>
-      <c r="U65" s="86" t="str">
+      <c r="U65" s="86" t="n">
         <f aca="false">IFERROR(T65-S65,"")</f>
-        <v/>
-      </c>
-      <c r="V65" s="87" t="str">
+        <v>2.0346</v>
+      </c>
+      <c r="V65" s="87" t="n">
         <f aca="false">IFERROR(U65-$C$14,"")</f>
-        <v/>
+        <v>2.0346</v>
       </c>
       <c r="W65" s="21" t="str">
         <f aca="false">IF(U65="","",IF(U65&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9809,14 +10073,16 @@
         <v>0</v>
       </c>
       <c r="L66" s="21"/>
-      <c r="M66" s="26"/>
+      <c r="M66" s="28" t="n">
+        <v>4</v>
+      </c>
       <c r="N66" s="28" t="str">
         <f aca="false">IFERROR(ROUNDUP(L66/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O66" s="84" t="str">
+      <c r="O66" s="84" t="n">
         <f aca="false">IFERROR(IF(M66="",N66,M66)*$C$12*181/30/D66,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P66" s="26"/>
       <c r="Q66" s="84" t="n">
@@ -9827,22 +10093,22 @@
         <f aca="false">IFERROR((G66/2)*$C$7*$C$10/(D66*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S66" s="86" t="str">
+      <c r="S66" s="86" t="n">
         <f aca="false">IFERROR($C$7/(1-$C$11)+K66+O66+Q66+R66,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T66" s="21"/>
-      <c r="U66" s="86" t="str">
+      <c r="U66" s="86" t="n">
         <f aca="false">IFERROR(T66-S66,"")</f>
-        <v/>
-      </c>
-      <c r="V66" s="87" t="str">
+        <v>0</v>
+      </c>
+      <c r="V66" s="87" t="n">
         <f aca="false">IFERROR(U66-$C$14,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W66" s="21" t="str">
         <f aca="false">IF(U66="","",IF(U66&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9887,14 +10153,16 @@
       <c r="L67" s="28" t="n">
         <v>154</v>
       </c>
-      <c r="M67" s="26"/>
+      <c r="M67" s="28" t="n">
+        <v>5</v>
+      </c>
       <c r="N67" s="85" t="str">
         <f aca="false">IFERROR(ROUNDUP(L67/$C$13,0),"")</f>
         <v/>
       </c>
-      <c r="O67" s="84" t="str">
+      <c r="O67" s="84" t="n">
         <f aca="false">IFERROR(IF(M67="",N67,M67)*$C$12*181/30/D67,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P67" s="26"/>
       <c r="Q67" s="84" t="n">
@@ -9905,24 +10173,24 @@
         <f aca="false">IFERROR((G67/2)*(0.503*$C$7+0.33*$C$8+0.167*$C$9)*$C$10/(D67*365/181),"")</f>
         <v>0</v>
       </c>
-      <c r="S67" s="86" t="str">
+      <c r="S67" s="86" t="n">
         <f aca="false">IFERROR((0.503*$C$7+0.33*$C$8+0.167*$C$9)/(1-$C$11)+K67+O67+Q67+R67,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T67" s="84" t="n">
         <v>2.0575</v>
       </c>
-      <c r="U67" s="86" t="str">
+      <c r="U67" s="86" t="n">
         <f aca="false">IFERROR(T67-S67,"")</f>
-        <v/>
-      </c>
-      <c r="V67" s="87" t="str">
+        <v>2.0575</v>
+      </c>
+      <c r="V67" s="87" t="n">
         <f aca="false">IFERROR(U67-$C$14,"")</f>
-        <v/>
+        <v>2.0575</v>
       </c>
       <c r="W67" s="21" t="str">
         <f aca="false">IF(U67="","",IF(U67&gt;=$C$14,"يحقق الهدف","دون الهدف"))</f>
-        <v/>
+        <v>يحقق الهدف</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9957,7 +10225,7 @@
       </c>
       <c r="M68" s="34" t="n">
         <f aca="false">SUM(M18:M67)</f>
-        <v>0</v>
+        <v>486</v>
       </c>
       <c r="N68" s="34" t="n">
         <f aca="false">SUM(N18:N67)</f>
@@ -10309,7 +10577,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>997</v>
       </c>
       <c r="D6" s="69"/>
@@ -10327,7 +10595,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="12" t="s">
         <v>1001</v>
       </c>
       <c r="D7" s="26" t="n">
@@ -13757,6 +14025,2978 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:P63"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="12" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>858</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>1142</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>1143</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>1144</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>915</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>1145</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>1146</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>914</v>
+      </c>
+      <c r="N4" s="15" t="s">
+        <v>1147</v>
+      </c>
+      <c r="O4" s="15" t="s">
+        <v>1148</v>
+      </c>
+      <c r="P4" s="15" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>926</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F5" s="28" t="n">
+        <v>7071</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="H5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="21" t="n">
+        <f aca="false">G5+H5</f>
+        <v>21</v>
+      </c>
+      <c r="J5" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="K5" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="L5" s="97" t="n">
+        <f aca="false">IF(K5="","",J5-K5)</f>
+        <v>3</v>
+      </c>
+      <c r="M5" s="21"/>
+      <c r="N5" s="28" t="n">
+        <f aca="false">IFERROR(M5/J5,"")</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="28" t="n">
+        <f aca="false">IFERROR(M5/I5,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="16" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="H6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="21" t="n">
+        <f aca="false">G6+H6</f>
+        <v>18</v>
+      </c>
+      <c r="J6" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="K6" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="L6" s="97" t="n">
+        <f aca="false">IF(K6="","",J6-K6)</f>
+        <v>-2</v>
+      </c>
+      <c r="M6" s="28" t="n">
+        <v>4236</v>
+      </c>
+      <c r="N6" s="28" t="n">
+        <f aca="false">IFERROR(M6/J6,"")</f>
+        <v>132.375</v>
+      </c>
+      <c r="O6" s="28" t="n">
+        <f aca="false">IFERROR(M6/I6,"")</f>
+        <v>235.333333333333</v>
+      </c>
+      <c r="P6" s="16"/>
+    </row>
+    <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>5618</v>
+      </c>
+      <c r="G7" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="21" t="n">
+        <f aca="false">G7+H7</f>
+        <v>12</v>
+      </c>
+      <c r="J7" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="K7" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="L7" s="97" t="n">
+        <f aca="false">IF(K7="","",J7-K7)</f>
+        <v>6</v>
+      </c>
+      <c r="M7" s="21"/>
+      <c r="N7" s="28" t="n">
+        <f aca="false">IFERROR(M7/J7,"")</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="28" t="n">
+        <f aca="false">IFERROR(M7/I7,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="16" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>927</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>20966</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" s="21" t="n">
+        <f aca="false">G8+H8</f>
+        <v>12</v>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="L8" s="97" t="n">
+        <f aca="false">IF(K8="","",J8-K8)</f>
+        <v>-1</v>
+      </c>
+      <c r="M8" s="21"/>
+      <c r="N8" s="28" t="n">
+        <f aca="false">IFERROR(M8/J8,"")</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="28" t="n">
+        <f aca="false">IFERROR(M8/I8,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="16" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>9029</v>
+      </c>
+      <c r="G9" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="21" t="n">
+        <f aca="false">G9+H9</f>
+        <v>9</v>
+      </c>
+      <c r="J9" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="K9" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="L9" s="97" t="n">
+        <f aca="false">IF(K9="","",J9-K9)</f>
+        <v>2</v>
+      </c>
+      <c r="M9" s="21"/>
+      <c r="N9" s="28" t="n">
+        <f aca="false">IFERROR(M9/J9,"")</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <f aca="false">IFERROR(M9/I9,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P9" s="16" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>929</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F10" s="28" t="n">
+        <v>2948</v>
+      </c>
+      <c r="G10" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="21" t="n">
+        <f aca="false">G10+H10</f>
+        <v>6</v>
+      </c>
+      <c r="J10" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="L10" s="97" t="n">
+        <f aca="false">IF(K10="","",J10-K10)</f>
+        <v>-1</v>
+      </c>
+      <c r="M10" s="28" t="n">
+        <v>2359</v>
+      </c>
+      <c r="N10" s="28" t="n">
+        <f aca="false">IFERROR(M10/J10,"")</f>
+        <v>168.5</v>
+      </c>
+      <c r="O10" s="28" t="n">
+        <f aca="false">IFERROR(M10/I10,"")</f>
+        <v>393.166666666667</v>
+      </c>
+      <c r="P10" s="16"/>
+    </row>
+    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F11" s="28" t="n">
+        <v>4735</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <f aca="false">G11+H11</f>
+        <v>12</v>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="L11" s="97" t="n">
+        <f aca="false">IF(K11="","",J11-K11)</f>
+        <v>1</v>
+      </c>
+      <c r="M11" s="21"/>
+      <c r="N11" s="28" t="n">
+        <f aca="false">IFERROR(M11/J11,"")</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <f aca="false">IFERROR(M11/I11,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P11" s="16" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>935</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F12" s="28" t="n">
+        <v>7246</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="21" t="n">
+        <f aca="false">G12+H12</f>
+        <v>9</v>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="L12" s="97" t="n">
+        <f aca="false">IF(K12="","",J12-K12)</f>
+        <v>1</v>
+      </c>
+      <c r="M12" s="28" t="n">
+        <v>1414</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <f aca="false">IFERROR(M12/J12,"")</f>
+        <v>108.769230769231</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <f aca="false">IFERROR(M12/I12,"")</f>
+        <v>157.111111111111</v>
+      </c>
+      <c r="P12" s="16"/>
+    </row>
+    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F13" s="28" t="n">
+        <v>13279</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="21" t="n">
+        <f aca="false">G13+H13</f>
+        <v>10</v>
+      </c>
+      <c r="J13" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="K13" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="L13" s="97" t="n">
+        <f aca="false">IF(K13="","",J13-K13)</f>
+        <v>1</v>
+      </c>
+      <c r="M13" s="28" t="n">
+        <v>1380</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <f aca="false">IFERROR(M13/J13,"")</f>
+        <v>106.153846153846</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <f aca="false">IFERROR(M13/I13,"")</f>
+        <v>138</v>
+      </c>
+      <c r="P13" s="16"/>
+    </row>
+    <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F14" s="28" t="n">
+        <v>8306</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="21" t="n">
+        <f aca="false">G14+H14</f>
+        <v>8</v>
+      </c>
+      <c r="J14" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="K14" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="L14" s="97" t="n">
+        <f aca="false">IF(K14="","",J14-K14)</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="28" t="n">
+        <v>1566</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <f aca="false">IFERROR(M14/J14,"")</f>
+        <v>130.5</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <f aca="false">IFERROR(M14/I14,"")</f>
+        <v>195.75</v>
+      </c>
+      <c r="P14" s="16"/>
+    </row>
+    <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F15" s="28" t="n">
+        <v>3120</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="21" t="n">
+        <f aca="false">G15+H15</f>
+        <v>8</v>
+      </c>
+      <c r="J15" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="K15" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="L15" s="97" t="n">
+        <f aca="false">IF(K15="","",J15-K15)</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="21"/>
+      <c r="N15" s="28" t="n">
+        <f aca="false">IFERROR(M15/J15,"")</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <f aca="false">IFERROR(M15/I15,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="16" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>940</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F16" s="28" t="n">
+        <v>4343.5</v>
+      </c>
+      <c r="G16" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="21" t="n">
+        <f aca="false">G16+H16</f>
+        <v>9</v>
+      </c>
+      <c r="J16" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="K16" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="L16" s="97" t="n">
+        <f aca="false">IF(K16="","",J16-K16)</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="28" t="n">
+        <v>1573</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <f aca="false">IFERROR(M16/J16,"")</f>
+        <v>143</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <f aca="false">IFERROR(M16/I16,"")</f>
+        <v>174.777777777778</v>
+      </c>
+      <c r="P16" s="16"/>
+    </row>
+    <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F17" s="28" t="n">
+        <v>43915</v>
+      </c>
+      <c r="G17" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="21" t="n">
+        <f aca="false">G17+H17</f>
+        <v>16</v>
+      </c>
+      <c r="J17" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="K17" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" s="97" t="n">
+        <f aca="false">IF(K17="","",J17-K17)</f>
+        <v>1</v>
+      </c>
+      <c r="M17" s="21"/>
+      <c r="N17" s="28" t="n">
+        <f aca="false">IFERROR(M17/J17,"")</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <f aca="false">IFERROR(M17/I17,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="16" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>938</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F18" s="28" t="n">
+        <v>2367</v>
+      </c>
+      <c r="G18" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="21" t="n">
+        <f aca="false">G18+H18</f>
+        <v>4</v>
+      </c>
+      <c r="J18" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="K18" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="L18" s="97" t="n">
+        <f aca="false">IF(K18="","",J18-K18)</f>
+        <v>-2</v>
+      </c>
+      <c r="M18" s="28" t="n">
+        <v>1872</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <f aca="false">IFERROR(M18/J18,"")</f>
+        <v>187.2</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <f aca="false">IFERROR(M18/I18,"")</f>
+        <v>468</v>
+      </c>
+      <c r="P18" s="16"/>
+    </row>
+    <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>931</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F19" s="28" t="n">
+        <v>5078</v>
+      </c>
+      <c r="G19" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="21" t="n">
+        <f aca="false">G19+H19</f>
+        <v>9</v>
+      </c>
+      <c r="J19" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="K19" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="L19" s="97" t="n">
+        <f aca="false">IF(K19="","",J19-K19)</f>
+        <v>-1</v>
+      </c>
+      <c r="M19" s="28" t="n">
+        <v>1702</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <f aca="false">IFERROR(M19/J19,"")</f>
+        <v>170.2</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <f aca="false">IFERROR(M19/I19,"")</f>
+        <v>189.111111111111</v>
+      </c>
+      <c r="P19" s="16"/>
+    </row>
+    <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F20" s="28" t="n">
+        <v>13300</v>
+      </c>
+      <c r="G20" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="I20" s="21" t="n">
+        <f aca="false">G20+H20</f>
+        <v>16</v>
+      </c>
+      <c r="J20" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="K20" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" s="97" t="n">
+        <f aca="false">IF(K20="","",J20-K20)</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="28" t="n">
+        <v>1169</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <f aca="false">IFERROR(M20/J20,"")</f>
+        <v>116.9</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <f aca="false">IFERROR(M20/I20,"")</f>
+        <v>73.0625</v>
+      </c>
+      <c r="P20" s="16"/>
+    </row>
+    <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>928</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F21" s="28" t="n">
+        <v>3408</v>
+      </c>
+      <c r="G21" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="21" t="n">
+        <f aca="false">G21+H21</f>
+        <v>6</v>
+      </c>
+      <c r="J21" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="K21" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="L21" s="97" t="n">
+        <f aca="false">IF(K21="","",J21-K21)</f>
+        <v>-1</v>
+      </c>
+      <c r="M21" s="21"/>
+      <c r="N21" s="28" t="n">
+        <f aca="false">IFERROR(M21/J21,"")</f>
+        <v>0</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <f aca="false">IFERROR(M21/I21,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P21" s="16" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>944</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F22" s="28" t="n">
+        <v>3625</v>
+      </c>
+      <c r="G22" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H22" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="21" t="n">
+        <f aca="false">G22+H22</f>
+        <v>9</v>
+      </c>
+      <c r="J22" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="K22" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="L22" s="97" t="n">
+        <f aca="false">IF(K22="","",J22-K22)</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="28" t="n">
+        <v>1290</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <f aca="false">IFERROR(M22/J22,"")</f>
+        <v>143.333333333333</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <f aca="false">IFERROR(M22/I22,"")</f>
+        <v>143.333333333333</v>
+      </c>
+      <c r="P22" s="16"/>
+    </row>
+    <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>943</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F23" s="28" t="n">
+        <v>4338</v>
+      </c>
+      <c r="G23" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="21" t="n">
+        <f aca="false">G23+H23</f>
+        <v>4</v>
+      </c>
+      <c r="J23" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="K23" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="L23" s="97" t="n">
+        <f aca="false">IF(K23="","",J23-K23)</f>
+        <v>-1</v>
+      </c>
+      <c r="M23" s="28" t="n">
+        <v>1363</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <f aca="false">IFERROR(M23/J23,"")</f>
+        <v>151.444444444444</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <f aca="false">IFERROR(M23/I23,"")</f>
+        <v>340.75</v>
+      </c>
+      <c r="P23" s="16"/>
+    </row>
+    <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F24" s="28" t="n">
+        <v>2991</v>
+      </c>
+      <c r="G24" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="21" t="n">
+        <f aca="false">G24+H24</f>
+        <v>9</v>
+      </c>
+      <c r="J24" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="K24" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L24" s="97" t="n">
+        <f aca="false">IF(K24="","",J24-K24)</f>
+        <v>1</v>
+      </c>
+      <c r="M24" s="28" t="n">
+        <v>1144</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <f aca="false">IFERROR(M24/J24,"")</f>
+        <v>127.111111111111</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <f aca="false">IFERROR(M24/I24,"")</f>
+        <v>127.111111111111</v>
+      </c>
+      <c r="P24" s="16"/>
+    </row>
+    <row r="25" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F25" s="28" t="n">
+        <v>5492</v>
+      </c>
+      <c r="G25" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="21" t="n">
+        <f aca="false">G25+H25</f>
+        <v>6</v>
+      </c>
+      <c r="J25" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="K25" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="L25" s="97" t="n">
+        <f aca="false">IF(K25="","",J25-K25)</f>
+        <v>-1</v>
+      </c>
+      <c r="M25" s="28" t="n">
+        <v>1112</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <f aca="false">IFERROR(M25/J25,"")</f>
+        <v>123.555555555556</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <f aca="false">IFERROR(M25/I25,"")</f>
+        <v>185.333333333333</v>
+      </c>
+      <c r="P25" s="16"/>
+    </row>
+    <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>948</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F26" s="28" t="n">
+        <v>6987</v>
+      </c>
+      <c r="G26" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="21" t="n">
+        <f aca="false">G26+H26</f>
+        <v>6</v>
+      </c>
+      <c r="J26" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="K26" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L26" s="97" t="n">
+        <f aca="false">IF(K26="","",J26-K26)</f>
+        <v>1</v>
+      </c>
+      <c r="M26" s="28" t="n">
+        <v>423</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <f aca="false">IFERROR(M26/J26,"")</f>
+        <v>47</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <f aca="false">IFERROR(M26/I26,"")</f>
+        <v>70.5</v>
+      </c>
+      <c r="P26" s="16"/>
+    </row>
+    <row r="27" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F27" s="28" t="n">
+        <v>3693</v>
+      </c>
+      <c r="G27" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="21" t="n">
+        <f aca="false">G27+H27</f>
+        <v>6</v>
+      </c>
+      <c r="J27" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="K27" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="L27" s="97" t="n">
+        <f aca="false">IF(K27="","",J27-K27)</f>
+        <v>-1</v>
+      </c>
+      <c r="M27" s="28" t="n">
+        <v>816</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <f aca="false">IFERROR(M27/J27,"")</f>
+        <v>102</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <f aca="false">IFERROR(M27/I27,"")</f>
+        <v>136</v>
+      </c>
+      <c r="P27" s="16"/>
+    </row>
+    <row r="28" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F28" s="28" t="n">
+        <v>7390</v>
+      </c>
+      <c r="G28" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="21" t="n">
+        <f aca="false">G28+H28</f>
+        <v>9</v>
+      </c>
+      <c r="J28" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="K28" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L28" s="97" t="n">
+        <f aca="false">IF(K28="","",J28-K28)</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="28" t="n">
+        <v>537</v>
+      </c>
+      <c r="N28" s="28" t="n">
+        <f aca="false">IFERROR(M28/J28,"")</f>
+        <v>67.125</v>
+      </c>
+      <c r="O28" s="28" t="n">
+        <f aca="false">IFERROR(M28/I28,"")</f>
+        <v>59.6666666666667</v>
+      </c>
+      <c r="P28" s="16"/>
+    </row>
+    <row r="29" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>950</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F29" s="28" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G29" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" s="21" t="n">
+        <f aca="false">G29+H29</f>
+        <v>6</v>
+      </c>
+      <c r="J29" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="K29" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L29" s="97" t="n">
+        <f aca="false">IF(K29="","",J29-K29)</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="28" t="n">
+        <v>922</v>
+      </c>
+      <c r="N29" s="28" t="n">
+        <f aca="false">IFERROR(M29/J29,"")</f>
+        <v>115.25</v>
+      </c>
+      <c r="O29" s="28" t="n">
+        <f aca="false">IFERROR(M29/I29,"")</f>
+        <v>153.666666666667</v>
+      </c>
+      <c r="P29" s="16"/>
+    </row>
+    <row r="30" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F30" s="28" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G30" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" s="21" t="n">
+        <f aca="false">G30+H30</f>
+        <v>8</v>
+      </c>
+      <c r="J30" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="K30" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L30" s="97" t="n">
+        <f aca="false">IF(K30="","",J30-K30)</f>
+        <v>1</v>
+      </c>
+      <c r="M30" s="28" t="n">
+        <v>650</v>
+      </c>
+      <c r="N30" s="28" t="n">
+        <f aca="false">IFERROR(M30/J30,"")</f>
+        <v>81.25</v>
+      </c>
+      <c r="O30" s="28" t="n">
+        <f aca="false">IFERROR(M30/I30,"")</f>
+        <v>81.25</v>
+      </c>
+      <c r="P30" s="16"/>
+    </row>
+    <row r="31" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>952</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F31" s="28" t="n">
+        <v>7071</v>
+      </c>
+      <c r="G31" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="21" t="n">
+        <f aca="false">G31+H31</f>
+        <v>10</v>
+      </c>
+      <c r="J31" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L31" s="97" t="n">
+        <f aca="false">IF(K31="","",J31-K31)</f>
+        <v>-1</v>
+      </c>
+      <c r="M31" s="28" t="n">
+        <v>913</v>
+      </c>
+      <c r="N31" s="28" t="n">
+        <f aca="false">IFERROR(M31/J31,"")</f>
+        <v>130.428571428571</v>
+      </c>
+      <c r="O31" s="28" t="n">
+        <f aca="false">IFERROR(M31/I31,"")</f>
+        <v>91.3</v>
+      </c>
+      <c r="P31" s="16"/>
+    </row>
+    <row r="32" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F32" s="28" t="n">
+        <v>4488</v>
+      </c>
+      <c r="G32" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="21" t="n">
+        <f aca="false">G32+H32</f>
+        <v>4</v>
+      </c>
+      <c r="J32" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K32" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L32" s="97" t="n">
+        <f aca="false">IF(K32="","",J32-K32)</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="28" t="n">
+        <v>807</v>
+      </c>
+      <c r="N32" s="28" t="n">
+        <f aca="false">IFERROR(M32/J32,"")</f>
+        <v>115.285714285714</v>
+      </c>
+      <c r="O32" s="28" t="n">
+        <f aca="false">IFERROR(M32/I32,"")</f>
+        <v>201.75</v>
+      </c>
+      <c r="P32" s="16"/>
+    </row>
+    <row r="33" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>957</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F33" s="28" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G33" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="21" t="n">
+        <f aca="false">G33+H33</f>
+        <v>9</v>
+      </c>
+      <c r="J33" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K33" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L33" s="97" t="n">
+        <f aca="false">IF(K33="","",J33-K33)</f>
+        <v>1</v>
+      </c>
+      <c r="M33" s="28" t="n">
+        <v>469</v>
+      </c>
+      <c r="N33" s="28" t="n">
+        <f aca="false">IFERROR(M33/J33,"")</f>
+        <v>67</v>
+      </c>
+      <c r="O33" s="28" t="n">
+        <f aca="false">IFERROR(M33/I33,"")</f>
+        <v>52.1111111111111</v>
+      </c>
+      <c r="P33" s="16"/>
+    </row>
+    <row r="34" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F34" s="28" t="n">
+        <v>3633</v>
+      </c>
+      <c r="G34" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H34" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="I34" s="21" t="n">
+        <f aca="false">G34+H34</f>
+        <v>15</v>
+      </c>
+      <c r="J34" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K34" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L34" s="97" t="n">
+        <f aca="false">IF(K34="","",J34-K34)</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="28" t="n">
+        <v>864</v>
+      </c>
+      <c r="N34" s="28" t="n">
+        <f aca="false">IFERROR(M34/J34,"")</f>
+        <v>123.428571428571</v>
+      </c>
+      <c r="O34" s="28" t="n">
+        <f aca="false">IFERROR(M34/I34,"")</f>
+        <v>57.6</v>
+      </c>
+      <c r="P34" s="16"/>
+    </row>
+    <row r="35" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F35" s="28" t="n">
+        <v>1607.22</v>
+      </c>
+      <c r="G35" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="21" t="n">
+        <f aca="false">G35+H35</f>
+        <v>3</v>
+      </c>
+      <c r="J35" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K35" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L35" s="97" t="n">
+        <f aca="false">IF(K35="","",J35-K35)</f>
+        <v>1</v>
+      </c>
+      <c r="M35" s="28" t="n">
+        <v>938</v>
+      </c>
+      <c r="N35" s="28" t="n">
+        <f aca="false">IFERROR(M35/J35,"")</f>
+        <v>134</v>
+      </c>
+      <c r="O35" s="28" t="n">
+        <f aca="false">IFERROR(M35/I35,"")</f>
+        <v>312.666666666667</v>
+      </c>
+      <c r="P35" s="16"/>
+    </row>
+    <row r="36" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F36" s="28" t="n">
+        <v>1413</v>
+      </c>
+      <c r="G36" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="21" t="n">
+        <f aca="false">G36+H36</f>
+        <v>4</v>
+      </c>
+      <c r="J36" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K36" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L36" s="97" t="n">
+        <f aca="false">IF(K36="","",J36-K36)</f>
+        <v>0</v>
+      </c>
+      <c r="M36" s="28" t="n">
+        <v>931</v>
+      </c>
+      <c r="N36" s="28" t="n">
+        <f aca="false">IFERROR(M36/J36,"")</f>
+        <v>133</v>
+      </c>
+      <c r="O36" s="28" t="n">
+        <f aca="false">IFERROR(M36/I36,"")</f>
+        <v>232.75</v>
+      </c>
+      <c r="P36" s="16"/>
+    </row>
+    <row r="37" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="21" t="n">
+        <f aca="false">G37+H37</f>
+        <v>7</v>
+      </c>
+      <c r="J37" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K37" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L37" s="97" t="n">
+        <f aca="false">IF(K37="","",J37-K37)</f>
+        <v>0</v>
+      </c>
+      <c r="M37" s="21"/>
+      <c r="N37" s="28" t="n">
+        <f aca="false">IFERROR(M37/J37,"")</f>
+        <v>0</v>
+      </c>
+      <c r="O37" s="28" t="n">
+        <f aca="false">IFERROR(M37/I37,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P37" s="16" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>971</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F38" s="28" t="n">
+        <v>10839</v>
+      </c>
+      <c r="G38" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H38" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" s="21" t="n">
+        <f aca="false">G38+H38</f>
+        <v>8</v>
+      </c>
+      <c r="J38" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K38" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L38" s="97" t="n">
+        <f aca="false">IF(K38="","",J38-K38)</f>
+        <v>0</v>
+      </c>
+      <c r="M38" s="21"/>
+      <c r="N38" s="28" t="n">
+        <f aca="false">IFERROR(M38/J38,"")</f>
+        <v>0</v>
+      </c>
+      <c r="O38" s="28" t="n">
+        <f aca="false">IFERROR(M38/I38,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P38" s="16" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F39" s="28" t="n">
+        <v>1463</v>
+      </c>
+      <c r="G39" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H39" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I39" s="21" t="n">
+        <f aca="false">G39+H39</f>
+        <v>8</v>
+      </c>
+      <c r="J39" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K39" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L39" s="97" t="n">
+        <f aca="false">IF(K39="","",J39-K39)</f>
+        <v>-1</v>
+      </c>
+      <c r="M39" s="21"/>
+      <c r="N39" s="28" t="n">
+        <f aca="false">IFERROR(M39/J39,"")</f>
+        <v>0</v>
+      </c>
+      <c r="O39" s="28" t="n">
+        <f aca="false">IFERROR(M39/I39,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P39" s="16" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C40" s="24" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F40" s="28" t="n">
+        <v>2262</v>
+      </c>
+      <c r="G40" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="21" t="n">
+        <f aca="false">G40+H40</f>
+        <v>4</v>
+      </c>
+      <c r="J40" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K40" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L40" s="97" t="n">
+        <f aca="false">IF(K40="","",J40-K40)</f>
+        <v>0</v>
+      </c>
+      <c r="M40" s="28" t="n">
+        <v>823</v>
+      </c>
+      <c r="N40" s="28" t="n">
+        <f aca="false">IFERROR(M40/J40,"")</f>
+        <v>137.166666666667</v>
+      </c>
+      <c r="O40" s="28" t="n">
+        <f aca="false">IFERROR(M40/I40,"")</f>
+        <v>205.75</v>
+      </c>
+      <c r="P40" s="16"/>
+    </row>
+    <row r="41" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>969</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F41" s="28" t="n">
+        <v>4361</v>
+      </c>
+      <c r="G41" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H41" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" s="21" t="n">
+        <f aca="false">G41+H41</f>
+        <v>6</v>
+      </c>
+      <c r="J41" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K41" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L41" s="97" t="n">
+        <f aca="false">IF(K41="","",J41-K41)</f>
+        <v>0</v>
+      </c>
+      <c r="M41" s="28" t="n">
+        <v>327</v>
+      </c>
+      <c r="N41" s="28" t="n">
+        <f aca="false">IFERROR(M41/J41,"")</f>
+        <v>54.5</v>
+      </c>
+      <c r="O41" s="28" t="n">
+        <f aca="false">IFERROR(M41/I41,"")</f>
+        <v>54.5</v>
+      </c>
+      <c r="P41" s="16"/>
+    </row>
+    <row r="42" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E42" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F42" s="28" t="n">
+        <v>3124</v>
+      </c>
+      <c r="G42" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H42" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="21" t="n">
+        <f aca="false">G42+H42</f>
+        <v>5</v>
+      </c>
+      <c r="J42" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K42" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L42" s="97" t="n">
+        <f aca="false">IF(K42="","",J42-K42)</f>
+        <v>0</v>
+      </c>
+      <c r="M42" s="28" t="n">
+        <v>538</v>
+      </c>
+      <c r="N42" s="28" t="n">
+        <f aca="false">IFERROR(M42/J42,"")</f>
+        <v>89.6666666666667</v>
+      </c>
+      <c r="O42" s="28" t="n">
+        <f aca="false">IFERROR(M42/I42,"")</f>
+        <v>107.6</v>
+      </c>
+      <c r="P42" s="16"/>
+    </row>
+    <row r="43" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C43" s="24" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E43" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F43" s="28" t="n">
+        <v>3375</v>
+      </c>
+      <c r="G43" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="21" t="n">
+        <f aca="false">G43+H43</f>
+        <v>6</v>
+      </c>
+      <c r="J43" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K43" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L43" s="97" t="n">
+        <f aca="false">IF(K43="","",J43-K43)</f>
+        <v>0</v>
+      </c>
+      <c r="M43" s="28" t="n">
+        <v>591</v>
+      </c>
+      <c r="N43" s="28" t="n">
+        <f aca="false">IFERROR(M43/J43,"")</f>
+        <v>98.5</v>
+      </c>
+      <c r="O43" s="28" t="n">
+        <f aca="false">IFERROR(M43/I43,"")</f>
+        <v>98.5</v>
+      </c>
+      <c r="P43" s="16"/>
+    </row>
+    <row r="44" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>967</v>
+      </c>
+      <c r="D44" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="E44" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F44" s="28" t="n">
+        <v>2486.43</v>
+      </c>
+      <c r="G44" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="21" t="n">
+        <f aca="false">G44+H44</f>
+        <v>4</v>
+      </c>
+      <c r="J44" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K44" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L44" s="97" t="n">
+        <f aca="false">IF(K44="","",J44-K44)</f>
+        <v>2</v>
+      </c>
+      <c r="M44" s="28" t="n">
+        <v>333</v>
+      </c>
+      <c r="N44" s="28" t="n">
+        <f aca="false">IFERROR(M44/J44,"")</f>
+        <v>55.5</v>
+      </c>
+      <c r="O44" s="28" t="n">
+        <f aca="false">IFERROR(M44/I44,"")</f>
+        <v>83.25</v>
+      </c>
+      <c r="P44" s="16"/>
+    </row>
+    <row r="45" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C45" s="24" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E45" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F45" s="28" t="n">
+        <v>7180</v>
+      </c>
+      <c r="G45" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H45" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I45" s="21" t="n">
+        <f aca="false">G45+H45</f>
+        <v>8</v>
+      </c>
+      <c r="J45" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K45" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L45" s="97" t="n">
+        <f aca="false">IF(K45="","",J45-K45)</f>
+        <v>0</v>
+      </c>
+      <c r="M45" s="28" t="n">
+        <v>441</v>
+      </c>
+      <c r="N45" s="28" t="n">
+        <f aca="false">IFERROR(M45/J45,"")</f>
+        <v>73.5</v>
+      </c>
+      <c r="O45" s="28" t="n">
+        <f aca="false">IFERROR(M45/I45,"")</f>
+        <v>55.125</v>
+      </c>
+      <c r="P45" s="16"/>
+    </row>
+    <row r="46" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="21" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C46" s="24" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D46" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="21" t="n">
+        <f aca="false">G46+H46</f>
+        <v>4</v>
+      </c>
+      <c r="J46" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K46" s="21"/>
+      <c r="L46" s="97" t="str">
+        <f aca="false">IF(K46="","",J46-K46)</f>
+        <v/>
+      </c>
+      <c r="M46" s="21"/>
+      <c r="N46" s="28" t="n">
+        <f aca="false">IFERROR(M46/J46,"")</f>
+        <v>0</v>
+      </c>
+      <c r="O46" s="28" t="n">
+        <f aca="false">IFERROR(M46/I46,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P46" s="16" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="21" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C47" s="24" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E47" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F47" s="21"/>
+      <c r="G47" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="21" t="n">
+        <f aca="false">G47+H47</f>
+        <v>4</v>
+      </c>
+      <c r="J47" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K47" s="21"/>
+      <c r="L47" s="97" t="str">
+        <f aca="false">IF(K47="","",J47-K47)</f>
+        <v/>
+      </c>
+      <c r="M47" s="21"/>
+      <c r="N47" s="28" t="n">
+        <f aca="false">IFERROR(M47/J47,"")</f>
+        <v>0</v>
+      </c>
+      <c r="O47" s="28" t="n">
+        <f aca="false">IFERROR(M47/I47,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P47" s="16" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C48" s="24" t="s">
+        <v>965</v>
+      </c>
+      <c r="D48" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F48" s="28" t="n">
+        <v>3270</v>
+      </c>
+      <c r="G48" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="21" t="n">
+        <f aca="false">G48+H48</f>
+        <v>6</v>
+      </c>
+      <c r="J48" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L48" s="97" t="n">
+        <f aca="false">IF(K48="","",J48-K48)</f>
+        <v>-1</v>
+      </c>
+      <c r="M48" s="28" t="n">
+        <v>456</v>
+      </c>
+      <c r="N48" s="28" t="n">
+        <f aca="false">IFERROR(M48/J48,"")</f>
+        <v>91.2</v>
+      </c>
+      <c r="O48" s="28" t="n">
+        <f aca="false">IFERROR(M48/I48,"")</f>
+        <v>76</v>
+      </c>
+      <c r="P48" s="16"/>
+    </row>
+    <row r="49" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C49" s="24" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E49" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F49" s="28" t="n">
+        <v>1754</v>
+      </c>
+      <c r="G49" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="21" t="n">
+        <f aca="false">G49+H49</f>
+        <v>6</v>
+      </c>
+      <c r="J49" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K49" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L49" s="97" t="n">
+        <f aca="false">IF(K49="","",J49-K49)</f>
+        <v>-1</v>
+      </c>
+      <c r="M49" s="28" t="n">
+        <v>586</v>
+      </c>
+      <c r="N49" s="28" t="n">
+        <f aca="false">IFERROR(M49/J49,"")</f>
+        <v>117.2</v>
+      </c>
+      <c r="O49" s="28" t="n">
+        <f aca="false">IFERROR(M49/I49,"")</f>
+        <v>97.6666666666667</v>
+      </c>
+      <c r="P49" s="16"/>
+    </row>
+    <row r="50" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C50" s="24" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="E50" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F50" s="28" t="n">
+        <v>7390</v>
+      </c>
+      <c r="G50" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="21" t="n">
+        <f aca="false">G50+H50</f>
+        <v>9</v>
+      </c>
+      <c r="J50" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L50" s="97" t="n">
+        <f aca="false">IF(K50="","",J50-K50)</f>
+        <v>0</v>
+      </c>
+      <c r="M50" s="28" t="n">
+        <v>402</v>
+      </c>
+      <c r="N50" s="28" t="n">
+        <f aca="false">IFERROR(M50/J50,"")</f>
+        <v>80.4</v>
+      </c>
+      <c r="O50" s="28" t="n">
+        <f aca="false">IFERROR(M50/I50,"")</f>
+        <v>44.6666666666667</v>
+      </c>
+      <c r="P50" s="16"/>
+    </row>
+    <row r="51" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E51" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F51" s="28" t="n">
+        <v>2641</v>
+      </c>
+      <c r="G51" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="21" t="n">
+        <f aca="false">G51+H51</f>
+        <v>6</v>
+      </c>
+      <c r="J51" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K51" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L51" s="97" t="n">
+        <f aca="false">IF(K51="","",J51-K51)</f>
+        <v>0</v>
+      </c>
+      <c r="M51" s="28" t="n">
+        <v>685</v>
+      </c>
+      <c r="N51" s="28" t="n">
+        <f aca="false">IFERROR(M51/J51,"")</f>
+        <v>137</v>
+      </c>
+      <c r="O51" s="28" t="n">
+        <f aca="false">IFERROR(M51/I51,"")</f>
+        <v>114.166666666667</v>
+      </c>
+      <c r="P51" s="16"/>
+    </row>
+    <row r="52" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D52" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E52" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F52" s="28" t="n">
+        <v>3211</v>
+      </c>
+      <c r="G52" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H52" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="21" t="n">
+        <f aca="false">G52+H52</f>
+        <v>4</v>
+      </c>
+      <c r="J52" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L52" s="97" t="n">
+        <f aca="false">IF(K52="","",J52-K52)</f>
+        <v>-1</v>
+      </c>
+      <c r="M52" s="28" t="n">
+        <v>455</v>
+      </c>
+      <c r="N52" s="28" t="n">
+        <f aca="false">IFERROR(M52/J52,"")</f>
+        <v>91</v>
+      </c>
+      <c r="O52" s="28" t="n">
+        <f aca="false">IFERROR(M52/I52,"")</f>
+        <v>113.75</v>
+      </c>
+      <c r="P52" s="16"/>
+    </row>
+    <row r="53" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="21" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>974</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E53" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F53" s="21"/>
+      <c r="G53" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="21" t="n">
+        <f aca="false">G53+H53</f>
+        <v>6</v>
+      </c>
+      <c r="J53" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" s="21"/>
+      <c r="L53" s="97" t="str">
+        <f aca="false">IF(K53="","",J53-K53)</f>
+        <v/>
+      </c>
+      <c r="M53" s="21"/>
+      <c r="N53" s="28" t="n">
+        <f aca="false">IFERROR(M53/J53,"")</f>
+        <v>0</v>
+      </c>
+      <c r="O53" s="28" t="n">
+        <f aca="false">IFERROR(M53/I53,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P53" s="16" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C54" s="24" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E54" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F54" s="28" t="n">
+        <v>5894</v>
+      </c>
+      <c r="G54" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H54" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="21" t="n">
+        <f aca="false">G54+H54</f>
+        <v>7</v>
+      </c>
+      <c r="J54" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K54" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L54" s="97" t="n">
+        <f aca="false">IF(K54="","",J54-K54)</f>
+        <v>0</v>
+      </c>
+      <c r="M54" s="28" t="n">
+        <v>408</v>
+      </c>
+      <c r="N54" s="28" t="n">
+        <f aca="false">IFERROR(M54/J54,"")</f>
+        <v>102</v>
+      </c>
+      <c r="O54" s="28" t="n">
+        <f aca="false">IFERROR(M54/I54,"")</f>
+        <v>58.2857142857143</v>
+      </c>
+      <c r="P54" s="16"/>
+    </row>
+    <row r="55" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="21" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C55" s="24" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D55" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E55" s="21" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F55" s="28" t="n">
+        <v>7276</v>
+      </c>
+      <c r="G55" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H55" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" s="21" t="n">
+        <f aca="false">G55+H55</f>
+        <v>6</v>
+      </c>
+      <c r="J55" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K55" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L55" s="97" t="n">
+        <f aca="false">IF(K55="","",J55-K55)</f>
+        <v>0</v>
+      </c>
+      <c r="M55" s="28" t="n">
+        <v>281</v>
+      </c>
+      <c r="N55" s="28" t="n">
+        <f aca="false">IFERROR(M55/J55,"")</f>
+        <v>70.25</v>
+      </c>
+      <c r="O55" s="28" t="n">
+        <f aca="false">IFERROR(M55/I55,"")</f>
+        <v>46.8333333333333</v>
+      </c>
+      <c r="P55" s="16"/>
+    </row>
+    <row r="56" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="21" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E56" s="21" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F56" s="21"/>
+      <c r="G56" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H56" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="21" t="n">
+        <f aca="false">G56+H56</f>
+        <v>4</v>
+      </c>
+      <c r="J56" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K56" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L56" s="97" t="n">
+        <f aca="false">IF(K56="","",J56-K56)</f>
+        <v>0</v>
+      </c>
+      <c r="M56" s="21"/>
+      <c r="N56" s="28" t="n">
+        <f aca="false">IFERROR(M56/J56,"")</f>
+        <v>0</v>
+      </c>
+      <c r="O56" s="28" t="n">
+        <f aca="false">IFERROR(M56/I56,"")</f>
+        <v>0</v>
+      </c>
+      <c r="P56" s="16" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="32"/>
+      <c r="B57" s="32"/>
+      <c r="C57" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="34" t="n">
+        <f aca="false">SUM(G5:G56)</f>
+        <v>359</v>
+      </c>
+      <c r="H57" s="34" t="n">
+        <f aca="false">SUM(H5:H56)</f>
+        <v>52</v>
+      </c>
+      <c r="I57" s="34" t="n">
+        <f aca="false">SUM(I5:I56)</f>
+        <v>411</v>
+      </c>
+      <c r="J57" s="34" t="n">
+        <f aca="false">SUM(J5:J56)</f>
+        <v>498</v>
+      </c>
+      <c r="K57" s="34" t="n">
+        <f aca="false">SUM(K5:K56)</f>
+        <v>475</v>
+      </c>
+      <c r="L57" s="34" t="n">
+        <f aca="false">SUM(L5:L56)</f>
+        <v>6</v>
+      </c>
+      <c r="M57" s="34" t="n">
+        <f aca="false">SUM(M5:M56)</f>
+        <v>36776</v>
+      </c>
+      <c r="N57" s="34" t="n">
+        <f aca="false">IFERROR(M57/J57,"")</f>
+        <v>73.8473895582329</v>
+      </c>
+      <c r="O57" s="34" t="n">
+        <f aca="false">IFERROR(M57/I57,"")</f>
+        <v>89.4793187347932</v>
+      </c>
+      <c r="P57" s="32"/>
+    </row>
+    <row r="59" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B59" s="52" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C59" s="53" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D59" s="53"/>
+      <c r="E59" s="53"/>
+      <c r="F59" s="53"/>
+      <c r="G59" s="53"/>
+      <c r="H59" s="53"/>
+      <c r="I59" s="53"/>
+      <c r="J59" s="53"/>
+      <c r="K59" s="53"/>
+      <c r="L59" s="53"/>
+      <c r="M59" s="53"/>
+      <c r="N59" s="53"/>
+      <c r="O59" s="53"/>
+      <c r="P59" s="53"/>
+    </row>
+    <row r="60" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B60" s="52" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C60" s="53" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D60" s="53"/>
+      <c r="E60" s="53"/>
+      <c r="F60" s="53"/>
+      <c r="G60" s="53"/>
+      <c r="H60" s="53"/>
+      <c r="I60" s="53"/>
+      <c r="J60" s="53"/>
+      <c r="K60" s="53"/>
+      <c r="L60" s="53"/>
+      <c r="M60" s="53"/>
+      <c r="N60" s="53"/>
+      <c r="O60" s="53"/>
+      <c r="P60" s="53"/>
+    </row>
+    <row r="61" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B61" s="54" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C61" s="53" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D61" s="53"/>
+      <c r="E61" s="53"/>
+      <c r="F61" s="53"/>
+      <c r="G61" s="53"/>
+      <c r="H61" s="53"/>
+      <c r="I61" s="53"/>
+      <c r="J61" s="53"/>
+      <c r="K61" s="53"/>
+      <c r="L61" s="53"/>
+      <c r="M61" s="53"/>
+      <c r="N61" s="53"/>
+      <c r="O61" s="53"/>
+      <c r="P61" s="53"/>
+    </row>
+    <row r="62" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B62" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C62" s="53" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D62" s="53"/>
+      <c r="E62" s="53"/>
+      <c r="F62" s="53"/>
+      <c r="G62" s="53"/>
+      <c r="H62" s="53"/>
+      <c r="I62" s="53"/>
+      <c r="J62" s="53"/>
+      <c r="K62" s="53"/>
+      <c r="L62" s="53"/>
+      <c r="M62" s="53"/>
+      <c r="N62" s="53"/>
+      <c r="O62" s="53"/>
+      <c r="P62" s="53"/>
+    </row>
+    <row r="63" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B63" s="54" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C63" s="53" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D63" s="53"/>
+      <c r="E63" s="53"/>
+      <c r="F63" s="53"/>
+      <c r="G63" s="53"/>
+      <c r="H63" s="53"/>
+      <c r="I63" s="53"/>
+      <c r="J63" s="53"/>
+      <c r="K63" s="53"/>
+      <c r="L63" s="53"/>
+      <c r="M63" s="53"/>
+      <c r="N63" s="53"/>
+      <c r="O63" s="53"/>
+      <c r="P63" s="53"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="C59:P59"/>
+    <mergeCell ref="C60:P60"/>
+    <mergeCell ref="C61:P61"/>
+    <mergeCell ref="C62:P62"/>
+    <mergeCell ref="C63:P63"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:O18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -13778,7 +17018,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1138</v>
+        <v>1192</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13797,7 +17037,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1139</v>
+        <v>1193</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -13828,86 +17068,86 @@
         <v>55</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>1140</v>
+        <v>1194</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1141</v>
+        <v>1195</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1142</v>
+        <v>1196</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1143</v>
+        <v>1197</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>58</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>1144</v>
+        <v>1198</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>1145</v>
+        <v>1199</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>59</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>1146</v>
+        <v>1200</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>1147</v>
+        <v>1201</v>
       </c>
       <c r="O3" s="15" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="97" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B4" s="98" t="s">
-        <v>1149</v>
-      </c>
-      <c r="C4" s="97" t="s">
+      <c r="A4" s="98" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B4" s="99" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C4" s="98" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="98" t="s">
-        <v>1150</v>
-      </c>
-      <c r="E4" s="97" t="n">
+      <c r="D4" s="99" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E4" s="98" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="97" t="s">
-        <v>1151</v>
-      </c>
-      <c r="G4" s="98" t="s">
-        <v>1152</v>
-      </c>
-      <c r="H4" s="97" t="n">
+      <c r="F4" s="98" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G4" s="99" t="s">
+        <v>1206</v>
+      </c>
+      <c r="H4" s="98" t="n">
         <v>20</v>
       </c>
-      <c r="I4" s="97" t="n">
+      <c r="I4" s="98" t="n">
         <f aca="false">IF(H4="","",H4-E4)</f>
         <v>14</v>
       </c>
-      <c r="J4" s="99" t="n">
+      <c r="J4" s="100" t="n">
         <f aca="false">IFERROR(IF(H4="","",(H4-E4)/E4),"")</f>
         <v>2.33333333333333</v>
       </c>
-      <c r="K4" s="98" t="s">
-        <v>1153</v>
-      </c>
-      <c r="L4" s="97" t="s">
+      <c r="K4" s="99" t="s">
+        <v>1207</v>
+      </c>
+      <c r="L4" s="98" t="s">
         <v>78</v>
       </c>
-      <c r="M4" s="98" t="s">
-        <v>1154</v>
-      </c>
-      <c r="N4" s="98" t="s">
-        <v>1155</v>
-      </c>
-      <c r="O4" s="97" t="s">
-        <v>1156</v>
+      <c r="M4" s="99" t="s">
+        <v>1208</v>
+      </c>
+      <c r="N4" s="99" t="s">
+        <v>1209</v>
+      </c>
+      <c r="O4" s="98" t="s">
+        <v>1210</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13923,17 +17163,17 @@
       <c r="D5" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="100" t="n">
+      <c r="E5" s="101" t="n">
         <v>1271</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>1157</v>
+        <v>1211</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>1158</v>
-      </c>
-      <c r="H5" s="101"/>
-      <c r="I5" s="100" t="str">
+        <v>1212</v>
+      </c>
+      <c r="H5" s="102"/>
+      <c r="I5" s="101" t="str">
         <f aca="false">IF(H5="","",H5-E5)</f>
         <v/>
       </c>
@@ -13941,15 +17181,15 @@
         <f aca="false">IFERROR(IF(H5="","",(H5-E5)/E5),"")</f>
         <v/>
       </c>
-      <c r="K5" s="102"/>
+      <c r="K5" s="103"/>
       <c r="L5" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M5" s="102"/>
+      <c r="M5" s="103"/>
       <c r="N5" s="16" t="s">
-        <v>1159</v>
-      </c>
-      <c r="O5" s="103"/>
+        <v>1213</v>
+      </c>
+      <c r="O5" s="104"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="n">
@@ -13964,17 +17204,17 @@
       <c r="D6" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="100" t="n">
+      <c r="E6" s="101" t="n">
         <v>25</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>1160</v>
+        <v>1214</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>1161</v>
-      </c>
-      <c r="H6" s="101"/>
-      <c r="I6" s="100" t="str">
+        <v>1215</v>
+      </c>
+      <c r="H6" s="102"/>
+      <c r="I6" s="101" t="str">
         <f aca="false">IF(H6="","",H6-E6)</f>
         <v/>
       </c>
@@ -13982,15 +17222,15 @@
         <f aca="false">IFERROR(IF(H6="","",(H6-E6)/E6),"")</f>
         <v/>
       </c>
-      <c r="K6" s="102"/>
+      <c r="K6" s="103"/>
       <c r="L6" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M6" s="102"/>
+      <c r="M6" s="103"/>
       <c r="N6" s="16" t="s">
-        <v>1162</v>
-      </c>
-      <c r="O6" s="103"/>
+        <v>1216</v>
+      </c>
+      <c r="O6" s="104"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="n">
@@ -14005,17 +17245,17 @@
       <c r="D7" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="100" t="n">
+      <c r="E7" s="101" t="n">
         <v>39</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>1163</v>
+        <v>1217</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>1152</v>
-      </c>
-      <c r="H7" s="101"/>
-      <c r="I7" s="100" t="str">
+        <v>1206</v>
+      </c>
+      <c r="H7" s="102"/>
+      <c r="I7" s="101" t="str">
         <f aca="false">IF(H7="","",H7-E7)</f>
         <v/>
       </c>
@@ -14023,15 +17263,15 @@
         <f aca="false">IFERROR(IF(H7="","",(H7-E7)/E7),"")</f>
         <v/>
       </c>
-      <c r="K7" s="102"/>
+      <c r="K7" s="103"/>
       <c r="L7" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M7" s="102"/>
+      <c r="M7" s="103"/>
       <c r="N7" s="16" t="s">
-        <v>1164</v>
-      </c>
-      <c r="O7" s="103"/>
+        <v>1218</v>
+      </c>
+      <c r="O7" s="104"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="n">
@@ -14046,17 +17286,17 @@
       <c r="D8" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="100" t="n">
+      <c r="E8" s="101" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>1165</v>
+        <v>1219</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>1166</v>
-      </c>
-      <c r="H8" s="101"/>
-      <c r="I8" s="100" t="str">
+        <v>1220</v>
+      </c>
+      <c r="H8" s="102"/>
+      <c r="I8" s="101" t="str">
         <f aca="false">IF(H8="","",H8-E8)</f>
         <v/>
       </c>
@@ -14064,40 +17304,40 @@
         <f aca="false">IFERROR(IF(H8="","",(H8-E8)/E8),"")</f>
         <v/>
       </c>
-      <c r="K8" s="102"/>
+      <c r="K8" s="103"/>
       <c r="L8" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="102"/>
+      <c r="M8" s="103"/>
       <c r="N8" s="16" t="s">
-        <v>1167</v>
-      </c>
-      <c r="O8" s="103"/>
+        <v>1221</v>
+      </c>
+      <c r="O8" s="104"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1168</v>
+        <v>1222</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>53</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>1169</v>
-      </c>
-      <c r="E9" s="100" t="n">
+        <v>1223</v>
+      </c>
+      <c r="E9" s="101" t="n">
         <v>0.28</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>1170</v>
+        <v>1224</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>1171</v>
-      </c>
-      <c r="H9" s="101"/>
-      <c r="I9" s="100" t="str">
+        <v>1225</v>
+      </c>
+      <c r="H9" s="102"/>
+      <c r="I9" s="101" t="str">
         <f aca="false">IF(H9="","",H9-E9)</f>
         <v/>
       </c>
@@ -14105,22 +17345,22 @@
         <f aca="false">IFERROR(IF(H9="","",(H9-E9)/E9),"")</f>
         <v/>
       </c>
-      <c r="K9" s="102"/>
+      <c r="K9" s="103"/>
       <c r="L9" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="M9" s="102"/>
+      <c r="M9" s="103"/>
       <c r="N9" s="16" t="s">
-        <v>1172</v>
-      </c>
-      <c r="O9" s="103"/>
+        <v>1226</v>
+      </c>
+      <c r="O9" s="104"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1173</v>
+        <v>1227</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>53</v>
@@ -14128,17 +17368,17 @@
       <c r="D10" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="E10" s="100" t="n">
+      <c r="E10" s="101" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>1174</v>
+        <v>1228</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>1175</v>
-      </c>
-      <c r="H10" s="101"/>
-      <c r="I10" s="100" t="str">
+        <v>1229</v>
+      </c>
+      <c r="H10" s="102"/>
+      <c r="I10" s="101" t="str">
         <f aca="false">IF(H10="","",H10-E10)</f>
         <v/>
       </c>
@@ -14146,15 +17386,15 @@
         <f aca="false">IFERROR(IF(H10="","",(H10-E10)/E10),"")</f>
         <v/>
       </c>
-      <c r="K10" s="102"/>
+      <c r="K10" s="103"/>
       <c r="L10" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M10" s="102"/>
+      <c r="M10" s="103"/>
       <c r="N10" s="16" t="s">
-        <v>1176</v>
-      </c>
-      <c r="O10" s="103"/>
+        <v>1230</v>
+      </c>
+      <c r="O10" s="104"/>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="n">
@@ -14167,19 +17407,19 @@
         <v>95</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>1177</v>
-      </c>
-      <c r="E11" s="100" t="n">
+        <v>1231</v>
+      </c>
+      <c r="E11" s="101" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>1178</v>
+        <v>1232</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>1179</v>
-      </c>
-      <c r="H11" s="101"/>
-      <c r="I11" s="100" t="str">
+        <v>1233</v>
+      </c>
+      <c r="H11" s="102"/>
+      <c r="I11" s="101" t="str">
         <f aca="false">IF(H11="","",H11-E11)</f>
         <v/>
       </c>
@@ -14187,15 +17427,15 @@
         <f aca="false">IFERROR(IF(H11="","",(H11-E11)/E11),"")</f>
         <v/>
       </c>
-      <c r="K11" s="102"/>
+      <c r="K11" s="103"/>
       <c r="L11" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="M11" s="102"/>
+      <c r="M11" s="103"/>
       <c r="N11" s="16" t="s">
-        <v>1180</v>
-      </c>
-      <c r="O11" s="103"/>
+        <v>1234</v>
+      </c>
+      <c r="O11" s="104"/>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="n">
@@ -14210,17 +17450,17 @@
       <c r="D12" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="100" t="n">
+      <c r="E12" s="101" t="n">
         <v>31</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>1181</v>
+        <v>1235</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>1182</v>
-      </c>
-      <c r="H12" s="101"/>
-      <c r="I12" s="100" t="str">
+        <v>1236</v>
+      </c>
+      <c r="H12" s="102"/>
+      <c r="I12" s="101" t="str">
         <f aca="false">IF(H12="","",H12-E12)</f>
         <v/>
       </c>
@@ -14228,15 +17468,15 @@
         <f aca="false">IFERROR(IF(H12="","",(H12-E12)/E12),"")</f>
         <v/>
       </c>
-      <c r="K12" s="102"/>
+      <c r="K12" s="103"/>
       <c r="L12" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M12" s="102"/>
+      <c r="M12" s="103"/>
       <c r="N12" s="16" t="s">
-        <v>1183</v>
-      </c>
-      <c r="O12" s="103"/>
+        <v>1237</v>
+      </c>
+      <c r="O12" s="104"/>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="n">
@@ -14251,17 +17491,17 @@
       <c r="D13" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="E13" s="100" t="n">
+      <c r="E13" s="101" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>1184</v>
+        <v>1238</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>1185</v>
-      </c>
-      <c r="H13" s="101"/>
-      <c r="I13" s="100" t="str">
+        <v>1239</v>
+      </c>
+      <c r="H13" s="102"/>
+      <c r="I13" s="101" t="str">
         <f aca="false">IF(H13="","",H13-E13)</f>
         <v/>
       </c>
@@ -14269,15 +17509,15 @@
         <f aca="false">IFERROR(IF(H13="","",(H13-E13)/E13),"")</f>
         <v/>
       </c>
-      <c r="K13" s="102"/>
+      <c r="K13" s="103"/>
       <c r="L13" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M13" s="102"/>
+      <c r="M13" s="103"/>
       <c r="N13" s="16" t="s">
-        <v>1186</v>
-      </c>
-      <c r="O13" s="103"/>
+        <v>1240</v>
+      </c>
+      <c r="O13" s="104"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="n">
@@ -14292,17 +17532,17 @@
       <c r="D14" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="E14" s="100" t="n">
+      <c r="E14" s="101" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>1187</v>
+        <v>1241</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>1188</v>
-      </c>
-      <c r="H14" s="101"/>
-      <c r="I14" s="100" t="str">
+        <v>1242</v>
+      </c>
+      <c r="H14" s="102"/>
+      <c r="I14" s="101" t="str">
         <f aca="false">IF(H14="","",H14-E14)</f>
         <v/>
       </c>
@@ -14310,15 +17550,15 @@
         <f aca="false">IFERROR(IF(H14="","",(H14-E14)/E14),"")</f>
         <v/>
       </c>
-      <c r="K14" s="102"/>
+      <c r="K14" s="103"/>
       <c r="L14" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="102"/>
+      <c r="M14" s="103"/>
       <c r="N14" s="16" t="s">
-        <v>1189</v>
-      </c>
-      <c r="O14" s="103"/>
+        <v>1243</v>
+      </c>
+      <c r="O14" s="104"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="n">
@@ -14331,19 +17571,19 @@
         <v>52</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>1150</v>
-      </c>
-      <c r="E15" s="100" t="n">
+        <v>1204</v>
+      </c>
+      <c r="E15" s="101" t="n">
         <v>6</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>1178</v>
+        <v>1232</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>1190</v>
-      </c>
-      <c r="H15" s="101"/>
-      <c r="I15" s="100" t="str">
+        <v>1244</v>
+      </c>
+      <c r="H15" s="102"/>
+      <c r="I15" s="101" t="str">
         <f aca="false">IF(H15="","",H15-E15)</f>
         <v/>
       </c>
@@ -14351,15 +17591,15 @@
         <f aca="false">IFERROR(IF(H15="","",(H15-E15)/E15),"")</f>
         <v/>
       </c>
-      <c r="K15" s="102"/>
+      <c r="K15" s="103"/>
       <c r="L15" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M15" s="102"/>
+      <c r="M15" s="103"/>
       <c r="N15" s="16" t="s">
-        <v>1191</v>
-      </c>
-      <c r="O15" s="103"/>
+        <v>1245</v>
+      </c>
+      <c r="O15" s="104"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="n">
@@ -14372,19 +17612,19 @@
         <v>52</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>1192</v>
-      </c>
-      <c r="E16" s="100" t="n">
+        <v>1246</v>
+      </c>
+      <c r="E16" s="101" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>1193</v>
+        <v>1247</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>1194</v>
-      </c>
-      <c r="H16" s="101"/>
-      <c r="I16" s="100" t="str">
+        <v>1248</v>
+      </c>
+      <c r="H16" s="102"/>
+      <c r="I16" s="101" t="str">
         <f aca="false">IF(H16="","",H16-E16)</f>
         <v/>
       </c>
@@ -14392,31 +17632,31 @@
         <f aca="false">IFERROR(IF(H16="","",(H16-E16)/E16),"")</f>
         <v/>
       </c>
-      <c r="K16" s="102"/>
+      <c r="K16" s="103"/>
       <c r="L16" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M16" s="102"/>
+      <c r="M16" s="103"/>
       <c r="N16" s="16" t="s">
-        <v>1195</v>
-      </c>
-      <c r="O16" s="103"/>
+        <v>1249</v>
+      </c>
+      <c r="O16" s="104"/>
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C18" s="104" t="s">
-        <v>1197</v>
-      </c>
-      <c r="D18" s="104"/>
-      <c r="E18" s="104"/>
-      <c r="F18" s="104"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="104"/>
-      <c r="I18" s="104"/>
-      <c r="J18" s="104"/>
-      <c r="K18" s="104"/>
+        <v>1250</v>
+      </c>
+      <c r="C18" s="105" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D18" s="105"/>
+      <c r="E18" s="105"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="105"/>
+      <c r="H18" s="105"/>
+      <c r="I18" s="105"/>
+      <c r="J18" s="105"/>
+      <c r="K18" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -14434,7 +17674,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -14468,7 +17708,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1198</v>
+        <v>1252</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -14489,52 +17729,52 @@
         <v>50</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>1147</v>
+        <v>1201</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>1140</v>
+        <v>1194</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>1199</v>
+        <v>1253</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1200</v>
+        <v>1254</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1201</v>
+        <v>1255</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1202</v>
+        <v>1256</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>1143</v>
+        <v>1197</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>1203</v>
+        <v>1257</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>1204</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="105" t="n">
+      <c r="A4" s="106" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="106" t="s">
-        <v>1159</v>
-      </c>
-      <c r="D4" s="107" t="n">
+      <c r="C4" s="107" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D4" s="108" t="n">
         <f aca="false">'الخطة التنفيذية'!E5</f>
         <v>1271</v>
       </c>
-      <c r="E4" s="101"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="101"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="107" t="str">
+      <c r="E4" s="102"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="102"/>
+      <c r="H4" s="102"/>
+      <c r="I4" s="108" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H5="","",'الخطة التنفيذية'!H5)</f>
         <v/>
       </c>
@@ -14548,24 +17788,24 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="105" t="n">
+      <c r="A5" s="106" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="106" t="s">
-        <v>1162</v>
-      </c>
-      <c r="D5" s="107" t="n">
+      <c r="C5" s="107" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D5" s="108" t="n">
         <f aca="false">'الخطة التنفيذية'!E6</f>
         <v>25</v>
       </c>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
-      <c r="H5" s="101"/>
-      <c r="I5" s="107" t="str">
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="102"/>
+      <c r="H5" s="102"/>
+      <c r="I5" s="108" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H6="","",'الخطة التنفيذية'!H6)</f>
         <v/>
       </c>
@@ -14579,24 +17819,24 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="105" t="n">
+      <c r="A6" s="106" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="106" t="s">
-        <v>1164</v>
-      </c>
-      <c r="D6" s="107" t="n">
+      <c r="C6" s="107" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D6" s="108" t="n">
         <f aca="false">'الخطة التنفيذية'!E7</f>
         <v>39</v>
       </c>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="101"/>
-      <c r="H6" s="101"/>
-      <c r="I6" s="107" t="str">
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="108" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H7="","",'الخطة التنفيذية'!H7)</f>
         <v/>
       </c>
@@ -14610,24 +17850,24 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="105" t="n">
+      <c r="A7" s="106" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="106" t="s">
-        <v>1167</v>
-      </c>
-      <c r="D7" s="107" t="n">
+      <c r="C7" s="107" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D7" s="108" t="n">
         <f aca="false">'الخطة التنفيذية'!E8</f>
         <v>0</v>
       </c>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="101"/>
-      <c r="H7" s="101"/>
-      <c r="I7" s="107" t="str">
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="108" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H8="","",'الخطة التنفيذية'!H8)</f>
         <v/>
       </c>
@@ -14641,24 +17881,24 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="105" t="n">
+      <c r="A8" s="106" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>1168</v>
-      </c>
-      <c r="C8" s="106" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D8" s="107" t="n">
+        <v>1222</v>
+      </c>
+      <c r="C8" s="107" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D8" s="108" t="n">
         <f aca="false">'الخطة التنفيذية'!E9</f>
         <v>0.28</v>
       </c>
-      <c r="E8" s="101"/>
-      <c r="F8" s="101"/>
-      <c r="G8" s="101"/>
-      <c r="H8" s="101"/>
-      <c r="I8" s="107" t="str">
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="102"/>
+      <c r="I8" s="108" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H9="","",'الخطة التنفيذية'!H9)</f>
         <v/>
       </c>
@@ -14672,24 +17912,24 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="105" t="n">
+      <c r="A9" s="106" t="n">
         <v>6</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C9" s="106" t="s">
-        <v>1176</v>
-      </c>
-      <c r="D9" s="107" t="n">
+        <v>1227</v>
+      </c>
+      <c r="C9" s="107" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D9" s="108" t="n">
         <f aca="false">'الخطة التنفيذية'!E10</f>
         <v>0</v>
       </c>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
-      <c r="H9" s="101"/>
-      <c r="I9" s="107" t="str">
+      <c r="E9" s="102"/>
+      <c r="F9" s="102"/>
+      <c r="G9" s="102"/>
+      <c r="H9" s="102"/>
+      <c r="I9" s="108" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H10="","",'الخطة التنفيذية'!H10)</f>
         <v/>
       </c>
@@ -14703,24 +17943,24 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="105" t="n">
+      <c r="A10" s="106" t="n">
         <v>7</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="106" t="s">
-        <v>1180</v>
-      </c>
-      <c r="D10" s="107" t="n">
+      <c r="C10" s="107" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D10" s="108" t="n">
         <f aca="false">'الخطة التنفيذية'!E11</f>
         <v>0</v>
       </c>
-      <c r="E10" s="101"/>
-      <c r="F10" s="101"/>
-      <c r="G10" s="101"/>
-      <c r="H10" s="101"/>
-      <c r="I10" s="107" t="str">
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="108" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H11="","",'الخطة التنفيذية'!H11)</f>
         <v/>
       </c>
@@ -14734,24 +17974,24 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="105" t="n">
+      <c r="A11" s="106" t="n">
         <v>8</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="106" t="s">
-        <v>1183</v>
-      </c>
-      <c r="D11" s="107" t="n">
+      <c r="C11" s="107" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D11" s="108" t="n">
         <f aca="false">'الخطة التنفيذية'!E12</f>
         <v>31</v>
       </c>
-      <c r="E11" s="101"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="101"/>
-      <c r="H11" s="101"/>
-      <c r="I11" s="107" t="str">
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="102"/>
+      <c r="I11" s="108" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H12="","",'الخطة التنفيذية'!H12)</f>
         <v/>
       </c>
@@ -14765,24 +18005,24 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="105" t="n">
+      <c r="A12" s="106" t="n">
         <v>9</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="C12" s="106" t="s">
-        <v>1186</v>
-      </c>
-      <c r="D12" s="107" t="n">
+      <c r="C12" s="107" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D12" s="108" t="n">
         <f aca="false">'الخطة التنفيذية'!E13</f>
         <v>0</v>
       </c>
-      <c r="E12" s="101"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="101"/>
-      <c r="H12" s="101"/>
-      <c r="I12" s="107" t="str">
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="102"/>
+      <c r="I12" s="108" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H13="","",'الخطة التنفيذية'!H13)</f>
         <v/>
       </c>
@@ -14796,24 +18036,24 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="105" t="n">
+      <c r="A13" s="106" t="n">
         <v>10</v>
       </c>
       <c r="B13" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="106" t="s">
-        <v>1189</v>
-      </c>
-      <c r="D13" s="107" t="n">
+      <c r="C13" s="107" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D13" s="108" t="n">
         <f aca="false">'الخطة التنفيذية'!E14</f>
         <v>0</v>
       </c>
-      <c r="E13" s="101"/>
-      <c r="F13" s="101"/>
-      <c r="G13" s="101"/>
-      <c r="H13" s="101"/>
-      <c r="I13" s="107" t="str">
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="102"/>
+      <c r="H13" s="102"/>
+      <c r="I13" s="108" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H14="","",'الخطة التنفيذية'!H14)</f>
         <v/>
       </c>
@@ -14827,24 +18067,24 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="105" t="n">
+      <c r="A14" s="106" t="n">
         <v>11</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="106" t="s">
-        <v>1191</v>
-      </c>
-      <c r="D14" s="107" t="n">
+      <c r="C14" s="107" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D14" s="108" t="n">
         <f aca="false">'الخطة التنفيذية'!E15</f>
         <v>6</v>
       </c>
-      <c r="E14" s="101"/>
-      <c r="F14" s="101"/>
-      <c r="G14" s="101"/>
-      <c r="H14" s="101"/>
-      <c r="I14" s="107" t="str">
+      <c r="E14" s="102"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="102"/>
+      <c r="H14" s="102"/>
+      <c r="I14" s="108" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H15="","",'الخطة التنفيذية'!H15)</f>
         <v/>
       </c>
@@ -14858,24 +18098,24 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="105" t="n">
+      <c r="A15" s="106" t="n">
         <v>12</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="106" t="s">
-        <v>1195</v>
-      </c>
-      <c r="D15" s="107" t="n">
+      <c r="C15" s="107" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D15" s="108" t="n">
         <f aca="false">'الخطة التنفيذية'!E16</f>
         <v>0</v>
       </c>
-      <c r="E15" s="101"/>
-      <c r="F15" s="101"/>
-      <c r="G15" s="101"/>
-      <c r="H15" s="101"/>
-      <c r="I15" s="107" t="str">
+      <c r="E15" s="102"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="102"/>
+      <c r="I15" s="108" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H16="","",'الخطة التنفيذية'!H16)</f>
         <v/>
       </c>
@@ -14903,7 +18143,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -14927,7 +18167,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1205</v>
+        <v>1259</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -14945,7 +18185,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1206</v>
+        <v>1260</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -14966,34 +18206,34 @@
         <v>49</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>1207</v>
+        <v>1261</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>50</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>1208</v>
+        <v>1262</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>59</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1146</v>
+        <v>1200</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1209</v>
+        <v>1263</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1210</v>
+        <v>1264</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>1211</v>
+        <v>1265</v>
       </c>
       <c r="J3" s="15" t="s">
         <v>60</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>1212</v>
+        <v>1266</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>679</v>
@@ -15002,561 +18242,561 @@
         <v>383</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>1213</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="97" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B4" s="98" t="s">
-        <v>1214</v>
-      </c>
-      <c r="C4" s="97" t="s">
+      <c r="A4" s="98" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B4" s="99" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C4" s="98" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="97" t="s">
+      <c r="D4" s="98" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="97" t="s">
+      <c r="E4" s="98" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="97" t="s">
-        <v>1154</v>
-      </c>
-      <c r="G4" s="108" t="n">
+      <c r="F4" s="98" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G4" s="109" t="n">
         <v>46235</v>
       </c>
-      <c r="H4" s="108" t="n">
+      <c r="H4" s="109" t="n">
         <v>46326</v>
       </c>
-      <c r="I4" s="97" t="n">
+      <c r="I4" s="98" t="n">
         <f aca="false">IF(OR(G4="",H4=""),"",H4-G4)</f>
         <v>91</v>
       </c>
-      <c r="J4" s="97" t="n">
+      <c r="J4" s="98" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="97" t="s">
-        <v>1215</v>
-      </c>
-      <c r="L4" s="98" t="s">
-        <v>1216</v>
-      </c>
-      <c r="M4" s="97" t="s">
-        <v>1156</v>
-      </c>
-      <c r="N4" s="109" t="n">
+      <c r="K4" s="98" t="s">
+        <v>1269</v>
+      </c>
+      <c r="L4" s="99" t="s">
+        <v>1270</v>
+      </c>
+      <c r="M4" s="98" t="s">
+        <v>1210</v>
+      </c>
+      <c r="N4" s="110" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="105" t="n">
+      <c r="A5" s="106" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="110"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="111"/>
+      <c r="H5" s="111"/>
       <c r="I5" s="21" t="str">
         <f aca="false">IF(OR(G5="",H5=""),"",H5-G5)</f>
         <v/>
       </c>
-      <c r="J5" s="103"/>
-      <c r="K5" s="103"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="103"/>
-      <c r="N5" s="111"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+      <c r="L5" s="103"/>
+      <c r="M5" s="104"/>
+      <c r="N5" s="112"/>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="105" t="n">
+      <c r="A6" s="106" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="102"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="103"/>
-      <c r="G6" s="110"/>
-      <c r="H6" s="110"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="104"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="111"/>
       <c r="I6" s="21" t="str">
         <f aca="false">IF(OR(G6="",H6=""),"",H6-G6)</f>
         <v/>
       </c>
-      <c r="J6" s="103"/>
-      <c r="K6" s="103"/>
-      <c r="L6" s="102"/>
-      <c r="M6" s="103"/>
-      <c r="N6" s="111"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="104"/>
+      <c r="L6" s="103"/>
+      <c r="M6" s="104"/>
+      <c r="N6" s="112"/>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="105" t="n">
+      <c r="A7" s="106" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="102"/>
-      <c r="C7" s="103"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="110"/>
-      <c r="H7" s="110"/>
+      <c r="B7" s="103"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="111"/>
+      <c r="H7" s="111"/>
       <c r="I7" s="21" t="str">
         <f aca="false">IF(OR(G7="",H7=""),"",H7-G7)</f>
         <v/>
       </c>
-      <c r="J7" s="103"/>
-      <c r="K7" s="103"/>
-      <c r="L7" s="102"/>
-      <c r="M7" s="103"/>
-      <c r="N7" s="111"/>
+      <c r="J7" s="104"/>
+      <c r="K7" s="104"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="104"/>
+      <c r="N7" s="112"/>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="105" t="n">
+      <c r="A8" s="106" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="102"/>
-      <c r="C8" s="103"/>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="103"/>
-      <c r="G8" s="110"/>
-      <c r="H8" s="110"/>
+      <c r="B8" s="103"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="111"/>
+      <c r="H8" s="111"/>
       <c r="I8" s="21" t="str">
         <f aca="false">IF(OR(G8="",H8=""),"",H8-G8)</f>
         <v/>
       </c>
-      <c r="J8" s="103"/>
-      <c r="K8" s="103"/>
-      <c r="L8" s="102"/>
-      <c r="M8" s="103"/>
-      <c r="N8" s="111"/>
+      <c r="J8" s="104"/>
+      <c r="K8" s="104"/>
+      <c r="L8" s="103"/>
+      <c r="M8" s="104"/>
+      <c r="N8" s="112"/>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="105" t="n">
+      <c r="A9" s="106" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="102"/>
-      <c r="C9" s="103"/>
-      <c r="D9" s="103"/>
-      <c r="E9" s="103"/>
-      <c r="F9" s="103"/>
-      <c r="G9" s="110"/>
-      <c r="H9" s="110"/>
+      <c r="B9" s="103"/>
+      <c r="C9" s="104"/>
+      <c r="D9" s="104"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="111"/>
+      <c r="H9" s="111"/>
       <c r="I9" s="21" t="str">
         <f aca="false">IF(OR(G9="",H9=""),"",H9-G9)</f>
         <v/>
       </c>
-      <c r="J9" s="103"/>
-      <c r="K9" s="103"/>
-      <c r="L9" s="102"/>
-      <c r="M9" s="103"/>
-      <c r="N9" s="111"/>
+      <c r="J9" s="104"/>
+      <c r="K9" s="104"/>
+      <c r="L9" s="103"/>
+      <c r="M9" s="104"/>
+      <c r="N9" s="112"/>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="105" t="n">
+      <c r="A10" s="106" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="102"/>
-      <c r="C10" s="103"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="103"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
+      <c r="B10" s="103"/>
+      <c r="C10" s="104"/>
+      <c r="D10" s="104"/>
+      <c r="E10" s="104"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="111"/>
+      <c r="H10" s="111"/>
       <c r="I10" s="21" t="str">
         <f aca="false">IF(OR(G10="",H10=""),"",H10-G10)</f>
         <v/>
       </c>
-      <c r="J10" s="103"/>
-      <c r="K10" s="103"/>
-      <c r="L10" s="102"/>
-      <c r="M10" s="103"/>
-      <c r="N10" s="111"/>
+      <c r="J10" s="104"/>
+      <c r="K10" s="104"/>
+      <c r="L10" s="103"/>
+      <c r="M10" s="104"/>
+      <c r="N10" s="112"/>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="105" t="n">
+      <c r="A11" s="106" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="102"/>
-      <c r="C11" s="103"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="103"/>
-      <c r="F11" s="103"/>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110"/>
+      <c r="B11" s="103"/>
+      <c r="C11" s="104"/>
+      <c r="D11" s="104"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="111"/>
+      <c r="H11" s="111"/>
       <c r="I11" s="21" t="str">
         <f aca="false">IF(OR(G11="",H11=""),"",H11-G11)</f>
         <v/>
       </c>
-      <c r="J11" s="103"/>
-      <c r="K11" s="103"/>
-      <c r="L11" s="102"/>
-      <c r="M11" s="103"/>
-      <c r="N11" s="111"/>
+      <c r="J11" s="104"/>
+      <c r="K11" s="104"/>
+      <c r="L11" s="103"/>
+      <c r="M11" s="104"/>
+      <c r="N11" s="112"/>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="105" t="n">
+      <c r="A12" s="106" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="102"/>
-      <c r="C12" s="103"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="103"/>
-      <c r="G12" s="110"/>
-      <c r="H12" s="110"/>
+      <c r="B12" s="103"/>
+      <c r="C12" s="104"/>
+      <c r="D12" s="104"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="111"/>
       <c r="I12" s="21" t="str">
         <f aca="false">IF(OR(G12="",H12=""),"",H12-G12)</f>
         <v/>
       </c>
-      <c r="J12" s="103"/>
-      <c r="K12" s="103"/>
-      <c r="L12" s="102"/>
-      <c r="M12" s="103"/>
-      <c r="N12" s="111"/>
+      <c r="J12" s="104"/>
+      <c r="K12" s="104"/>
+      <c r="L12" s="103"/>
+      <c r="M12" s="104"/>
+      <c r="N12" s="112"/>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="105" t="n">
+      <c r="A13" s="106" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="102"/>
-      <c r="C13" s="103"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="103"/>
-      <c r="F13" s="103"/>
-      <c r="G13" s="110"/>
-      <c r="H13" s="110"/>
+      <c r="B13" s="103"/>
+      <c r="C13" s="104"/>
+      <c r="D13" s="104"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="111"/>
       <c r="I13" s="21" t="str">
         <f aca="false">IF(OR(G13="",H13=""),"",H13-G13)</f>
         <v/>
       </c>
-      <c r="J13" s="103"/>
-      <c r="K13" s="103"/>
-      <c r="L13" s="102"/>
-      <c r="M13" s="103"/>
-      <c r="N13" s="111"/>
+      <c r="J13" s="104"/>
+      <c r="K13" s="104"/>
+      <c r="L13" s="103"/>
+      <c r="M13" s="104"/>
+      <c r="N13" s="112"/>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="105" t="n">
+      <c r="A14" s="106" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="102"/>
-      <c r="C14" s="103"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="103"/>
-      <c r="F14" s="103"/>
-      <c r="G14" s="110"/>
-      <c r="H14" s="110"/>
+      <c r="B14" s="103"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="104"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="104"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
       <c r="I14" s="21" t="str">
         <f aca="false">IF(OR(G14="",H14=""),"",H14-G14)</f>
         <v/>
       </c>
-      <c r="J14" s="103"/>
-      <c r="K14" s="103"/>
-      <c r="L14" s="102"/>
-      <c r="M14" s="103"/>
-      <c r="N14" s="111"/>
+      <c r="J14" s="104"/>
+      <c r="K14" s="104"/>
+      <c r="L14" s="103"/>
+      <c r="M14" s="104"/>
+      <c r="N14" s="112"/>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="105" t="n">
+      <c r="A15" s="106" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="102"/>
-      <c r="C15" s="103"/>
-      <c r="D15" s="103"/>
-      <c r="E15" s="103"/>
-      <c r="F15" s="103"/>
-      <c r="G15" s="110"/>
-      <c r="H15" s="110"/>
+      <c r="B15" s="103"/>
+      <c r="C15" s="104"/>
+      <c r="D15" s="104"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="111"/>
       <c r="I15" s="21" t="str">
         <f aca="false">IF(OR(G15="",H15=""),"",H15-G15)</f>
         <v/>
       </c>
-      <c r="J15" s="103"/>
-      <c r="K15" s="103"/>
-      <c r="L15" s="102"/>
-      <c r="M15" s="103"/>
-      <c r="N15" s="111"/>
+      <c r="J15" s="104"/>
+      <c r="K15" s="104"/>
+      <c r="L15" s="103"/>
+      <c r="M15" s="104"/>
+      <c r="N15" s="112"/>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="105" t="n">
+      <c r="A16" s="106" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="102"/>
-      <c r="C16" s="103"/>
-      <c r="D16" s="103"/>
-      <c r="E16" s="103"/>
-      <c r="F16" s="103"/>
-      <c r="G16" s="110"/>
-      <c r="H16" s="110"/>
+      <c r="B16" s="103"/>
+      <c r="C16" s="104"/>
+      <c r="D16" s="104"/>
+      <c r="E16" s="104"/>
+      <c r="F16" s="104"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
       <c r="I16" s="21" t="str">
         <f aca="false">IF(OR(G16="",H16=""),"",H16-G16)</f>
         <v/>
       </c>
-      <c r="J16" s="103"/>
-      <c r="K16" s="103"/>
-      <c r="L16" s="102"/>
-      <c r="M16" s="103"/>
-      <c r="N16" s="111"/>
+      <c r="J16" s="104"/>
+      <c r="K16" s="104"/>
+      <c r="L16" s="103"/>
+      <c r="M16" s="104"/>
+      <c r="N16" s="112"/>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="105" t="n">
+      <c r="A17" s="106" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="102"/>
-      <c r="C17" s="103"/>
-      <c r="D17" s="103"/>
-      <c r="E17" s="103"/>
-      <c r="F17" s="103"/>
-      <c r="G17" s="110"/>
-      <c r="H17" s="110"/>
+      <c r="B17" s="103"/>
+      <c r="C17" s="104"/>
+      <c r="D17" s="104"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="111"/>
+      <c r="H17" s="111"/>
       <c r="I17" s="21" t="str">
         <f aca="false">IF(OR(G17="",H17=""),"",H17-G17)</f>
         <v/>
       </c>
-      <c r="J17" s="103"/>
-      <c r="K17" s="103"/>
-      <c r="L17" s="102"/>
-      <c r="M17" s="103"/>
-      <c r="N17" s="111"/>
+      <c r="J17" s="104"/>
+      <c r="K17" s="104"/>
+      <c r="L17" s="103"/>
+      <c r="M17" s="104"/>
+      <c r="N17" s="112"/>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="105" t="n">
+      <c r="A18" s="106" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="102"/>
-      <c r="C18" s="103"/>
-      <c r="D18" s="103"/>
-      <c r="E18" s="103"/>
-      <c r="F18" s="103"/>
-      <c r="G18" s="110"/>
-      <c r="H18" s="110"/>
+      <c r="B18" s="103"/>
+      <c r="C18" s="104"/>
+      <c r="D18" s="104"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="104"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="111"/>
       <c r="I18" s="21" t="str">
         <f aca="false">IF(OR(G18="",H18=""),"",H18-G18)</f>
         <v/>
       </c>
-      <c r="J18" s="103"/>
-      <c r="K18" s="103"/>
-      <c r="L18" s="102"/>
-      <c r="M18" s="103"/>
-      <c r="N18" s="111"/>
+      <c r="J18" s="104"/>
+      <c r="K18" s="104"/>
+      <c r="L18" s="103"/>
+      <c r="M18" s="104"/>
+      <c r="N18" s="112"/>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="105" t="n">
+      <c r="A19" s="106" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="102"/>
-      <c r="C19" s="103"/>
-      <c r="D19" s="103"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="103"/>
-      <c r="G19" s="110"/>
-      <c r="H19" s="110"/>
+      <c r="B19" s="103"/>
+      <c r="C19" s="104"/>
+      <c r="D19" s="104"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="111"/>
       <c r="I19" s="21" t="str">
         <f aca="false">IF(OR(G19="",H19=""),"",H19-G19)</f>
         <v/>
       </c>
-      <c r="J19" s="103"/>
-      <c r="K19" s="103"/>
-      <c r="L19" s="102"/>
-      <c r="M19" s="103"/>
-      <c r="N19" s="111"/>
+      <c r="J19" s="104"/>
+      <c r="K19" s="104"/>
+      <c r="L19" s="103"/>
+      <c r="M19" s="104"/>
+      <c r="N19" s="112"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="105" t="n">
+      <c r="A20" s="106" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="102"/>
-      <c r="C20" s="103"/>
-      <c r="D20" s="103"/>
-      <c r="E20" s="103"/>
-      <c r="F20" s="103"/>
-      <c r="G20" s="110"/>
-      <c r="H20" s="110"/>
+      <c r="B20" s="103"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="104"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="104"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="111"/>
       <c r="I20" s="21" t="str">
         <f aca="false">IF(OR(G20="",H20=""),"",H20-G20)</f>
         <v/>
       </c>
-      <c r="J20" s="103"/>
-      <c r="K20" s="103"/>
-      <c r="L20" s="102"/>
-      <c r="M20" s="103"/>
-      <c r="N20" s="111"/>
+      <c r="J20" s="104"/>
+      <c r="K20" s="104"/>
+      <c r="L20" s="103"/>
+      <c r="M20" s="104"/>
+      <c r="N20" s="112"/>
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="105" t="n">
+      <c r="A21" s="106" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="102"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="103"/>
-      <c r="G21" s="110"/>
-      <c r="H21" s="110"/>
+      <c r="B21" s="103"/>
+      <c r="C21" s="104"/>
+      <c r="D21" s="104"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="104"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="111"/>
       <c r="I21" s="21" t="str">
         <f aca="false">IF(OR(G21="",H21=""),"",H21-G21)</f>
         <v/>
       </c>
-      <c r="J21" s="103"/>
-      <c r="K21" s="103"/>
-      <c r="L21" s="102"/>
-      <c r="M21" s="103"/>
-      <c r="N21" s="111"/>
+      <c r="J21" s="104"/>
+      <c r="K21" s="104"/>
+      <c r="L21" s="103"/>
+      <c r="M21" s="104"/>
+      <c r="N21" s="112"/>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="105" t="n">
+      <c r="A22" s="106" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="102"/>
-      <c r="C22" s="103"/>
-      <c r="D22" s="103"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="103"/>
-      <c r="G22" s="110"/>
-      <c r="H22" s="110"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="104"/>
+      <c r="D22" s="104"/>
+      <c r="E22" s="104"/>
+      <c r="F22" s="104"/>
+      <c r="G22" s="111"/>
+      <c r="H22" s="111"/>
       <c r="I22" s="21" t="str">
         <f aca="false">IF(OR(G22="",H22=""),"",H22-G22)</f>
         <v/>
       </c>
-      <c r="J22" s="103"/>
-      <c r="K22" s="103"/>
-      <c r="L22" s="102"/>
-      <c r="M22" s="103"/>
-      <c r="N22" s="111"/>
+      <c r="J22" s="104"/>
+      <c r="K22" s="104"/>
+      <c r="L22" s="103"/>
+      <c r="M22" s="104"/>
+      <c r="N22" s="112"/>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="105" t="n">
+      <c r="A23" s="106" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="102"/>
-      <c r="C23" s="103"/>
-      <c r="D23" s="103"/>
-      <c r="E23" s="103"/>
-      <c r="F23" s="103"/>
-      <c r="G23" s="110"/>
-      <c r="H23" s="110"/>
+      <c r="B23" s="103"/>
+      <c r="C23" s="104"/>
+      <c r="D23" s="104"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="104"/>
+      <c r="G23" s="111"/>
+      <c r="H23" s="111"/>
       <c r="I23" s="21" t="str">
         <f aca="false">IF(OR(G23="",H23=""),"",H23-G23)</f>
         <v/>
       </c>
-      <c r="J23" s="103"/>
-      <c r="K23" s="103"/>
-      <c r="L23" s="102"/>
-      <c r="M23" s="103"/>
-      <c r="N23" s="111"/>
+      <c r="J23" s="104"/>
+      <c r="K23" s="104"/>
+      <c r="L23" s="103"/>
+      <c r="M23" s="104"/>
+      <c r="N23" s="112"/>
     </row>
     <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="105" t="n">
+      <c r="A24" s="106" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="102"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="103"/>
-      <c r="E24" s="103"/>
-      <c r="F24" s="103"/>
-      <c r="G24" s="110"/>
-      <c r="H24" s="110"/>
+      <c r="B24" s="103"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="104"/>
+      <c r="G24" s="111"/>
+      <c r="H24" s="111"/>
       <c r="I24" s="21" t="str">
         <f aca="false">IF(OR(G24="",H24=""),"",H24-G24)</f>
         <v/>
       </c>
-      <c r="J24" s="103"/>
-      <c r="K24" s="103"/>
-      <c r="L24" s="102"/>
-      <c r="M24" s="103"/>
-      <c r="N24" s="111"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="104"/>
+      <c r="L24" s="103"/>
+      <c r="M24" s="104"/>
+      <c r="N24" s="112"/>
     </row>
     <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="105" t="n">
+      <c r="A25" s="106" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="102"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="103"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="103"/>
-      <c r="G25" s="110"/>
-      <c r="H25" s="110"/>
+      <c r="B25" s="103"/>
+      <c r="C25" s="104"/>
+      <c r="D25" s="104"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="104"/>
+      <c r="G25" s="111"/>
+      <c r="H25" s="111"/>
       <c r="I25" s="21" t="str">
         <f aca="false">IF(OR(G25="",H25=""),"",H25-G25)</f>
         <v/>
       </c>
-      <c r="J25" s="103"/>
-      <c r="K25" s="103"/>
-      <c r="L25" s="102"/>
-      <c r="M25" s="103"/>
-      <c r="N25" s="111"/>
+      <c r="J25" s="104"/>
+      <c r="K25" s="104"/>
+      <c r="L25" s="103"/>
+      <c r="M25" s="104"/>
+      <c r="N25" s="112"/>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="105" t="n">
+      <c r="A26" s="106" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="102"/>
-      <c r="C26" s="103"/>
-      <c r="D26" s="103"/>
-      <c r="E26" s="103"/>
-      <c r="F26" s="103"/>
-      <c r="G26" s="110"/>
-      <c r="H26" s="110"/>
+      <c r="B26" s="103"/>
+      <c r="C26" s="104"/>
+      <c r="D26" s="104"/>
+      <c r="E26" s="104"/>
+      <c r="F26" s="104"/>
+      <c r="G26" s="111"/>
+      <c r="H26" s="111"/>
       <c r="I26" s="21" t="str">
         <f aca="false">IF(OR(G26="",H26=""),"",H26-G26)</f>
         <v/>
       </c>
-      <c r="J26" s="103"/>
-      <c r="K26" s="103"/>
-      <c r="L26" s="102"/>
-      <c r="M26" s="103"/>
-      <c r="N26" s="111"/>
+      <c r="J26" s="104"/>
+      <c r="K26" s="104"/>
+      <c r="L26" s="103"/>
+      <c r="M26" s="104"/>
+      <c r="N26" s="112"/>
     </row>
     <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="105" t="n">
+      <c r="A27" s="106" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="102"/>
-      <c r="C27" s="103"/>
-      <c r="D27" s="103"/>
-      <c r="E27" s="103"/>
-      <c r="F27" s="103"/>
-      <c r="G27" s="110"/>
-      <c r="H27" s="110"/>
+      <c r="B27" s="103"/>
+      <c r="C27" s="104"/>
+      <c r="D27" s="104"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="104"/>
+      <c r="G27" s="111"/>
+      <c r="H27" s="111"/>
       <c r="I27" s="21" t="str">
         <f aca="false">IF(OR(G27="",H27=""),"",H27-G27)</f>
         <v/>
       </c>
-      <c r="J27" s="103"/>
-      <c r="K27" s="103"/>
-      <c r="L27" s="102"/>
-      <c r="M27" s="103"/>
-      <c r="N27" s="111"/>
+      <c r="J27" s="104"/>
+      <c r="K27" s="104"/>
+      <c r="L27" s="103"/>
+      <c r="M27" s="104"/>
+      <c r="N27" s="112"/>
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="105" t="n">
+      <c r="A28" s="106" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="102"/>
-      <c r="C28" s="103"/>
-      <c r="D28" s="103"/>
-      <c r="E28" s="103"/>
-      <c r="F28" s="103"/>
-      <c r="G28" s="110"/>
-      <c r="H28" s="110"/>
+      <c r="B28" s="103"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="104"/>
+      <c r="G28" s="111"/>
+      <c r="H28" s="111"/>
       <c r="I28" s="21" t="str">
         <f aca="false">IF(OR(G28="",H28=""),"",H28-G28)</f>
         <v/>
       </c>
-      <c r="J28" s="103"/>
-      <c r="K28" s="103"/>
-      <c r="L28" s="102"/>
-      <c r="M28" s="103"/>
-      <c r="N28" s="111"/>
+      <c r="J28" s="104"/>
+      <c r="K28" s="104"/>
+      <c r="L28" s="103"/>
+      <c r="M28" s="104"/>
+      <c r="N28" s="112"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="24" t="s">
-        <v>1217</v>
+        <v>1271</v>
       </c>
       <c r="M30" s="21" t="str">
         <f aca="false">COUNTA(B5:B28)&amp;" مبادرة"</f>
@@ -15582,7 +18822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -15608,7 +18848,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1218</v>
+        <v>1272</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -15627,7 +18867,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1219</v>
+        <v>1273</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -15646,7 +18886,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>1220</v>
+        <v>1274</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>858</v>
@@ -15655,40 +18895,40 @@
         <v>1012</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>1221</v>
+        <v>1275</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>1222</v>
+        <v>1276</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1223</v>
+        <v>1277</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1224</v>
+        <v>1278</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1225</v>
+        <v>1279</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>1226</v>
+        <v>1280</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>1227</v>
+        <v>1281</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>860</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>1228</v>
+        <v>1282</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>1229</v>
+        <v>1283</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>1230</v>
+        <v>1284</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>1231</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15720,7 +18960,7 @@
       <c r="I4" s="28" t="n">
         <v>23493282</v>
       </c>
-      <c r="J4" s="100" t="n">
+      <c r="J4" s="101" t="n">
         <v>64.69</v>
       </c>
       <c r="K4" s="57" t="n">
@@ -15736,7 +18976,7 @@
         <v>0.281</v>
       </c>
       <c r="O4" s="21" t="s">
-        <v>1232</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15768,10 +19008,10 @@
       <c r="I5" s="28" t="n">
         <v>8841940</v>
       </c>
-      <c r="J5" s="100" t="n">
+      <c r="J5" s="101" t="n">
         <v>61.72</v>
       </c>
-      <c r="K5" s="112" t="n">
+      <c r="K5" s="113" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="45" t="n">
@@ -15784,7 +19024,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>1233</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15816,10 +19056,10 @@
       <c r="I6" s="28" t="n">
         <v>7467484</v>
       </c>
-      <c r="J6" s="100" t="n">
+      <c r="J6" s="101" t="n">
         <v>80.21</v>
       </c>
-      <c r="K6" s="112" t="n">
+      <c r="K6" s="113" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="45" t="n">
@@ -15832,7 +19072,7 @@
         <v>0.344</v>
       </c>
       <c r="O6" s="21" t="s">
-        <v>1234</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15864,10 +19104,10 @@
       <c r="I7" s="28" t="n">
         <v>14552120</v>
       </c>
-      <c r="J7" s="100" t="n">
+      <c r="J7" s="101" t="n">
         <v>84.21</v>
       </c>
-      <c r="K7" s="113" t="n">
+      <c r="K7" s="114" t="n">
         <v>0.273</v>
       </c>
       <c r="L7" s="45" t="n">
@@ -15880,7 +19120,7 @@
         <v>0.641</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>1235</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15912,7 +19152,7 @@
       <c r="I8" s="28" t="n">
         <v>2916708</v>
       </c>
-      <c r="J8" s="100" t="n">
+      <c r="J8" s="101" t="n">
         <v>48.35</v>
       </c>
       <c r="K8" s="57" t="n">
@@ -15928,7 +19168,7 @@
         <v>0.134</v>
       </c>
       <c r="O8" s="21" t="s">
-        <v>1236</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15960,10 +19200,10 @@
       <c r="I9" s="28" t="n">
         <v>2916316</v>
       </c>
-      <c r="J9" s="100" t="n">
+      <c r="J9" s="101" t="n">
         <v>65.82</v>
       </c>
-      <c r="K9" s="112" t="n">
+      <c r="K9" s="113" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="45" t="n">
@@ -15976,7 +19216,7 @@
         <v>0.309</v>
       </c>
       <c r="O9" s="21" t="s">
-        <v>1232</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16008,10 +19248,10 @@
       <c r="I10" s="28" t="n">
         <v>2831981</v>
       </c>
-      <c r="J10" s="100" t="n">
+      <c r="J10" s="101" t="n">
         <v>59.14</v>
       </c>
-      <c r="K10" s="112" t="n">
+      <c r="K10" s="113" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="45" t="n">
@@ -16024,7 +19264,7 @@
         <v>0.006</v>
       </c>
       <c r="O10" s="21" t="s">
-        <v>1234</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16056,10 +19296,10 @@
       <c r="I11" s="28" t="n">
         <v>2931550</v>
       </c>
-      <c r="J11" s="100" t="n">
+      <c r="J11" s="101" t="n">
         <v>49.84</v>
       </c>
-      <c r="K11" s="112" t="n">
+      <c r="K11" s="113" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="45" t="n">
@@ -16072,7 +19312,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="21" t="s">
-        <v>1234</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16104,7 +19344,7 @@
       <c r="I12" s="28" t="n">
         <v>8679738</v>
       </c>
-      <c r="J12" s="100" t="n">
+      <c r="J12" s="101" t="n">
         <v>59.34</v>
       </c>
       <c r="K12" s="57" t="n">
@@ -16120,7 +19360,7 @@
         <v>0.277</v>
       </c>
       <c r="O12" s="21" t="s">
-        <v>1234</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16152,7 +19392,7 @@
       <c r="I13" s="28" t="n">
         <v>7729931</v>
       </c>
-      <c r="J13" s="100" t="n">
+      <c r="J13" s="101" t="n">
         <v>67.66</v>
       </c>
       <c r="K13" s="57" t="n">
@@ -16168,7 +19408,7 @@
         <v>0.082</v>
       </c>
       <c r="O13" s="21" t="s">
-        <v>1234</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16200,7 +19440,7 @@
       <c r="I14" s="28" t="n">
         <v>2676944</v>
       </c>
-      <c r="J14" s="100" t="n">
+      <c r="J14" s="101" t="n">
         <v>59.47</v>
       </c>
       <c r="K14" s="45" t="n">
@@ -16216,7 +19456,7 @@
         <v>0.231</v>
       </c>
       <c r="O14" s="21" t="s">
-        <v>1234</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16248,7 +19488,7 @@
       <c r="I15" s="28" t="n">
         <v>7806709</v>
       </c>
-      <c r="J15" s="100" t="n">
+      <c r="J15" s="101" t="n">
         <v>63.18</v>
       </c>
       <c r="K15" s="57" t="n">
@@ -16264,7 +19504,7 @@
         <v>0.458</v>
       </c>
       <c r="O15" s="21" t="s">
-        <v>1236</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16296,10 +19536,10 @@
       <c r="I16" s="28" t="n">
         <v>4791911</v>
       </c>
-      <c r="J16" s="100" t="n">
+      <c r="J16" s="101" t="n">
         <v>74.3</v>
       </c>
-      <c r="K16" s="113" t="n">
+      <c r="K16" s="114" t="n">
         <v>0.151</v>
       </c>
       <c r="L16" s="45" t="n">
@@ -16312,7 +19552,7 @@
         <v>0.076</v>
       </c>
       <c r="O16" s="21" t="s">
-        <v>1234</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16344,10 +19584,10 @@
       <c r="I17" s="28" t="n">
         <v>2078856</v>
       </c>
-      <c r="J17" s="100" t="n">
+      <c r="J17" s="101" t="n">
         <v>55.76</v>
       </c>
-      <c r="K17" s="112" t="n">
+      <c r="K17" s="113" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="45" t="n">
@@ -16360,7 +19600,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="21" t="s">
-        <v>1232</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16392,7 +19632,7 @@
       <c r="I18" s="28" t="n">
         <v>6570004</v>
       </c>
-      <c r="J18" s="100" t="n">
+      <c r="J18" s="101" t="n">
         <v>43.71</v>
       </c>
       <c r="K18" s="45" t="n">
@@ -16408,7 +19648,7 @@
         <v>0</v>
       </c>
       <c r="O18" s="21" t="s">
-        <v>1232</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16440,10 +19680,10 @@
       <c r="I19" s="28" t="n">
         <v>4445436</v>
       </c>
-      <c r="J19" s="100" t="n">
+      <c r="J19" s="101" t="n">
         <v>42.14</v>
       </c>
-      <c r="K19" s="113" t="n">
+      <c r="K19" s="114" t="n">
         <v>0.275</v>
       </c>
       <c r="L19" s="45" t="n">
@@ -16456,7 +19696,7 @@
         <v>0.048</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>1235</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16488,10 +19728,10 @@
       <c r="I20" s="28" t="n">
         <v>2229579</v>
       </c>
-      <c r="J20" s="100" t="n">
+      <c r="J20" s="101" t="n">
         <v>43.6</v>
       </c>
-      <c r="K20" s="112" t="n">
+      <c r="K20" s="113" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="45" t="n">
@@ -16504,7 +19744,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="21" t="s">
-        <v>1233</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16536,7 +19776,7 @@
       <c r="I21" s="28" t="n">
         <v>5504980</v>
       </c>
-      <c r="J21" s="100" t="n">
+      <c r="J21" s="101" t="n">
         <v>43.52</v>
       </c>
       <c r="K21" s="57" t="n">
@@ -16552,7 +19792,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="21" t="s">
-        <v>1234</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16584,10 +19824,10 @@
       <c r="I22" s="28" t="n">
         <v>4722403</v>
       </c>
-      <c r="J22" s="100" t="n">
+      <c r="J22" s="101" t="n">
         <v>49.88</v>
       </c>
-      <c r="K22" s="113" t="n">
+      <c r="K22" s="114" t="n">
         <v>0.068</v>
       </c>
       <c r="L22" s="45" t="n">
@@ -16600,7 +19840,7 @@
         <v>0.329</v>
       </c>
       <c r="O22" s="21" t="s">
-        <v>1236</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16632,10 +19872,10 @@
       <c r="I23" s="28" t="n">
         <v>4924931</v>
       </c>
-      <c r="J23" s="100" t="n">
+      <c r="J23" s="101" t="n">
         <v>47.68</v>
       </c>
-      <c r="K23" s="113" t="n">
+      <c r="K23" s="114" t="n">
         <v>0.069</v>
       </c>
       <c r="L23" s="45" t="n">
@@ -16648,7 +19888,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="21" t="s">
-        <v>1234</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16680,7 +19920,7 @@
       <c r="I24" s="28" t="n">
         <v>4740020</v>
       </c>
-      <c r="J24" s="100" t="n">
+      <c r="J24" s="101" t="n">
         <v>43.42</v>
       </c>
       <c r="K24" s="45" t="n">
@@ -16696,7 +19936,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="21" t="s">
-        <v>1234</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16728,10 +19968,10 @@
       <c r="I25" s="28" t="n">
         <v>4771577</v>
       </c>
-      <c r="J25" s="100" t="n">
+      <c r="J25" s="101" t="n">
         <v>51.68</v>
       </c>
-      <c r="K25" s="113" t="n">
+      <c r="K25" s="114" t="n">
         <v>0.177</v>
       </c>
       <c r="L25" s="45" t="n">
@@ -16744,7 +19984,7 @@
         <v>0.058</v>
       </c>
       <c r="O25" s="21" t="s">
-        <v>1232</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16776,7 +20016,7 @@
       <c r="I26" s="28" t="n">
         <v>4933540</v>
       </c>
-      <c r="J26" s="100" t="n">
+      <c r="J26" s="101" t="n">
         <v>51.76</v>
       </c>
       <c r="K26" s="45" t="n">
@@ -16792,7 +20032,7 @@
         <v>0.276</v>
       </c>
       <c r="O26" s="21" t="s">
-        <v>1232</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16824,10 +20064,10 @@
       <c r="I27" s="28" t="n">
         <v>4643058</v>
       </c>
-      <c r="J27" s="100" t="n">
+      <c r="J27" s="101" t="n">
         <v>66.28</v>
       </c>
-      <c r="K27" s="113" t="n">
+      <c r="K27" s="114" t="n">
         <v>0.083</v>
       </c>
       <c r="L27" s="45" t="n">
@@ -16840,7 +20080,7 @@
         <v>0.27</v>
       </c>
       <c r="O27" s="21" t="s">
-        <v>1237</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16872,10 +20112,10 @@
       <c r="I28" s="28" t="n">
         <v>2834084</v>
       </c>
-      <c r="J28" s="100" t="n">
+      <c r="J28" s="101" t="n">
         <v>77.81</v>
       </c>
-      <c r="K28" s="112" t="n">
+      <c r="K28" s="113" t="n">
         <v>-0.033</v>
       </c>
       <c r="L28" s="45" t="n">
@@ -16888,7 +20128,7 @@
         <v>0.349</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>1235</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16920,7 +20160,7 @@
       <c r="I29" s="28" t="n">
         <v>4558563</v>
       </c>
-      <c r="J29" s="100" t="n">
+      <c r="J29" s="101" t="n">
         <v>64.44</v>
       </c>
       <c r="K29" s="45" t="n">
@@ -16936,7 +20176,7 @@
         <v>0.321</v>
       </c>
       <c r="O29" s="21" t="s">
-        <v>1232</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16968,10 +20208,10 @@
       <c r="I30" s="28" t="n">
         <v>2127665</v>
       </c>
-      <c r="J30" s="100" t="n">
+      <c r="J30" s="101" t="n">
         <v>48.52</v>
       </c>
-      <c r="K30" s="112" t="n">
+      <c r="K30" s="113" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="45" t="n">
@@ -16984,7 +20224,7 @@
         <v>0.176</v>
       </c>
       <c r="O30" s="21" t="s">
-        <v>1232</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17016,10 +20256,10 @@
       <c r="I31" s="28" t="n">
         <v>3884721</v>
       </c>
-      <c r="J31" s="100" t="n">
+      <c r="J31" s="101" t="n">
         <v>54.76</v>
       </c>
-      <c r="K31" s="113" t="n">
+      <c r="K31" s="114" t="n">
         <v>0.186</v>
       </c>
       <c r="L31" s="45" t="n">
@@ -17032,7 +20272,7 @@
         <v>0.082</v>
       </c>
       <c r="O31" s="21" t="s">
-        <v>1234</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17064,10 +20304,10 @@
       <c r="I32" s="28" t="n">
         <v>1471112</v>
       </c>
-      <c r="J32" s="100" t="n">
+      <c r="J32" s="101" t="n">
         <v>49.67</v>
       </c>
-      <c r="K32" s="112" t="n">
+      <c r="K32" s="113" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="45" t="n">
@@ -17080,7 +20320,7 @@
         <v>0.103</v>
       </c>
       <c r="O32" s="20" t="s">
-        <v>1235</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17112,10 +20352,10 @@
       <c r="I33" s="28" t="n">
         <v>3774634</v>
       </c>
-      <c r="J33" s="100" t="n">
+      <c r="J33" s="101" t="n">
         <v>50.81</v>
       </c>
-      <c r="K33" s="113" t="n">
+      <c r="K33" s="114" t="n">
         <v>0.18</v>
       </c>
       <c r="L33" s="45" t="n">
@@ -17128,7 +20368,7 @@
         <v>0.023</v>
       </c>
       <c r="O33" s="21" t="s">
-        <v>1232</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17160,7 +20400,7 @@
       <c r="I34" s="28" t="n">
         <v>4263083</v>
       </c>
-      <c r="J34" s="100" t="n">
+      <c r="J34" s="101" t="n">
         <v>110.06</v>
       </c>
       <c r="K34" s="57" t="n">
@@ -17176,7 +20416,7 @@
         <v>0.559</v>
       </c>
       <c r="O34" s="21" t="s">
-        <v>1237</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17208,7 +20448,7 @@
       <c r="I35" s="28" t="n">
         <v>3471225</v>
       </c>
-      <c r="J35" s="100" t="n">
+      <c r="J35" s="101" t="n">
         <v>47.35</v>
       </c>
       <c r="K35" s="57" t="n">
@@ -17224,7 +20464,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="21" t="s">
-        <v>1234</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17256,7 +20496,7 @@
       <c r="I36" s="28" t="n">
         <v>3512113</v>
       </c>
-      <c r="J36" s="100" t="n">
+      <c r="J36" s="101" t="n">
         <v>45.88</v>
       </c>
       <c r="K36" s="57" t="n">
@@ -17272,7 +20512,7 @@
         <v>0.115</v>
       </c>
       <c r="O36" s="21" t="s">
-        <v>1236</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17304,10 +20544,10 @@
       <c r="I37" s="28" t="n">
         <v>486162</v>
       </c>
-      <c r="J37" s="100" t="n">
+      <c r="J37" s="101" t="n">
         <v>33.35</v>
       </c>
-      <c r="K37" s="112" t="n">
+      <c r="K37" s="113" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="45" t="n">
@@ -17352,10 +20592,10 @@
       <c r="I38" s="28" t="n">
         <v>3406904</v>
       </c>
-      <c r="J38" s="100" t="n">
+      <c r="J38" s="101" t="n">
         <v>43.04</v>
       </c>
-      <c r="K38" s="113" t="n">
+      <c r="K38" s="114" t="n">
         <v>0.083</v>
       </c>
       <c r="L38" s="45" t="n">
@@ -17368,7 +20608,7 @@
         <v>0.167</v>
       </c>
       <c r="O38" s="21" t="s">
-        <v>1232</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17400,7 +20640,7 @@
       <c r="I39" s="28" t="n">
         <v>3076219</v>
       </c>
-      <c r="J39" s="100" t="n">
+      <c r="J39" s="101" t="n">
         <v>69.64</v>
       </c>
       <c r="K39" s="57" t="n">
@@ -17416,7 +20656,7 @@
         <v>0.106</v>
       </c>
       <c r="O39" s="21" t="s">
-        <v>1232</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17448,7 +20688,7 @@
       <c r="I40" s="28" t="n">
         <v>3314721</v>
       </c>
-      <c r="J40" s="100" t="n">
+      <c r="J40" s="101" t="n">
         <v>69.44</v>
       </c>
       <c r="K40" s="45" t="n">
@@ -17464,7 +20704,7 @@
         <v>0.373</v>
       </c>
       <c r="O40" s="21" t="s">
-        <v>1232</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17496,7 +20736,7 @@
       <c r="I41" s="28" t="n">
         <v>2925368</v>
       </c>
-      <c r="J41" s="100" t="n">
+      <c r="J41" s="101" t="n">
         <v>45.21</v>
       </c>
       <c r="K41" s="57" t="n">
@@ -17512,7 +20752,7 @@
         <v>0</v>
       </c>
       <c r="O41" s="21" t="s">
-        <v>1232</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17544,10 +20784,10 @@
       <c r="I42" s="28" t="n">
         <v>1114635</v>
       </c>
-      <c r="J42" s="100" t="n">
+      <c r="J42" s="101" t="n">
         <v>45.6</v>
       </c>
-      <c r="K42" s="112" t="n">
+      <c r="K42" s="113" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="45" t="n">
@@ -17560,7 +20800,7 @@
         <v>0.056</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>1235</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17592,10 +20832,10 @@
       <c r="I43" s="28" t="n">
         <v>2839338</v>
       </c>
-      <c r="J43" s="100" t="n">
+      <c r="J43" s="101" t="n">
         <v>50.86</v>
       </c>
-      <c r="K43" s="113" t="n">
+      <c r="K43" s="114" t="n">
         <v>0.082</v>
       </c>
       <c r="L43" s="45" t="n">
@@ -17608,7 +20848,7 @@
         <v>0.077</v>
       </c>
       <c r="O43" s="21" t="s">
-        <v>1237</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17640,10 +20880,10 @@
       <c r="I44" s="28" t="n">
         <v>2759664</v>
       </c>
-      <c r="J44" s="100" t="n">
+      <c r="J44" s="101" t="n">
         <v>56.84</v>
       </c>
-      <c r="K44" s="113" t="n">
+      <c r="K44" s="114" t="n">
         <v>0.327</v>
       </c>
       <c r="L44" s="45" t="n">
@@ -17656,7 +20896,7 @@
         <v>0.066</v>
       </c>
       <c r="O44" s="20" t="s">
-        <v>1235</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17688,7 +20928,7 @@
       <c r="I45" s="28" t="n">
         <v>2940822</v>
       </c>
-      <c r="J45" s="100" t="n">
+      <c r="J45" s="101" t="n">
         <v>74.93</v>
       </c>
       <c r="K45" s="45" t="n">
@@ -17704,7 +20944,7 @@
         <v>0.392</v>
       </c>
       <c r="O45" s="20" t="s">
-        <v>1235</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17736,7 +20976,7 @@
       <c r="I46" s="28" t="n">
         <v>2694118</v>
       </c>
-      <c r="J46" s="100" t="n">
+      <c r="J46" s="101" t="n">
         <v>53.94</v>
       </c>
       <c r="K46" s="57" t="n">
@@ -17752,7 +20992,7 @@
         <v>0.236</v>
       </c>
       <c r="O46" s="21" t="s">
-        <v>1234</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17784,7 +21024,7 @@
       <c r="I47" s="28" t="n">
         <v>2650896</v>
       </c>
-      <c r="J47" s="100" t="n">
+      <c r="J47" s="101" t="n">
         <v>48.6</v>
       </c>
       <c r="K47" s="45" t="n">
@@ -17800,7 +21040,7 @@
         <v>0.184</v>
       </c>
       <c r="O47" s="21" t="s">
-        <v>1237</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17832,10 +21072,10 @@
       <c r="I48" s="28" t="n">
         <v>2153145</v>
       </c>
-      <c r="J48" s="100" t="n">
+      <c r="J48" s="101" t="n">
         <v>57.15</v>
       </c>
-      <c r="K48" s="113" t="n">
+      <c r="K48" s="114" t="n">
         <v>0.064</v>
       </c>
       <c r="L48" s="45" t="n">
@@ -17848,7 +21088,7 @@
         <v>0</v>
       </c>
       <c r="O48" s="21" t="s">
-        <v>1232</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17880,10 +21120,10 @@
       <c r="I49" s="28" t="n">
         <v>2133587</v>
       </c>
-      <c r="J49" s="100" t="n">
+      <c r="J49" s="101" t="n">
         <v>62.82</v>
       </c>
-      <c r="K49" s="113" t="n">
+      <c r="K49" s="114" t="n">
         <v>0.256</v>
       </c>
       <c r="L49" s="45" t="n">
@@ -17896,7 +21136,7 @@
         <v>0.201</v>
       </c>
       <c r="O49" s="21" t="s">
-        <v>1232</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17928,7 +21168,7 @@
       <c r="I50" s="28" t="n">
         <v>1912969</v>
       </c>
-      <c r="J50" s="100" t="n">
+      <c r="J50" s="101" t="n">
         <v>52.46</v>
       </c>
       <c r="K50" s="57" t="n">
@@ -17944,7 +21184,7 @@
         <v>0</v>
       </c>
       <c r="O50" s="21" t="s">
-        <v>1234</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17976,10 +21216,10 @@
       <c r="I51" s="28" t="n">
         <v>568922</v>
       </c>
-      <c r="J51" s="100" t="n">
+      <c r="J51" s="101" t="n">
         <v>50.9</v>
       </c>
-      <c r="K51" s="112" t="n">
+      <c r="K51" s="113" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="45" t="n">
@@ -18024,10 +21264,10 @@
       <c r="I52" s="28" t="n">
         <v>1672588</v>
       </c>
-      <c r="J52" s="100" t="n">
+      <c r="J52" s="101" t="n">
         <v>45.95</v>
       </c>
-      <c r="K52" s="113" t="n">
+      <c r="K52" s="114" t="n">
         <v>0.137</v>
       </c>
       <c r="L52" s="45" t="n">
@@ -18040,7 +21280,7 @@
         <v>0.017</v>
       </c>
       <c r="O52" s="21" t="s">
-        <v>1236</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18072,7 +21312,7 @@
       <c r="I53" s="28" t="n">
         <v>1601535</v>
       </c>
-      <c r="J53" s="100" t="n">
+      <c r="J53" s="101" t="n">
         <v>55.38</v>
       </c>
       <c r="K53" s="45" t="n">
@@ -18088,7 +21328,7 @@
         <v>0.292</v>
       </c>
       <c r="O53" s="21" t="s">
-        <v>1236</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18120,7 +21360,7 @@
       <c r="I54" s="28" t="n">
         <v>1431054</v>
       </c>
-      <c r="J54" s="100" t="n">
+      <c r="J54" s="101" t="n">
         <v>53.68</v>
       </c>
       <c r="K54" s="45" t="n">
@@ -18136,7 +21376,7 @@
         <v>0.077</v>
       </c>
       <c r="O54" s="21" t="s">
-        <v>1232</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18168,10 +21408,10 @@
       <c r="I55" s="28" t="n">
         <v>1262094</v>
       </c>
-      <c r="J55" s="100" t="n">
+      <c r="J55" s="101" t="n">
         <v>53.3</v>
       </c>
-      <c r="K55" s="113" t="n">
+      <c r="K55" s="114" t="n">
         <v>0.188</v>
       </c>
       <c r="L55" s="45" t="n">
@@ -18184,7 +21424,7 @@
         <v>0.18</v>
       </c>
       <c r="O55" s="20" t="s">
-        <v>1235</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18216,10 +21456,10 @@
       <c r="I56" s="28" t="n">
         <v>1204453</v>
       </c>
-      <c r="J56" s="100" t="n">
+      <c r="J56" s="101" t="n">
         <v>34.88</v>
       </c>
-      <c r="K56" s="113" t="n">
+      <c r="K56" s="114" t="n">
         <v>0.06</v>
       </c>
       <c r="L56" s="45" t="n">
@@ -18232,7 +21472,7 @@
         <v>0.194</v>
       </c>
       <c r="O56" s="21" t="s">
-        <v>1236</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18264,10 +21504,10 @@
       <c r="I57" s="28" t="n">
         <v>206212</v>
       </c>
-      <c r="J57" s="100" t="n">
+      <c r="J57" s="101" t="n">
         <v>57.08</v>
       </c>
-      <c r="K57" s="112" t="n">
+      <c r="K57" s="113" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="45" t="n">
@@ -18280,7 +21520,7 @@
         <v>0.249</v>
       </c>
       <c r="O57" s="20" t="s">
-        <v>1235</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18312,10 +21552,10 @@
       <c r="I58" s="28" t="n">
         <v>21693</v>
       </c>
-      <c r="J58" s="100" t="n">
+      <c r="J58" s="101" t="n">
         <v>49.96</v>
       </c>
-      <c r="K58" s="112" t="n">
+      <c r="K58" s="113" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="45" t="n">
@@ -18328,51 +21568,51 @@
         <v>0.167</v>
       </c>
       <c r="O58" s="20" t="s">
-        <v>1235</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="67" t="s">
-        <v>1238</v>
+        <v>1292</v>
       </c>
       <c r="B59" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="F59" s="114" t="n">
+      <c r="F59" s="115" t="n">
         <f aca="false">SUM(F4:F58)</f>
         <v>502415662</v>
       </c>
-      <c r="G59" s="114" t="n">
+      <c r="G59" s="115" t="n">
         <f aca="false">SUM(G4:G58)</f>
         <v>1271395370.83428</v>
       </c>
-      <c r="H59" s="114" t="n">
+      <c r="H59" s="115" t="n">
         <f aca="false">SUM(H4:H58)</f>
         <v>8824895</v>
       </c>
-      <c r="I59" s="114" t="n">
+      <c r="I59" s="115" t="n">
         <f aca="false">SUM(I4:I58)</f>
         <v>219475297</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="115" t="s">
-        <v>1239</v>
-      </c>
-      <c r="B61" s="115"/>
-      <c r="C61" s="115"/>
-      <c r="D61" s="115"/>
-      <c r="E61" s="115"/>
-      <c r="F61" s="115"/>
-      <c r="G61" s="115"/>
-      <c r="H61" s="115"/>
-      <c r="I61" s="115"/>
-      <c r="J61" s="115"/>
-      <c r="K61" s="115"/>
-      <c r="L61" s="115"/>
-      <c r="M61" s="115"/>
-      <c r="N61" s="115"/>
-      <c r="O61" s="115"/>
+      <c r="A61" s="116" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B61" s="116"/>
+      <c r="C61" s="116"/>
+      <c r="D61" s="116"/>
+      <c r="E61" s="116"/>
+      <c r="F61" s="116"/>
+      <c r="G61" s="116"/>
+      <c r="H61" s="116"/>
+      <c r="I61" s="116"/>
+      <c r="J61" s="116"/>
+      <c r="K61" s="116"/>
+      <c r="L61" s="116"/>
+      <c r="M61" s="116"/>
+      <c r="N61" s="116"/>
+      <c r="O61" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/docs/executive-plan.xlsx
+++ b/docs/executive-plan.xlsx
@@ -21,10 +21,11 @@
     <sheet name="تكلفة اللتر" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="مستهدفات البنزين" sheetId="12" state="visible" r:id="rId14"/>
     <sheet name="العمالة والمضخات" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="الخطة التنفيذية" sheetId="14" state="visible" r:id="rId16"/>
-    <sheet name="المستهدفات الربعية" sheetId="15" state="visible" r:id="rId17"/>
-    <sheet name="المبادرات" sheetId="16" state="visible" r:id="rId18"/>
-    <sheet name="المحطات" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="شكاوى العملاء" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="الخطة التنفيذية" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="المستهدفات الربعية" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="المبادرات" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="المحطات" sheetId="18" state="visible" r:id="rId20"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2368" uniqueCount="1294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="1326">
   <si>
     <t xml:space="preserve">نموذج الخطة التنفيذية — الإدارة التجارية</t>
   </si>
@@ -125,18 +126,18 @@
     <t xml:space="preserve">صف مثال توضيحي — يُحذف قبل الاعتماد</t>
   </si>
   <si>
-    <t xml:space="preserve">منفذ ٤ — الإكسسوارات</t>
+    <t xml:space="preserve">منفذ ٢ — العقار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تفصيل الشواغر والعلامات — الأولوية الأولى.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حالة المنفذ</t>
   </si>
   <si>
     <t xml:space="preserve">السوق واللاعبون وقرار التأجير مقابل التشغيل.</t>
   </si>
   <si>
-    <t xml:space="preserve">حالة المنفذ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حصص محطات المملكة وأين نقف.</t>
-  </si>
-  <si>
     <t xml:space="preserve">قائم</t>
   </si>
   <si>
@@ -3612,6 +3613,102 @@
   </si>
   <si>
     <t xml:space="preserve">عمود «عدد المحلات التجارية» مملوء في 3 محطات فقط من 52 — غير قابل للاستخدام. وعمود «عمال الصيانة» نصّي لا رقمي («لجميع المحطات»). و«July Sales» مبيعات بالريال لا عدد معاملات رغم وقوعه في مجموعة Transactions. وخمسة أكواد صُحّحت بالمطابقة بالاسم، ومحطتان (MK257 الربوة · MK258 الستين) لا مقابل لهما في بيانات المبيعات — وقد تكونا محطتين جديدتين.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شكاوى العملاء — 103 شكوى في 5 محطات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">النصف الأول 2026 · وأربع من الخمس هي محطاتنا المنهارة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شكاوى</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قوقل ماب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شكوى/100 ألف زيارة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عمال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أعلى معدل شكاوى وأكبر محطة — 24 مراجعة عامة سلبية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الوحيدة النامية — ومعدل شكاواها نصف الباقي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التصنيف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">غير مصنّفة — تحتاج تبويباً أدق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سلوك العمال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تعامل مباشر — يُحل بالإشراف والمحاسبة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بطء الخدمة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زمن الانتظار — والمراجعات تقول «ومافي زحمة»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رفض التعبئة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">امتناع عن الخدمة — الأخطر سمعةً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تعبئة وقود خاطئ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سحب مبلغ زائد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تطبيقات تعبئة وقود</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التأكد من صحة التعبئة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔑 الإشارة الأقوى حتى الآن على سبب تراجع مكة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56% من الشكاوى الـ103 عن العامل مباشرة: بطء الخدمة (23) · سلوك العمال (28) · رفض التعبئة (5) · تدخين (1). وفي MK007 وحدها 22 بطء خدمة + 21 سلوك عمال = 74% من شكاواها. ومحطات مكة التي وردت فيها شكاوى متوسط نموها −22.9%، مقابل −7.7% لباقي محطات مكة.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ حدّ منهجي يجب ألا يُتجاوز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الملف يضم خمس محطات اختيرت لأنها الأكثر شكاوى — فلا يصحّ الاستنتاج منه أن الشكاوى تسبّب التراجع. لكن النمط الداخلي دالّ: المحطة الوحيدة النامية (MK017 +6.9%) معدل شكاواها 3.43 لكل 100 ألف زيارة — نصف المتراجعة (6.6–7.6). والاستثناء MK002: أدنى معدل شكاوى (1.82) وأسوأ تراجع (−53.3%) — فالشكاوى لا تفسّرها، ولها سبب آخر.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هذا يصحّح فرضية الازدحام لا يعيدها</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رفضنا سابقاً أن نقص المضخات سبب التراجع، وهذه الشكاوى تؤكد الرفض لا تنقضه: مراجعة حرفية تقول «تأخير 20 دقيقة ومافي زحمة والموظفين غير منظمين». أي أن المشكلة في تنفيذ الخدمة لا في الطاقة الفيزيائية — وعلاجها إشراف وتدريب وجدولة ورديات، لا مضخات جديدة. وهذا فارق بملايين الريالات في قرار الاستثمار.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔴 الإجراءات المتخذة لا تُغلق المشكلة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">من 58 شكوى في MK007: 31 انتهت بـ«إبلاغ/تنبيه المدير» · 9 بتدريب · 3 اعتذار · و**صفر استبدال أو إيقاف عامل**. ولذلك استمرت الشكاوى سبعة أشهر متصلة (13 · 8 · 9 · 11 · 7 · 6 · 4). التنبيه بلا أثر ليس إجراءً تصحيحياً.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قناة قوقل ماب تضرب الاكتساب لا الاحتفاظ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41 من 103 شكوى نُشرت على قوقل ماب — منها 24 على MK007 وحدها. هذه مراجعات عامة يقرأها كل عميل محتمل قبل أن يدخل، فأثرها يمتد إلى من لم يزرنا أصلاً. وهي أيضاً القناة الوحيدة التي يراها المنافس.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الخطوة التالية — أرخص اختبار متاح</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK007 و MK072 معاً 86 شكوى و141.6 مليون ريال إيراد سنوي مُطبَّع وتفقدان نحو 21–22%. تدخّل إشرافي مركّز فيهما لثلاثة أشهر (جدولة الذروتين 17 و21 · محاسبة على السلوك · قياس زمن الخدمة) يُختبر أثره على الشكاوى والزيارات معاً. وإن تحسّن الاتجاه فقد وجدنا السبب — وإن لم يتحسّن استبعدناه بتكلفة شبه صفرية.</t>
   </si>
   <si>
     <t xml:space="preserve">الخطة التنفيذية لمنافذ البيع</t>
@@ -4230,7 +4327,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="120">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4279,12 +4376,12 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -4620,6 +4717,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5121,15 +5230,15 @@
       <c r="B23" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="13" t="s">
         <v>40</v>
       </c>
     </row>
@@ -5137,7 +5246,7 @@
       <c r="B25" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="13" t="s">
         <v>42</v>
       </c>
     </row>
@@ -5939,7 +6048,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>888</v>
       </c>
       <c r="C7" s="81"/>
@@ -5951,7 +6060,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="13" t="s">
         <v>890</v>
       </c>
       <c r="C8" s="81"/>
@@ -5961,7 +6070,7 @@
       <c r="F8" s="26"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>892</v>
       </c>
       <c r="C9" s="81"/>
@@ -5971,7 +6080,7 @@
       <c r="F9" s="26"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="13" t="s">
         <v>894</v>
       </c>
       <c r="C10" s="83"/>
@@ -5981,7 +6090,7 @@
       <c r="F10" s="26"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="13" t="s">
         <v>896</v>
       </c>
       <c r="C11" s="83"/>
@@ -5991,7 +6100,7 @@
       <c r="F11" s="26"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="13" t="s">
         <v>898</v>
       </c>
       <c r="C12" s="83"/>
@@ -6001,7 +6110,7 @@
       <c r="F12" s="26"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="13" t="s">
         <v>900</v>
       </c>
       <c r="C13" s="83"/>
@@ -6011,7 +6120,7 @@
       <c r="F13" s="26"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="13" t="s">
         <v>902</v>
       </c>
       <c r="C14" s="83"/>
@@ -10577,7 +10686,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>997</v>
       </c>
       <c r="D6" s="69"/>
@@ -10595,7 +10704,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>1001</v>
       </c>
       <c r="D7" s="26" t="n">
@@ -16997,6 +17106,620 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:K28"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>858</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>914</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>1196</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>860</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>1197</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="E5" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" s="28" t="n">
+        <v>4236</v>
+      </c>
+      <c r="G5" s="98" t="n">
+        <f aca="false">IFERROR(D5/(F5*181)*100000,"")</f>
+        <v>7.56473061733419</v>
+      </c>
+      <c r="H5" s="99" t="n">
+        <v>-0.223</v>
+      </c>
+      <c r="I5" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="J5" s="28" t="n">
+        <f aca="false">IFERROR(F5/I5,"")</f>
+        <v>132.375</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>2359</v>
+      </c>
+      <c r="G6" s="98" t="n">
+        <f aca="false">IFERROR(D6/(F6*180)*100000,"")</f>
+        <v>6.59413122321134</v>
+      </c>
+      <c r="H6" s="99" t="n">
+        <v>-0.211</v>
+      </c>
+      <c r="I6" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="J6" s="28" t="n">
+        <f aca="false">IFERROR(F6/I6,"")</f>
+        <v>168.5</v>
+      </c>
+      <c r="K6" s="16"/>
+    </row>
+    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>944</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>1290</v>
+      </c>
+      <c r="G7" s="98" t="n">
+        <f aca="false">IFERROR(D7/(F7*181)*100000,"")</f>
+        <v>3.42627093237398</v>
+      </c>
+      <c r="H7" s="100" t="n">
+        <v>0.069</v>
+      </c>
+      <c r="I7" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" s="28" t="n">
+        <f aca="false">IFERROR(F7/I7,"")</f>
+        <v>143.333333333333</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D8" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>456</v>
+      </c>
+      <c r="G8" s="98" t="n">
+        <f aca="false">IFERROR(D8/(F8*181)*100000,"")</f>
+        <v>7.26955510322768</v>
+      </c>
+      <c r="H8" s="99" t="n">
+        <v>-0.249</v>
+      </c>
+      <c r="I8" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" s="28" t="n">
+        <f aca="false">IFERROR(F8/I8,"")</f>
+        <v>91.2</v>
+      </c>
+      <c r="K8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>952</v>
+      </c>
+      <c r="D9" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>913</v>
+      </c>
+      <c r="G9" s="98" t="n">
+        <f aca="false">IFERROR(D9/(F9*181)*100000,"")</f>
+        <v>1.81539820759684</v>
+      </c>
+      <c r="H9" s="99" t="n">
+        <v>-0.533</v>
+      </c>
+      <c r="I9" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" s="28" t="n">
+        <f aca="false">IFERROR(F9/I9,"")</f>
+        <v>130.428571428571</v>
+      </c>
+      <c r="K9" s="16"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="32"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="32" t="n">
+        <f aca="false">SUM(D5:D9)</f>
+        <v>103</v>
+      </c>
+      <c r="E10" s="32" t="n">
+        <f aca="false">SUM(E5:E9)</f>
+        <v>41</v>
+      </c>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="78" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>406</v>
+      </c>
+      <c r="C14" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="D14" s="45" t="n">
+        <f aca="false">C14/103</f>
+        <v>0.271844660194175</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="16" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C15" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="D15" s="45" t="n">
+        <f aca="false">C15/103</f>
+        <v>0.271844660194175</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="16" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C16" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="D16" s="45" t="n">
+        <f aca="false">C16/103</f>
+        <v>0.233009708737864</v>
+      </c>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="16" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C17" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="45" t="n">
+        <f aca="false">C17/103</f>
+        <v>0.0485436893203884</v>
+      </c>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="16" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C18" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="45" t="n">
+        <f aca="false">C18/103</f>
+        <v>0.029126213592233</v>
+      </c>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="16"/>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C19" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="45" t="n">
+        <f aca="false">C19/103</f>
+        <v>0.0194174757281553</v>
+      </c>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="16"/>
+    </row>
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C20" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="45" t="n">
+        <f aca="false">C20/103</f>
+        <v>0.0194174757281553</v>
+      </c>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="16"/>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C21" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="45" t="n">
+        <f aca="false">C21/103</f>
+        <v>0.0194174757281553</v>
+      </c>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="16"/>
+    </row>
+    <row r="23" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="54" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="53"/>
+    </row>
+    <row r="24" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="52" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="53"/>
+    </row>
+    <row r="25" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="54" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+    </row>
+    <row r="26" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="54" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+    </row>
+    <row r="27" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="52" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+    </row>
+    <row r="28" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="52" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="C23:K23"/>
+    <mergeCell ref="C24:K24"/>
+    <mergeCell ref="C25:K25"/>
+    <mergeCell ref="C26:K26"/>
+    <mergeCell ref="C27:K27"/>
+    <mergeCell ref="C28:K28"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:O18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -17018,7 +17741,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1192</v>
+        <v>1224</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -17037,7 +17760,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1193</v>
+        <v>1225</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -17068,86 +17791,86 @@
         <v>55</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>1194</v>
+        <v>1226</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1195</v>
+        <v>1227</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1196</v>
+        <v>1228</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1197</v>
+        <v>1229</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>58</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>1198</v>
+        <v>1230</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>1199</v>
+        <v>1231</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>59</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>1200</v>
+        <v>1232</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>1201</v>
+        <v>1233</v>
       </c>
       <c r="O3" s="15" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="98" t="s">
-        <v>1202</v>
-      </c>
-      <c r="B4" s="99" t="s">
-        <v>1203</v>
-      </c>
-      <c r="C4" s="98" t="s">
+      <c r="A4" s="101" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B4" s="102" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C4" s="101" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="99" t="s">
-        <v>1204</v>
-      </c>
-      <c r="E4" s="98" t="n">
+      <c r="D4" s="102" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E4" s="101" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="98" t="s">
-        <v>1205</v>
-      </c>
-      <c r="G4" s="99" t="s">
-        <v>1206</v>
-      </c>
-      <c r="H4" s="98" t="n">
+      <c r="F4" s="101" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G4" s="102" t="s">
+        <v>1238</v>
+      </c>
+      <c r="H4" s="101" t="n">
         <v>20</v>
       </c>
-      <c r="I4" s="98" t="n">
+      <c r="I4" s="101" t="n">
         <f aca="false">IF(H4="","",H4-E4)</f>
         <v>14</v>
       </c>
-      <c r="J4" s="100" t="n">
+      <c r="J4" s="103" t="n">
         <f aca="false">IFERROR(IF(H4="","",(H4-E4)/E4),"")</f>
         <v>2.33333333333333</v>
       </c>
-      <c r="K4" s="99" t="s">
-        <v>1207</v>
-      </c>
-      <c r="L4" s="98" t="s">
+      <c r="K4" s="102" t="s">
+        <v>1239</v>
+      </c>
+      <c r="L4" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="M4" s="99" t="s">
-        <v>1208</v>
-      </c>
-      <c r="N4" s="99" t="s">
-        <v>1209</v>
-      </c>
-      <c r="O4" s="98" t="s">
-        <v>1210</v>
+      <c r="M4" s="102" t="s">
+        <v>1240</v>
+      </c>
+      <c r="N4" s="102" t="s">
+        <v>1241</v>
+      </c>
+      <c r="O4" s="101" t="s">
+        <v>1242</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17163,17 +17886,17 @@
       <c r="D5" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="101" t="n">
+      <c r="E5" s="104" t="n">
         <v>1271</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>1211</v>
+        <v>1243</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>1212</v>
-      </c>
-      <c r="H5" s="102"/>
-      <c r="I5" s="101" t="str">
+        <v>1244</v>
+      </c>
+      <c r="H5" s="105"/>
+      <c r="I5" s="104" t="str">
         <f aca="false">IF(H5="","",H5-E5)</f>
         <v/>
       </c>
@@ -17181,15 +17904,15 @@
         <f aca="false">IFERROR(IF(H5="","",(H5-E5)/E5),"")</f>
         <v/>
       </c>
-      <c r="K5" s="103"/>
+      <c r="K5" s="106"/>
       <c r="L5" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M5" s="103"/>
+      <c r="M5" s="106"/>
       <c r="N5" s="16" t="s">
-        <v>1213</v>
-      </c>
-      <c r="O5" s="104"/>
+        <v>1245</v>
+      </c>
+      <c r="O5" s="107"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="n">
@@ -17204,17 +17927,17 @@
       <c r="D6" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="101" t="n">
+      <c r="E6" s="104" t="n">
         <v>25</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>1214</v>
+        <v>1246</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>1215</v>
-      </c>
-      <c r="H6" s="102"/>
-      <c r="I6" s="101" t="str">
+        <v>1247</v>
+      </c>
+      <c r="H6" s="105"/>
+      <c r="I6" s="104" t="str">
         <f aca="false">IF(H6="","",H6-E6)</f>
         <v/>
       </c>
@@ -17222,15 +17945,15 @@
         <f aca="false">IFERROR(IF(H6="","",(H6-E6)/E6),"")</f>
         <v/>
       </c>
-      <c r="K6" s="103"/>
+      <c r="K6" s="106"/>
       <c r="L6" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M6" s="103"/>
+      <c r="M6" s="106"/>
       <c r="N6" s="16" t="s">
-        <v>1216</v>
-      </c>
-      <c r="O6" s="104"/>
+        <v>1248</v>
+      </c>
+      <c r="O6" s="107"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="n">
@@ -17245,17 +17968,17 @@
       <c r="D7" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="101" t="n">
+      <c r="E7" s="104" t="n">
         <v>39</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>1217</v>
+        <v>1249</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>1206</v>
-      </c>
-      <c r="H7" s="102"/>
-      <c r="I7" s="101" t="str">
+        <v>1238</v>
+      </c>
+      <c r="H7" s="105"/>
+      <c r="I7" s="104" t="str">
         <f aca="false">IF(H7="","",H7-E7)</f>
         <v/>
       </c>
@@ -17263,15 +17986,15 @@
         <f aca="false">IFERROR(IF(H7="","",(H7-E7)/E7),"")</f>
         <v/>
       </c>
-      <c r="K7" s="103"/>
+      <c r="K7" s="106"/>
       <c r="L7" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M7" s="103"/>
+      <c r="M7" s="106"/>
       <c r="N7" s="16" t="s">
-        <v>1218</v>
-      </c>
-      <c r="O7" s="104"/>
+        <v>1250</v>
+      </c>
+      <c r="O7" s="107"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="n">
@@ -17286,17 +18009,17 @@
       <c r="D8" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="101" t="n">
+      <c r="E8" s="104" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>1219</v>
+        <v>1251</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>1220</v>
-      </c>
-      <c r="H8" s="102"/>
-      <c r="I8" s="101" t="str">
+        <v>1252</v>
+      </c>
+      <c r="H8" s="105"/>
+      <c r="I8" s="104" t="str">
         <f aca="false">IF(H8="","",H8-E8)</f>
         <v/>
       </c>
@@ -17304,40 +18027,40 @@
         <f aca="false">IFERROR(IF(H8="","",(H8-E8)/E8),"")</f>
         <v/>
       </c>
-      <c r="K8" s="103"/>
+      <c r="K8" s="106"/>
       <c r="L8" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="103"/>
+      <c r="M8" s="106"/>
       <c r="N8" s="16" t="s">
-        <v>1221</v>
-      </c>
-      <c r="O8" s="104"/>
+        <v>1253</v>
+      </c>
+      <c r="O8" s="107"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1222</v>
+        <v>1254</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>53</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>1223</v>
-      </c>
-      <c r="E9" s="101" t="n">
+        <v>1255</v>
+      </c>
+      <c r="E9" s="104" t="n">
         <v>0.28</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>1224</v>
+        <v>1256</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>1225</v>
-      </c>
-      <c r="H9" s="102"/>
-      <c r="I9" s="101" t="str">
+        <v>1257</v>
+      </c>
+      <c r="H9" s="105"/>
+      <c r="I9" s="104" t="str">
         <f aca="false">IF(H9="","",H9-E9)</f>
         <v/>
       </c>
@@ -17345,22 +18068,22 @@
         <f aca="false">IFERROR(IF(H9="","",(H9-E9)/E9),"")</f>
         <v/>
       </c>
-      <c r="K9" s="103"/>
+      <c r="K9" s="106"/>
       <c r="L9" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="M9" s="103"/>
+      <c r="M9" s="106"/>
       <c r="N9" s="16" t="s">
-        <v>1226</v>
-      </c>
-      <c r="O9" s="104"/>
+        <v>1258</v>
+      </c>
+      <c r="O9" s="107"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1227</v>
+        <v>1259</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>53</v>
@@ -17368,17 +18091,17 @@
       <c r="D10" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="E10" s="101" t="n">
+      <c r="E10" s="104" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>1228</v>
+        <v>1260</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>1229</v>
-      </c>
-      <c r="H10" s="102"/>
-      <c r="I10" s="101" t="str">
+        <v>1261</v>
+      </c>
+      <c r="H10" s="105"/>
+      <c r="I10" s="104" t="str">
         <f aca="false">IF(H10="","",H10-E10)</f>
         <v/>
       </c>
@@ -17386,15 +18109,15 @@
         <f aca="false">IFERROR(IF(H10="","",(H10-E10)/E10),"")</f>
         <v/>
       </c>
-      <c r="K10" s="103"/>
+      <c r="K10" s="106"/>
       <c r="L10" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M10" s="103"/>
+      <c r="M10" s="106"/>
       <c r="N10" s="16" t="s">
-        <v>1230</v>
-      </c>
-      <c r="O10" s="104"/>
+        <v>1262</v>
+      </c>
+      <c r="O10" s="107"/>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="n">
@@ -17407,19 +18130,19 @@
         <v>95</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>1231</v>
-      </c>
-      <c r="E11" s="101" t="n">
+        <v>1263</v>
+      </c>
+      <c r="E11" s="104" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>1232</v>
+        <v>1264</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>1233</v>
-      </c>
-      <c r="H11" s="102"/>
-      <c r="I11" s="101" t="str">
+        <v>1265</v>
+      </c>
+      <c r="H11" s="105"/>
+      <c r="I11" s="104" t="str">
         <f aca="false">IF(H11="","",H11-E11)</f>
         <v/>
       </c>
@@ -17427,15 +18150,15 @@
         <f aca="false">IFERROR(IF(H11="","",(H11-E11)/E11),"")</f>
         <v/>
       </c>
-      <c r="K11" s="103"/>
+      <c r="K11" s="106"/>
       <c r="L11" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="M11" s="103"/>
+      <c r="M11" s="106"/>
       <c r="N11" s="16" t="s">
-        <v>1234</v>
-      </c>
-      <c r="O11" s="104"/>
+        <v>1266</v>
+      </c>
+      <c r="O11" s="107"/>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="n">
@@ -17450,17 +18173,17 @@
       <c r="D12" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="101" t="n">
+      <c r="E12" s="104" t="n">
         <v>31</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>1235</v>
+        <v>1267</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>1236</v>
-      </c>
-      <c r="H12" s="102"/>
-      <c r="I12" s="101" t="str">
+        <v>1268</v>
+      </c>
+      <c r="H12" s="105"/>
+      <c r="I12" s="104" t="str">
         <f aca="false">IF(H12="","",H12-E12)</f>
         <v/>
       </c>
@@ -17468,15 +18191,15 @@
         <f aca="false">IFERROR(IF(H12="","",(H12-E12)/E12),"")</f>
         <v/>
       </c>
-      <c r="K12" s="103"/>
+      <c r="K12" s="106"/>
       <c r="L12" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M12" s="103"/>
+      <c r="M12" s="106"/>
       <c r="N12" s="16" t="s">
-        <v>1237</v>
-      </c>
-      <c r="O12" s="104"/>
+        <v>1269</v>
+      </c>
+      <c r="O12" s="107"/>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="n">
@@ -17491,17 +18214,17 @@
       <c r="D13" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="E13" s="101" t="n">
+      <c r="E13" s="104" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>1238</v>
+        <v>1270</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>1239</v>
-      </c>
-      <c r="H13" s="102"/>
-      <c r="I13" s="101" t="str">
+        <v>1271</v>
+      </c>
+      <c r="H13" s="105"/>
+      <c r="I13" s="104" t="str">
         <f aca="false">IF(H13="","",H13-E13)</f>
         <v/>
       </c>
@@ -17509,15 +18232,15 @@
         <f aca="false">IFERROR(IF(H13="","",(H13-E13)/E13),"")</f>
         <v/>
       </c>
-      <c r="K13" s="103"/>
+      <c r="K13" s="106"/>
       <c r="L13" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M13" s="103"/>
+      <c r="M13" s="106"/>
       <c r="N13" s="16" t="s">
-        <v>1240</v>
-      </c>
-      <c r="O13" s="104"/>
+        <v>1272</v>
+      </c>
+      <c r="O13" s="107"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="n">
@@ -17532,17 +18255,17 @@
       <c r="D14" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="E14" s="101" t="n">
+      <c r="E14" s="104" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>1241</v>
+        <v>1273</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>1242</v>
-      </c>
-      <c r="H14" s="102"/>
-      <c r="I14" s="101" t="str">
+        <v>1274</v>
+      </c>
+      <c r="H14" s="105"/>
+      <c r="I14" s="104" t="str">
         <f aca="false">IF(H14="","",H14-E14)</f>
         <v/>
       </c>
@@ -17550,15 +18273,15 @@
         <f aca="false">IFERROR(IF(H14="","",(H14-E14)/E14),"")</f>
         <v/>
       </c>
-      <c r="K14" s="103"/>
+      <c r="K14" s="106"/>
       <c r="L14" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="103"/>
+      <c r="M14" s="106"/>
       <c r="N14" s="16" t="s">
-        <v>1243</v>
-      </c>
-      <c r="O14" s="104"/>
+        <v>1275</v>
+      </c>
+      <c r="O14" s="107"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="n">
@@ -17571,19 +18294,19 @@
         <v>52</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>1204</v>
-      </c>
-      <c r="E15" s="101" t="n">
+        <v>1236</v>
+      </c>
+      <c r="E15" s="104" t="n">
         <v>6</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>1232</v>
+        <v>1264</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H15" s="102"/>
-      <c r="I15" s="101" t="str">
+        <v>1276</v>
+      </c>
+      <c r="H15" s="105"/>
+      <c r="I15" s="104" t="str">
         <f aca="false">IF(H15="","",H15-E15)</f>
         <v/>
       </c>
@@ -17591,15 +18314,15 @@
         <f aca="false">IFERROR(IF(H15="","",(H15-E15)/E15),"")</f>
         <v/>
       </c>
-      <c r="K15" s="103"/>
+      <c r="K15" s="106"/>
       <c r="L15" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M15" s="103"/>
+      <c r="M15" s="106"/>
       <c r="N15" s="16" t="s">
-        <v>1245</v>
-      </c>
-      <c r="O15" s="104"/>
+        <v>1277</v>
+      </c>
+      <c r="O15" s="107"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="n">
@@ -17612,19 +18335,19 @@
         <v>52</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>1246</v>
-      </c>
-      <c r="E16" s="101" t="n">
+        <v>1278</v>
+      </c>
+      <c r="E16" s="104" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>1247</v>
+        <v>1279</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>1248</v>
-      </c>
-      <c r="H16" s="102"/>
-      <c r="I16" s="101" t="str">
+        <v>1280</v>
+      </c>
+      <c r="H16" s="105"/>
+      <c r="I16" s="104" t="str">
         <f aca="false">IF(H16="","",H16-E16)</f>
         <v/>
       </c>
@@ -17632,31 +18355,31 @@
         <f aca="false">IFERROR(IF(H16="","",(H16-E16)/E16),"")</f>
         <v/>
       </c>
-      <c r="K16" s="103"/>
+      <c r="K16" s="106"/>
       <c r="L16" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M16" s="103"/>
+      <c r="M16" s="106"/>
       <c r="N16" s="16" t="s">
-        <v>1249</v>
-      </c>
-      <c r="O16" s="104"/>
+        <v>1281</v>
+      </c>
+      <c r="O16" s="107"/>
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
-        <v>1250</v>
-      </c>
-      <c r="C18" s="105" t="s">
-        <v>1251</v>
-      </c>
-      <c r="D18" s="105"/>
-      <c r="E18" s="105"/>
-      <c r="F18" s="105"/>
-      <c r="G18" s="105"/>
-      <c r="H18" s="105"/>
-      <c r="I18" s="105"/>
-      <c r="J18" s="105"/>
-      <c r="K18" s="105"/>
+        <v>1282</v>
+      </c>
+      <c r="C18" s="108" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D18" s="108"/>
+      <c r="E18" s="108"/>
+      <c r="F18" s="108"/>
+      <c r="G18" s="108"/>
+      <c r="H18" s="108"/>
+      <c r="I18" s="108"/>
+      <c r="J18" s="108"/>
+      <c r="K18" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -17674,7 +18397,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -17708,7 +18431,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1252</v>
+        <v>1284</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -17729,52 +18452,52 @@
         <v>50</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>1201</v>
+        <v>1233</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>1194</v>
+        <v>1226</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>1253</v>
+        <v>1285</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1254</v>
+        <v>1286</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1255</v>
+        <v>1287</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1256</v>
+        <v>1288</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>1197</v>
+        <v>1229</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>1257</v>
+        <v>1289</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>1258</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="106" t="n">
+      <c r="A4" s="109" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="107" t="s">
-        <v>1213</v>
-      </c>
-      <c r="D4" s="108" t="n">
+      <c r="C4" s="110" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D4" s="111" t="n">
         <f aca="false">'الخطة التنفيذية'!E5</f>
         <v>1271</v>
       </c>
-      <c r="E4" s="102"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="108" t="str">
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="111" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H5="","",'الخطة التنفيذية'!H5)</f>
         <v/>
       </c>
@@ -17788,24 +18511,24 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="106" t="n">
+      <c r="A5" s="109" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="107" t="s">
-        <v>1216</v>
-      </c>
-      <c r="D5" s="108" t="n">
+      <c r="C5" s="110" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D5" s="111" t="n">
         <f aca="false">'الخطة التنفيذية'!E6</f>
         <v>25</v>
       </c>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="102"/>
-      <c r="I5" s="108" t="str">
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="111" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H6="","",'الخطة التنفيذية'!H6)</f>
         <v/>
       </c>
@@ -17819,24 +18542,24 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="106" t="n">
+      <c r="A6" s="109" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="107" t="s">
-        <v>1218</v>
-      </c>
-      <c r="D6" s="108" t="n">
+      <c r="C6" s="110" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D6" s="111" t="n">
         <f aca="false">'الخطة التنفيذية'!E7</f>
         <v>39</v>
       </c>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="108" t="str">
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="105"/>
+      <c r="I6" s="111" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H7="","",'الخطة التنفيذية'!H7)</f>
         <v/>
       </c>
@@ -17850,24 +18573,24 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="106" t="n">
+      <c r="A7" s="109" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="107" t="s">
-        <v>1221</v>
-      </c>
-      <c r="D7" s="108" t="n">
+      <c r="C7" s="110" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D7" s="111" t="n">
         <f aca="false">'الخطة التنفيذية'!E8</f>
         <v>0</v>
       </c>
-      <c r="E7" s="102"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="108" t="str">
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="111" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H8="","",'الخطة التنفيذية'!H8)</f>
         <v/>
       </c>
@@ -17881,24 +18604,24 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="106" t="n">
+      <c r="A8" s="109" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>1222</v>
-      </c>
-      <c r="C8" s="107" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D8" s="108" t="n">
+        <v>1254</v>
+      </c>
+      <c r="C8" s="110" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D8" s="111" t="n">
         <f aca="false">'الخطة التنفيذية'!E9</f>
         <v>0.28</v>
       </c>
-      <c r="E8" s="102"/>
-      <c r="F8" s="102"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="102"/>
-      <c r="I8" s="108" t="str">
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="105"/>
+      <c r="I8" s="111" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H9="","",'الخطة التنفيذية'!H9)</f>
         <v/>
       </c>
@@ -17912,24 +18635,24 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="106" t="n">
+      <c r="A9" s="109" t="n">
         <v>6</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1227</v>
-      </c>
-      <c r="C9" s="107" t="s">
-        <v>1230</v>
-      </c>
-      <c r="D9" s="108" t="n">
+        <v>1259</v>
+      </c>
+      <c r="C9" s="110" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D9" s="111" t="n">
         <f aca="false">'الخطة التنفيذية'!E10</f>
         <v>0</v>
       </c>
-      <c r="E9" s="102"/>
-      <c r="F9" s="102"/>
-      <c r="G9" s="102"/>
-      <c r="H9" s="102"/>
-      <c r="I9" s="108" t="str">
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="111" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H10="","",'الخطة التنفيذية'!H10)</f>
         <v/>
       </c>
@@ -17943,24 +18666,24 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="106" t="n">
+      <c r="A10" s="109" t="n">
         <v>7</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="107" t="s">
-        <v>1234</v>
-      </c>
-      <c r="D10" s="108" t="n">
+      <c r="C10" s="110" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D10" s="111" t="n">
         <f aca="false">'الخطة التنفيذية'!E11</f>
         <v>0</v>
       </c>
-      <c r="E10" s="102"/>
-      <c r="F10" s="102"/>
-      <c r="G10" s="102"/>
-      <c r="H10" s="102"/>
-      <c r="I10" s="108" t="str">
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="111" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H11="","",'الخطة التنفيذية'!H11)</f>
         <v/>
       </c>
@@ -17974,24 +18697,24 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="106" t="n">
+      <c r="A11" s="109" t="n">
         <v>8</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="107" t="s">
-        <v>1237</v>
-      </c>
-      <c r="D11" s="108" t="n">
+      <c r="C11" s="110" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D11" s="111" t="n">
         <f aca="false">'الخطة التنفيذية'!E12</f>
         <v>31</v>
       </c>
-      <c r="E11" s="102"/>
-      <c r="F11" s="102"/>
-      <c r="G11" s="102"/>
-      <c r="H11" s="102"/>
-      <c r="I11" s="108" t="str">
+      <c r="E11" s="105"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="105"/>
+      <c r="I11" s="111" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H12="","",'الخطة التنفيذية'!H12)</f>
         <v/>
       </c>
@@ -18005,24 +18728,24 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="106" t="n">
+      <c r="A12" s="109" t="n">
         <v>9</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="C12" s="107" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D12" s="108" t="n">
+      <c r="C12" s="110" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D12" s="111" t="n">
         <f aca="false">'الخطة التنفيذية'!E13</f>
         <v>0</v>
       </c>
-      <c r="E12" s="102"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="102"/>
-      <c r="I12" s="108" t="str">
+      <c r="E12" s="105"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="111" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H13="","",'الخطة التنفيذية'!H13)</f>
         <v/>
       </c>
@@ -18036,24 +18759,24 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="106" t="n">
+      <c r="A13" s="109" t="n">
         <v>10</v>
       </c>
       <c r="B13" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="107" t="s">
-        <v>1243</v>
-      </c>
-      <c r="D13" s="108" t="n">
+      <c r="C13" s="110" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D13" s="111" t="n">
         <f aca="false">'الخطة التنفيذية'!E14</f>
         <v>0</v>
       </c>
-      <c r="E13" s="102"/>
-      <c r="F13" s="102"/>
-      <c r="G13" s="102"/>
-      <c r="H13" s="102"/>
-      <c r="I13" s="108" t="str">
+      <c r="E13" s="105"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="111" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H14="","",'الخطة التنفيذية'!H14)</f>
         <v/>
       </c>
@@ -18067,24 +18790,24 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="106" t="n">
+      <c r="A14" s="109" t="n">
         <v>11</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="107" t="s">
-        <v>1245</v>
-      </c>
-      <c r="D14" s="108" t="n">
+      <c r="C14" s="110" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D14" s="111" t="n">
         <f aca="false">'الخطة التنفيذية'!E15</f>
         <v>6</v>
       </c>
-      <c r="E14" s="102"/>
-      <c r="F14" s="102"/>
-      <c r="G14" s="102"/>
-      <c r="H14" s="102"/>
-      <c r="I14" s="108" t="str">
+      <c r="E14" s="105"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="105"/>
+      <c r="I14" s="111" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H15="","",'الخطة التنفيذية'!H15)</f>
         <v/>
       </c>
@@ -18098,24 +18821,24 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="106" t="n">
+      <c r="A15" s="109" t="n">
         <v>12</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="107" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D15" s="108" t="n">
+      <c r="C15" s="110" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D15" s="111" t="n">
         <f aca="false">'الخطة التنفيذية'!E16</f>
         <v>0</v>
       </c>
-      <c r="E15" s="102"/>
-      <c r="F15" s="102"/>
-      <c r="G15" s="102"/>
-      <c r="H15" s="102"/>
-      <c r="I15" s="108" t="str">
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="111" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H16="","",'الخطة التنفيذية'!H16)</f>
         <v/>
       </c>
@@ -18143,7 +18866,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -18167,7 +18890,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1259</v>
+        <v>1291</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -18185,7 +18908,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1260</v>
+        <v>1292</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -18206,34 +18929,34 @@
         <v>49</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>1261</v>
+        <v>1293</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>50</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>1262</v>
+        <v>1294</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>59</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1200</v>
+        <v>1232</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1263</v>
+        <v>1295</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1264</v>
+        <v>1296</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>1265</v>
+        <v>1297</v>
       </c>
       <c r="J3" s="15" t="s">
         <v>60</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>1266</v>
+        <v>1298</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>679</v>
@@ -18242,561 +18965,561 @@
         <v>383</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>1267</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="98" t="s">
-        <v>1202</v>
-      </c>
-      <c r="B4" s="99" t="s">
-        <v>1268</v>
-      </c>
-      <c r="C4" s="98" t="s">
+      <c r="A4" s="101" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B4" s="102" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C4" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="98" t="s">
+      <c r="D4" s="101" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="98" t="s">
+      <c r="E4" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="98" t="s">
-        <v>1208</v>
-      </c>
-      <c r="G4" s="109" t="n">
+      <c r="F4" s="101" t="s">
+        <v>1240</v>
+      </c>
+      <c r="G4" s="112" t="n">
         <v>46235</v>
       </c>
-      <c r="H4" s="109" t="n">
+      <c r="H4" s="112" t="n">
         <v>46326</v>
       </c>
-      <c r="I4" s="98" t="n">
+      <c r="I4" s="101" t="n">
         <f aca="false">IF(OR(G4="",H4=""),"",H4-G4)</f>
         <v>91</v>
       </c>
-      <c r="J4" s="98" t="n">
+      <c r="J4" s="101" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="98" t="s">
-        <v>1269</v>
-      </c>
-      <c r="L4" s="99" t="s">
-        <v>1270</v>
-      </c>
-      <c r="M4" s="98" t="s">
-        <v>1210</v>
-      </c>
-      <c r="N4" s="110" t="n">
+      <c r="K4" s="101" t="s">
+        <v>1301</v>
+      </c>
+      <c r="L4" s="102" t="s">
+        <v>1302</v>
+      </c>
+      <c r="M4" s="101" t="s">
+        <v>1242</v>
+      </c>
+      <c r="N4" s="113" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="106" t="n">
+      <c r="A5" s="109" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="103"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
+      <c r="B5" s="106"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
       <c r="I5" s="21" t="str">
         <f aca="false">IF(OR(G5="",H5=""),"",H5-G5)</f>
         <v/>
       </c>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-      <c r="L5" s="103"/>
-      <c r="M5" s="104"/>
-      <c r="N5" s="112"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="107"/>
+      <c r="L5" s="106"/>
+      <c r="M5" s="107"/>
+      <c r="N5" s="115"/>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="106" t="n">
+      <c r="A6" s="109" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="103"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
-      <c r="F6" s="104"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="111"/>
+      <c r="B6" s="106"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="107"/>
+      <c r="F6" s="107"/>
+      <c r="G6" s="114"/>
+      <c r="H6" s="114"/>
       <c r="I6" s="21" t="str">
         <f aca="false">IF(OR(G6="",H6=""),"",H6-G6)</f>
         <v/>
       </c>
-      <c r="J6" s="104"/>
-      <c r="K6" s="104"/>
-      <c r="L6" s="103"/>
-      <c r="M6" s="104"/>
-      <c r="N6" s="112"/>
+      <c r="J6" s="107"/>
+      <c r="K6" s="107"/>
+      <c r="L6" s="106"/>
+      <c r="M6" s="107"/>
+      <c r="N6" s="115"/>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="106" t="n">
+      <c r="A7" s="109" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="103"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
+      <c r="B7" s="106"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="107"/>
+      <c r="F7" s="107"/>
+      <c r="G7" s="114"/>
+      <c r="H7" s="114"/>
       <c r="I7" s="21" t="str">
         <f aca="false">IF(OR(G7="",H7=""),"",H7-G7)</f>
         <v/>
       </c>
-      <c r="J7" s="104"/>
-      <c r="K7" s="104"/>
-      <c r="L7" s="103"/>
-      <c r="M7" s="104"/>
-      <c r="N7" s="112"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="106"/>
+      <c r="M7" s="107"/>
+      <c r="N7" s="115"/>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="106" t="n">
+      <c r="A8" s="109" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="103"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
-      <c r="F8" s="104"/>
-      <c r="G8" s="111"/>
-      <c r="H8" s="111"/>
+      <c r="B8" s="106"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="114"/>
+      <c r="H8" s="114"/>
       <c r="I8" s="21" t="str">
         <f aca="false">IF(OR(G8="",H8=""),"",H8-G8)</f>
         <v/>
       </c>
-      <c r="J8" s="104"/>
-      <c r="K8" s="104"/>
-      <c r="L8" s="103"/>
-      <c r="M8" s="104"/>
-      <c r="N8" s="112"/>
+      <c r="J8" s="107"/>
+      <c r="K8" s="107"/>
+      <c r="L8" s="106"/>
+      <c r="M8" s="107"/>
+      <c r="N8" s="115"/>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="106" t="n">
+      <c r="A9" s="109" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="103"/>
-      <c r="C9" s="104"/>
-      <c r="D9" s="104"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="111"/>
-      <c r="H9" s="111"/>
+      <c r="B9" s="106"/>
+      <c r="C9" s="107"/>
+      <c r="D9" s="107"/>
+      <c r="E9" s="107"/>
+      <c r="F9" s="107"/>
+      <c r="G9" s="114"/>
+      <c r="H9" s="114"/>
       <c r="I9" s="21" t="str">
         <f aca="false">IF(OR(G9="",H9=""),"",H9-G9)</f>
         <v/>
       </c>
-      <c r="J9" s="104"/>
-      <c r="K9" s="104"/>
-      <c r="L9" s="103"/>
-      <c r="M9" s="104"/>
-      <c r="N9" s="112"/>
+      <c r="J9" s="107"/>
+      <c r="K9" s="107"/>
+      <c r="L9" s="106"/>
+      <c r="M9" s="107"/>
+      <c r="N9" s="115"/>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="106" t="n">
+      <c r="A10" s="109" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="103"/>
-      <c r="C10" s="104"/>
-      <c r="D10" s="104"/>
-      <c r="E10" s="104"/>
-      <c r="F10" s="104"/>
-      <c r="G10" s="111"/>
-      <c r="H10" s="111"/>
+      <c r="B10" s="106"/>
+      <c r="C10" s="107"/>
+      <c r="D10" s="107"/>
+      <c r="E10" s="107"/>
+      <c r="F10" s="107"/>
+      <c r="G10" s="114"/>
+      <c r="H10" s="114"/>
       <c r="I10" s="21" t="str">
         <f aca="false">IF(OR(G10="",H10=""),"",H10-G10)</f>
         <v/>
       </c>
-      <c r="J10" s="104"/>
-      <c r="K10" s="104"/>
-      <c r="L10" s="103"/>
-      <c r="M10" s="104"/>
-      <c r="N10" s="112"/>
+      <c r="J10" s="107"/>
+      <c r="K10" s="107"/>
+      <c r="L10" s="106"/>
+      <c r="M10" s="107"/>
+      <c r="N10" s="115"/>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="106" t="n">
+      <c r="A11" s="109" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="103"/>
-      <c r="C11" s="104"/>
-      <c r="D11" s="104"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="111"/>
-      <c r="H11" s="111"/>
+      <c r="B11" s="106"/>
+      <c r="C11" s="107"/>
+      <c r="D11" s="107"/>
+      <c r="E11" s="107"/>
+      <c r="F11" s="107"/>
+      <c r="G11" s="114"/>
+      <c r="H11" s="114"/>
       <c r="I11" s="21" t="str">
         <f aca="false">IF(OR(G11="",H11=""),"",H11-G11)</f>
         <v/>
       </c>
-      <c r="J11" s="104"/>
-      <c r="K11" s="104"/>
-      <c r="L11" s="103"/>
-      <c r="M11" s="104"/>
-      <c r="N11" s="112"/>
+      <c r="J11" s="107"/>
+      <c r="K11" s="107"/>
+      <c r="L11" s="106"/>
+      <c r="M11" s="107"/>
+      <c r="N11" s="115"/>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="106" t="n">
+      <c r="A12" s="109" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="103"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="111"/>
-      <c r="H12" s="111"/>
+      <c r="B12" s="106"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="107"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="114"/>
+      <c r="H12" s="114"/>
       <c r="I12" s="21" t="str">
         <f aca="false">IF(OR(G12="",H12=""),"",H12-G12)</f>
         <v/>
       </c>
-      <c r="J12" s="104"/>
-      <c r="K12" s="104"/>
-      <c r="L12" s="103"/>
-      <c r="M12" s="104"/>
-      <c r="N12" s="112"/>
+      <c r="J12" s="107"/>
+      <c r="K12" s="107"/>
+      <c r="L12" s="106"/>
+      <c r="M12" s="107"/>
+      <c r="N12" s="115"/>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="106" t="n">
+      <c r="A13" s="109" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="103"/>
-      <c r="C13" s="104"/>
-      <c r="D13" s="104"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="111"/>
+      <c r="B13" s="106"/>
+      <c r="C13" s="107"/>
+      <c r="D13" s="107"/>
+      <c r="E13" s="107"/>
+      <c r="F13" s="107"/>
+      <c r="G13" s="114"/>
+      <c r="H13" s="114"/>
       <c r="I13" s="21" t="str">
         <f aca="false">IF(OR(G13="",H13=""),"",H13-G13)</f>
         <v/>
       </c>
-      <c r="J13" s="104"/>
-      <c r="K13" s="104"/>
-      <c r="L13" s="103"/>
-      <c r="M13" s="104"/>
-      <c r="N13" s="112"/>
+      <c r="J13" s="107"/>
+      <c r="K13" s="107"/>
+      <c r="L13" s="106"/>
+      <c r="M13" s="107"/>
+      <c r="N13" s="115"/>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="106" t="n">
+      <c r="A14" s="109" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="103"/>
-      <c r="C14" s="104"/>
-      <c r="D14" s="104"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="104"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="111"/>
+      <c r="B14" s="106"/>
+      <c r="C14" s="107"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="107"/>
+      <c r="F14" s="107"/>
+      <c r="G14" s="114"/>
+      <c r="H14" s="114"/>
       <c r="I14" s="21" t="str">
         <f aca="false">IF(OR(G14="",H14=""),"",H14-G14)</f>
         <v/>
       </c>
-      <c r="J14" s="104"/>
-      <c r="K14" s="104"/>
-      <c r="L14" s="103"/>
-      <c r="M14" s="104"/>
-      <c r="N14" s="112"/>
+      <c r="J14" s="107"/>
+      <c r="K14" s="107"/>
+      <c r="L14" s="106"/>
+      <c r="M14" s="107"/>
+      <c r="N14" s="115"/>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="106" t="n">
+      <c r="A15" s="109" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="103"/>
-      <c r="C15" s="104"/>
-      <c r="D15" s="104"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="104"/>
-      <c r="G15" s="111"/>
-      <c r="H15" s="111"/>
+      <c r="B15" s="106"/>
+      <c r="C15" s="107"/>
+      <c r="D15" s="107"/>
+      <c r="E15" s="107"/>
+      <c r="F15" s="107"/>
+      <c r="G15" s="114"/>
+      <c r="H15" s="114"/>
       <c r="I15" s="21" t="str">
         <f aca="false">IF(OR(G15="",H15=""),"",H15-G15)</f>
         <v/>
       </c>
-      <c r="J15" s="104"/>
-      <c r="K15" s="104"/>
-      <c r="L15" s="103"/>
-      <c r="M15" s="104"/>
-      <c r="N15" s="112"/>
+      <c r="J15" s="107"/>
+      <c r="K15" s="107"/>
+      <c r="L15" s="106"/>
+      <c r="M15" s="107"/>
+      <c r="N15" s="115"/>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="106" t="n">
+      <c r="A16" s="109" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="103"/>
-      <c r="C16" s="104"/>
-      <c r="D16" s="104"/>
-      <c r="E16" s="104"/>
-      <c r="F16" s="104"/>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
+      <c r="B16" s="106"/>
+      <c r="C16" s="107"/>
+      <c r="D16" s="107"/>
+      <c r="E16" s="107"/>
+      <c r="F16" s="107"/>
+      <c r="G16" s="114"/>
+      <c r="H16" s="114"/>
       <c r="I16" s="21" t="str">
         <f aca="false">IF(OR(G16="",H16=""),"",H16-G16)</f>
         <v/>
       </c>
-      <c r="J16" s="104"/>
-      <c r="K16" s="104"/>
-      <c r="L16" s="103"/>
-      <c r="M16" s="104"/>
-      <c r="N16" s="112"/>
+      <c r="J16" s="107"/>
+      <c r="K16" s="107"/>
+      <c r="L16" s="106"/>
+      <c r="M16" s="107"/>
+      <c r="N16" s="115"/>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="106" t="n">
+      <c r="A17" s="109" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="103"/>
-      <c r="C17" s="104"/>
-      <c r="D17" s="104"/>
-      <c r="E17" s="104"/>
-      <c r="F17" s="104"/>
-      <c r="G17" s="111"/>
-      <c r="H17" s="111"/>
+      <c r="B17" s="106"/>
+      <c r="C17" s="107"/>
+      <c r="D17" s="107"/>
+      <c r="E17" s="107"/>
+      <c r="F17" s="107"/>
+      <c r="G17" s="114"/>
+      <c r="H17" s="114"/>
       <c r="I17" s="21" t="str">
         <f aca="false">IF(OR(G17="",H17=""),"",H17-G17)</f>
         <v/>
       </c>
-      <c r="J17" s="104"/>
-      <c r="K17" s="104"/>
-      <c r="L17" s="103"/>
-      <c r="M17" s="104"/>
-      <c r="N17" s="112"/>
+      <c r="J17" s="107"/>
+      <c r="K17" s="107"/>
+      <c r="L17" s="106"/>
+      <c r="M17" s="107"/>
+      <c r="N17" s="115"/>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="106" t="n">
+      <c r="A18" s="109" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="103"/>
-      <c r="C18" s="104"/>
-      <c r="D18" s="104"/>
-      <c r="E18" s="104"/>
-      <c r="F18" s="104"/>
-      <c r="G18" s="111"/>
-      <c r="H18" s="111"/>
+      <c r="B18" s="106"/>
+      <c r="C18" s="107"/>
+      <c r="D18" s="107"/>
+      <c r="E18" s="107"/>
+      <c r="F18" s="107"/>
+      <c r="G18" s="114"/>
+      <c r="H18" s="114"/>
       <c r="I18" s="21" t="str">
         <f aca="false">IF(OR(G18="",H18=""),"",H18-G18)</f>
         <v/>
       </c>
-      <c r="J18" s="104"/>
-      <c r="K18" s="104"/>
-      <c r="L18" s="103"/>
-      <c r="M18" s="104"/>
-      <c r="N18" s="112"/>
+      <c r="J18" s="107"/>
+      <c r="K18" s="107"/>
+      <c r="L18" s="106"/>
+      <c r="M18" s="107"/>
+      <c r="N18" s="115"/>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="106" t="n">
+      <c r="A19" s="109" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="103"/>
-      <c r="C19" s="104"/>
-      <c r="D19" s="104"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="104"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="111"/>
+      <c r="B19" s="106"/>
+      <c r="C19" s="107"/>
+      <c r="D19" s="107"/>
+      <c r="E19" s="107"/>
+      <c r="F19" s="107"/>
+      <c r="G19" s="114"/>
+      <c r="H19" s="114"/>
       <c r="I19" s="21" t="str">
         <f aca="false">IF(OR(G19="",H19=""),"",H19-G19)</f>
         <v/>
       </c>
-      <c r="J19" s="104"/>
-      <c r="K19" s="104"/>
-      <c r="L19" s="103"/>
-      <c r="M19" s="104"/>
-      <c r="N19" s="112"/>
+      <c r="J19" s="107"/>
+      <c r="K19" s="107"/>
+      <c r="L19" s="106"/>
+      <c r="M19" s="107"/>
+      <c r="N19" s="115"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="106" t="n">
+      <c r="A20" s="109" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="103"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="104"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="104"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="111"/>
+      <c r="B20" s="106"/>
+      <c r="C20" s="107"/>
+      <c r="D20" s="107"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="114"/>
+      <c r="H20" s="114"/>
       <c r="I20" s="21" t="str">
         <f aca="false">IF(OR(G20="",H20=""),"",H20-G20)</f>
         <v/>
       </c>
-      <c r="J20" s="104"/>
-      <c r="K20" s="104"/>
-      <c r="L20" s="103"/>
-      <c r="M20" s="104"/>
-      <c r="N20" s="112"/>
+      <c r="J20" s="107"/>
+      <c r="K20" s="107"/>
+      <c r="L20" s="106"/>
+      <c r="M20" s="107"/>
+      <c r="N20" s="115"/>
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="106" t="n">
+      <c r="A21" s="109" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="103"/>
-      <c r="C21" s="104"/>
-      <c r="D21" s="104"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="104"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="111"/>
+      <c r="B21" s="106"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="107"/>
+      <c r="E21" s="107"/>
+      <c r="F21" s="107"/>
+      <c r="G21" s="114"/>
+      <c r="H21" s="114"/>
       <c r="I21" s="21" t="str">
         <f aca="false">IF(OR(G21="",H21=""),"",H21-G21)</f>
         <v/>
       </c>
-      <c r="J21" s="104"/>
-      <c r="K21" s="104"/>
-      <c r="L21" s="103"/>
-      <c r="M21" s="104"/>
-      <c r="N21" s="112"/>
+      <c r="J21" s="107"/>
+      <c r="K21" s="107"/>
+      <c r="L21" s="106"/>
+      <c r="M21" s="107"/>
+      <c r="N21" s="115"/>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="106" t="n">
+      <c r="A22" s="109" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="103"/>
-      <c r="C22" s="104"/>
-      <c r="D22" s="104"/>
-      <c r="E22" s="104"/>
-      <c r="F22" s="104"/>
-      <c r="G22" s="111"/>
-      <c r="H22" s="111"/>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
+      <c r="D22" s="107"/>
+      <c r="E22" s="107"/>
+      <c r="F22" s="107"/>
+      <c r="G22" s="114"/>
+      <c r="H22" s="114"/>
       <c r="I22" s="21" t="str">
         <f aca="false">IF(OR(G22="",H22=""),"",H22-G22)</f>
         <v/>
       </c>
-      <c r="J22" s="104"/>
-      <c r="K22" s="104"/>
-      <c r="L22" s="103"/>
-      <c r="M22" s="104"/>
-      <c r="N22" s="112"/>
+      <c r="J22" s="107"/>
+      <c r="K22" s="107"/>
+      <c r="L22" s="106"/>
+      <c r="M22" s="107"/>
+      <c r="N22" s="115"/>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="106" t="n">
+      <c r="A23" s="109" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="103"/>
-      <c r="C23" s="104"/>
-      <c r="D23" s="104"/>
-      <c r="E23" s="104"/>
-      <c r="F23" s="104"/>
-      <c r="G23" s="111"/>
-      <c r="H23" s="111"/>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="107"/>
+      <c r="E23" s="107"/>
+      <c r="F23" s="107"/>
+      <c r="G23" s="114"/>
+      <c r="H23" s="114"/>
       <c r="I23" s="21" t="str">
         <f aca="false">IF(OR(G23="",H23=""),"",H23-G23)</f>
         <v/>
       </c>
-      <c r="J23" s="104"/>
-      <c r="K23" s="104"/>
-      <c r="L23" s="103"/>
-      <c r="M23" s="104"/>
-      <c r="N23" s="112"/>
+      <c r="J23" s="107"/>
+      <c r="K23" s="107"/>
+      <c r="L23" s="106"/>
+      <c r="M23" s="107"/>
+      <c r="N23" s="115"/>
     </row>
     <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="106" t="n">
+      <c r="A24" s="109" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="103"/>
-      <c r="C24" s="104"/>
-      <c r="D24" s="104"/>
-      <c r="E24" s="104"/>
-      <c r="F24" s="104"/>
-      <c r="G24" s="111"/>
-      <c r="H24" s="111"/>
+      <c r="B24" s="106"/>
+      <c r="C24" s="107"/>
+      <c r="D24" s="107"/>
+      <c r="E24" s="107"/>
+      <c r="F24" s="107"/>
+      <c r="G24" s="114"/>
+      <c r="H24" s="114"/>
       <c r="I24" s="21" t="str">
         <f aca="false">IF(OR(G24="",H24=""),"",H24-G24)</f>
         <v/>
       </c>
-      <c r="J24" s="104"/>
-      <c r="K24" s="104"/>
-      <c r="L24" s="103"/>
-      <c r="M24" s="104"/>
-      <c r="N24" s="112"/>
+      <c r="J24" s="107"/>
+      <c r="K24" s="107"/>
+      <c r="L24" s="106"/>
+      <c r="M24" s="107"/>
+      <c r="N24" s="115"/>
     </row>
     <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="106" t="n">
+      <c r="A25" s="109" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="103"/>
-      <c r="C25" s="104"/>
-      <c r="D25" s="104"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="104"/>
-      <c r="G25" s="111"/>
-      <c r="H25" s="111"/>
+      <c r="B25" s="106"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="107"/>
+      <c r="E25" s="107"/>
+      <c r="F25" s="107"/>
+      <c r="G25" s="114"/>
+      <c r="H25" s="114"/>
       <c r="I25" s="21" t="str">
         <f aca="false">IF(OR(G25="",H25=""),"",H25-G25)</f>
         <v/>
       </c>
-      <c r="J25" s="104"/>
-      <c r="K25" s="104"/>
-      <c r="L25" s="103"/>
-      <c r="M25" s="104"/>
-      <c r="N25" s="112"/>
+      <c r="J25" s="107"/>
+      <c r="K25" s="107"/>
+      <c r="L25" s="106"/>
+      <c r="M25" s="107"/>
+      <c r="N25" s="115"/>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="106" t="n">
+      <c r="A26" s="109" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="103"/>
-      <c r="C26" s="104"/>
-      <c r="D26" s="104"/>
-      <c r="E26" s="104"/>
-      <c r="F26" s="104"/>
-      <c r="G26" s="111"/>
-      <c r="H26" s="111"/>
+      <c r="B26" s="106"/>
+      <c r="C26" s="107"/>
+      <c r="D26" s="107"/>
+      <c r="E26" s="107"/>
+      <c r="F26" s="107"/>
+      <c r="G26" s="114"/>
+      <c r="H26" s="114"/>
       <c r="I26" s="21" t="str">
         <f aca="false">IF(OR(G26="",H26=""),"",H26-G26)</f>
         <v/>
       </c>
-      <c r="J26" s="104"/>
-      <c r="K26" s="104"/>
-      <c r="L26" s="103"/>
-      <c r="M26" s="104"/>
-      <c r="N26" s="112"/>
+      <c r="J26" s="107"/>
+      <c r="K26" s="107"/>
+      <c r="L26" s="106"/>
+      <c r="M26" s="107"/>
+      <c r="N26" s="115"/>
     </row>
     <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="106" t="n">
+      <c r="A27" s="109" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="103"/>
-      <c r="C27" s="104"/>
-      <c r="D27" s="104"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="104"/>
-      <c r="G27" s="111"/>
-      <c r="H27" s="111"/>
+      <c r="B27" s="106"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="107"/>
+      <c r="E27" s="107"/>
+      <c r="F27" s="107"/>
+      <c r="G27" s="114"/>
+      <c r="H27" s="114"/>
       <c r="I27" s="21" t="str">
         <f aca="false">IF(OR(G27="",H27=""),"",H27-G27)</f>
         <v/>
       </c>
-      <c r="J27" s="104"/>
-      <c r="K27" s="104"/>
-      <c r="L27" s="103"/>
-      <c r="M27" s="104"/>
-      <c r="N27" s="112"/>
+      <c r="J27" s="107"/>
+      <c r="K27" s="107"/>
+      <c r="L27" s="106"/>
+      <c r="M27" s="107"/>
+      <c r="N27" s="115"/>
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="106" t="n">
+      <c r="A28" s="109" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="103"/>
-      <c r="C28" s="104"/>
-      <c r="D28" s="104"/>
-      <c r="E28" s="104"/>
-      <c r="F28" s="104"/>
-      <c r="G28" s="111"/>
-      <c r="H28" s="111"/>
+      <c r="B28" s="106"/>
+      <c r="C28" s="107"/>
+      <c r="D28" s="107"/>
+      <c r="E28" s="107"/>
+      <c r="F28" s="107"/>
+      <c r="G28" s="114"/>
+      <c r="H28" s="114"/>
       <c r="I28" s="21" t="str">
         <f aca="false">IF(OR(G28="",H28=""),"",H28-G28)</f>
         <v/>
       </c>
-      <c r="J28" s="104"/>
-      <c r="K28" s="104"/>
-      <c r="L28" s="103"/>
-      <c r="M28" s="104"/>
-      <c r="N28" s="112"/>
+      <c r="J28" s="107"/>
+      <c r="K28" s="107"/>
+      <c r="L28" s="106"/>
+      <c r="M28" s="107"/>
+      <c r="N28" s="115"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="24" t="s">
-        <v>1271</v>
+        <v>1303</v>
       </c>
       <c r="M30" s="21" t="str">
         <f aca="false">COUNTA(B5:B28)&amp;" مبادرة"</f>
@@ -18822,7 +19545,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -18848,7 +19571,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1272</v>
+        <v>1304</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -18867,7 +19590,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1273</v>
+        <v>1305</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -18886,7 +19609,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>1274</v>
+        <v>1306</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>858</v>
@@ -18895,40 +19618,40 @@
         <v>1012</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>1275</v>
+        <v>1307</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>1276</v>
+        <v>1308</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1277</v>
+        <v>1309</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1278</v>
+        <v>1310</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1279</v>
+        <v>1311</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>1280</v>
+        <v>1312</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>1281</v>
+        <v>1313</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>860</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>1282</v>
+        <v>1314</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>1283</v>
+        <v>1315</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>1284</v>
+        <v>1316</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>1285</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18960,7 +19683,7 @@
       <c r="I4" s="28" t="n">
         <v>23493282</v>
       </c>
-      <c r="J4" s="101" t="n">
+      <c r="J4" s="104" t="n">
         <v>64.69</v>
       </c>
       <c r="K4" s="57" t="n">
@@ -18976,7 +19699,7 @@
         <v>0.281</v>
       </c>
       <c r="O4" s="21" t="s">
-        <v>1286</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19008,10 +19731,10 @@
       <c r="I5" s="28" t="n">
         <v>8841940</v>
       </c>
-      <c r="J5" s="101" t="n">
+      <c r="J5" s="104" t="n">
         <v>61.72</v>
       </c>
-      <c r="K5" s="113" t="n">
+      <c r="K5" s="116" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="45" t="n">
@@ -19024,7 +19747,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>1287</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19056,10 +19779,10 @@
       <c r="I6" s="28" t="n">
         <v>7467484</v>
       </c>
-      <c r="J6" s="101" t="n">
+      <c r="J6" s="104" t="n">
         <v>80.21</v>
       </c>
-      <c r="K6" s="113" t="n">
+      <c r="K6" s="116" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="45" t="n">
@@ -19072,7 +19795,7 @@
         <v>0.344</v>
       </c>
       <c r="O6" s="21" t="s">
-        <v>1288</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19104,10 +19827,10 @@
       <c r="I7" s="28" t="n">
         <v>14552120</v>
       </c>
-      <c r="J7" s="101" t="n">
+      <c r="J7" s="104" t="n">
         <v>84.21</v>
       </c>
-      <c r="K7" s="114" t="n">
+      <c r="K7" s="117" t="n">
         <v>0.273</v>
       </c>
       <c r="L7" s="45" t="n">
@@ -19120,7 +19843,7 @@
         <v>0.641</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>1289</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19152,7 +19875,7 @@
       <c r="I8" s="28" t="n">
         <v>2916708</v>
       </c>
-      <c r="J8" s="101" t="n">
+      <c r="J8" s="104" t="n">
         <v>48.35</v>
       </c>
       <c r="K8" s="57" t="n">
@@ -19168,7 +19891,7 @@
         <v>0.134</v>
       </c>
       <c r="O8" s="21" t="s">
-        <v>1290</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19200,10 +19923,10 @@
       <c r="I9" s="28" t="n">
         <v>2916316</v>
       </c>
-      <c r="J9" s="101" t="n">
+      <c r="J9" s="104" t="n">
         <v>65.82</v>
       </c>
-      <c r="K9" s="113" t="n">
+      <c r="K9" s="116" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="45" t="n">
@@ -19216,7 +19939,7 @@
         <v>0.309</v>
       </c>
       <c r="O9" s="21" t="s">
-        <v>1286</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19248,10 +19971,10 @@
       <c r="I10" s="28" t="n">
         <v>2831981</v>
       </c>
-      <c r="J10" s="101" t="n">
+      <c r="J10" s="104" t="n">
         <v>59.14</v>
       </c>
-      <c r="K10" s="113" t="n">
+      <c r="K10" s="116" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="45" t="n">
@@ -19264,7 +19987,7 @@
         <v>0.006</v>
       </c>
       <c r="O10" s="21" t="s">
-        <v>1288</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19296,10 +20019,10 @@
       <c r="I11" s="28" t="n">
         <v>2931550</v>
       </c>
-      <c r="J11" s="101" t="n">
+      <c r="J11" s="104" t="n">
         <v>49.84</v>
       </c>
-      <c r="K11" s="113" t="n">
+      <c r="K11" s="116" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="45" t="n">
@@ -19312,7 +20035,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="21" t="s">
-        <v>1288</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19344,7 +20067,7 @@
       <c r="I12" s="28" t="n">
         <v>8679738</v>
       </c>
-      <c r="J12" s="101" t="n">
+      <c r="J12" s="104" t="n">
         <v>59.34</v>
       </c>
       <c r="K12" s="57" t="n">
@@ -19360,7 +20083,7 @@
         <v>0.277</v>
       </c>
       <c r="O12" s="21" t="s">
-        <v>1288</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19392,7 +20115,7 @@
       <c r="I13" s="28" t="n">
         <v>7729931</v>
       </c>
-      <c r="J13" s="101" t="n">
+      <c r="J13" s="104" t="n">
         <v>67.66</v>
       </c>
       <c r="K13" s="57" t="n">
@@ -19408,7 +20131,7 @@
         <v>0.082</v>
       </c>
       <c r="O13" s="21" t="s">
-        <v>1288</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19440,7 +20163,7 @@
       <c r="I14" s="28" t="n">
         <v>2676944</v>
       </c>
-      <c r="J14" s="101" t="n">
+      <c r="J14" s="104" t="n">
         <v>59.47</v>
       </c>
       <c r="K14" s="45" t="n">
@@ -19456,7 +20179,7 @@
         <v>0.231</v>
       </c>
       <c r="O14" s="21" t="s">
-        <v>1288</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19488,7 +20211,7 @@
       <c r="I15" s="28" t="n">
         <v>7806709</v>
       </c>
-      <c r="J15" s="101" t="n">
+      <c r="J15" s="104" t="n">
         <v>63.18</v>
       </c>
       <c r="K15" s="57" t="n">
@@ -19504,7 +20227,7 @@
         <v>0.458</v>
       </c>
       <c r="O15" s="21" t="s">
-        <v>1290</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19536,10 +20259,10 @@
       <c r="I16" s="28" t="n">
         <v>4791911</v>
       </c>
-      <c r="J16" s="101" t="n">
+      <c r="J16" s="104" t="n">
         <v>74.3</v>
       </c>
-      <c r="K16" s="114" t="n">
+      <c r="K16" s="117" t="n">
         <v>0.151</v>
       </c>
       <c r="L16" s="45" t="n">
@@ -19552,7 +20275,7 @@
         <v>0.076</v>
       </c>
       <c r="O16" s="21" t="s">
-        <v>1288</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19584,10 +20307,10 @@
       <c r="I17" s="28" t="n">
         <v>2078856</v>
       </c>
-      <c r="J17" s="101" t="n">
+      <c r="J17" s="104" t="n">
         <v>55.76</v>
       </c>
-      <c r="K17" s="113" t="n">
+      <c r="K17" s="116" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="45" t="n">
@@ -19600,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="21" t="s">
-        <v>1286</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19632,7 +20355,7 @@
       <c r="I18" s="28" t="n">
         <v>6570004</v>
       </c>
-      <c r="J18" s="101" t="n">
+      <c r="J18" s="104" t="n">
         <v>43.71</v>
       </c>
       <c r="K18" s="45" t="n">
@@ -19648,7 +20371,7 @@
         <v>0</v>
       </c>
       <c r="O18" s="21" t="s">
-        <v>1286</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19680,10 +20403,10 @@
       <c r="I19" s="28" t="n">
         <v>4445436</v>
       </c>
-      <c r="J19" s="101" t="n">
+      <c r="J19" s="104" t="n">
         <v>42.14</v>
       </c>
-      <c r="K19" s="114" t="n">
+      <c r="K19" s="117" t="n">
         <v>0.275</v>
       </c>
       <c r="L19" s="45" t="n">
@@ -19696,7 +20419,7 @@
         <v>0.048</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>1289</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19728,10 +20451,10 @@
       <c r="I20" s="28" t="n">
         <v>2229579</v>
       </c>
-      <c r="J20" s="101" t="n">
+      <c r="J20" s="104" t="n">
         <v>43.6</v>
       </c>
-      <c r="K20" s="113" t="n">
+      <c r="K20" s="116" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="45" t="n">
@@ -19744,7 +20467,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="21" t="s">
-        <v>1287</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19776,7 +20499,7 @@
       <c r="I21" s="28" t="n">
         <v>5504980</v>
       </c>
-      <c r="J21" s="101" t="n">
+      <c r="J21" s="104" t="n">
         <v>43.52</v>
       </c>
       <c r="K21" s="57" t="n">
@@ -19792,7 +20515,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="21" t="s">
-        <v>1288</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19824,10 +20547,10 @@
       <c r="I22" s="28" t="n">
         <v>4722403</v>
       </c>
-      <c r="J22" s="101" t="n">
+      <c r="J22" s="104" t="n">
         <v>49.88</v>
       </c>
-      <c r="K22" s="114" t="n">
+      <c r="K22" s="117" t="n">
         <v>0.068</v>
       </c>
       <c r="L22" s="45" t="n">
@@ -19840,7 +20563,7 @@
         <v>0.329</v>
       </c>
       <c r="O22" s="21" t="s">
-        <v>1290</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19872,10 +20595,10 @@
       <c r="I23" s="28" t="n">
         <v>4924931</v>
       </c>
-      <c r="J23" s="101" t="n">
+      <c r="J23" s="104" t="n">
         <v>47.68</v>
       </c>
-      <c r="K23" s="114" t="n">
+      <c r="K23" s="117" t="n">
         <v>0.069</v>
       </c>
       <c r="L23" s="45" t="n">
@@ -19888,7 +20611,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="21" t="s">
-        <v>1288</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19920,7 +20643,7 @@
       <c r="I24" s="28" t="n">
         <v>4740020</v>
       </c>
-      <c r="J24" s="101" t="n">
+      <c r="J24" s="104" t="n">
         <v>43.42</v>
       </c>
       <c r="K24" s="45" t="n">
@@ -19936,7 +20659,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="21" t="s">
-        <v>1288</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19968,10 +20691,10 @@
       <c r="I25" s="28" t="n">
         <v>4771577</v>
       </c>
-      <c r="J25" s="101" t="n">
+      <c r="J25" s="104" t="n">
         <v>51.68</v>
       </c>
-      <c r="K25" s="114" t="n">
+      <c r="K25" s="117" t="n">
         <v>0.177</v>
       </c>
       <c r="L25" s="45" t="n">
@@ -19984,7 +20707,7 @@
         <v>0.058</v>
       </c>
       <c r="O25" s="21" t="s">
-        <v>1286</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20016,7 +20739,7 @@
       <c r="I26" s="28" t="n">
         <v>4933540</v>
       </c>
-      <c r="J26" s="101" t="n">
+      <c r="J26" s="104" t="n">
         <v>51.76</v>
       </c>
       <c r="K26" s="45" t="n">
@@ -20032,7 +20755,7 @@
         <v>0.276</v>
       </c>
       <c r="O26" s="21" t="s">
-        <v>1286</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20064,10 +20787,10 @@
       <c r="I27" s="28" t="n">
         <v>4643058</v>
       </c>
-      <c r="J27" s="101" t="n">
+      <c r="J27" s="104" t="n">
         <v>66.28</v>
       </c>
-      <c r="K27" s="114" t="n">
+      <c r="K27" s="117" t="n">
         <v>0.083</v>
       </c>
       <c r="L27" s="45" t="n">
@@ -20080,7 +20803,7 @@
         <v>0.27</v>
       </c>
       <c r="O27" s="21" t="s">
-        <v>1291</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20112,10 +20835,10 @@
       <c r="I28" s="28" t="n">
         <v>2834084</v>
       </c>
-      <c r="J28" s="101" t="n">
+      <c r="J28" s="104" t="n">
         <v>77.81</v>
       </c>
-      <c r="K28" s="113" t="n">
+      <c r="K28" s="116" t="n">
         <v>-0.033</v>
       </c>
       <c r="L28" s="45" t="n">
@@ -20128,7 +20851,7 @@
         <v>0.349</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>1289</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20160,7 +20883,7 @@
       <c r="I29" s="28" t="n">
         <v>4558563</v>
       </c>
-      <c r="J29" s="101" t="n">
+      <c r="J29" s="104" t="n">
         <v>64.44</v>
       </c>
       <c r="K29" s="45" t="n">
@@ -20176,7 +20899,7 @@
         <v>0.321</v>
       </c>
       <c r="O29" s="21" t="s">
-        <v>1286</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20208,10 +20931,10 @@
       <c r="I30" s="28" t="n">
         <v>2127665</v>
       </c>
-      <c r="J30" s="101" t="n">
+      <c r="J30" s="104" t="n">
         <v>48.52</v>
       </c>
-      <c r="K30" s="113" t="n">
+      <c r="K30" s="116" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="45" t="n">
@@ -20224,7 +20947,7 @@
         <v>0.176</v>
       </c>
       <c r="O30" s="21" t="s">
-        <v>1286</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20256,10 +20979,10 @@
       <c r="I31" s="28" t="n">
         <v>3884721</v>
       </c>
-      <c r="J31" s="101" t="n">
+      <c r="J31" s="104" t="n">
         <v>54.76</v>
       </c>
-      <c r="K31" s="114" t="n">
+      <c r="K31" s="117" t="n">
         <v>0.186</v>
       </c>
       <c r="L31" s="45" t="n">
@@ -20272,7 +20995,7 @@
         <v>0.082</v>
       </c>
       <c r="O31" s="21" t="s">
-        <v>1288</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20304,10 +21027,10 @@
       <c r="I32" s="28" t="n">
         <v>1471112</v>
       </c>
-      <c r="J32" s="101" t="n">
+      <c r="J32" s="104" t="n">
         <v>49.67</v>
       </c>
-      <c r="K32" s="113" t="n">
+      <c r="K32" s="116" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="45" t="n">
@@ -20320,7 +21043,7 @@
         <v>0.103</v>
       </c>
       <c r="O32" s="20" t="s">
-        <v>1289</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20352,10 +21075,10 @@
       <c r="I33" s="28" t="n">
         <v>3774634</v>
       </c>
-      <c r="J33" s="101" t="n">
+      <c r="J33" s="104" t="n">
         <v>50.81</v>
       </c>
-      <c r="K33" s="114" t="n">
+      <c r="K33" s="117" t="n">
         <v>0.18</v>
       </c>
       <c r="L33" s="45" t="n">
@@ -20368,7 +21091,7 @@
         <v>0.023</v>
       </c>
       <c r="O33" s="21" t="s">
-        <v>1286</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20400,7 +21123,7 @@
       <c r="I34" s="28" t="n">
         <v>4263083</v>
       </c>
-      <c r="J34" s="101" t="n">
+      <c r="J34" s="104" t="n">
         <v>110.06</v>
       </c>
       <c r="K34" s="57" t="n">
@@ -20416,7 +21139,7 @@
         <v>0.559</v>
       </c>
       <c r="O34" s="21" t="s">
-        <v>1291</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20448,7 +21171,7 @@
       <c r="I35" s="28" t="n">
         <v>3471225</v>
       </c>
-      <c r="J35" s="101" t="n">
+      <c r="J35" s="104" t="n">
         <v>47.35</v>
       </c>
       <c r="K35" s="57" t="n">
@@ -20464,7 +21187,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="21" t="s">
-        <v>1288</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20496,7 +21219,7 @@
       <c r="I36" s="28" t="n">
         <v>3512113</v>
       </c>
-      <c r="J36" s="101" t="n">
+      <c r="J36" s="104" t="n">
         <v>45.88</v>
       </c>
       <c r="K36" s="57" t="n">
@@ -20512,7 +21235,7 @@
         <v>0.115</v>
       </c>
       <c r="O36" s="21" t="s">
-        <v>1290</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20544,10 +21267,10 @@
       <c r="I37" s="28" t="n">
         <v>486162</v>
       </c>
-      <c r="J37" s="101" t="n">
+      <c r="J37" s="104" t="n">
         <v>33.35</v>
       </c>
-      <c r="K37" s="113" t="n">
+      <c r="K37" s="116" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="45" t="n">
@@ -20592,10 +21315,10 @@
       <c r="I38" s="28" t="n">
         <v>3406904</v>
       </c>
-      <c r="J38" s="101" t="n">
+      <c r="J38" s="104" t="n">
         <v>43.04</v>
       </c>
-      <c r="K38" s="114" t="n">
+      <c r="K38" s="117" t="n">
         <v>0.083</v>
       </c>
       <c r="L38" s="45" t="n">
@@ -20608,7 +21331,7 @@
         <v>0.167</v>
       </c>
       <c r="O38" s="21" t="s">
-        <v>1286</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20640,7 +21363,7 @@
       <c r="I39" s="28" t="n">
         <v>3076219</v>
       </c>
-      <c r="J39" s="101" t="n">
+      <c r="J39" s="104" t="n">
         <v>69.64</v>
       </c>
       <c r="K39" s="57" t="n">
@@ -20656,7 +21379,7 @@
         <v>0.106</v>
       </c>
       <c r="O39" s="21" t="s">
-        <v>1286</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20688,7 +21411,7 @@
       <c r="I40" s="28" t="n">
         <v>3314721</v>
       </c>
-      <c r="J40" s="101" t="n">
+      <c r="J40" s="104" t="n">
         <v>69.44</v>
       </c>
       <c r="K40" s="45" t="n">
@@ -20704,7 +21427,7 @@
         <v>0.373</v>
       </c>
       <c r="O40" s="21" t="s">
-        <v>1286</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20736,7 +21459,7 @@
       <c r="I41" s="28" t="n">
         <v>2925368</v>
       </c>
-      <c r="J41" s="101" t="n">
+      <c r="J41" s="104" t="n">
         <v>45.21</v>
       </c>
       <c r="K41" s="57" t="n">
@@ -20752,7 +21475,7 @@
         <v>0</v>
       </c>
       <c r="O41" s="21" t="s">
-        <v>1286</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20784,10 +21507,10 @@
       <c r="I42" s="28" t="n">
         <v>1114635</v>
       </c>
-      <c r="J42" s="101" t="n">
+      <c r="J42" s="104" t="n">
         <v>45.6</v>
       </c>
-      <c r="K42" s="113" t="n">
+      <c r="K42" s="116" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="45" t="n">
@@ -20800,7 +21523,7 @@
         <v>0.056</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>1289</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20832,10 +21555,10 @@
       <c r="I43" s="28" t="n">
         <v>2839338</v>
       </c>
-      <c r="J43" s="101" t="n">
+      <c r="J43" s="104" t="n">
         <v>50.86</v>
       </c>
-      <c r="K43" s="114" t="n">
+      <c r="K43" s="117" t="n">
         <v>0.082</v>
       </c>
       <c r="L43" s="45" t="n">
@@ -20848,7 +21571,7 @@
         <v>0.077</v>
       </c>
       <c r="O43" s="21" t="s">
-        <v>1291</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20880,10 +21603,10 @@
       <c r="I44" s="28" t="n">
         <v>2759664</v>
       </c>
-      <c r="J44" s="101" t="n">
+      <c r="J44" s="104" t="n">
         <v>56.84</v>
       </c>
-      <c r="K44" s="114" t="n">
+      <c r="K44" s="117" t="n">
         <v>0.327</v>
       </c>
       <c r="L44" s="45" t="n">
@@ -20896,7 +21619,7 @@
         <v>0.066</v>
       </c>
       <c r="O44" s="20" t="s">
-        <v>1289</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20928,7 +21651,7 @@
       <c r="I45" s="28" t="n">
         <v>2940822</v>
       </c>
-      <c r="J45" s="101" t="n">
+      <c r="J45" s="104" t="n">
         <v>74.93</v>
       </c>
       <c r="K45" s="45" t="n">
@@ -20944,7 +21667,7 @@
         <v>0.392</v>
       </c>
       <c r="O45" s="20" t="s">
-        <v>1289</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20976,7 +21699,7 @@
       <c r="I46" s="28" t="n">
         <v>2694118</v>
       </c>
-      <c r="J46" s="101" t="n">
+      <c r="J46" s="104" t="n">
         <v>53.94</v>
       </c>
       <c r="K46" s="57" t="n">
@@ -20992,7 +21715,7 @@
         <v>0.236</v>
       </c>
       <c r="O46" s="21" t="s">
-        <v>1288</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21024,7 +21747,7 @@
       <c r="I47" s="28" t="n">
         <v>2650896</v>
       </c>
-      <c r="J47" s="101" t="n">
+      <c r="J47" s="104" t="n">
         <v>48.6</v>
       </c>
       <c r="K47" s="45" t="n">
@@ -21040,7 +21763,7 @@
         <v>0.184</v>
       </c>
       <c r="O47" s="21" t="s">
-        <v>1291</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21072,10 +21795,10 @@
       <c r="I48" s="28" t="n">
         <v>2153145</v>
       </c>
-      <c r="J48" s="101" t="n">
+      <c r="J48" s="104" t="n">
         <v>57.15</v>
       </c>
-      <c r="K48" s="114" t="n">
+      <c r="K48" s="117" t="n">
         <v>0.064</v>
       </c>
       <c r="L48" s="45" t="n">
@@ -21088,7 +21811,7 @@
         <v>0</v>
       </c>
       <c r="O48" s="21" t="s">
-        <v>1286</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21120,10 +21843,10 @@
       <c r="I49" s="28" t="n">
         <v>2133587</v>
       </c>
-      <c r="J49" s="101" t="n">
+      <c r="J49" s="104" t="n">
         <v>62.82</v>
       </c>
-      <c r="K49" s="114" t="n">
+      <c r="K49" s="117" t="n">
         <v>0.256</v>
       </c>
       <c r="L49" s="45" t="n">
@@ -21136,7 +21859,7 @@
         <v>0.201</v>
       </c>
       <c r="O49" s="21" t="s">
-        <v>1286</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21168,7 +21891,7 @@
       <c r="I50" s="28" t="n">
         <v>1912969</v>
       </c>
-      <c r="J50" s="101" t="n">
+      <c r="J50" s="104" t="n">
         <v>52.46</v>
       </c>
       <c r="K50" s="57" t="n">
@@ -21184,7 +21907,7 @@
         <v>0</v>
       </c>
       <c r="O50" s="21" t="s">
-        <v>1288</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21216,10 +21939,10 @@
       <c r="I51" s="28" t="n">
         <v>568922</v>
       </c>
-      <c r="J51" s="101" t="n">
+      <c r="J51" s="104" t="n">
         <v>50.9</v>
       </c>
-      <c r="K51" s="113" t="n">
+      <c r="K51" s="116" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="45" t="n">
@@ -21264,10 +21987,10 @@
       <c r="I52" s="28" t="n">
         <v>1672588</v>
       </c>
-      <c r="J52" s="101" t="n">
+      <c r="J52" s="104" t="n">
         <v>45.95</v>
       </c>
-      <c r="K52" s="114" t="n">
+      <c r="K52" s="117" t="n">
         <v>0.137</v>
       </c>
       <c r="L52" s="45" t="n">
@@ -21280,7 +22003,7 @@
         <v>0.017</v>
       </c>
       <c r="O52" s="21" t="s">
-        <v>1290</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21312,7 +22035,7 @@
       <c r="I53" s="28" t="n">
         <v>1601535</v>
       </c>
-      <c r="J53" s="101" t="n">
+      <c r="J53" s="104" t="n">
         <v>55.38</v>
       </c>
       <c r="K53" s="45" t="n">
@@ -21328,7 +22051,7 @@
         <v>0.292</v>
       </c>
       <c r="O53" s="21" t="s">
-        <v>1290</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21360,7 +22083,7 @@
       <c r="I54" s="28" t="n">
         <v>1431054</v>
       </c>
-      <c r="J54" s="101" t="n">
+      <c r="J54" s="104" t="n">
         <v>53.68</v>
       </c>
       <c r="K54" s="45" t="n">
@@ -21376,7 +22099,7 @@
         <v>0.077</v>
       </c>
       <c r="O54" s="21" t="s">
-        <v>1286</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21408,10 +22131,10 @@
       <c r="I55" s="28" t="n">
         <v>1262094</v>
       </c>
-      <c r="J55" s="101" t="n">
+      <c r="J55" s="104" t="n">
         <v>53.3</v>
       </c>
-      <c r="K55" s="114" t="n">
+      <c r="K55" s="117" t="n">
         <v>0.188</v>
       </c>
       <c r="L55" s="45" t="n">
@@ -21424,7 +22147,7 @@
         <v>0.18</v>
       </c>
       <c r="O55" s="20" t="s">
-        <v>1289</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21456,10 +22179,10 @@
       <c r="I56" s="28" t="n">
         <v>1204453</v>
       </c>
-      <c r="J56" s="101" t="n">
+      <c r="J56" s="104" t="n">
         <v>34.88</v>
       </c>
-      <c r="K56" s="114" t="n">
+      <c r="K56" s="117" t="n">
         <v>0.06</v>
       </c>
       <c r="L56" s="45" t="n">
@@ -21472,7 +22195,7 @@
         <v>0.194</v>
       </c>
       <c r="O56" s="21" t="s">
-        <v>1290</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21504,10 +22227,10 @@
       <c r="I57" s="28" t="n">
         <v>206212</v>
       </c>
-      <c r="J57" s="101" t="n">
+      <c r="J57" s="104" t="n">
         <v>57.08</v>
       </c>
-      <c r="K57" s="113" t="n">
+      <c r="K57" s="116" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="45" t="n">
@@ -21520,7 +22243,7 @@
         <v>0.249</v>
       </c>
       <c r="O57" s="20" t="s">
-        <v>1289</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21552,10 +22275,10 @@
       <c r="I58" s="28" t="n">
         <v>21693</v>
       </c>
-      <c r="J58" s="101" t="n">
+      <c r="J58" s="104" t="n">
         <v>49.96</v>
       </c>
-      <c r="K58" s="113" t="n">
+      <c r="K58" s="116" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="45" t="n">
@@ -21568,51 +22291,51 @@
         <v>0.167</v>
       </c>
       <c r="O58" s="20" t="s">
-        <v>1289</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="67" t="s">
-        <v>1292</v>
+        <v>1324</v>
       </c>
       <c r="B59" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="F59" s="115" t="n">
+      <c r="F59" s="118" t="n">
         <f aca="false">SUM(F4:F58)</f>
         <v>502415662</v>
       </c>
-      <c r="G59" s="115" t="n">
+      <c r="G59" s="118" t="n">
         <f aca="false">SUM(G4:G58)</f>
         <v>1271395370.83428</v>
       </c>
-      <c r="H59" s="115" t="n">
+      <c r="H59" s="118" t="n">
         <f aca="false">SUM(H4:H58)</f>
         <v>8824895</v>
       </c>
-      <c r="I59" s="115" t="n">
+      <c r="I59" s="118" t="n">
         <f aca="false">SUM(I4:I58)</f>
         <v>219475297</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="116" t="s">
-        <v>1293</v>
-      </c>
-      <c r="B61" s="116"/>
-      <c r="C61" s="116"/>
-      <c r="D61" s="116"/>
-      <c r="E61" s="116"/>
-      <c r="F61" s="116"/>
-      <c r="G61" s="116"/>
-      <c r="H61" s="116"/>
-      <c r="I61" s="116"/>
-      <c r="J61" s="116"/>
-      <c r="K61" s="116"/>
-      <c r="L61" s="116"/>
-      <c r="M61" s="116"/>
-      <c r="N61" s="116"/>
-      <c r="O61" s="116"/>
+      <c r="A61" s="119" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B61" s="119"/>
+      <c r="C61" s="119"/>
+      <c r="D61" s="119"/>
+      <c r="E61" s="119"/>
+      <c r="F61" s="119"/>
+      <c r="G61" s="119"/>
+      <c r="H61" s="119"/>
+      <c r="I61" s="119"/>
+      <c r="J61" s="119"/>
+      <c r="K61" s="119"/>
+      <c r="L61" s="119"/>
+      <c r="M61" s="119"/>
+      <c r="N61" s="119"/>
+      <c r="O61" s="119"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/docs/executive-plan.xlsx
+++ b/docs/executive-plan.xlsx
@@ -22,10 +22,11 @@
     <sheet name="مستهدفات البنزين" sheetId="12" state="visible" r:id="rId14"/>
     <sheet name="العمالة والمضخات" sheetId="13" state="visible" r:id="rId15"/>
     <sheet name="شكاوى العملاء" sheetId="14" state="visible" r:id="rId16"/>
-    <sheet name="الخطة التنفيذية" sheetId="15" state="visible" r:id="rId17"/>
-    <sheet name="المستهدفات الربعية" sheetId="16" state="visible" r:id="rId18"/>
-    <sheet name="المبادرات" sheetId="17" state="visible" r:id="rId19"/>
-    <sheet name="المحطات" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="اقتصاديات اللتر" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="الخطة التنفيذية" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="المستهدفات الربعية" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="المبادرات" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="المحطات" sheetId="19" state="visible" r:id="rId21"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="1326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2473" uniqueCount="1367">
   <si>
     <t xml:space="preserve">نموذج الخطة التنفيذية — الإدارة التجارية</t>
   </si>
@@ -99,7 +100,7 @@
     <t xml:space="preserve">دليل الألوان</t>
   </si>
   <si>
-    <t xml:space="preserve">نموذج تكلفة اللتر لكل محطة — محرّكات محسوبة ومُدخلات مطلوبة.</t>
+    <t xml:space="preserve">أرقام محققة من قائمة الدخل — هللة لكل لتر.</t>
   </si>
   <si>
     <t xml:space="preserve">أصفر + خط أزرق</t>
@@ -126,18 +127,18 @@
     <t xml:space="preserve">صف مثال توضيحي — يُحذف قبل الاعتماد</t>
   </si>
   <si>
-    <t xml:space="preserve">منفذ ٢ — العقار</t>
+    <t xml:space="preserve">جاهزية الإطلاق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أربع موجات: ما يبدأ الآن وما يتأخر ولماذا.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حالة المنفذ</t>
   </si>
   <si>
     <t xml:space="preserve">تفصيل الشواغر والعلامات — الأولوية الأولى.</t>
   </si>
   <si>
-    <t xml:space="preserve">حالة المنفذ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السوق واللاعبون وقرار التأجير مقابل التشغيل.</t>
-  </si>
-  <si>
     <t xml:space="preserve">قائم</t>
   </si>
   <si>
@@ -3709,6 +3710,129 @@
   </si>
   <si>
     <t xml:space="preserve">MK007 و MK072 معاً 86 شكوى و141.6 مليون ريال إيراد سنوي مُطبَّع وتفقدان نحو 21–22%. تدخّل إشرافي مركّز فيهما لثلاثة أشهر (جدولة الذروتين 17 و21 · محاسبة على السلوك · قياس زمن الخدمة) يُختبر أثره على الشكاوى والزيارات معاً. وإن تحسّن الاتجاه فقد وجدنا السبب — وإن لم يتحسّن استبعدناه بتكلفة شبه صفرية.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اقتصاديات اللتر الفعلية — من قائمة الدخل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">النصف الأول 2026 · أرقام مُحققة لا تقديرات · الوحدة: هللة لكل لتر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔑 المصدر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تقرير DARB التجاري (يونيو 2026) — قائمة دخل تفصيلية لكل محطة. هذه أول أرقام تكلفة حقيقية في الملف كله، وتحلّ محل كل المُدخلات الافتراضية في نموذج تكلفة اللتر.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK007 العمرة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK019 الشرايع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الإيراد لكل لتر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK019 إيرادها أعلى للتر — مزيج منتجات مختلف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تكلفة البضاعة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المكوّن الأكبر — 93% من الإيراد · لا نتحكم فيه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">النقل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أجرة الرحلة الفعلية 623 ريال — لا 1,800 كما افترضتُ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التبخّر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32% من التكلفة — أقل بكثير من 1.10% المقيسة من فرق التوريد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">◄ هامش مساهمة الوقود</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الهدف 15 هللة — والفجوة 4.9 و1.6 هللة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صافي التأجير</t>
+  </si>
+  <si>
+    <t xml:space="preserve">موجب في العمرة وسالب في الشرايع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المصاريف التشغيلية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88% منها إهلاك غير نقدي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">◄ صافي الربح</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 هللة صافية تعني مضاعفة الربح ثلاث مرات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مقابل هدف 15 هللة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المقياس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الهدف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هامش مساهمة الوقود</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأقرب للهدف — الفجوة 4.9 و1.6 هللة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صافي الربح الفعلي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الفجوة 9.9 و11.1 هللة — أي مضاعفة ثلاث مرات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المصاريف النقدية القابلة للخفض</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔴 أقل من هللة واحدة — فلا مجال لبلوغ الهدف بخفض التكاليف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔴 الإهلاك يبتلع المصاريف — والنقدي أقل من هللة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مصاريف MK007 التشغيلية 2,416 ألف ريال، منها 1,696 إهلاكاً واستهلاكاً = 88%. والباقي النقدي كله (صيانة ومرافق 179 · متنوعة 26 · تأمين 10 · أزياء 6) = 221 ألفاً = 0.94 هللة لكل لتر. أي أن مساحة «خفض التكلفة» أقل من هللة واحدة، والإهلاك لا يُخفَّض تشغيلياً. فالوصول إلى 15 هللة لا يمرّ عبر التكلفة إطلاقاً.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔑 أين الطريق إذن — ثلاثة مسارات فقط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① رفع اللترات: الإهلاك ثابت، فكل لتر إضافي يوزّعه على قاعدة أكبر ويرفع الربح للتر دون أي إنفاق جديد. ② رفع صافي التأجير: وهو المسار الأقوى كما يلي. ③ رفع هامش المساهمة نفسه — ولا نتحكم فيه لأن السعر مقنَّن.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🏪 اكتشاف يقلب حجّة منفذ التأجير</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دخل الإيجار في العمرة 3,887 ألفاً، لكن التمويل (1,813) وإهلاك حق الاستخدام (623) يلتهمان 63% منه فيبقى 1,253. وفي الشرايع يلتهمان 106% فيصبح صافي التأجير سالباً (43). والمعنى الحاسم: هذان البندان ثابتان — مدفوعان على الأرض كاملةً سواء أُجّرت الوحدات أم لا. فكل ريال إيجار إضافي من الوحدات الـ96 الشاغرة يتدفّق إلى صافي الربح شبه كاملاً. التأجير ليس منفذاً جانبياً — هو أرخص رافعة ربح لدينا.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تصحيحان لنموذج التكلفة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① أجرة الرحلة الفعلية 623 ريال (447 ألفاً ÷ 718 رحلة) — كنت أستخدم 1,800 في الاختبار، أي 2.9 أضعاف الواقع، فتقديري لتكلفة النقل كان 5.5 هللة والحقيقة 1.89. ② التبخّر المحاسبي 0.32% من التكلفة، بينما الفرق بين التوريد والمبيعات 1.10% — الفارق بينهما فروق قياس ومخزون لا تبخّراً، ويحتاج تفسيراً من العمليات.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ العيّنة محطتان من 221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كل ما سبق مبني على محطتين فقط ظهرتا في اللقطات. التقرير الكامل يغطي 221 محطة — وبه تصبح كل ورقة في هذا الملف مبنية على أرقام محققة بدل مُدخلات افتراضية.</t>
   </si>
   <si>
     <t xml:space="preserve">الخطة التنفيذية لمنافذ البيع</t>
@@ -4021,7 +4145,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="18">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
@@ -4038,8 +4162,9 @@
     <numFmt numFmtId="177" formatCode="\+0.0%;\-0.0%"/>
     <numFmt numFmtId="178" formatCode="\+#,##0;\-#,##0"/>
     <numFmt numFmtId="179" formatCode="\+0;\-0;0"/>
-    <numFmt numFmtId="180" formatCode="#,##0.00"/>
-    <numFmt numFmtId="181" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="180" formatCode="\+0.00;\-0.00"/>
+    <numFmt numFmtId="181" formatCode="#,##0.00"/>
+    <numFmt numFmtId="182" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -4327,7 +4452,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="125">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4380,12 +4505,12 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -4732,6 +4857,26 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="180" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="180" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
@@ -4744,11 +4889,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="180" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="181" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4772,11 +4917,11 @@
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="181" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="182" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4784,7 +4929,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="181" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="182" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5238,15 +5383,15 @@
       <c r="B24" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="4" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="14" t="s">
         <v>42</v>
       </c>
     </row>
@@ -6048,7 +6193,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>888</v>
       </c>
       <c r="C7" s="81"/>
@@ -6060,7 +6205,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>890</v>
       </c>
       <c r="C8" s="81"/>
@@ -6070,7 +6215,7 @@
       <c r="F8" s="26"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>892</v>
       </c>
       <c r="C9" s="81"/>
@@ -6080,7 +6225,7 @@
       <c r="F9" s="26"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>894</v>
       </c>
       <c r="C10" s="83"/>
@@ -6090,7 +6235,7 @@
       <c r="F10" s="26"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>896</v>
       </c>
       <c r="C11" s="83"/>
@@ -6100,7 +6245,7 @@
       <c r="F11" s="26"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>898</v>
       </c>
       <c r="C12" s="83"/>
@@ -6110,7 +6255,7 @@
       <c r="F12" s="26"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>900</v>
       </c>
       <c r="C13" s="83"/>
@@ -6120,7 +6265,7 @@
       <c r="F13" s="26"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>902</v>
       </c>
       <c r="C14" s="83"/>
@@ -10686,7 +10831,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>997</v>
       </c>
       <c r="D6" s="69"/>
@@ -10704,7 +10849,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>1001</v>
       </c>
       <c r="D7" s="26" t="n">
@@ -17720,6 +17865,399 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="54" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>1229</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C5" s="98" t="n">
+        <v>182.51</v>
+      </c>
+      <c r="D5" s="98" t="n">
+        <v>196.77</v>
+      </c>
+      <c r="E5" s="101" t="n">
+        <f aca="false">C5-D5</f>
+        <v>-14.26</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C6" s="98" t="n">
+        <v>-170</v>
+      </c>
+      <c r="D6" s="98" t="n">
+        <v>-180.67</v>
+      </c>
+      <c r="E6" s="101" t="n">
+        <f aca="false">C6-D6</f>
+        <v>10.67</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C7" s="98" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="D7" s="98" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="E7" s="101" t="n">
+        <f aca="false">C7-D7</f>
+        <v>-0.01</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C8" s="98" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="D8" s="98" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="E8" s="101" t="n">
+        <f aca="false">C8-D8</f>
+        <v>0.3</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="102" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C9" s="103" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="D9" s="103" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="E9" s="104" t="n">
+        <f aca="false">C9-D9</f>
+        <v>-3.31</v>
+      </c>
+      <c r="F9" s="47" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C10" s="98" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D10" s="98" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="E10" s="101" t="n">
+        <f aca="false">C10-D10</f>
+        <v>7.55</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C11" s="98" t="n">
+        <v>-10.23</v>
+      </c>
+      <c r="D11" s="98" t="n">
+        <v>-7.21</v>
+      </c>
+      <c r="E11" s="101" t="n">
+        <f aca="false">C11-D11</f>
+        <v>-3.02</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="102" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C12" s="103" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="D12" s="103" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="E12" s="104" t="n">
+        <f aca="false">C12-D12</f>
+        <v>1.28</v>
+      </c>
+      <c r="F12" s="47" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="71" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C16" s="98" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="D16" s="98" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="E16" s="98" t="n">
+        <v>15</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C17" s="98" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="D17" s="98" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="E17" s="98" t="n">
+        <v>15</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C18" s="105" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="D18" s="21"/>
+      <c r="E18" s="98" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="54" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+    </row>
+    <row r="21" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="52" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+    </row>
+    <row r="22" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="54" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+    </row>
+    <row r="23" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="52" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+    </row>
+    <row r="24" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="54" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:O18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -17741,7 +18279,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1224</v>
+        <v>1265</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -17760,7 +18298,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1225</v>
+        <v>1266</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -17791,86 +18329,86 @@
         <v>55</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>1226</v>
+        <v>1267</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1227</v>
+        <v>1268</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1228</v>
+        <v>1269</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1229</v>
+        <v>1270</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>58</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>1230</v>
+        <v>1271</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>1231</v>
+        <v>1272</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>59</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>1232</v>
+        <v>1273</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>1233</v>
+        <v>1274</v>
       </c>
       <c r="O3" s="15" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="101" t="s">
-        <v>1234</v>
-      </c>
-      <c r="B4" s="102" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C4" s="101" t="s">
+      <c r="A4" s="106" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B4" s="107" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C4" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="102" t="s">
-        <v>1236</v>
-      </c>
-      <c r="E4" s="101" t="n">
+      <c r="D4" s="107" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E4" s="106" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="101" t="s">
-        <v>1237</v>
-      </c>
-      <c r="G4" s="102" t="s">
-        <v>1238</v>
-      </c>
-      <c r="H4" s="101" t="n">
+      <c r="F4" s="106" t="s">
+        <v>1278</v>
+      </c>
+      <c r="G4" s="107" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H4" s="106" t="n">
         <v>20</v>
       </c>
-      <c r="I4" s="101" t="n">
+      <c r="I4" s="106" t="n">
         <f aca="false">IF(H4="","",H4-E4)</f>
         <v>14</v>
       </c>
-      <c r="J4" s="103" t="n">
+      <c r="J4" s="108" t="n">
         <f aca="false">IFERROR(IF(H4="","",(H4-E4)/E4),"")</f>
         <v>2.33333333333333</v>
       </c>
-      <c r="K4" s="102" t="s">
-        <v>1239</v>
-      </c>
-      <c r="L4" s="101" t="s">
+      <c r="K4" s="107" t="s">
+        <v>1280</v>
+      </c>
+      <c r="L4" s="106" t="s">
         <v>78</v>
       </c>
-      <c r="M4" s="102" t="s">
-        <v>1240</v>
-      </c>
-      <c r="N4" s="102" t="s">
-        <v>1241</v>
-      </c>
-      <c r="O4" s="101" t="s">
-        <v>1242</v>
+      <c r="M4" s="107" t="s">
+        <v>1281</v>
+      </c>
+      <c r="N4" s="107" t="s">
+        <v>1282</v>
+      </c>
+      <c r="O4" s="106" t="s">
+        <v>1283</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17886,17 +18424,17 @@
       <c r="D5" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="104" t="n">
+      <c r="E5" s="109" t="n">
         <v>1271</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>1243</v>
+        <v>1284</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H5" s="105"/>
-      <c r="I5" s="104" t="str">
+        <v>1285</v>
+      </c>
+      <c r="H5" s="110"/>
+      <c r="I5" s="109" t="str">
         <f aca="false">IF(H5="","",H5-E5)</f>
         <v/>
       </c>
@@ -17904,15 +18442,15 @@
         <f aca="false">IFERROR(IF(H5="","",(H5-E5)/E5),"")</f>
         <v/>
       </c>
-      <c r="K5" s="106"/>
+      <c r="K5" s="111"/>
       <c r="L5" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M5" s="106"/>
+      <c r="M5" s="111"/>
       <c r="N5" s="16" t="s">
-        <v>1245</v>
-      </c>
-      <c r="O5" s="107"/>
+        <v>1286</v>
+      </c>
+      <c r="O5" s="112"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="n">
@@ -17927,17 +18465,17 @@
       <c r="D6" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="104" t="n">
+      <c r="E6" s="109" t="n">
         <v>25</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>1246</v>
+        <v>1287</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>1247</v>
-      </c>
-      <c r="H6" s="105"/>
-      <c r="I6" s="104" t="str">
+        <v>1288</v>
+      </c>
+      <c r="H6" s="110"/>
+      <c r="I6" s="109" t="str">
         <f aca="false">IF(H6="","",H6-E6)</f>
         <v/>
       </c>
@@ -17945,15 +18483,15 @@
         <f aca="false">IFERROR(IF(H6="","",(H6-E6)/E6),"")</f>
         <v/>
       </c>
-      <c r="K6" s="106"/>
+      <c r="K6" s="111"/>
       <c r="L6" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M6" s="106"/>
+      <c r="M6" s="111"/>
       <c r="N6" s="16" t="s">
-        <v>1248</v>
-      </c>
-      <c r="O6" s="107"/>
+        <v>1289</v>
+      </c>
+      <c r="O6" s="112"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="n">
@@ -17968,17 +18506,17 @@
       <c r="D7" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="104" t="n">
+      <c r="E7" s="109" t="n">
         <v>39</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>1249</v>
+        <v>1290</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>1238</v>
-      </c>
-      <c r="H7" s="105"/>
-      <c r="I7" s="104" t="str">
+        <v>1279</v>
+      </c>
+      <c r="H7" s="110"/>
+      <c r="I7" s="109" t="str">
         <f aca="false">IF(H7="","",H7-E7)</f>
         <v/>
       </c>
@@ -17986,15 +18524,15 @@
         <f aca="false">IFERROR(IF(H7="","",(H7-E7)/E7),"")</f>
         <v/>
       </c>
-      <c r="K7" s="106"/>
+      <c r="K7" s="111"/>
       <c r="L7" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M7" s="106"/>
+      <c r="M7" s="111"/>
       <c r="N7" s="16" t="s">
-        <v>1250</v>
-      </c>
-      <c r="O7" s="107"/>
+        <v>1291</v>
+      </c>
+      <c r="O7" s="112"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="n">
@@ -18009,17 +18547,17 @@
       <c r="D8" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="104" t="n">
+      <c r="E8" s="109" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>1251</v>
+        <v>1292</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>1252</v>
-      </c>
-      <c r="H8" s="105"/>
-      <c r="I8" s="104" t="str">
+        <v>1293</v>
+      </c>
+      <c r="H8" s="110"/>
+      <c r="I8" s="109" t="str">
         <f aca="false">IF(H8="","",H8-E8)</f>
         <v/>
       </c>
@@ -18027,40 +18565,40 @@
         <f aca="false">IFERROR(IF(H8="","",(H8-E8)/E8),"")</f>
         <v/>
       </c>
-      <c r="K8" s="106"/>
+      <c r="K8" s="111"/>
       <c r="L8" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="106"/>
+      <c r="M8" s="111"/>
       <c r="N8" s="16" t="s">
-        <v>1253</v>
-      </c>
-      <c r="O8" s="107"/>
+        <v>1294</v>
+      </c>
+      <c r="O8" s="112"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1254</v>
+        <v>1295</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>53</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>1255</v>
-      </c>
-      <c r="E9" s="104" t="n">
+        <v>1296</v>
+      </c>
+      <c r="E9" s="109" t="n">
         <v>0.28</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>1256</v>
+        <v>1297</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>1257</v>
-      </c>
-      <c r="H9" s="105"/>
-      <c r="I9" s="104" t="str">
+        <v>1298</v>
+      </c>
+      <c r="H9" s="110"/>
+      <c r="I9" s="109" t="str">
         <f aca="false">IF(H9="","",H9-E9)</f>
         <v/>
       </c>
@@ -18068,22 +18606,22 @@
         <f aca="false">IFERROR(IF(H9="","",(H9-E9)/E9),"")</f>
         <v/>
       </c>
-      <c r="K9" s="106"/>
+      <c r="K9" s="111"/>
       <c r="L9" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="M9" s="106"/>
+      <c r="M9" s="111"/>
       <c r="N9" s="16" t="s">
-        <v>1258</v>
-      </c>
-      <c r="O9" s="107"/>
+        <v>1299</v>
+      </c>
+      <c r="O9" s="112"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1259</v>
+        <v>1300</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>53</v>
@@ -18091,17 +18629,17 @@
       <c r="D10" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="E10" s="104" t="n">
+      <c r="E10" s="109" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>1260</v>
+        <v>1301</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>1261</v>
-      </c>
-      <c r="H10" s="105"/>
-      <c r="I10" s="104" t="str">
+        <v>1302</v>
+      </c>
+      <c r="H10" s="110"/>
+      <c r="I10" s="109" t="str">
         <f aca="false">IF(H10="","",H10-E10)</f>
         <v/>
       </c>
@@ -18109,15 +18647,15 @@
         <f aca="false">IFERROR(IF(H10="","",(H10-E10)/E10),"")</f>
         <v/>
       </c>
-      <c r="K10" s="106"/>
+      <c r="K10" s="111"/>
       <c r="L10" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M10" s="106"/>
+      <c r="M10" s="111"/>
       <c r="N10" s="16" t="s">
-        <v>1262</v>
-      </c>
-      <c r="O10" s="107"/>
+        <v>1303</v>
+      </c>
+      <c r="O10" s="112"/>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="n">
@@ -18130,19 +18668,19 @@
         <v>95</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>1263</v>
-      </c>
-      <c r="E11" s="104" t="n">
+        <v>1304</v>
+      </c>
+      <c r="E11" s="109" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>1264</v>
+        <v>1305</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>1265</v>
-      </c>
-      <c r="H11" s="105"/>
-      <c r="I11" s="104" t="str">
+        <v>1306</v>
+      </c>
+      <c r="H11" s="110"/>
+      <c r="I11" s="109" t="str">
         <f aca="false">IF(H11="","",H11-E11)</f>
         <v/>
       </c>
@@ -18150,15 +18688,15 @@
         <f aca="false">IFERROR(IF(H11="","",(H11-E11)/E11),"")</f>
         <v/>
       </c>
-      <c r="K11" s="106"/>
+      <c r="K11" s="111"/>
       <c r="L11" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="M11" s="106"/>
+      <c r="M11" s="111"/>
       <c r="N11" s="16" t="s">
-        <v>1266</v>
-      </c>
-      <c r="O11" s="107"/>
+        <v>1307</v>
+      </c>
+      <c r="O11" s="112"/>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="n">
@@ -18173,17 +18711,17 @@
       <c r="D12" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="104" t="n">
+      <c r="E12" s="109" t="n">
         <v>31</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>1267</v>
+        <v>1308</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>1268</v>
-      </c>
-      <c r="H12" s="105"/>
-      <c r="I12" s="104" t="str">
+        <v>1309</v>
+      </c>
+      <c r="H12" s="110"/>
+      <c r="I12" s="109" t="str">
         <f aca="false">IF(H12="","",H12-E12)</f>
         <v/>
       </c>
@@ -18191,15 +18729,15 @@
         <f aca="false">IFERROR(IF(H12="","",(H12-E12)/E12),"")</f>
         <v/>
       </c>
-      <c r="K12" s="106"/>
+      <c r="K12" s="111"/>
       <c r="L12" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M12" s="106"/>
+      <c r="M12" s="111"/>
       <c r="N12" s="16" t="s">
-        <v>1269</v>
-      </c>
-      <c r="O12" s="107"/>
+        <v>1310</v>
+      </c>
+      <c r="O12" s="112"/>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="n">
@@ -18214,17 +18752,17 @@
       <c r="D13" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="E13" s="104" t="n">
+      <c r="E13" s="109" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>1270</v>
+        <v>1311</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>1271</v>
-      </c>
-      <c r="H13" s="105"/>
-      <c r="I13" s="104" t="str">
+        <v>1312</v>
+      </c>
+      <c r="H13" s="110"/>
+      <c r="I13" s="109" t="str">
         <f aca="false">IF(H13="","",H13-E13)</f>
         <v/>
       </c>
@@ -18232,15 +18770,15 @@
         <f aca="false">IFERROR(IF(H13="","",(H13-E13)/E13),"")</f>
         <v/>
       </c>
-      <c r="K13" s="106"/>
+      <c r="K13" s="111"/>
       <c r="L13" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M13" s="106"/>
+      <c r="M13" s="111"/>
       <c r="N13" s="16" t="s">
-        <v>1272</v>
-      </c>
-      <c r="O13" s="107"/>
+        <v>1313</v>
+      </c>
+      <c r="O13" s="112"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="n">
@@ -18255,17 +18793,17 @@
       <c r="D14" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="E14" s="104" t="n">
+      <c r="E14" s="109" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>1273</v>
+        <v>1314</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>1274</v>
-      </c>
-      <c r="H14" s="105"/>
-      <c r="I14" s="104" t="str">
+        <v>1315</v>
+      </c>
+      <c r="H14" s="110"/>
+      <c r="I14" s="109" t="str">
         <f aca="false">IF(H14="","",H14-E14)</f>
         <v/>
       </c>
@@ -18273,15 +18811,15 @@
         <f aca="false">IFERROR(IF(H14="","",(H14-E14)/E14),"")</f>
         <v/>
       </c>
-      <c r="K14" s="106"/>
+      <c r="K14" s="111"/>
       <c r="L14" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="106"/>
+      <c r="M14" s="111"/>
       <c r="N14" s="16" t="s">
-        <v>1275</v>
-      </c>
-      <c r="O14" s="107"/>
+        <v>1316</v>
+      </c>
+      <c r="O14" s="112"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="n">
@@ -18294,19 +18832,19 @@
         <v>52</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>1236</v>
-      </c>
-      <c r="E15" s="104" t="n">
+        <v>1277</v>
+      </c>
+      <c r="E15" s="109" t="n">
         <v>6</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>1264</v>
+        <v>1305</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>1276</v>
-      </c>
-      <c r="H15" s="105"/>
-      <c r="I15" s="104" t="str">
+        <v>1317</v>
+      </c>
+      <c r="H15" s="110"/>
+      <c r="I15" s="109" t="str">
         <f aca="false">IF(H15="","",H15-E15)</f>
         <v/>
       </c>
@@ -18314,15 +18852,15 @@
         <f aca="false">IFERROR(IF(H15="","",(H15-E15)/E15),"")</f>
         <v/>
       </c>
-      <c r="K15" s="106"/>
+      <c r="K15" s="111"/>
       <c r="L15" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M15" s="106"/>
+      <c r="M15" s="111"/>
       <c r="N15" s="16" t="s">
-        <v>1277</v>
-      </c>
-      <c r="O15" s="107"/>
+        <v>1318</v>
+      </c>
+      <c r="O15" s="112"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="n">
@@ -18335,19 +18873,19 @@
         <v>52</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>1278</v>
-      </c>
-      <c r="E16" s="104" t="n">
+        <v>1319</v>
+      </c>
+      <c r="E16" s="109" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>1279</v>
+        <v>1320</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>1280</v>
-      </c>
-      <c r="H16" s="105"/>
-      <c r="I16" s="104" t="str">
+        <v>1321</v>
+      </c>
+      <c r="H16" s="110"/>
+      <c r="I16" s="109" t="str">
         <f aca="false">IF(H16="","",H16-E16)</f>
         <v/>
       </c>
@@ -18355,31 +18893,31 @@
         <f aca="false">IFERROR(IF(H16="","",(H16-E16)/E16),"")</f>
         <v/>
       </c>
-      <c r="K16" s="106"/>
+      <c r="K16" s="111"/>
       <c r="L16" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M16" s="106"/>
+      <c r="M16" s="111"/>
       <c r="N16" s="16" t="s">
-        <v>1281</v>
-      </c>
-      <c r="O16" s="107"/>
+        <v>1322</v>
+      </c>
+      <c r="O16" s="112"/>
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
-        <v>1282</v>
-      </c>
-      <c r="C18" s="108" t="s">
-        <v>1283</v>
-      </c>
-      <c r="D18" s="108"/>
-      <c r="E18" s="108"/>
-      <c r="F18" s="108"/>
-      <c r="G18" s="108"/>
-      <c r="H18" s="108"/>
-      <c r="I18" s="108"/>
-      <c r="J18" s="108"/>
-      <c r="K18" s="108"/>
+        <v>1323</v>
+      </c>
+      <c r="C18" s="113" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D18" s="113"/>
+      <c r="E18" s="113"/>
+      <c r="F18" s="113"/>
+      <c r="G18" s="113"/>
+      <c r="H18" s="113"/>
+      <c r="I18" s="113"/>
+      <c r="J18" s="113"/>
+      <c r="K18" s="113"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -18397,7 +18935,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -18431,7 +18969,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1284</v>
+        <v>1325</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -18452,52 +18990,52 @@
         <v>50</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>1233</v>
+        <v>1274</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>1226</v>
+        <v>1267</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>1285</v>
+        <v>1326</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1286</v>
+        <v>1327</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1287</v>
+        <v>1328</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1288</v>
+        <v>1329</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>1229</v>
+        <v>1270</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>1289</v>
+        <v>1330</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>1290</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="109" t="n">
+      <c r="A4" s="114" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="110" t="s">
-        <v>1245</v>
-      </c>
-      <c r="D4" s="111" t="n">
+      <c r="C4" s="115" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D4" s="116" t="n">
         <f aca="false">'الخطة التنفيذية'!E5</f>
         <v>1271</v>
       </c>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="111" t="str">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="116" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H5="","",'الخطة التنفيذية'!H5)</f>
         <v/>
       </c>
@@ -18511,24 +19049,24 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="109" t="n">
+      <c r="A5" s="114" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="110" t="s">
-        <v>1248</v>
-      </c>
-      <c r="D5" s="111" t="n">
+      <c r="C5" s="115" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D5" s="116" t="n">
         <f aca="false">'الخطة التنفيذية'!E6</f>
         <v>25</v>
       </c>
-      <c r="E5" s="105"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="105"/>
-      <c r="H5" s="105"/>
-      <c r="I5" s="111" t="str">
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="116" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H6="","",'الخطة التنفيذية'!H6)</f>
         <v/>
       </c>
@@ -18542,24 +19080,24 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="109" t="n">
+      <c r="A6" s="114" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="110" t="s">
-        <v>1250</v>
-      </c>
-      <c r="D6" s="111" t="n">
+      <c r="C6" s="115" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D6" s="116" t="n">
         <f aca="false">'الخطة التنفيذية'!E7</f>
         <v>39</v>
       </c>
-      <c r="E6" s="105"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="105"/>
-      <c r="H6" s="105"/>
-      <c r="I6" s="111" t="str">
+      <c r="E6" s="110"/>
+      <c r="F6" s="110"/>
+      <c r="G6" s="110"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="116" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H7="","",'الخطة التنفيذية'!H7)</f>
         <v/>
       </c>
@@ -18573,24 +19111,24 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="109" t="n">
+      <c r="A7" s="114" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="110" t="s">
-        <v>1253</v>
-      </c>
-      <c r="D7" s="111" t="n">
+      <c r="C7" s="115" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D7" s="116" t="n">
         <f aca="false">'الخطة التنفيذية'!E8</f>
         <v>0</v>
       </c>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="111" t="str">
+      <c r="E7" s="110"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="116" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H8="","",'الخطة التنفيذية'!H8)</f>
         <v/>
       </c>
@@ -18604,24 +19142,24 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="109" t="n">
+      <c r="A8" s="114" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>1254</v>
-      </c>
-      <c r="C8" s="110" t="s">
-        <v>1258</v>
-      </c>
-      <c r="D8" s="111" t="n">
+        <v>1295</v>
+      </c>
+      <c r="C8" s="115" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D8" s="116" t="n">
         <f aca="false">'الخطة التنفيذية'!E9</f>
         <v>0.28</v>
       </c>
-      <c r="E8" s="105"/>
-      <c r="F8" s="105"/>
-      <c r="G8" s="105"/>
-      <c r="H8" s="105"/>
-      <c r="I8" s="111" t="str">
+      <c r="E8" s="110"/>
+      <c r="F8" s="110"/>
+      <c r="G8" s="110"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="116" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H9="","",'الخطة التنفيذية'!H9)</f>
         <v/>
       </c>
@@ -18635,24 +19173,24 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="109" t="n">
+      <c r="A9" s="114" t="n">
         <v>6</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1259</v>
-      </c>
-      <c r="C9" s="110" t="s">
-        <v>1262</v>
-      </c>
-      <c r="D9" s="111" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C9" s="115" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D9" s="116" t="n">
         <f aca="false">'الخطة التنفيذية'!E10</f>
         <v>0</v>
       </c>
-      <c r="E9" s="105"/>
-      <c r="F9" s="105"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="105"/>
-      <c r="I9" s="111" t="str">
+      <c r="E9" s="110"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="110"/>
+      <c r="I9" s="116" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H10="","",'الخطة التنفيذية'!H10)</f>
         <v/>
       </c>
@@ -18666,24 +19204,24 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="109" t="n">
+      <c r="A10" s="114" t="n">
         <v>7</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="110" t="s">
-        <v>1266</v>
-      </c>
-      <c r="D10" s="111" t="n">
+      <c r="C10" s="115" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D10" s="116" t="n">
         <f aca="false">'الخطة التنفيذية'!E11</f>
         <v>0</v>
       </c>
-      <c r="E10" s="105"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="111" t="str">
+      <c r="E10" s="110"/>
+      <c r="F10" s="110"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="110"/>
+      <c r="I10" s="116" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H11="","",'الخطة التنفيذية'!H11)</f>
         <v/>
       </c>
@@ -18697,24 +19235,24 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="109" t="n">
+      <c r="A11" s="114" t="n">
         <v>8</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="110" t="s">
-        <v>1269</v>
-      </c>
-      <c r="D11" s="111" t="n">
+      <c r="C11" s="115" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D11" s="116" t="n">
         <f aca="false">'الخطة التنفيذية'!E12</f>
         <v>31</v>
       </c>
-      <c r="E11" s="105"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="105"/>
-      <c r="I11" s="111" t="str">
+      <c r="E11" s="110"/>
+      <c r="F11" s="110"/>
+      <c r="G11" s="110"/>
+      <c r="H11" s="110"/>
+      <c r="I11" s="116" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H12="","",'الخطة التنفيذية'!H12)</f>
         <v/>
       </c>
@@ -18728,24 +19266,24 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="109" t="n">
+      <c r="A12" s="114" t="n">
         <v>9</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="C12" s="110" t="s">
-        <v>1272</v>
-      </c>
-      <c r="D12" s="111" t="n">
+      <c r="C12" s="115" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D12" s="116" t="n">
         <f aca="false">'الخطة التنفيذية'!E13</f>
         <v>0</v>
       </c>
-      <c r="E12" s="105"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="111" t="str">
+      <c r="E12" s="110"/>
+      <c r="F12" s="110"/>
+      <c r="G12" s="110"/>
+      <c r="H12" s="110"/>
+      <c r="I12" s="116" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H13="","",'الخطة التنفيذية'!H13)</f>
         <v/>
       </c>
@@ -18759,24 +19297,24 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="109" t="n">
+      <c r="A13" s="114" t="n">
         <v>10</v>
       </c>
       <c r="B13" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="110" t="s">
-        <v>1275</v>
-      </c>
-      <c r="D13" s="111" t="n">
+      <c r="C13" s="115" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D13" s="116" t="n">
         <f aca="false">'الخطة التنفيذية'!E14</f>
         <v>0</v>
       </c>
-      <c r="E13" s="105"/>
-      <c r="F13" s="105"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="105"/>
-      <c r="I13" s="111" t="str">
+      <c r="E13" s="110"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="110"/>
+      <c r="H13" s="110"/>
+      <c r="I13" s="116" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H14="","",'الخطة التنفيذية'!H14)</f>
         <v/>
       </c>
@@ -18790,24 +19328,24 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="109" t="n">
+      <c r="A14" s="114" t="n">
         <v>11</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="110" t="s">
-        <v>1277</v>
-      </c>
-      <c r="D14" s="111" t="n">
+      <c r="C14" s="115" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D14" s="116" t="n">
         <f aca="false">'الخطة التنفيذية'!E15</f>
         <v>6</v>
       </c>
-      <c r="E14" s="105"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="105"/>
-      <c r="I14" s="111" t="str">
+      <c r="E14" s="110"/>
+      <c r="F14" s="110"/>
+      <c r="G14" s="110"/>
+      <c r="H14" s="110"/>
+      <c r="I14" s="116" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H15="","",'الخطة التنفيذية'!H15)</f>
         <v/>
       </c>
@@ -18821,24 +19359,24 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="109" t="n">
+      <c r="A15" s="114" t="n">
         <v>12</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="110" t="s">
-        <v>1281</v>
-      </c>
-      <c r="D15" s="111" t="n">
+      <c r="C15" s="115" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D15" s="116" t="n">
         <f aca="false">'الخطة التنفيذية'!E16</f>
         <v>0</v>
       </c>
-      <c r="E15" s="105"/>
-      <c r="F15" s="105"/>
-      <c r="G15" s="105"/>
-      <c r="H15" s="105"/>
-      <c r="I15" s="111" t="str">
+      <c r="E15" s="110"/>
+      <c r="F15" s="110"/>
+      <c r="G15" s="110"/>
+      <c r="H15" s="110"/>
+      <c r="I15" s="116" t="str">
         <f aca="false">IF('الخطة التنفيذية'!H16="","",'الخطة التنفيذية'!H16)</f>
         <v/>
       </c>
@@ -18866,7 +19404,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -18890,7 +19428,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1291</v>
+        <v>1332</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -18908,7 +19446,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1292</v>
+        <v>1333</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -18929,34 +19467,34 @@
         <v>49</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>1293</v>
+        <v>1334</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>50</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>1294</v>
+        <v>1335</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>59</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1232</v>
+        <v>1273</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1295</v>
+        <v>1336</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1296</v>
+        <v>1337</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>1297</v>
+        <v>1338</v>
       </c>
       <c r="J3" s="15" t="s">
         <v>60</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>1298</v>
+        <v>1339</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>679</v>
@@ -18965,561 +19503,561 @@
         <v>383</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>1299</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="101" t="s">
-        <v>1234</v>
-      </c>
-      <c r="B4" s="102" t="s">
-        <v>1300</v>
-      </c>
-      <c r="C4" s="101" t="s">
+      <c r="A4" s="106" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B4" s="107" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C4" s="106" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="101" t="s">
+      <c r="D4" s="106" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="101" t="s">
+      <c r="E4" s="106" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="101" t="s">
-        <v>1240</v>
-      </c>
-      <c r="G4" s="112" t="n">
+      <c r="F4" s="106" t="s">
+        <v>1281</v>
+      </c>
+      <c r="G4" s="117" t="n">
         <v>46235</v>
       </c>
-      <c r="H4" s="112" t="n">
+      <c r="H4" s="117" t="n">
         <v>46326</v>
       </c>
-      <c r="I4" s="101" t="n">
+      <c r="I4" s="106" t="n">
         <f aca="false">IF(OR(G4="",H4=""),"",H4-G4)</f>
         <v>91</v>
       </c>
-      <c r="J4" s="101" t="n">
+      <c r="J4" s="106" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="101" t="s">
-        <v>1301</v>
-      </c>
-      <c r="L4" s="102" t="s">
-        <v>1302</v>
-      </c>
-      <c r="M4" s="101" t="s">
-        <v>1242</v>
-      </c>
-      <c r="N4" s="113" t="n">
+      <c r="K4" s="106" t="s">
+        <v>1342</v>
+      </c>
+      <c r="L4" s="107" t="s">
+        <v>1343</v>
+      </c>
+      <c r="M4" s="106" t="s">
+        <v>1283</v>
+      </c>
+      <c r="N4" s="118" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="109" t="n">
+      <c r="A5" s="114" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="106"/>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="107"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="114"/>
+      <c r="B5" s="111"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="112"/>
+      <c r="F5" s="112"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="119"/>
       <c r="I5" s="21" t="str">
         <f aca="false">IF(OR(G5="",H5=""),"",H5-G5)</f>
         <v/>
       </c>
-      <c r="J5" s="107"/>
-      <c r="K5" s="107"/>
-      <c r="L5" s="106"/>
-      <c r="M5" s="107"/>
-      <c r="N5" s="115"/>
+      <c r="J5" s="112"/>
+      <c r="K5" s="112"/>
+      <c r="L5" s="111"/>
+      <c r="M5" s="112"/>
+      <c r="N5" s="120"/>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="109" t="n">
+      <c r="A6" s="114" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="106"/>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="107"/>
-      <c r="F6" s="107"/>
-      <c r="G6" s="114"/>
-      <c r="H6" s="114"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="112"/>
+      <c r="D6" s="112"/>
+      <c r="E6" s="112"/>
+      <c r="F6" s="112"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="119"/>
       <c r="I6" s="21" t="str">
         <f aca="false">IF(OR(G6="",H6=""),"",H6-G6)</f>
         <v/>
       </c>
-      <c r="J6" s="107"/>
-      <c r="K6" s="107"/>
-      <c r="L6" s="106"/>
-      <c r="M6" s="107"/>
-      <c r="N6" s="115"/>
+      <c r="J6" s="112"/>
+      <c r="K6" s="112"/>
+      <c r="L6" s="111"/>
+      <c r="M6" s="112"/>
+      <c r="N6" s="120"/>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="109" t="n">
+      <c r="A7" s="114" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="106"/>
-      <c r="C7" s="107"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="107"/>
-      <c r="F7" s="107"/>
-      <c r="G7" s="114"/>
-      <c r="H7" s="114"/>
+      <c r="B7" s="111"/>
+      <c r="C7" s="112"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="112"/>
+      <c r="F7" s="112"/>
+      <c r="G7" s="119"/>
+      <c r="H7" s="119"/>
       <c r="I7" s="21" t="str">
         <f aca="false">IF(OR(G7="",H7=""),"",H7-G7)</f>
         <v/>
       </c>
-      <c r="J7" s="107"/>
-      <c r="K7" s="107"/>
-      <c r="L7" s="106"/>
-      <c r="M7" s="107"/>
-      <c r="N7" s="115"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="112"/>
+      <c r="L7" s="111"/>
+      <c r="M7" s="112"/>
+      <c r="N7" s="120"/>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="109" t="n">
+      <c r="A8" s="114" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="106"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="107"/>
-      <c r="G8" s="114"/>
-      <c r="H8" s="114"/>
+      <c r="B8" s="111"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
       <c r="I8" s="21" t="str">
         <f aca="false">IF(OR(G8="",H8=""),"",H8-G8)</f>
         <v/>
       </c>
-      <c r="J8" s="107"/>
-      <c r="K8" s="107"/>
-      <c r="L8" s="106"/>
-      <c r="M8" s="107"/>
-      <c r="N8" s="115"/>
+      <c r="J8" s="112"/>
+      <c r="K8" s="112"/>
+      <c r="L8" s="111"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="120"/>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="109" t="n">
+      <c r="A9" s="114" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="106"/>
-      <c r="C9" s="107"/>
-      <c r="D9" s="107"/>
-      <c r="E9" s="107"/>
-      <c r="F9" s="107"/>
-      <c r="G9" s="114"/>
-      <c r="H9" s="114"/>
+      <c r="B9" s="111"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="112"/>
+      <c r="F9" s="112"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
       <c r="I9" s="21" t="str">
         <f aca="false">IF(OR(G9="",H9=""),"",H9-G9)</f>
         <v/>
       </c>
-      <c r="J9" s="107"/>
-      <c r="K9" s="107"/>
-      <c r="L9" s="106"/>
-      <c r="M9" s="107"/>
-      <c r="N9" s="115"/>
+      <c r="J9" s="112"/>
+      <c r="K9" s="112"/>
+      <c r="L9" s="111"/>
+      <c r="M9" s="112"/>
+      <c r="N9" s="120"/>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="109" t="n">
+      <c r="A10" s="114" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="106"/>
-      <c r="C10" s="107"/>
-      <c r="D10" s="107"/>
-      <c r="E10" s="107"/>
-      <c r="F10" s="107"/>
-      <c r="G10" s="114"/>
-      <c r="H10" s="114"/>
+      <c r="B10" s="111"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
       <c r="I10" s="21" t="str">
         <f aca="false">IF(OR(G10="",H10=""),"",H10-G10)</f>
         <v/>
       </c>
-      <c r="J10" s="107"/>
-      <c r="K10" s="107"/>
-      <c r="L10" s="106"/>
-      <c r="M10" s="107"/>
-      <c r="N10" s="115"/>
+      <c r="J10" s="112"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="111"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="120"/>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="109" t="n">
+      <c r="A11" s="114" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="106"/>
-      <c r="C11" s="107"/>
-      <c r="D11" s="107"/>
-      <c r="E11" s="107"/>
-      <c r="F11" s="107"/>
-      <c r="G11" s="114"/>
-      <c r="H11" s="114"/>
+      <c r="B11" s="111"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
       <c r="I11" s="21" t="str">
         <f aca="false">IF(OR(G11="",H11=""),"",H11-G11)</f>
         <v/>
       </c>
-      <c r="J11" s="107"/>
-      <c r="K11" s="107"/>
-      <c r="L11" s="106"/>
-      <c r="M11" s="107"/>
-      <c r="N11" s="115"/>
+      <c r="J11" s="112"/>
+      <c r="K11" s="112"/>
+      <c r="L11" s="111"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="120"/>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="109" t="n">
+      <c r="A12" s="114" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="106"/>
-      <c r="C12" s="107"/>
-      <c r="D12" s="107"/>
-      <c r="E12" s="107"/>
-      <c r="F12" s="107"/>
-      <c r="G12" s="114"/>
-      <c r="H12" s="114"/>
+      <c r="B12" s="111"/>
+      <c r="C12" s="112"/>
+      <c r="D12" s="112"/>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="119"/>
+      <c r="H12" s="119"/>
       <c r="I12" s="21" t="str">
         <f aca="false">IF(OR(G12="",H12=""),"",H12-G12)</f>
         <v/>
       </c>
-      <c r="J12" s="107"/>
-      <c r="K12" s="107"/>
-      <c r="L12" s="106"/>
-      <c r="M12" s="107"/>
-      <c r="N12" s="115"/>
+      <c r="J12" s="112"/>
+      <c r="K12" s="112"/>
+      <c r="L12" s="111"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="120"/>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="109" t="n">
+      <c r="A13" s="114" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="106"/>
-      <c r="C13" s="107"/>
-      <c r="D13" s="107"/>
-      <c r="E13" s="107"/>
-      <c r="F13" s="107"/>
-      <c r="G13" s="114"/>
-      <c r="H13" s="114"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="112"/>
+      <c r="D13" s="112"/>
+      <c r="E13" s="112"/>
+      <c r="F13" s="112"/>
+      <c r="G13" s="119"/>
+      <c r="H13" s="119"/>
       <c r="I13" s="21" t="str">
         <f aca="false">IF(OR(G13="",H13=""),"",H13-G13)</f>
         <v/>
       </c>
-      <c r="J13" s="107"/>
-      <c r="K13" s="107"/>
-      <c r="L13" s="106"/>
-      <c r="M13" s="107"/>
-      <c r="N13" s="115"/>
+      <c r="J13" s="112"/>
+      <c r="K13" s="112"/>
+      <c r="L13" s="111"/>
+      <c r="M13" s="112"/>
+      <c r="N13" s="120"/>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="109" t="n">
+      <c r="A14" s="114" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="106"/>
-      <c r="C14" s="107"/>
-      <c r="D14" s="107"/>
-      <c r="E14" s="107"/>
-      <c r="F14" s="107"/>
-      <c r="G14" s="114"/>
-      <c r="H14" s="114"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="112"/>
+      <c r="D14" s="112"/>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="119"/>
+      <c r="H14" s="119"/>
       <c r="I14" s="21" t="str">
         <f aca="false">IF(OR(G14="",H14=""),"",H14-G14)</f>
         <v/>
       </c>
-      <c r="J14" s="107"/>
-      <c r="K14" s="107"/>
-      <c r="L14" s="106"/>
-      <c r="M14" s="107"/>
-      <c r="N14" s="115"/>
+      <c r="J14" s="112"/>
+      <c r="K14" s="112"/>
+      <c r="L14" s="111"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="120"/>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="109" t="n">
+      <c r="A15" s="114" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="106"/>
-      <c r="C15" s="107"/>
-      <c r="D15" s="107"/>
-      <c r="E15" s="107"/>
-      <c r="F15" s="107"/>
-      <c r="G15" s="114"/>
-      <c r="H15" s="114"/>
+      <c r="B15" s="111"/>
+      <c r="C15" s="112"/>
+      <c r="D15" s="112"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="119"/>
+      <c r="H15" s="119"/>
       <c r="I15" s="21" t="str">
         <f aca="false">IF(OR(G15="",H15=""),"",H15-G15)</f>
         <v/>
       </c>
-      <c r="J15" s="107"/>
-      <c r="K15" s="107"/>
-      <c r="L15" s="106"/>
-      <c r="M15" s="107"/>
-      <c r="N15" s="115"/>
+      <c r="J15" s="112"/>
+      <c r="K15" s="112"/>
+      <c r="L15" s="111"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="120"/>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="109" t="n">
+      <c r="A16" s="114" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="106"/>
-      <c r="C16" s="107"/>
-      <c r="D16" s="107"/>
-      <c r="E16" s="107"/>
-      <c r="F16" s="107"/>
-      <c r="G16" s="114"/>
-      <c r="H16" s="114"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="112"/>
+      <c r="D16" s="112"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="119"/>
+      <c r="H16" s="119"/>
       <c r="I16" s="21" t="str">
         <f aca="false">IF(OR(G16="",H16=""),"",H16-G16)</f>
         <v/>
       </c>
-      <c r="J16" s="107"/>
-      <c r="K16" s="107"/>
-      <c r="L16" s="106"/>
-      <c r="M16" s="107"/>
-      <c r="N16" s="115"/>
+      <c r="J16" s="112"/>
+      <c r="K16" s="112"/>
+      <c r="L16" s="111"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="120"/>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="109" t="n">
+      <c r="A17" s="114" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="106"/>
-      <c r="C17" s="107"/>
-      <c r="D17" s="107"/>
-      <c r="E17" s="107"/>
-      <c r="F17" s="107"/>
-      <c r="G17" s="114"/>
-      <c r="H17" s="114"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="112"/>
+      <c r="D17" s="112"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="119"/>
+      <c r="H17" s="119"/>
       <c r="I17" s="21" t="str">
         <f aca="false">IF(OR(G17="",H17=""),"",H17-G17)</f>
         <v/>
       </c>
-      <c r="J17" s="107"/>
-      <c r="K17" s="107"/>
-      <c r="L17" s="106"/>
-      <c r="M17" s="107"/>
-      <c r="N17" s="115"/>
+      <c r="J17" s="112"/>
+      <c r="K17" s="112"/>
+      <c r="L17" s="111"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="120"/>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="109" t="n">
+      <c r="A18" s="114" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="106"/>
-      <c r="C18" s="107"/>
-      <c r="D18" s="107"/>
-      <c r="E18" s="107"/>
-      <c r="F18" s="107"/>
-      <c r="G18" s="114"/>
-      <c r="H18" s="114"/>
+      <c r="B18" s="111"/>
+      <c r="C18" s="112"/>
+      <c r="D18" s="112"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="119"/>
+      <c r="H18" s="119"/>
       <c r="I18" s="21" t="str">
         <f aca="false">IF(OR(G18="",H18=""),"",H18-G18)</f>
         <v/>
       </c>
-      <c r="J18" s="107"/>
-      <c r="K18" s="107"/>
-      <c r="L18" s="106"/>
-      <c r="M18" s="107"/>
-      <c r="N18" s="115"/>
+      <c r="J18" s="112"/>
+      <c r="K18" s="112"/>
+      <c r="L18" s="111"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="120"/>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="109" t="n">
+      <c r="A19" s="114" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="106"/>
-      <c r="C19" s="107"/>
-      <c r="D19" s="107"/>
-      <c r="E19" s="107"/>
-      <c r="F19" s="107"/>
-      <c r="G19" s="114"/>
-      <c r="H19" s="114"/>
+      <c r="B19" s="111"/>
+      <c r="C19" s="112"/>
+      <c r="D19" s="112"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="119"/>
+      <c r="H19" s="119"/>
       <c r="I19" s="21" t="str">
         <f aca="false">IF(OR(G19="",H19=""),"",H19-G19)</f>
         <v/>
       </c>
-      <c r="J19" s="107"/>
-      <c r="K19" s="107"/>
-      <c r="L19" s="106"/>
-      <c r="M19" s="107"/>
-      <c r="N19" s="115"/>
+      <c r="J19" s="112"/>
+      <c r="K19" s="112"/>
+      <c r="L19" s="111"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="120"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="109" t="n">
+      <c r="A20" s="114" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="106"/>
-      <c r="C20" s="107"/>
-      <c r="D20" s="107"/>
-      <c r="E20" s="107"/>
-      <c r="F20" s="107"/>
-      <c r="G20" s="114"/>
-      <c r="H20" s="114"/>
+      <c r="B20" s="111"/>
+      <c r="C20" s="112"/>
+      <c r="D20" s="112"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="119"/>
+      <c r="H20" s="119"/>
       <c r="I20" s="21" t="str">
         <f aca="false">IF(OR(G20="",H20=""),"",H20-G20)</f>
         <v/>
       </c>
-      <c r="J20" s="107"/>
-      <c r="K20" s="107"/>
-      <c r="L20" s="106"/>
-      <c r="M20" s="107"/>
-      <c r="N20" s="115"/>
+      <c r="J20" s="112"/>
+      <c r="K20" s="112"/>
+      <c r="L20" s="111"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="120"/>
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="109" t="n">
+      <c r="A21" s="114" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="106"/>
-      <c r="C21" s="107"/>
-      <c r="D21" s="107"/>
-      <c r="E21" s="107"/>
-      <c r="F21" s="107"/>
-      <c r="G21" s="114"/>
-      <c r="H21" s="114"/>
+      <c r="B21" s="111"/>
+      <c r="C21" s="112"/>
+      <c r="D21" s="112"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="119"/>
+      <c r="H21" s="119"/>
       <c r="I21" s="21" t="str">
         <f aca="false">IF(OR(G21="",H21=""),"",H21-G21)</f>
         <v/>
       </c>
-      <c r="J21" s="107"/>
-      <c r="K21" s="107"/>
-      <c r="L21" s="106"/>
-      <c r="M21" s="107"/>
-      <c r="N21" s="115"/>
+      <c r="J21" s="112"/>
+      <c r="K21" s="112"/>
+      <c r="L21" s="111"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="120"/>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="109" t="n">
+      <c r="A22" s="114" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="106"/>
-      <c r="C22" s="107"/>
-      <c r="D22" s="107"/>
-      <c r="E22" s="107"/>
-      <c r="F22" s="107"/>
-      <c r="G22" s="114"/>
-      <c r="H22" s="114"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="112"/>
+      <c r="D22" s="112"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="119"/>
       <c r="I22" s="21" t="str">
         <f aca="false">IF(OR(G22="",H22=""),"",H22-G22)</f>
         <v/>
       </c>
-      <c r="J22" s="107"/>
-      <c r="K22" s="107"/>
-      <c r="L22" s="106"/>
-      <c r="M22" s="107"/>
-      <c r="N22" s="115"/>
+      <c r="J22" s="112"/>
+      <c r="K22" s="112"/>
+      <c r="L22" s="111"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="120"/>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="109" t="n">
+      <c r="A23" s="114" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="106"/>
-      <c r="C23" s="107"/>
-      <c r="D23" s="107"/>
-      <c r="E23" s="107"/>
-      <c r="F23" s="107"/>
-      <c r="G23" s="114"/>
-      <c r="H23" s="114"/>
+      <c r="B23" s="111"/>
+      <c r="C23" s="112"/>
+      <c r="D23" s="112"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="119"/>
+      <c r="H23" s="119"/>
       <c r="I23" s="21" t="str">
         <f aca="false">IF(OR(G23="",H23=""),"",H23-G23)</f>
         <v/>
       </c>
-      <c r="J23" s="107"/>
-      <c r="K23" s="107"/>
-      <c r="L23" s="106"/>
-      <c r="M23" s="107"/>
-      <c r="N23" s="115"/>
+      <c r="J23" s="112"/>
+      <c r="K23" s="112"/>
+      <c r="L23" s="111"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="120"/>
     </row>
     <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="109" t="n">
+      <c r="A24" s="114" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="106"/>
-      <c r="C24" s="107"/>
-      <c r="D24" s="107"/>
-      <c r="E24" s="107"/>
-      <c r="F24" s="107"/>
-      <c r="G24" s="114"/>
-      <c r="H24" s="114"/>
+      <c r="B24" s="111"/>
+      <c r="C24" s="112"/>
+      <c r="D24" s="112"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="119"/>
+      <c r="H24" s="119"/>
       <c r="I24" s="21" t="str">
         <f aca="false">IF(OR(G24="",H24=""),"",H24-G24)</f>
         <v/>
       </c>
-      <c r="J24" s="107"/>
-      <c r="K24" s="107"/>
-      <c r="L24" s="106"/>
-      <c r="M24" s="107"/>
-      <c r="N24" s="115"/>
+      <c r="J24" s="112"/>
+      <c r="K24" s="112"/>
+      <c r="L24" s="111"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="120"/>
     </row>
     <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="109" t="n">
+      <c r="A25" s="114" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="106"/>
-      <c r="C25" s="107"/>
-      <c r="D25" s="107"/>
-      <c r="E25" s="107"/>
-      <c r="F25" s="107"/>
-      <c r="G25" s="114"/>
-      <c r="H25" s="114"/>
+      <c r="B25" s="111"/>
+      <c r="C25" s="112"/>
+      <c r="D25" s="112"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="119"/>
+      <c r="H25" s="119"/>
       <c r="I25" s="21" t="str">
         <f aca="false">IF(OR(G25="",H25=""),"",H25-G25)</f>
         <v/>
       </c>
-      <c r="J25" s="107"/>
-      <c r="K25" s="107"/>
-      <c r="L25" s="106"/>
-      <c r="M25" s="107"/>
-      <c r="N25" s="115"/>
+      <c r="J25" s="112"/>
+      <c r="K25" s="112"/>
+      <c r="L25" s="111"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="120"/>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="109" t="n">
+      <c r="A26" s="114" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="106"/>
-      <c r="C26" s="107"/>
-      <c r="D26" s="107"/>
-      <c r="E26" s="107"/>
-      <c r="F26" s="107"/>
-      <c r="G26" s="114"/>
-      <c r="H26" s="114"/>
+      <c r="B26" s="111"/>
+      <c r="C26" s="112"/>
+      <c r="D26" s="112"/>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="119"/>
+      <c r="H26" s="119"/>
       <c r="I26" s="21" t="str">
         <f aca="false">IF(OR(G26="",H26=""),"",H26-G26)</f>
         <v/>
       </c>
-      <c r="J26" s="107"/>
-      <c r="K26" s="107"/>
-      <c r="L26" s="106"/>
-      <c r="M26" s="107"/>
-      <c r="N26" s="115"/>
+      <c r="J26" s="112"/>
+      <c r="K26" s="112"/>
+      <c r="L26" s="111"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="120"/>
     </row>
     <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="109" t="n">
+      <c r="A27" s="114" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="106"/>
-      <c r="C27" s="107"/>
-      <c r="D27" s="107"/>
-      <c r="E27" s="107"/>
-      <c r="F27" s="107"/>
-      <c r="G27" s="114"/>
-      <c r="H27" s="114"/>
+      <c r="B27" s="111"/>
+      <c r="C27" s="112"/>
+      <c r="D27" s="112"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="119"/>
+      <c r="H27" s="119"/>
       <c r="I27" s="21" t="str">
         <f aca="false">IF(OR(G27="",H27=""),"",H27-G27)</f>
         <v/>
       </c>
-      <c r="J27" s="107"/>
-      <c r="K27" s="107"/>
-      <c r="L27" s="106"/>
-      <c r="M27" s="107"/>
-      <c r="N27" s="115"/>
+      <c r="J27" s="112"/>
+      <c r="K27" s="112"/>
+      <c r="L27" s="111"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="120"/>
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="109" t="n">
+      <c r="A28" s="114" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="106"/>
-      <c r="C28" s="107"/>
-      <c r="D28" s="107"/>
-      <c r="E28" s="107"/>
-      <c r="F28" s="107"/>
-      <c r="G28" s="114"/>
-      <c r="H28" s="114"/>
+      <c r="B28" s="111"/>
+      <c r="C28" s="112"/>
+      <c r="D28" s="112"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="119"/>
+      <c r="H28" s="119"/>
       <c r="I28" s="21" t="str">
         <f aca="false">IF(OR(G28="",H28=""),"",H28-G28)</f>
         <v/>
       </c>
-      <c r="J28" s="107"/>
-      <c r="K28" s="107"/>
-      <c r="L28" s="106"/>
-      <c r="M28" s="107"/>
-      <c r="N28" s="115"/>
+      <c r="J28" s="112"/>
+      <c r="K28" s="112"/>
+      <c r="L28" s="111"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="120"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="24" t="s">
-        <v>1303</v>
+        <v>1344</v>
       </c>
       <c r="M30" s="21" t="str">
         <f aca="false">COUNTA(B5:B28)&amp;" مبادرة"</f>
@@ -19545,7 +20083,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -19571,7 +20109,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1304</v>
+        <v>1345</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -19590,7 +20128,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1305</v>
+        <v>1346</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -19609,7 +20147,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>1306</v>
+        <v>1347</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>858</v>
@@ -19618,40 +20156,40 @@
         <v>1012</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>1307</v>
+        <v>1348</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>1308</v>
+        <v>1349</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1309</v>
+        <v>1350</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1310</v>
+        <v>1351</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1311</v>
+        <v>1352</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>1312</v>
+        <v>1353</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>1313</v>
+        <v>1354</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>860</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>1314</v>
+        <v>1355</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>1315</v>
+        <v>1356</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>1316</v>
+        <v>1357</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>1317</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19683,7 +20221,7 @@
       <c r="I4" s="28" t="n">
         <v>23493282</v>
       </c>
-      <c r="J4" s="104" t="n">
+      <c r="J4" s="109" t="n">
         <v>64.69</v>
       </c>
       <c r="K4" s="57" t="n">
@@ -19699,7 +20237,7 @@
         <v>0.281</v>
       </c>
       <c r="O4" s="21" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19731,10 +20269,10 @@
       <c r="I5" s="28" t="n">
         <v>8841940</v>
       </c>
-      <c r="J5" s="104" t="n">
+      <c r="J5" s="109" t="n">
         <v>61.72</v>
       </c>
-      <c r="K5" s="116" t="n">
+      <c r="K5" s="121" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="45" t="n">
@@ -19747,7 +20285,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>1319</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19779,10 +20317,10 @@
       <c r="I6" s="28" t="n">
         <v>7467484</v>
       </c>
-      <c r="J6" s="104" t="n">
+      <c r="J6" s="109" t="n">
         <v>80.21</v>
       </c>
-      <c r="K6" s="116" t="n">
+      <c r="K6" s="121" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="45" t="n">
@@ -19795,7 +20333,7 @@
         <v>0.344</v>
       </c>
       <c r="O6" s="21" t="s">
-        <v>1320</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19827,10 +20365,10 @@
       <c r="I7" s="28" t="n">
         <v>14552120</v>
       </c>
-      <c r="J7" s="104" t="n">
+      <c r="J7" s="109" t="n">
         <v>84.21</v>
       </c>
-      <c r="K7" s="117" t="n">
+      <c r="K7" s="122" t="n">
         <v>0.273</v>
       </c>
       <c r="L7" s="45" t="n">
@@ -19843,7 +20381,7 @@
         <v>0.641</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>1321</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19875,7 +20413,7 @@
       <c r="I8" s="28" t="n">
         <v>2916708</v>
       </c>
-      <c r="J8" s="104" t="n">
+      <c r="J8" s="109" t="n">
         <v>48.35</v>
       </c>
       <c r="K8" s="57" t="n">
@@ -19891,7 +20429,7 @@
         <v>0.134</v>
       </c>
       <c r="O8" s="21" t="s">
-        <v>1322</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19923,10 +20461,10 @@
       <c r="I9" s="28" t="n">
         <v>2916316</v>
       </c>
-      <c r="J9" s="104" t="n">
+      <c r="J9" s="109" t="n">
         <v>65.82</v>
       </c>
-      <c r="K9" s="116" t="n">
+      <c r="K9" s="121" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="45" t="n">
@@ -19939,7 +20477,7 @@
         <v>0.309</v>
       </c>
       <c r="O9" s="21" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19971,10 +20509,10 @@
       <c r="I10" s="28" t="n">
         <v>2831981</v>
       </c>
-      <c r="J10" s="104" t="n">
+      <c r="J10" s="109" t="n">
         <v>59.14</v>
       </c>
-      <c r="K10" s="116" t="n">
+      <c r="K10" s="121" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="45" t="n">
@@ -19987,7 +20525,7 @@
         <v>0.006</v>
       </c>
       <c r="O10" s="21" t="s">
-        <v>1320</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20019,10 +20557,10 @@
       <c r="I11" s="28" t="n">
         <v>2931550</v>
       </c>
-      <c r="J11" s="104" t="n">
+      <c r="J11" s="109" t="n">
         <v>49.84</v>
       </c>
-      <c r="K11" s="116" t="n">
+      <c r="K11" s="121" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="45" t="n">
@@ -20035,7 +20573,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="21" t="s">
-        <v>1320</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20067,7 +20605,7 @@
       <c r="I12" s="28" t="n">
         <v>8679738</v>
       </c>
-      <c r="J12" s="104" t="n">
+      <c r="J12" s="109" t="n">
         <v>59.34</v>
       </c>
       <c r="K12" s="57" t="n">
@@ -20083,7 +20621,7 @@
         <v>0.277</v>
       </c>
       <c r="O12" s="21" t="s">
-        <v>1320</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20115,7 +20653,7 @@
       <c r="I13" s="28" t="n">
         <v>7729931</v>
       </c>
-      <c r="J13" s="104" t="n">
+      <c r="J13" s="109" t="n">
         <v>67.66</v>
       </c>
       <c r="K13" s="57" t="n">
@@ -20131,7 +20669,7 @@
         <v>0.082</v>
       </c>
       <c r="O13" s="21" t="s">
-        <v>1320</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20163,7 +20701,7 @@
       <c r="I14" s="28" t="n">
         <v>2676944</v>
       </c>
-      <c r="J14" s="104" t="n">
+      <c r="J14" s="109" t="n">
         <v>59.47</v>
       </c>
       <c r="K14" s="45" t="n">
@@ -20179,7 +20717,7 @@
         <v>0.231</v>
       </c>
       <c r="O14" s="21" t="s">
-        <v>1320</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20211,7 +20749,7 @@
       <c r="I15" s="28" t="n">
         <v>7806709</v>
       </c>
-      <c r="J15" s="104" t="n">
+      <c r="J15" s="109" t="n">
         <v>63.18</v>
       </c>
       <c r="K15" s="57" t="n">
@@ -20227,7 +20765,7 @@
         <v>0.458</v>
       </c>
       <c r="O15" s="21" t="s">
-        <v>1322</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20259,10 +20797,10 @@
       <c r="I16" s="28" t="n">
         <v>4791911</v>
       </c>
-      <c r="J16" s="104" t="n">
+      <c r="J16" s="109" t="n">
         <v>74.3</v>
       </c>
-      <c r="K16" s="117" t="n">
+      <c r="K16" s="122" t="n">
         <v>0.151</v>
       </c>
       <c r="L16" s="45" t="n">
@@ -20275,7 +20813,7 @@
         <v>0.076</v>
       </c>
       <c r="O16" s="21" t="s">
-        <v>1320</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20307,10 +20845,10 @@
       <c r="I17" s="28" t="n">
         <v>2078856</v>
       </c>
-      <c r="J17" s="104" t="n">
+      <c r="J17" s="109" t="n">
         <v>55.76</v>
       </c>
-      <c r="K17" s="116" t="n">
+      <c r="K17" s="121" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="45" t="n">
@@ -20323,7 +20861,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="21" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20355,7 +20893,7 @@
       <c r="I18" s="28" t="n">
         <v>6570004</v>
       </c>
-      <c r="J18" s="104" t="n">
+      <c r="J18" s="109" t="n">
         <v>43.71</v>
       </c>
       <c r="K18" s="45" t="n">
@@ -20371,7 +20909,7 @@
         <v>0</v>
       </c>
       <c r="O18" s="21" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20403,10 +20941,10 @@
       <c r="I19" s="28" t="n">
         <v>4445436</v>
       </c>
-      <c r="J19" s="104" t="n">
+      <c r="J19" s="109" t="n">
         <v>42.14</v>
       </c>
-      <c r="K19" s="117" t="n">
+      <c r="K19" s="122" t="n">
         <v>0.275</v>
       </c>
       <c r="L19" s="45" t="n">
@@ -20419,7 +20957,7 @@
         <v>0.048</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>1321</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20451,10 +20989,10 @@
       <c r="I20" s="28" t="n">
         <v>2229579</v>
       </c>
-      <c r="J20" s="104" t="n">
+      <c r="J20" s="109" t="n">
         <v>43.6</v>
       </c>
-      <c r="K20" s="116" t="n">
+      <c r="K20" s="121" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="45" t="n">
@@ -20467,7 +21005,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="21" t="s">
-        <v>1319</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20499,7 +21037,7 @@
       <c r="I21" s="28" t="n">
         <v>5504980</v>
       </c>
-      <c r="J21" s="104" t="n">
+      <c r="J21" s="109" t="n">
         <v>43.52</v>
       </c>
       <c r="K21" s="57" t="n">
@@ -20515,7 +21053,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="21" t="s">
-        <v>1320</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20547,10 +21085,10 @@
       <c r="I22" s="28" t="n">
         <v>4722403</v>
       </c>
-      <c r="J22" s="104" t="n">
+      <c r="J22" s="109" t="n">
         <v>49.88</v>
       </c>
-      <c r="K22" s="117" t="n">
+      <c r="K22" s="122" t="n">
         <v>0.068</v>
       </c>
       <c r="L22" s="45" t="n">
@@ -20563,7 +21101,7 @@
         <v>0.329</v>
       </c>
       <c r="O22" s="21" t="s">
-        <v>1322</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20595,10 +21133,10 @@
       <c r="I23" s="28" t="n">
         <v>4924931</v>
       </c>
-      <c r="J23" s="104" t="n">
+      <c r="J23" s="109" t="n">
         <v>47.68</v>
       </c>
-      <c r="K23" s="117" t="n">
+      <c r="K23" s="122" t="n">
         <v>0.069</v>
       </c>
       <c r="L23" s="45" t="n">
@@ -20611,7 +21149,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="21" t="s">
-        <v>1320</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20643,7 +21181,7 @@
       <c r="I24" s="28" t="n">
         <v>4740020</v>
       </c>
-      <c r="J24" s="104" t="n">
+      <c r="J24" s="109" t="n">
         <v>43.42</v>
       </c>
       <c r="K24" s="45" t="n">
@@ -20659,7 +21197,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="21" t="s">
-        <v>1320</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20691,10 +21229,10 @@
       <c r="I25" s="28" t="n">
         <v>4771577</v>
       </c>
-      <c r="J25" s="104" t="n">
+      <c r="J25" s="109" t="n">
         <v>51.68</v>
       </c>
-      <c r="K25" s="117" t="n">
+      <c r="K25" s="122" t="n">
         <v>0.177</v>
       </c>
       <c r="L25" s="45" t="n">
@@ -20707,7 +21245,7 @@
         <v>0.058</v>
       </c>
       <c r="O25" s="21" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20739,7 +21277,7 @@
       <c r="I26" s="28" t="n">
         <v>4933540</v>
       </c>
-      <c r="J26" s="104" t="n">
+      <c r="J26" s="109" t="n">
         <v>51.76</v>
       </c>
       <c r="K26" s="45" t="n">
@@ -20755,7 +21293,7 @@
         <v>0.276</v>
       </c>
       <c r="O26" s="21" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20787,10 +21325,10 @@
       <c r="I27" s="28" t="n">
         <v>4643058</v>
       </c>
-      <c r="J27" s="104" t="n">
+      <c r="J27" s="109" t="n">
         <v>66.28</v>
       </c>
-      <c r="K27" s="117" t="n">
+      <c r="K27" s="122" t="n">
         <v>0.083</v>
       </c>
       <c r="L27" s="45" t="n">
@@ -20803,7 +21341,7 @@
         <v>0.27</v>
       </c>
       <c r="O27" s="21" t="s">
-        <v>1323</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20835,10 +21373,10 @@
       <c r="I28" s="28" t="n">
         <v>2834084</v>
       </c>
-      <c r="J28" s="104" t="n">
+      <c r="J28" s="109" t="n">
         <v>77.81</v>
       </c>
-      <c r="K28" s="116" t="n">
+      <c r="K28" s="121" t="n">
         <v>-0.033</v>
       </c>
       <c r="L28" s="45" t="n">
@@ -20851,7 +21389,7 @@
         <v>0.349</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>1321</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20883,7 +21421,7 @@
       <c r="I29" s="28" t="n">
         <v>4558563</v>
       </c>
-      <c r="J29" s="104" t="n">
+      <c r="J29" s="109" t="n">
         <v>64.44</v>
       </c>
       <c r="K29" s="45" t="n">
@@ -20899,7 +21437,7 @@
         <v>0.321</v>
       </c>
       <c r="O29" s="21" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20931,10 +21469,10 @@
       <c r="I30" s="28" t="n">
         <v>2127665</v>
       </c>
-      <c r="J30" s="104" t="n">
+      <c r="J30" s="109" t="n">
         <v>48.52</v>
       </c>
-      <c r="K30" s="116" t="n">
+      <c r="K30" s="121" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="45" t="n">
@@ -20947,7 +21485,7 @@
         <v>0.176</v>
       </c>
       <c r="O30" s="21" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20979,10 +21517,10 @@
       <c r="I31" s="28" t="n">
         <v>3884721</v>
       </c>
-      <c r="J31" s="104" t="n">
+      <c r="J31" s="109" t="n">
         <v>54.76</v>
       </c>
-      <c r="K31" s="117" t="n">
+      <c r="K31" s="122" t="n">
         <v>0.186</v>
       </c>
       <c r="L31" s="45" t="n">
@@ -20995,7 +21533,7 @@
         <v>0.082</v>
       </c>
       <c r="O31" s="21" t="s">
-        <v>1320</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21027,10 +21565,10 @@
       <c r="I32" s="28" t="n">
         <v>1471112</v>
       </c>
-      <c r="J32" s="104" t="n">
+      <c r="J32" s="109" t="n">
         <v>49.67</v>
       </c>
-      <c r="K32" s="116" t="n">
+      <c r="K32" s="121" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="45" t="n">
@@ -21043,7 +21581,7 @@
         <v>0.103</v>
       </c>
       <c r="O32" s="20" t="s">
-        <v>1321</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21075,10 +21613,10 @@
       <c r="I33" s="28" t="n">
         <v>3774634</v>
       </c>
-      <c r="J33" s="104" t="n">
+      <c r="J33" s="109" t="n">
         <v>50.81</v>
       </c>
-      <c r="K33" s="117" t="n">
+      <c r="K33" s="122" t="n">
         <v>0.18</v>
       </c>
       <c r="L33" s="45" t="n">
@@ -21091,7 +21629,7 @@
         <v>0.023</v>
       </c>
       <c r="O33" s="21" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21123,7 +21661,7 @@
       <c r="I34" s="28" t="n">
         <v>4263083</v>
       </c>
-      <c r="J34" s="104" t="n">
+      <c r="J34" s="109" t="n">
         <v>110.06</v>
       </c>
       <c r="K34" s="57" t="n">
@@ -21139,7 +21677,7 @@
         <v>0.559</v>
       </c>
       <c r="O34" s="21" t="s">
-        <v>1323</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21171,7 +21709,7 @@
       <c r="I35" s="28" t="n">
         <v>3471225</v>
       </c>
-      <c r="J35" s="104" t="n">
+      <c r="J35" s="109" t="n">
         <v>47.35</v>
       </c>
       <c r="K35" s="57" t="n">
@@ -21187,7 +21725,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="21" t="s">
-        <v>1320</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21219,7 +21757,7 @@
       <c r="I36" s="28" t="n">
         <v>3512113</v>
       </c>
-      <c r="J36" s="104" t="n">
+      <c r="J36" s="109" t="n">
         <v>45.88</v>
       </c>
       <c r="K36" s="57" t="n">
@@ -21235,7 +21773,7 @@
         <v>0.115</v>
       </c>
       <c r="O36" s="21" t="s">
-        <v>1322</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21267,10 +21805,10 @@
       <c r="I37" s="28" t="n">
         <v>486162</v>
       </c>
-      <c r="J37" s="104" t="n">
+      <c r="J37" s="109" t="n">
         <v>33.35</v>
       </c>
-      <c r="K37" s="116" t="n">
+      <c r="K37" s="121" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="45" t="n">
@@ -21315,10 +21853,10 @@
       <c r="I38" s="28" t="n">
         <v>3406904</v>
       </c>
-      <c r="J38" s="104" t="n">
+      <c r="J38" s="109" t="n">
         <v>43.04</v>
       </c>
-      <c r="K38" s="117" t="n">
+      <c r="K38" s="122" t="n">
         <v>0.083</v>
       </c>
       <c r="L38" s="45" t="n">
@@ -21331,7 +21869,7 @@
         <v>0.167</v>
       </c>
       <c r="O38" s="21" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21363,7 +21901,7 @@
       <c r="I39" s="28" t="n">
         <v>3076219</v>
       </c>
-      <c r="J39" s="104" t="n">
+      <c r="J39" s="109" t="n">
         <v>69.64</v>
       </c>
       <c r="K39" s="57" t="n">
@@ -21379,7 +21917,7 @@
         <v>0.106</v>
       </c>
       <c r="O39" s="21" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21411,7 +21949,7 @@
       <c r="I40" s="28" t="n">
         <v>3314721</v>
       </c>
-      <c r="J40" s="104" t="n">
+      <c r="J40" s="109" t="n">
         <v>69.44</v>
       </c>
       <c r="K40" s="45" t="n">
@@ -21427,7 +21965,7 @@
         <v>0.373</v>
       </c>
       <c r="O40" s="21" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21459,7 +21997,7 @@
       <c r="I41" s="28" t="n">
         <v>2925368</v>
       </c>
-      <c r="J41" s="104" t="n">
+      <c r="J41" s="109" t="n">
         <v>45.21</v>
       </c>
       <c r="K41" s="57" t="n">
@@ -21475,7 +22013,7 @@
         <v>0</v>
       </c>
       <c r="O41" s="21" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21507,10 +22045,10 @@
       <c r="I42" s="28" t="n">
         <v>1114635</v>
       </c>
-      <c r="J42" s="104" t="n">
+      <c r="J42" s="109" t="n">
         <v>45.6</v>
       </c>
-      <c r="K42" s="116" t="n">
+      <c r="K42" s="121" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="45" t="n">
@@ -21523,7 +22061,7 @@
         <v>0.056</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>1321</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21555,10 +22093,10 @@
       <c r="I43" s="28" t="n">
         <v>2839338</v>
       </c>
-      <c r="J43" s="104" t="n">
+      <c r="J43" s="109" t="n">
         <v>50.86</v>
       </c>
-      <c r="K43" s="117" t="n">
+      <c r="K43" s="122" t="n">
         <v>0.082</v>
       </c>
       <c r="L43" s="45" t="n">
@@ -21571,7 +22109,7 @@
         <v>0.077</v>
       </c>
       <c r="O43" s="21" t="s">
-        <v>1323</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21603,10 +22141,10 @@
       <c r="I44" s="28" t="n">
         <v>2759664</v>
       </c>
-      <c r="J44" s="104" t="n">
+      <c r="J44" s="109" t="n">
         <v>56.84</v>
       </c>
-      <c r="K44" s="117" t="n">
+      <c r="K44" s="122" t="n">
         <v>0.327</v>
       </c>
       <c r="L44" s="45" t="n">
@@ -21619,7 +22157,7 @@
         <v>0.066</v>
       </c>
       <c r="O44" s="20" t="s">
-        <v>1321</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21651,7 +22189,7 @@
       <c r="I45" s="28" t="n">
         <v>2940822</v>
       </c>
-      <c r="J45" s="104" t="n">
+      <c r="J45" s="109" t="n">
         <v>74.93</v>
       </c>
       <c r="K45" s="45" t="n">
@@ -21667,7 +22205,7 @@
         <v>0.392</v>
       </c>
       <c r="O45" s="20" t="s">
-        <v>1321</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21699,7 +22237,7 @@
       <c r="I46" s="28" t="n">
         <v>2694118</v>
       </c>
-      <c r="J46" s="104" t="n">
+      <c r="J46" s="109" t="n">
         <v>53.94</v>
       </c>
       <c r="K46" s="57" t="n">
@@ -21715,7 +22253,7 @@
         <v>0.236</v>
       </c>
       <c r="O46" s="21" t="s">
-        <v>1320</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21747,7 +22285,7 @@
       <c r="I47" s="28" t="n">
         <v>2650896</v>
       </c>
-      <c r="J47" s="104" t="n">
+      <c r="J47" s="109" t="n">
         <v>48.6</v>
       </c>
       <c r="K47" s="45" t="n">
@@ -21763,7 +22301,7 @@
         <v>0.184</v>
       </c>
       <c r="O47" s="21" t="s">
-        <v>1323</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21795,10 +22333,10 @@
       <c r="I48" s="28" t="n">
         <v>2153145</v>
       </c>
-      <c r="J48" s="104" t="n">
+      <c r="J48" s="109" t="n">
         <v>57.15</v>
       </c>
-      <c r="K48" s="117" t="n">
+      <c r="K48" s="122" t="n">
         <v>0.064</v>
       </c>
       <c r="L48" s="45" t="n">
@@ -21811,7 +22349,7 @@
         <v>0</v>
       </c>
       <c r="O48" s="21" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21843,10 +22381,10 @@
       <c r="I49" s="28" t="n">
         <v>2133587</v>
       </c>
-      <c r="J49" s="104" t="n">
+      <c r="J49" s="109" t="n">
         <v>62.82</v>
       </c>
-      <c r="K49" s="117" t="n">
+      <c r="K49" s="122" t="n">
         <v>0.256</v>
       </c>
       <c r="L49" s="45" t="n">
@@ -21859,7 +22397,7 @@
         <v>0.201</v>
       </c>
       <c r="O49" s="21" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21891,7 +22429,7 @@
       <c r="I50" s="28" t="n">
         <v>1912969</v>
       </c>
-      <c r="J50" s="104" t="n">
+      <c r="J50" s="109" t="n">
         <v>52.46</v>
       </c>
       <c r="K50" s="57" t="n">
@@ -21907,7 +22445,7 @@
         <v>0</v>
       </c>
       <c r="O50" s="21" t="s">
-        <v>1320</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21939,10 +22477,10 @@
       <c r="I51" s="28" t="n">
         <v>568922</v>
       </c>
-      <c r="J51" s="104" t="n">
+      <c r="J51" s="109" t="n">
         <v>50.9</v>
       </c>
-      <c r="K51" s="116" t="n">
+      <c r="K51" s="121" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="45" t="n">
@@ -21987,10 +22525,10 @@
       <c r="I52" s="28" t="n">
         <v>1672588</v>
       </c>
-      <c r="J52" s="104" t="n">
+      <c r="J52" s="109" t="n">
         <v>45.95</v>
       </c>
-      <c r="K52" s="117" t="n">
+      <c r="K52" s="122" t="n">
         <v>0.137</v>
       </c>
       <c r="L52" s="45" t="n">
@@ -22003,7 +22541,7 @@
         <v>0.017</v>
       </c>
       <c r="O52" s="21" t="s">
-        <v>1322</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22035,7 +22573,7 @@
       <c r="I53" s="28" t="n">
         <v>1601535</v>
       </c>
-      <c r="J53" s="104" t="n">
+      <c r="J53" s="109" t="n">
         <v>55.38</v>
       </c>
       <c r="K53" s="45" t="n">
@@ -22051,7 +22589,7 @@
         <v>0.292</v>
       </c>
       <c r="O53" s="21" t="s">
-        <v>1322</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22083,7 +22621,7 @@
       <c r="I54" s="28" t="n">
         <v>1431054</v>
       </c>
-      <c r="J54" s="104" t="n">
+      <c r="J54" s="109" t="n">
         <v>53.68</v>
       </c>
       <c r="K54" s="45" t="n">
@@ -22099,7 +22637,7 @@
         <v>0.077</v>
       </c>
       <c r="O54" s="21" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22131,10 +22669,10 @@
       <c r="I55" s="28" t="n">
         <v>1262094</v>
       </c>
-      <c r="J55" s="104" t="n">
+      <c r="J55" s="109" t="n">
         <v>53.3</v>
       </c>
-      <c r="K55" s="117" t="n">
+      <c r="K55" s="122" t="n">
         <v>0.188</v>
       </c>
       <c r="L55" s="45" t="n">
@@ -22147,7 +22685,7 @@
         <v>0.18</v>
       </c>
       <c r="O55" s="20" t="s">
-        <v>1321</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22179,10 +22717,10 @@
       <c r="I56" s="28" t="n">
         <v>1204453</v>
       </c>
-      <c r="J56" s="104" t="n">
+      <c r="J56" s="109" t="n">
         <v>34.88</v>
       </c>
-      <c r="K56" s="117" t="n">
+      <c r="K56" s="122" t="n">
         <v>0.06</v>
       </c>
       <c r="L56" s="45" t="n">
@@ -22195,7 +22733,7 @@
         <v>0.194</v>
       </c>
       <c r="O56" s="21" t="s">
-        <v>1322</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22227,10 +22765,10 @@
       <c r="I57" s="28" t="n">
         <v>206212</v>
       </c>
-      <c r="J57" s="104" t="n">
+      <c r="J57" s="109" t="n">
         <v>57.08</v>
       </c>
-      <c r="K57" s="116" t="n">
+      <c r="K57" s="121" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="45" t="n">
@@ -22243,7 +22781,7 @@
         <v>0.249</v>
       </c>
       <c r="O57" s="20" t="s">
-        <v>1321</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22275,10 +22813,10 @@
       <c r="I58" s="28" t="n">
         <v>21693</v>
       </c>
-      <c r="J58" s="104" t="n">
+      <c r="J58" s="109" t="n">
         <v>49.96</v>
       </c>
-      <c r="K58" s="116" t="n">
+      <c r="K58" s="121" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="45" t="n">
@@ -22291,51 +22829,51 @@
         <v>0.167</v>
       </c>
       <c r="O58" s="20" t="s">
-        <v>1321</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="67" t="s">
-        <v>1324</v>
+        <v>1365</v>
       </c>
       <c r="B59" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="F59" s="118" t="n">
+      <c r="F59" s="123" t="n">
         <f aca="false">SUM(F4:F58)</f>
         <v>502415662</v>
       </c>
-      <c r="G59" s="118" t="n">
+      <c r="G59" s="123" t="n">
         <f aca="false">SUM(G4:G58)</f>
         <v>1271395370.83428</v>
       </c>
-      <c r="H59" s="118" t="n">
+      <c r="H59" s="123" t="n">
         <f aca="false">SUM(H4:H58)</f>
         <v>8824895</v>
       </c>
-      <c r="I59" s="118" t="n">
+      <c r="I59" s="123" t="n">
         <f aca="false">SUM(I4:I58)</f>
         <v>219475297</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="119" t="s">
-        <v>1325</v>
-      </c>
-      <c r="B61" s="119"/>
-      <c r="C61" s="119"/>
-      <c r="D61" s="119"/>
-      <c r="E61" s="119"/>
-      <c r="F61" s="119"/>
-      <c r="G61" s="119"/>
-      <c r="H61" s="119"/>
-      <c r="I61" s="119"/>
-      <c r="J61" s="119"/>
-      <c r="K61" s="119"/>
-      <c r="L61" s="119"/>
-      <c r="M61" s="119"/>
-      <c r="N61" s="119"/>
-      <c r="O61" s="119"/>
+      <c r="A61" s="124" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B61" s="124"/>
+      <c r="C61" s="124"/>
+      <c r="D61" s="124"/>
+      <c r="E61" s="124"/>
+      <c r="F61" s="124"/>
+      <c r="G61" s="124"/>
+      <c r="H61" s="124"/>
+      <c r="I61" s="124"/>
+      <c r="J61" s="124"/>
+      <c r="K61" s="124"/>
+      <c r="L61" s="124"/>
+      <c r="M61" s="124"/>
+      <c r="N61" s="124"/>
+      <c r="O61" s="124"/>
     </row>
   </sheetData>
   <mergeCells count="3">
